--- a/jogos_2025-09-30.xlsx
+++ b/jogos_2025-09-30.xlsx
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Sogdiana</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Sogdiana</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,13 +1572,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>24</v>
+        <v>1.5</v>
       </c>
       <c r="M9" t="n">
-        <v>8.5</v>
+        <v>4.4</v>
       </c>
       <c r="N9" t="n">
-        <v>1.12</v>
+        <v>6.2</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1611,16 +1611,16 @@
         <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.3</v>
+        <v>1.7</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.4</v>
+        <v>2.15</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,13 +1701,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.5</v>
+        <v>24</v>
       </c>
       <c r="M10" t="n">
-        <v>4.4</v>
+        <v>8.5</v>
       </c>
       <c r="N10" t="n">
-        <v>6.2</v>
+        <v>1.12</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1740,16 +1740,16 @@
         <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.7</v>
+        <v>1.3</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.15</v>
+        <v>3.4</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -1923,22 +1923,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Hansa Rostock</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2052,22 +2052,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Erzgebirge Aue</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Havelse</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Waldhof Mannheim</t>
+          <t>Wehen Wiesbaden</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>Saarbrucken</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Wehen Wiesbaden</t>
+          <t>MSV Duisburg</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Saarbrucken</t>
+          <t>Havelse</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>MSV Duisburg</t>
+          <t>Waldhof Mannheim</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>Hansa Rostock</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Erzgebirge Aue</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Mantova</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mantova</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4116,7 +4116,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4148,65 +4148,65 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L29" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>3.19</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="T29" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="U29" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="V29" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W29" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="X29" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="Z29" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
@@ -4219,10 +4219,10 @@
         </is>
       </c>
       <c r="AG29" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AI29" t="n">
         <v>0</v>
@@ -4245,7 +4245,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4277,65 +4277,65 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>4.07</v>
+        <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>5.62</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="T30" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="U30" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="V30" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="W30" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="X30" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="Z30" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AC30" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
@@ -4348,10 +4348,10 @@
         </is>
       </c>
       <c r="AG30" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AH30" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AI30" t="n">
         <v>0</v>
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4632,7 +4632,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4664,65 +4664,65 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="O33" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S33" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="T33" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U33" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="V33" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W33" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="X33" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="Y33" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="Z33" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AA33" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AB33" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AC33" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AD33" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AE33" t="inlineStr">
         <is>
@@ -4735,10 +4735,10 @@
         </is>
       </c>
       <c r="AG33" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AH33" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AI33" t="n">
         <v>0</v>
@@ -4761,7 +4761,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4793,65 +4793,65 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>4.07</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>5.62</v>
       </c>
       <c r="O34" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S34" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="T34" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="U34" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="V34" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="W34" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X34" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="Y34" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Z34" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA34" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AB34" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AC34" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD34" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AE34" t="inlineStr">
         <is>
@@ -4864,10 +4864,10 @@
         </is>
       </c>
       <c r="AG34" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AH34" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AI34" t="n">
         <v>0</v>
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5277,7 +5277,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,13 +5313,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5352,10 +5352,10 @@
         <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z38" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AA38" t="n">
         <v>0</v>
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,13 +5442,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>3.65</v>
+        <v>19</v>
       </c>
       <c r="M39" t="n">
-        <v>3.65</v>
+        <v>7.6</v>
       </c>
       <c r="N39" t="n">
-        <v>1.98</v>
+        <v>1.15</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5481,16 +5481,16 @@
         <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z39" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AA39" t="n">
-        <v>2.25</v>
+        <v>1.83</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.65</v>
+        <v>1.97</v>
       </c>
       <c r="AC39" t="n">
         <v>0</v>
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,13 +5571,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>1.5</v>
+        <v>9.5</v>
       </c>
       <c r="M40" t="n">
-        <v>3.95</v>
+        <v>5.1</v>
       </c>
       <c r="N40" t="n">
-        <v>7.5</v>
+        <v>1.33</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5610,16 +5610,16 @@
         <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.63</v>
+        <v>1.44</v>
       </c>
       <c r="Z40" t="n">
-        <v>2.25</v>
+        <v>2.75</v>
       </c>
       <c r="AA40" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB40" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Olympique Marseille</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,13 +5700,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1.7</v>
+        <v>1.35</v>
       </c>
       <c r="M41" t="n">
-        <v>3.85</v>
+        <v>4.7</v>
       </c>
       <c r="N41" t="n">
-        <v>4.9</v>
+        <v>10.5</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5739,10 +5739,10 @@
         <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="Z41" t="n">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
       <c r="AA41" t="n">
         <v>0</v>
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,13 +5829,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>1.75</v>
+        <v>3.65</v>
       </c>
       <c r="M42" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="N42" t="n">
-        <v>5.1</v>
+        <v>1.98</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5868,16 +5868,16 @@
         <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="Z42" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB42" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC42" t="n">
         <v>0</v>
@@ -5922,7 +5922,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5958,13 +5958,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="M43" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5997,10 +5997,10 @@
         <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Z43" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AA43" t="n">
         <v>0</v>
@@ -6061,12 +6061,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6087,13 +6087,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>9.5</v>
+        <v>1.5</v>
       </c>
       <c r="M44" t="n">
-        <v>5.1</v>
+        <v>3.95</v>
       </c>
       <c r="N44" t="n">
-        <v>1.33</v>
+        <v>7.5</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -6126,16 +6126,16 @@
         <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.44</v>
+        <v>1.63</v>
       </c>
       <c r="Z44" t="n">
-        <v>2.75</v>
+        <v>2.25</v>
       </c>
       <c r="AA44" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC44" t="n">
         <v>0</v>
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Olympique Marseille</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6216,13 +6216,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>19</v>
+        <v>1.7</v>
       </c>
       <c r="M45" t="n">
-        <v>7.6</v>
+        <v>3.85</v>
       </c>
       <c r="N45" t="n">
-        <v>1.15</v>
+        <v>4.9</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -6255,16 +6255,16 @@
         <v>0</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.44</v>
+        <v>1.63</v>
       </c>
       <c r="Z45" t="n">
-        <v>2.75</v>
+        <v>2.25</v>
       </c>
       <c r="AA45" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AC45" t="n">
         <v>0</v>

--- a/jogos_2025-09-30.xlsx
+++ b/jogos_2025-09-30.xlsx
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sogdiana</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Sogdiana</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1278,7 +1278,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Police</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Ulinzi Stars</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Police</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ulinzi Stars</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,13 +1572,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.5</v>
+        <v>24</v>
       </c>
       <c r="M9" t="n">
-        <v>4.4</v>
+        <v>8.5</v>
       </c>
       <c r="N9" t="n">
-        <v>6.2</v>
+        <v>1.12</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1611,16 +1611,16 @@
         <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.7</v>
+        <v>1.3</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.15</v>
+        <v>3.4</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,13 +1701,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>24</v>
+        <v>1.5</v>
       </c>
       <c r="M10" t="n">
-        <v>8.5</v>
+        <v>4.4</v>
       </c>
       <c r="N10" t="n">
-        <v>1.12</v>
+        <v>6.2</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1740,16 +1740,16 @@
         <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.3</v>
+        <v>1.7</v>
       </c>
       <c r="Z10" t="n">
-        <v>3.4</v>
+        <v>2.15</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>Havelse</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Erzgebirge Aue</t>
+          <t>Waldhof Mannheim</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>Hansa Rostock</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Wehen Wiesbaden</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Saarbrucken</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>MSV Duisburg</t>
+          <t>Erzgebirge Aue</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Havelse</t>
+          <t>Saarbrucken</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Waldhof Mannheim</t>
+          <t>MSV Duisburg</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Hansa Rostock</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>Wehen Wiesbaden</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>Mantova</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mantova</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4116,7 +4116,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4148,65 +4148,65 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="O29" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S29" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="T29" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="V29" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W29" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="X29" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="Z29" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AC29" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AD29" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
@@ -4219,10 +4219,10 @@
         </is>
       </c>
       <c r="AG29" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AH29" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AI29" t="n">
         <v>0</v>
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4632,7 +4632,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4664,65 +4664,65 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L33" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>3.19</v>
+        <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="S33" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="T33" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="U33" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="V33" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W33" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="X33" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="Z33" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AC33" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AE33" t="inlineStr">
         <is>
@@ -4735,10 +4735,10 @@
         </is>
       </c>
       <c r="AG33" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AI33" t="n">
         <v>0</v>
@@ -4761,7 +4761,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4793,65 +4793,65 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>4.07</v>
+        <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>5.62</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="T34" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="U34" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="V34" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="W34" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="X34" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="Z34" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AC34" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD34" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AE34" t="inlineStr">
         <is>
@@ -4864,10 +4864,10 @@
         </is>
       </c>
       <c r="AG34" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AH34" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AI34" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4922,65 +4922,65 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>4.07</v>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>5.62</v>
       </c>
       <c r="O35" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S35" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="T35" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="V35" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="W35" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X35" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="Y35" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Z35" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA35" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AB35" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AC35" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD35" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AE35" t="inlineStr">
         <is>
@@ -4993,10 +4993,10 @@
         </is>
       </c>
       <c r="AG35" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AH35" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AI35" t="n">
         <v>0</v>
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5277,7 +5277,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,13 +5313,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5352,10 +5352,10 @@
         <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Z38" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AA38" t="n">
         <v>0</v>
@@ -5406,7 +5406,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,13 +5442,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5481,16 +5481,16 @@
         <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="Z39" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AC39" t="n">
         <v>0</v>
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,13 +5700,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1.35</v>
+        <v>3.65</v>
       </c>
       <c r="M41" t="n">
-        <v>4.7</v>
+        <v>3.65</v>
       </c>
       <c r="N41" t="n">
-        <v>10.5</v>
+        <v>1.98</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5739,16 +5739,16 @@
         <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z41" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB41" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC41" t="n">
         <v>0</v>
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,13 +5829,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>3.65</v>
+        <v>19</v>
       </c>
       <c r="M42" t="n">
-        <v>3.65</v>
+        <v>7.6</v>
       </c>
       <c r="N42" t="n">
-        <v>1.98</v>
+        <v>1.15</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5868,16 +5868,16 @@
         <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z42" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AA42" t="n">
-        <v>2.25</v>
+        <v>1.83</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.65</v>
+        <v>1.97</v>
       </c>
       <c r="AC42" t="n">
         <v>0</v>
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5958,13 +5958,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>1.75</v>
+        <v>1.35</v>
       </c>
       <c r="M43" t="n">
-        <v>3.55</v>
+        <v>4.7</v>
       </c>
       <c r="N43" t="n">
-        <v>5.1</v>
+        <v>10.5</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5997,10 +5997,10 @@
         <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.68</v>
+        <v>1.6</v>
       </c>
       <c r="Z43" t="n">
-        <v>2.18</v>
+        <v>2.35</v>
       </c>
       <c r="AA43" t="n">
         <v>0</v>

--- a/jogos_2025-09-30.xlsx
+++ b/jogos_2025-09-30.xlsx
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,13 +1572,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>24</v>
+        <v>1.5</v>
       </c>
       <c r="M9" t="n">
-        <v>8.5</v>
+        <v>4.4</v>
       </c>
       <c r="N9" t="n">
-        <v>1.12</v>
+        <v>6.2</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1611,16 +1611,16 @@
         <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.3</v>
+        <v>1.7</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.4</v>
+        <v>2.15</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,13 +1701,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.5</v>
+        <v>24</v>
       </c>
       <c r="M10" t="n">
-        <v>4.4</v>
+        <v>8.5</v>
       </c>
       <c r="N10" t="n">
-        <v>6.2</v>
+        <v>1.12</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1740,16 +1740,16 @@
         <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.7</v>
+        <v>1.3</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.15</v>
+        <v>3.4</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -1794,22 +1794,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Wehen Wiesbaden</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1923,22 +1923,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Hansa Rostock</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2052,22 +2052,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Havelse</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Waldhof Mannheim</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Hansa Rostock</t>
+          <t>Saarbrucken</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>MSV Duisburg</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Saarbrucken</t>
+          <t>Havelse</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>MSV Duisburg</t>
+          <t>Waldhof Mannheim</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2568,22 +2568,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Wehen Wiesbaden</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Calcio Padova</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mantova</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Calcio Padova</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Mantova</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4116,7 +4116,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4148,65 +4148,65 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L29" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>3.19</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="T29" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="U29" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="V29" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W29" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="X29" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="Z29" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
@@ -4219,10 +4219,10 @@
         </is>
       </c>
       <c r="AG29" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AI29" t="n">
         <v>0</v>
@@ -4245,7 +4245,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4277,65 +4277,65 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>4.07</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>5.62</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S30" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Z30" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD30" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
@@ -4348,10 +4348,10 @@
         </is>
       </c>
       <c r="AG30" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AH30" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AI30" t="n">
         <v>0</v>
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4632,7 +4632,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4664,65 +4664,65 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="O33" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S33" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="T33" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U33" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="V33" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W33" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="X33" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="Y33" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="Z33" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AA33" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AB33" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AC33" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AD33" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AE33" t="inlineStr">
         <is>
@@ -4735,10 +4735,10 @@
         </is>
       </c>
       <c r="AG33" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AH33" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AI33" t="n">
         <v>0</v>
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4922,65 +4922,65 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L35" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>4.07</v>
+        <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v>5.62</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="T35" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="U35" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="V35" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="W35" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="X35" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="Z35" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AC35" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD35" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AE35" t="inlineStr">
         <is>
@@ -4993,10 +4993,10 @@
         </is>
       </c>
       <c r="AG35" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AH35" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AI35" t="n">
         <v>0</v>
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,13 +5313,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>1.75</v>
+        <v>1.35</v>
       </c>
       <c r="M38" t="n">
-        <v>3.55</v>
+        <v>4.7</v>
       </c>
       <c r="N38" t="n">
-        <v>5.1</v>
+        <v>10.5</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5352,10 +5352,10 @@
         <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.68</v>
+        <v>1.6</v>
       </c>
       <c r="Z38" t="n">
-        <v>2.18</v>
+        <v>2.35</v>
       </c>
       <c r="AA38" t="n">
         <v>0</v>
@@ -5406,7 +5406,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,13 +5442,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5481,16 +5481,16 @@
         <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z39" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AA39" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB39" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC39" t="n">
         <v>0</v>
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Olympique Marseille</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,13 +5571,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>9.5</v>
+        <v>1.7</v>
       </c>
       <c r="M40" t="n">
-        <v>5.1</v>
+        <v>3.85</v>
       </c>
       <c r="N40" t="n">
-        <v>1.33</v>
+        <v>4.9</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5610,16 +5610,16 @@
         <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.44</v>
+        <v>1.63</v>
       </c>
       <c r="Z40" t="n">
-        <v>2.75</v>
+        <v>2.25</v>
       </c>
       <c r="AA40" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,13 +5700,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>3.65</v>
+        <v>1.75</v>
       </c>
       <c r="M41" t="n">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="N41" t="n">
-        <v>1.98</v>
+        <v>5.1</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5739,16 +5739,16 @@
         <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Z41" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AA41" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC41" t="n">
         <v>0</v>
@@ -5793,7 +5793,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,13 +5829,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5868,16 +5868,16 @@
         <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="Z42" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AC42" t="n">
         <v>0</v>
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5958,13 +5958,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>1.35</v>
+        <v>1.5</v>
       </c>
       <c r="M43" t="n">
-        <v>4.7</v>
+        <v>3.95</v>
       </c>
       <c r="N43" t="n">
-        <v>10.5</v>
+        <v>7.5</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5997,10 +5997,10 @@
         <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="Z43" t="n">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="AA43" t="n">
         <v>0</v>
@@ -6061,12 +6061,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6087,13 +6087,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>1.5</v>
+        <v>19</v>
       </c>
       <c r="M44" t="n">
-        <v>3.95</v>
+        <v>7.6</v>
       </c>
       <c r="N44" t="n">
-        <v>7.5</v>
+        <v>1.15</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -6126,16 +6126,16 @@
         <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.63</v>
+        <v>1.44</v>
       </c>
       <c r="Z44" t="n">
-        <v>2.25</v>
+        <v>2.75</v>
       </c>
       <c r="AA44" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB44" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AC44" t="n">
         <v>0</v>
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Olympique Marseille</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6216,13 +6216,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>1.7</v>
+        <v>3.65</v>
       </c>
       <c r="M45" t="n">
-        <v>3.85</v>
+        <v>3.65</v>
       </c>
       <c r="N45" t="n">
-        <v>4.9</v>
+        <v>1.98</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -6255,16 +6255,16 @@
         <v>0</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Z45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA45" t="n">
         <v>2.25</v>
       </c>
-      <c r="AA45" t="n">
-        <v>0</v>
-      </c>
       <c r="AB45" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC45" t="n">
         <v>0</v>

--- a/jogos_2025-09-30.xlsx
+++ b/jogos_2025-09-30.xlsx
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Sogdiana</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Sogdiana</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1794,22 +1794,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Wehen Wiesbaden</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1923,22 +1923,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Hansa Rostock</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2052,22 +2052,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Wehen Wiesbaden</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Saarbrucken</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>MSV Duisburg</t>
+          <t>Erzgebirge Aue</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>Hansa Rostock</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Erzgebirge Aue</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2568,22 +2568,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Saarbrucken</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>MSV Duisburg</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Calcio Padova</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Calcio Padova</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>Mantova</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mantova</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4245,7 +4245,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4277,65 +4277,65 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>4.07</v>
+        <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>5.62</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="T30" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="U30" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="V30" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="W30" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="X30" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="Z30" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AC30" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
@@ -4348,10 +4348,10 @@
         </is>
       </c>
       <c r="AG30" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AH30" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AI30" t="n">
         <v>0</v>
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,61 +4668,61 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>3</v>
+        <v>1.47</v>
       </c>
       <c r="M33" t="n">
-        <v>3.19</v>
+        <v>4.07</v>
       </c>
       <c r="N33" t="n">
-        <v>2.31</v>
+        <v>5.62</v>
       </c>
       <c r="O33" t="n">
-        <v>3.6</v>
+        <v>1.96</v>
       </c>
       <c r="P33" t="n">
-        <v>2.05</v>
+        <v>2.38</v>
       </c>
       <c r="Q33" t="n">
-        <v>2.92</v>
+        <v>5.5</v>
       </c>
       <c r="R33" t="n">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="S33" t="n">
-        <v>2.75</v>
+        <v>3.08</v>
       </c>
       <c r="T33" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="V33" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W33" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="X33" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AA33" t="n">
         <v>2.8</v>
       </c>
-      <c r="U33" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="V33" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W33" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="X33" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="Y33" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="Z33" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AA33" t="n">
-        <v>3.55</v>
-      </c>
       <c r="AB33" t="n">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AC33" t="n">
-        <v>1.76</v>
+        <v>1.85</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AE33" t="inlineStr">
         <is>
@@ -4735,10 +4735,10 @@
         </is>
       </c>
       <c r="AG33" t="n">
-        <v>1.62</v>
+        <v>1.15</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.37</v>
+        <v>2.6</v>
       </c>
       <c r="AI33" t="n">
         <v>0</v>
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5019,7 +5019,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5051,65 +5051,65 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="O36" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S36" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="T36" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U36" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="V36" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W36" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="X36" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="Y36" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="Z36" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AA36" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AB36" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AC36" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AD36" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AE36" t="inlineStr">
         <is>
@@ -5122,10 +5122,10 @@
         </is>
       </c>
       <c r="AG36" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AH36" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AI36" t="n">
         <v>0</v>
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,13 +5313,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>1.35</v>
+        <v>9.5</v>
       </c>
       <c r="M38" t="n">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="N38" t="n">
-        <v>10.5</v>
+        <v>1.33</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5352,16 +5352,16 @@
         <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.6</v>
+        <v>1.44</v>
       </c>
       <c r="Z38" t="n">
-        <v>2.35</v>
+        <v>2.75</v>
       </c>
       <c r="AA38" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB38" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC38" t="n">
         <v>0</v>
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Olympique Marseille</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,13 +5442,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>9.5</v>
+        <v>1.7</v>
       </c>
       <c r="M39" t="n">
-        <v>5.1</v>
+        <v>3.85</v>
       </c>
       <c r="N39" t="n">
-        <v>1.33</v>
+        <v>4.9</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5481,16 +5481,16 @@
         <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.44</v>
+        <v>1.63</v>
       </c>
       <c r="Z39" t="n">
-        <v>2.75</v>
+        <v>2.25</v>
       </c>
       <c r="AA39" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC39" t="n">
         <v>0</v>
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Olympique Marseille</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,13 +5571,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="M40" t="n">
-        <v>3.85</v>
+        <v>3.55</v>
       </c>
       <c r="N40" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5610,10 +5610,10 @@
         <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.63</v>
+        <v>1.68</v>
       </c>
       <c r="Z40" t="n">
-        <v>2.25</v>
+        <v>2.18</v>
       </c>
       <c r="AA40" t="n">
         <v>0</v>
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,13 +5700,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1.75</v>
+        <v>1.35</v>
       </c>
       <c r="M41" t="n">
-        <v>3.55</v>
+        <v>4.7</v>
       </c>
       <c r="N41" t="n">
-        <v>5.1</v>
+        <v>10.5</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5739,10 +5739,10 @@
         <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.68</v>
+        <v>1.6</v>
       </c>
       <c r="Z41" t="n">
-        <v>2.18</v>
+        <v>2.35</v>
       </c>
       <c r="AA41" t="n">
         <v>0</v>
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5958,13 +5958,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>1.5</v>
+        <v>3.65</v>
       </c>
       <c r="M43" t="n">
-        <v>3.95</v>
+        <v>3.65</v>
       </c>
       <c r="N43" t="n">
-        <v>7.5</v>
+        <v>1.98</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5997,16 +5997,16 @@
         <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Z43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA43" t="n">
         <v>2.25</v>
       </c>
-      <c r="AA43" t="n">
-        <v>0</v>
-      </c>
       <c r="AB43" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC43" t="n">
         <v>0</v>
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6216,13 +6216,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>3.65</v>
+        <v>1.5</v>
       </c>
       <c r="M45" t="n">
-        <v>3.65</v>
+        <v>3.95</v>
       </c>
       <c r="N45" t="n">
-        <v>1.98</v>
+        <v>7.5</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -6255,16 +6255,16 @@
         <v>0</v>
       </c>
       <c r="Y45" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Z45" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA45" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC45" t="n">
         <v>0</v>

--- a/jogos_2025-09-30.xlsx
+++ b/jogos_2025-09-30.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK48"/>
+  <dimension ref="A1:AK51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sogdiana</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Sogdiana</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1531,12 +1531,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Carrarese</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,13 +1572,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1611,10 +1611,10 @@
         <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
         <v>0</v>
@@ -1651,7 +1651,7 @@
         <v>0</v>
       </c>
       <c r="AK9" s="3" t="n">
-        <v>45930.57291666666</v>
+        <v>45930.5</v>
       </c>
     </row>
     <row r="10">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Pescara</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,13 +1701,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1740,16 +1740,16 @@
         <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -1780,7 +1780,7 @@
         <v>0</v>
       </c>
       <c r="AK10" s="3" t="n">
-        <v>45930.57291666666</v>
+        <v>45930.5</v>
       </c>
     </row>
     <row r="11">
@@ -1789,27 +1789,27 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1909,7 +1909,7 @@
         <v>0</v>
       </c>
       <c r="AK11" s="3" t="n">
-        <v>45930.58333333334</v>
+        <v>45930.5</v>
       </c>
     </row>
     <row r="12">
@@ -1918,27 +1918,27 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,13 +1959,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1998,10 +1998,10 @@
         <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AA12" t="n">
         <v>0</v>
@@ -2038,7 +2038,7 @@
         <v>0</v>
       </c>
       <c r="AK12" s="3" t="n">
-        <v>45930.58333333334</v>
+        <v>45930.57291666666</v>
       </c>
     </row>
     <row r="13">
@@ -2047,12 +2047,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Wehen Wiesbaden</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,13 +2088,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2127,16 +2127,16 @@
         <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2167,7 +2167,7 @@
         <v>0</v>
       </c>
       <c r="AK13" s="3" t="n">
-        <v>45930.58333333334</v>
+        <v>45930.57291666666</v>
       </c>
     </row>
     <row r="14">
@@ -2181,22 +2181,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Erzgebirge Aue</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Hansa Rostock</t>
+          <t>Saarbrucken</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>MSV Duisburg</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2439,22 +2439,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Havelse</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Waldhof Mannheim</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Saarbrucken</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>MSV Duisburg</t>
+          <t>Wehen Wiesbaden</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2692,12 +2692,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Hansa Rostock</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2812,7 +2812,7 @@
         <v>0</v>
       </c>
       <c r="AK18" s="3" t="n">
-        <v>45930.625</v>
+        <v>45930.58333333334</v>
       </c>
     </row>
     <row r="19">
@@ -2821,12 +2821,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Havelse</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Waldhof Mannheim</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2941,7 +2941,7 @@
         <v>0</v>
       </c>
       <c r="AK19" s="3" t="n">
-        <v>45930.625</v>
+        <v>45930.58333333334</v>
       </c>
     </row>
     <row r="20">
@@ -2950,12 +2950,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Erzgebirge Aue</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3070,7 +3070,7 @@
         <v>0</v>
       </c>
       <c r="AK20" s="3" t="n">
-        <v>45930.625</v>
+        <v>45930.58333333334</v>
       </c>
     </row>
     <row r="21">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3337,12 +3337,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Calcio Padova</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3457,7 +3457,7 @@
         <v>0</v>
       </c>
       <c r="AK23" s="3" t="n">
-        <v>45930.64583333334</v>
+        <v>45930.625</v>
       </c>
     </row>
     <row r="24">
@@ -3466,12 +3466,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3586,7 +3586,7 @@
         <v>0</v>
       </c>
       <c r="AK24" s="3" t="n">
-        <v>45930.64583333334</v>
+        <v>45930.625</v>
       </c>
     </row>
     <row r="25">
@@ -3595,12 +3595,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3715,7 +3715,7 @@
         <v>0</v>
       </c>
       <c r="AK25" s="3" t="n">
-        <v>45930.64583333334</v>
+        <v>45930.625</v>
       </c>
     </row>
     <row r="26">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mantova</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,13 +3765,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3804,10 +3804,10 @@
         <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AA26" t="n">
         <v>0</v>
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Mantova</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,13 +4023,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -4062,10 +4062,10 @@
         <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Z28" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AA28" t="n">
         <v>0</v>
@@ -4111,12 +4111,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,13 +4152,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -4191,10 +4191,10 @@
         <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Z29" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AA29" t="n">
         <v>0</v>
@@ -4231,7 +4231,7 @@
         <v>0</v>
       </c>
       <c r="AK29" s="3" t="n">
-        <v>45930.65625</v>
+        <v>45930.64583333334</v>
       </c>
     </row>
     <row r="30">
@@ -4240,12 +4240,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Calcio Padova</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4360,7 +4360,7 @@
         <v>0</v>
       </c>
       <c r="AK30" s="3" t="n">
-        <v>45930.65625</v>
+        <v>45930.64583333334</v>
       </c>
     </row>
     <row r="31">
@@ -4369,12 +4369,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,13 +4410,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4449,10 +4449,10 @@
         <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="Z31" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AA31" t="n">
         <v>0</v>
@@ -4489,7 +4489,7 @@
         <v>0</v>
       </c>
       <c r="AK31" s="3" t="n">
-        <v>45930.65625</v>
+        <v>45930.64583333334</v>
       </c>
     </row>
     <row r="32">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4632,7 +4632,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4664,65 +4664,65 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>4.07</v>
+        <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>5.62</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="S33" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="T33" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="U33" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="V33" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="W33" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="X33" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="Z33" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AC33" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AE33" t="inlineStr">
         <is>
@@ -4735,10 +4735,10 @@
         </is>
       </c>
       <c r="AG33" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AH33" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AI33" t="n">
         <v>0</v>
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,61 +5055,61 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>3</v>
+        <v>1.47</v>
       </c>
       <c r="M36" t="n">
-        <v>3.19</v>
+        <v>4.07</v>
       </c>
       <c r="N36" t="n">
-        <v>2.31</v>
+        <v>5.62</v>
       </c>
       <c r="O36" t="n">
-        <v>3.6</v>
+        <v>1.96</v>
       </c>
       <c r="P36" t="n">
-        <v>2.05</v>
+        <v>2.38</v>
       </c>
       <c r="Q36" t="n">
-        <v>2.92</v>
+        <v>5.5</v>
       </c>
       <c r="R36" t="n">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="S36" t="n">
-        <v>2.75</v>
+        <v>3.08</v>
       </c>
       <c r="T36" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="U36" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="V36" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W36" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="X36" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AA36" t="n">
         <v>2.8</v>
       </c>
-      <c r="U36" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="V36" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W36" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="X36" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="Y36" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="Z36" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AA36" t="n">
-        <v>3.55</v>
-      </c>
       <c r="AB36" t="n">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AC36" t="n">
-        <v>1.76</v>
+        <v>1.85</v>
       </c>
       <c r="AD36" t="n">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AE36" t="inlineStr">
         <is>
@@ -5122,10 +5122,10 @@
         </is>
       </c>
       <c r="AG36" t="n">
-        <v>1.62</v>
+        <v>1.15</v>
       </c>
       <c r="AH36" t="n">
-        <v>1.37</v>
+        <v>2.6</v>
       </c>
       <c r="AI36" t="n">
         <v>0</v>
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5272,12 +5272,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5309,65 +5309,65 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L38" t="n">
-        <v>9.5</v>
+        <v>3</v>
       </c>
       <c r="M38" t="n">
-        <v>5.1</v>
+        <v>3.19</v>
       </c>
       <c r="N38" t="n">
-        <v>1.33</v>
+        <v>2.31</v>
       </c>
       <c r="O38" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S38" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="T38" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U38" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="V38" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W38" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="X38" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.44</v>
+        <v>2.01</v>
       </c>
       <c r="Z38" t="n">
-        <v>2.75</v>
+        <v>1.8</v>
       </c>
       <c r="AA38" t="n">
-        <v>2.15</v>
+        <v>3.55</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.7</v>
+        <v>1.27</v>
       </c>
       <c r="AC38" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AD38" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AE38" t="inlineStr">
         <is>
@@ -5380,10 +5380,10 @@
         </is>
       </c>
       <c r="AG38" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AH38" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AI38" t="n">
         <v>0</v>
@@ -5392,7 +5392,7 @@
         <v>0</v>
       </c>
       <c r="AK38" s="3" t="n">
-        <v>45930.66666666666</v>
+        <v>45930.65625</v>
       </c>
     </row>
     <row r="39">
@@ -5401,12 +5401,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Olympique Marseille</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,13 +5442,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5481,10 +5481,10 @@
         <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Z39" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AA39" t="n">
         <v>0</v>
@@ -5521,7 +5521,7 @@
         <v>0</v>
       </c>
       <c r="AK39" s="3" t="n">
-        <v>45930.66666666666</v>
+        <v>45930.65625</v>
       </c>
     </row>
     <row r="40">
@@ -5530,12 +5530,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,13 +5571,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5610,10 +5610,10 @@
         <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="Z40" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AA40" t="n">
         <v>0</v>
@@ -5650,7 +5650,7 @@
         <v>0</v>
       </c>
       <c r="AK40" s="3" t="n">
-        <v>45930.66666666666</v>
+        <v>45930.65625</v>
       </c>
     </row>
     <row r="41">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,13 +5700,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1.35</v>
+        <v>9.5</v>
       </c>
       <c r="M41" t="n">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="N41" t="n">
-        <v>10.5</v>
+        <v>1.33</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5739,16 +5739,16 @@
         <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.6</v>
+        <v>1.44</v>
       </c>
       <c r="Z41" t="n">
-        <v>2.35</v>
+        <v>2.75</v>
       </c>
       <c r="AA41" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB41" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC41" t="n">
         <v>0</v>
@@ -5793,7 +5793,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,13 +5829,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="M42" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5868,10 +5868,10 @@
         <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Z42" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA42" t="n">
         <v>0</v>
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5958,13 +5958,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>3.65</v>
+        <v>1.75</v>
       </c>
       <c r="M43" t="n">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="N43" t="n">
-        <v>1.98</v>
+        <v>5.1</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5997,16 +5997,16 @@
         <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Z43" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AA43" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC43" t="n">
         <v>0</v>
@@ -6061,12 +6061,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Olympique Marseille</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6087,13 +6087,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>19</v>
+        <v>1.7</v>
       </c>
       <c r="M44" t="n">
-        <v>7.6</v>
+        <v>3.85</v>
       </c>
       <c r="N44" t="n">
-        <v>1.15</v>
+        <v>4.9</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -6126,16 +6126,16 @@
         <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.44</v>
+        <v>1.63</v>
       </c>
       <c r="Z44" t="n">
-        <v>2.75</v>
+        <v>2.25</v>
       </c>
       <c r="AA44" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AC44" t="n">
         <v>0</v>
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6216,13 +6216,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>1.5</v>
+        <v>1.35</v>
       </c>
       <c r="M45" t="n">
-        <v>3.95</v>
+        <v>4.7</v>
       </c>
       <c r="N45" t="n">
-        <v>7.5</v>
+        <v>10.5</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -6255,10 +6255,10 @@
         <v>0</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="Z45" t="n">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
       <c r="AA45" t="n">
         <v>0</v>
@@ -6304,27 +6304,27 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6345,13 +6345,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>1.54</v>
+        <v>19</v>
       </c>
       <c r="M46" t="n">
-        <v>4.3</v>
+        <v>7.6</v>
       </c>
       <c r="N46" t="n">
-        <v>5</v>
+        <v>1.15</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -6384,16 +6384,16 @@
         <v>0</v>
       </c>
       <c r="Y46" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="Z46" t="n">
         <v>2.75</v>
       </c>
       <c r="AA46" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.85</v>
+        <v>1.97</v>
       </c>
       <c r="AC46" t="n">
         <v>0</v>
@@ -6424,7 +6424,7 @@
         <v>0</v>
       </c>
       <c r="AK46" s="3" t="n">
-        <v>45930.85416666666</v>
+        <v>45930.66666666666</v>
       </c>
     </row>
     <row r="47">
@@ -6433,27 +6433,27 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6474,13 +6474,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>1.43</v>
+        <v>3.65</v>
       </c>
       <c r="M47" t="n">
-        <v>4.4</v>
+        <v>3.65</v>
       </c>
       <c r="N47" t="n">
-        <v>6.4</v>
+        <v>1.98</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6513,16 +6513,16 @@
         <v>0</v>
       </c>
       <c r="Y47" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Z47" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AA47" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB47" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC47" t="n">
         <v>0</v>
@@ -6553,7 +6553,7 @@
         <v>0</v>
       </c>
       <c r="AK47" s="3" t="n">
-        <v>45930.89583333334</v>
+        <v>45930.66666666666</v>
       </c>
     </row>
     <row r="48">
@@ -6562,126 +6562,513 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>England Championship</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Derby County</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Charlton Athletic</t>
+        </is>
+      </c>
+      <c r="G48" t="n">
+        <v>0</v>
+      </c>
+      <c r="H48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I48" t="n">
+        <v>0</v>
+      </c>
+      <c r="J48" t="n">
+        <v>0</v>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L48" t="n">
+        <v>0</v>
+      </c>
+      <c r="M48" t="n">
+        <v>0</v>
+      </c>
+      <c r="N48" t="n">
+        <v>0</v>
+      </c>
+      <c r="O48" t="n">
+        <v>0</v>
+      </c>
+      <c r="P48" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>0</v>
+      </c>
+      <c r="R48" t="n">
+        <v>0</v>
+      </c>
+      <c r="S48" t="n">
+        <v>0</v>
+      </c>
+      <c r="T48" t="n">
+        <v>0</v>
+      </c>
+      <c r="U48" t="n">
+        <v>0</v>
+      </c>
+      <c r="V48" t="n">
+        <v>0</v>
+      </c>
+      <c r="W48" t="n">
+        <v>0</v>
+      </c>
+      <c r="X48" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y48" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF48" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK48" s="3" t="n">
+        <v>45930.66666666666</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="n">
+        <v>45930</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>USA MLS</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Inter Miami</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Chicago Fire</t>
+        </is>
+      </c>
+      <c r="G49" t="n">
+        <v>0</v>
+      </c>
+      <c r="H49" t="n">
+        <v>0</v>
+      </c>
+      <c r="I49" t="n">
+        <v>0</v>
+      </c>
+      <c r="J49" t="n">
+        <v>0</v>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L49" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="M49" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="N49" t="n">
+        <v>5</v>
+      </c>
+      <c r="O49" t="n">
+        <v>0</v>
+      </c>
+      <c r="P49" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>0</v>
+      </c>
+      <c r="R49" t="n">
+        <v>0</v>
+      </c>
+      <c r="S49" t="n">
+        <v>0</v>
+      </c>
+      <c r="T49" t="n">
+        <v>0</v>
+      </c>
+      <c r="U49" t="n">
+        <v>0</v>
+      </c>
+      <c r="V49" t="n">
+        <v>0</v>
+      </c>
+      <c r="W49" t="n">
+        <v>0</v>
+      </c>
+      <c r="X49" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y49" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z49" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AA49" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AB49" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AC49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF49" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK49" s="3" t="n">
+        <v>45930.85416666666</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="n">
+        <v>45930</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Atlético Mineiro</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Juventude</t>
+        </is>
+      </c>
+      <c r="G50" t="n">
+        <v>0</v>
+      </c>
+      <c r="H50" t="n">
+        <v>0</v>
+      </c>
+      <c r="I50" t="n">
+        <v>0</v>
+      </c>
+      <c r="J50" t="n">
+        <v>0</v>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L50" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="M50" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="N50" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="O50" t="n">
+        <v>0</v>
+      </c>
+      <c r="P50" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>0</v>
+      </c>
+      <c r="R50" t="n">
+        <v>0</v>
+      </c>
+      <c r="S50" t="n">
+        <v>0</v>
+      </c>
+      <c r="T50" t="n">
+        <v>0</v>
+      </c>
+      <c r="U50" t="n">
+        <v>0</v>
+      </c>
+      <c r="V50" t="n">
+        <v>0</v>
+      </c>
+      <c r="W50" t="n">
+        <v>0</v>
+      </c>
+      <c r="X50" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y50" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="Z50" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AA50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF50" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK50" s="3" t="n">
+        <v>45930.89583333334</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="n">
+        <v>45930</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
           <t>21:35</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr">
+      <c r="C51" t="inlineStr">
         <is>
           <t>Brazil Serie B</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr">
+      <c r="D51" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr">
+      <c r="E51" t="inlineStr">
         <is>
           <t>Goiás</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr">
+      <c r="F51" t="inlineStr">
         <is>
           <t>Atlético GO</t>
         </is>
       </c>
-      <c r="G48" t="n">
-        <v>0</v>
-      </c>
-      <c r="H48" t="n">
-        <v>0</v>
-      </c>
-      <c r="I48" t="n">
-        <v>0</v>
-      </c>
-      <c r="J48" t="n">
-        <v>0</v>
-      </c>
-      <c r="K48" t="inlineStr">
+      <c r="G51" t="n">
+        <v>0</v>
+      </c>
+      <c r="H51" t="n">
+        <v>0</v>
+      </c>
+      <c r="I51" t="n">
+        <v>0</v>
+      </c>
+      <c r="J51" t="n">
+        <v>0</v>
+      </c>
+      <c r="K51" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L48" t="n">
-        <v>0</v>
-      </c>
-      <c r="M48" t="n">
-        <v>0</v>
-      </c>
-      <c r="N48" t="n">
-        <v>0</v>
-      </c>
-      <c r="O48" t="n">
-        <v>0</v>
-      </c>
-      <c r="P48" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q48" t="n">
-        <v>0</v>
-      </c>
-      <c r="R48" t="n">
-        <v>0</v>
-      </c>
-      <c r="S48" t="n">
-        <v>0</v>
-      </c>
-      <c r="T48" t="n">
-        <v>0</v>
-      </c>
-      <c r="U48" t="n">
-        <v>0</v>
-      </c>
-      <c r="V48" t="n">
-        <v>0</v>
-      </c>
-      <c r="W48" t="n">
-        <v>0</v>
-      </c>
-      <c r="X48" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y48" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE48" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF48" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK48" s="3" t="n">
+      <c r="L51" t="n">
+        <v>0</v>
+      </c>
+      <c r="M51" t="n">
+        <v>0</v>
+      </c>
+      <c r="N51" t="n">
+        <v>0</v>
+      </c>
+      <c r="O51" t="n">
+        <v>0</v>
+      </c>
+      <c r="P51" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>0</v>
+      </c>
+      <c r="R51" t="n">
+        <v>0</v>
+      </c>
+      <c r="S51" t="n">
+        <v>0</v>
+      </c>
+      <c r="T51" t="n">
+        <v>0</v>
+      </c>
+      <c r="U51" t="n">
+        <v>0</v>
+      </c>
+      <c r="V51" t="n">
+        <v>0</v>
+      </c>
+      <c r="W51" t="n">
+        <v>0</v>
+      </c>
+      <c r="X51" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y51" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF51" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK51" s="3" t="n">
         <v>45930.89930555555</v>
       </c>
     </row>

--- a/jogos_2025-09-30.xlsx
+++ b/jogos_2025-09-30.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK51"/>
+  <dimension ref="A1:AK48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1185,13 +1185,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>3.35</v>
+        <v>4.6</v>
       </c>
       <c r="M6" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="N6" t="n">
-        <v>2.04</v>
+        <v>1.82</v>
       </c>
       <c r="O6" t="n">
         <v>4.4</v>
@@ -1227,7 +1227,7 @@
         <v>2.25</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AA6" t="n">
         <v>4</v>
@@ -1278,7 +1278,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Police</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ulinzi Stars</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Police</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Ulinzi Stars</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1531,12 +1531,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Carrarese</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,13 +1572,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>8.9</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1611,16 +1611,16 @@
         <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -1651,7 +1651,7 @@
         <v>0</v>
       </c>
       <c r="AK9" s="3" t="n">
-        <v>45930.5</v>
+        <v>45930.57291666666</v>
       </c>
     </row>
     <row r="10">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Pescara</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,13 +1701,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1740,10 +1740,10 @@
         <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AA10" t="n">
         <v>0</v>
@@ -1780,7 +1780,7 @@
         <v>0</v>
       </c>
       <c r="AK10" s="3" t="n">
-        <v>45930.5</v>
+        <v>45930.57291666666</v>
       </c>
     </row>
     <row r="11">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Saarbrucken</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>MSV Duisburg</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1909,7 +1909,7 @@
         <v>0</v>
       </c>
       <c r="AK11" s="3" t="n">
-        <v>45930.5</v>
+        <v>45930.58333333334</v>
       </c>
     </row>
     <row r="12">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Erzgebirge Aue</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,13 +1959,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1998,10 +1998,10 @@
         <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
         <v>0</v>
@@ -2038,7 +2038,7 @@
         <v>0</v>
       </c>
       <c r="AK12" s="3" t="n">
-        <v>45930.57291666666</v>
+        <v>45930.58333333334</v>
       </c>
     </row>
     <row r="13">
@@ -2047,12 +2047,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Hansa Rostock</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,13 +2088,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2127,16 +2127,16 @@
         <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2167,7 +2167,7 @@
         <v>0</v>
       </c>
       <c r="AK13" s="3" t="n">
-        <v>45930.57291666666</v>
+        <v>45930.58333333334</v>
       </c>
     </row>
     <row r="14">
@@ -2181,22 +2181,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Havelse</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Waldhof Mannheim</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2310,22 +2310,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Saarbrucken</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>MSV Duisburg</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,13 +2346,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2391,10 +2391,10 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -2475,13 +2475,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2520,10 +2520,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -2692,12 +2692,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Hansa Rostock</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2812,7 +2812,7 @@
         <v>0</v>
       </c>
       <c r="AK18" s="3" t="n">
-        <v>45930.58333333334</v>
+        <v>45930.625</v>
       </c>
     </row>
     <row r="19">
@@ -2821,12 +2821,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Havelse</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Waldhof Mannheim</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2941,7 +2941,7 @@
         <v>0</v>
       </c>
       <c r="AK19" s="3" t="n">
-        <v>45930.58333333334</v>
+        <v>45930.625</v>
       </c>
     </row>
     <row r="20">
@@ -2950,12 +2950,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Erzgebirge Aue</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3070,7 +3070,7 @@
         <v>0</v>
       </c>
       <c r="AK20" s="3" t="n">
-        <v>45930.58333333334</v>
+        <v>45930.625</v>
       </c>
     </row>
     <row r="21">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3337,12 +3337,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Mantova</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,13 +3378,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3417,10 +3417,10 @@
         <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AA23" t="n">
         <v>0</v>
@@ -3457,7 +3457,7 @@
         <v>0</v>
       </c>
       <c r="AK23" s="3" t="n">
-        <v>45930.625</v>
+        <v>45930.64583333334</v>
       </c>
     </row>
     <row r="24">
@@ -3466,12 +3466,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,13 +3507,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3546,10 +3546,10 @@
         <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AA24" t="n">
         <v>0</v>
@@ -3586,7 +3586,7 @@
         <v>0</v>
       </c>
       <c r="AK24" s="3" t="n">
-        <v>45930.625</v>
+        <v>45930.64583333334</v>
       </c>
     </row>
     <row r="25">
@@ -3595,12 +3595,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,13 +3636,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3675,10 +3675,10 @@
         <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA25" t="n">
         <v>0</v>
@@ -3715,7 +3715,7 @@
         <v>0</v>
       </c>
       <c r="AK25" s="3" t="n">
-        <v>45930.625</v>
+        <v>45930.64583333334</v>
       </c>
     </row>
     <row r="26">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,13 +3765,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.5</v>
+        <v>2.15</v>
       </c>
       <c r="M26" t="n">
-        <v>3</v>
+        <v>3.35</v>
       </c>
       <c r="N26" t="n">
-        <v>2.6</v>
+        <v>3.45</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3804,10 +3804,10 @@
         <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="Z26" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="AA26" t="n">
         <v>0</v>
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Calcio Padova</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,13 +3894,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3933,10 +3933,10 @@
         <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z27" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AA27" t="n">
         <v>0</v>
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mantova</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,13 +4023,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.8</v>
+        <v>3.6</v>
       </c>
       <c r="M28" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="N28" t="n">
-        <v>3.8</v>
+        <v>2.05</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -4062,10 +4062,10 @@
         <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.85</v>
+        <v>2.07</v>
       </c>
       <c r="Z28" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AA28" t="n">
         <v>0</v>
@@ -4111,12 +4111,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,13 +4152,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -4191,10 +4191,10 @@
         <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Z29" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AA29" t="n">
         <v>0</v>
@@ -4231,7 +4231,7 @@
         <v>0</v>
       </c>
       <c r="AK29" s="3" t="n">
-        <v>45930.64583333334</v>
+        <v>45930.65625</v>
       </c>
     </row>
     <row r="30">
@@ -4240,12 +4240,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Calcio Padova</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4360,7 +4360,7 @@
         <v>0</v>
       </c>
       <c r="AK30" s="3" t="n">
-        <v>45930.64583333334</v>
+        <v>45930.65625</v>
       </c>
     </row>
     <row r="31">
@@ -4369,12 +4369,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,13 +4410,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4449,10 +4449,10 @@
         <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="Z31" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AA31" t="n">
         <v>0</v>
@@ -4489,7 +4489,7 @@
         <v>0</v>
       </c>
       <c r="AK31" s="3" t="n">
-        <v>45930.64583333334</v>
+        <v>45930.65625</v>
       </c>
     </row>
     <row r="32">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4761,7 +4761,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4793,65 +4793,65 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="O34" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S34" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="T34" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U34" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="V34" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W34" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="X34" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="Y34" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="Z34" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AA34" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AB34" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AC34" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AD34" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AE34" t="inlineStr">
         <is>
@@ -4864,10 +4864,10 @@
         </is>
       </c>
       <c r="AG34" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AH34" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AI34" t="n">
         <v>0</v>
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5019,7 +5019,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5051,65 +5051,65 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L36" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>4.07</v>
+        <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>5.62</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="S36" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="T36" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="U36" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="V36" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="W36" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="X36" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="Z36" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AC36" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD36" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AE36" t="inlineStr">
         <is>
@@ -5122,10 +5122,10 @@
         </is>
       </c>
       <c r="AG36" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AH36" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AI36" t="n">
         <v>0</v>
@@ -5148,7 +5148,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5180,65 +5180,65 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="O37" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="R37" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S37" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="T37" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="U37" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="V37" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="W37" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X37" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="Y37" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z37" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA37" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AB37" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AC37" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD37" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AE37" t="inlineStr">
         <is>
@@ -5251,10 +5251,10 @@
         </is>
       </c>
       <c r="AG37" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AH37" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AI37" t="n">
         <v>0</v>
@@ -5272,12 +5272,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Olympique Marseille</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5309,65 +5309,65 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L38" t="n">
-        <v>3</v>
+        <v>1.56</v>
       </c>
       <c r="M38" t="n">
-        <v>3.19</v>
+        <v>4.3</v>
       </c>
       <c r="N38" t="n">
-        <v>2.31</v>
+        <v>5.1</v>
       </c>
       <c r="O38" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="P38" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="T38" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="U38" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="V38" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W38" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="X38" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>2.01</v>
+        <v>1.63</v>
       </c>
       <c r="Z38" t="n">
-        <v>1.8</v>
+        <v>2.25</v>
       </c>
       <c r="AA38" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AC38" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AD38" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AE38" t="inlineStr">
         <is>
@@ -5380,10 +5380,10 @@
         </is>
       </c>
       <c r="AG38" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AH38" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AI38" t="n">
         <v>0</v>
@@ -5392,7 +5392,7 @@
         <v>0</v>
       </c>
       <c r="AK38" s="3" t="n">
-        <v>45930.65625</v>
+        <v>45930.66666666666</v>
       </c>
     </row>
     <row r="39">
@@ -5401,12 +5401,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,13 +5442,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5481,16 +5481,16 @@
         <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z39" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AA39" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB39" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC39" t="n">
         <v>0</v>
@@ -5521,7 +5521,7 @@
         <v>0</v>
       </c>
       <c r="AK39" s="3" t="n">
-        <v>45930.65625</v>
+        <v>45930.66666666666</v>
       </c>
     </row>
     <row r="40">
@@ -5530,12 +5530,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,13 +5571,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5610,10 +5610,10 @@
         <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Z40" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AA40" t="n">
         <v>0</v>
@@ -5650,7 +5650,7 @@
         <v>0</v>
       </c>
       <c r="AK40" s="3" t="n">
-        <v>45930.65625</v>
+        <v>45930.66666666666</v>
       </c>
     </row>
     <row r="41">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,13 +5700,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>9.5</v>
+        <v>1.35</v>
       </c>
       <c r="M41" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="N41" t="n">
-        <v>1.33</v>
+        <v>7</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5739,16 +5739,16 @@
         <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="Z41" t="n">
-        <v>2.75</v>
+        <v>2.35</v>
       </c>
       <c r="AA41" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC41" t="n">
         <v>0</v>
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,13 +5829,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="M42" t="n">
-        <v>3.95</v>
+        <v>3.83</v>
       </c>
       <c r="N42" t="n">
-        <v>7.5</v>
+        <v>2.1</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5868,16 +5868,16 @@
         <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Z42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA42" t="n">
         <v>2.25</v>
       </c>
-      <c r="AA42" t="n">
-        <v>0</v>
-      </c>
       <c r="AB42" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC42" t="n">
         <v>0</v>
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5958,13 +5958,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>1.75</v>
+        <v>15</v>
       </c>
       <c r="M43" t="n">
-        <v>3.55</v>
+        <v>7.6</v>
       </c>
       <c r="N43" t="n">
-        <v>5.1</v>
+        <v>1.15</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5997,16 +5997,16 @@
         <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.68</v>
+        <v>1.44</v>
       </c>
       <c r="Z43" t="n">
-        <v>2.18</v>
+        <v>2.75</v>
       </c>
       <c r="AA43" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB43" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AC43" t="n">
         <v>0</v>
@@ -6051,7 +6051,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6061,12 +6061,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Olympique Marseille</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6087,13 +6087,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="N44" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -6126,10 +6126,10 @@
         <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Z44" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AA44" t="n">
         <v>0</v>
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6216,13 +6216,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>1.35</v>
+        <v>1.56</v>
       </c>
       <c r="M45" t="n">
-        <v>4.7</v>
+        <v>4.1</v>
       </c>
       <c r="N45" t="n">
-        <v>10.5</v>
+        <v>5.4</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -6255,10 +6255,10 @@
         <v>0</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="Z45" t="n">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="AA45" t="n">
         <v>0</v>
@@ -6304,27 +6304,27 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6345,13 +6345,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>19</v>
+        <v>1.57</v>
       </c>
       <c r="M46" t="n">
-        <v>7.6</v>
+        <v>4.8</v>
       </c>
       <c r="N46" t="n">
-        <v>1.15</v>
+        <v>4.9</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -6384,16 +6384,16 @@
         <v>0</v>
       </c>
       <c r="Y46" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="Z46" t="n">
         <v>2.75</v>
       </c>
       <c r="AA46" t="n">
-        <v>1.83</v>
+        <v>1.88</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.97</v>
+        <v>1.92</v>
       </c>
       <c r="AC46" t="n">
         <v>0</v>
@@ -6424,7 +6424,7 @@
         <v>0</v>
       </c>
       <c r="AK46" s="3" t="n">
-        <v>45930.66666666666</v>
+        <v>45930.85416666666</v>
       </c>
     </row>
     <row r="47">
@@ -6433,27 +6433,27 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6474,13 +6474,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>3.65</v>
+        <v>1.45</v>
       </c>
       <c r="M47" t="n">
-        <v>3.65</v>
+        <v>4.4</v>
       </c>
       <c r="N47" t="n">
-        <v>1.98</v>
+        <v>7.4</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6513,16 +6513,16 @@
         <v>0</v>
       </c>
       <c r="Y47" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Z47" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA47" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC47" t="n">
         <v>0</v>
@@ -6553,7 +6553,7 @@
         <v>0</v>
       </c>
       <c r="AK47" s="3" t="n">
-        <v>45930.66666666666</v>
+        <v>45930.89583333334</v>
       </c>
     </row>
     <row r="48">
@@ -6562,27 +6562,27 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>21:35</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6682,393 +6682,6 @@
         <v>0</v>
       </c>
       <c r="AK48" s="3" t="n">
-        <v>45930.66666666666</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="2" t="n">
-        <v>45930</v>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>20:30</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>USA MLS</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>Inter Miami</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>Chicago Fire</t>
-        </is>
-      </c>
-      <c r="G49" t="n">
-        <v>0</v>
-      </c>
-      <c r="H49" t="n">
-        <v>0</v>
-      </c>
-      <c r="I49" t="n">
-        <v>0</v>
-      </c>
-      <c r="J49" t="n">
-        <v>0</v>
-      </c>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L49" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="M49" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="N49" t="n">
-        <v>5</v>
-      </c>
-      <c r="O49" t="n">
-        <v>0</v>
-      </c>
-      <c r="P49" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q49" t="n">
-        <v>0</v>
-      </c>
-      <c r="R49" t="n">
-        <v>0</v>
-      </c>
-      <c r="S49" t="n">
-        <v>0</v>
-      </c>
-      <c r="T49" t="n">
-        <v>0</v>
-      </c>
-      <c r="U49" t="n">
-        <v>0</v>
-      </c>
-      <c r="V49" t="n">
-        <v>0</v>
-      </c>
-      <c r="W49" t="n">
-        <v>0</v>
-      </c>
-      <c r="X49" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y49" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Z49" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AA49" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AB49" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AC49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE49" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF49" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK49" s="3" t="n">
-        <v>45930.85416666666</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="2" t="n">
-        <v>45930</v>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>21:30</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Brazil Serie A</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>Atlético Mineiro</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>Juventude</t>
-        </is>
-      </c>
-      <c r="G50" t="n">
-        <v>0</v>
-      </c>
-      <c r="H50" t="n">
-        <v>0</v>
-      </c>
-      <c r="I50" t="n">
-        <v>0</v>
-      </c>
-      <c r="J50" t="n">
-        <v>0</v>
-      </c>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L50" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="M50" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="N50" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="O50" t="n">
-        <v>0</v>
-      </c>
-      <c r="P50" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q50" t="n">
-        <v>0</v>
-      </c>
-      <c r="R50" t="n">
-        <v>0</v>
-      </c>
-      <c r="S50" t="n">
-        <v>0</v>
-      </c>
-      <c r="T50" t="n">
-        <v>0</v>
-      </c>
-      <c r="U50" t="n">
-        <v>0</v>
-      </c>
-      <c r="V50" t="n">
-        <v>0</v>
-      </c>
-      <c r="W50" t="n">
-        <v>0</v>
-      </c>
-      <c r="X50" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y50" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="Z50" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AA50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE50" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF50" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK50" s="3" t="n">
-        <v>45930.89583333334</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="2" t="n">
-        <v>45930</v>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>21:35</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Brazil Serie B</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>Goiás</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>Atlético GO</t>
-        </is>
-      </c>
-      <c r="G51" t="n">
-        <v>0</v>
-      </c>
-      <c r="H51" t="n">
-        <v>0</v>
-      </c>
-      <c r="I51" t="n">
-        <v>0</v>
-      </c>
-      <c r="J51" t="n">
-        <v>0</v>
-      </c>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L51" t="n">
-        <v>0</v>
-      </c>
-      <c r="M51" t="n">
-        <v>0</v>
-      </c>
-      <c r="N51" t="n">
-        <v>0</v>
-      </c>
-      <c r="O51" t="n">
-        <v>0</v>
-      </c>
-      <c r="P51" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q51" t="n">
-        <v>0</v>
-      </c>
-      <c r="R51" t="n">
-        <v>0</v>
-      </c>
-      <c r="S51" t="n">
-        <v>0</v>
-      </c>
-      <c r="T51" t="n">
-        <v>0</v>
-      </c>
-      <c r="U51" t="n">
-        <v>0</v>
-      </c>
-      <c r="V51" t="n">
-        <v>0</v>
-      </c>
-      <c r="W51" t="n">
-        <v>0</v>
-      </c>
-      <c r="X51" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y51" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE51" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF51" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK51" s="3" t="n">
         <v>45930.89930555555</v>
       </c>
     </row>

--- a/jogos_2025-09-30.xlsx
+++ b/jogos_2025-09-30.xlsx
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Sogdiana</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Sogdiana</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1278,7 +1278,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Police</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Ulinzi Stars</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Police</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ulinzi Stars</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,13 +1572,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>19</v>
+        <v>1.86</v>
       </c>
       <c r="M9" t="n">
-        <v>8.9</v>
+        <v>3.84</v>
       </c>
       <c r="N9" t="n">
-        <v>1.11</v>
+        <v>3.7</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1611,16 +1611,16 @@
         <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.3</v>
+        <v>1.7</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.4</v>
+        <v>2.15</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,13 +1701,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.86</v>
+        <v>19</v>
       </c>
       <c r="M10" t="n">
-        <v>3.84</v>
+        <v>8.9</v>
       </c>
       <c r="N10" t="n">
-        <v>3.7</v>
+        <v>1.11</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1740,16 +1740,16 @@
         <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.7</v>
+        <v>1.3</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.15</v>
+        <v>3.4</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -1794,22 +1794,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Saarbrucken</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>MSV Duisburg</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,13 +1830,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1875,10 +1875,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>Saarbrucken</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Erzgebirge Aue</t>
+          <t>MSV Duisburg</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Hansa Rostock</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>Erzgebirge Aue</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Havelse</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Waldhof Mannheim</t>
+          <t>Wehen Wiesbaden</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2310,22 +2310,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Havelse</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Waldhof Mannheim</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,13 +2346,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2391,10 +2391,10 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,13 +2475,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.26</v>
+        <v>1.56</v>
       </c>
       <c r="M16" t="n">
-        <v>5.1</v>
+        <v>4.2</v>
       </c>
       <c r="N16" t="n">
-        <v>7.6</v>
+        <v>4.2</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2520,10 +2520,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.17</v>
+        <v>1.92</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.62</v>
+        <v>1.78</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>Hansa Rostock</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Wehen Wiesbaden</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Calcio Padova</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mantova</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,13 +3378,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.8</v>
+        <v>2.15</v>
       </c>
       <c r="M23" t="n">
-        <v>3.7</v>
+        <v>3.35</v>
       </c>
       <c r="N23" t="n">
-        <v>4.3</v>
+        <v>3.45</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3417,10 +3417,10 @@
         <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.95</v>
+        <v>2.2</v>
       </c>
       <c r="Z23" t="n">
-        <v>1.85</v>
+        <v>1.65</v>
       </c>
       <c r="AA23" t="n">
         <v>0</v>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,13 +3507,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.6</v>
+        <v>2.15</v>
       </c>
       <c r="M24" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="N24" t="n">
-        <v>2.75</v>
+        <v>3.45</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3546,10 +3546,10 @@
         <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="Z24" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AA24" t="n">
         <v>0</v>
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,14 +3636,14 @@
         </is>
       </c>
       <c r="L25" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="M25" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="N25" t="n">
         <v>2.05</v>
       </c>
-      <c r="M25" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="N25" t="n">
-        <v>3.45</v>
-      </c>
       <c r="O25" t="n">
         <v>0</v>
       </c>
@@ -3675,10 +3675,10 @@
         <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.8</v>
+        <v>2.07</v>
       </c>
       <c r="Z25" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AA25" t="n">
         <v>0</v>
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,10 +3765,10 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="M26" t="n">
-        <v>3.35</v>
+        <v>3.65</v>
       </c>
       <c r="N26" t="n">
         <v>3.45</v>
@@ -3804,10 +3804,10 @@
         <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>2.18</v>
+        <v>1.8</v>
       </c>
       <c r="Z26" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="AA26" t="n">
         <v>0</v>
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Calcio Padova</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,13 +3894,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.15</v>
+        <v>2.6</v>
       </c>
       <c r="M27" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="N27" t="n">
-        <v>3.45</v>
+        <v>2.75</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3936,7 +3936,7 @@
         <v>2.2</v>
       </c>
       <c r="Z27" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AA27" t="n">
         <v>0</v>
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>Mantova</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,13 +4023,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>3.6</v>
+        <v>1.8</v>
       </c>
       <c r="M28" t="n">
-        <v>3.45</v>
+        <v>3.7</v>
       </c>
       <c r="N28" t="n">
-        <v>2.05</v>
+        <v>4.3</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -4062,10 +4062,10 @@
         <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>2.07</v>
+        <v>1.95</v>
       </c>
       <c r="Z28" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AA28" t="n">
         <v>0</v>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4406,65 +4406,65 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="O31" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S31" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="T31" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="V31" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="W31" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X31" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="Y31" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z31" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA31" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AB31" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AC31" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD31" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AE31" t="inlineStr">
         <is>
@@ -4477,10 +4477,10 @@
         </is>
       </c>
       <c r="AG31" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AH31" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AI31" t="n">
         <v>0</v>
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4761,7 +4761,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4793,65 +4793,65 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L34" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>3.19</v>
+        <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="T34" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="U34" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="V34" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W34" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="X34" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="Z34" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AC34" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AD34" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AE34" t="inlineStr">
         <is>
@@ -4864,10 +4864,10 @@
         </is>
       </c>
       <c r="AG34" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AI34" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4922,65 +4922,65 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="O35" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S35" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="T35" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="V35" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W35" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="X35" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="Y35" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="Z35" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AA35" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AB35" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AC35" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AD35" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AE35" t="inlineStr">
         <is>
@@ -4993,10 +4993,10 @@
         </is>
       </c>
       <c r="AG35" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AH35" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AI35" t="n">
         <v>0</v>
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5148,7 +5148,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5180,65 +5180,65 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L37" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="S37" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="T37" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="U37" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="V37" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="W37" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="X37" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Z37" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AC37" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD37" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AE37" t="inlineStr">
         <is>
@@ -5251,10 +5251,10 @@
         </is>
       </c>
       <c r="AG37" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AH37" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AI37" t="n">
         <v>0</v>
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Olympique Marseille</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,13 +5313,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>1.56</v>
+        <v>4.3</v>
       </c>
       <c r="M38" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="N38" t="n">
-        <v>5.1</v>
+        <v>1.64</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5352,16 +5352,16 @@
         <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.63</v>
+        <v>1.44</v>
       </c>
       <c r="Z38" t="n">
-        <v>2.25</v>
+        <v>2.75</v>
       </c>
       <c r="AA38" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB38" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC38" t="n">
         <v>0</v>
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,13 +5442,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>4.3</v>
+        <v>1.56</v>
       </c>
       <c r="M39" t="n">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="N39" t="n">
-        <v>1.64</v>
+        <v>5.4</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5481,16 +5481,16 @@
         <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.44</v>
+        <v>1.63</v>
       </c>
       <c r="Z39" t="n">
-        <v>2.75</v>
+        <v>2.25</v>
       </c>
       <c r="AA39" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC39" t="n">
         <v>0</v>
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,13 +5571,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>1.62</v>
+        <v>3</v>
       </c>
       <c r="M40" t="n">
-        <v>4.1</v>
+        <v>3.83</v>
       </c>
       <c r="N40" t="n">
-        <v>4.9</v>
+        <v>2.1</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5610,16 +5610,16 @@
         <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="Z40" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB40" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,13 +5700,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1.35</v>
+        <v>15</v>
       </c>
       <c r="M41" t="n">
-        <v>5.3</v>
+        <v>7.6</v>
       </c>
       <c r="N41" t="n">
-        <v>7</v>
+        <v>1.15</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5739,16 +5739,16 @@
         <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.6</v>
+        <v>1.44</v>
       </c>
       <c r="Z41" t="n">
-        <v>2.35</v>
+        <v>2.75</v>
       </c>
       <c r="AA41" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB41" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AC41" t="n">
         <v>0</v>
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Olympique Marseille</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,13 +5829,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>3</v>
+        <v>1.56</v>
       </c>
       <c r="M42" t="n">
-        <v>3.83</v>
+        <v>4.3</v>
       </c>
       <c r="N42" t="n">
-        <v>2.1</v>
+        <v>5.1</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5868,16 +5868,16 @@
         <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Z42" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA42" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC42" t="n">
         <v>0</v>
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5958,13 +5958,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>15</v>
+        <v>1.62</v>
       </c>
       <c r="M43" t="n">
-        <v>7.6</v>
+        <v>4.1</v>
       </c>
       <c r="N43" t="n">
-        <v>1.15</v>
+        <v>4.9</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5997,16 +5997,16 @@
         <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.44</v>
+        <v>1.68</v>
       </c>
       <c r="Z43" t="n">
-        <v>2.75</v>
+        <v>2.18</v>
       </c>
       <c r="AA43" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AC43" t="n">
         <v>0</v>
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6216,13 +6216,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>1.56</v>
+        <v>1.35</v>
       </c>
       <c r="M45" t="n">
-        <v>4.1</v>
+        <v>5.3</v>
       </c>
       <c r="N45" t="n">
-        <v>5.4</v>
+        <v>7</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -6255,10 +6255,10 @@
         <v>0</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="Z45" t="n">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
       <c r="AA45" t="n">
         <v>0</v>

--- a/jogos_2025-09-30.xlsx
+++ b/jogos_2025-09-30.xlsx
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,13 +1830,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.26</v>
+        <v>1.56</v>
       </c>
       <c r="M11" t="n">
-        <v>5.1</v>
+        <v>4.2</v>
       </c>
       <c r="N11" t="n">
-        <v>7.6</v>
+        <v>4.2</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1875,10 +1875,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.17</v>
+        <v>1.92</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.62</v>
+        <v>1.78</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Erzgebirge Aue</t>
+          <t>Wehen Wiesbaden</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>Havelse</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Wehen Wiesbaden</t>
+          <t>Waldhof Mannheim</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2310,22 +2310,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Havelse</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Waldhof Mannheim</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,13 +2346,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2385,16 +2385,16 @@
         <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -2439,22 +2439,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Erzgebirge Aue</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,13 +2475,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2520,10 +2520,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,10 +3507,10 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="M24" t="n">
-        <v>3.35</v>
+        <v>3.65</v>
       </c>
       <c r="N24" t="n">
         <v>3.45</v>
@@ -3546,10 +3546,10 @@
         <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>2.18</v>
+        <v>1.8</v>
       </c>
       <c r="Z24" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="AA24" t="n">
         <v>0</v>
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Mantova</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,13 +3765,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.05</v>
+        <v>1.8</v>
       </c>
       <c r="M26" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="N26" t="n">
-        <v>3.45</v>
+        <v>4.3</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3804,10 +3804,10 @@
         <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="Z26" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AA26" t="n">
         <v>0</v>
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mantova</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,13 +4023,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.8</v>
+        <v>2.15</v>
       </c>
       <c r="M28" t="n">
-        <v>3.7</v>
+        <v>3.35</v>
       </c>
       <c r="N28" t="n">
-        <v>4.3</v>
+        <v>3.45</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -4062,10 +4062,10 @@
         <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.95</v>
+        <v>2.18</v>
       </c>
       <c r="Z28" t="n">
-        <v>1.85</v>
+        <v>1.7</v>
       </c>
       <c r="AA28" t="n">
         <v>0</v>
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4374,7 +4374,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4406,65 +4406,65 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="T31" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="U31" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="V31" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="W31" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="X31" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Z31" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AE31" t="inlineStr">
         <is>
@@ -4477,10 +4477,10 @@
         </is>
       </c>
       <c r="AG31" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AH31" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AI31" t="n">
         <v>0</v>
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4632,7 +4632,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4664,65 +4664,65 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="O33" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S33" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="T33" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U33" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="V33" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W33" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="X33" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="Y33" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="Z33" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AA33" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AB33" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AC33" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AD33" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AE33" t="inlineStr">
         <is>
@@ -4735,10 +4735,10 @@
         </is>
       </c>
       <c r="AG33" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AH33" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AI33" t="n">
         <v>0</v>
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,61 +4926,61 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>3</v>
+        <v>1.45</v>
       </c>
       <c r="M35" t="n">
-        <v>3.19</v>
+        <v>4.4</v>
       </c>
       <c r="N35" t="n">
-        <v>2.31</v>
+        <v>6.4</v>
       </c>
       <c r="O35" t="n">
-        <v>3.6</v>
+        <v>1.96</v>
       </c>
       <c r="P35" t="n">
-        <v>2.05</v>
+        <v>2.38</v>
       </c>
       <c r="Q35" t="n">
-        <v>2.92</v>
+        <v>5.5</v>
       </c>
       <c r="R35" t="n">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="S35" t="n">
-        <v>2.75</v>
+        <v>3.08</v>
       </c>
       <c r="T35" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="V35" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W35" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="X35" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AA35" t="n">
         <v>2.8</v>
       </c>
-      <c r="U35" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="V35" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W35" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="X35" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="Y35" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="Z35" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AA35" t="n">
-        <v>3.55</v>
-      </c>
       <c r="AB35" t="n">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AC35" t="n">
-        <v>1.76</v>
+        <v>1.85</v>
       </c>
       <c r="AD35" t="n">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AE35" t="inlineStr">
         <is>
@@ -4993,10 +4993,10 @@
         </is>
       </c>
       <c r="AG35" t="n">
-        <v>1.62</v>
+        <v>1.15</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.37</v>
+        <v>2.6</v>
       </c>
       <c r="AI35" t="n">
         <v>0</v>
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5406,7 +5406,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,13 +5442,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5481,10 +5481,10 @@
         <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Z39" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AA39" t="n">
         <v>0</v>
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,13 +5571,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>3</v>
+        <v>1.62</v>
       </c>
       <c r="M40" t="n">
-        <v>3.83</v>
+        <v>4.1</v>
       </c>
       <c r="N40" t="n">
-        <v>2.1</v>
+        <v>4.9</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5610,16 +5610,16 @@
         <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Z40" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AA40" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Olympique Marseille</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,13 +5700,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>15</v>
+        <v>1.56</v>
       </c>
       <c r="M41" t="n">
-        <v>7.6</v>
+        <v>4.3</v>
       </c>
       <c r="N41" t="n">
-        <v>1.15</v>
+        <v>5.1</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5739,16 +5739,16 @@
         <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.44</v>
+        <v>1.63</v>
       </c>
       <c r="Z41" t="n">
-        <v>2.75</v>
+        <v>2.25</v>
       </c>
       <c r="AA41" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AC41" t="n">
         <v>0</v>
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Olympique Marseille</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5832,10 +5832,10 @@
         <v>1.56</v>
       </c>
       <c r="M42" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="N42" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5958,13 +5958,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>1.62</v>
+        <v>3</v>
       </c>
       <c r="M43" t="n">
-        <v>4.1</v>
+        <v>3.83</v>
       </c>
       <c r="N43" t="n">
-        <v>4.9</v>
+        <v>2.1</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5997,16 +5997,16 @@
         <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="Z43" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AA43" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB43" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC43" t="n">
         <v>0</v>
@@ -6051,7 +6051,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6061,12 +6061,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6087,13 +6087,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="M44" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -6126,10 +6126,10 @@
         <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z44" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AA44" t="n">
         <v>0</v>
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6216,13 +6216,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>1.35</v>
+        <v>15</v>
       </c>
       <c r="M45" t="n">
-        <v>5.3</v>
+        <v>7.6</v>
       </c>
       <c r="N45" t="n">
-        <v>7</v>
+        <v>1.15</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -6255,16 +6255,16 @@
         <v>0</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.6</v>
+        <v>1.44</v>
       </c>
       <c r="Z45" t="n">
-        <v>2.35</v>
+        <v>2.75</v>
       </c>
       <c r="AA45" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB45" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC45" t="n">
         <v>0</v>

--- a/jogos_2025-09-30.xlsx
+++ b/jogos_2025-09-30.xlsx
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sogdiana</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Sogdiana</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1794,22 +1794,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Havelse</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Waldhof Mannheim</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,13 +1830,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1875,10 +1875,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Saarbrucken</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>MSV Duisburg</t>
+          <t>Wehen Wiesbaden</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2052,22 +2052,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Wehen Wiesbaden</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,13 +2088,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2127,16 +2127,16 @@
         <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2181,22 +2181,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Havelse</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Waldhof Mannheim</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,13 +2217,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2262,10 +2262,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -2310,22 +2310,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Saarbrucken</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>MSV Duisburg</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,13 +2346,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2385,16 +2385,16 @@
         <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Calcio Padova</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Mantova</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,13 +3378,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.15</v>
+        <v>1.8</v>
       </c>
       <c r="M23" t="n">
-        <v>3.35</v>
+        <v>3.7</v>
       </c>
       <c r="N23" t="n">
-        <v>3.45</v>
+        <v>4.3</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3417,10 +3417,10 @@
         <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>2.2</v>
+        <v>1.95</v>
       </c>
       <c r="Z23" t="n">
-        <v>1.65</v>
+        <v>1.85</v>
       </c>
       <c r="AA23" t="n">
         <v>0</v>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,10 +3507,10 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="M24" t="n">
-        <v>3.65</v>
+        <v>3.35</v>
       </c>
       <c r="N24" t="n">
         <v>3.45</v>
@@ -3546,10 +3546,10 @@
         <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.8</v>
+        <v>2.18</v>
       </c>
       <c r="Z24" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="AA24" t="n">
         <v>0</v>
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Calcio Padova</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,14 +3636,14 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>3.6</v>
+        <v>2.15</v>
       </c>
       <c r="M25" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="N25" t="n">
         <v>3.45</v>
       </c>
-      <c r="N25" t="n">
-        <v>2.05</v>
-      </c>
       <c r="O25" t="n">
         <v>0</v>
       </c>
@@ -3675,10 +3675,10 @@
         <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>2.07</v>
+        <v>2.2</v>
       </c>
       <c r="Z25" t="n">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="AA25" t="n">
         <v>0</v>
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mantova</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,49 +3765,49 @@
         </is>
       </c>
       <c r="L26" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="M26" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="N26" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>0</v>
+      </c>
+      <c r="R26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S26" t="n">
+        <v>0</v>
+      </c>
+      <c r="T26" t="n">
+        <v>0</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0</v>
+      </c>
+      <c r="V26" t="n">
+        <v>0</v>
+      </c>
+      <c r="W26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y26" t="n">
         <v>1.8</v>
       </c>
-      <c r="M26" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="N26" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="O26" t="n">
-        <v>0</v>
-      </c>
-      <c r="P26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>0</v>
-      </c>
-      <c r="R26" t="n">
-        <v>0</v>
-      </c>
-      <c r="S26" t="n">
-        <v>0</v>
-      </c>
-      <c r="T26" t="n">
-        <v>0</v>
-      </c>
-      <c r="U26" t="n">
-        <v>0</v>
-      </c>
-      <c r="V26" t="n">
-        <v>0</v>
-      </c>
-      <c r="W26" t="n">
-        <v>0</v>
-      </c>
-      <c r="X26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>1.95</v>
-      </c>
       <c r="Z26" t="n">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AA26" t="n">
         <v>0</v>
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,13 +4023,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.15</v>
+        <v>3.6</v>
       </c>
       <c r="M28" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="N28" t="n">
-        <v>3.45</v>
+        <v>2.05</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -4062,10 +4062,10 @@
         <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>2.18</v>
+        <v>2.07</v>
       </c>
       <c r="Z28" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AA28" t="n">
         <v>0</v>
@@ -4116,7 +4116,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4148,65 +4148,65 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="O29" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S29" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="T29" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="V29" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="W29" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X29" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z29" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AC29" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD29" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
@@ -4219,10 +4219,10 @@
         </is>
       </c>
       <c r="AG29" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AH29" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AI29" t="n">
         <v>0</v>
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4922,65 +4922,65 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L35" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="T35" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="U35" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="V35" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="W35" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="X35" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Z35" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AC35" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD35" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AE35" t="inlineStr">
         <is>
@@ -4993,10 +4993,10 @@
         </is>
       </c>
       <c r="AG35" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AH35" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AI35" t="n">
         <v>0</v>
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,13 +5313,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>4.3</v>
+        <v>15</v>
       </c>
       <c r="M38" t="n">
-        <v>4.4</v>
+        <v>7.6</v>
       </c>
       <c r="N38" t="n">
-        <v>1.64</v>
+        <v>1.15</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5358,10 +5358,10 @@
         <v>2.75</v>
       </c>
       <c r="AA38" t="n">
-        <v>2.15</v>
+        <v>1.95</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.7</v>
+        <v>1.79</v>
       </c>
       <c r="AC38" t="n">
         <v>0</v>
@@ -5406,7 +5406,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,13 +5442,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5481,16 +5481,16 @@
         <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z39" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AA39" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB39" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC39" t="n">
         <v>0</v>
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Olympique Marseille</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,13 +5700,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1.56</v>
+        <v>3</v>
       </c>
       <c r="M41" t="n">
-        <v>4.3</v>
+        <v>3.83</v>
       </c>
       <c r="N41" t="n">
-        <v>5.1</v>
+        <v>2.1</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5739,16 +5739,16 @@
         <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Z41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA41" t="n">
         <v>2.25</v>
       </c>
-      <c r="AA41" t="n">
-        <v>0</v>
-      </c>
       <c r="AB41" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC41" t="n">
         <v>0</v>
@@ -5793,7 +5793,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,13 +5829,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5868,10 +5868,10 @@
         <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Z42" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AA42" t="n">
         <v>0</v>
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5958,13 +5958,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>3</v>
+        <v>1.56</v>
       </c>
       <c r="M43" t="n">
-        <v>3.83</v>
+        <v>4.1</v>
       </c>
       <c r="N43" t="n">
-        <v>2.1</v>
+        <v>5.4</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5997,16 +5997,16 @@
         <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Z43" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA43" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC43" t="n">
         <v>0</v>
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Olympique Marseille</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6216,13 +6216,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>15</v>
+        <v>1.56</v>
       </c>
       <c r="M45" t="n">
-        <v>7.6</v>
+        <v>4.3</v>
       </c>
       <c r="N45" t="n">
-        <v>1.15</v>
+        <v>5.1</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -6255,16 +6255,16 @@
         <v>0</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.44</v>
+        <v>1.63</v>
       </c>
       <c r="Z45" t="n">
-        <v>2.75</v>
+        <v>2.25</v>
       </c>
       <c r="AA45" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AC45" t="n">
         <v>0</v>

--- a/jogos_2025-09-30.xlsx
+++ b/jogos_2025-09-30.xlsx
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Sogdiana</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Sogdiana</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,13 +1572,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.86</v>
+        <v>19</v>
       </c>
       <c r="M9" t="n">
-        <v>3.84</v>
+        <v>8.9</v>
       </c>
       <c r="N9" t="n">
-        <v>3.7</v>
+        <v>1.11</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1611,16 +1611,16 @@
         <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.7</v>
+        <v>1.3</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.15</v>
+        <v>3.4</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,13 +1701,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>19</v>
+        <v>1.86</v>
       </c>
       <c r="M10" t="n">
-        <v>8.9</v>
+        <v>3.84</v>
       </c>
       <c r="N10" t="n">
-        <v>1.11</v>
+        <v>3.7</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1740,16 +1740,16 @@
         <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.3</v>
+        <v>1.7</v>
       </c>
       <c r="Z10" t="n">
-        <v>3.4</v>
+        <v>2.15</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -1923,22 +1923,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Wehen Wiesbaden</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,13 +1959,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -2004,10 +2004,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -2052,22 +2052,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Wehen Wiesbaden</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,13 +2088,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2127,16 +2127,16 @@
         <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2181,22 +2181,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Erzgebirge Aue</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,13 +2217,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2262,10 +2262,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -2439,22 +2439,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Erzgebirge Aue</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,13 +2475,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2514,16 +2514,16 @@
         <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mantova</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,13 +3378,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.8</v>
+        <v>2.15</v>
       </c>
       <c r="M23" t="n">
-        <v>3.7</v>
+        <v>3.35</v>
       </c>
       <c r="N23" t="n">
-        <v>4.3</v>
+        <v>3.45</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3417,10 +3417,10 @@
         <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.95</v>
+        <v>2.18</v>
       </c>
       <c r="Z23" t="n">
-        <v>1.85</v>
+        <v>1.7</v>
       </c>
       <c r="AA23" t="n">
         <v>0</v>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Mantova</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,13 +3507,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.15</v>
+        <v>1.8</v>
       </c>
       <c r="M24" t="n">
-        <v>3.35</v>
+        <v>3.7</v>
       </c>
       <c r="N24" t="n">
-        <v>3.45</v>
+        <v>4.3</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3546,10 +3546,10 @@
         <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>2.18</v>
+        <v>1.95</v>
       </c>
       <c r="Z24" t="n">
-        <v>1.7</v>
+        <v>1.85</v>
       </c>
       <c r="AA24" t="n">
         <v>0</v>
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Calcio Padova</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,13 +3636,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.15</v>
+        <v>2.6</v>
       </c>
       <c r="M25" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="N25" t="n">
-        <v>3.45</v>
+        <v>2.75</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3678,7 +3678,7 @@
         <v>2.2</v>
       </c>
       <c r="Z25" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AA25" t="n">
         <v>0</v>
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,13 +3894,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.6</v>
+        <v>3.6</v>
       </c>
       <c r="M27" t="n">
-        <v>3.25</v>
+        <v>3.45</v>
       </c>
       <c r="N27" t="n">
-        <v>2.75</v>
+        <v>2.05</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3933,10 +3933,10 @@
         <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>2.2</v>
+        <v>2.07</v>
       </c>
       <c r="Z27" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AA27" t="n">
         <v>0</v>
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Calcio Padova</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,14 +4023,14 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>3.6</v>
+        <v>2.15</v>
       </c>
       <c r="M28" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="N28" t="n">
         <v>3.45</v>
       </c>
-      <c r="N28" t="n">
-        <v>2.05</v>
-      </c>
       <c r="O28" t="n">
         <v>0</v>
       </c>
@@ -4062,10 +4062,10 @@
         <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>2.07</v>
+        <v>2.2</v>
       </c>
       <c r="Z28" t="n">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="AA28" t="n">
         <v>0</v>
@@ -4245,7 +4245,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4277,65 +4277,65 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S30" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="Z30" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AD30" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
@@ -4348,10 +4348,10 @@
         </is>
       </c>
       <c r="AG30" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AH30" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AI30" t="n">
         <v>0</v>
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4632,7 +4632,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4664,65 +4664,65 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L33" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>3.19</v>
+        <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="S33" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="T33" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="U33" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="V33" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W33" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="X33" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="Z33" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AC33" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AE33" t="inlineStr">
         <is>
@@ -4735,10 +4735,10 @@
         </is>
       </c>
       <c r="AG33" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AI33" t="n">
         <v>0</v>
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,13 +5313,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>15</v>
+        <v>1.35</v>
       </c>
       <c r="M38" t="n">
-        <v>7.6</v>
+        <v>5.3</v>
       </c>
       <c r="N38" t="n">
-        <v>1.15</v>
+        <v>7</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5352,16 +5352,16 @@
         <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="Z38" t="n">
-        <v>2.75</v>
+        <v>2.35</v>
       </c>
       <c r="AA38" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AC38" t="n">
         <v>0</v>
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Olympique Marseille</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,13 +5442,13 @@
         </is>
       </c>
       <c r="L39" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="M39" t="n">
         <v>4.3</v>
       </c>
-      <c r="M39" t="n">
-        <v>4.4</v>
-      </c>
       <c r="N39" t="n">
-        <v>1.64</v>
+        <v>5.1</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5481,16 +5481,16 @@
         <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.44</v>
+        <v>1.63</v>
       </c>
       <c r="Z39" t="n">
-        <v>2.75</v>
+        <v>2.25</v>
       </c>
       <c r="AA39" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC39" t="n">
         <v>0</v>
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,13 +5571,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>1.62</v>
+        <v>4.3</v>
       </c>
       <c r="M40" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="N40" t="n">
-        <v>4.9</v>
+        <v>1.64</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5610,16 +5610,16 @@
         <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.68</v>
+        <v>1.44</v>
       </c>
       <c r="Z40" t="n">
-        <v>2.18</v>
+        <v>2.75</v>
       </c>
       <c r="AA40" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB40" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -5793,7 +5793,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,13 +5829,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="M42" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5868,16 +5868,16 @@
         <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z42" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AA42" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB42" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC42" t="n">
         <v>0</v>
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5958,13 +5958,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>1.56</v>
+        <v>1.62</v>
       </c>
       <c r="M43" t="n">
         <v>4.1</v>
       </c>
       <c r="N43" t="n">
-        <v>5.4</v>
+        <v>4.9</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5997,10 +5997,10 @@
         <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.63</v>
+        <v>1.68</v>
       </c>
       <c r="Z43" t="n">
-        <v>2.25</v>
+        <v>2.18</v>
       </c>
       <c r="AA43" t="n">
         <v>0</v>
@@ -6051,7 +6051,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6061,12 +6061,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6087,13 +6087,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="N44" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -6126,10 +6126,10 @@
         <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z44" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AA44" t="n">
         <v>0</v>
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Olympique Marseille</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6219,10 +6219,10 @@
         <v>1.56</v>
       </c>
       <c r="M45" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="N45" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>

--- a/jogos_2025-09-30.xlsx
+++ b/jogos_2025-09-30.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK48"/>
+  <dimension ref="A1:AK47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -757,27 +757,27 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Kariobangi Sharks</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>KCB</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -877,7 +877,7 @@
         <v>0</v>
       </c>
       <c r="AK3" s="3" t="n">
-        <v>45930.41666666666</v>
+        <v>45930.45833333334</v>
       </c>
     </row>
     <row r="4">
@@ -1015,27 +1015,27 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Botev Plovdiv</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1052,65 +1052,65 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
@@ -1123,19 +1123,19 @@
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AK5" s="3" t="n">
-        <v>45930.45833333334</v>
+        <v>45930.47916666666</v>
       </c>
     </row>
     <row r="6">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Botev Plovdiv</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1181,65 +1181,65 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>4.6</v>
+        <v>19</v>
       </c>
       <c r="M6" t="n">
-        <v>3.5</v>
+        <v>8.9</v>
       </c>
       <c r="N6" t="n">
-        <v>1.82</v>
+        <v>1.11</v>
       </c>
       <c r="O6" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>2.25</v>
+        <v>1.3</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.65</v>
+        <v>3.4</v>
       </c>
       <c r="AA6" t="n">
-        <v>4</v>
+        <v>1.8</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.22</v>
+        <v>1.94</v>
       </c>
       <c r="AC6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
@@ -1252,19 +1252,19 @@
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AI6" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AK6" s="3" t="n">
-        <v>45930.47916666666</v>
+        <v>45930.57291666666</v>
       </c>
     </row>
     <row r="7">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Police</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ulinzi Stars</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1314,13 +1314,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1353,10 +1353,10 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AA7" t="n">
         <v>0</v>
@@ -1393,7 +1393,7 @@
         <v>0</v>
       </c>
       <c r="AK7" s="3" t="n">
-        <v>45930.5</v>
+        <v>45930.57291666666</v>
       </c>
     </row>
     <row r="8">
@@ -1402,12 +1402,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Wehen Wiesbaden</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1522,7 +1522,7 @@
         <v>0</v>
       </c>
       <c r="AK8" s="3" t="n">
-        <v>45930.5</v>
+        <v>45930.58333333334</v>
       </c>
     </row>
     <row r="9">
@@ -1531,12 +1531,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Havelse</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Waldhof Mannheim</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,13 +1572,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>8.9</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1611,16 +1611,16 @@
         <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -1651,7 +1651,7 @@
         <v>0</v>
       </c>
       <c r="AK9" s="3" t="n">
-        <v>45930.57291666666</v>
+        <v>45930.58333333334</v>
       </c>
     </row>
     <row r="10">
@@ -1660,27 +1660,27 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,13 +1701,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.86</v>
+        <v>1.56</v>
       </c>
       <c r="M10" t="n">
-        <v>3.84</v>
+        <v>4.2</v>
       </c>
       <c r="N10" t="n">
-        <v>3.7</v>
+        <v>4.2</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1740,16 +1740,16 @@
         <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -1780,7 +1780,7 @@
         <v>0</v>
       </c>
       <c r="AK10" s="3" t="n">
-        <v>45930.57291666666</v>
+        <v>45930.58333333334</v>
       </c>
     </row>
     <row r="11">
@@ -1794,22 +1794,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Havelse</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Waldhof Mannheim</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,13 +1830,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1869,16 +1869,16 @@
         <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -1923,22 +1923,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Hansa Rostock</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,13 +1959,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -2004,10 +2004,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Wehen Wiesbaden</t>
+          <t>Erzgebirge Aue</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>Saarbrucken</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Erzgebirge Aue</t>
+          <t>MSV Duisburg</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2305,12 +2305,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Saarbrucken</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>MSV Duisburg</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2425,7 +2425,7 @@
         <v>0</v>
       </c>
       <c r="AK15" s="3" t="n">
-        <v>45930.58333333334</v>
+        <v>45930.625</v>
       </c>
     </row>
     <row r="16">
@@ -2434,27 +2434,27 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,13 +2475,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2514,16 +2514,16 @@
         <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -2554,7 +2554,7 @@
         <v>0</v>
       </c>
       <c r="AK16" s="3" t="n">
-        <v>45930.58333333334</v>
+        <v>45930.625</v>
       </c>
     </row>
     <row r="17">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Hansa Rostock</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2683,7 +2683,7 @@
         <v>0</v>
       </c>
       <c r="AK17" s="3" t="n">
-        <v>45930.58333333334</v>
+        <v>45930.625</v>
       </c>
     </row>
     <row r="18">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2950,12 +2950,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Mantova</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3030,10 +3030,10 @@
         <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AA20" t="n">
         <v>0</v>
@@ -3070,7 +3070,7 @@
         <v>0</v>
       </c>
       <c r="AK20" s="3" t="n">
-        <v>45930.625</v>
+        <v>45930.64583333334</v>
       </c>
     </row>
     <row r="21">
@@ -3079,12 +3079,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,13 +3120,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3159,10 +3159,10 @@
         <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AA21" t="n">
         <v>0</v>
@@ -3199,7 +3199,7 @@
         <v>0</v>
       </c>
       <c r="AK21" s="3" t="n">
-        <v>45930.625</v>
+        <v>45930.64583333334</v>
       </c>
     </row>
     <row r="22">
@@ -3208,12 +3208,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Calcio Padova</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,13 +3249,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3288,10 +3288,10 @@
         <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AA22" t="n">
         <v>0</v>
@@ -3328,7 +3328,7 @@
         <v>0</v>
       </c>
       <c r="AK22" s="3" t="n">
-        <v>45930.625</v>
+        <v>45930.64583333334</v>
       </c>
     </row>
     <row r="23">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,10 +3378,10 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="M23" t="n">
-        <v>3.35</v>
+        <v>3.65</v>
       </c>
       <c r="N23" t="n">
         <v>3.45</v>
@@ -3417,10 +3417,10 @@
         <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>2.18</v>
+        <v>1.8</v>
       </c>
       <c r="Z23" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="AA23" t="n">
         <v>0</v>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mantova</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,13 +3507,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.8</v>
+        <v>2.15</v>
       </c>
       <c r="M24" t="n">
-        <v>3.7</v>
+        <v>3.35</v>
       </c>
       <c r="N24" t="n">
-        <v>4.3</v>
+        <v>3.45</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3546,10 +3546,10 @@
         <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.95</v>
+        <v>2.18</v>
       </c>
       <c r="Z24" t="n">
-        <v>1.85</v>
+        <v>1.7</v>
       </c>
       <c r="AA24" t="n">
         <v>0</v>
@@ -3724,12 +3724,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,13 +3765,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.05</v>
+        <v>2.13</v>
       </c>
       <c r="M26" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="N26" t="n">
-        <v>3.45</v>
+        <v>3.15</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3804,10 +3804,10 @@
         <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="Z26" t="n">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="AA26" t="n">
         <v>0</v>
@@ -3844,7 +3844,7 @@
         <v>0</v>
       </c>
       <c r="AK26" s="3" t="n">
-        <v>45930.64583333334</v>
+        <v>45930.65625</v>
       </c>
     </row>
     <row r="27">
@@ -3853,12 +3853,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,13 +3894,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>3.6</v>
+        <v>2.55</v>
       </c>
       <c r="M27" t="n">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="N27" t="n">
-        <v>2.05</v>
+        <v>2.8</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3933,10 +3933,10 @@
         <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>2.07</v>
+        <v>2.2</v>
       </c>
       <c r="Z27" t="n">
-        <v>1.75</v>
+        <v>1.68</v>
       </c>
       <c r="AA27" t="n">
         <v>0</v>
@@ -3973,7 +3973,7 @@
         <v>0</v>
       </c>
       <c r="AK27" s="3" t="n">
-        <v>45930.64583333334</v>
+        <v>45930.65625</v>
       </c>
     </row>
     <row r="28">
@@ -3982,12 +3982,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Calcio Padova</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4019,65 +4019,65 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.15</v>
+        <v>1.45</v>
       </c>
       <c r="M28" t="n">
-        <v>3.35</v>
+        <v>4.4</v>
       </c>
       <c r="N28" t="n">
-        <v>3.45</v>
+        <v>6.4</v>
       </c>
       <c r="O28" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="T28" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X28" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="Y28" t="n">
-        <v>2.2</v>
+        <v>1.65</v>
       </c>
       <c r="Z28" t="n">
-        <v>1.65</v>
+        <v>2.1</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD28" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
@@ -4090,10 +4090,10 @@
         </is>
       </c>
       <c r="AG28" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AH28" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AI28" t="n">
         <v>0</v>
@@ -4102,7 +4102,7 @@
         <v>0</v>
       </c>
       <c r="AK28" s="3" t="n">
-        <v>45930.64583333334</v>
+        <v>45930.65625</v>
       </c>
     </row>
     <row r="29">
@@ -4116,7 +4116,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4148,65 +4148,65 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.45</v>
+        <v>2.18</v>
       </c>
       <c r="M29" t="n">
-        <v>4.4</v>
+        <v>3.45</v>
       </c>
       <c r="N29" t="n">
-        <v>6.4</v>
+        <v>3.25</v>
       </c>
       <c r="O29" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="T29" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="U29" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="V29" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="W29" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="X29" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.65</v>
+        <v>2</v>
       </c>
       <c r="Z29" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="AA29" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
@@ -4219,10 +4219,10 @@
         </is>
       </c>
       <c r="AG29" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AH29" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AI29" t="n">
         <v>0</v>
@@ -4245,7 +4245,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4277,65 +4277,65 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L30" t="n">
-        <v>3</v>
+        <v>1.9</v>
       </c>
       <c r="M30" t="n">
-        <v>3.19</v>
+        <v>3.6</v>
       </c>
       <c r="N30" t="n">
-        <v>2.31</v>
+        <v>4</v>
       </c>
       <c r="O30" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="T30" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="U30" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="V30" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W30" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="X30" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>2.01</v>
+        <v>1.97</v>
       </c>
       <c r="Z30" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AA30" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AC30" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
@@ -4348,10 +4348,10 @@
         </is>
       </c>
       <c r="AG30" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AI30" t="n">
         <v>0</v>
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,13 +4410,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4449,10 +4449,10 @@
         <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Z31" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA31" t="n">
         <v>0</v>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4535,65 +4535,65 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="O32" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S32" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="T32" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U32" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="V32" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W32" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="X32" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="Y32" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="Z32" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AA32" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AB32" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AC32" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AD32" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AE32" t="inlineStr">
         <is>
@@ -4606,10 +4606,10 @@
         </is>
       </c>
       <c r="AG32" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AH32" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AI32" t="n">
         <v>0</v>
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,13 +4668,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4707,10 +4707,10 @@
         <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Z33" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA33" t="n">
         <v>0</v>
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,13 +4797,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4836,10 +4836,10 @@
         <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="Z34" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AA34" t="n">
         <v>0</v>
@@ -4885,12 +4885,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,13 +4926,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4965,10 +4965,10 @@
         <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z35" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AA35" t="n">
         <v>0</v>
@@ -5005,7 +5005,7 @@
         <v>0</v>
       </c>
       <c r="AK35" s="3" t="n">
-        <v>45930.65625</v>
+        <v>45930.66666666666</v>
       </c>
     </row>
     <row r="36">
@@ -5014,12 +5014,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Olympique Marseille</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,13 +5055,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5094,10 +5094,10 @@
         <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Z36" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA36" t="n">
         <v>0</v>
@@ -5134,7 +5134,7 @@
         <v>0</v>
       </c>
       <c r="AK36" s="3" t="n">
-        <v>45930.65625</v>
+        <v>45930.66666666666</v>
       </c>
     </row>
     <row r="37">
@@ -5143,12 +5143,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,13 +5184,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>3.83</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5229,10 +5229,10 @@
         <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB37" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC37" t="n">
         <v>0</v>
@@ -5263,7 +5263,7 @@
         <v>0</v>
       </c>
       <c r="AK37" s="3" t="n">
-        <v>45930.65625</v>
+        <v>45930.66666666666</v>
       </c>
     </row>
     <row r="38">
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,13 +5313,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>1.35</v>
+        <v>1.62</v>
       </c>
       <c r="M38" t="n">
-        <v>5.3</v>
+        <v>4.1</v>
       </c>
       <c r="N38" t="n">
-        <v>7</v>
+        <v>4.9</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5352,10 +5352,10 @@
         <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.6</v>
+        <v>1.68</v>
       </c>
       <c r="Z38" t="n">
-        <v>2.35</v>
+        <v>2.18</v>
       </c>
       <c r="AA38" t="n">
         <v>0</v>
@@ -5406,7 +5406,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Olympique Marseille</t>
+          <t>Kariobangi Sharks</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>KCB</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,13 +5442,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5481,10 +5481,10 @@
         <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Z39" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AA39" t="n">
         <v>0</v>
@@ -5664,7 +5664,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,13 +5700,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>3</v>
+        <v>2.45</v>
       </c>
       <c r="M41" t="n">
-        <v>3.83</v>
+        <v>3.15</v>
       </c>
       <c r="N41" t="n">
-        <v>2.1</v>
+        <v>3.05</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5733,22 +5733,22 @@
         <v>0</v>
       </c>
       <c r="W41" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="X41" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Y41" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="Z41" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AA41" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC41" t="n">
         <v>0</v>
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,13 +5829,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>15</v>
+        <v>1.56</v>
       </c>
       <c r="M42" t="n">
-        <v>7.6</v>
+        <v>4.1</v>
       </c>
       <c r="N42" t="n">
-        <v>1.15</v>
+        <v>5.4</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5868,16 +5868,16 @@
         <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.44</v>
+        <v>1.63</v>
       </c>
       <c r="Z42" t="n">
-        <v>2.75</v>
+        <v>2.25</v>
       </c>
       <c r="AA42" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AC42" t="n">
         <v>0</v>
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5958,13 +5958,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>1.62</v>
+        <v>15</v>
       </c>
       <c r="M43" t="n">
-        <v>4.1</v>
+        <v>7.6</v>
       </c>
       <c r="N43" t="n">
-        <v>4.9</v>
+        <v>1.15</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5997,16 +5997,16 @@
         <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.68</v>
+        <v>1.44</v>
       </c>
       <c r="Z43" t="n">
-        <v>2.18</v>
+        <v>2.75</v>
       </c>
       <c r="AA43" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB43" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC43" t="n">
         <v>0</v>
@@ -6046,12 +6046,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6061,12 +6061,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Police</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Ulinzi Stars</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6166,7 +6166,7 @@
         <v>0</v>
       </c>
       <c r="AK44" s="3" t="n">
-        <v>45930.66666666666</v>
+        <v>45930.75</v>
       </c>
     </row>
     <row r="45">
@@ -6175,27 +6175,27 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6216,13 +6216,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="M45" t="n">
-        <v>4.1</v>
+        <v>4.8</v>
       </c>
       <c r="N45" t="n">
-        <v>5.4</v>
+        <v>4.9</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -6255,16 +6255,16 @@
         <v>0</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.63</v>
+        <v>1.4</v>
       </c>
       <c r="Z45" t="n">
-        <v>2.25</v>
+        <v>2.75</v>
       </c>
       <c r="AA45" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB45" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AC45" t="n">
         <v>0</v>
@@ -6295,7 +6295,7 @@
         <v>0</v>
       </c>
       <c r="AK45" s="3" t="n">
-        <v>45930.66666666666</v>
+        <v>45930.85416666666</v>
       </c>
     </row>
     <row r="46">
@@ -6304,12 +6304,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6319,12 +6319,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6345,13 +6345,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>1.57</v>
+        <v>1.4</v>
       </c>
       <c r="M46" t="n">
-        <v>4.8</v>
+        <v>4.2</v>
       </c>
       <c r="N46" t="n">
-        <v>4.9</v>
+        <v>6</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -6384,16 +6384,16 @@
         <v>0</v>
       </c>
       <c r="Y46" t="n">
-        <v>1.4</v>
+        <v>1.86</v>
       </c>
       <c r="Z46" t="n">
-        <v>2.75</v>
+        <v>1.84</v>
       </c>
       <c r="AA46" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AC46" t="n">
         <v>0</v>
@@ -6424,7 +6424,7 @@
         <v>0</v>
       </c>
       <c r="AK46" s="3" t="n">
-        <v>45930.85416666666</v>
+        <v>45930.89583333334</v>
       </c>
     </row>
     <row r="47">
@@ -6433,12 +6433,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:35</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -6448,12 +6448,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6474,13 +6474,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>1.45</v>
+        <v>1.92</v>
       </c>
       <c r="M47" t="n">
-        <v>4.4</v>
+        <v>3.35</v>
       </c>
       <c r="N47" t="n">
-        <v>7.4</v>
+        <v>3.8</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6513,10 +6513,10 @@
         <v>0</v>
       </c>
       <c r="Y47" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Z47" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AA47" t="n">
         <v>0</v>
@@ -6553,135 +6553,6 @@
         <v>0</v>
       </c>
       <c r="AK47" s="3" t="n">
-        <v>45930.89583333334</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="2" t="n">
-        <v>45930</v>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>21:35</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Brazil Serie B</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>Goiás</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>Atlético GO</t>
-        </is>
-      </c>
-      <c r="G48" t="n">
-        <v>0</v>
-      </c>
-      <c r="H48" t="n">
-        <v>0</v>
-      </c>
-      <c r="I48" t="n">
-        <v>0</v>
-      </c>
-      <c r="J48" t="n">
-        <v>0</v>
-      </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L48" t="n">
-        <v>0</v>
-      </c>
-      <c r="M48" t="n">
-        <v>0</v>
-      </c>
-      <c r="N48" t="n">
-        <v>0</v>
-      </c>
-      <c r="O48" t="n">
-        <v>0</v>
-      </c>
-      <c r="P48" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q48" t="n">
-        <v>0</v>
-      </c>
-      <c r="R48" t="n">
-        <v>0</v>
-      </c>
-      <c r="S48" t="n">
-        <v>0</v>
-      </c>
-      <c r="T48" t="n">
-        <v>0</v>
-      </c>
-      <c r="U48" t="n">
-        <v>0</v>
-      </c>
-      <c r="V48" t="n">
-        <v>0</v>
-      </c>
-      <c r="W48" t="n">
-        <v>0</v>
-      </c>
-      <c r="X48" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y48" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE48" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF48" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK48" s="3" t="n">
         <v>45930.89930555555</v>
       </c>
     </row>

--- a/jogos_2025-09-30.xlsx
+++ b/jogos_2025-09-30.xlsx
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Sogdiana</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sogdiana</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1665,22 +1665,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Erzgebirge Aue</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,13 +1701,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1746,10 +1746,10 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -1794,22 +1794,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Hansa Rostock</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,13 +1830,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1869,16 +1869,16 @@
         <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -1923,22 +1923,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Hansa Rostock</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,13 +1959,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1998,16 +1998,16 @@
         <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -2052,22 +2052,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Erzgebirge Aue</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,13 +2088,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2133,10 +2133,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mantova</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.8</v>
+        <v>3.6</v>
       </c>
       <c r="M20" t="n">
-        <v>3.7</v>
+        <v>3.45</v>
       </c>
       <c r="N20" t="n">
-        <v>4.3</v>
+        <v>2.05</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3030,10 +3030,10 @@
         <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.95</v>
+        <v>2.07</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AA20" t="n">
         <v>0</v>
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Calcio Padova</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,14 +3120,14 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>3.6</v>
+        <v>2.15</v>
       </c>
       <c r="M21" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="N21" t="n">
         <v>3.45</v>
       </c>
-      <c r="N21" t="n">
-        <v>2.05</v>
-      </c>
       <c r="O21" t="n">
         <v>0</v>
       </c>
@@ -3159,10 +3159,10 @@
         <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>2.07</v>
+        <v>2.2</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="AA21" t="n">
         <v>0</v>
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Calcio Padova</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3288,10 +3288,10 @@
         <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="Z22" t="n">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="AA22" t="n">
         <v>0</v>
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,13 +3378,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.05</v>
+        <v>2.6</v>
       </c>
       <c r="M23" t="n">
-        <v>3.65</v>
+        <v>3.25</v>
       </c>
       <c r="N23" t="n">
-        <v>3.45</v>
+        <v>2.75</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3417,10 +3417,10 @@
         <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="Z23" t="n">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="AA23" t="n">
         <v>0</v>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,10 +3507,10 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="M24" t="n">
-        <v>3.35</v>
+        <v>3.65</v>
       </c>
       <c r="N24" t="n">
         <v>3.45</v>
@@ -3546,10 +3546,10 @@
         <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>2.18</v>
+        <v>1.8</v>
       </c>
       <c r="Z24" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="AA24" t="n">
         <v>0</v>
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>Mantova</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,13 +3636,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.6</v>
+        <v>1.8</v>
       </c>
       <c r="M25" t="n">
-        <v>3.25</v>
+        <v>3.7</v>
       </c>
       <c r="N25" t="n">
-        <v>2.75</v>
+        <v>4.3</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3675,10 +3675,10 @@
         <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>2.2</v>
+        <v>1.95</v>
       </c>
       <c r="Z25" t="n">
-        <v>1.67</v>
+        <v>1.85</v>
       </c>
       <c r="AA25" t="n">
         <v>0</v>
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,13 +3765,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.13</v>
+        <v>2.55</v>
       </c>
       <c r="M26" t="n">
-        <v>3.75</v>
+        <v>3.3</v>
       </c>
       <c r="N26" t="n">
-        <v>3.15</v>
+        <v>2.8</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3804,10 +3804,10 @@
         <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.7</v>
+        <v>2.2</v>
       </c>
       <c r="Z26" t="n">
-        <v>2.15</v>
+        <v>1.68</v>
       </c>
       <c r="AA26" t="n">
         <v>0</v>
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,13 +3894,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.55</v>
+        <v>3.2</v>
       </c>
       <c r="M27" t="n">
-        <v>3.3</v>
+        <v>3.55</v>
       </c>
       <c r="N27" t="n">
-        <v>2.8</v>
+        <v>2.2</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3933,10 +3933,10 @@
         <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>2.2</v>
+        <v>1.88</v>
       </c>
       <c r="Z27" t="n">
-        <v>1.68</v>
+        <v>1.92</v>
       </c>
       <c r="AA27" t="n">
         <v>0</v>
@@ -3987,7 +3987,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4019,65 +4019,65 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.45</v>
+        <v>1.3</v>
       </c>
       <c r="M28" t="n">
-        <v>4.4</v>
+        <v>5.4</v>
       </c>
       <c r="N28" t="n">
-        <v>6.4</v>
+        <v>10.5</v>
       </c>
       <c r="O28" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="T28" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="U28" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="V28" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="W28" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="X28" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="Z28" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AA28" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
@@ -4090,10 +4090,10 @@
         </is>
       </c>
       <c r="AG28" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AH28" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AI28" t="n">
         <v>0</v>
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,13 +4152,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.18</v>
+        <v>2.13</v>
       </c>
       <c r="M29" t="n">
-        <v>3.45</v>
+        <v>3.75</v>
       </c>
       <c r="N29" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -4191,10 +4191,10 @@
         <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="Z29" t="n">
-        <v>1.8</v>
+        <v>2.15</v>
       </c>
       <c r="AA29" t="n">
         <v>0</v>
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,13 +4281,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.9</v>
+        <v>1.63</v>
       </c>
       <c r="M30" t="n">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="N30" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4320,10 +4320,10 @@
         <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.97</v>
+        <v>1.68</v>
       </c>
       <c r="Z30" t="n">
-        <v>1.83</v>
+        <v>2.2</v>
       </c>
       <c r="AA30" t="n">
         <v>0</v>
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,13 +4410,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.3</v>
+        <v>1.9</v>
       </c>
       <c r="M31" t="n">
-        <v>5.4</v>
+        <v>3.6</v>
       </c>
       <c r="N31" t="n">
-        <v>10.5</v>
+        <v>4</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4449,10 +4449,10 @@
         <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.67</v>
+        <v>1.97</v>
       </c>
       <c r="Z31" t="n">
-        <v>2.2</v>
+        <v>1.83</v>
       </c>
       <c r="AA31" t="n">
         <v>0</v>
@@ -4632,7 +4632,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4664,65 +4664,65 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.63</v>
+        <v>1.45</v>
       </c>
       <c r="M33" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="N33" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="O33" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="P33" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="R33" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S33" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="V33" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W33" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="X33" t="n">
         <v>4.2</v>
       </c>
-      <c r="N33" t="n">
-        <v>5</v>
-      </c>
-      <c r="O33" t="n">
-        <v>0</v>
-      </c>
-      <c r="P33" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>0</v>
-      </c>
-      <c r="R33" t="n">
-        <v>0</v>
-      </c>
-      <c r="S33" t="n">
-        <v>0</v>
-      </c>
-      <c r="T33" t="n">
-        <v>0</v>
-      </c>
-      <c r="U33" t="n">
-        <v>0</v>
-      </c>
-      <c r="V33" t="n">
-        <v>0</v>
-      </c>
-      <c r="W33" t="n">
-        <v>0</v>
-      </c>
-      <c r="X33" t="n">
-        <v>0</v>
-      </c>
       <c r="Y33" t="n">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="Z33" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AA33" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AB33" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AC33" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD33" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AE33" t="inlineStr">
         <is>
@@ -4735,10 +4735,10 @@
         </is>
       </c>
       <c r="AG33" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AH33" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AI33" t="n">
         <v>0</v>
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,13 +4797,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>3.2</v>
+        <v>2.18</v>
       </c>
       <c r="M34" t="n">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="N34" t="n">
-        <v>2.2</v>
+        <v>3.25</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4836,10 +4836,10 @@
         <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="Z34" t="n">
-        <v>1.92</v>
+        <v>1.8</v>
       </c>
       <c r="AA34" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Kariobangi Sharks</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>KCB</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,13 +4926,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4965,10 +4965,10 @@
         <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z35" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AA35" t="n">
         <v>0</v>
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Olympique Marseille</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,13 +5055,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>1.56</v>
+        <v>3</v>
       </c>
       <c r="M36" t="n">
-        <v>4.3</v>
+        <v>3.83</v>
       </c>
       <c r="N36" t="n">
-        <v>5.1</v>
+        <v>2.1</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5094,16 +5094,16 @@
         <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Z36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA36" t="n">
         <v>2.25</v>
       </c>
-      <c r="AA36" t="n">
-        <v>0</v>
-      </c>
       <c r="AB36" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC36" t="n">
         <v>0</v>
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,13 +5184,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>3</v>
+        <v>1.35</v>
       </c>
       <c r="M37" t="n">
-        <v>3.83</v>
+        <v>5.3</v>
       </c>
       <c r="N37" t="n">
-        <v>2.1</v>
+        <v>7</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5223,16 +5223,16 @@
         <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z37" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AA37" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC37" t="n">
         <v>0</v>
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,13 +5313,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>1.62</v>
+        <v>15</v>
       </c>
       <c r="M38" t="n">
-        <v>4.1</v>
+        <v>7.6</v>
       </c>
       <c r="N38" t="n">
-        <v>4.9</v>
+        <v>1.15</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5352,16 +5352,16 @@
         <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.68</v>
+        <v>1.44</v>
       </c>
       <c r="Z38" t="n">
-        <v>2.18</v>
+        <v>2.75</v>
       </c>
       <c r="AA38" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB38" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC38" t="n">
         <v>0</v>
@@ -5406,7 +5406,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Kariobangi Sharks</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>KCB</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,13 +5442,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5481,10 +5481,10 @@
         <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Z39" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA39" t="n">
         <v>0</v>
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,13 +5571,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>4.3</v>
+        <v>1.62</v>
       </c>
       <c r="M40" t="n">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="N40" t="n">
-        <v>1.64</v>
+        <v>4.9</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5610,16 +5610,16 @@
         <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.44</v>
+        <v>1.68</v>
       </c>
       <c r="Z40" t="n">
-        <v>2.75</v>
+        <v>2.18</v>
       </c>
       <c r="AA40" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -5664,7 +5664,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Olympique Marseille</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,13 +5700,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>2.45</v>
+        <v>1.56</v>
       </c>
       <c r="M41" t="n">
-        <v>3.15</v>
+        <v>4.3</v>
       </c>
       <c r="N41" t="n">
-        <v>3.05</v>
+        <v>5.1</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5733,16 +5733,16 @@
         <v>0</v>
       </c>
       <c r="W41" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="X41" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>2.52</v>
+        <v>1.63</v>
       </c>
       <c r="Z41" t="n">
-        <v>1.52</v>
+        <v>2.25</v>
       </c>
       <c r="AA41" t="n">
         <v>0</v>
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,13 +5829,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>1.56</v>
+        <v>4.3</v>
       </c>
       <c r="M42" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="N42" t="n">
-        <v>5.4</v>
+        <v>1.64</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5868,16 +5868,16 @@
         <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.63</v>
+        <v>1.44</v>
       </c>
       <c r="Z42" t="n">
-        <v>2.25</v>
+        <v>2.75</v>
       </c>
       <c r="AA42" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB42" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC42" t="n">
         <v>0</v>
@@ -5922,7 +5922,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5958,13 +5958,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>15</v>
+        <v>2.45</v>
       </c>
       <c r="M43" t="n">
-        <v>7.6</v>
+        <v>3.15</v>
       </c>
       <c r="N43" t="n">
-        <v>1.15</v>
+        <v>3.05</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5991,22 +5991,22 @@
         <v>0</v>
       </c>
       <c r="W43" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="X43" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.44</v>
+        <v>2.52</v>
       </c>
       <c r="Z43" t="n">
-        <v>2.75</v>
+        <v>1.52</v>
       </c>
       <c r="AA43" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AC43" t="n">
         <v>0</v>

--- a/jogos_2025-09-30.xlsx
+++ b/jogos_2025-09-30.xlsx
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1185,13 +1185,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>19</v>
+        <v>1.86</v>
       </c>
       <c r="M6" t="n">
-        <v>8.9</v>
+        <v>3.84</v>
       </c>
       <c r="N6" t="n">
-        <v>1.11</v>
+        <v>3.7</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1224,16 +1224,16 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.3</v>
+        <v>1.7</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.4</v>
+        <v>2.15</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1314,13 +1314,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.86</v>
+        <v>19</v>
       </c>
       <c r="M7" t="n">
-        <v>3.84</v>
+        <v>8.9</v>
       </c>
       <c r="N7" t="n">
-        <v>3.7</v>
+        <v>1.11</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1353,16 +1353,16 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.7</v>
+        <v>1.3</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.15</v>
+        <v>3.4</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1536,22 +1536,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Havelse</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Waldhof Mannheim</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,13 +1572,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1617,10 +1617,10 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -1665,22 +1665,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Erzgebirge Aue</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,13 +1701,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1740,16 +1740,16 @@
         <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Hansa Rostock</t>
+          <t>Saarbrucken</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>MSV Duisburg</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1923,22 +1923,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Hansa Rostock</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,13 +1959,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1998,16 +1998,16 @@
         <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -2052,22 +2052,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Erzgebirge Aue</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,13 +2088,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2133,10 +2133,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Saarbrucken</t>
+          <t>Havelse</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>MSV Duisburg</t>
+          <t>Waldhof Mannheim</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>3.6</v>
+        <v>2.6</v>
       </c>
       <c r="M20" t="n">
-        <v>3.45</v>
+        <v>3.25</v>
       </c>
       <c r="N20" t="n">
-        <v>2.05</v>
+        <v>2.75</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3030,10 +3030,10 @@
         <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>2.07</v>
+        <v>2.2</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AA20" t="n">
         <v>0</v>
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Calcio Padova</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3159,10 +3159,10 @@
         <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="AA21" t="n">
         <v>0</v>
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Calcio Padova</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3288,10 +3288,10 @@
         <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="Z22" t="n">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AA22" t="n">
         <v>0</v>
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,13 +3378,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.6</v>
+        <v>2.05</v>
       </c>
       <c r="M23" t="n">
-        <v>3.25</v>
+        <v>3.65</v>
       </c>
       <c r="N23" t="n">
-        <v>2.75</v>
+        <v>3.45</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3417,10 +3417,10 @@
         <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="Z23" t="n">
-        <v>1.67</v>
+        <v>2</v>
       </c>
       <c r="AA23" t="n">
         <v>0</v>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Mantova</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,13 +3507,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.05</v>
+        <v>1.8</v>
       </c>
       <c r="M24" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="N24" t="n">
-        <v>3.45</v>
+        <v>4.3</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3546,10 +3546,10 @@
         <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="Z24" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AA24" t="n">
         <v>0</v>
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mantova</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,13 +3636,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.8</v>
+        <v>3.6</v>
       </c>
       <c r="M25" t="n">
-        <v>3.7</v>
+        <v>3.45</v>
       </c>
       <c r="N25" t="n">
-        <v>4.3</v>
+        <v>2.05</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3675,10 +3675,10 @@
         <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.95</v>
+        <v>2.07</v>
       </c>
       <c r="Z25" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AA25" t="n">
         <v>0</v>
@@ -3729,7 +3729,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3761,65 +3761,65 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.55</v>
+        <v>1.45</v>
       </c>
       <c r="M26" t="n">
-        <v>3.3</v>
+        <v>4.4</v>
       </c>
       <c r="N26" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="O26" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="P26" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S26" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="V26" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W26" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="X26" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AA26" t="n">
         <v>2.8</v>
       </c>
-      <c r="O26" t="n">
-        <v>0</v>
-      </c>
-      <c r="P26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>0</v>
-      </c>
-      <c r="R26" t="n">
-        <v>0</v>
-      </c>
-      <c r="S26" t="n">
-        <v>0</v>
-      </c>
-      <c r="T26" t="n">
-        <v>0</v>
-      </c>
-      <c r="U26" t="n">
-        <v>0</v>
-      </c>
-      <c r="V26" t="n">
-        <v>0</v>
-      </c>
-      <c r="W26" t="n">
-        <v>0</v>
-      </c>
-      <c r="X26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>0</v>
-      </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AC26" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD26" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
@@ -3832,10 +3832,10 @@
         </is>
       </c>
       <c r="AG26" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AH26" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AI26" t="n">
         <v>0</v>
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,49 +3894,49 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>3.2</v>
+        <v>2.55</v>
       </c>
       <c r="M27" t="n">
-        <v>3.55</v>
+        <v>3.3</v>
       </c>
       <c r="N27" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>0</v>
+      </c>
+      <c r="R27" t="n">
+        <v>0</v>
+      </c>
+      <c r="S27" t="n">
+        <v>0</v>
+      </c>
+      <c r="T27" t="n">
+        <v>0</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0</v>
+      </c>
+      <c r="V27" t="n">
+        <v>0</v>
+      </c>
+      <c r="W27" t="n">
+        <v>0</v>
+      </c>
+      <c r="X27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y27" t="n">
         <v>2.2</v>
       </c>
-      <c r="O27" t="n">
-        <v>0</v>
-      </c>
-      <c r="P27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>0</v>
-      </c>
-      <c r="R27" t="n">
-        <v>0</v>
-      </c>
-      <c r="S27" t="n">
-        <v>0</v>
-      </c>
-      <c r="T27" t="n">
-        <v>0</v>
-      </c>
-      <c r="U27" t="n">
-        <v>0</v>
-      </c>
-      <c r="V27" t="n">
-        <v>0</v>
-      </c>
-      <c r="W27" t="n">
-        <v>0</v>
-      </c>
-      <c r="X27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>1.88</v>
-      </c>
       <c r="Z27" t="n">
-        <v>1.92</v>
+        <v>1.68</v>
       </c>
       <c r="AA27" t="n">
         <v>0</v>
@@ -3987,7 +3987,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4019,65 +4019,65 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.3</v>
+        <v>3</v>
       </c>
       <c r="M28" t="n">
-        <v>5.4</v>
+        <v>3.19</v>
       </c>
       <c r="N28" t="n">
-        <v>10.5</v>
+        <v>2.31</v>
       </c>
       <c r="O28" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="T28" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="X28" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.67</v>
+        <v>2.01</v>
       </c>
       <c r="Z28" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AD28" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
@@ -4090,10 +4090,10 @@
         </is>
       </c>
       <c r="AG28" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AH28" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AI28" t="n">
         <v>0</v>
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,13 +4152,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.13</v>
+        <v>2.18</v>
       </c>
       <c r="M29" t="n">
-        <v>3.75</v>
+        <v>3.45</v>
       </c>
       <c r="N29" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -4191,10 +4191,10 @@
         <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="Z29" t="n">
-        <v>2.15</v>
+        <v>1.8</v>
       </c>
       <c r="AA29" t="n">
         <v>0</v>
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,13 +4281,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.63</v>
+        <v>2.13</v>
       </c>
       <c r="M30" t="n">
-        <v>4.2</v>
+        <v>3.75</v>
       </c>
       <c r="N30" t="n">
-        <v>5</v>
+        <v>3.15</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4320,10 +4320,10 @@
         <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="Z30" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AA30" t="n">
         <v>0</v>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4535,65 +4535,65 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L32" t="n">
-        <v>3</v>
+        <v>1.63</v>
       </c>
       <c r="M32" t="n">
-        <v>3.19</v>
+        <v>4.2</v>
       </c>
       <c r="N32" t="n">
-        <v>2.31</v>
+        <v>5</v>
       </c>
       <c r="O32" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="T32" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="U32" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="V32" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W32" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="X32" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>2.01</v>
+        <v>1.68</v>
       </c>
       <c r="Z32" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="AA32" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AC32" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AE32" t="inlineStr">
         <is>
@@ -4606,10 +4606,10 @@
         </is>
       </c>
       <c r="AG32" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AI32" t="n">
         <v>0</v>
@@ -4632,7 +4632,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4664,65 +4664,65 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.45</v>
+        <v>1.3</v>
       </c>
       <c r="M33" t="n">
-        <v>4.4</v>
+        <v>5.4</v>
       </c>
       <c r="N33" t="n">
-        <v>6.4</v>
+        <v>10.5</v>
       </c>
       <c r="O33" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="S33" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="T33" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="U33" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="V33" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="W33" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="X33" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="Z33" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AA33" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AC33" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AE33" t="inlineStr">
         <is>
@@ -4735,10 +4735,10 @@
         </is>
       </c>
       <c r="AG33" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AH33" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AI33" t="n">
         <v>0</v>
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,13 +4797,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.18</v>
+        <v>3.2</v>
       </c>
       <c r="M34" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="N34" t="n">
-        <v>3.25</v>
+        <v>2.2</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4836,10 +4836,10 @@
         <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="Z34" t="n">
-        <v>1.8</v>
+        <v>1.92</v>
       </c>
       <c r="AA34" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Kariobangi Sharks</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>KCB</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,13 +4926,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4965,10 +4965,10 @@
         <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z35" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AA35" t="n">
         <v>0</v>
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,13 +5055,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>3</v>
+        <v>1.56</v>
       </c>
       <c r="M36" t="n">
-        <v>3.83</v>
+        <v>4.1</v>
       </c>
       <c r="N36" t="n">
-        <v>2.1</v>
+        <v>5.4</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5094,16 +5094,16 @@
         <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Z36" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA36" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC36" t="n">
         <v>0</v>
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Olympique Marseille</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,13 +5184,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>1.35</v>
+        <v>1.56</v>
       </c>
       <c r="M37" t="n">
-        <v>5.3</v>
+        <v>4.3</v>
       </c>
       <c r="N37" t="n">
-        <v>7</v>
+        <v>5.1</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5223,10 +5223,10 @@
         <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="Z37" t="n">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="AA37" t="n">
         <v>0</v>
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,13 +5313,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>15</v>
+        <v>1.62</v>
       </c>
       <c r="M38" t="n">
-        <v>7.6</v>
+        <v>4.1</v>
       </c>
       <c r="N38" t="n">
-        <v>1.15</v>
+        <v>4.9</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5352,16 +5352,16 @@
         <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.44</v>
+        <v>1.68</v>
       </c>
       <c r="Z38" t="n">
-        <v>2.75</v>
+        <v>2.18</v>
       </c>
       <c r="AA38" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AC38" t="n">
         <v>0</v>
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,13 +5442,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>1.56</v>
+        <v>4.3</v>
       </c>
       <c r="M39" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="N39" t="n">
-        <v>5.4</v>
+        <v>1.64</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5481,16 +5481,16 @@
         <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.63</v>
+        <v>1.44</v>
       </c>
       <c r="Z39" t="n">
-        <v>2.25</v>
+        <v>2.75</v>
       </c>
       <c r="AA39" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB39" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC39" t="n">
         <v>0</v>
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,13 +5571,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>1.62</v>
+        <v>3</v>
       </c>
       <c r="M40" t="n">
-        <v>4.1</v>
+        <v>3.83</v>
       </c>
       <c r="N40" t="n">
-        <v>4.9</v>
+        <v>2.1</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5610,16 +5610,16 @@
         <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="Z40" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB40" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Olympique Marseille</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,13 +5700,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1.56</v>
+        <v>15</v>
       </c>
       <c r="M41" t="n">
-        <v>4.3</v>
+        <v>7.6</v>
       </c>
       <c r="N41" t="n">
-        <v>5.1</v>
+        <v>1.15</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5739,16 +5739,16 @@
         <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.63</v>
+        <v>1.44</v>
       </c>
       <c r="Z41" t="n">
-        <v>2.25</v>
+        <v>2.75</v>
       </c>
       <c r="AA41" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB41" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC41" t="n">
         <v>0</v>
@@ -5793,7 +5793,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Kariobangi Sharks</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>KCB</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,13 +5829,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5868,16 +5868,16 @@
         <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="Z42" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC42" t="n">
         <v>0</v>

--- a/jogos_2025-09-30.xlsx
+++ b/jogos_2025-09-30.xlsx
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>Havelse</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Wehen Wiesbaden</t>
+          <t>Waldhof Mannheim</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1536,22 +1536,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Erzgebirge Aue</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,13 +1572,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1617,10 +1617,10 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -1665,22 +1665,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Wehen Wiesbaden</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,13 +1701,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1740,16 +1740,16 @@
         <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -1923,22 +1923,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Hansa Rostock</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,13 +1959,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -2004,10 +2004,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -2052,22 +2052,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Erzgebirge Aue</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,13 +2088,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2127,16 +2127,16 @@
         <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Havelse</t>
+          <t>Hansa Rostock</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Waldhof Mannheim</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.6</v>
+        <v>3.6</v>
       </c>
       <c r="M20" t="n">
-        <v>3.25</v>
+        <v>3.45</v>
       </c>
       <c r="N20" t="n">
-        <v>2.75</v>
+        <v>2.05</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3030,10 +3030,10 @@
         <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>2.2</v>
+        <v>2.07</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AA20" t="n">
         <v>0</v>
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Calcio Padova</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Mantova</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,13 +3249,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.15</v>
+        <v>1.8</v>
       </c>
       <c r="M22" t="n">
-        <v>3.35</v>
+        <v>3.7</v>
       </c>
       <c r="N22" t="n">
-        <v>3.45</v>
+        <v>4.3</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3288,10 +3288,10 @@
         <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>2.2</v>
+        <v>1.95</v>
       </c>
       <c r="Z22" t="n">
-        <v>1.65</v>
+        <v>1.85</v>
       </c>
       <c r="AA22" t="n">
         <v>0</v>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mantova</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,13 +3507,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.8</v>
+        <v>2.6</v>
       </c>
       <c r="M24" t="n">
-        <v>3.7</v>
+        <v>3.25</v>
       </c>
       <c r="N24" t="n">
-        <v>4.3</v>
+        <v>2.75</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3546,10 +3546,10 @@
         <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.95</v>
+        <v>2.2</v>
       </c>
       <c r="Z24" t="n">
-        <v>1.85</v>
+        <v>1.67</v>
       </c>
       <c r="AA24" t="n">
         <v>0</v>
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Calcio Padova</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,14 +3636,14 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>3.6</v>
+        <v>2.15</v>
       </c>
       <c r="M25" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="N25" t="n">
         <v>3.45</v>
       </c>
-      <c r="N25" t="n">
-        <v>2.05</v>
-      </c>
       <c r="O25" t="n">
         <v>0</v>
       </c>
@@ -3675,10 +3675,10 @@
         <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>2.07</v>
+        <v>2.2</v>
       </c>
       <c r="Z25" t="n">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="AA25" t="n">
         <v>0</v>
@@ -3729,7 +3729,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3761,65 +3761,65 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.45</v>
+        <v>2.55</v>
       </c>
       <c r="M26" t="n">
-        <v>4.4</v>
+        <v>3.3</v>
       </c>
       <c r="N26" t="n">
-        <v>6.4</v>
+        <v>2.8</v>
       </c>
       <c r="O26" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="T26" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="U26" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="V26" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="W26" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.65</v>
+        <v>2.2</v>
       </c>
       <c r="Z26" t="n">
-        <v>2.1</v>
+        <v>1.68</v>
       </c>
       <c r="AA26" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
@@ -3832,10 +3832,10 @@
         </is>
       </c>
       <c r="AG26" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AH26" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AI26" t="n">
         <v>0</v>
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,13 +3894,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.55</v>
+        <v>2.18</v>
       </c>
       <c r="M27" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="N27" t="n">
-        <v>2.8</v>
+        <v>3.25</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3933,10 +3933,10 @@
         <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="Z27" t="n">
-        <v>1.68</v>
+        <v>1.8</v>
       </c>
       <c r="AA27" t="n">
         <v>0</v>
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,13 +4152,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.18</v>
+        <v>2.13</v>
       </c>
       <c r="M29" t="n">
-        <v>3.45</v>
+        <v>3.75</v>
       </c>
       <c r="N29" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -4191,10 +4191,10 @@
         <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="Z29" t="n">
-        <v>1.8</v>
+        <v>2.15</v>
       </c>
       <c r="AA29" t="n">
         <v>0</v>
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,13 +4281,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.13</v>
+        <v>1.63</v>
       </c>
       <c r="M30" t="n">
-        <v>3.75</v>
+        <v>4.2</v>
       </c>
       <c r="N30" t="n">
-        <v>3.15</v>
+        <v>5</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4320,10 +4320,10 @@
         <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="Z30" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AA30" t="n">
         <v>0</v>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4406,65 +4406,65 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.9</v>
+        <v>1.45</v>
       </c>
       <c r="M31" t="n">
-        <v>3.6</v>
+        <v>4.4</v>
       </c>
       <c r="N31" t="n">
-        <v>4</v>
+        <v>6.4</v>
       </c>
       <c r="O31" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S31" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="T31" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="V31" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="W31" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X31" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.97</v>
+        <v>1.65</v>
       </c>
       <c r="Z31" t="n">
-        <v>1.83</v>
+        <v>2.1</v>
       </c>
       <c r="AA31" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AB31" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AC31" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD31" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AE31" t="inlineStr">
         <is>
@@ -4477,10 +4477,10 @@
         </is>
       </c>
       <c r="AG31" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AH31" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AI31" t="n">
         <v>0</v>
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,13 +4539,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.63</v>
+        <v>1.3</v>
       </c>
       <c r="M32" t="n">
-        <v>4.2</v>
+        <v>5.4</v>
       </c>
       <c r="N32" t="n">
-        <v>5</v>
+        <v>10.5</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4578,7 +4578,7 @@
         <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="Z32" t="n">
         <v>2.2</v>
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,13 +4668,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.3</v>
+        <v>3.2</v>
       </c>
       <c r="M33" t="n">
-        <v>5.4</v>
+        <v>3.55</v>
       </c>
       <c r="N33" t="n">
-        <v>10.5</v>
+        <v>2.2</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4707,10 +4707,10 @@
         <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.67</v>
+        <v>1.88</v>
       </c>
       <c r="Z33" t="n">
-        <v>2.2</v>
+        <v>1.92</v>
       </c>
       <c r="AA33" t="n">
         <v>0</v>
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,13 +4797,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>3.2</v>
+        <v>1.9</v>
       </c>
       <c r="M34" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="N34" t="n">
-        <v>2.2</v>
+        <v>4</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4836,10 +4836,10 @@
         <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.88</v>
+        <v>1.97</v>
       </c>
       <c r="Z34" t="n">
-        <v>1.92</v>
+        <v>1.83</v>
       </c>
       <c r="AA34" t="n">
         <v>0</v>
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,13 +4926,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>1.35</v>
+        <v>4.3</v>
       </c>
       <c r="M35" t="n">
-        <v>5.3</v>
+        <v>4.4</v>
       </c>
       <c r="N35" t="n">
-        <v>7</v>
+        <v>1.64</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4965,16 +4965,16 @@
         <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.6</v>
+        <v>1.44</v>
       </c>
       <c r="Z35" t="n">
-        <v>2.35</v>
+        <v>2.75</v>
       </c>
       <c r="AA35" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB35" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC35" t="n">
         <v>0</v>
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Olympique Marseille</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5058,10 +5058,10 @@
         <v>1.56</v>
       </c>
       <c r="M36" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="N36" t="n">
-        <v>5.4</v>
+        <v>5.1</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Olympique Marseille</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,13 +5184,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>1.56</v>
+        <v>1.62</v>
       </c>
       <c r="M37" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="N37" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5223,10 +5223,10 @@
         <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.63</v>
+        <v>1.68</v>
       </c>
       <c r="Z37" t="n">
-        <v>2.25</v>
+        <v>2.18</v>
       </c>
       <c r="AA37" t="n">
         <v>0</v>
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,13 +5313,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>1.62</v>
+        <v>3</v>
       </c>
       <c r="M38" t="n">
-        <v>4.1</v>
+        <v>3.83</v>
       </c>
       <c r="N38" t="n">
-        <v>4.9</v>
+        <v>2.1</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5352,16 +5352,16 @@
         <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="Z38" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB38" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC38" t="n">
         <v>0</v>
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,13 +5442,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>4.3</v>
+        <v>1.56</v>
       </c>
       <c r="M39" t="n">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="N39" t="n">
-        <v>1.64</v>
+        <v>5.4</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5481,16 +5481,16 @@
         <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.44</v>
+        <v>1.63</v>
       </c>
       <c r="Z39" t="n">
-        <v>2.75</v>
+        <v>2.25</v>
       </c>
       <c r="AA39" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC39" t="n">
         <v>0</v>
@@ -5535,7 +5535,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,13 +5571,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>3</v>
+        <v>2.45</v>
       </c>
       <c r="M40" t="n">
-        <v>3.83</v>
+        <v>3.15</v>
       </c>
       <c r="N40" t="n">
-        <v>2.1</v>
+        <v>3.05</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5604,22 +5604,22 @@
         <v>0</v>
       </c>
       <c r="W40" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="X40" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Y40" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="Z40" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AA40" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -5664,7 +5664,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Kariobangi Sharks</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>KCB</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,13 +5700,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5739,16 +5739,16 @@
         <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="Z41" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AC41" t="n">
         <v>0</v>
@@ -5793,7 +5793,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Kariobangi Sharks</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>KCB</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,13 +5829,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="M42" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5868,10 +5868,10 @@
         <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z42" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AA42" t="n">
         <v>0</v>
@@ -5922,7 +5922,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5958,13 +5958,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>2.45</v>
+        <v>15</v>
       </c>
       <c r="M43" t="n">
-        <v>3.15</v>
+        <v>7.6</v>
       </c>
       <c r="N43" t="n">
-        <v>3.05</v>
+        <v>1.15</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5991,22 +5991,22 @@
         <v>0</v>
       </c>
       <c r="W43" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="X43" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>2.52</v>
+        <v>1.44</v>
       </c>
       <c r="Z43" t="n">
-        <v>1.52</v>
+        <v>2.75</v>
       </c>
       <c r="AA43" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB43" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC43" t="n">
         <v>0</v>
@@ -6474,13 +6474,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="M47" t="n">
-        <v>3.35</v>
+        <v>3.1</v>
       </c>
       <c r="N47" t="n">
-        <v>3.8</v>
+        <v>3.57</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6513,10 +6513,10 @@
         <v>0</v>
       </c>
       <c r="Y47" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="Z47" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AA47" t="n">
         <v>0</v>

--- a/jogos_2025-09-30.xlsx
+++ b/jogos_2025-09-30.xlsx
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Sogdiana</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Sogdiana</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Havelse</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Waldhof Mannheim</t>
+          <t>Erzgebirge Aue</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>Havelse</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Erzgebirge Aue</t>
+          <t>Waldhof Mannheim</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1665,22 +1665,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Wehen Wiesbaden</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,13 +1701,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1746,10 +1746,10 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -1794,22 +1794,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Saarbrucken</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>MSV Duisburg</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,13 +1830,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1869,16 +1869,16 @@
         <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -1923,22 +1923,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Saarbrucken</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>MSV Duisburg</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,13 +1959,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -2004,10 +2004,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -2052,22 +2052,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Wehen Wiesbaden</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,13 +2088,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2127,16 +2127,16 @@
         <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,14 +2991,14 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>3.6</v>
+        <v>2.05</v>
       </c>
       <c r="M20" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="N20" t="n">
         <v>3.45</v>
       </c>
-      <c r="N20" t="n">
-        <v>2.05</v>
-      </c>
       <c r="O20" t="n">
         <v>0</v>
       </c>
@@ -3030,10 +3030,10 @@
         <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>2.07</v>
+        <v>1.8</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AA20" t="n">
         <v>0</v>
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,13 +3120,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.15</v>
+        <v>3.6</v>
       </c>
       <c r="M21" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="N21" t="n">
-        <v>3.45</v>
+        <v>2.05</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3159,10 +3159,10 @@
         <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>2.18</v>
+        <v>2.07</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AA21" t="n">
         <v>0</v>
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Calcio Padova</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,10 +3378,10 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="M23" t="n">
-        <v>3.65</v>
+        <v>3.35</v>
       </c>
       <c r="N23" t="n">
         <v>3.45</v>
@@ -3417,10 +3417,10 @@
         <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="Z23" t="n">
-        <v>2</v>
+        <v>1.65</v>
       </c>
       <c r="AA23" t="n">
         <v>0</v>
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Calcio Padova</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3675,10 +3675,10 @@
         <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="Z25" t="n">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="AA25" t="n">
         <v>0</v>
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,13 +3765,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.55</v>
+        <v>1.9</v>
       </c>
       <c r="M26" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="N26" t="n">
-        <v>2.8</v>
+        <v>4</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3804,10 +3804,10 @@
         <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>2.2</v>
+        <v>1.97</v>
       </c>
       <c r="Z26" t="n">
-        <v>1.68</v>
+        <v>1.83</v>
       </c>
       <c r="AA26" t="n">
         <v>0</v>
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,13 +3894,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.18</v>
+        <v>1.3</v>
       </c>
       <c r="M27" t="n">
-        <v>3.45</v>
+        <v>5.4</v>
       </c>
       <c r="N27" t="n">
-        <v>3.25</v>
+        <v>10.5</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3933,10 +3933,10 @@
         <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="Z27" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="AA27" t="n">
         <v>0</v>
@@ -3987,7 +3987,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4019,65 +4019,65 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L28" t="n">
-        <v>3</v>
+        <v>2.13</v>
       </c>
       <c r="M28" t="n">
-        <v>3.19</v>
+        <v>3.75</v>
       </c>
       <c r="N28" t="n">
-        <v>2.31</v>
+        <v>3.15</v>
       </c>
       <c r="O28" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="T28" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="U28" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="V28" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W28" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="X28" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>2.01</v>
+        <v>1.7</v>
       </c>
       <c r="Z28" t="n">
-        <v>1.8</v>
+        <v>2.15</v>
       </c>
       <c r="AA28" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
@@ -4090,10 +4090,10 @@
         </is>
       </c>
       <c r="AG28" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AI28" t="n">
         <v>0</v>
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,13 +4152,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.13</v>
+        <v>1.63</v>
       </c>
       <c r="M29" t="n">
-        <v>3.75</v>
+        <v>4.2</v>
       </c>
       <c r="N29" t="n">
-        <v>3.15</v>
+        <v>5</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -4191,10 +4191,10 @@
         <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="Z29" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AA29" t="n">
         <v>0</v>
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,13 +4281,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.63</v>
+        <v>2.18</v>
       </c>
       <c r="M30" t="n">
-        <v>4.2</v>
+        <v>3.45</v>
       </c>
       <c r="N30" t="n">
-        <v>5</v>
+        <v>3.25</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4320,10 +4320,10 @@
         <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.68</v>
+        <v>2</v>
       </c>
       <c r="Z30" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="AA30" t="n">
         <v>0</v>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4406,65 +4406,65 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.45</v>
+        <v>2.55</v>
       </c>
       <c r="M31" t="n">
-        <v>4.4</v>
+        <v>3.3</v>
       </c>
       <c r="N31" t="n">
-        <v>6.4</v>
+        <v>2.8</v>
       </c>
       <c r="O31" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="T31" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="U31" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="V31" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="W31" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="X31" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.65</v>
+        <v>2.2</v>
       </c>
       <c r="Z31" t="n">
-        <v>2.1</v>
+        <v>1.68</v>
       </c>
       <c r="AA31" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AE31" t="inlineStr">
         <is>
@@ -4477,10 +4477,10 @@
         </is>
       </c>
       <c r="AG31" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AH31" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AI31" t="n">
         <v>0</v>
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,13 +4539,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.3</v>
+        <v>3.2</v>
       </c>
       <c r="M32" t="n">
-        <v>5.4</v>
+        <v>3.55</v>
       </c>
       <c r="N32" t="n">
-        <v>10.5</v>
+        <v>2.2</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4578,10 +4578,10 @@
         <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.67</v>
+        <v>1.88</v>
       </c>
       <c r="Z32" t="n">
-        <v>2.2</v>
+        <v>1.92</v>
       </c>
       <c r="AA32" t="n">
         <v>0</v>
@@ -4632,7 +4632,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4664,65 +4664,65 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L33" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="M33" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="N33" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="O33" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="P33" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="R33" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S33" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="V33" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W33" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="X33" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AA33" t="n">
         <v>3.55</v>
       </c>
-      <c r="N33" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="O33" t="n">
-        <v>0</v>
-      </c>
-      <c r="P33" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>0</v>
-      </c>
-      <c r="R33" t="n">
-        <v>0</v>
-      </c>
-      <c r="S33" t="n">
-        <v>0</v>
-      </c>
-      <c r="T33" t="n">
-        <v>0</v>
-      </c>
-      <c r="U33" t="n">
-        <v>0</v>
-      </c>
-      <c r="V33" t="n">
-        <v>0</v>
-      </c>
-      <c r="W33" t="n">
-        <v>0</v>
-      </c>
-      <c r="X33" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y33" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="Z33" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AA33" t="n">
-        <v>0</v>
-      </c>
       <c r="AB33" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AC33" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AD33" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AE33" t="inlineStr">
         <is>
@@ -4735,10 +4735,10 @@
         </is>
       </c>
       <c r="AG33" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AH33" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AI33" t="n">
         <v>0</v>
@@ -4761,7 +4761,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4793,65 +4793,65 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.9</v>
+        <v>1.45</v>
       </c>
       <c r="M34" t="n">
-        <v>3.6</v>
+        <v>4.4</v>
       </c>
       <c r="N34" t="n">
-        <v>4</v>
+        <v>6.4</v>
       </c>
       <c r="O34" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S34" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="T34" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="U34" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="V34" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="W34" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X34" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.97</v>
+        <v>1.65</v>
       </c>
       <c r="Z34" t="n">
-        <v>1.83</v>
+        <v>2.1</v>
       </c>
       <c r="AA34" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AB34" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AC34" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD34" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AE34" t="inlineStr">
         <is>
@@ -4864,10 +4864,10 @@
         </is>
       </c>
       <c r="AG34" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AH34" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AI34" t="n">
         <v>0</v>
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,13 +4926,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>4.3</v>
+        <v>1.56</v>
       </c>
       <c r="M35" t="n">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="N35" t="n">
-        <v>1.64</v>
+        <v>5.4</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4965,16 +4965,16 @@
         <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.44</v>
+        <v>1.63</v>
       </c>
       <c r="Z35" t="n">
-        <v>2.75</v>
+        <v>2.25</v>
       </c>
       <c r="AA35" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC35" t="n">
         <v>0</v>
@@ -5019,7 +5019,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Olympique Marseille</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,13 +5055,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>1.56</v>
+        <v>2.45</v>
       </c>
       <c r="M36" t="n">
-        <v>4.3</v>
+        <v>3.15</v>
       </c>
       <c r="N36" t="n">
-        <v>5.1</v>
+        <v>3.05</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5088,16 +5088,16 @@
         <v>0</v>
       </c>
       <c r="W36" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="X36" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.63</v>
+        <v>2.52</v>
       </c>
       <c r="Z36" t="n">
-        <v>2.25</v>
+        <v>1.52</v>
       </c>
       <c r="AA36" t="n">
         <v>0</v>
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Olympique Marseille</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,13 +5184,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>1.62</v>
+        <v>1.56</v>
       </c>
       <c r="M37" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="N37" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5223,10 +5223,10 @@
         <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.68</v>
+        <v>1.63</v>
       </c>
       <c r="Z37" t="n">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AA37" t="n">
         <v>0</v>
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,13 +5313,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>3</v>
+        <v>4.3</v>
       </c>
       <c r="M38" t="n">
-        <v>3.83</v>
+        <v>4.4</v>
       </c>
       <c r="N38" t="n">
-        <v>2.1</v>
+        <v>1.64</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5352,16 +5352,16 @@
         <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z38" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AA38" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="AC38" t="n">
         <v>0</v>
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,13 +5442,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>1.56</v>
+        <v>1.35</v>
       </c>
       <c r="M39" t="n">
-        <v>4.1</v>
+        <v>5.3</v>
       </c>
       <c r="N39" t="n">
-        <v>5.4</v>
+        <v>7</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5481,10 +5481,10 @@
         <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="Z39" t="n">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
       <c r="AA39" t="n">
         <v>0</v>
@@ -5535,7 +5535,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,13 +5571,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2.45</v>
+        <v>3</v>
       </c>
       <c r="M40" t="n">
-        <v>3.15</v>
+        <v>3.83</v>
       </c>
       <c r="N40" t="n">
-        <v>3.05</v>
+        <v>2.1</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5604,22 +5604,22 @@
         <v>0</v>
       </c>
       <c r="W40" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="X40" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="Z40" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB40" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -5664,7 +5664,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Kariobangi Sharks</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>KCB</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,13 +5700,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5739,16 +5739,16 @@
         <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z41" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AA41" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB41" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC41" t="n">
         <v>0</v>
@@ -5793,7 +5793,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Kariobangi Sharks</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>KCB</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,13 +5829,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5868,10 +5868,10 @@
         <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z42" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AA42" t="n">
         <v>0</v>
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5958,13 +5958,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>15</v>
+        <v>1.62</v>
       </c>
       <c r="M43" t="n">
-        <v>7.6</v>
+        <v>4.1</v>
       </c>
       <c r="N43" t="n">
-        <v>1.15</v>
+        <v>4.9</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5997,16 +5997,16 @@
         <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.44</v>
+        <v>1.68</v>
       </c>
       <c r="Z43" t="n">
-        <v>2.75</v>
+        <v>2.18</v>
       </c>
       <c r="AA43" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AC43" t="n">
         <v>0</v>

--- a/jogos_2025-09-30.xlsx
+++ b/jogos_2025-09-30.xlsx
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Sogdiana</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sogdiana</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Erzgebirge Aue</t>
+          <t>Wehen Wiesbaden</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Havelse</t>
+          <t>Saarbrucken</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Waldhof Mannheim</t>
+          <t>MSV Duisburg</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,13 +1701,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.56</v>
+        <v>1.26</v>
       </c>
       <c r="M10" t="n">
-        <v>4.2</v>
+        <v>5.1</v>
       </c>
       <c r="N10" t="n">
-        <v>4.2</v>
+        <v>7.6</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1740,16 +1740,16 @@
         <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.92</v>
+        <v>2.17</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.78</v>
+        <v>1.62</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -1794,22 +1794,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Hansa Rostock</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,13 +1830,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1869,16 +1869,16 @@
         <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -1923,22 +1923,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Saarbrucken</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>MSV Duisburg</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,13 +1959,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -2004,10 +2004,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>Havelse</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Wehen Wiesbaden</t>
+          <t>Waldhof Mannheim</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Hansa Rostock</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>Erzgebirge Aue</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Mantova</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.05</v>
+        <v>1.8</v>
       </c>
       <c r="M20" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="N20" t="n">
-        <v>3.45</v>
+        <v>4.3</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3030,10 +3030,10 @@
         <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="Z20" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AA20" t="n">
         <v>0</v>
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,14 +3120,14 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>3.6</v>
+        <v>2.05</v>
       </c>
       <c r="M21" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="N21" t="n">
         <v>3.45</v>
       </c>
-      <c r="N21" t="n">
-        <v>2.05</v>
-      </c>
       <c r="O21" t="n">
         <v>0</v>
       </c>
@@ -3159,10 +3159,10 @@
         <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>2.07</v>
+        <v>1.8</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AA21" t="n">
         <v>0</v>
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mantova</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,13 +3249,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.8</v>
+        <v>2.6</v>
       </c>
       <c r="M22" t="n">
-        <v>3.7</v>
+        <v>3.25</v>
       </c>
       <c r="N22" t="n">
-        <v>4.3</v>
+        <v>2.75</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3288,10 +3288,10 @@
         <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.95</v>
+        <v>2.2</v>
       </c>
       <c r="Z22" t="n">
-        <v>1.85</v>
+        <v>1.67</v>
       </c>
       <c r="AA22" t="n">
         <v>0</v>
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Calcio Padova</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,13 +3378,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.15</v>
+        <v>3.6</v>
       </c>
       <c r="M23" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="N23" t="n">
-        <v>3.45</v>
+        <v>2.05</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3417,10 +3417,10 @@
         <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>2.2</v>
+        <v>2.07</v>
       </c>
       <c r="Z23" t="n">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="AA23" t="n">
         <v>0</v>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Calcio Padova</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,13 +3507,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.6</v>
+        <v>2.15</v>
       </c>
       <c r="M24" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="N24" t="n">
-        <v>2.75</v>
+        <v>3.45</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3549,7 +3549,7 @@
         <v>2.2</v>
       </c>
       <c r="Z24" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AA24" t="n">
         <v>0</v>
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,13 +3765,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.9</v>
+        <v>1.3</v>
       </c>
       <c r="M26" t="n">
-        <v>3.6</v>
+        <v>5.4</v>
       </c>
       <c r="N26" t="n">
-        <v>4</v>
+        <v>10.5</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3804,10 +3804,10 @@
         <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.97</v>
+        <v>1.67</v>
       </c>
       <c r="Z26" t="n">
-        <v>1.83</v>
+        <v>2.2</v>
       </c>
       <c r="AA26" t="n">
         <v>0</v>
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,13 +3894,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.3</v>
+        <v>2.13</v>
       </c>
       <c r="M27" t="n">
-        <v>5.4</v>
+        <v>3.75</v>
       </c>
       <c r="N27" t="n">
-        <v>10.5</v>
+        <v>3.15</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3933,10 +3933,10 @@
         <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="Z27" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AA27" t="n">
         <v>0</v>
@@ -3987,7 +3987,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4019,65 +4019,65 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.13</v>
+        <v>3</v>
       </c>
       <c r="M28" t="n">
-        <v>3.75</v>
+        <v>3.19</v>
       </c>
       <c r="N28" t="n">
-        <v>3.15</v>
+        <v>2.31</v>
       </c>
       <c r="O28" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="T28" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="X28" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.7</v>
+        <v>2.01</v>
       </c>
       <c r="Z28" t="n">
-        <v>2.15</v>
+        <v>1.8</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AD28" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
@@ -4090,10 +4090,10 @@
         </is>
       </c>
       <c r="AG28" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AH28" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AI28" t="n">
         <v>0</v>
@@ -4116,7 +4116,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4148,65 +4148,65 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.63</v>
+        <v>1.45</v>
       </c>
       <c r="M29" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="N29" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="O29" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="P29" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="R29" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S29" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="V29" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W29" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="X29" t="n">
         <v>4.2</v>
       </c>
-      <c r="N29" t="n">
-        <v>5</v>
-      </c>
-      <c r="O29" t="n">
-        <v>0</v>
-      </c>
-      <c r="P29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>0</v>
-      </c>
-      <c r="R29" t="n">
-        <v>0</v>
-      </c>
-      <c r="S29" t="n">
-        <v>0</v>
-      </c>
-      <c r="T29" t="n">
-        <v>0</v>
-      </c>
-      <c r="U29" t="n">
-        <v>0</v>
-      </c>
-      <c r="V29" t="n">
-        <v>0</v>
-      </c>
-      <c r="W29" t="n">
-        <v>0</v>
-      </c>
-      <c r="X29" t="n">
-        <v>0</v>
-      </c>
       <c r="Y29" t="n">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="Z29" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AC29" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD29" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
@@ -4219,10 +4219,10 @@
         </is>
       </c>
       <c r="AG29" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AH29" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AI29" t="n">
         <v>0</v>
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,49 +4539,49 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>3.2</v>
+        <v>1.63</v>
       </c>
       <c r="M32" t="n">
-        <v>3.55</v>
+        <v>4.2</v>
       </c>
       <c r="N32" t="n">
+        <v>5</v>
+      </c>
+      <c r="O32" t="n">
+        <v>0</v>
+      </c>
+      <c r="P32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>0</v>
+      </c>
+      <c r="R32" t="n">
+        <v>0</v>
+      </c>
+      <c r="S32" t="n">
+        <v>0</v>
+      </c>
+      <c r="T32" t="n">
+        <v>0</v>
+      </c>
+      <c r="U32" t="n">
+        <v>0</v>
+      </c>
+      <c r="V32" t="n">
+        <v>0</v>
+      </c>
+      <c r="W32" t="n">
+        <v>0</v>
+      </c>
+      <c r="X32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="Z32" t="n">
         <v>2.2</v>
-      </c>
-      <c r="O32" t="n">
-        <v>0</v>
-      </c>
-      <c r="P32" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>0</v>
-      </c>
-      <c r="R32" t="n">
-        <v>0</v>
-      </c>
-      <c r="S32" t="n">
-        <v>0</v>
-      </c>
-      <c r="T32" t="n">
-        <v>0</v>
-      </c>
-      <c r="U32" t="n">
-        <v>0</v>
-      </c>
-      <c r="V32" t="n">
-        <v>0</v>
-      </c>
-      <c r="W32" t="n">
-        <v>0</v>
-      </c>
-      <c r="X32" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y32" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>1.92</v>
       </c>
       <c r="AA32" t="n">
         <v>0</v>
@@ -4632,7 +4632,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4664,65 +4664,65 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L33" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="M33" t="n">
-        <v>3.19</v>
+        <v>3.55</v>
       </c>
       <c r="N33" t="n">
-        <v>2.31</v>
+        <v>2.2</v>
       </c>
       <c r="O33" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="S33" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="T33" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="U33" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="V33" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W33" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="X33" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>2.01</v>
+        <v>1.88</v>
       </c>
       <c r="Z33" t="n">
-        <v>1.8</v>
+        <v>1.92</v>
       </c>
       <c r="AA33" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AC33" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AE33" t="inlineStr">
         <is>
@@ -4735,10 +4735,10 @@
         </is>
       </c>
       <c r="AG33" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AI33" t="n">
         <v>0</v>
@@ -4761,7 +4761,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4793,65 +4793,65 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.45</v>
+        <v>1.9</v>
       </c>
       <c r="M34" t="n">
-        <v>4.4</v>
+        <v>3.6</v>
       </c>
       <c r="N34" t="n">
-        <v>6.4</v>
+        <v>4</v>
       </c>
       <c r="O34" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="T34" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="U34" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="V34" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="W34" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="X34" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.65</v>
+        <v>1.97</v>
       </c>
       <c r="Z34" t="n">
-        <v>2.1</v>
+        <v>1.83</v>
       </c>
       <c r="AA34" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AC34" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD34" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AE34" t="inlineStr">
         <is>
@@ -4864,10 +4864,10 @@
         </is>
       </c>
       <c r="AG34" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AH34" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AI34" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Kariobangi Sharks</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>KCB</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,13 +4926,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4965,10 +4965,10 @@
         <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Z35" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AA35" t="n">
         <v>0</v>
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,13 +5571,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="M40" t="n">
-        <v>3.83</v>
+        <v>7.6</v>
       </c>
       <c r="N40" t="n">
-        <v>2.1</v>
+        <v>1.15</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5610,16 +5610,16 @@
         <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z40" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AA40" t="n">
-        <v>2.25</v>
+        <v>1.95</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.65</v>
+        <v>1.79</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,13 +5700,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>15</v>
+        <v>1.56</v>
       </c>
       <c r="M41" t="n">
-        <v>7.6</v>
+        <v>4.1</v>
       </c>
       <c r="N41" t="n">
-        <v>1.15</v>
+        <v>5.4</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5739,16 +5739,16 @@
         <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.44</v>
+        <v>1.63</v>
       </c>
       <c r="Z41" t="n">
-        <v>2.75</v>
+        <v>2.25</v>
       </c>
       <c r="AA41" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AC41" t="n">
         <v>0</v>
@@ -5793,7 +5793,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Kariobangi Sharks</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>KCB</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,13 +5829,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="M42" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5868,10 +5868,10 @@
         <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Z42" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AA42" t="n">
         <v>0</v>
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5958,13 +5958,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>1.62</v>
+        <v>3</v>
       </c>
       <c r="M43" t="n">
-        <v>4.1</v>
+        <v>3.83</v>
       </c>
       <c r="N43" t="n">
-        <v>4.9</v>
+        <v>2.1</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5997,16 +5997,16 @@
         <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="Z43" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AA43" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB43" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC43" t="n">
         <v>0</v>

--- a/jogos_2025-09-30.xlsx
+++ b/jogos_2025-09-30.xlsx
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Sogdiana</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Sogdiana</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1185,13 +1185,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.86</v>
+        <v>19</v>
       </c>
       <c r="M6" t="n">
-        <v>3.84</v>
+        <v>8.9</v>
       </c>
       <c r="N6" t="n">
-        <v>3.7</v>
+        <v>1.11</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1224,16 +1224,16 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.7</v>
+        <v>1.3</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.15</v>
+        <v>3.4</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1314,13 +1314,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>19</v>
+        <v>1.86</v>
       </c>
       <c r="M7" t="n">
-        <v>8.9</v>
+        <v>3.84</v>
       </c>
       <c r="N7" t="n">
-        <v>1.11</v>
+        <v>3.7</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1353,16 +1353,16 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.3</v>
+        <v>1.7</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.4</v>
+        <v>2.15</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>Havelse</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Wehen Wiesbaden</t>
+          <t>Waldhof Mannheim</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Saarbrucken</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>MSV Duisburg</t>
+          <t>Erzgebirge Aue</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1794,22 +1794,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Hansa Rostock</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,13 +1830,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1875,10 +1875,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -1923,22 +1923,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Wehen Wiesbaden</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,13 +1959,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -2004,10 +2004,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Havelse</t>
+          <t>Hansa Rostock</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Waldhof Mannheim</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>Saarbrucken</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Erzgebirge Aue</t>
+          <t>MSV Duisburg</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mantova</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.8</v>
+        <v>2.6</v>
       </c>
       <c r="M20" t="n">
-        <v>3.7</v>
+        <v>3.25</v>
       </c>
       <c r="N20" t="n">
-        <v>4.3</v>
+        <v>2.75</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3030,10 +3030,10 @@
         <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.95</v>
+        <v>2.2</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.85</v>
+        <v>1.67</v>
       </c>
       <c r="AA20" t="n">
         <v>0</v>
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>Mantova</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,13 +3249,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.6</v>
+        <v>1.8</v>
       </c>
       <c r="M22" t="n">
-        <v>3.25</v>
+        <v>3.7</v>
       </c>
       <c r="N22" t="n">
-        <v>2.75</v>
+        <v>4.3</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3288,10 +3288,10 @@
         <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>2.2</v>
+        <v>1.95</v>
       </c>
       <c r="Z22" t="n">
-        <v>1.67</v>
+        <v>1.85</v>
       </c>
       <c r="AA22" t="n">
         <v>0</v>
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,13 +3765,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.3</v>
+        <v>1.63</v>
       </c>
       <c r="M26" t="n">
-        <v>5.4</v>
+        <v>4.2</v>
       </c>
       <c r="N26" t="n">
-        <v>10.5</v>
+        <v>5</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3804,7 +3804,7 @@
         <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="Z26" t="n">
         <v>2.2</v>
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,13 +3894,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.13</v>
+        <v>3.2</v>
       </c>
       <c r="M27" t="n">
-        <v>3.75</v>
+        <v>3.55</v>
       </c>
       <c r="N27" t="n">
-        <v>3.15</v>
+        <v>2.2</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3933,10 +3933,10 @@
         <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.7</v>
+        <v>1.88</v>
       </c>
       <c r="Z27" t="n">
-        <v>2.15</v>
+        <v>1.92</v>
       </c>
       <c r="AA27" t="n">
         <v>0</v>
@@ -3987,7 +3987,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4019,65 +4019,65 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L28" t="n">
-        <v>3</v>
+        <v>1.3</v>
       </c>
       <c r="M28" t="n">
-        <v>3.19</v>
+        <v>5.4</v>
       </c>
       <c r="N28" t="n">
-        <v>2.31</v>
+        <v>10.5</v>
       </c>
       <c r="O28" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="T28" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="U28" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="V28" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W28" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="X28" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>2.01</v>
+        <v>1.67</v>
       </c>
       <c r="Z28" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="AA28" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
@@ -4090,10 +4090,10 @@
         </is>
       </c>
       <c r="AG28" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AI28" t="n">
         <v>0</v>
@@ -4116,7 +4116,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4148,65 +4148,65 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.45</v>
+        <v>2.18</v>
       </c>
       <c r="M29" t="n">
-        <v>4.4</v>
+        <v>3.45</v>
       </c>
       <c r="N29" t="n">
-        <v>6.4</v>
+        <v>3.25</v>
       </c>
       <c r="O29" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="T29" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="U29" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="V29" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="W29" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="X29" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.65</v>
+        <v>2</v>
       </c>
       <c r="Z29" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="AA29" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
@@ -4219,10 +4219,10 @@
         </is>
       </c>
       <c r="AG29" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AH29" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AI29" t="n">
         <v>0</v>
@@ -4245,7 +4245,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4277,65 +4277,65 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.18</v>
+        <v>3</v>
       </c>
       <c r="M30" t="n">
-        <v>3.45</v>
+        <v>3.19</v>
       </c>
       <c r="N30" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="O30" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="P30" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="R30" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S30" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="V30" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W30" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="X30" t="n">
         <v>3.25</v>
       </c>
-      <c r="O30" t="n">
-        <v>0</v>
-      </c>
-      <c r="P30" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>0</v>
-      </c>
-      <c r="R30" t="n">
-        <v>0</v>
-      </c>
-      <c r="S30" t="n">
-        <v>0</v>
-      </c>
-      <c r="T30" t="n">
-        <v>0</v>
-      </c>
-      <c r="U30" t="n">
-        <v>0</v>
-      </c>
-      <c r="V30" t="n">
-        <v>0</v>
-      </c>
-      <c r="W30" t="n">
-        <v>0</v>
-      </c>
-      <c r="X30" t="n">
-        <v>0</v>
-      </c>
       <c r="Y30" t="n">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="Z30" t="n">
         <v>1.8</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AD30" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
@@ -4348,10 +4348,10 @@
         </is>
       </c>
       <c r="AG30" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AH30" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AI30" t="n">
         <v>0</v>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4406,65 +4406,65 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.55</v>
+        <v>1.45</v>
       </c>
       <c r="M31" t="n">
-        <v>3.3</v>
+        <v>4.4</v>
       </c>
       <c r="N31" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="O31" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="P31" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="R31" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S31" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="V31" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W31" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="X31" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AA31" t="n">
         <v>2.8</v>
       </c>
-      <c r="O31" t="n">
-        <v>0</v>
-      </c>
-      <c r="P31" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>0</v>
-      </c>
-      <c r="R31" t="n">
-        <v>0</v>
-      </c>
-      <c r="S31" t="n">
-        <v>0</v>
-      </c>
-      <c r="T31" t="n">
-        <v>0</v>
-      </c>
-      <c r="U31" t="n">
-        <v>0</v>
-      </c>
-      <c r="V31" t="n">
-        <v>0</v>
-      </c>
-      <c r="W31" t="n">
-        <v>0</v>
-      </c>
-      <c r="X31" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Z31" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>0</v>
-      </c>
       <c r="AB31" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AC31" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD31" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AE31" t="inlineStr">
         <is>
@@ -4477,10 +4477,10 @@
         </is>
       </c>
       <c r="AG31" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AH31" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AI31" t="n">
         <v>0</v>
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,13 +4539,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.63</v>
+        <v>2.13</v>
       </c>
       <c r="M32" t="n">
-        <v>4.2</v>
+        <v>3.75</v>
       </c>
       <c r="N32" t="n">
-        <v>5</v>
+        <v>3.15</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4578,10 +4578,10 @@
         <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="Z32" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AA32" t="n">
         <v>0</v>
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,13 +4668,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>3.2</v>
+        <v>1.9</v>
       </c>
       <c r="M33" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="N33" t="n">
-        <v>2.2</v>
+        <v>4</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4707,10 +4707,10 @@
         <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.88</v>
+        <v>1.97</v>
       </c>
       <c r="Z33" t="n">
-        <v>1.92</v>
+        <v>1.83</v>
       </c>
       <c r="AA33" t="n">
         <v>0</v>
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,13 +4797,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.9</v>
+        <v>2.55</v>
       </c>
       <c r="M34" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="N34" t="n">
-        <v>4</v>
+        <v>2.8</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4836,10 +4836,10 @@
         <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.97</v>
+        <v>2.2</v>
       </c>
       <c r="Z34" t="n">
-        <v>1.83</v>
+        <v>1.68</v>
       </c>
       <c r="AA34" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Kariobangi Sharks</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>KCB</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,13 +4926,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4965,16 +4965,16 @@
         <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z35" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AA35" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB35" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC35" t="n">
         <v>0</v>
@@ -5019,7 +5019,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,13 +5055,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.45</v>
+        <v>15</v>
       </c>
       <c r="M36" t="n">
-        <v>3.15</v>
+        <v>7.6</v>
       </c>
       <c r="N36" t="n">
-        <v>3.05</v>
+        <v>1.15</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5088,22 +5088,22 @@
         <v>0</v>
       </c>
       <c r="W36" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="X36" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>2.52</v>
+        <v>1.44</v>
       </c>
       <c r="Z36" t="n">
-        <v>1.52</v>
+        <v>2.75</v>
       </c>
       <c r="AA36" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB36" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC36" t="n">
         <v>0</v>
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Olympique Marseille</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,13 +5184,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>1.56</v>
+        <v>3</v>
       </c>
       <c r="M37" t="n">
-        <v>4.3</v>
+        <v>3.83</v>
       </c>
       <c r="N37" t="n">
-        <v>5.1</v>
+        <v>2.1</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5223,16 +5223,16 @@
         <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Z37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA37" t="n">
         <v>2.25</v>
       </c>
-      <c r="AA37" t="n">
-        <v>0</v>
-      </c>
       <c r="AB37" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC37" t="n">
         <v>0</v>
@@ -5277,7 +5277,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,13 +5313,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>4.3</v>
+        <v>2.45</v>
       </c>
       <c r="M38" t="n">
-        <v>4.4</v>
+        <v>3.15</v>
       </c>
       <c r="N38" t="n">
-        <v>1.64</v>
+        <v>3.05</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5346,22 +5346,22 @@
         <v>0</v>
       </c>
       <c r="W38" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="X38" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.44</v>
+        <v>2.52</v>
       </c>
       <c r="Z38" t="n">
-        <v>2.75</v>
+        <v>1.52</v>
       </c>
       <c r="AA38" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC38" t="n">
         <v>0</v>
@@ -5406,7 +5406,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Kariobangi Sharks</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>KCB</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,13 +5442,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5481,10 +5481,10 @@
         <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z39" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AA39" t="n">
         <v>0</v>
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,13 +5571,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>15</v>
+        <v>1.35</v>
       </c>
       <c r="M40" t="n">
-        <v>7.6</v>
+        <v>5.3</v>
       </c>
       <c r="N40" t="n">
-        <v>1.15</v>
+        <v>7</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5610,16 +5610,16 @@
         <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="Z40" t="n">
-        <v>2.75</v>
+        <v>2.35</v>
       </c>
       <c r="AA40" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Olympique Marseille</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5703,10 +5703,10 @@
         <v>1.56</v>
       </c>
       <c r="M41" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="N41" t="n">
-        <v>5.4</v>
+        <v>5.1</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,13 +5829,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>1.62</v>
+        <v>1.56</v>
       </c>
       <c r="M42" t="n">
         <v>4.1</v>
       </c>
       <c r="N42" t="n">
-        <v>4.9</v>
+        <v>5.4</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5868,10 +5868,10 @@
         <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.68</v>
+        <v>1.63</v>
       </c>
       <c r="Z42" t="n">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AA42" t="n">
         <v>0</v>
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5958,13 +5958,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>3</v>
+        <v>1.62</v>
       </c>
       <c r="M43" t="n">
-        <v>3.83</v>
+        <v>4.1</v>
       </c>
       <c r="N43" t="n">
-        <v>2.1</v>
+        <v>4.9</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5997,16 +5997,16 @@
         <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Z43" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AA43" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC43" t="n">
         <v>0</v>

--- a/jogos_2025-09-30.xlsx
+++ b/jogos_2025-09-30.xlsx
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Sogdiana</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sogdiana</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1185,13 +1185,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>19</v>
+        <v>1.86</v>
       </c>
       <c r="M6" t="n">
-        <v>8.9</v>
+        <v>3.84</v>
       </c>
       <c r="N6" t="n">
-        <v>1.11</v>
+        <v>3.7</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1224,16 +1224,16 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.3</v>
+        <v>1.7</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.4</v>
+        <v>2.15</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1314,13 +1314,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.86</v>
+        <v>19</v>
       </c>
       <c r="M7" t="n">
-        <v>3.84</v>
+        <v>8.9</v>
       </c>
       <c r="N7" t="n">
-        <v>3.7</v>
+        <v>1.11</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1353,16 +1353,16 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.7</v>
+        <v>1.3</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.15</v>
+        <v>3.4</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Havelse</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Waldhof Mannheim</t>
+          <t>Erzgebirge Aue</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Erzgebirge Aue</t>
+          <t>Wehen Wiesbaden</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1665,22 +1665,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Hansa Rostock</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,13 +1701,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1740,16 +1740,16 @@
         <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -1923,22 +1923,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Wehen Wiesbaden</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,13 +1959,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1998,16 +1998,16 @@
         <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Hansa Rostock</t>
+          <t>Havelse</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>Waldhof Mannheim</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.6</v>
+        <v>3.6</v>
       </c>
       <c r="M20" t="n">
-        <v>3.25</v>
+        <v>3.45</v>
       </c>
       <c r="N20" t="n">
-        <v>2.75</v>
+        <v>2.05</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3030,10 +3030,10 @@
         <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>2.2</v>
+        <v>2.07</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AA20" t="n">
         <v>0</v>
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,14 +3378,14 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>3.6</v>
+        <v>2.15</v>
       </c>
       <c r="M23" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="N23" t="n">
         <v>3.45</v>
       </c>
-      <c r="N23" t="n">
-        <v>2.05</v>
-      </c>
       <c r="O23" t="n">
         <v>0</v>
       </c>
@@ -3417,10 +3417,10 @@
         <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>2.07</v>
+        <v>2.18</v>
       </c>
       <c r="Z23" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AA23" t="n">
         <v>0</v>
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,13 +3636,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.15</v>
+        <v>2.6</v>
       </c>
       <c r="M25" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="N25" t="n">
-        <v>3.45</v>
+        <v>2.75</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3675,10 +3675,10 @@
         <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="Z25" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AA25" t="n">
         <v>0</v>
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,49 +3894,49 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>3.2</v>
+        <v>2.55</v>
       </c>
       <c r="M27" t="n">
-        <v>3.55</v>
+        <v>3.3</v>
       </c>
       <c r="N27" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>0</v>
+      </c>
+      <c r="R27" t="n">
+        <v>0</v>
+      </c>
+      <c r="S27" t="n">
+        <v>0</v>
+      </c>
+      <c r="T27" t="n">
+        <v>0</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0</v>
+      </c>
+      <c r="V27" t="n">
+        <v>0</v>
+      </c>
+      <c r="W27" t="n">
+        <v>0</v>
+      </c>
+      <c r="X27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y27" t="n">
         <v>2.2</v>
       </c>
-      <c r="O27" t="n">
-        <v>0</v>
-      </c>
-      <c r="P27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>0</v>
-      </c>
-      <c r="R27" t="n">
-        <v>0</v>
-      </c>
-      <c r="S27" t="n">
-        <v>0</v>
-      </c>
-      <c r="T27" t="n">
-        <v>0</v>
-      </c>
-      <c r="U27" t="n">
-        <v>0</v>
-      </c>
-      <c r="V27" t="n">
-        <v>0</v>
-      </c>
-      <c r="W27" t="n">
-        <v>0</v>
-      </c>
-      <c r="X27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>1.88</v>
-      </c>
       <c r="Z27" t="n">
-        <v>1.92</v>
+        <v>1.68</v>
       </c>
       <c r="AA27" t="n">
         <v>0</v>
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,13 +4023,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.3</v>
+        <v>2.13</v>
       </c>
       <c r="M28" t="n">
-        <v>5.4</v>
+        <v>3.75</v>
       </c>
       <c r="N28" t="n">
-        <v>10.5</v>
+        <v>3.15</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -4062,10 +4062,10 @@
         <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="Z28" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AA28" t="n">
         <v>0</v>
@@ -4116,7 +4116,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4148,65 +4148,65 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.18</v>
+        <v>1.45</v>
       </c>
       <c r="M29" t="n">
-        <v>3.45</v>
+        <v>4.4</v>
       </c>
       <c r="N29" t="n">
-        <v>3.25</v>
+        <v>6.4</v>
       </c>
       <c r="O29" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S29" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="T29" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="V29" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="W29" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X29" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="Y29" t="n">
-        <v>2</v>
+        <v>1.65</v>
       </c>
       <c r="Z29" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AC29" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD29" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
@@ -4219,10 +4219,10 @@
         </is>
       </c>
       <c r="AG29" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AH29" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AI29" t="n">
         <v>0</v>
@@ -4245,7 +4245,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4277,65 +4277,65 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L30" t="n">
-        <v>3</v>
+        <v>1.9</v>
       </c>
       <c r="M30" t="n">
-        <v>3.19</v>
+        <v>3.6</v>
       </c>
       <c r="N30" t="n">
-        <v>2.31</v>
+        <v>4</v>
       </c>
       <c r="O30" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="T30" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="U30" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="V30" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W30" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="X30" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>2.01</v>
+        <v>1.97</v>
       </c>
       <c r="Z30" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AA30" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AC30" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
@@ -4348,10 +4348,10 @@
         </is>
       </c>
       <c r="AG30" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AI30" t="n">
         <v>0</v>
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,61 +4410,61 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.45</v>
+        <v>3</v>
       </c>
       <c r="M31" t="n">
-        <v>4.4</v>
+        <v>3.19</v>
       </c>
       <c r="N31" t="n">
-        <v>6.4</v>
+        <v>2.31</v>
       </c>
       <c r="O31" t="n">
-        <v>1.96</v>
+        <v>3.6</v>
       </c>
       <c r="P31" t="n">
-        <v>2.38</v>
+        <v>2.05</v>
       </c>
       <c r="Q31" t="n">
-        <v>5.5</v>
+        <v>2.92</v>
       </c>
       <c r="R31" t="n">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="S31" t="n">
-        <v>3.08</v>
+        <v>2.75</v>
       </c>
       <c r="T31" t="n">
-        <v>2.4</v>
+        <v>2.8</v>
       </c>
       <c r="U31" t="n">
-        <v>1.49</v>
+        <v>1.37</v>
       </c>
       <c r="V31" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="W31" t="n">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="X31" t="n">
-        <v>4.2</v>
+        <v>3.25</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.65</v>
+        <v>2.01</v>
       </c>
       <c r="Z31" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="AA31" t="n">
-        <v>2.8</v>
+        <v>3.55</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.42</v>
+        <v>1.27</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.85</v>
+        <v>1.76</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AE31" t="inlineStr">
         <is>
@@ -4477,10 +4477,10 @@
         </is>
       </c>
       <c r="AG31" t="n">
-        <v>1.15</v>
+        <v>1.62</v>
       </c>
       <c r="AH31" t="n">
-        <v>2.6</v>
+        <v>1.37</v>
       </c>
       <c r="AI31" t="n">
         <v>0</v>
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,13 +4539,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.13</v>
+        <v>2.18</v>
       </c>
       <c r="M32" t="n">
-        <v>3.75</v>
+        <v>3.45</v>
       </c>
       <c r="N32" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4578,10 +4578,10 @@
         <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="Z32" t="n">
-        <v>2.15</v>
+        <v>1.8</v>
       </c>
       <c r="AA32" t="n">
         <v>0</v>
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,13 +4668,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.9</v>
+        <v>3.2</v>
       </c>
       <c r="M33" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="N33" t="n">
-        <v>4</v>
+        <v>2.2</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4707,10 +4707,10 @@
         <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.97</v>
+        <v>1.88</v>
       </c>
       <c r="Z33" t="n">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AA33" t="n">
         <v>0</v>
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,13 +4797,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.55</v>
+        <v>1.3</v>
       </c>
       <c r="M34" t="n">
-        <v>3.3</v>
+        <v>5.4</v>
       </c>
       <c r="N34" t="n">
-        <v>2.8</v>
+        <v>10.5</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4836,10 +4836,10 @@
         <v>0</v>
       </c>
       <c r="Y34" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="Z34" t="n">
         <v>2.2</v>
-      </c>
-      <c r="Z34" t="n">
-        <v>1.68</v>
       </c>
       <c r="AA34" t="n">
         <v>0</v>
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Olympique Marseille</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,13 +4926,13 @@
         </is>
       </c>
       <c r="L35" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="M35" t="n">
         <v>4.3</v>
       </c>
-      <c r="M35" t="n">
-        <v>4.4</v>
-      </c>
       <c r="N35" t="n">
-        <v>1.64</v>
+        <v>5.1</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4965,16 +4965,16 @@
         <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.44</v>
+        <v>1.63</v>
       </c>
       <c r="Z35" t="n">
-        <v>2.75</v>
+        <v>2.25</v>
       </c>
       <c r="AA35" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC35" t="n">
         <v>0</v>
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,13 +5055,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>15</v>
+        <v>1.35</v>
       </c>
       <c r="M36" t="n">
-        <v>7.6</v>
+        <v>5.3</v>
       </c>
       <c r="N36" t="n">
-        <v>1.15</v>
+        <v>7</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5094,16 +5094,16 @@
         <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="Z36" t="n">
-        <v>2.75</v>
+        <v>2.35</v>
       </c>
       <c r="AA36" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AC36" t="n">
         <v>0</v>
@@ -5148,7 +5148,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,13 +5184,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>3</v>
+        <v>2.45</v>
       </c>
       <c r="M37" t="n">
-        <v>3.83</v>
+        <v>3.15</v>
       </c>
       <c r="N37" t="n">
-        <v>2.1</v>
+        <v>3.05</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5217,22 +5217,22 @@
         <v>0</v>
       </c>
       <c r="W37" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="X37" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Y37" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="Z37" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AA37" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC37" t="n">
         <v>0</v>
@@ -5277,7 +5277,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,13 +5313,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.45</v>
+        <v>3</v>
       </c>
       <c r="M38" t="n">
-        <v>3.15</v>
+        <v>3.83</v>
       </c>
       <c r="N38" t="n">
-        <v>3.05</v>
+        <v>2.1</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5346,22 +5346,22 @@
         <v>0</v>
       </c>
       <c r="W38" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="X38" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="Z38" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB38" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC38" t="n">
         <v>0</v>
@@ -5406,7 +5406,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Kariobangi Sharks</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>KCB</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,13 +5442,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5481,16 +5481,16 @@
         <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z39" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AA39" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB39" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC39" t="n">
         <v>0</v>
@@ -5535,7 +5535,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Kariobangi Sharks</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>KCB</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,13 +5571,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5610,10 +5610,10 @@
         <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z40" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AA40" t="n">
         <v>0</v>
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Olympique Marseille</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,13 +5700,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1.56</v>
+        <v>1.62</v>
       </c>
       <c r="M41" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="N41" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5739,10 +5739,10 @@
         <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.63</v>
+        <v>1.68</v>
       </c>
       <c r="Z41" t="n">
-        <v>2.25</v>
+        <v>2.18</v>
       </c>
       <c r="AA41" t="n">
         <v>0</v>
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5958,13 +5958,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>1.62</v>
+        <v>4.3</v>
       </c>
       <c r="M43" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="N43" t="n">
-        <v>4.9</v>
+        <v>1.64</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5997,16 +5997,16 @@
         <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.68</v>
+        <v>1.44</v>
       </c>
       <c r="Z43" t="n">
-        <v>2.18</v>
+        <v>2.75</v>
       </c>
       <c r="AA43" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB43" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC43" t="n">
         <v>0</v>

--- a/jogos_2025-09-30.xlsx
+++ b/jogos_2025-09-30.xlsx
@@ -1185,61 +1185,61 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="M6" t="n">
-        <v>3.84</v>
+        <v>3.55</v>
       </c>
       <c r="N6" t="n">
-        <v>3.7</v>
+        <v>3.25</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.7</v>
+        <v>1.61</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.15</v>
+        <v>2.31</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
@@ -1252,10 +1252,10 @@
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AI6" t="n">
         <v>0</v>
@@ -1407,22 +1407,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Erzgebirge Aue</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,13 +1443,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1488,10 +1488,10 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
@@ -1536,22 +1536,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Wehen Wiesbaden</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,13 +1572,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1611,16 +1611,16 @@
         <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Hansa Rostock</t>
+          <t>Saarbrucken</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>MSV Duisburg</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1794,22 +1794,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Erzgebirge Aue</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,13 +1830,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1875,10 +1875,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -1923,22 +1923,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Hansa Rostock</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,13 +1959,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1998,16 +1998,16 @@
         <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Havelse</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Waldhof Mannheim</t>
+          <t>Wehen Wiesbaden</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Saarbrucken</t>
+          <t>Havelse</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>MSV Duisburg</t>
+          <t>Waldhof Mannheim</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,14 +2991,14 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>3.6</v>
+        <v>2.05</v>
       </c>
       <c r="M20" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="N20" t="n">
         <v>3.45</v>
       </c>
-      <c r="N20" t="n">
-        <v>2.05</v>
-      </c>
       <c r="O20" t="n">
         <v>0</v>
       </c>
@@ -3030,10 +3030,10 @@
         <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>2.07</v>
+        <v>1.8</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AA20" t="n">
         <v>0</v>
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,13 +3120,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.05</v>
+        <v>2.6</v>
       </c>
       <c r="M21" t="n">
-        <v>3.65</v>
+        <v>3.25</v>
       </c>
       <c r="N21" t="n">
-        <v>3.45</v>
+        <v>2.75</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3159,10 +3159,10 @@
         <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="Z21" t="n">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="AA21" t="n">
         <v>0</v>
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Calcio Padova</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mantova</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,13 +3249,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.8</v>
+        <v>2.15</v>
       </c>
       <c r="M22" t="n">
-        <v>3.7</v>
+        <v>3.35</v>
       </c>
       <c r="N22" t="n">
-        <v>4.3</v>
+        <v>3.45</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3288,10 +3288,10 @@
         <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.95</v>
+        <v>2.2</v>
       </c>
       <c r="Z22" t="n">
-        <v>1.85</v>
+        <v>1.65</v>
       </c>
       <c r="AA22" t="n">
         <v>0</v>
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Mantova</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,13 +3378,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.15</v>
+        <v>1.8</v>
       </c>
       <c r="M23" t="n">
-        <v>3.35</v>
+        <v>3.7</v>
       </c>
       <c r="N23" t="n">
-        <v>3.45</v>
+        <v>4.3</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3417,10 +3417,10 @@
         <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>2.18</v>
+        <v>1.95</v>
       </c>
       <c r="Z23" t="n">
-        <v>1.7</v>
+        <v>1.85</v>
       </c>
       <c r="AA23" t="n">
         <v>0</v>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Calcio Padova</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,13 +3507,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.15</v>
+        <v>3.6</v>
       </c>
       <c r="M24" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="N24" t="n">
-        <v>3.45</v>
+        <v>2.05</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3546,10 +3546,10 @@
         <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>2.2</v>
+        <v>2.07</v>
       </c>
       <c r="Z24" t="n">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="AA24" t="n">
         <v>0</v>
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,13 +3636,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.6</v>
+        <v>2.15</v>
       </c>
       <c r="M25" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="N25" t="n">
-        <v>2.75</v>
+        <v>3.45</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3675,10 +3675,10 @@
         <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="Z25" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AA25" t="n">
         <v>0</v>
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,13 +3765,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.63</v>
+        <v>2.18</v>
       </c>
       <c r="M26" t="n">
-        <v>4.2</v>
+        <v>3.45</v>
       </c>
       <c r="N26" t="n">
-        <v>5</v>
+        <v>3.25</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3804,10 +3804,10 @@
         <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.68</v>
+        <v>2</v>
       </c>
       <c r="Z26" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="AA26" t="n">
         <v>0</v>
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,13 +3894,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.55</v>
+        <v>3.2</v>
       </c>
       <c r="M27" t="n">
-        <v>3.3</v>
+        <v>3.55</v>
       </c>
       <c r="N27" t="n">
-        <v>2.8</v>
+        <v>2.2</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3933,10 +3933,10 @@
         <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>2.2</v>
+        <v>1.88</v>
       </c>
       <c r="Z27" t="n">
-        <v>1.68</v>
+        <v>1.92</v>
       </c>
       <c r="AA27" t="n">
         <v>0</v>
@@ -4116,7 +4116,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4148,65 +4148,65 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.45</v>
+        <v>1.3</v>
       </c>
       <c r="M29" t="n">
-        <v>4.4</v>
+        <v>5.4</v>
       </c>
       <c r="N29" t="n">
-        <v>6.4</v>
+        <v>10.5</v>
       </c>
       <c r="O29" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="T29" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="U29" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="V29" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="W29" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="X29" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="Z29" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AA29" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
@@ -4219,10 +4219,10 @@
         </is>
       </c>
       <c r="AG29" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AH29" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AI29" t="n">
         <v>0</v>
@@ -4245,7 +4245,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4277,65 +4277,65 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.9</v>
+        <v>1.45</v>
       </c>
       <c r="M30" t="n">
-        <v>3.6</v>
+        <v>4.4</v>
       </c>
       <c r="N30" t="n">
-        <v>4</v>
+        <v>6.4</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S30" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.97</v>
+        <v>1.65</v>
       </c>
       <c r="Z30" t="n">
-        <v>1.83</v>
+        <v>2.1</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD30" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
@@ -4348,10 +4348,10 @@
         </is>
       </c>
       <c r="AG30" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AH30" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AI30" t="n">
         <v>0</v>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4406,65 +4406,65 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L31" t="n">
-        <v>3</v>
+        <v>2.55</v>
       </c>
       <c r="M31" t="n">
-        <v>3.19</v>
+        <v>3.3</v>
       </c>
       <c r="N31" t="n">
-        <v>2.31</v>
+        <v>2.8</v>
       </c>
       <c r="O31" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="T31" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="U31" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="V31" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W31" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="X31" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>2.01</v>
+        <v>2.2</v>
       </c>
       <c r="Z31" t="n">
-        <v>1.8</v>
+        <v>1.68</v>
       </c>
       <c r="AA31" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AE31" t="inlineStr">
         <is>
@@ -4477,10 +4477,10 @@
         </is>
       </c>
       <c r="AG31" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AI31" t="n">
         <v>0</v>
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,13 +4539,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.18</v>
+        <v>1.63</v>
       </c>
       <c r="M32" t="n">
-        <v>3.45</v>
+        <v>4.2</v>
       </c>
       <c r="N32" t="n">
-        <v>3.25</v>
+        <v>5</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4578,10 +4578,10 @@
         <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>2</v>
+        <v>1.68</v>
       </c>
       <c r="Z32" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="AA32" t="n">
         <v>0</v>
@@ -4632,7 +4632,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4664,65 +4664,65 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L33" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="M33" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="N33" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="O33" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="P33" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="R33" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S33" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="V33" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W33" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="X33" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AA33" t="n">
         <v>3.55</v>
       </c>
-      <c r="N33" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="O33" t="n">
-        <v>0</v>
-      </c>
-      <c r="P33" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>0</v>
-      </c>
-      <c r="R33" t="n">
-        <v>0</v>
-      </c>
-      <c r="S33" t="n">
-        <v>0</v>
-      </c>
-      <c r="T33" t="n">
-        <v>0</v>
-      </c>
-      <c r="U33" t="n">
-        <v>0</v>
-      </c>
-      <c r="V33" t="n">
-        <v>0</v>
-      </c>
-      <c r="W33" t="n">
-        <v>0</v>
-      </c>
-      <c r="X33" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y33" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="Z33" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AA33" t="n">
-        <v>0</v>
-      </c>
       <c r="AB33" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AC33" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AD33" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AE33" t="inlineStr">
         <is>
@@ -4735,10 +4735,10 @@
         </is>
       </c>
       <c r="AG33" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AH33" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AI33" t="n">
         <v>0</v>
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,13 +4797,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.3</v>
+        <v>1.9</v>
       </c>
       <c r="M34" t="n">
-        <v>5.4</v>
+        <v>3.6</v>
       </c>
       <c r="N34" t="n">
-        <v>10.5</v>
+        <v>4</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4836,10 +4836,10 @@
         <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.67</v>
+        <v>1.97</v>
       </c>
       <c r="Z34" t="n">
-        <v>2.2</v>
+        <v>1.83</v>
       </c>
       <c r="AA34" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Olympique Marseille</t>
+          <t>Kariobangi Sharks</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>KCB</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,13 +4926,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4965,10 +4965,10 @@
         <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Z35" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AA35" t="n">
         <v>0</v>
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,61 +5055,61 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>1.35</v>
+        <v>1.62</v>
       </c>
       <c r="M36" t="n">
-        <v>5.3</v>
+        <v>4.2</v>
       </c>
       <c r="N36" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="O36" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="S36" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="T36" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="U36" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="V36" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W36" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="X36" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="Z36" t="n">
-        <v>2.35</v>
+        <v>2.38</v>
       </c>
       <c r="AA36" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AB36" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AC36" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AD36" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AE36" t="inlineStr">
         <is>
@@ -5122,10 +5122,10 @@
         </is>
       </c>
       <c r="AG36" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AH36" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AI36" t="n">
         <v>0</v>
@@ -5148,7 +5148,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Olympique Marseille</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,13 +5184,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.45</v>
+        <v>1.56</v>
       </c>
       <c r="M37" t="n">
-        <v>3.15</v>
+        <v>4.3</v>
       </c>
       <c r="N37" t="n">
-        <v>3.05</v>
+        <v>5.1</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5217,16 +5217,16 @@
         <v>0</v>
       </c>
       <c r="W37" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="X37" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>2.52</v>
+        <v>1.63</v>
       </c>
       <c r="Z37" t="n">
-        <v>1.52</v>
+        <v>2.25</v>
       </c>
       <c r="AA37" t="n">
         <v>0</v>
@@ -5277,7 +5277,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,13 +5313,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>3</v>
+        <v>2.45</v>
       </c>
       <c r="M38" t="n">
-        <v>3.83</v>
+        <v>3.15</v>
       </c>
       <c r="N38" t="n">
-        <v>2.1</v>
+        <v>3.05</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5346,22 +5346,22 @@
         <v>0</v>
       </c>
       <c r="W38" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="X38" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Y38" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="Z38" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AA38" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC38" t="n">
         <v>0</v>
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,13 +5442,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="M39" t="n">
-        <v>7.6</v>
+        <v>3.83</v>
       </c>
       <c r="N39" t="n">
-        <v>1.15</v>
+        <v>2.1</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5481,16 +5481,16 @@
         <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="Z39" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>1.95</v>
+        <v>2.25</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.79</v>
+        <v>1.65</v>
       </c>
       <c r="AC39" t="n">
         <v>0</v>
@@ -5535,7 +5535,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Kariobangi Sharks</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>KCB</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5580,52 +5580,52 @@
         <v>0</v>
       </c>
       <c r="O40" t="n">
-        <v>0</v>
+        <v>12.47</v>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="R40" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="S40" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="T40" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="U40" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="V40" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W40" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X40" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="Y40" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z40" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AA40" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AB40" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AC40" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD40" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AE40" t="inlineStr">
         <is>
@@ -5638,10 +5638,10 @@
         </is>
       </c>
       <c r="AG40" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AH40" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AI40" t="n">
         <v>0</v>
@@ -5700,61 +5700,61 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1.62</v>
+        <v>1.66</v>
       </c>
       <c r="M41" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="N41" t="n">
+        <v>5</v>
+      </c>
+      <c r="O41" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="P41" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="Q41" t="n">
         <v>4.9</v>
       </c>
-      <c r="O41" t="n">
-        <v>0</v>
-      </c>
-      <c r="P41" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q41" t="n">
-        <v>0</v>
-      </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="S41" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="T41" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="U41" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="V41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W41" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="X41" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="Y41" t="n">
         <v>1.68</v>
       </c>
       <c r="Z41" t="n">
-        <v>2.18</v>
+        <v>2.26</v>
       </c>
       <c r="AA41" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AB41" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AC41" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AD41" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AE41" t="inlineStr">
         <is>
@@ -5767,10 +5767,10 @@
         </is>
       </c>
       <c r="AG41" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH41" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AI41" t="n">
         <v>0</v>
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,61 +5829,61 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>1.56</v>
+        <v>3.85</v>
       </c>
       <c r="M42" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="N42" t="n">
-        <v>5.4</v>
+        <v>1.58</v>
       </c>
       <c r="O42" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="P42" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="R42" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="S42" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="T42" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="U42" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="V42" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W42" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X42" t="n">
-        <v>0</v>
+        <v>5.35</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.63</v>
+        <v>1.43</v>
       </c>
       <c r="Z42" t="n">
-        <v>2.25</v>
+        <v>2.67</v>
       </c>
       <c r="AA42" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AB42" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC42" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AD42" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AE42" t="inlineStr">
         <is>
@@ -5896,10 +5896,10 @@
         </is>
       </c>
       <c r="AG42" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AH42" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AI42" t="n">
         <v>0</v>
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5958,61 +5958,61 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>4.3</v>
+        <v>1.3</v>
       </c>
       <c r="M43" t="n">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="N43" t="n">
-        <v>1.64</v>
+        <v>8</v>
       </c>
       <c r="O43" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="P43" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q43" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="R43" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="S43" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="T43" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="U43" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="V43" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W43" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="X43" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="Z43" t="n">
-        <v>2.75</v>
+        <v>2.37</v>
       </c>
       <c r="AA43" t="n">
-        <v>2.15</v>
+        <v>2.42</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="AC43" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AD43" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AE43" t="inlineStr">
         <is>
@@ -6025,10 +6025,10 @@
         </is>
       </c>
       <c r="AG43" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AH43" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AI43" t="n">
         <v>0</v>

--- a/jogos_2025-09-30.xlsx
+++ b/jogos_2025-09-30.xlsx
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Sogdiana</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Sogdiana</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1056,61 +1056,61 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="M5" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="N5" t="n">
-        <v>1.82</v>
+        <v>1.73</v>
       </c>
       <c r="O5" t="n">
-        <v>4.4</v>
+        <v>4.85</v>
       </c>
       <c r="P5" t="n">
         <v>2.05</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.77</v>
+        <v>2.46</v>
       </c>
       <c r="R5" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="S5" t="n">
         <v>2.62</v>
       </c>
       <c r="T5" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="U5" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="V5" t="n">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="W5" t="n">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="X5" t="n">
-        <v>2.75</v>
+        <v>2.79</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.25</v>
+        <v>2.12</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AA5" t="n">
-        <v>4</v>
+        <v>3.86</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AC5" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.29</v>
+        <v>1.21</v>
       </c>
       <c r="AI5" t="n">
         <v>2.38</v>
@@ -1185,61 +1185,61 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.93</v>
+        <v>1.86</v>
       </c>
       <c r="M6" t="n">
-        <v>3.55</v>
+        <v>3.84</v>
       </c>
       <c r="N6" t="n">
-        <v>3.25</v>
+        <v>3.7</v>
       </c>
       <c r="O6" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>4.45</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.61</v>
+        <v>1.7</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.31</v>
+        <v>2.15</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
@@ -1252,10 +1252,10 @@
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AI6" t="n">
         <v>0</v>
@@ -1407,22 +1407,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Wehen Wiesbaden</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,13 +1443,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1488,10 +1488,10 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
@@ -1665,22 +1665,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Saarbrucken</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>MSV Duisburg</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,13 +1701,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1746,10 +1746,10 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>Havelse</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Erzgebirge Aue</t>
+          <t>Waldhof Mannheim</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Wehen Wiesbaden</t>
+          <t>Erzgebirge Aue</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Havelse</t>
+          <t>Saarbrucken</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Waldhof Mannheim</t>
+          <t>MSV Duisburg</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Calcio Padova</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,13 +3120,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.6</v>
+        <v>2.15</v>
       </c>
       <c r="M21" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="N21" t="n">
-        <v>2.75</v>
+        <v>3.45</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3162,7 +3162,7 @@
         <v>2.2</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AA21" t="n">
         <v>0</v>
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Calcio Padova</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,13 +3249,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.15</v>
+        <v>3.6</v>
       </c>
       <c r="M22" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="N22" t="n">
-        <v>3.45</v>
+        <v>2.05</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3288,10 +3288,10 @@
         <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>2.2</v>
+        <v>2.07</v>
       </c>
       <c r="Z22" t="n">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="AA22" t="n">
         <v>0</v>
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mantova</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,13 +3378,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.8</v>
+        <v>2.6</v>
       </c>
       <c r="M23" t="n">
-        <v>3.7</v>
+        <v>3.25</v>
       </c>
       <c r="N23" t="n">
-        <v>4.3</v>
+        <v>2.75</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3417,10 +3417,10 @@
         <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.95</v>
+        <v>2.2</v>
       </c>
       <c r="Z23" t="n">
-        <v>1.85</v>
+        <v>1.67</v>
       </c>
       <c r="AA23" t="n">
         <v>0</v>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>Mantova</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,13 +3507,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>3.6</v>
+        <v>1.8</v>
       </c>
       <c r="M24" t="n">
-        <v>3.45</v>
+        <v>3.7</v>
       </c>
       <c r="N24" t="n">
-        <v>2.05</v>
+        <v>4.3</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3546,10 +3546,10 @@
         <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>2.07</v>
+        <v>1.95</v>
       </c>
       <c r="Z24" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AA24" t="n">
         <v>0</v>
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,13 +3765,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.18</v>
+        <v>2.55</v>
       </c>
       <c r="M26" t="n">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="N26" t="n">
-        <v>3.25</v>
+        <v>2.8</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3804,10 +3804,10 @@
         <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="Z26" t="n">
-        <v>1.8</v>
+        <v>1.68</v>
       </c>
       <c r="AA26" t="n">
         <v>0</v>
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,13 +3894,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>3.2</v>
+        <v>2.18</v>
       </c>
       <c r="M27" t="n">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="N27" t="n">
-        <v>2.2</v>
+        <v>3.25</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3933,10 +3933,10 @@
         <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="Z27" t="n">
-        <v>1.92</v>
+        <v>1.8</v>
       </c>
       <c r="AA27" t="n">
         <v>0</v>
@@ -3987,7 +3987,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4019,65 +4019,65 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.13</v>
+        <v>3</v>
       </c>
       <c r="M28" t="n">
-        <v>3.75</v>
+        <v>3.19</v>
       </c>
       <c r="N28" t="n">
-        <v>3.15</v>
+        <v>2.31</v>
       </c>
       <c r="O28" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="T28" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="X28" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.7</v>
+        <v>2.01</v>
       </c>
       <c r="Z28" t="n">
-        <v>2.15</v>
+        <v>1.8</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AD28" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
@@ -4090,10 +4090,10 @@
         </is>
       </c>
       <c r="AG28" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AH28" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AI28" t="n">
         <v>0</v>
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,13 +4410,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.55</v>
+        <v>2.13</v>
       </c>
       <c r="M31" t="n">
-        <v>3.3</v>
+        <v>3.75</v>
       </c>
       <c r="N31" t="n">
-        <v>2.8</v>
+        <v>3.15</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4449,10 +4449,10 @@
         <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>2.2</v>
+        <v>1.7</v>
       </c>
       <c r="Z31" t="n">
-        <v>1.68</v>
+        <v>2.15</v>
       </c>
       <c r="AA31" t="n">
         <v>0</v>
@@ -4632,7 +4632,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4664,65 +4664,65 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L33" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="M33" t="n">
-        <v>3.19</v>
+        <v>3.55</v>
       </c>
       <c r="N33" t="n">
-        <v>2.31</v>
+        <v>2.2</v>
       </c>
       <c r="O33" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="S33" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="T33" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="U33" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="V33" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W33" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="X33" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>2.01</v>
+        <v>1.88</v>
       </c>
       <c r="Z33" t="n">
-        <v>1.8</v>
+        <v>1.92</v>
       </c>
       <c r="AA33" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AC33" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AE33" t="inlineStr">
         <is>
@@ -4735,10 +4735,10 @@
         </is>
       </c>
       <c r="AG33" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AI33" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Kariobangi Sharks</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>KCB</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,13 +4926,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4965,10 +4965,10 @@
         <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Z35" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA35" t="n">
         <v>0</v>
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5058,58 +5058,58 @@
         <v>1.62</v>
       </c>
       <c r="M36" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="N36" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="O36" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="S36" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="T36" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="U36" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="V36" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W36" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="X36" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.61</v>
+        <v>1.68</v>
       </c>
       <c r="Z36" t="n">
-        <v>2.38</v>
+        <v>2.18</v>
       </c>
       <c r="AA36" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AC36" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AD36" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AE36" t="inlineStr">
         <is>
@@ -5122,10 +5122,10 @@
         </is>
       </c>
       <c r="AG36" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AH36" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="AI36" t="n">
         <v>0</v>
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Olympique Marseille</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,61 +5184,61 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>1.56</v>
+        <v>1.35</v>
       </c>
       <c r="M37" t="n">
-        <v>4.3</v>
+        <v>5.3</v>
       </c>
       <c r="N37" t="n">
-        <v>5.1</v>
+        <v>7</v>
       </c>
       <c r="O37" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="R37" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="S37" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="T37" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="U37" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="V37" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W37" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="X37" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="Z37" t="n">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
       <c r="AA37" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AB37" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC37" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AD37" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AE37" t="inlineStr">
         <is>
@@ -5251,10 +5251,10 @@
         </is>
       </c>
       <c r="AG37" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AH37" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AI37" t="n">
         <v>0</v>
@@ -5277,7 +5277,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,13 +5313,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.45</v>
+        <v>15</v>
       </c>
       <c r="M38" t="n">
-        <v>3.15</v>
+        <v>7.6</v>
       </c>
       <c r="N38" t="n">
-        <v>3.05</v>
+        <v>1.15</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5346,22 +5346,22 @@
         <v>0</v>
       </c>
       <c r="W38" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="X38" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>2.52</v>
+        <v>1.44</v>
       </c>
       <c r="Z38" t="n">
-        <v>1.52</v>
+        <v>2.75</v>
       </c>
       <c r="AA38" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB38" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC38" t="n">
         <v>0</v>
@@ -5535,7 +5535,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Kariobangi Sharks</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>KCB</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5580,52 +5580,52 @@
         <v>0</v>
       </c>
       <c r="O40" t="n">
-        <v>12.47</v>
+        <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="R40" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="S40" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="T40" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="U40" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="V40" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W40" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X40" t="n">
-        <v>6.1</v>
+        <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Z40" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AC40" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AD40" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AE40" t="inlineStr">
         <is>
@@ -5638,10 +5638,10 @@
         </is>
       </c>
       <c r="AG40" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AH40" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AI40" t="n">
         <v>0</v>
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Olympique Marseille</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,61 +5700,61 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1.66</v>
+        <v>1.56</v>
       </c>
       <c r="M41" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="N41" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="O41" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="P41" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="S41" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="T41" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="U41" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="V41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W41" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="X41" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.68</v>
+        <v>1.63</v>
       </c>
       <c r="Z41" t="n">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="AA41" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AC41" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AD41" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AE41" t="inlineStr">
         <is>
@@ -5767,10 +5767,10 @@
         </is>
       </c>
       <c r="AG41" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH41" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="AI41" t="n">
         <v>0</v>
@@ -5793,7 +5793,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,61 +5829,61 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>3.85</v>
+        <v>2.45</v>
       </c>
       <c r="M42" t="n">
-        <v>4.4</v>
+        <v>3.15</v>
       </c>
       <c r="N42" t="n">
-        <v>1.58</v>
+        <v>3.05</v>
       </c>
       <c r="O42" t="n">
-        <v>4.45</v>
+        <v>0</v>
       </c>
       <c r="P42" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="S42" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="T42" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="U42" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="V42" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W42" t="n">
-        <v>1.12</v>
+        <v>1.53</v>
       </c>
       <c r="X42" t="n">
-        <v>5.35</v>
+        <v>2.5</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.43</v>
+        <v>2.52</v>
       </c>
       <c r="Z42" t="n">
-        <v>2.67</v>
+        <v>1.52</v>
       </c>
       <c r="AA42" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AC42" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AD42" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AE42" t="inlineStr">
         <is>
@@ -5896,10 +5896,10 @@
         </is>
       </c>
       <c r="AG42" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AH42" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AI42" t="n">
         <v>0</v>
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5958,61 +5958,61 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>1.3</v>
+        <v>4.3</v>
       </c>
       <c r="M43" t="n">
-        <v>5</v>
+        <v>4.4</v>
       </c>
       <c r="N43" t="n">
-        <v>8</v>
+        <v>1.64</v>
       </c>
       <c r="O43" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="P43" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="R43" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="S43" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="T43" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="U43" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="V43" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W43" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="X43" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="Z43" t="n">
-        <v>2.37</v>
+        <v>2.75</v>
       </c>
       <c r="AA43" t="n">
-        <v>2.42</v>
+        <v>2.15</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="AC43" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AD43" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AE43" t="inlineStr">
         <is>
@@ -6025,10 +6025,10 @@
         </is>
       </c>
       <c r="AG43" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AH43" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AI43" t="n">
         <v>0</v>

--- a/jogos_2025-09-30.xlsx
+++ b/jogos_2025-09-30.xlsx
@@ -1194,34 +1194,34 @@
         <v>3.7</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="Y6" t="n">
         <v>1.7</v>
@@ -1230,16 +1230,16 @@
         <v>2.15</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
@@ -1252,10 +1252,10 @@
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AI6" t="n">
         <v>0</v>
@@ -1407,22 +1407,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Wehen Wiesbaden</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,61 +1443,61 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>6.89</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>4.77</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AI8" t="n">
         <v>0</v>
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,61 +1572,61 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.26</v>
+        <v>1.46</v>
       </c>
       <c r="M9" t="n">
-        <v>5.1</v>
+        <v>4.25</v>
       </c>
       <c r="N9" t="n">
-        <v>7.6</v>
+        <v>4.8</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.47</v>
+        <v>1.42</v>
       </c>
       <c r="Z9" t="n">
         <v>2.5</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.17</v>
+        <v>2.25</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
@@ -1665,22 +1665,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Havelse</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Waldhof Mannheim</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,13 +1701,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1746,10 +1746,10 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Havelse</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Waldhof Mannheim</t>
+          <t>Wehen Wiesbaden</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>Saarbrucken</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Erzgebirge Aue</t>
+          <t>MSV Duisburg</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Saarbrucken</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>MSV Duisburg</t>
+          <t>Erzgebirge Aue</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,61 +2346,61 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
@@ -2413,10 +2413,10 @@
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AI15" t="n">
         <v>0</v>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,61 +2475,61 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
@@ -2542,10 +2542,10 @@
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AI16" t="n">
         <v>0</v>
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2613,52 +2613,52 @@
         <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>6.74</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>5.65</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
@@ -2671,10 +2671,10 @@
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AI17" t="n">
         <v>0</v>
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,61 +2733,61 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
@@ -2800,10 +2800,10 @@
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AI18" t="n">
         <v>0</v>
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,61 +2862,61 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>3.43</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
@@ -2929,10 +2929,10 @@
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AI19" t="n">
         <v>0</v>
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Mantova</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,61 +2991,61 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.05</v>
+        <v>1.8</v>
       </c>
       <c r="M20" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="N20" t="n">
-        <v>3.45</v>
+        <v>4.3</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="Z20" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
@@ -3058,10 +3058,10 @@
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AI20" t="n">
         <v>0</v>
@@ -3129,34 +3129,34 @@
         <v>3.45</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="Y21" t="n">
         <v>2.2</v>
@@ -3165,16 +3165,16 @@
         <v>1.65</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
@@ -3187,10 +3187,10 @@
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AI21" t="n">
         <v>0</v>
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,61 +3249,61 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>3.6</v>
+        <v>2.6</v>
       </c>
       <c r="M22" t="n">
-        <v>3.45</v>
+        <v>3.25</v>
       </c>
       <c r="N22" t="n">
-        <v>2.05</v>
+        <v>2.75</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="Y22" t="n">
-        <v>2.07</v>
+        <v>2.2</v>
       </c>
       <c r="Z22" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
@@ -3316,10 +3316,10 @@
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AI22" t="n">
         <v>0</v>
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,61 +3378,61 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.6</v>
+        <v>2.15</v>
       </c>
       <c r="M23" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="N23" t="n">
-        <v>2.75</v>
+        <v>3.45</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="Y23" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="Z23" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
@@ -3445,10 +3445,10 @@
         </is>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AH23" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AI23" t="n">
         <v>0</v>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mantova</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,61 +3507,61 @@
         </is>
       </c>
       <c r="L24" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="M24" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="N24" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="O24" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="P24" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S24" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="V24" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="X24" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="Y24" t="n">
         <v>1.8</v>
       </c>
-      <c r="M24" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="N24" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="O24" t="n">
-        <v>0</v>
-      </c>
-      <c r="P24" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>0</v>
-      </c>
-      <c r="R24" t="n">
-        <v>0</v>
-      </c>
-      <c r="S24" t="n">
-        <v>0</v>
-      </c>
-      <c r="T24" t="n">
-        <v>0</v>
-      </c>
-      <c r="U24" t="n">
-        <v>0</v>
-      </c>
-      <c r="V24" t="n">
-        <v>0</v>
-      </c>
-      <c r="W24" t="n">
-        <v>0</v>
-      </c>
-      <c r="X24" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>1.95</v>
-      </c>
       <c r="Z24" t="n">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
@@ -3574,10 +3574,10 @@
         </is>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AI24" t="n">
         <v>0</v>
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,61 +3636,61 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.15</v>
+        <v>3.6</v>
       </c>
       <c r="M25" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="N25" t="n">
-        <v>3.45</v>
+        <v>2.05</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>4.24</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="Y25" t="n">
-        <v>2.18</v>
+        <v>2.07</v>
       </c>
       <c r="Z25" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
@@ -3703,10 +3703,10 @@
         </is>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AH25" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AI25" t="n">
         <v>0</v>
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,61 +3765,61 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.55</v>
+        <v>1.9</v>
       </c>
       <c r="M26" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="N26" t="n">
-        <v>2.8</v>
+        <v>4</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="Y26" t="n">
-        <v>2.2</v>
+        <v>1.97</v>
       </c>
       <c r="Z26" t="n">
-        <v>1.68</v>
+        <v>1.83</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AC26" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AD26" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
@@ -3832,10 +3832,10 @@
         </is>
       </c>
       <c r="AG26" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH26" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AI26" t="n">
         <v>0</v>
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,61 +3894,61 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.18</v>
+        <v>2.13</v>
       </c>
       <c r="M27" t="n">
-        <v>3.45</v>
+        <v>3.75</v>
       </c>
       <c r="N27" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="O27" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X27" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="Y27" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="Z27" t="n">
-        <v>1.8</v>
+        <v>2.15</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AC27" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AD27" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
@@ -3961,10 +3961,10 @@
         </is>
       </c>
       <c r="AG27" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AH27" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AI27" t="n">
         <v>0</v>
@@ -3987,7 +3987,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4019,38 +4019,38 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L28" t="n">
-        <v>3</v>
+        <v>2.18</v>
       </c>
       <c r="M28" t="n">
-        <v>3.19</v>
+        <v>3.45</v>
       </c>
       <c r="N28" t="n">
-        <v>2.31</v>
+        <v>3.25</v>
       </c>
       <c r="O28" t="n">
-        <v>3.6</v>
+        <v>2.84</v>
       </c>
       <c r="P28" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.92</v>
+        <v>3.9</v>
       </c>
       <c r="R28" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="S28" t="n">
         <v>2.75</v>
       </c>
       <c r="T28" t="n">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="U28" t="n">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="V28" t="n">
         <v>1.02</v>
@@ -4059,25 +4059,25 @@
         <v>1.28</v>
       </c>
       <c r="X28" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="Y28" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="Z28" t="n">
         <v>1.8</v>
       </c>
       <c r="AA28" t="n">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
@@ -4090,10 +4090,10 @@
         </is>
       </c>
       <c r="AG28" t="n">
-        <v>1.62</v>
+        <v>1.31</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.37</v>
+        <v>1.67</v>
       </c>
       <c r="AI28" t="n">
         <v>0</v>
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,61 +4152,61 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.3</v>
+        <v>3.2</v>
       </c>
       <c r="M29" t="n">
-        <v>5.4</v>
+        <v>3.55</v>
       </c>
       <c r="N29" t="n">
-        <v>10.5</v>
+        <v>2.2</v>
       </c>
       <c r="O29" t="n">
-        <v>0</v>
+        <v>3.81</v>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="S29" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="T29" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="V29" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W29" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="X29" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.67</v>
+        <v>1.88</v>
       </c>
       <c r="Z29" t="n">
-        <v>2.2</v>
+        <v>1.92</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AC29" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AD29" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
@@ -4219,10 +4219,10 @@
         </is>
       </c>
       <c r="AG29" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH29" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AI29" t="n">
         <v>0</v>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4406,65 +4406,65 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.13</v>
+        <v>3</v>
       </c>
       <c r="M31" t="n">
-        <v>3.75</v>
+        <v>3.19</v>
       </c>
       <c r="N31" t="n">
-        <v>3.15</v>
+        <v>2.31</v>
       </c>
       <c r="O31" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S31" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="T31" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="V31" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W31" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="X31" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.7</v>
+        <v>2.01</v>
       </c>
       <c r="Z31" t="n">
-        <v>2.15</v>
+        <v>1.8</v>
       </c>
       <c r="AA31" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AB31" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AC31" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AD31" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AE31" t="inlineStr">
         <is>
@@ -4477,10 +4477,10 @@
         </is>
       </c>
       <c r="AG31" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AH31" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AI31" t="n">
         <v>0</v>
@@ -4548,34 +4548,34 @@
         <v>5</v>
       </c>
       <c r="O32" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>5.03</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="S32" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="T32" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="U32" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="V32" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W32" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X32" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="Y32" t="n">
         <v>1.68</v>
@@ -4584,16 +4584,16 @@
         <v>2.2</v>
       </c>
       <c r="AA32" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AB32" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AC32" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AD32" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AE32" t="inlineStr">
         <is>
@@ -4606,10 +4606,10 @@
         </is>
       </c>
       <c r="AG32" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AH32" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AI32" t="n">
         <v>0</v>
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,61 +4668,61 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>3.2</v>
+        <v>1.3</v>
       </c>
       <c r="M33" t="n">
-        <v>3.55</v>
+        <v>5.4</v>
       </c>
       <c r="N33" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="O33" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="P33" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="R33" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S33" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V33" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W33" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="X33" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="Z33" t="n">
         <v>2.2</v>
       </c>
-      <c r="O33" t="n">
-        <v>0</v>
-      </c>
-      <c r="P33" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>0</v>
-      </c>
-      <c r="R33" t="n">
-        <v>0</v>
-      </c>
-      <c r="S33" t="n">
-        <v>0</v>
-      </c>
-      <c r="T33" t="n">
-        <v>0</v>
-      </c>
-      <c r="U33" t="n">
-        <v>0</v>
-      </c>
-      <c r="V33" t="n">
-        <v>0</v>
-      </c>
-      <c r="W33" t="n">
-        <v>0</v>
-      </c>
-      <c r="X33" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y33" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="Z33" t="n">
-        <v>1.92</v>
-      </c>
       <c r="AA33" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AB33" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AC33" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AD33" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AE33" t="inlineStr">
         <is>
@@ -4735,10 +4735,10 @@
         </is>
       </c>
       <c r="AG33" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AH33" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="AI33" t="n">
         <v>0</v>
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,61 +4797,61 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.9</v>
+        <v>2.55</v>
       </c>
       <c r="M34" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="N34" t="n">
-        <v>4</v>
+        <v>2.8</v>
       </c>
       <c r="O34" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="S34" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="T34" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="U34" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V34" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W34" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="X34" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.97</v>
+        <v>2.2</v>
       </c>
       <c r="Z34" t="n">
-        <v>1.83</v>
+        <v>1.68</v>
       </c>
       <c r="AA34" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="AB34" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AC34" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AD34" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AE34" t="inlineStr">
         <is>
@@ -4864,10 +4864,10 @@
         </is>
       </c>
       <c r="AG34" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AH34" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AI34" t="n">
         <v>0</v>
@@ -4935,34 +4935,34 @@
         <v>5.4</v>
       </c>
       <c r="O35" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="S35" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="T35" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="V35" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W35" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="X35" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="Y35" t="n">
         <v>1.63</v>
@@ -4971,16 +4971,16 @@
         <v>2.25</v>
       </c>
       <c r="AA35" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AB35" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AC35" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AD35" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AE35" t="inlineStr">
         <is>
@@ -4993,10 +4993,10 @@
         </is>
       </c>
       <c r="AG35" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AH35" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AI35" t="n">
         <v>0</v>
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,13 +5055,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>1.62</v>
+        <v>3</v>
       </c>
       <c r="M36" t="n">
-        <v>4.1</v>
+        <v>3.83</v>
       </c>
       <c r="N36" t="n">
-        <v>4.9</v>
+        <v>2.1</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5094,16 +5094,16 @@
         <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="Z36" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB36" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC36" t="n">
         <v>0</v>
@@ -5148,7 +5148,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Kariobangi Sharks</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>KCB</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,61 +5184,61 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="S37" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="T37" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="U37" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="V37" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W37" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="X37" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z37" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC37" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AD37" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AE37" t="inlineStr">
         <is>
@@ -5251,10 +5251,10 @@
         </is>
       </c>
       <c r="AG37" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AH37" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AI37" t="n">
         <v>0</v>
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,13 +5313,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>15</v>
+        <v>1.62</v>
       </c>
       <c r="M38" t="n">
-        <v>7.6</v>
+        <v>4.1</v>
       </c>
       <c r="N38" t="n">
-        <v>1.15</v>
+        <v>4.9</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5352,16 +5352,16 @@
         <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.44</v>
+        <v>1.68</v>
       </c>
       <c r="Z38" t="n">
-        <v>2.75</v>
+        <v>2.18</v>
       </c>
       <c r="AA38" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AC38" t="n">
         <v>0</v>
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,77 +5442,77 @@
         </is>
       </c>
       <c r="L39" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="M39" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="N39" t="n">
+        <v>7</v>
+      </c>
+      <c r="O39" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="P39" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="R39" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="S39" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="T39" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="V39" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W39" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="X39" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AE39" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF39" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG39" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AH39" t="n">
         <v>3</v>
-      </c>
-      <c r="M39" t="n">
-        <v>3.83</v>
-      </c>
-      <c r="N39" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="O39" t="n">
-        <v>0</v>
-      </c>
-      <c r="P39" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q39" t="n">
-        <v>0</v>
-      </c>
-      <c r="R39" t="n">
-        <v>0</v>
-      </c>
-      <c r="S39" t="n">
-        <v>0</v>
-      </c>
-      <c r="T39" t="n">
-        <v>0</v>
-      </c>
-      <c r="U39" t="n">
-        <v>0</v>
-      </c>
-      <c r="V39" t="n">
-        <v>0</v>
-      </c>
-      <c r="W39" t="n">
-        <v>0</v>
-      </c>
-      <c r="X39" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y39" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA39" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AB39" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AC39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE39" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF39" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH39" t="n">
-        <v>0</v>
       </c>
       <c r="AI39" t="n">
         <v>0</v>
@@ -5535,7 +5535,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Kariobangi Sharks</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>KCB</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,13 +5571,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5610,16 +5610,16 @@
         <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z40" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AA40" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB40" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Olympique Marseille</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,13 +5700,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1.56</v>
+        <v>4.3</v>
       </c>
       <c r="M41" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="N41" t="n">
-        <v>5.1</v>
+        <v>1.64</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5739,16 +5739,16 @@
         <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.63</v>
+        <v>1.44</v>
       </c>
       <c r="Z41" t="n">
-        <v>2.25</v>
+        <v>2.75</v>
       </c>
       <c r="AA41" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB41" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC41" t="n">
         <v>0</v>
@@ -5838,28 +5838,28 @@
         <v>3.05</v>
       </c>
       <c r="O42" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P42" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="R42" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="S42" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="T42" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="U42" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="V42" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="W42" t="n">
         <v>1.53</v>
@@ -5874,16 +5874,16 @@
         <v>1.52</v>
       </c>
       <c r="AA42" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AB42" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AC42" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AD42" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AE42" t="inlineStr">
         <is>
@@ -5896,10 +5896,10 @@
         </is>
       </c>
       <c r="AG42" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AH42" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AI42" t="n">
         <v>0</v>
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Olympique Marseille</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5958,61 +5958,61 @@
         </is>
       </c>
       <c r="L43" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="M43" t="n">
         <v>4.3</v>
       </c>
-      <c r="M43" t="n">
+      <c r="N43" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="O43" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="P43" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="Q43" t="n">
         <v>4.4</v>
       </c>
-      <c r="N43" t="n">
+      <c r="R43" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S43" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="T43" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="U43" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="V43" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W43" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="X43" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AB43" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AC43" t="n">
         <v>1.64</v>
       </c>
-      <c r="O43" t="n">
-        <v>0</v>
-      </c>
-      <c r="P43" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q43" t="n">
-        <v>0</v>
-      </c>
-      <c r="R43" t="n">
-        <v>0</v>
-      </c>
-      <c r="S43" t="n">
-        <v>0</v>
-      </c>
-      <c r="T43" t="n">
-        <v>0</v>
-      </c>
-      <c r="U43" t="n">
-        <v>0</v>
-      </c>
-      <c r="V43" t="n">
-        <v>0</v>
-      </c>
-      <c r="W43" t="n">
-        <v>0</v>
-      </c>
-      <c r="X43" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y43" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="Z43" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AA43" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AB43" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AC43" t="n">
-        <v>0</v>
-      </c>
       <c r="AD43" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AE43" t="inlineStr">
         <is>
@@ -6025,10 +6025,10 @@
         </is>
       </c>
       <c r="AG43" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH43" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AI43" t="n">
         <v>0</v>

--- a/jogos_2025-09-30.xlsx
+++ b/jogos_2025-09-30.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK47"/>
+  <dimension ref="A1:AK46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -757,27 +757,27 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Kariobangi Sharks</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>KCB</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -877,7 +877,7 @@
         <v>0</v>
       </c>
       <c r="AK3" s="3" t="n">
-        <v>45930.45833333334</v>
+        <v>45930.41666666666</v>
       </c>
     </row>
     <row r="4">
@@ -1015,27 +1015,27 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Botev Plovdiv</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1052,65 +1052,65 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>4.85</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>3.86</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
@@ -1123,19 +1123,19 @@
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AI5" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AK5" s="3" t="n">
-        <v>45930.47916666666</v>
+        <v>45930.45833333334</v>
       </c>
     </row>
     <row r="6">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Police</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Ulinzi Stars</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1185,61 +1185,61 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>4.45</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
@@ -1252,10 +1252,10 @@
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AI6" t="n">
         <v>0</v>
@@ -1264,7 +1264,7 @@
         <v>0</v>
       </c>
       <c r="AK6" s="3" t="n">
-        <v>45930.57291666666</v>
+        <v>45930.5</v>
       </c>
     </row>
     <row r="7">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1314,13 +1314,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>19</v>
+        <v>1.86</v>
       </c>
       <c r="M7" t="n">
-        <v>8.9</v>
+        <v>3.84</v>
       </c>
       <c r="N7" t="n">
-        <v>1.11</v>
+        <v>3.7</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1353,16 +1353,16 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.3</v>
+        <v>1.7</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.4</v>
+        <v>2.15</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1402,27 +1402,27 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,62 +1443,62 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.36</v>
+        <v>19</v>
       </c>
       <c r="M8" t="n">
-        <v>4.75</v>
+        <v>8.9</v>
       </c>
       <c r="N8" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="O8" t="n">
+        <v>15</v>
+      </c>
+      <c r="P8" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S8" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X8" t="n">
         <v>7</v>
       </c>
-      <c r="O8" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="P8" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>6.89</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="S8" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="T8" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="U8" t="n">
+      <c r="Y8" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AD8" t="n">
         <v>1.62</v>
       </c>
-      <c r="V8" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="X8" t="n">
-        <v>4.77</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>2</v>
-      </c>
       <c r="AE8" t="inlineStr">
         <is>
           <t>[]</t>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="AH8" t="n">
-        <v>2.75</v>
+        <v>1.01</v>
       </c>
       <c r="AI8" t="n">
         <v>0</v>
@@ -1522,7 +1522,7 @@
         <v>0</v>
       </c>
       <c r="AK8" s="3" t="n">
-        <v>45930.58333333334</v>
+        <v>45930.57291666666</v>
       </c>
     </row>
     <row r="9">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Havelse</t>
+          <t>Hansa Rostock</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Waldhof Mannheim</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1794,22 +1794,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Wehen Wiesbaden</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,61 +1830,61 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>6.89</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>4.77</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -1897,10 +1897,10 @@
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AI11" t="n">
         <v>0</v>
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Hansa Rostock</t>
+          <t>Havelse</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>Waldhof Mannheim</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Saarbrucken</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>MSV Duisburg</t>
+          <t>Erzgebirge Aue</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Erzgebirge Aue</t>
+          <t>Wehen Wiesbaden</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2305,12 +2305,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Saarbrucken</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>MSV Duisburg</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,61 +2346,61 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
@@ -2413,10 +2413,10 @@
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="AI15" t="n">
         <v>0</v>
@@ -2425,7 +2425,7 @@
         <v>0</v>
       </c>
       <c r="AK15" s="3" t="n">
-        <v>45930.625</v>
+        <v>45930.58333333334</v>
       </c>
     </row>
     <row r="16">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,58 +2475,58 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.15</v>
+        <v>2.75</v>
       </c>
       <c r="M16" t="n">
-        <v>3.78</v>
+        <v>3.5</v>
       </c>
       <c r="N16" t="n">
-        <v>2.97</v>
+        <v>2.25</v>
       </c>
       <c r="O16" t="n">
-        <v>2.56</v>
+        <v>3</v>
       </c>
       <c r="P16" t="n">
         <v>2.45</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.4</v>
+        <v>2.65</v>
       </c>
       <c r="R16" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="S16" t="n">
-        <v>3.5</v>
+        <v>3.34</v>
       </c>
       <c r="T16" t="n">
-        <v>2.18</v>
+        <v>2.32</v>
       </c>
       <c r="U16" t="n">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="V16" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W16" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="X16" t="n">
-        <v>4.55</v>
+        <v>4.8</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.55</v>
+        <v>1.59</v>
       </c>
       <c r="Z16" t="n">
-        <v>2.39</v>
+        <v>2.3</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.29</v>
+        <v>2.4</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AD16" t="n">
         <v>2.5</v>
@@ -2542,10 +2542,10 @@
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.69</v>
+        <v>1.39</v>
       </c>
       <c r="AI16" t="n">
         <v>0</v>
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,77 +2604,77 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>3.43</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="O17" t="n">
-        <v>1.7</v>
+        <v>3.78</v>
       </c>
       <c r="P17" t="n">
-        <v>2.85</v>
+        <v>2.4</v>
       </c>
       <c r="Q17" t="n">
-        <v>6.74</v>
+        <v>2.38</v>
       </c>
       <c r="R17" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S17" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X17" t="n">
+        <v>5.05</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AE17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG17" t="n">
         <v>1.2</v>
       </c>
-      <c r="S17" t="n">
-        <v>4</v>
-      </c>
-      <c r="T17" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="V17" t="n">
-        <v>0</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X17" t="n">
-        <v>5.65</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AE17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG17" t="n">
-        <v>1.13</v>
-      </c>
       <c r="AH17" t="n">
-        <v>3.34</v>
+        <v>1.27</v>
       </c>
       <c r="AI17" t="n">
         <v>0</v>
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,61 +2862,61 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>3.43</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>3.94</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>3.78</v>
+        <v>1.7</v>
       </c>
       <c r="P19" t="n">
-        <v>2.4</v>
+        <v>2.85</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.38</v>
+        <v>6.74</v>
       </c>
       <c r="R19" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="S19" t="n">
-        <v>3.55</v>
+        <v>4</v>
       </c>
       <c r="T19" t="n">
-        <v>2.2</v>
+        <v>2.08</v>
       </c>
       <c r="U19" t="n">
-        <v>1.63</v>
+        <v>1.73</v>
       </c>
       <c r="V19" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X19" t="n">
-        <v>5.05</v>
+        <v>5.65</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.44</v>
+        <v>1.37</v>
       </c>
       <c r="Z19" t="n">
-        <v>2.5</v>
+        <v>2.67</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.24</v>
+        <v>2.08</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.61</v>
+        <v>1.8</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.46</v>
+        <v>1.66</v>
       </c>
       <c r="AD19" t="n">
-        <v>2.5</v>
+        <v>2.07</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
@@ -2929,10 +2929,10 @@
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.27</v>
+        <v>3.34</v>
       </c>
       <c r="AI19" t="n">
         <v>0</v>
@@ -2950,12 +2950,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mantova</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,77 +2991,77 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.8</v>
+        <v>2.15</v>
       </c>
       <c r="M20" t="n">
-        <v>3.7</v>
+        <v>3.78</v>
       </c>
       <c r="N20" t="n">
-        <v>4.3</v>
+        <v>2.97</v>
       </c>
       <c r="O20" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="P20" t="n">
         <v>2.45</v>
       </c>
-      <c r="P20" t="n">
-        <v>2.14</v>
-      </c>
       <c r="Q20" t="n">
-        <v>4.8</v>
+        <v>3.4</v>
       </c>
       <c r="R20" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S20" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="X20" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AE20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG20" t="n">
         <v>1.38</v>
       </c>
-      <c r="S20" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="T20" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="U20" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V20" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W20" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="X20" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>3.32</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AE20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG20" t="n">
-        <v>1.23</v>
-      </c>
       <c r="AH20" t="n">
-        <v>1.94</v>
+        <v>1.69</v>
       </c>
       <c r="AI20" t="n">
         <v>0</v>
@@ -3070,7 +3070,7 @@
         <v>0</v>
       </c>
       <c r="AK20" s="3" t="n">
-        <v>45930.64583333334</v>
+        <v>45930.625</v>
       </c>
     </row>
     <row r="21">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Calcio Padova</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,77 +3120,77 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.15</v>
+        <v>3.6</v>
       </c>
       <c r="M21" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="N21" t="n">
-        <v>3.45</v>
+        <v>2.05</v>
       </c>
       <c r="O21" t="n">
-        <v>2.81</v>
+        <v>4.24</v>
       </c>
       <c r="P21" t="n">
-        <v>2.03</v>
+        <v>2.08</v>
       </c>
       <c r="Q21" t="n">
-        <v>4.15</v>
+        <v>2.7</v>
       </c>
       <c r="R21" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="S21" t="n">
-        <v>2.51</v>
+        <v>2.64</v>
       </c>
       <c r="T21" t="n">
-        <v>3.08</v>
+        <v>2.8</v>
       </c>
       <c r="U21" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="X21" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AE21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG21" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AH21" t="n">
         <v>1.3</v>
-      </c>
-      <c r="V21" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W21" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="X21" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AE21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG21" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>1.69</v>
       </c>
       <c r="AI21" t="n">
         <v>0</v>
@@ -3267,10 +3267,10 @@
         <v>3.35</v>
       </c>
       <c r="R22" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="S22" t="n">
-        <v>2.51</v>
+        <v>2.55</v>
       </c>
       <c r="T22" t="n">
         <v>3.08</v>
@@ -3300,10 +3300,10 @@
         <v>1.19</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.85</v>
+        <v>1.78</v>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Calcio Padova</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3387,52 +3387,52 @@
         <v>3.45</v>
       </c>
       <c r="O23" t="n">
-        <v>2.81</v>
+        <v>2.8</v>
       </c>
       <c r="P23" t="n">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="Q23" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="R23" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="S23" t="n">
-        <v>2.57</v>
+        <v>2.51</v>
       </c>
       <c r="T23" t="n">
-        <v>3.04</v>
+        <v>3</v>
       </c>
       <c r="U23" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="V23" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="W23" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="X23" t="n">
-        <v>2.88</v>
+        <v>2.78</v>
       </c>
       <c r="Y23" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="Z23" t="n">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AA23" t="n">
-        <v>3.82</v>
+        <v>3.9</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.87</v>
+        <v>1.93</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.85</v>
+        <v>1.76</v>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
@@ -3448,7 +3448,7 @@
         <v>1.32</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="AI23" t="n">
         <v>0</v>
@@ -3516,7 +3516,7 @@
         <v>3.45</v>
       </c>
       <c r="O24" t="n">
-        <v>2.66</v>
+        <v>2.55</v>
       </c>
       <c r="P24" t="n">
         <v>2.17</v>
@@ -3528,22 +3528,22 @@
         <v>1.32</v>
       </c>
       <c r="S24" t="n">
-        <v>2.98</v>
+        <v>2.95</v>
       </c>
       <c r="T24" t="n">
         <v>2.6</v>
       </c>
       <c r="U24" t="n">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="V24" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="W24" t="n">
         <v>1.21</v>
       </c>
       <c r="X24" t="n">
-        <v>3.74</v>
+        <v>3.7</v>
       </c>
       <c r="Y24" t="n">
         <v>1.8</v>
@@ -3561,7 +3561,7 @@
         <v>1.65</v>
       </c>
       <c r="AD24" t="n">
-        <v>2.11</v>
+        <v>2.13</v>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
@@ -3574,7 +3574,7 @@
         </is>
       </c>
       <c r="AG24" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AH24" t="n">
         <v>1.74</v>
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,61 +3636,61 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>3.6</v>
+        <v>2.15</v>
       </c>
       <c r="M25" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="N25" t="n">
         <v>3.45</v>
       </c>
-      <c r="N25" t="n">
-        <v>2.05</v>
-      </c>
       <c r="O25" t="n">
-        <v>4.24</v>
+        <v>2.75</v>
       </c>
       <c r="P25" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.72</v>
+        <v>3.9</v>
       </c>
       <c r="R25" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="S25" t="n">
-        <v>2.64</v>
+        <v>2.57</v>
       </c>
       <c r="T25" t="n">
-        <v>2.93</v>
+        <v>3</v>
       </c>
       <c r="U25" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="V25" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="W25" t="n">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="X25" t="n">
-        <v>3.02</v>
+        <v>2.88</v>
       </c>
       <c r="Y25" t="n">
-        <v>2.07</v>
+        <v>2.18</v>
       </c>
       <c r="Z25" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AA25" t="n">
-        <v>3.55</v>
+        <v>3.82</v>
       </c>
       <c r="AB25" t="n">
         <v>1.23</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.89</v>
+        <v>1.77</v>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
@@ -3703,10 +3703,10 @@
         </is>
       </c>
       <c r="AG25" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.3</v>
+        <v>1.7</v>
       </c>
       <c r="AI25" t="n">
         <v>0</v>
@@ -3724,12 +3724,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Mantova</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,61 +3765,61 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="M26" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="N26" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="O26" t="n">
-        <v>2.48</v>
+        <v>2.45</v>
       </c>
       <c r="P26" t="n">
-        <v>2.13</v>
+        <v>2.14</v>
       </c>
       <c r="Q26" t="n">
-        <v>4.55</v>
+        <v>4.8</v>
       </c>
       <c r="R26" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S26" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="U26" t="n">
         <v>1.36</v>
       </c>
-      <c r="S26" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="T26" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="U26" t="n">
-        <v>1.35</v>
-      </c>
       <c r="V26" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="W26" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="X26" t="n">
-        <v>3.25</v>
+        <v>3.12</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="Z26" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AA26" t="n">
-        <v>3.4</v>
+        <v>3.32</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.81</v>
+        <v>1.84</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.91</v>
+        <v>1.88</v>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
@@ -3832,10 +3832,10 @@
         </is>
       </c>
       <c r="AG26" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.9</v>
+        <v>1.94</v>
       </c>
       <c r="AI26" t="n">
         <v>0</v>
@@ -3844,7 +3844,7 @@
         <v>0</v>
       </c>
       <c r="AK26" s="3" t="n">
-        <v>45930.65625</v>
+        <v>45930.64583333334</v>
       </c>
     </row>
     <row r="27">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,61 +3894,61 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.13</v>
+        <v>3.1</v>
       </c>
       <c r="M27" t="n">
-        <v>3.75</v>
+        <v>3.4</v>
       </c>
       <c r="N27" t="n">
-        <v>3.15</v>
+        <v>2.2</v>
       </c>
       <c r="O27" t="n">
-        <v>2.73</v>
+        <v>3.81</v>
       </c>
       <c r="P27" t="n">
-        <v>2.27</v>
+        <v>2.15</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.54</v>
+        <v>2.7</v>
       </c>
       <c r="R27" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="S27" t="n">
-        <v>3.14</v>
+        <v>2.88</v>
       </c>
       <c r="T27" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="U27" t="n">
-        <v>1.48</v>
+        <v>1.42</v>
       </c>
       <c r="V27" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W27" t="n">
-        <v>1.18</v>
+        <v>1.28</v>
       </c>
       <c r="X27" t="n">
-        <v>4.05</v>
+        <v>3.48</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.7</v>
+        <v>1.89</v>
       </c>
       <c r="Z27" t="n">
-        <v>2.15</v>
+        <v>1.91</v>
       </c>
       <c r="AA27" t="n">
-        <v>2.56</v>
+        <v>3.12</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.42</v>
+        <v>1.33</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.55</v>
+        <v>1.68</v>
       </c>
       <c r="AD27" t="n">
-        <v>2.3</v>
+        <v>2.06</v>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
@@ -3961,10 +3961,10 @@
         </is>
       </c>
       <c r="AG27" t="n">
-        <v>1.38</v>
+        <v>1.28</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.67</v>
+        <v>1.33</v>
       </c>
       <c r="AI27" t="n">
         <v>0</v>
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,61 +4023,61 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.18</v>
+        <v>2.55</v>
       </c>
       <c r="M28" t="n">
-        <v>3.45</v>
+        <v>3.2</v>
       </c>
       <c r="N28" t="n">
-        <v>3.25</v>
+        <v>2.8</v>
       </c>
       <c r="O28" t="n">
-        <v>2.84</v>
+        <v>3.18</v>
       </c>
       <c r="P28" t="n">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.9</v>
+        <v>3.35</v>
       </c>
       <c r="R28" t="n">
-        <v>1.37</v>
+        <v>1.43</v>
       </c>
       <c r="S28" t="n">
-        <v>2.75</v>
+        <v>2.54</v>
       </c>
       <c r="T28" t="n">
-        <v>2.88</v>
+        <v>3.08</v>
       </c>
       <c r="U28" t="n">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="V28" t="n">
         <v>1.02</v>
       </c>
       <c r="W28" t="n">
-        <v>1.28</v>
+        <v>1.38</v>
       </c>
       <c r="X28" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="Y28" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="Z28" t="n">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="AA28" t="n">
-        <v>3.4</v>
+        <v>3.92</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.78</v>
+        <v>1.88</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.92</v>
+        <v>1.82</v>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
@@ -4090,10 +4090,10 @@
         </is>
       </c>
       <c r="AG28" t="n">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.67</v>
+        <v>1.52</v>
       </c>
       <c r="AI28" t="n">
         <v>0</v>
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,55 +4152,55 @@
         </is>
       </c>
       <c r="L29" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="M29" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="N29" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="O29" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="P29" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="R29" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S29" t="n">
         <v>3.2</v>
       </c>
-      <c r="M29" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="N29" t="n">
+      <c r="T29" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="V29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W29" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="X29" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="Z29" t="n">
         <v>2.2</v>
       </c>
-      <c r="O29" t="n">
-        <v>3.81</v>
-      </c>
-      <c r="P29" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="R29" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="S29" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="T29" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="U29" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="V29" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W29" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="X29" t="n">
-        <v>3.48</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>1.92</v>
-      </c>
       <c r="AA29" t="n">
-        <v>3.12</v>
+        <v>2.62</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="AC29" t="n">
         <v>1.68</v>
@@ -4219,10 +4219,10 @@
         </is>
       </c>
       <c r="AG29" t="n">
-        <v>1.28</v>
+        <v>1.17</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.33</v>
+        <v>2.2</v>
       </c>
       <c r="AI29" t="n">
         <v>0</v>
@@ -4245,7 +4245,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4277,65 +4277,65 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.45</v>
+        <v>1.92</v>
       </c>
       <c r="M30" t="n">
-        <v>4.4</v>
+        <v>3.58</v>
       </c>
       <c r="N30" t="n">
-        <v>6.4</v>
+        <v>3.95</v>
       </c>
       <c r="O30" t="n">
-        <v>1.96</v>
+        <v>2.48</v>
       </c>
       <c r="P30" t="n">
-        <v>2.38</v>
+        <v>2.13</v>
       </c>
       <c r="Q30" t="n">
-        <v>5.5</v>
+        <v>4.55</v>
       </c>
       <c r="R30" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="S30" t="n">
-        <v>3.08</v>
+        <v>2.88</v>
       </c>
       <c r="T30" t="n">
-        <v>2.4</v>
+        <v>2.75</v>
       </c>
       <c r="U30" t="n">
-        <v>1.49</v>
+        <v>1.38</v>
       </c>
       <c r="V30" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="W30" t="n">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="X30" t="n">
-        <v>4.2</v>
+        <v>3.25</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.65</v>
+        <v>1.98</v>
       </c>
       <c r="Z30" t="n">
-        <v>2.1</v>
+        <v>1.82</v>
       </c>
       <c r="AA30" t="n">
-        <v>2.8</v>
+        <v>3.4</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.42</v>
+        <v>1.25</v>
       </c>
       <c r="AC30" t="n">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
@@ -4348,10 +4348,10 @@
         </is>
       </c>
       <c r="AG30" t="n">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AH30" t="n">
-        <v>2.6</v>
+        <v>1.9</v>
       </c>
       <c r="AI30" t="n">
         <v>0</v>
@@ -4406,7 +4406,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L31" t="n">
@@ -4416,7 +4416,7 @@
         <v>3.19</v>
       </c>
       <c r="N31" t="n">
-        <v>2.31</v>
+        <v>2.15</v>
       </c>
       <c r="O31" t="n">
         <v>3.6</v>
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,61 +4539,61 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.63</v>
+        <v>2.21</v>
       </c>
       <c r="M32" t="n">
-        <v>4.2</v>
+        <v>3.42</v>
       </c>
       <c r="N32" t="n">
-        <v>5</v>
+        <v>3.3</v>
       </c>
       <c r="O32" t="n">
-        <v>2.15</v>
+        <v>2.82</v>
       </c>
       <c r="P32" t="n">
-        <v>2.38</v>
+        <v>2.1</v>
       </c>
       <c r="Q32" t="n">
-        <v>5.03</v>
+        <v>3.65</v>
       </c>
       <c r="R32" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="S32" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T32" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V32" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W32" t="n">
         <v>1.28</v>
       </c>
-      <c r="S32" t="n">
+      <c r="X32" t="n">
         <v>3.2</v>
       </c>
-      <c r="T32" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="U32" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="V32" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W32" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="X32" t="n">
-        <v>4.1</v>
-      </c>
       <c r="Y32" t="n">
-        <v>1.68</v>
+        <v>2</v>
       </c>
       <c r="Z32" t="n">
-        <v>2.2</v>
+        <v>1.81</v>
       </c>
       <c r="AA32" t="n">
-        <v>2.62</v>
+        <v>3.4</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="AC32" t="n">
-        <v>1.68</v>
+        <v>1.78</v>
       </c>
       <c r="AD32" t="n">
-        <v>2.06</v>
+        <v>1.92</v>
       </c>
       <c r="AE32" t="inlineStr">
         <is>
@@ -4606,10 +4606,10 @@
         </is>
       </c>
       <c r="AG32" t="n">
-        <v>1.17</v>
+        <v>1.35</v>
       </c>
       <c r="AH32" t="n">
-        <v>2.3</v>
+        <v>1.67</v>
       </c>
       <c r="AI32" t="n">
         <v>0</v>
@@ -4668,13 +4668,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="M33" t="n">
         <v>5.4</v>
       </c>
       <c r="N33" t="n">
-        <v>10.5</v>
+        <v>9</v>
       </c>
       <c r="O33" t="n">
         <v>1.79</v>
@@ -4710,7 +4710,7 @@
         <v>1.67</v>
       </c>
       <c r="Z33" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AA33" t="n">
         <v>2.85</v>
@@ -4719,10 +4719,10 @@
         <v>1.38</v>
       </c>
       <c r="AC33" t="n">
-        <v>2.09</v>
+        <v>2.11</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="AE33" t="inlineStr">
         <is>
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,61 +4797,61 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.55</v>
+        <v>2.2</v>
       </c>
       <c r="M34" t="n">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="N34" t="n">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="O34" t="n">
-        <v>3.18</v>
+        <v>2.73</v>
       </c>
       <c r="P34" t="n">
-        <v>2.02</v>
+        <v>2.27</v>
       </c>
       <c r="Q34" t="n">
         <v>3.54</v>
       </c>
       <c r="R34" t="n">
-        <v>1.43</v>
+        <v>1.3</v>
       </c>
       <c r="S34" t="n">
-        <v>2.54</v>
+        <v>3.14</v>
       </c>
       <c r="T34" t="n">
-        <v>3.08</v>
+        <v>2.33</v>
       </c>
       <c r="U34" t="n">
-        <v>1.3</v>
+        <v>1.55</v>
       </c>
       <c r="V34" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W34" t="n">
-        <v>1.35</v>
+        <v>1.18</v>
       </c>
       <c r="X34" t="n">
-        <v>2.83</v>
+        <v>4.05</v>
       </c>
       <c r="Y34" t="n">
-        <v>2.2</v>
+        <v>1.69</v>
       </c>
       <c r="Z34" t="n">
-        <v>1.68</v>
+        <v>2.17</v>
       </c>
       <c r="AA34" t="n">
-        <v>3.92</v>
+        <v>2.56</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.19</v>
+        <v>1.45</v>
       </c>
       <c r="AC34" t="n">
-        <v>1.88</v>
+        <v>1.55</v>
       </c>
       <c r="AD34" t="n">
-        <v>1.82</v>
+        <v>2.3</v>
       </c>
       <c r="AE34" t="inlineStr">
         <is>
@@ -4864,10 +4864,10 @@
         </is>
       </c>
       <c r="AG34" t="n">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.52</v>
+        <v>1.67</v>
       </c>
       <c r="AI34" t="n">
         <v>0</v>
@@ -4885,12 +4885,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,77 +4926,77 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>1.56</v>
+        <v>1.47</v>
       </c>
       <c r="M35" t="n">
-        <v>4.1</v>
+        <v>4.7</v>
       </c>
       <c r="N35" t="n">
-        <v>5.4</v>
+        <v>6.4</v>
       </c>
       <c r="O35" t="n">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="P35" t="n">
-        <v>2.42</v>
+        <v>2.45</v>
       </c>
       <c r="Q35" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="R35" t="n">
         <v>1.28</v>
       </c>
       <c r="S35" t="n">
-        <v>3.45</v>
+        <v>3.2</v>
       </c>
       <c r="T35" t="n">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="U35" t="n">
-        <v>1.58</v>
+        <v>1.5</v>
       </c>
       <c r="V35" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W35" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="X35" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AE35" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF35" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG35" t="n">
         <v>1.2</v>
       </c>
-      <c r="X35" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="Y35" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="Z35" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AA35" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AB35" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AC35" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AD35" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AE35" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF35" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG35" t="n">
-        <v>1.18</v>
-      </c>
       <c r="AH35" t="n">
-        <v>2.41</v>
+        <v>2.71</v>
       </c>
       <c r="AI35" t="n">
         <v>0</v>
@@ -5005,7 +5005,7 @@
         <v>0</v>
       </c>
       <c r="AK35" s="3" t="n">
-        <v>45930.66666666666</v>
+        <v>45930.65625</v>
       </c>
     </row>
     <row r="36">
@@ -5019,7 +5019,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,61 +5055,61 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="M36" t="n">
-        <v>3.83</v>
+        <v>3.15</v>
       </c>
       <c r="N36" t="n">
-        <v>2.1</v>
+        <v>3.1</v>
       </c>
       <c r="O36" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="S36" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="T36" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="U36" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="V36" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="W36" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="X36" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Y36" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Z36" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AA36" t="n">
-        <v>2.25</v>
+        <v>4.8</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.65</v>
+        <v>1.13</v>
       </c>
       <c r="AC36" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AD36" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AE36" t="inlineStr">
         <is>
@@ -5122,10 +5122,10 @@
         </is>
       </c>
       <c r="AG36" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AH36" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AI36" t="n">
         <v>0</v>
@@ -5148,7 +5148,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Kariobangi Sharks</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>KCB</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,61 +5184,61 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="O37" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="R37" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="S37" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="T37" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="U37" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="V37" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W37" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X37" t="n">
-        <v>0</v>
+        <v>5.35</v>
       </c>
       <c r="Y37" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z37" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AA37" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB37" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC37" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AD37" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AE37" t="inlineStr">
         <is>
@@ -5251,10 +5251,10 @@
         </is>
       </c>
       <c r="AG37" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AH37" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AI37" t="n">
         <v>0</v>
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Olympique Marseille</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,13 +5313,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>1.62</v>
+        <v>1.56</v>
       </c>
       <c r="M38" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="N38" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5352,10 +5352,10 @@
         <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.68</v>
+        <v>1.63</v>
       </c>
       <c r="Z38" t="n">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AA38" t="n">
         <v>0</v>
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,61 +5442,61 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>1.35</v>
+        <v>3</v>
       </c>
       <c r="M39" t="n">
-        <v>5.3</v>
+        <v>3.83</v>
       </c>
       <c r="N39" t="n">
-        <v>7</v>
+        <v>2.1</v>
       </c>
       <c r="O39" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="S39" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="T39" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="U39" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="V39" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W39" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="X39" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z39" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>2.42</v>
+        <v>2.25</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AC39" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AD39" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AE39" t="inlineStr">
         <is>
@@ -5509,10 +5509,10 @@
         </is>
       </c>
       <c r="AG39" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AH39" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AI39" t="n">
         <v>0</v>
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,62 +5700,62 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>4.3</v>
+        <v>1.62</v>
       </c>
       <c r="M41" t="n">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="N41" t="n">
-        <v>1.64</v>
+        <v>4.9</v>
       </c>
       <c r="O41" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="S41" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="T41" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="U41" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="V41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W41" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="X41" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="Y41" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AB41" t="n">
         <v>1.44</v>
       </c>
-      <c r="Z41" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AA41" t="n">
+      <c r="AC41" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AD41" t="n">
         <v>2.15</v>
       </c>
-      <c r="AB41" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AC41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD41" t="n">
-        <v>0</v>
-      </c>
       <c r="AE41" t="inlineStr">
         <is>
           <t>[]</t>
@@ -5767,10 +5767,10 @@
         </is>
       </c>
       <c r="AG41" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH41" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AI41" t="n">
         <v>0</v>
@@ -5793,7 +5793,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,61 +5829,61 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>2.45</v>
+        <v>1.35</v>
       </c>
       <c r="M42" t="n">
-        <v>3.15</v>
+        <v>5.3</v>
       </c>
       <c r="N42" t="n">
-        <v>3.05</v>
+        <v>7</v>
       </c>
       <c r="O42" t="n">
-        <v>3.2</v>
+        <v>1.8</v>
       </c>
       <c r="P42" t="n">
-        <v>1.92</v>
+        <v>2.6</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.94</v>
+        <v>7.4</v>
       </c>
       <c r="R42" t="n">
-        <v>1.53</v>
+        <v>1.24</v>
       </c>
       <c r="S42" t="n">
-        <v>2.34</v>
+        <v>3.54</v>
       </c>
       <c r="T42" t="n">
-        <v>3.48</v>
+        <v>2.3</v>
       </c>
       <c r="U42" t="n">
-        <v>1.22</v>
+        <v>1.62</v>
       </c>
       <c r="V42" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="W42" t="n">
-        <v>1.53</v>
+        <v>1.16</v>
       </c>
       <c r="X42" t="n">
-        <v>2.5</v>
+        <v>5</v>
       </c>
       <c r="Y42" t="n">
-        <v>2.52</v>
+        <v>1.6</v>
       </c>
       <c r="Z42" t="n">
-        <v>1.52</v>
+        <v>2.35</v>
       </c>
       <c r="AA42" t="n">
-        <v>4.8</v>
+        <v>2.42</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.13</v>
+        <v>1.6</v>
       </c>
       <c r="AC42" t="n">
-        <v>2.08</v>
+        <v>1.86</v>
       </c>
       <c r="AD42" t="n">
-        <v>1.66</v>
+        <v>1.94</v>
       </c>
       <c r="AE42" t="inlineStr">
         <is>
@@ -5896,10 +5896,10 @@
         </is>
       </c>
       <c r="AG42" t="n">
-        <v>1.37</v>
+        <v>1.17</v>
       </c>
       <c r="AH42" t="n">
-        <v>1.54</v>
+        <v>3</v>
       </c>
       <c r="AI42" t="n">
         <v>0</v>
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Olympique Marseille</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5961,40 +5961,40 @@
         <v>1.56</v>
       </c>
       <c r="M43" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="N43" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="O43" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="P43" t="n">
-        <v>2.45</v>
+        <v>2.42</v>
       </c>
       <c r="Q43" t="n">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="R43" t="n">
         <v>1.28</v>
       </c>
       <c r="S43" t="n">
-        <v>3.32</v>
+        <v>3.45</v>
       </c>
       <c r="T43" t="n">
-        <v>2.36</v>
+        <v>2.25</v>
       </c>
       <c r="U43" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="V43" t="n">
         <v>1.01</v>
       </c>
       <c r="W43" t="n">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="X43" t="n">
-        <v>4.65</v>
+        <v>4.33</v>
       </c>
       <c r="Y43" t="n">
         <v>1.63</v>
@@ -6003,16 +6003,16 @@
         <v>2.25</v>
       </c>
       <c r="AA43" t="n">
-        <v>2.4</v>
+        <v>2.75</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="AC43" t="n">
-        <v>1.64</v>
+        <v>1.61</v>
       </c>
       <c r="AD43" t="n">
-        <v>2.25</v>
+        <v>2.04</v>
       </c>
       <c r="AE43" t="inlineStr">
         <is>
@@ -6025,10 +6025,10 @@
         </is>
       </c>
       <c r="AG43" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AH43" t="n">
-        <v>2.46</v>
+        <v>2.41</v>
       </c>
       <c r="AI43" t="n">
         <v>0</v>
@@ -6046,27 +6046,27 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Police</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Ulinzi Stars</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6087,13 +6087,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="M44" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -6126,16 +6126,16 @@
         <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z44" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AA44" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB44" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AC44" t="n">
         <v>0</v>
@@ -6166,7 +6166,7 @@
         <v>0</v>
       </c>
       <c r="AK44" s="3" t="n">
-        <v>45930.75</v>
+        <v>45930.85416666666</v>
       </c>
     </row>
     <row r="45">
@@ -6175,12 +6175,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6216,13 +6216,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>1.57</v>
+        <v>1.4</v>
       </c>
       <c r="M45" t="n">
-        <v>4.8</v>
+        <v>4.2</v>
       </c>
       <c r="N45" t="n">
-        <v>4.9</v>
+        <v>6</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -6255,16 +6255,16 @@
         <v>0</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.4</v>
+        <v>1.86</v>
       </c>
       <c r="Z45" t="n">
-        <v>2.75</v>
+        <v>1.84</v>
       </c>
       <c r="AA45" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AC45" t="n">
         <v>0</v>
@@ -6295,7 +6295,7 @@
         <v>0</v>
       </c>
       <c r="AK45" s="3" t="n">
-        <v>45930.85416666666</v>
+        <v>45930.89583333334</v>
       </c>
     </row>
     <row r="46">
@@ -6304,12 +6304,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:35</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6319,12 +6319,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6345,13 +6345,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>1.4</v>
+        <v>1.93</v>
       </c>
       <c r="M46" t="n">
-        <v>4.2</v>
+        <v>3.1</v>
       </c>
       <c r="N46" t="n">
-        <v>6</v>
+        <v>3.57</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -6384,10 +6384,10 @@
         <v>0</v>
       </c>
       <c r="Y46" t="n">
-        <v>1.86</v>
+        <v>2.12</v>
       </c>
       <c r="Z46" t="n">
-        <v>1.84</v>
+        <v>1.64</v>
       </c>
       <c r="AA46" t="n">
         <v>0</v>
@@ -6424,135 +6424,6 @@
         <v>0</v>
       </c>
       <c r="AK46" s="3" t="n">
-        <v>45930.89583333334</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="2" t="n">
-        <v>45930</v>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>21:35</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Brazil Serie B</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>Goiás</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>Atlético GO</t>
-        </is>
-      </c>
-      <c r="G47" t="n">
-        <v>0</v>
-      </c>
-      <c r="H47" t="n">
-        <v>0</v>
-      </c>
-      <c r="I47" t="n">
-        <v>0</v>
-      </c>
-      <c r="J47" t="n">
-        <v>0</v>
-      </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L47" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="M47" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="N47" t="n">
-        <v>3.57</v>
-      </c>
-      <c r="O47" t="n">
-        <v>0</v>
-      </c>
-      <c r="P47" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q47" t="n">
-        <v>0</v>
-      </c>
-      <c r="R47" t="n">
-        <v>0</v>
-      </c>
-      <c r="S47" t="n">
-        <v>0</v>
-      </c>
-      <c r="T47" t="n">
-        <v>0</v>
-      </c>
-      <c r="U47" t="n">
-        <v>0</v>
-      </c>
-      <c r="V47" t="n">
-        <v>0</v>
-      </c>
-      <c r="W47" t="n">
-        <v>0</v>
-      </c>
-      <c r="X47" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y47" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="Z47" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AA47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE47" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF47" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK47" s="3" t="n">
         <v>45930.89930555555</v>
       </c>
     </row>

--- a/jogos_2025-09-30.xlsx
+++ b/jogos_2025-09-30.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK46"/>
+  <dimension ref="A1:AK47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -927,13 +927,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -966,10 +966,10 @@
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AA4" t="n">
         <v>0</v>
@@ -1056,13 +1056,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1095,10 +1095,10 @@
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AA5" t="n">
         <v>0</v>
@@ -1144,12 +1144,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Police</t>
+          <t>Botev Plovdiv</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ulinzi Stars</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1185,61 +1185,61 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>5.83</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
@@ -1252,19 +1252,19 @@
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AI6" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AK6" s="3" t="n">
-        <v>45930.5</v>
+        <v>45930.47916666666</v>
       </c>
     </row>
     <row r="7">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Police</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Ulinzi Stars</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1314,13 +1314,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1353,10 +1353,10 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
         <v>0</v>
@@ -1393,7 +1393,7 @@
         <v>0</v>
       </c>
       <c r="AK7" s="3" t="n">
-        <v>45930.57291666666</v>
+        <v>45930.5</v>
       </c>
     </row>
     <row r="8">
@@ -1452,7 +1452,7 @@
         <v>1.11</v>
       </c>
       <c r="O8" t="n">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="P8" t="n">
         <v>3.5</v>
@@ -1464,7 +1464,7 @@
         <v>1.18</v>
       </c>
       <c r="S8" t="n">
-        <v>4.2</v>
+        <v>4.25</v>
       </c>
       <c r="T8" t="n">
         <v>2.01</v>
@@ -1476,7 +1476,7 @@
         <v>1.01</v>
       </c>
       <c r="W8" t="n">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="X8" t="n">
         <v>7</v>
@@ -1494,10 +1494,10 @@
         <v>1.94</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.19</v>
+        <v>2.21</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
@@ -1513,7 +1513,7 @@
         <v>1.05</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AI8" t="n">
         <v>0</v>
@@ -1531,27 +1531,27 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,61 +1572,61 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.46</v>
+        <v>1.86</v>
       </c>
       <c r="M9" t="n">
-        <v>4.25</v>
+        <v>3.84</v>
       </c>
       <c r="N9" t="n">
-        <v>4.8</v>
+        <v>3.7</v>
       </c>
       <c r="O9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.42</v>
+        <v>1.7</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.5</v>
+        <v>2.15</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
@@ -1651,7 +1651,7 @@
         <v>0</v>
       </c>
       <c r="AK9" s="3" t="n">
-        <v>45930.58333333334</v>
+        <v>45930.57291666666</v>
       </c>
     </row>
     <row r="10">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Hansa Rostock</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>Wehen Wiesbaden</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,13 +1701,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1794,22 +1794,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Havelse</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Waldhof Mannheim</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,61 +1830,61 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.36</v>
+        <v>3.38</v>
       </c>
       <c r="M11" t="n">
-        <v>4.75</v>
+        <v>3.7</v>
       </c>
       <c r="N11" t="n">
-        <v>7</v>
+        <v>1.91</v>
       </c>
       <c r="O11" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>6.89</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>4.77</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -1897,10 +1897,10 @@
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AI11" t="n">
         <v>0</v>
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Havelse</t>
+          <t>Hansa Rostock</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Waldhof Mannheim</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,13 +1959,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>3.73</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -2052,22 +2052,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Erzgebirge Aue</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,61 +2088,61 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>6.89</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>4.77</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
@@ -2155,10 +2155,10 @@
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AI13" t="n">
         <v>0</v>
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Wehen Wiesbaden</t>
+          <t>Erzgebirge Aue</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,13 +2217,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2310,22 +2310,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Saarbrucken</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>MSV Duisburg</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,61 +2346,61 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
@@ -2413,10 +2413,10 @@
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AI15" t="n">
         <v>0</v>
@@ -2434,12 +2434,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Saarbrucken</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>MSV Duisburg</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,61 +2475,61 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.75</v>
+        <v>1.87</v>
       </c>
       <c r="M16" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="N16" t="n">
-        <v>2.25</v>
+        <v>3.55</v>
       </c>
       <c r="O16" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
@@ -2542,10 +2542,10 @@
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="AI16" t="n">
         <v>0</v>
@@ -2554,7 +2554,7 @@
         <v>0</v>
       </c>
       <c r="AK16" s="3" t="n">
-        <v>45930.625</v>
+        <v>45930.58333333334</v>
       </c>
     </row>
     <row r="17">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,58 +2604,58 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>3.43</v>
+        <v>2.16</v>
       </c>
       <c r="M17" t="n">
-        <v>3.94</v>
+        <v>3.7</v>
       </c>
       <c r="N17" t="n">
-        <v>1.95</v>
+        <v>2.9</v>
       </c>
       <c r="O17" t="n">
-        <v>3.78</v>
+        <v>2.56</v>
       </c>
       <c r="P17" t="n">
-        <v>2.4</v>
+        <v>2.39</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.38</v>
+        <v>3.46</v>
       </c>
       <c r="R17" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="S17" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="T17" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="U17" t="n">
-        <v>1.63</v>
+        <v>1.59</v>
       </c>
       <c r="V17" t="n">
         <v>1.01</v>
       </c>
       <c r="W17" t="n">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="X17" t="n">
-        <v>5.05</v>
+        <v>5.29</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.44</v>
+        <v>1.55</v>
       </c>
       <c r="Z17" t="n">
-        <v>2.5</v>
+        <v>2.39</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.24</v>
+        <v>2.38</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.61</v>
+        <v>1.5</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="AD17" t="n">
         <v>2.5</v>
@@ -2671,10 +2671,10 @@
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.27</v>
+        <v>1.69</v>
       </c>
       <c r="AI17" t="n">
         <v>0</v>
@@ -2733,13 +2733,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="M18" t="n">
-        <v>3.75</v>
+        <v>3.95</v>
       </c>
       <c r="N18" t="n">
-        <v>4</v>
+        <v>4.28</v>
       </c>
       <c r="O18" t="n">
         <v>2.25</v>
@@ -2748,13 +2748,13 @@
         <v>2.3</v>
       </c>
       <c r="Q18" t="n">
-        <v>4.5</v>
+        <v>4.62</v>
       </c>
       <c r="R18" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="S18" t="n">
-        <v>3.2</v>
+        <v>3.28</v>
       </c>
       <c r="T18" t="n">
         <v>2.44</v>
@@ -2766,7 +2766,7 @@
         <v>1.03</v>
       </c>
       <c r="W18" t="n">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="X18" t="n">
         <v>4.15</v>
@@ -2784,10 +2784,10 @@
         <v>1.39</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="AD18" t="n">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
@@ -2803,7 +2803,7 @@
         <v>1.24</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.9</v>
+        <v>2.08</v>
       </c>
       <c r="AI18" t="n">
         <v>0</v>
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,61 +2862,61 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O19" t="n">
-        <v>1.7</v>
+        <v>3</v>
       </c>
       <c r="P19" t="n">
-        <v>2.85</v>
+        <v>2.45</v>
       </c>
       <c r="Q19" t="n">
-        <v>6.74</v>
+        <v>2.62</v>
       </c>
       <c r="R19" t="n">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="S19" t="n">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="T19" t="n">
-        <v>2.08</v>
+        <v>2.3</v>
       </c>
       <c r="U19" t="n">
-        <v>1.73</v>
+        <v>1.57</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W19" t="n">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="X19" t="n">
-        <v>5.65</v>
+        <v>4.85</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.37</v>
+        <v>1.57</v>
       </c>
       <c r="Z19" t="n">
-        <v>2.67</v>
+        <v>2.33</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.08</v>
+        <v>2.4</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.8</v>
+        <v>1.48</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.66</v>
+        <v>1.45</v>
       </c>
       <c r="AD19" t="n">
-        <v>2.07</v>
+        <v>2.5</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
@@ -2929,10 +2929,10 @@
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>1.13</v>
+        <v>1.26</v>
       </c>
       <c r="AH19" t="n">
-        <v>3.34</v>
+        <v>1.36</v>
       </c>
       <c r="AI19" t="n">
         <v>0</v>
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,58 +2991,58 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.15</v>
+        <v>3.52</v>
       </c>
       <c r="M20" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="N20" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="O20" t="n">
         <v>3.78</v>
       </c>
-      <c r="N20" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="O20" t="n">
-        <v>2.56</v>
-      </c>
       <c r="P20" t="n">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.4</v>
+        <v>2.35</v>
       </c>
       <c r="R20" t="n">
         <v>1.25</v>
       </c>
       <c r="S20" t="n">
-        <v>3.5</v>
+        <v>3.64</v>
       </c>
       <c r="T20" t="n">
-        <v>2.18</v>
+        <v>2.21</v>
       </c>
       <c r="U20" t="n">
-        <v>1.57</v>
+        <v>1.63</v>
       </c>
       <c r="V20" t="n">
         <v>1.02</v>
       </c>
       <c r="W20" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="X20" t="n">
-        <v>4.55</v>
+        <v>5.05</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.55</v>
+        <v>1.51</v>
       </c>
       <c r="Z20" t="n">
-        <v>2.39</v>
+        <v>2.44</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.29</v>
+        <v>2.24</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AD20" t="n">
         <v>2.5</v>
@@ -3058,10 +3058,10 @@
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>1.38</v>
+        <v>1.2</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.69</v>
+        <v>1.27</v>
       </c>
       <c r="AI20" t="n">
         <v>0</v>
@@ -3079,12 +3079,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,61 +3120,61 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>4.24</v>
+        <v>1.69</v>
       </c>
       <c r="P21" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>7.14</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="S21" t="n">
+        <v>3.94</v>
+      </c>
+      <c r="T21" t="n">
         <v>2.08</v>
       </c>
-      <c r="Q21" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="R21" t="n">
+      <c r="U21" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="V21" t="n">
+        <v>0</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X21" t="n">
+        <v>5.65</v>
+      </c>
+      <c r="Y21" t="n">
         <v>1.4</v>
       </c>
-      <c r="S21" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="T21" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="U21" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V21" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W21" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="X21" t="n">
-        <v>3.02</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>2.07</v>
-      </c>
       <c r="Z21" t="n">
-        <v>1.75</v>
+        <v>2.67</v>
       </c>
       <c r="AA21" t="n">
-        <v>3.55</v>
+        <v>2.08</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.25</v>
+        <v>1.74</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.86</v>
+        <v>1.71</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.82</v>
+        <v>2.04</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
@@ -3187,10 +3187,10 @@
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>1.31</v>
+        <v>1.12</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.3</v>
+        <v>3.5</v>
       </c>
       <c r="AI21" t="n">
         <v>0</v>
@@ -3199,7 +3199,7 @@
         <v>0</v>
       </c>
       <c r="AK21" s="3" t="n">
-        <v>45930.64583333334</v>
+        <v>45930.625</v>
       </c>
     </row>
     <row r="22">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,77 +3249,77 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.6</v>
+        <v>3.6</v>
       </c>
       <c r="M22" t="n">
-        <v>3.25</v>
+        <v>3.45</v>
       </c>
       <c r="N22" t="n">
-        <v>2.75</v>
+        <v>2.05</v>
       </c>
       <c r="O22" t="n">
-        <v>3.25</v>
+        <v>4.15</v>
       </c>
       <c r="P22" t="n">
-        <v>2.02</v>
+        <v>2.05</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.35</v>
+        <v>2.7</v>
       </c>
       <c r="R22" t="n">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="S22" t="n">
-        <v>2.55</v>
+        <v>2.64</v>
       </c>
       <c r="T22" t="n">
-        <v>3.08</v>
+        <v>2.93</v>
       </c>
       <c r="U22" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="X22" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AE22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG22" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AH22" t="n">
         <v>1.3</v>
-      </c>
-      <c r="V22" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W22" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="X22" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AE22" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF22" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG22" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>1.49</v>
       </c>
       <c r="AI22" t="n">
         <v>0</v>
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Calcio Padova</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,22 +3378,22 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.15</v>
+        <v>2.6</v>
       </c>
       <c r="M23" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="N23" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="O23" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="P23" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q23" t="n">
         <v>3.35</v>
-      </c>
-      <c r="N23" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="O23" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="P23" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>3.95</v>
       </c>
       <c r="R23" t="n">
         <v>1.44</v>
@@ -3402,16 +3402,16 @@
         <v>2.51</v>
       </c>
       <c r="T23" t="n">
-        <v>3</v>
+        <v>3.08</v>
       </c>
       <c r="U23" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="V23" t="n">
         <v>1.03</v>
       </c>
       <c r="W23" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="X23" t="n">
         <v>2.78</v>
@@ -3420,7 +3420,7 @@
         <v>2.2</v>
       </c>
       <c r="Z23" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AA23" t="n">
         <v>3.9</v>
@@ -3429,10 +3429,10 @@
         <v>1.19</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.93</v>
+        <v>1.87</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.76</v>
+        <v>1.85</v>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
@@ -3445,10 +3445,10 @@
         </is>
       </c>
       <c r="AG23" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.69</v>
+        <v>1.49</v>
       </c>
       <c r="AI23" t="n">
         <v>0</v>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,61 +3507,61 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="M24" t="n">
-        <v>3.65</v>
+        <v>3.35</v>
       </c>
       <c r="N24" t="n">
         <v>3.45</v>
       </c>
       <c r="O24" t="n">
-        <v>2.55</v>
+        <v>2.79</v>
       </c>
       <c r="P24" t="n">
-        <v>2.17</v>
+        <v>2.04</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.92</v>
+        <v>4.19</v>
       </c>
       <c r="R24" t="n">
-        <v>1.32</v>
+        <v>1.42</v>
       </c>
       <c r="S24" t="n">
-        <v>2.95</v>
+        <v>2.57</v>
       </c>
       <c r="T24" t="n">
-        <v>2.6</v>
+        <v>3</v>
       </c>
       <c r="U24" t="n">
-        <v>1.45</v>
+        <v>1.31</v>
       </c>
       <c r="V24" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="W24" t="n">
-        <v>1.21</v>
+        <v>1.34</v>
       </c>
       <c r="X24" t="n">
-        <v>3.7</v>
+        <v>2.88</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.8</v>
+        <v>2.18</v>
       </c>
       <c r="Z24" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.92</v>
+        <v>3.82</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.65</v>
+        <v>1.87</v>
       </c>
       <c r="AD24" t="n">
-        <v>2.13</v>
+        <v>1.85</v>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
@@ -3574,10 +3574,10 @@
         </is>
       </c>
       <c r="AG24" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.74</v>
+        <v>1.7</v>
       </c>
       <c r="AI24" t="n">
         <v>0</v>
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Mantova</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,61 +3636,61 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.15</v>
+        <v>1.8</v>
       </c>
       <c r="M25" t="n">
-        <v>3.35</v>
+        <v>3.7</v>
       </c>
       <c r="N25" t="n">
-        <v>3.45</v>
+        <v>4.3</v>
       </c>
       <c r="O25" t="n">
-        <v>2.75</v>
+        <v>2.45</v>
       </c>
       <c r="P25" t="n">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.9</v>
+        <v>4.8</v>
       </c>
       <c r="R25" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="S25" t="n">
-        <v>2.57</v>
+        <v>2.71</v>
       </c>
       <c r="T25" t="n">
-        <v>3</v>
+        <v>2.79</v>
       </c>
       <c r="U25" t="n">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="V25" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="W25" t="n">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
       <c r="X25" t="n">
-        <v>2.88</v>
+        <v>3.12</v>
       </c>
       <c r="Y25" t="n">
-        <v>2.18</v>
+        <v>1.95</v>
       </c>
       <c r="Z25" t="n">
-        <v>1.7</v>
+        <v>1.85</v>
       </c>
       <c r="AA25" t="n">
-        <v>3.82</v>
+        <v>3.32</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.91</v>
+        <v>1.84</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.77</v>
+        <v>1.88</v>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
@@ -3703,10 +3703,10 @@
         </is>
       </c>
       <c r="AG25" t="n">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.7</v>
+        <v>1.94</v>
       </c>
       <c r="AI25" t="n">
         <v>0</v>
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mantova</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,61 +3765,61 @@
         </is>
       </c>
       <c r="L26" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="M26" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="N26" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="O26" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="P26" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S26" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="V26" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W26" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X26" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="Y26" t="n">
         <v>1.8</v>
       </c>
-      <c r="M26" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="N26" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="O26" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="P26" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="R26" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S26" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="T26" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="U26" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V26" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="W26" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="X26" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>1.95</v>
-      </c>
       <c r="Z26" t="n">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AA26" t="n">
-        <v>3.32</v>
+        <v>3</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.84</v>
+        <v>1.65</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.88</v>
+        <v>2.13</v>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
@@ -3832,10 +3832,10 @@
         </is>
       </c>
       <c r="AG26" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.94</v>
+        <v>1.74</v>
       </c>
       <c r="AI26" t="n">
         <v>0</v>
@@ -3853,12 +3853,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Calcio Padova</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,77 +3894,77 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>3.1</v>
+        <v>2.15</v>
       </c>
       <c r="M27" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="N27" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="O27" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="P27" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>4.24</v>
+      </c>
+      <c r="R27" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="S27" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="T27" t="n">
+        <v>3</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V27" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W27" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="X27" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="Y27" t="n">
         <v>2.2</v>
       </c>
-      <c r="O27" t="n">
-        <v>3.81</v>
-      </c>
-      <c r="P27" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="R27" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="S27" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="T27" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="U27" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="V27" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W27" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="X27" t="n">
-        <v>3.48</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>1.89</v>
-      </c>
       <c r="Z27" t="n">
-        <v>1.91</v>
+        <v>1.65</v>
       </c>
       <c r="AA27" t="n">
-        <v>3.12</v>
+        <v>3.9</v>
       </c>
       <c r="AB27" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AE27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG27" t="n">
         <v>1.33</v>
       </c>
-      <c r="AC27" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AE27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG27" t="n">
-        <v>1.28</v>
-      </c>
       <c r="AH27" t="n">
-        <v>1.33</v>
+        <v>1.69</v>
       </c>
       <c r="AI27" t="n">
         <v>0</v>
@@ -3973,7 +3973,7 @@
         <v>0</v>
       </c>
       <c r="AK27" s="3" t="n">
-        <v>45930.65625</v>
+        <v>45930.64583333334</v>
       </c>
     </row>
     <row r="28">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,61 +4023,61 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.55</v>
+        <v>1.63</v>
       </c>
       <c r="M28" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="N28" t="n">
+        <v>5</v>
+      </c>
+      <c r="O28" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="P28" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>5.03</v>
+      </c>
+      <c r="R28" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S28" t="n">
         <v>3.2</v>
       </c>
-      <c r="N28" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="O28" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="P28" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="R28" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="S28" t="n">
-        <v>2.54</v>
-      </c>
       <c r="T28" t="n">
-        <v>3.08</v>
+        <v>2.42</v>
       </c>
       <c r="U28" t="n">
-        <v>1.3</v>
+        <v>1.47</v>
       </c>
       <c r="V28" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W28" t="n">
-        <v>1.38</v>
+        <v>1.18</v>
       </c>
       <c r="X28" t="n">
-        <v>3</v>
+        <v>4.1</v>
       </c>
       <c r="Y28" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="Z28" t="n">
         <v>2.2</v>
       </c>
-      <c r="Z28" t="n">
-        <v>1.67</v>
-      </c>
       <c r="AA28" t="n">
-        <v>3.92</v>
+        <v>2.62</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.19</v>
+        <v>1.4</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.88</v>
+        <v>1.7</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.82</v>
+        <v>2.05</v>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
@@ -4090,10 +4090,10 @@
         </is>
       </c>
       <c r="AG28" t="n">
-        <v>1.34</v>
+        <v>1.17</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.52</v>
+        <v>2.3</v>
       </c>
       <c r="AI28" t="n">
         <v>0</v>
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,61 +4152,61 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.55</v>
+        <v>3.2</v>
       </c>
       <c r="M29" t="n">
-        <v>3.75</v>
+        <v>3.55</v>
       </c>
       <c r="N29" t="n">
-        <v>4.9</v>
+        <v>2.2</v>
       </c>
       <c r="O29" t="n">
-        <v>2.14</v>
+        <v>3.81</v>
       </c>
       <c r="P29" t="n">
-        <v>2.45</v>
+        <v>2.15</v>
       </c>
       <c r="Q29" t="n">
-        <v>4.5</v>
+        <v>2.8</v>
       </c>
       <c r="R29" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="S29" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="V29" t="n">
+        <v>1</v>
+      </c>
+      <c r="W29" t="n">
         <v>1.28</v>
       </c>
-      <c r="S29" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="T29" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="U29" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="V29" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W29" t="n">
-        <v>1.18</v>
-      </c>
       <c r="X29" t="n">
-        <v>4.1</v>
+        <v>3.48</v>
       </c>
       <c r="Y29" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AC29" t="n">
         <v>1.69</v>
       </c>
-      <c r="Z29" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>1.68</v>
-      </c>
       <c r="AD29" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
@@ -4219,10 +4219,10 @@
         </is>
       </c>
       <c r="AG29" t="n">
-        <v>1.17</v>
+        <v>1.3</v>
       </c>
       <c r="AH29" t="n">
-        <v>2.2</v>
+        <v>1.36</v>
       </c>
       <c r="AI29" t="n">
         <v>0</v>
@@ -4245,7 +4245,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,61 +4281,61 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.92</v>
+        <v>3</v>
       </c>
       <c r="M30" t="n">
-        <v>3.58</v>
+        <v>3.19</v>
       </c>
       <c r="N30" t="n">
-        <v>3.95</v>
+        <v>2.15</v>
       </c>
       <c r="O30" t="n">
-        <v>2.48</v>
+        <v>3.6</v>
       </c>
       <c r="P30" t="n">
-        <v>2.13</v>
+        <v>2.05</v>
       </c>
       <c r="Q30" t="n">
-        <v>4.55</v>
+        <v>2.92</v>
       </c>
       <c r="R30" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="S30" t="n">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="T30" t="n">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="U30" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="V30" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W30" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="X30" t="n">
         <v>3.25</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.98</v>
+        <v>2.01</v>
       </c>
       <c r="Z30" t="n">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="AA30" t="n">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AC30" t="n">
-        <v>1.82</v>
+        <v>1.76</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
@@ -4348,10 +4348,10 @@
         </is>
       </c>
       <c r="AG30" t="n">
-        <v>1.29</v>
+        <v>1.62</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.9</v>
+        <v>1.37</v>
       </c>
       <c r="AI30" t="n">
         <v>0</v>
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,61 +4410,61 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>3</v>
+        <v>1.45</v>
       </c>
       <c r="M31" t="n">
-        <v>3.19</v>
+        <v>4.4</v>
       </c>
       <c r="N31" t="n">
-        <v>2.15</v>
+        <v>6.4</v>
       </c>
       <c r="O31" t="n">
-        <v>3.6</v>
+        <v>1.96</v>
       </c>
       <c r="P31" t="n">
-        <v>2.05</v>
+        <v>2.4</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.92</v>
+        <v>6.3</v>
       </c>
       <c r="R31" t="n">
-        <v>1.38</v>
+        <v>1.28</v>
       </c>
       <c r="S31" t="n">
-        <v>2.75</v>
+        <v>3.2</v>
       </c>
       <c r="T31" t="n">
-        <v>2.8</v>
+        <v>2.42</v>
       </c>
       <c r="U31" t="n">
-        <v>1.37</v>
+        <v>1.47</v>
       </c>
       <c r="V31" t="n">
         <v>1.02</v>
       </c>
       <c r="W31" t="n">
-        <v>1.28</v>
+        <v>1.17</v>
       </c>
       <c r="X31" t="n">
-        <v>3.25</v>
+        <v>4.33</v>
       </c>
       <c r="Y31" t="n">
-        <v>2.01</v>
+        <v>1.65</v>
       </c>
       <c r="Z31" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="AA31" t="n">
-        <v>3.55</v>
+        <v>2.63</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.27</v>
+        <v>1.4</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.76</v>
+        <v>1.81</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AE31" t="inlineStr">
         <is>
@@ -4477,10 +4477,10 @@
         </is>
       </c>
       <c r="AG31" t="n">
-        <v>1.62</v>
+        <v>1.2</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.37</v>
+        <v>2.71</v>
       </c>
       <c r="AI31" t="n">
         <v>0</v>
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,61 +4539,61 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.21</v>
+        <v>1.3</v>
       </c>
       <c r="M32" t="n">
-        <v>3.42</v>
+        <v>5.4</v>
       </c>
       <c r="N32" t="n">
-        <v>3.3</v>
+        <v>10.5</v>
       </c>
       <c r="O32" t="n">
-        <v>2.82</v>
+        <v>1.79</v>
       </c>
       <c r="P32" t="n">
-        <v>2.1</v>
+        <v>2.48</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.65</v>
+        <v>8.1</v>
       </c>
       <c r="R32" t="n">
-        <v>1.37</v>
+        <v>1.3</v>
       </c>
       <c r="S32" t="n">
-        <v>2.75</v>
+        <v>3.08</v>
       </c>
       <c r="T32" t="n">
-        <v>2.88</v>
+        <v>2.5</v>
       </c>
       <c r="U32" t="n">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="V32" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="W32" t="n">
-        <v>1.28</v>
+        <v>1.19</v>
       </c>
       <c r="X32" t="n">
-        <v>3.2</v>
+        <v>3.92</v>
       </c>
       <c r="Y32" t="n">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="Z32" t="n">
-        <v>1.81</v>
+        <v>2.2</v>
       </c>
       <c r="AA32" t="n">
-        <v>3.4</v>
+        <v>2.85</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AC32" t="n">
-        <v>1.78</v>
+        <v>2.09</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.92</v>
+        <v>1.66</v>
       </c>
       <c r="AE32" t="inlineStr">
         <is>
@@ -4606,10 +4606,10 @@
         </is>
       </c>
       <c r="AG32" t="n">
-        <v>1.35</v>
+        <v>1.16</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.67</v>
+        <v>3.38</v>
       </c>
       <c r="AI32" t="n">
         <v>0</v>
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,77 +4668,77 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.26</v>
+        <v>2.18</v>
       </c>
       <c r="M33" t="n">
-        <v>5.4</v>
+        <v>3.45</v>
       </c>
       <c r="N33" t="n">
-        <v>9</v>
+        <v>3.25</v>
       </c>
       <c r="O33" t="n">
-        <v>1.79</v>
+        <v>2.82</v>
       </c>
       <c r="P33" t="n">
-        <v>2.48</v>
+        <v>2.1</v>
       </c>
       <c r="Q33" t="n">
-        <v>8.1</v>
+        <v>3.9</v>
       </c>
       <c r="R33" t="n">
-        <v>1.3</v>
+        <v>1.37</v>
       </c>
       <c r="S33" t="n">
-        <v>3.25</v>
+        <v>2.75</v>
       </c>
       <c r="T33" t="n">
-        <v>2.5</v>
+        <v>2.88</v>
       </c>
       <c r="U33" t="n">
-        <v>1.44</v>
+        <v>1.34</v>
       </c>
       <c r="V33" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W33" t="n">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="X33" t="n">
-        <v>4.2</v>
+        <v>3.2</v>
       </c>
       <c r="Y33" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AE33" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF33" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG33" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AH33" t="n">
         <v>1.67</v>
-      </c>
-      <c r="Z33" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AA33" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AB33" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AC33" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="AD33" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AE33" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF33" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG33" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AH33" t="n">
-        <v>3.38</v>
       </c>
       <c r="AI33" t="n">
         <v>0</v>
@@ -4797,13 +4797,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.2</v>
+        <v>2.13</v>
       </c>
       <c r="M34" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="N34" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="O34" t="n">
         <v>2.73</v>
@@ -4812,22 +4812,22 @@
         <v>2.27</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.54</v>
+        <v>3.6</v>
       </c>
       <c r="R34" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="S34" t="n">
         <v>3.14</v>
       </c>
       <c r="T34" t="n">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="U34" t="n">
-        <v>1.55</v>
+        <v>1.48</v>
       </c>
       <c r="V34" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="W34" t="n">
         <v>1.18</v>
@@ -4836,19 +4836,19 @@
         <v>4.05</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="Z34" t="n">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="AA34" t="n">
         <v>2.56</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AC34" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="AD34" t="n">
         <v>2.3</v>
@@ -4864,7 +4864,7 @@
         </is>
       </c>
       <c r="AG34" t="n">
-        <v>1.38</v>
+        <v>1.28</v>
       </c>
       <c r="AH34" t="n">
         <v>1.67</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,61 +4926,61 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>1.47</v>
+        <v>2.55</v>
       </c>
       <c r="M35" t="n">
-        <v>4.7</v>
+        <v>3.3</v>
       </c>
       <c r="N35" t="n">
-        <v>6.4</v>
+        <v>2.8</v>
       </c>
       <c r="O35" t="n">
-        <v>1.94</v>
+        <v>3.18</v>
       </c>
       <c r="P35" t="n">
-        <v>2.45</v>
+        <v>2.02</v>
       </c>
       <c r="Q35" t="n">
-        <v>5.5</v>
+        <v>3.54</v>
       </c>
       <c r="R35" t="n">
-        <v>1.28</v>
+        <v>1.43</v>
       </c>
       <c r="S35" t="n">
-        <v>3.2</v>
+        <v>2.54</v>
       </c>
       <c r="T35" t="n">
-        <v>2.33</v>
+        <v>3.08</v>
       </c>
       <c r="U35" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="V35" t="n">
         <v>1.02</v>
       </c>
       <c r="W35" t="n">
-        <v>1.17</v>
+        <v>1.35</v>
       </c>
       <c r="X35" t="n">
-        <v>4.2</v>
+        <v>2.83</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.69</v>
+        <v>2.2</v>
       </c>
       <c r="Z35" t="n">
-        <v>2.16</v>
+        <v>1.68</v>
       </c>
       <c r="AA35" t="n">
-        <v>2.63</v>
+        <v>3.92</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.4</v>
+        <v>1.19</v>
       </c>
       <c r="AC35" t="n">
-        <v>1.81</v>
+        <v>1.87</v>
       </c>
       <c r="AD35" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="AE35" t="inlineStr">
         <is>
@@ -4993,10 +4993,10 @@
         </is>
       </c>
       <c r="AG35" t="n">
-        <v>1.2</v>
+        <v>1.34</v>
       </c>
       <c r="AH35" t="n">
-        <v>2.71</v>
+        <v>1.52</v>
       </c>
       <c r="AI35" t="n">
         <v>0</v>
@@ -5014,7 +5014,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,61 +5055,61 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.5</v>
+        <v>1.9</v>
       </c>
       <c r="M36" t="n">
-        <v>3.15</v>
+        <v>3.6</v>
       </c>
       <c r="N36" t="n">
-        <v>3.1</v>
+        <v>4</v>
       </c>
       <c r="O36" t="n">
-        <v>3.2</v>
+        <v>2.48</v>
       </c>
       <c r="P36" t="n">
-        <v>1.92</v>
+        <v>2.13</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.94</v>
+        <v>4.2</v>
       </c>
       <c r="R36" t="n">
-        <v>1.53</v>
+        <v>1.36</v>
       </c>
       <c r="S36" t="n">
-        <v>2.34</v>
+        <v>2.78</v>
       </c>
       <c r="T36" t="n">
-        <v>3.48</v>
+        <v>2.84</v>
       </c>
       <c r="U36" t="n">
-        <v>1.22</v>
+        <v>1.35</v>
       </c>
       <c r="V36" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="W36" t="n">
-        <v>1.46</v>
+        <v>1.27</v>
       </c>
       <c r="X36" t="n">
-        <v>2.6</v>
+        <v>3.25</v>
       </c>
       <c r="Y36" t="n">
-        <v>2.55</v>
+        <v>1.97</v>
       </c>
       <c r="Z36" t="n">
-        <v>1.51</v>
+        <v>1.83</v>
       </c>
       <c r="AA36" t="n">
-        <v>4.8</v>
+        <v>3.4</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.13</v>
+        <v>1.25</v>
       </c>
       <c r="AC36" t="n">
-        <v>2.08</v>
+        <v>1.81</v>
       </c>
       <c r="AD36" t="n">
-        <v>1.66</v>
+        <v>1.91</v>
       </c>
       <c r="AE36" t="inlineStr">
         <is>
@@ -5122,10 +5122,10 @@
         </is>
       </c>
       <c r="AG36" t="n">
-        <v>1.37</v>
+        <v>1.29</v>
       </c>
       <c r="AH36" t="n">
-        <v>1.54</v>
+        <v>1.9</v>
       </c>
       <c r="AI36" t="n">
         <v>0</v>
@@ -5134,7 +5134,7 @@
         <v>0</v>
       </c>
       <c r="AK36" s="3" t="n">
-        <v>45930.66666666666</v>
+        <v>45930.65625</v>
       </c>
     </row>
     <row r="37">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,61 +5184,61 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>4.3</v>
+        <v>1.56</v>
       </c>
       <c r="M37" t="n">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="N37" t="n">
-        <v>1.64</v>
+        <v>5.4</v>
       </c>
       <c r="O37" t="n">
-        <v>4.45</v>
+        <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="S37" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="T37" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="U37" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="V37" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W37" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="X37" t="n">
-        <v>5.35</v>
+        <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.44</v>
+        <v>1.63</v>
       </c>
       <c r="Z37" t="n">
-        <v>2.75</v>
+        <v>2.25</v>
       </c>
       <c r="AA37" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC37" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AD37" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AE37" t="inlineStr">
         <is>
@@ -5251,10 +5251,10 @@
         </is>
       </c>
       <c r="AG37" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AH37" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AI37" t="n">
         <v>0</v>
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Olympique Marseille</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,13 +5313,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>1.56</v>
+        <v>1.62</v>
       </c>
       <c r="M38" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="N38" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5352,10 +5352,10 @@
         <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.63</v>
+        <v>1.68</v>
       </c>
       <c r="Z38" t="n">
-        <v>2.25</v>
+        <v>2.18</v>
       </c>
       <c r="AA38" t="n">
         <v>0</v>
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,13 +5442,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>3</v>
+        <v>4.3</v>
       </c>
       <c r="M39" t="n">
-        <v>3.83</v>
+        <v>4.4</v>
       </c>
       <c r="N39" t="n">
-        <v>2.1</v>
+        <v>1.64</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5481,16 +5481,16 @@
         <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z39" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AA39" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="AC39" t="n">
         <v>0</v>
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,13 +5571,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>15</v>
+        <v>1.35</v>
       </c>
       <c r="M40" t="n">
-        <v>7.6</v>
+        <v>5.3</v>
       </c>
       <c r="N40" t="n">
-        <v>1.15</v>
+        <v>7</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5610,16 +5610,16 @@
         <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="Z40" t="n">
-        <v>2.75</v>
+        <v>2.35</v>
       </c>
       <c r="AA40" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,61 +5700,61 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1.62</v>
+        <v>3</v>
       </c>
       <c r="M41" t="n">
-        <v>4.1</v>
+        <v>3.83</v>
       </c>
       <c r="N41" t="n">
-        <v>4.9</v>
+        <v>2.1</v>
       </c>
       <c r="O41" t="n">
-        <v>2.16</v>
+        <v>3.58</v>
       </c>
       <c r="P41" t="n">
-        <v>2.52</v>
+        <v>2.38</v>
       </c>
       <c r="Q41" t="n">
-        <v>4.9</v>
+        <v>2.62</v>
       </c>
       <c r="R41" t="n">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="S41" t="n">
-        <v>3.24</v>
+        <v>3.45</v>
       </c>
       <c r="T41" t="n">
-        <v>2.42</v>
+        <v>2.25</v>
       </c>
       <c r="U41" t="n">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="V41" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="W41" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="X41" t="n">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.68</v>
+        <v>1.58</v>
       </c>
       <c r="Z41" t="n">
-        <v>2.18</v>
+        <v>2.38</v>
       </c>
       <c r="AA41" t="n">
-        <v>2.63</v>
+        <v>2.25</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.44</v>
+        <v>1.65</v>
       </c>
       <c r="AC41" t="n">
-        <v>1.7</v>
+        <v>1.49</v>
       </c>
       <c r="AD41" t="n">
-        <v>2.15</v>
+        <v>2.47</v>
       </c>
       <c r="AE41" t="inlineStr">
         <is>
@@ -5767,10 +5767,10 @@
         </is>
       </c>
       <c r="AG41" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AH41" t="n">
-        <v>2.27</v>
+        <v>1.39</v>
       </c>
       <c r="AI41" t="n">
         <v>0</v>
@@ -5793,7 +5793,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,61 +5829,61 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>1.35</v>
+        <v>2.45</v>
       </c>
       <c r="M42" t="n">
-        <v>5.3</v>
+        <v>3.15</v>
       </c>
       <c r="N42" t="n">
-        <v>7</v>
+        <v>3.05</v>
       </c>
       <c r="O42" t="n">
-        <v>1.8</v>
+        <v>3.22</v>
       </c>
       <c r="P42" t="n">
-        <v>2.6</v>
+        <v>1.92</v>
       </c>
       <c r="Q42" t="n">
-        <v>7.4</v>
+        <v>3.94</v>
       </c>
       <c r="R42" t="n">
-        <v>1.24</v>
+        <v>1.53</v>
       </c>
       <c r="S42" t="n">
-        <v>3.54</v>
+        <v>2.34</v>
       </c>
       <c r="T42" t="n">
-        <v>2.3</v>
+        <v>3.48</v>
       </c>
       <c r="U42" t="n">
-        <v>1.62</v>
+        <v>1.22</v>
       </c>
       <c r="V42" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="W42" t="n">
-        <v>1.16</v>
+        <v>1.53</v>
       </c>
       <c r="X42" t="n">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.6</v>
+        <v>2.52</v>
       </c>
       <c r="Z42" t="n">
-        <v>2.35</v>
+        <v>1.52</v>
       </c>
       <c r="AA42" t="n">
-        <v>2.42</v>
+        <v>4.8</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.6</v>
+        <v>1.13</v>
       </c>
       <c r="AC42" t="n">
-        <v>1.86</v>
+        <v>2.06</v>
       </c>
       <c r="AD42" t="n">
-        <v>1.94</v>
+        <v>1.7</v>
       </c>
       <c r="AE42" t="inlineStr">
         <is>
@@ -5896,10 +5896,10 @@
         </is>
       </c>
       <c r="AG42" t="n">
-        <v>1.17</v>
+        <v>1.37</v>
       </c>
       <c r="AH42" t="n">
-        <v>3</v>
+        <v>1.54</v>
       </c>
       <c r="AI42" t="n">
         <v>0</v>
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Olympique Marseille</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5961,40 +5961,40 @@
         <v>1.56</v>
       </c>
       <c r="M43" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="N43" t="n">
-        <v>5.4</v>
+        <v>5.1</v>
       </c>
       <c r="O43" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="P43" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="Q43" t="n">
-        <v>5</v>
+        <v>4.4</v>
       </c>
       <c r="R43" t="n">
         <v>1.28</v>
       </c>
       <c r="S43" t="n">
-        <v>3.45</v>
+        <v>3.32</v>
       </c>
       <c r="T43" t="n">
-        <v>2.25</v>
+        <v>2.46</v>
       </c>
       <c r="U43" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="V43" t="n">
         <v>1.01</v>
       </c>
       <c r="W43" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="X43" t="n">
-        <v>4.33</v>
+        <v>4.55</v>
       </c>
       <c r="Y43" t="n">
         <v>1.63</v>
@@ -6003,16 +6003,16 @@
         <v>2.25</v>
       </c>
       <c r="AA43" t="n">
-        <v>2.75</v>
+        <v>2.4</v>
       </c>
       <c r="AB43" t="n">
         <v>1.52</v>
       </c>
       <c r="AC43" t="n">
-        <v>1.61</v>
+        <v>1.66</v>
       </c>
       <c r="AD43" t="n">
-        <v>2.04</v>
+        <v>2.16</v>
       </c>
       <c r="AE43" t="inlineStr">
         <is>
@@ -6025,10 +6025,10 @@
         </is>
       </c>
       <c r="AG43" t="n">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="AH43" t="n">
-        <v>2.41</v>
+        <v>2.39</v>
       </c>
       <c r="AI43" t="n">
         <v>0</v>
@@ -6046,27 +6046,27 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6087,13 +6087,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>1.57</v>
+        <v>15</v>
       </c>
       <c r="M44" t="n">
-        <v>4.8</v>
+        <v>7.6</v>
       </c>
       <c r="N44" t="n">
-        <v>4.9</v>
+        <v>1.15</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -6126,16 +6126,16 @@
         <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="Z44" t="n">
         <v>2.75</v>
       </c>
       <c r="AA44" t="n">
-        <v>1.88</v>
+        <v>1.95</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.92</v>
+        <v>1.79</v>
       </c>
       <c r="AC44" t="n">
         <v>0</v>
@@ -6166,7 +6166,7 @@
         <v>0</v>
       </c>
       <c r="AK44" s="3" t="n">
-        <v>45930.85416666666</v>
+        <v>45930.66666666666</v>
       </c>
     </row>
     <row r="45">
@@ -6175,12 +6175,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6216,61 +6216,61 @@
         </is>
       </c>
       <c r="L45" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="M45" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="N45" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="O45" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="P45" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="R45" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="S45" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="T45" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="U45" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="V45" t="n">
+        <v>0</v>
+      </c>
+      <c r="W45" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X45" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="Y45" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z45" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AA45" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AB45" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AC45" t="n">
         <v>1.4</v>
       </c>
-      <c r="M45" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="N45" t="n">
-        <v>6</v>
-      </c>
-      <c r="O45" t="n">
-        <v>0</v>
-      </c>
-      <c r="P45" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q45" t="n">
-        <v>0</v>
-      </c>
-      <c r="R45" t="n">
-        <v>0</v>
-      </c>
-      <c r="S45" t="n">
-        <v>0</v>
-      </c>
-      <c r="T45" t="n">
-        <v>0</v>
-      </c>
-      <c r="U45" t="n">
-        <v>0</v>
-      </c>
-      <c r="V45" t="n">
-        <v>0</v>
-      </c>
-      <c r="W45" t="n">
-        <v>0</v>
-      </c>
-      <c r="X45" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y45" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="Z45" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AA45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC45" t="n">
-        <v>0</v>
-      </c>
       <c r="AD45" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="AE45" t="inlineStr">
         <is>
@@ -6283,10 +6283,10 @@
         </is>
       </c>
       <c r="AG45" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AH45" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AI45" t="n">
         <v>0</v>
@@ -6295,7 +6295,7 @@
         <v>0</v>
       </c>
       <c r="AK45" s="3" t="n">
-        <v>45930.89583333334</v>
+        <v>45930.85416666666</v>
       </c>
     </row>
     <row r="46">
@@ -6304,126 +6304,255 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Atlético Mineiro</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Juventude</t>
+        </is>
+      </c>
+      <c r="G46" t="n">
+        <v>0</v>
+      </c>
+      <c r="H46" t="n">
+        <v>0</v>
+      </c>
+      <c r="I46" t="n">
+        <v>0</v>
+      </c>
+      <c r="J46" t="n">
+        <v>0</v>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L46" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="M46" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="N46" t="n">
+        <v>6</v>
+      </c>
+      <c r="O46" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="P46" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="R46" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="S46" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="T46" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="U46" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="V46" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W46" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="X46" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="Y46" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="Z46" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AA46" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AB46" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AC46" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AD46" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AE46" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF46" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG46" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AH46" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="AI46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK46" s="3" t="n">
+        <v>45930.89583333334</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="n">
+        <v>45930</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
           <t>21:35</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr">
+      <c r="C47" t="inlineStr">
         <is>
           <t>Brazil Serie B</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr">
+      <c r="D47" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr">
+      <c r="E47" t="inlineStr">
         <is>
           <t>Goiás</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr">
+      <c r="F47" t="inlineStr">
         <is>
           <t>Atlético GO</t>
         </is>
       </c>
-      <c r="G46" t="n">
-        <v>0</v>
-      </c>
-      <c r="H46" t="n">
-        <v>0</v>
-      </c>
-      <c r="I46" t="n">
-        <v>0</v>
-      </c>
-      <c r="J46" t="n">
-        <v>0</v>
-      </c>
-      <c r="K46" t="inlineStr">
+      <c r="G47" t="n">
+        <v>0</v>
+      </c>
+      <c r="H47" t="n">
+        <v>0</v>
+      </c>
+      <c r="I47" t="n">
+        <v>0</v>
+      </c>
+      <c r="J47" t="n">
+        <v>0</v>
+      </c>
+      <c r="K47" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L46" t="n">
+      <c r="L47" t="n">
         <v>1.93</v>
       </c>
-      <c r="M46" t="n">
+      <c r="M47" t="n">
         <v>3.1</v>
       </c>
-      <c r="N46" t="n">
+      <c r="N47" t="n">
         <v>3.57</v>
       </c>
-      <c r="O46" t="n">
-        <v>0</v>
-      </c>
-      <c r="P46" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q46" t="n">
-        <v>0</v>
-      </c>
-      <c r="R46" t="n">
-        <v>0</v>
-      </c>
-      <c r="S46" t="n">
-        <v>0</v>
-      </c>
-      <c r="T46" t="n">
-        <v>0</v>
-      </c>
-      <c r="U46" t="n">
-        <v>0</v>
-      </c>
-      <c r="V46" t="n">
-        <v>0</v>
-      </c>
-      <c r="W46" t="n">
-        <v>0</v>
-      </c>
-      <c r="X46" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y46" t="n">
+      <c r="O47" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="P47" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="R47" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="S47" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="T47" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="U47" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="V47" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W47" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="X47" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y47" t="n">
         <v>2.12</v>
       </c>
-      <c r="Z46" t="n">
+      <c r="Z47" t="n">
         <v>1.64</v>
       </c>
-      <c r="AA46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE46" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF46" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK46" s="3" t="n">
+      <c r="AA47" t="n">
+        <v>4.73</v>
+      </c>
+      <c r="AB47" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AC47" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AD47" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AE47" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF47" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG47" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AH47" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AI47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK47" s="3" t="n">
         <v>45930.89930555555</v>
       </c>
     </row>

--- a/jogos_2025-09-30.xlsx
+++ b/jogos_2025-09-30.xlsx
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sogdiana</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -927,13 +927,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.95</v>
+        <v>3.35</v>
       </c>
       <c r="M4" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="N4" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -966,10 +966,10 @@
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.08</v>
+        <v>2.25</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AA4" t="n">
         <v>0</v>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Sogdiana</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1056,13 +1056,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>3.35</v>
+        <v>2.95</v>
       </c>
       <c r="M5" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="N5" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1095,10 +1095,10 @@
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.25</v>
+        <v>2.08</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AA5" t="n">
         <v>0</v>
@@ -1581,34 +1581,34 @@
         <v>3.7</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="Y9" t="n">
         <v>1.7</v>
@@ -1617,16 +1617,16 @@
         <v>2.15</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
@@ -1794,22 +1794,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Havelse</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Waldhof Mannheim</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,61 +1830,61 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>3.38</v>
+        <v>1.35</v>
       </c>
       <c r="M11" t="n">
-        <v>3.7</v>
+        <v>4.83</v>
       </c>
       <c r="N11" t="n">
-        <v>1.91</v>
+        <v>7</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>6.89</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>4.77</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -1897,10 +1897,10 @@
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AI11" t="n">
         <v>0</v>
@@ -2052,22 +2052,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Saarbrucken</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>MSV Duisburg</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,61 +2088,61 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.26</v>
+        <v>1.87</v>
       </c>
       <c r="M13" t="n">
-        <v>5.1</v>
+        <v>3.8</v>
       </c>
       <c r="N13" t="n">
-        <v>7.6</v>
+        <v>3.55</v>
       </c>
       <c r="O13" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>6.89</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>4.77</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
@@ -2155,10 +2155,10 @@
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AI13" t="n">
         <v>0</v>
@@ -2181,22 +2181,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Erzgebirge Aue</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,61 +2217,61 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.02</v>
+        <v>1.53</v>
       </c>
       <c r="M14" t="n">
-        <v>3.45</v>
+        <v>4.4</v>
       </c>
       <c r="N14" t="n">
-        <v>3.29</v>
+        <v>5</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
@@ -2284,10 +2284,10 @@
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AI14" t="n">
         <v>0</v>
@@ -2310,22 +2310,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Erzgebirge Aue</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,61 +2346,61 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.56</v>
+        <v>2.02</v>
       </c>
       <c r="M15" t="n">
-        <v>4.2</v>
+        <v>3.45</v>
       </c>
       <c r="N15" t="n">
-        <v>4.2</v>
+        <v>3.29</v>
       </c>
       <c r="O15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
@@ -2413,10 +2413,10 @@
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AH15" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AI15" t="n">
         <v>0</v>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Saarbrucken</t>
+          <t>Havelse</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>MSV Duisburg</t>
+          <t>Waldhof Mannheim</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,13 +2475,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.87</v>
+        <v>3.38</v>
       </c>
       <c r="M16" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="N16" t="n">
-        <v>3.55</v>
+        <v>1.91</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,77 +2604,77 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>2.56</v>
+        <v>1.69</v>
       </c>
       <c r="P17" t="n">
-        <v>2.39</v>
+        <v>2.76</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.46</v>
+        <v>7.14</v>
       </c>
       <c r="R17" t="n">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="S17" t="n">
+        <v>3.94</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="V17" t="n">
+        <v>0</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X17" t="n">
+        <v>5.65</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AE17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG17" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AH17" t="n">
         <v>3.5</v>
-      </c>
-      <c r="T17" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="V17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="X17" t="n">
-        <v>5.29</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AE17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG17" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>1.69</v>
       </c>
       <c r="AI17" t="n">
         <v>0</v>
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,61 +2733,61 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.74</v>
+        <v>2.16</v>
       </c>
       <c r="M18" t="n">
-        <v>3.95</v>
+        <v>3.7</v>
       </c>
       <c r="N18" t="n">
-        <v>4.28</v>
+        <v>2.9</v>
       </c>
       <c r="O18" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="P18" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>3.46</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="S18" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T18" t="n">
         <v>2.25</v>
       </c>
-      <c r="P18" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>4.62</v>
-      </c>
-      <c r="R18" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="S18" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="T18" t="n">
-        <v>2.44</v>
-      </c>
       <c r="U18" t="n">
-        <v>1.49</v>
+        <v>1.59</v>
       </c>
       <c r="V18" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="W18" t="n">
-        <v>1.22</v>
+        <v>1.13</v>
       </c>
       <c r="X18" t="n">
-        <v>4.15</v>
+        <v>5.29</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.68</v>
+        <v>1.55</v>
       </c>
       <c r="Z18" t="n">
-        <v>2.14</v>
+        <v>2.39</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.6</v>
+        <v>2.38</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.39</v>
+        <v>1.5</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.64</v>
+        <v>1.48</v>
       </c>
       <c r="AD18" t="n">
-        <v>2.15</v>
+        <v>2.5</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
@@ -2803,7 +2803,7 @@
         <v>1.24</v>
       </c>
       <c r="AH18" t="n">
-        <v>2.08</v>
+        <v>1.69</v>
       </c>
       <c r="AI18" t="n">
         <v>0</v>
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,77 +3120,77 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>4.28</v>
       </c>
       <c r="O21" t="n">
-        <v>1.69</v>
+        <v>2.25</v>
       </c>
       <c r="P21" t="n">
-        <v>2.76</v>
+        <v>2.3</v>
       </c>
       <c r="Q21" t="n">
-        <v>7.14</v>
+        <v>4.62</v>
       </c>
       <c r="R21" t="n">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="S21" t="n">
-        <v>3.94</v>
+        <v>3.28</v>
       </c>
       <c r="T21" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="V21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="X21" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AE21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG21" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AH21" t="n">
         <v>2.08</v>
-      </c>
-      <c r="U21" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="V21" t="n">
-        <v>0</v>
-      </c>
-      <c r="W21" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X21" t="n">
-        <v>5.65</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AE21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG21" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>3.5</v>
       </c>
       <c r="AI21" t="n">
         <v>0</v>
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,61 +3249,61 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>3.6</v>
+        <v>2.6</v>
       </c>
       <c r="M22" t="n">
-        <v>3.45</v>
+        <v>3.25</v>
       </c>
       <c r="N22" t="n">
-        <v>2.05</v>
+        <v>2.75</v>
       </c>
       <c r="O22" t="n">
-        <v>4.15</v>
+        <v>3.25</v>
       </c>
       <c r="P22" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.7</v>
+        <v>3.35</v>
       </c>
       <c r="R22" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="S22" t="n">
-        <v>2.64</v>
+        <v>2.51</v>
       </c>
       <c r="T22" t="n">
-        <v>2.93</v>
+        <v>3.08</v>
       </c>
       <c r="U22" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="V22" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="W22" t="n">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="X22" t="n">
-        <v>3.02</v>
+        <v>2.78</v>
       </c>
       <c r="Y22" t="n">
-        <v>2.07</v>
+        <v>2.2</v>
       </c>
       <c r="Z22" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AA22" t="n">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.89</v>
+        <v>1.85</v>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
@@ -3316,10 +3316,10 @@
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.3</v>
+        <v>1.49</v>
       </c>
       <c r="AI22" t="n">
         <v>0</v>
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>Mantova</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,61 +3378,61 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.6</v>
+        <v>1.8</v>
       </c>
       <c r="M23" t="n">
-        <v>3.25</v>
+        <v>3.7</v>
       </c>
       <c r="N23" t="n">
-        <v>2.75</v>
+        <v>4.3</v>
       </c>
       <c r="O23" t="n">
-        <v>3.25</v>
+        <v>2.45</v>
       </c>
       <c r="P23" t="n">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.35</v>
+        <v>4.8</v>
       </c>
       <c r="R23" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="S23" t="n">
-        <v>2.51</v>
+        <v>2.71</v>
       </c>
       <c r="T23" t="n">
-        <v>3.08</v>
+        <v>2.79</v>
       </c>
       <c r="U23" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="V23" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="W23" t="n">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="X23" t="n">
-        <v>2.78</v>
+        <v>3.12</v>
       </c>
       <c r="Y23" t="n">
-        <v>2.2</v>
+        <v>1.95</v>
       </c>
       <c r="Z23" t="n">
-        <v>1.67</v>
+        <v>1.85</v>
       </c>
       <c r="AA23" t="n">
-        <v>3.9</v>
+        <v>3.32</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.19</v>
+        <v>1.26</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.87</v>
+        <v>1.84</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
@@ -3445,10 +3445,10 @@
         </is>
       </c>
       <c r="AG23" t="n">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.49</v>
+        <v>1.94</v>
       </c>
       <c r="AI23" t="n">
         <v>0</v>
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mantova</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,61 +3636,61 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.8</v>
+        <v>3.6</v>
       </c>
       <c r="M25" t="n">
-        <v>3.7</v>
+        <v>3.45</v>
       </c>
       <c r="N25" t="n">
-        <v>4.3</v>
+        <v>2.05</v>
       </c>
       <c r="O25" t="n">
-        <v>2.45</v>
+        <v>4.15</v>
       </c>
       <c r="P25" t="n">
-        <v>2.14</v>
+        <v>2.05</v>
       </c>
       <c r="Q25" t="n">
-        <v>4.8</v>
+        <v>2.7</v>
       </c>
       <c r="R25" t="n">
         <v>1.4</v>
       </c>
       <c r="S25" t="n">
-        <v>2.71</v>
+        <v>2.64</v>
       </c>
       <c r="T25" t="n">
-        <v>2.79</v>
+        <v>2.93</v>
       </c>
       <c r="U25" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="V25" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="W25" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="X25" t="n">
-        <v>3.12</v>
+        <v>3.02</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.95</v>
+        <v>2.07</v>
       </c>
       <c r="Z25" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AA25" t="n">
-        <v>3.32</v>
+        <v>3.6</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
@@ -3703,10 +3703,10 @@
         </is>
       </c>
       <c r="AG25" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.94</v>
+        <v>1.3</v>
       </c>
       <c r="AI25" t="n">
         <v>0</v>
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,61 +4023,61 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.63</v>
+        <v>3.2</v>
       </c>
       <c r="M28" t="n">
-        <v>4.2</v>
+        <v>3.52</v>
       </c>
       <c r="N28" t="n">
-        <v>5</v>
+        <v>2.2</v>
       </c>
       <c r="O28" t="n">
+        <v>3.81</v>
+      </c>
+      <c r="P28" t="n">
         <v>2.15</v>
       </c>
-      <c r="P28" t="n">
-        <v>2.38</v>
-      </c>
       <c r="Q28" t="n">
-        <v>5.03</v>
+        <v>2.8</v>
       </c>
       <c r="R28" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="S28" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="V28" t="n">
+        <v>1</v>
+      </c>
+      <c r="W28" t="n">
         <v>1.28</v>
       </c>
-      <c r="S28" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="T28" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="U28" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="V28" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W28" t="n">
-        <v>1.18</v>
-      </c>
       <c r="X28" t="n">
-        <v>4.1</v>
+        <v>3.48</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.68</v>
+        <v>1.89</v>
       </c>
       <c r="Z28" t="n">
-        <v>2.2</v>
+        <v>1.91</v>
       </c>
       <c r="AA28" t="n">
-        <v>2.62</v>
+        <v>3.08</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="AD28" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
@@ -4090,10 +4090,10 @@
         </is>
       </c>
       <c r="AG28" t="n">
-        <v>1.17</v>
+        <v>1.3</v>
       </c>
       <c r="AH28" t="n">
-        <v>2.3</v>
+        <v>1.36</v>
       </c>
       <c r="AI28" t="n">
         <v>0</v>
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,61 +4152,61 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>3.2</v>
+        <v>1.33</v>
       </c>
       <c r="M29" t="n">
-        <v>3.55</v>
+        <v>5.15</v>
       </c>
       <c r="N29" t="n">
-        <v>2.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="O29" t="n">
-        <v>3.81</v>
+        <v>1.77</v>
       </c>
       <c r="P29" t="n">
-        <v>2.15</v>
+        <v>2.48</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.8</v>
+        <v>7</v>
       </c>
       <c r="R29" t="n">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="S29" t="n">
-        <v>2.88</v>
+        <v>3.08</v>
       </c>
       <c r="T29" t="n">
-        <v>2.71</v>
+        <v>2.5</v>
       </c>
       <c r="U29" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W29" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="X29" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB29" t="n">
         <v>1.38</v>
       </c>
-      <c r="V29" t="n">
-        <v>1</v>
-      </c>
-      <c r="W29" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="X29" t="n">
-        <v>3.48</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AC29" t="n">
-        <v>1.69</v>
+        <v>2.09</v>
       </c>
       <c r="AD29" t="n">
-        <v>2.07</v>
+        <v>1.68</v>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
@@ -4219,10 +4219,10 @@
         </is>
       </c>
       <c r="AG29" t="n">
-        <v>1.3</v>
+        <v>1.16</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.36</v>
+        <v>3.38</v>
       </c>
       <c r="AI29" t="n">
         <v>0</v>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,77 +4410,77 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.45</v>
+        <v>1.95</v>
       </c>
       <c r="M31" t="n">
-        <v>4.4</v>
+        <v>3.5</v>
       </c>
       <c r="N31" t="n">
-        <v>6.4</v>
+        <v>3.9</v>
       </c>
       <c r="O31" t="n">
-        <v>1.96</v>
+        <v>2.45</v>
       </c>
       <c r="P31" t="n">
-        <v>2.4</v>
+        <v>2.13</v>
       </c>
       <c r="Q31" t="n">
-        <v>6.3</v>
+        <v>4.2</v>
       </c>
       <c r="R31" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S31" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="V31" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W31" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="X31" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AE31" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF31" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG31" t="n">
         <v>1.28</v>
       </c>
-      <c r="S31" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="T31" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="U31" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="V31" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W31" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="X31" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="Z31" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AE31" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF31" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG31" t="n">
-        <v>1.2</v>
-      </c>
       <c r="AH31" t="n">
-        <v>2.71</v>
+        <v>1.8</v>
       </c>
       <c r="AI31" t="n">
         <v>0</v>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,61 +4539,61 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="M32" t="n">
-        <v>5.4</v>
+        <v>4.4</v>
       </c>
       <c r="N32" t="n">
-        <v>10.5</v>
+        <v>6.4</v>
       </c>
       <c r="O32" t="n">
-        <v>1.79</v>
+        <v>1.96</v>
       </c>
       <c r="P32" t="n">
-        <v>2.48</v>
+        <v>2.4</v>
       </c>
       <c r="Q32" t="n">
-        <v>8.1</v>
+        <v>6.3</v>
       </c>
       <c r="R32" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="S32" t="n">
-        <v>3.08</v>
+        <v>3.2</v>
       </c>
       <c r="T32" t="n">
-        <v>2.5</v>
+        <v>2.42</v>
       </c>
       <c r="U32" t="n">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="V32" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W32" t="n">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="X32" t="n">
-        <v>3.92</v>
+        <v>4.33</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="Z32" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AA32" t="n">
-        <v>2.85</v>
+        <v>2.63</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AC32" t="n">
-        <v>2.09</v>
+        <v>1.81</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.66</v>
+        <v>1.91</v>
       </c>
       <c r="AE32" t="inlineStr">
         <is>
@@ -4606,10 +4606,10 @@
         </is>
       </c>
       <c r="AG32" t="n">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="AH32" t="n">
-        <v>3.38</v>
+        <v>2.71</v>
       </c>
       <c r="AI32" t="n">
         <v>0</v>
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,74 +4668,74 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.18</v>
+        <v>2</v>
       </c>
       <c r="M33" t="n">
-        <v>3.45</v>
+        <v>3.65</v>
       </c>
       <c r="N33" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="O33" t="n">
-        <v>2.82</v>
+        <v>2.73</v>
       </c>
       <c r="P33" t="n">
-        <v>2.1</v>
+        <v>2.27</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="R33" t="n">
-        <v>1.37</v>
+        <v>1.29</v>
       </c>
       <c r="S33" t="n">
-        <v>2.75</v>
+        <v>3.14</v>
       </c>
       <c r="T33" t="n">
-        <v>2.88</v>
+        <v>2.4</v>
       </c>
       <c r="U33" t="n">
-        <v>1.34</v>
+        <v>1.48</v>
       </c>
       <c r="V33" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W33" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="X33" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AE33" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF33" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG33" t="n">
         <v>1.28</v>
-      </c>
-      <c r="X33" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="Y33" t="n">
-        <v>2</v>
-      </c>
-      <c r="Z33" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AA33" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AB33" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AC33" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AD33" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="AE33" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF33" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG33" t="n">
-        <v>1.35</v>
       </c>
       <c r="AH33" t="n">
         <v>1.67</v>
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,61 +4797,61 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.13</v>
+        <v>2.55</v>
       </c>
       <c r="M34" t="n">
-        <v>3.75</v>
+        <v>3.2</v>
       </c>
       <c r="N34" t="n">
-        <v>3.15</v>
+        <v>2.85</v>
       </c>
       <c r="O34" t="n">
-        <v>2.73</v>
+        <v>3.18</v>
       </c>
       <c r="P34" t="n">
-        <v>2.27</v>
+        <v>2.02</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.6</v>
+        <v>3.54</v>
       </c>
       <c r="R34" t="n">
-        <v>1.29</v>
+        <v>1.43</v>
       </c>
       <c r="S34" t="n">
-        <v>3.14</v>
+        <v>2.54</v>
       </c>
       <c r="T34" t="n">
-        <v>2.4</v>
+        <v>3.08</v>
       </c>
       <c r="U34" t="n">
-        <v>1.48</v>
+        <v>1.3</v>
       </c>
       <c r="V34" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="W34" t="n">
-        <v>1.18</v>
+        <v>1.35</v>
       </c>
       <c r="X34" t="n">
-        <v>4.05</v>
+        <v>2.95</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.7</v>
+        <v>2.2</v>
       </c>
       <c r="Z34" t="n">
-        <v>2.15</v>
+        <v>1.67</v>
       </c>
       <c r="AA34" t="n">
-        <v>2.56</v>
+        <v>3.92</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.42</v>
+        <v>1.19</v>
       </c>
       <c r="AC34" t="n">
-        <v>1.56</v>
+        <v>1.87</v>
       </c>
       <c r="AD34" t="n">
-        <v>2.3</v>
+        <v>1.85</v>
       </c>
       <c r="AE34" t="inlineStr">
         <is>
@@ -4864,10 +4864,10 @@
         </is>
       </c>
       <c r="AG34" t="n">
-        <v>1.28</v>
+        <v>1.34</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.67</v>
+        <v>1.52</v>
       </c>
       <c r="AI34" t="n">
         <v>0</v>
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,77 +4926,77 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.55</v>
+        <v>2.21</v>
       </c>
       <c r="M35" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="N35" t="n">
         <v>3.3</v>
       </c>
-      <c r="N35" t="n">
-        <v>2.8</v>
-      </c>
       <c r="O35" t="n">
-        <v>3.18</v>
+        <v>2.82</v>
       </c>
       <c r="P35" t="n">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.54</v>
+        <v>3.9</v>
       </c>
       <c r="R35" t="n">
-        <v>1.43</v>
+        <v>1.37</v>
       </c>
       <c r="S35" t="n">
-        <v>2.54</v>
+        <v>2.75</v>
       </c>
       <c r="T35" t="n">
-        <v>3.08</v>
+        <v>2.75</v>
       </c>
       <c r="U35" t="n">
-        <v>1.3</v>
+        <v>1.41</v>
       </c>
       <c r="V35" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="W35" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="X35" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AE35" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF35" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG35" t="n">
         <v>1.35</v>
       </c>
-      <c r="X35" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="Y35" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Z35" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AA35" t="n">
-        <v>3.92</v>
-      </c>
-      <c r="AB35" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AC35" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AD35" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AE35" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF35" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG35" t="n">
-        <v>1.34</v>
-      </c>
       <c r="AH35" t="n">
-        <v>1.52</v>
+        <v>1.67</v>
       </c>
       <c r="AI35" t="n">
         <v>0</v>
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,61 +5055,61 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>1.9</v>
+        <v>1.55</v>
       </c>
       <c r="M36" t="n">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="N36" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O36" t="n">
-        <v>2.48</v>
+        <v>2.15</v>
       </c>
       <c r="P36" t="n">
-        <v>2.13</v>
+        <v>2.38</v>
       </c>
       <c r="Q36" t="n">
-        <v>4.2</v>
+        <v>5.03</v>
       </c>
       <c r="R36" t="n">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="S36" t="n">
-        <v>2.78</v>
+        <v>3.2</v>
       </c>
       <c r="T36" t="n">
-        <v>2.84</v>
+        <v>2.42</v>
       </c>
       <c r="U36" t="n">
-        <v>1.35</v>
+        <v>1.47</v>
       </c>
       <c r="V36" t="n">
         <v>1.01</v>
       </c>
       <c r="W36" t="n">
-        <v>1.27</v>
+        <v>1.18</v>
       </c>
       <c r="X36" t="n">
-        <v>3.25</v>
+        <v>4.1</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.97</v>
+        <v>1.69</v>
       </c>
       <c r="Z36" t="n">
-        <v>1.83</v>
+        <v>2.16</v>
       </c>
       <c r="AA36" t="n">
-        <v>3.4</v>
+        <v>2.62</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="AC36" t="n">
-        <v>1.81</v>
+        <v>1.7</v>
       </c>
       <c r="AD36" t="n">
-        <v>1.91</v>
+        <v>2.05</v>
       </c>
       <c r="AE36" t="inlineStr">
         <is>
@@ -5122,10 +5122,10 @@
         </is>
       </c>
       <c r="AG36" t="n">
-        <v>1.29</v>
+        <v>1.17</v>
       </c>
       <c r="AH36" t="n">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
       <c r="AI36" t="n">
         <v>0</v>
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,61 +5184,61 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>1.56</v>
+        <v>15</v>
       </c>
       <c r="M37" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="N37" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="O37" t="n">
+        <v>11</v>
+      </c>
+      <c r="P37" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="R37" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="S37" t="n">
         <v>4.1</v>
       </c>
-      <c r="N37" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="O37" t="n">
-        <v>0</v>
-      </c>
-      <c r="P37" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q37" t="n">
-        <v>0</v>
-      </c>
-      <c r="R37" t="n">
-        <v>0</v>
-      </c>
-      <c r="S37" t="n">
-        <v>0</v>
-      </c>
       <c r="T37" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="U37" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="V37" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W37" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X37" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.63</v>
+        <v>1.44</v>
       </c>
       <c r="Z37" t="n">
-        <v>2.25</v>
+        <v>2.75</v>
       </c>
       <c r="AA37" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB37" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC37" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD37" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AE37" t="inlineStr">
         <is>
@@ -5251,10 +5251,10 @@
         </is>
       </c>
       <c r="AG37" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AH37" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AI37" t="n">
         <v>0</v>
@@ -5277,7 +5277,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,61 +5313,61 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>1.62</v>
+        <v>2.49</v>
       </c>
       <c r="M38" t="n">
-        <v>4.1</v>
+        <v>3.1</v>
       </c>
       <c r="N38" t="n">
-        <v>4.9</v>
+        <v>3</v>
       </c>
       <c r="O38" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="S38" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="T38" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="U38" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="V38" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="W38" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="X38" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.68</v>
+        <v>2.55</v>
       </c>
       <c r="Z38" t="n">
-        <v>2.18</v>
+        <v>1.51</v>
       </c>
       <c r="AA38" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AB38" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AC38" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AD38" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AE38" t="inlineStr">
         <is>
@@ -5380,10 +5380,10 @@
         </is>
       </c>
       <c r="AG38" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AH38" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AI38" t="n">
         <v>0</v>
@@ -5451,34 +5451,34 @@
         <v>1.64</v>
       </c>
       <c r="O39" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="R39" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="S39" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="T39" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="U39" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="V39" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W39" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X39" t="n">
-        <v>0</v>
+        <v>5.35</v>
       </c>
       <c r="Y39" t="n">
         <v>1.44</v>
@@ -5493,10 +5493,10 @@
         <v>1.7</v>
       </c>
       <c r="AC39" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AD39" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AE39" t="inlineStr">
         <is>
@@ -5509,10 +5509,10 @@
         </is>
       </c>
       <c r="AG39" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AH39" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AI39" t="n">
         <v>0</v>
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Olympique Marseille</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,61 +5571,61 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>1.35</v>
+        <v>1.56</v>
       </c>
       <c r="M40" t="n">
-        <v>5.3</v>
+        <v>4.3</v>
       </c>
       <c r="N40" t="n">
-        <v>7</v>
+        <v>5.1</v>
       </c>
       <c r="O40" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="R40" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="S40" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="T40" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="U40" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="V40" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W40" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X40" t="n">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="Z40" t="n">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="AA40" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AB40" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AC40" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AD40" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AE40" t="inlineStr">
         <is>
@@ -5638,10 +5638,10 @@
         </is>
       </c>
       <c r="AG40" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AH40" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="AI40" t="n">
         <v>0</v>
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,77 +5700,77 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>3</v>
+        <v>1.56</v>
       </c>
       <c r="M41" t="n">
-        <v>3.83</v>
+        <v>4.1</v>
       </c>
       <c r="N41" t="n">
-        <v>2.1</v>
+        <v>5.4</v>
       </c>
       <c r="O41" t="n">
-        <v>3.58</v>
+        <v>2</v>
       </c>
       <c r="P41" t="n">
-        <v>2.38</v>
+        <v>2.45</v>
       </c>
       <c r="Q41" t="n">
-        <v>2.62</v>
+        <v>5</v>
       </c>
       <c r="R41" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="S41" t="n">
         <v>3.45</v>
       </c>
       <c r="T41" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="U41" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="V41" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W41" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="X41" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="Z41" t="n">
         <v>2.25</v>
       </c>
-      <c r="U41" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="V41" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W41" t="n">
+      <c r="AA41" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AE41" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF41" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG41" t="n">
         <v>1.18</v>
       </c>
-      <c r="X41" t="n">
-        <v>5</v>
-      </c>
-      <c r="Y41" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="Z41" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AA41" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AB41" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AC41" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AD41" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="AE41" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF41" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG41" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AH41" t="n">
-        <v>1.39</v>
+        <v>2.43</v>
       </c>
       <c r="AI41" t="n">
         <v>0</v>
@@ -5793,7 +5793,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,61 +5829,61 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>2.45</v>
+        <v>1.35</v>
       </c>
       <c r="M42" t="n">
-        <v>3.15</v>
+        <v>5.3</v>
       </c>
       <c r="N42" t="n">
-        <v>3.05</v>
+        <v>7</v>
       </c>
       <c r="O42" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="P42" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.94</v>
+        <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="S42" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="T42" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="U42" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="V42" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="W42" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="X42" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>2.52</v>
+        <v>1.6</v>
       </c>
       <c r="Z42" t="n">
-        <v>1.52</v>
+        <v>2.35</v>
       </c>
       <c r="AA42" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AC42" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AD42" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AE42" t="inlineStr">
         <is>
@@ -5896,10 +5896,10 @@
         </is>
       </c>
       <c r="AG42" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AH42" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AI42" t="n">
         <v>0</v>
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Olympique Marseille</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5958,61 +5958,61 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>1.56</v>
+        <v>1.62</v>
       </c>
       <c r="M43" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="N43" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="O43" t="n">
-        <v>2.08</v>
+        <v>2.16</v>
       </c>
       <c r="P43" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="Q43" t="n">
-        <v>4.4</v>
+        <v>4.9</v>
       </c>
       <c r="R43" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="S43" t="n">
-        <v>3.32</v>
+        <v>3.24</v>
       </c>
       <c r="T43" t="n">
-        <v>2.46</v>
+        <v>2.42</v>
       </c>
       <c r="U43" t="n">
-        <v>1.59</v>
+        <v>1.52</v>
       </c>
       <c r="V43" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="W43" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="X43" t="n">
-        <v>4.55</v>
+        <v>4.2</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.63</v>
+        <v>1.68</v>
       </c>
       <c r="Z43" t="n">
-        <v>2.25</v>
+        <v>2.18</v>
       </c>
       <c r="AA43" t="n">
-        <v>2.4</v>
+        <v>2.62</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.52</v>
+        <v>1.44</v>
       </c>
       <c r="AC43" t="n">
-        <v>1.66</v>
+        <v>1.69</v>
       </c>
       <c r="AD43" t="n">
-        <v>2.16</v>
+        <v>2.17</v>
       </c>
       <c r="AE43" t="inlineStr">
         <is>
@@ -6025,10 +6025,10 @@
         </is>
       </c>
       <c r="AG43" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="AH43" t="n">
-        <v>2.39</v>
+        <v>2.27</v>
       </c>
       <c r="AI43" t="n">
         <v>0</v>
@@ -6061,12 +6061,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6087,13 +6087,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="M44" t="n">
-        <v>7.6</v>
+        <v>3.83</v>
       </c>
       <c r="N44" t="n">
-        <v>1.15</v>
+        <v>2.1</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -6126,16 +6126,16 @@
         <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="Z44" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AA44" t="n">
-        <v>1.95</v>
+        <v>2.25</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.79</v>
+        <v>1.65</v>
       </c>
       <c r="AC44" t="n">
         <v>0</v>
@@ -6474,16 +6474,16 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>1.93</v>
+        <v>2.05</v>
       </c>
       <c r="M47" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="N47" t="n">
-        <v>3.57</v>
+        <v>4</v>
       </c>
       <c r="O47" t="n">
-        <v>2.66</v>
+        <v>2.67</v>
       </c>
       <c r="P47" t="n">
         <v>2</v>
@@ -6495,10 +6495,10 @@
         <v>1.51</v>
       </c>
       <c r="S47" t="n">
-        <v>2.47</v>
+        <v>2.39</v>
       </c>
       <c r="T47" t="n">
-        <v>3.3</v>
+        <v>3.34</v>
       </c>
       <c r="U47" t="n">
         <v>1.28</v>
@@ -6507,28 +6507,28 @@
         <v>1.05</v>
       </c>
       <c r="W47" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="X47" t="n">
-        <v>3</v>
+        <v>2.53</v>
       </c>
       <c r="Y47" t="n">
-        <v>2.12</v>
+        <v>2.38</v>
       </c>
       <c r="Z47" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="AA47" t="n">
         <v>4.73</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="AC47" t="n">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="AD47" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="AE47" t="inlineStr">
         <is>
@@ -6541,7 +6541,7 @@
         </is>
       </c>
       <c r="AG47" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AH47" t="n">
         <v>1.77</v>

--- a/jogos_2025-09-30.xlsx
+++ b/jogos_2025-09-30.xlsx
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Sogdiana</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -927,13 +927,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>3.35</v>
+        <v>2.95</v>
       </c>
       <c r="M4" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="N4" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -966,10 +966,10 @@
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.25</v>
+        <v>2.08</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AA4" t="n">
         <v>0</v>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Sogdiana</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1056,13 +1056,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.95</v>
+        <v>3.35</v>
       </c>
       <c r="M5" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="N5" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1095,10 +1095,10 @@
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.08</v>
+        <v>2.25</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AA5" t="n">
         <v>0</v>
@@ -1194,7 +1194,7 @@
         <v>1.82</v>
       </c>
       <c r="O6" t="n">
-        <v>5.83</v>
+        <v>5.84</v>
       </c>
       <c r="P6" t="n">
         <v>2.25</v>
@@ -1203,19 +1203,19 @@
         <v>2.2</v>
       </c>
       <c r="R6" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="S6" t="n">
-        <v>2.7</v>
+        <v>2.85</v>
       </c>
       <c r="T6" t="n">
         <v>2.88</v>
       </c>
       <c r="U6" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="V6" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W6" t="n">
         <v>1.31</v>
@@ -1236,10 +1236,10 @@
         <v>1.23</v>
       </c>
       <c r="AC6" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.71</v>
+        <v>1.78</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
@@ -1252,10 +1252,10 @@
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>2.16</v>
+        <v>1.28</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AI6" t="n">
         <v>2.38</v>
@@ -1452,34 +1452,34 @@
         <v>1.11</v>
       </c>
       <c r="O8" t="n">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
         <v>1.3</v>
@@ -1494,10 +1494,10 @@
         <v>1.94</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AI8" t="n">
         <v>0</v>
@@ -1581,34 +1581,34 @@
         <v>3.7</v>
       </c>
       <c r="O9" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>4.45</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
         <v>1.7</v>
@@ -1617,16 +1617,16 @@
         <v>2.15</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
@@ -1665,22 +1665,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Wehen Wiesbaden</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,61 +1701,61 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.88</v>
+        <v>1.56</v>
       </c>
       <c r="M10" t="n">
-        <v>3.55</v>
+        <v>4.2</v>
       </c>
       <c r="N10" t="n">
-        <v>2.17</v>
+        <v>4.2</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -1768,10 +1768,10 @@
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AI10" t="n">
         <v>0</v>
@@ -1794,22 +1794,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Hansa Rostock</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,61 +1830,61 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.35</v>
+        <v>1.8</v>
       </c>
       <c r="M11" t="n">
-        <v>4.83</v>
+        <v>3.8</v>
       </c>
       <c r="N11" t="n">
-        <v>7</v>
+        <v>3.8</v>
       </c>
       <c r="O11" t="n">
-        <v>1.83</v>
+        <v>2.28</v>
       </c>
       <c r="P11" t="n">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="Q11" t="n">
-        <v>6.89</v>
+        <v>3.95</v>
       </c>
       <c r="R11" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="U11" t="n">
-        <v>1.62</v>
+        <v>1.54</v>
       </c>
       <c r="V11" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="X11" t="n">
-        <v>4.77</v>
+        <v>4</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.56</v>
+        <v>1.61</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.39</v>
+        <v>2.1</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.43</v>
+        <v>2.55</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.55</v>
+        <v>1.41</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.73</v>
+        <v>1.57</v>
       </c>
       <c r="AD11" t="n">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -1897,10 +1897,10 @@
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>1.1</v>
+        <v>1.21</v>
       </c>
       <c r="AH11" t="n">
-        <v>2.75</v>
+        <v>1.85</v>
       </c>
       <c r="AI11" t="n">
         <v>0</v>
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Hansa Rostock</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>Wehen Wiesbaden</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,22 +1959,22 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.8</v>
+        <v>2.9</v>
       </c>
       <c r="M12" t="n">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="N12" t="n">
-        <v>3.73</v>
+        <v>2.18</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -1983,37 +1983,37 @@
         <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -2026,10 +2026,10 @@
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AI12" t="n">
         <v>0</v>
@@ -2052,22 +2052,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Saarbrucken</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>MSV Duisburg</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,61 +2088,61 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.87</v>
+        <v>1.26</v>
       </c>
       <c r="M13" t="n">
-        <v>3.8</v>
+        <v>5.1</v>
       </c>
       <c r="N13" t="n">
-        <v>3.55</v>
+        <v>7.6</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>6.89</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>4.77</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
@@ -2155,10 +2155,10 @@
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AI13" t="n">
         <v>0</v>
@@ -2181,22 +2181,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Saarbrucken</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>MSV Duisburg</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,61 +2217,61 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.53</v>
+        <v>1.87</v>
       </c>
       <c r="M14" t="n">
-        <v>4.4</v>
+        <v>3.8</v>
       </c>
       <c r="N14" t="n">
-        <v>5</v>
+        <v>3.55</v>
       </c>
       <c r="O14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
@@ -2284,10 +2284,10 @@
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AI14" t="n">
         <v>0</v>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>Havelse</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Erzgebirge Aue</t>
+          <t>Waldhof Mannheim</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,22 +2346,22 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.02</v>
+        <v>3.4</v>
       </c>
       <c r="M15" t="n">
-        <v>3.45</v>
+        <v>3.75</v>
       </c>
       <c r="N15" t="n">
-        <v>3.29</v>
+        <v>1.92</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -2370,37 +2370,37 @@
         <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
@@ -2413,10 +2413,10 @@
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AI15" t="n">
         <v>0</v>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Havelse</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Waldhof Mannheim</t>
+          <t>Erzgebirge Aue</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,61 +2475,61 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>3.38</v>
+        <v>2.03</v>
       </c>
       <c r="M16" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="N16" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="O16" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="P16" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="X16" t="n">
         <v>3.7</v>
       </c>
-      <c r="N16" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>0</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0</v>
-      </c>
-      <c r="S16" t="n">
-        <v>0</v>
-      </c>
-      <c r="T16" t="n">
-        <v>0</v>
-      </c>
-      <c r="U16" t="n">
-        <v>0</v>
-      </c>
-      <c r="V16" t="n">
-        <v>0</v>
-      </c>
-      <c r="W16" t="n">
-        <v>0</v>
-      </c>
-      <c r="X16" t="n">
-        <v>0</v>
-      </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
@@ -2542,10 +2542,10 @@
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AI16" t="n">
         <v>0</v>
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,61 +2604,61 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O17" t="n">
-        <v>1.69</v>
+        <v>3.5</v>
       </c>
       <c r="P17" t="n">
-        <v>2.76</v>
+        <v>2.28</v>
       </c>
       <c r="Q17" t="n">
-        <v>7.14</v>
+        <v>2.64</v>
       </c>
       <c r="R17" t="n">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="S17" t="n">
-        <v>3.94</v>
+        <v>3.4</v>
       </c>
       <c r="T17" t="n">
-        <v>2.08</v>
+        <v>2.32</v>
       </c>
       <c r="U17" t="n">
-        <v>1.7</v>
+        <v>1.54</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W17" t="n">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="X17" t="n">
-        <v>5.65</v>
+        <v>4.85</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.4</v>
+        <v>1.59</v>
       </c>
       <c r="Z17" t="n">
-        <v>2.67</v>
+        <v>2.36</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.08</v>
+        <v>2.36</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.74</v>
+        <v>1.56</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.71</v>
+        <v>1.5</v>
       </c>
       <c r="AD17" t="n">
-        <v>2.04</v>
+        <v>2.41</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
@@ -2671,10 +2671,10 @@
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>1.12</v>
+        <v>1.26</v>
       </c>
       <c r="AH17" t="n">
-        <v>3.5</v>
+        <v>1.36</v>
       </c>
       <c r="AI17" t="n">
         <v>0</v>
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,77 +2733,77 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>2.56</v>
+        <v>1.71</v>
       </c>
       <c r="P18" t="n">
-        <v>2.39</v>
+        <v>2.74</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.46</v>
+        <v>6.84</v>
       </c>
       <c r="R18" t="n">
-        <v>1.24</v>
+        <v>1.19</v>
       </c>
       <c r="S18" t="n">
-        <v>3.5</v>
+        <v>3.94</v>
       </c>
       <c r="T18" t="n">
-        <v>2.25</v>
+        <v>2.08</v>
       </c>
       <c r="U18" t="n">
-        <v>1.59</v>
+        <v>1.7</v>
       </c>
       <c r="V18" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X18" t="n">
+        <v>5.65</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AE18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG18" t="n">
         <v>1.13</v>
       </c>
-      <c r="X18" t="n">
-        <v>5.29</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AE18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG18" t="n">
-        <v>1.24</v>
-      </c>
       <c r="AH18" t="n">
-        <v>1.69</v>
+        <v>3.34</v>
       </c>
       <c r="AI18" t="n">
         <v>0</v>
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,61 +2862,61 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.9</v>
+        <v>2.16</v>
       </c>
       <c r="M19" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="N19" t="n">
-        <v>2.1</v>
+        <v>2.97</v>
       </c>
       <c r="O19" t="n">
-        <v>3</v>
+        <v>2.58</v>
       </c>
       <c r="P19" t="n">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.62</v>
+        <v>3.43</v>
       </c>
       <c r="R19" t="n">
-        <v>1.27</v>
+        <v>1.23</v>
       </c>
       <c r="S19" t="n">
-        <v>3.4</v>
+        <v>3.58</v>
       </c>
       <c r="T19" t="n">
-        <v>2.3</v>
+        <v>2.21</v>
       </c>
       <c r="U19" t="n">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="V19" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="W19" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="X19" t="n">
-        <v>4.85</v>
+        <v>4.75</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="Z19" t="n">
-        <v>2.33</v>
+        <v>2.39</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.4</v>
+        <v>2.28</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.48</v>
+        <v>1.6</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="AD19" t="n">
-        <v>2.5</v>
+        <v>2.59</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
@@ -2929,10 +2929,10 @@
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.36</v>
+        <v>1.68</v>
       </c>
       <c r="AI19" t="n">
         <v>0</v>
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,61 +2991,61 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>3.52</v>
+        <v>1.79</v>
       </c>
       <c r="M20" t="n">
-        <v>3.98</v>
+        <v>3.95</v>
       </c>
       <c r="N20" t="n">
-        <v>1.9</v>
+        <v>3.9</v>
       </c>
       <c r="O20" t="n">
-        <v>3.78</v>
+        <v>2.25</v>
       </c>
       <c r="P20" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.35</v>
+        <v>4.62</v>
       </c>
       <c r="R20" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="S20" t="n">
-        <v>3.64</v>
+        <v>3.28</v>
       </c>
       <c r="T20" t="n">
-        <v>2.21</v>
+        <v>2.44</v>
       </c>
       <c r="U20" t="n">
-        <v>1.63</v>
+        <v>1.49</v>
       </c>
       <c r="V20" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="W20" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="X20" t="n">
-        <v>5.05</v>
+        <v>4.15</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.51</v>
+        <v>1.68</v>
       </c>
       <c r="Z20" t="n">
-        <v>2.44</v>
+        <v>2.14</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.24</v>
+        <v>2.6</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.62</v>
+        <v>1.39</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.46</v>
+        <v>1.64</v>
       </c>
       <c r="AD20" t="n">
-        <v>2.5</v>
+        <v>2.15</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
@@ -3058,10 +3058,10 @@
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.27</v>
+        <v>2.08</v>
       </c>
       <c r="AI20" t="n">
         <v>0</v>
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,61 +3120,61 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.74</v>
+        <v>3.2</v>
       </c>
       <c r="M21" t="n">
-        <v>3.95</v>
+        <v>3.7</v>
       </c>
       <c r="N21" t="n">
-        <v>4.28</v>
+        <v>1.91</v>
       </c>
       <c r="O21" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="P21" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S21" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="V21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X21" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AA21" t="n">
         <v>2.25</v>
       </c>
-      <c r="P21" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>4.62</v>
-      </c>
-      <c r="R21" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="S21" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="T21" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="U21" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="V21" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W21" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="X21" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>2.6</v>
-      </c>
       <c r="AB21" t="n">
-        <v>1.39</v>
+        <v>1.62</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.64</v>
+        <v>1.46</v>
       </c>
       <c r="AD21" t="n">
-        <v>2.15</v>
+        <v>2.56</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
@@ -3190,7 +3190,7 @@
         <v>1.24</v>
       </c>
       <c r="AH21" t="n">
-        <v>2.08</v>
+        <v>1.29</v>
       </c>
       <c r="AI21" t="n">
         <v>0</v>
@@ -3249,19 +3249,19 @@
         </is>
       </c>
       <c r="L22" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="M22" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="N22" t="n">
         <v>2.6</v>
-      </c>
-      <c r="M22" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="N22" t="n">
-        <v>2.75</v>
       </c>
       <c r="O22" t="n">
         <v>3.25</v>
       </c>
       <c r="P22" t="n">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="Q22" t="n">
         <v>3.35</v>
@@ -3291,7 +3291,7 @@
         <v>2.2</v>
       </c>
       <c r="Z22" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="AA22" t="n">
         <v>3.9</v>
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mantova</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,61 +3378,61 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.8</v>
+        <v>3.6</v>
       </c>
       <c r="M23" t="n">
-        <v>3.7</v>
+        <v>3.45</v>
       </c>
       <c r="N23" t="n">
-        <v>4.3</v>
+        <v>2.05</v>
       </c>
       <c r="O23" t="n">
-        <v>2.45</v>
+        <v>4.15</v>
       </c>
       <c r="P23" t="n">
-        <v>2.14</v>
+        <v>2.05</v>
       </c>
       <c r="Q23" t="n">
-        <v>4.8</v>
+        <v>2.72</v>
       </c>
       <c r="R23" t="n">
         <v>1.4</v>
       </c>
       <c r="S23" t="n">
-        <v>2.71</v>
+        <v>2.64</v>
       </c>
       <c r="T23" t="n">
-        <v>2.79</v>
+        <v>2.93</v>
       </c>
       <c r="U23" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="V23" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="W23" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="X23" t="n">
-        <v>3.12</v>
+        <v>3.02</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.95</v>
+        <v>2.07</v>
       </c>
       <c r="Z23" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AA23" t="n">
-        <v>3.32</v>
+        <v>3.6</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
@@ -3445,10 +3445,10 @@
         </is>
       </c>
       <c r="AG23" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.94</v>
+        <v>1.3</v>
       </c>
       <c r="AI23" t="n">
         <v>0</v>
@@ -3507,16 +3507,16 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="M24" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="N24" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="O24" t="n">
-        <v>2.79</v>
+        <v>2.81</v>
       </c>
       <c r="P24" t="n">
         <v>2.04</v>
@@ -3546,10 +3546,10 @@
         <v>2.88</v>
       </c>
       <c r="Y24" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="Z24" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="AA24" t="n">
         <v>3.82</v>
@@ -3574,7 +3574,7 @@
         </is>
       </c>
       <c r="AG24" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="AH24" t="n">
         <v>1.7</v>
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,61 +3636,61 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>3.6</v>
+        <v>2.11</v>
       </c>
       <c r="M25" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N25" t="n">
         <v>3.45</v>
       </c>
-      <c r="N25" t="n">
-        <v>2.05</v>
-      </c>
       <c r="O25" t="n">
-        <v>4.15</v>
+        <v>2.68</v>
       </c>
       <c r="P25" t="n">
-        <v>2.05</v>
+        <v>2.17</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.7</v>
+        <v>3.92</v>
       </c>
       <c r="R25" t="n">
-        <v>1.4</v>
+        <v>1.32</v>
       </c>
       <c r="S25" t="n">
-        <v>2.64</v>
+        <v>2.98</v>
       </c>
       <c r="T25" t="n">
-        <v>2.93</v>
+        <v>2.6</v>
       </c>
       <c r="U25" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="V25" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W25" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="X25" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="AB25" t="n">
         <v>1.33</v>
       </c>
-      <c r="V25" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W25" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="X25" t="n">
-        <v>3.02</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AC25" t="n">
-        <v>1.83</v>
+        <v>1.65</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.89</v>
+        <v>2.13</v>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
@@ -3703,10 +3703,10 @@
         </is>
       </c>
       <c r="AG25" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.3</v>
+        <v>1.74</v>
       </c>
       <c r="AI25" t="n">
         <v>0</v>
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Mantova</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,61 +3765,61 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.05</v>
+        <v>1.88</v>
       </c>
       <c r="M26" t="n">
         <v>3.65</v>
       </c>
       <c r="N26" t="n">
-        <v>3.45</v>
+        <v>4.08</v>
       </c>
       <c r="O26" t="n">
-        <v>2.55</v>
+        <v>2.45</v>
       </c>
       <c r="P26" t="n">
-        <v>2.17</v>
+        <v>2.14</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.92</v>
+        <v>4.7</v>
       </c>
       <c r="R26" t="n">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
       <c r="S26" t="n">
-        <v>2.98</v>
+        <v>2.71</v>
       </c>
       <c r="T26" t="n">
-        <v>2.6</v>
+        <v>2.79</v>
       </c>
       <c r="U26" t="n">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="V26" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="W26" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="X26" t="n">
-        <v>3.7</v>
+        <v>3.12</v>
       </c>
       <c r="Y26" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="Z26" t="n">
         <v>1.8</v>
       </c>
-      <c r="Z26" t="n">
-        <v>2</v>
-      </c>
       <c r="AA26" t="n">
-        <v>3</v>
+        <v>3.32</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.65</v>
+        <v>1.84</v>
       </c>
       <c r="AD26" t="n">
-        <v>2.13</v>
+        <v>1.88</v>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
@@ -3832,10 +3832,10 @@
         </is>
       </c>
       <c r="AG26" t="n">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.74</v>
+        <v>1.94</v>
       </c>
       <c r="AI26" t="n">
         <v>0</v>
@@ -3894,16 +3894,16 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.15</v>
+        <v>2.18</v>
       </c>
       <c r="M27" t="n">
-        <v>3.35</v>
+        <v>3.32</v>
       </c>
       <c r="N27" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="O27" t="n">
-        <v>2.81</v>
+        <v>2.8</v>
       </c>
       <c r="P27" t="n">
         <v>2.03</v>
@@ -3912,16 +3912,16 @@
         <v>4.24</v>
       </c>
       <c r="R27" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="S27" t="n">
         <v>2.51</v>
       </c>
       <c r="T27" t="n">
-        <v>3</v>
+        <v>3.08</v>
       </c>
       <c r="U27" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="V27" t="n">
         <v>1.03</v>
@@ -3933,13 +3933,13 @@
         <v>2.78</v>
       </c>
       <c r="Y27" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="Z27" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AA27" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="AB27" t="n">
         <v>1.19</v>
@@ -4026,7 +4026,7 @@
         <v>3.2</v>
       </c>
       <c r="M28" t="n">
-        <v>3.52</v>
+        <v>3.3</v>
       </c>
       <c r="N28" t="n">
         <v>2.2</v>
@@ -4062,10 +4062,10 @@
         <v>3.48</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.89</v>
+        <v>1.77</v>
       </c>
       <c r="Z28" t="n">
-        <v>1.91</v>
+        <v>1.98</v>
       </c>
       <c r="AA28" t="n">
         <v>3.08</v>
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,61 +4152,61 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.33</v>
+        <v>2.19</v>
       </c>
       <c r="M29" t="n">
-        <v>5.15</v>
+        <v>3.47</v>
       </c>
       <c r="N29" t="n">
-        <v>9.199999999999999</v>
+        <v>3.08</v>
       </c>
       <c r="O29" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="P29" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="R29" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="S29" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="V29" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W29" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="X29" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="Z29" t="n">
         <v>1.77</v>
       </c>
-      <c r="P29" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>7</v>
-      </c>
-      <c r="R29" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S29" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="T29" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="U29" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="V29" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W29" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="X29" t="n">
-        <v>4</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>2</v>
-      </c>
       <c r="AA29" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.38</v>
+        <v>1.25</v>
       </c>
       <c r="AC29" t="n">
-        <v>2.09</v>
+        <v>1.76</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.68</v>
+        <v>1.97</v>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
@@ -4219,10 +4219,10 @@
         </is>
       </c>
       <c r="AG29" t="n">
-        <v>1.16</v>
+        <v>1.35</v>
       </c>
       <c r="AH29" t="n">
-        <v>3.38</v>
+        <v>1.67</v>
       </c>
       <c r="AI29" t="n">
         <v>0</v>
@@ -4245,7 +4245,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,62 +4281,62 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>3</v>
+        <v>1.65</v>
       </c>
       <c r="M30" t="n">
-        <v>3.19</v>
+        <v>3.82</v>
       </c>
       <c r="N30" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="O30" t="n">
         <v>2.15</v>
       </c>
-      <c r="O30" t="n">
-        <v>3.6</v>
-      </c>
       <c r="P30" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>5.03</v>
+      </c>
+      <c r="R30" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S30" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="V30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W30" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="X30" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AD30" t="n">
         <v>2.05</v>
       </c>
-      <c r="Q30" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="R30" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="S30" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="T30" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="U30" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="V30" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W30" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="X30" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AC30" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AD30" t="n">
-        <v>1.9</v>
-      </c>
       <c r="AE30" t="inlineStr">
         <is>
           <t>[]</t>
@@ -4348,10 +4348,10 @@
         </is>
       </c>
       <c r="AG30" t="n">
-        <v>1.62</v>
+        <v>1.17</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.37</v>
+        <v>2.3</v>
       </c>
       <c r="AI30" t="n">
         <v>0</v>
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,61 +4410,61 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.95</v>
+        <v>1.36</v>
       </c>
       <c r="M31" t="n">
-        <v>3.5</v>
+        <v>4.75</v>
       </c>
       <c r="N31" t="n">
-        <v>3.9</v>
+        <v>8</v>
       </c>
       <c r="O31" t="n">
-        <v>2.45</v>
+        <v>1.77</v>
       </c>
       <c r="P31" t="n">
-        <v>2.13</v>
+        <v>2.48</v>
       </c>
       <c r="Q31" t="n">
-        <v>4.2</v>
+        <v>7</v>
       </c>
       <c r="R31" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="S31" t="n">
-        <v>2.78</v>
+        <v>3.08</v>
       </c>
       <c r="T31" t="n">
-        <v>2.84</v>
+        <v>2.5</v>
       </c>
       <c r="U31" t="n">
-        <v>1.35</v>
+        <v>1.44</v>
       </c>
       <c r="V31" t="n">
         <v>1.01</v>
       </c>
       <c r="W31" t="n">
-        <v>1.27</v>
+        <v>1.23</v>
       </c>
       <c r="X31" t="n">
-        <v>3.25</v>
+        <v>4</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.98</v>
+        <v>1.85</v>
       </c>
       <c r="Z31" t="n">
-        <v>1.82</v>
+        <v>1.89</v>
       </c>
       <c r="AA31" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.82</v>
+        <v>2.09</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.9</v>
+        <v>1.68</v>
       </c>
       <c r="AE31" t="inlineStr">
         <is>
@@ -4477,10 +4477,10 @@
         </is>
       </c>
       <c r="AG31" t="n">
-        <v>1.28</v>
+        <v>1.16</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.8</v>
+        <v>3.38</v>
       </c>
       <c r="AI31" t="n">
         <v>0</v>
@@ -4548,13 +4548,13 @@
         <v>6.4</v>
       </c>
       <c r="O32" t="n">
-        <v>1.96</v>
+        <v>1.93</v>
       </c>
       <c r="P32" t="n">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="Q32" t="n">
-        <v>6.3</v>
+        <v>5.5</v>
       </c>
       <c r="R32" t="n">
         <v>1.28</v>
@@ -4575,7 +4575,7 @@
         <v>1.17</v>
       </c>
       <c r="X32" t="n">
-        <v>4.33</v>
+        <v>4.2</v>
       </c>
       <c r="Y32" t="n">
         <v>1.65</v>
@@ -4606,10 +4606,10 @@
         </is>
       </c>
       <c r="AG32" t="n">
-        <v>1.2</v>
+        <v>1.11</v>
       </c>
       <c r="AH32" t="n">
-        <v>2.71</v>
+        <v>2.45</v>
       </c>
       <c r="AI32" t="n">
         <v>0</v>
@@ -4632,7 +4632,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,61 +4668,61 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2</v>
+        <v>3.06</v>
       </c>
       <c r="M33" t="n">
-        <v>3.65</v>
+        <v>3.19</v>
       </c>
       <c r="N33" t="n">
-        <v>3.1</v>
+        <v>2.08</v>
       </c>
       <c r="O33" t="n">
-        <v>2.73</v>
+        <v>3.6</v>
       </c>
       <c r="P33" t="n">
-        <v>2.27</v>
+        <v>2.05</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.6</v>
+        <v>2.92</v>
       </c>
       <c r="R33" t="n">
-        <v>1.29</v>
+        <v>1.38</v>
       </c>
       <c r="S33" t="n">
-        <v>3.14</v>
+        <v>2.75</v>
       </c>
       <c r="T33" t="n">
-        <v>2.4</v>
+        <v>2.8</v>
       </c>
       <c r="U33" t="n">
-        <v>1.48</v>
+        <v>1.37</v>
       </c>
       <c r="V33" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W33" t="n">
-        <v>1.18</v>
+        <v>1.28</v>
       </c>
       <c r="X33" t="n">
-        <v>4.05</v>
+        <v>3.25</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.69</v>
+        <v>1.84</v>
       </c>
       <c r="Z33" t="n">
-        <v>2.15</v>
+        <v>1.86</v>
       </c>
       <c r="AA33" t="n">
-        <v>2.56</v>
+        <v>3.55</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.42</v>
+        <v>1.27</v>
       </c>
       <c r="AC33" t="n">
-        <v>1.56</v>
+        <v>1.76</v>
       </c>
       <c r="AD33" t="n">
-        <v>2.3</v>
+        <v>1.9</v>
       </c>
       <c r="AE33" t="inlineStr">
         <is>
@@ -4735,10 +4735,10 @@
         </is>
       </c>
       <c r="AG33" t="n">
-        <v>1.28</v>
+        <v>1.62</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.67</v>
+        <v>1.37</v>
       </c>
       <c r="AI33" t="n">
         <v>0</v>
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,61 +4797,61 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.55</v>
+        <v>1.9</v>
       </c>
       <c r="M34" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="N34" t="n">
-        <v>2.85</v>
+        <v>4</v>
       </c>
       <c r="O34" t="n">
-        <v>3.18</v>
+        <v>2.45</v>
       </c>
       <c r="P34" t="n">
-        <v>2.02</v>
+        <v>2.13</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.54</v>
+        <v>4.2</v>
       </c>
       <c r="R34" t="n">
-        <v>1.43</v>
+        <v>1.36</v>
       </c>
       <c r="S34" t="n">
-        <v>2.54</v>
+        <v>2.78</v>
       </c>
       <c r="T34" t="n">
-        <v>3.08</v>
+        <v>2.84</v>
       </c>
       <c r="U34" t="n">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="V34" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W34" t="n">
-        <v>1.35</v>
+        <v>1.27</v>
       </c>
       <c r="X34" t="n">
-        <v>2.95</v>
+        <v>3.25</v>
       </c>
       <c r="Y34" t="n">
-        <v>2.2</v>
+        <v>1.98</v>
       </c>
       <c r="Z34" t="n">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AA34" t="n">
-        <v>3.92</v>
+        <v>3.4</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="AC34" t="n">
-        <v>1.87</v>
+        <v>1.82</v>
       </c>
       <c r="AD34" t="n">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AE34" t="inlineStr">
         <is>
@@ -4864,10 +4864,10 @@
         </is>
       </c>
       <c r="AG34" t="n">
-        <v>1.34</v>
+        <v>1.28</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.52</v>
+        <v>1.8</v>
       </c>
       <c r="AI34" t="n">
         <v>0</v>
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,74 +4926,74 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.21</v>
+        <v>2.36</v>
       </c>
       <c r="M35" t="n">
-        <v>3.55</v>
+        <v>3.38</v>
       </c>
       <c r="N35" t="n">
-        <v>3.3</v>
+        <v>2.86</v>
       </c>
       <c r="O35" t="n">
-        <v>2.82</v>
+        <v>2.73</v>
       </c>
       <c r="P35" t="n">
-        <v>2.1</v>
+        <v>2.27</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="R35" t="n">
-        <v>1.37</v>
+        <v>1.29</v>
       </c>
       <c r="S35" t="n">
-        <v>2.75</v>
+        <v>3.14</v>
       </c>
       <c r="T35" t="n">
-        <v>2.75</v>
+        <v>2.4</v>
       </c>
       <c r="U35" t="n">
-        <v>1.41</v>
+        <v>1.48</v>
       </c>
       <c r="V35" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="W35" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="X35" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AE35" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF35" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG35" t="n">
         <v>1.28</v>
-      </c>
-      <c r="X35" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="Y35" t="n">
-        <v>2</v>
-      </c>
-      <c r="Z35" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AA35" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AB35" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AC35" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AD35" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="AE35" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF35" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG35" t="n">
-        <v>1.35</v>
       </c>
       <c r="AH35" t="n">
         <v>1.67</v>
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,61 +5055,61 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>1.55</v>
+        <v>2.49</v>
       </c>
       <c r="M36" t="n">
-        <v>4.1</v>
+        <v>3.29</v>
       </c>
       <c r="N36" t="n">
-        <v>5</v>
+        <v>2.74</v>
       </c>
       <c r="O36" t="n">
-        <v>2.15</v>
+        <v>3.18</v>
       </c>
       <c r="P36" t="n">
-        <v>2.38</v>
+        <v>2.02</v>
       </c>
       <c r="Q36" t="n">
-        <v>5.03</v>
+        <v>3.54</v>
       </c>
       <c r="R36" t="n">
-        <v>1.28</v>
+        <v>1.43</v>
       </c>
       <c r="S36" t="n">
-        <v>3.2</v>
+        <v>2.54</v>
       </c>
       <c r="T36" t="n">
-        <v>2.42</v>
+        <v>3.08</v>
       </c>
       <c r="U36" t="n">
-        <v>1.47</v>
+        <v>1.3</v>
       </c>
       <c r="V36" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W36" t="n">
-        <v>1.18</v>
+        <v>1.35</v>
       </c>
       <c r="X36" t="n">
-        <v>4.1</v>
+        <v>2.95</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.69</v>
+        <v>2.2</v>
       </c>
       <c r="Z36" t="n">
-        <v>2.16</v>
+        <v>1.68</v>
       </c>
       <c r="AA36" t="n">
-        <v>2.62</v>
+        <v>3.92</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.4</v>
+        <v>1.19</v>
       </c>
       <c r="AC36" t="n">
-        <v>1.7</v>
+        <v>1.87</v>
       </c>
       <c r="AD36" t="n">
-        <v>2.05</v>
+        <v>1.85</v>
       </c>
       <c r="AE36" t="inlineStr">
         <is>
@@ -5122,10 +5122,10 @@
         </is>
       </c>
       <c r="AG36" t="n">
-        <v>1.17</v>
+        <v>1.34</v>
       </c>
       <c r="AH36" t="n">
-        <v>2.3</v>
+        <v>1.52</v>
       </c>
       <c r="AI36" t="n">
         <v>0</v>
@@ -5148,7 +5148,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,61 +5184,61 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>15</v>
+        <v>2.4</v>
       </c>
       <c r="M37" t="n">
-        <v>7.6</v>
+        <v>3.39</v>
       </c>
       <c r="N37" t="n">
-        <v>1.15</v>
+        <v>2.79</v>
       </c>
       <c r="O37" t="n">
-        <v>11</v>
+        <v>3.2</v>
       </c>
       <c r="P37" t="n">
-        <v>2.95</v>
+        <v>1.92</v>
       </c>
       <c r="Q37" t="n">
-        <v>1.44</v>
+        <v>3.85</v>
       </c>
       <c r="R37" t="n">
-        <v>1.19</v>
+        <v>1.53</v>
       </c>
       <c r="S37" t="n">
-        <v>4.1</v>
+        <v>2.34</v>
       </c>
       <c r="T37" t="n">
-        <v>2.12</v>
+        <v>3.48</v>
       </c>
       <c r="U37" t="n">
-        <v>1.78</v>
+        <v>1.22</v>
       </c>
       <c r="V37" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="W37" t="n">
-        <v>1.08</v>
+        <v>1.53</v>
       </c>
       <c r="X37" t="n">
-        <v>6.1</v>
+        <v>2.5</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.44</v>
+        <v>2.52</v>
       </c>
       <c r="Z37" t="n">
-        <v>2.75</v>
+        <v>1.52</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.95</v>
+        <v>4.8</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.79</v>
+        <v>1.13</v>
       </c>
       <c r="AC37" t="n">
-        <v>2.15</v>
+        <v>2.06</v>
       </c>
       <c r="AD37" t="n">
-        <v>1.58</v>
+        <v>1.7</v>
       </c>
       <c r="AE37" t="inlineStr">
         <is>
@@ -5251,10 +5251,10 @@
         </is>
       </c>
       <c r="AG37" t="n">
-        <v>1.09</v>
+        <v>1.37</v>
       </c>
       <c r="AH37" t="n">
-        <v>1.03</v>
+        <v>1.54</v>
       </c>
       <c r="AI37" t="n">
         <v>0</v>
@@ -5277,7 +5277,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,61 +5313,61 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.49</v>
+        <v>3</v>
       </c>
       <c r="M38" t="n">
-        <v>3.1</v>
+        <v>3.83</v>
       </c>
       <c r="N38" t="n">
-        <v>3</v>
+        <v>2.1</v>
       </c>
       <c r="O38" t="n">
-        <v>3.2</v>
+        <v>3.58</v>
       </c>
       <c r="P38" t="n">
-        <v>1.92</v>
+        <v>2.38</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.85</v>
+        <v>2.62</v>
       </c>
       <c r="R38" t="n">
-        <v>1.53</v>
+        <v>1.25</v>
       </c>
       <c r="S38" t="n">
-        <v>2.34</v>
+        <v>3.45</v>
       </c>
       <c r="T38" t="n">
-        <v>3.48</v>
+        <v>2.25</v>
       </c>
       <c r="U38" t="n">
-        <v>1.22</v>
+        <v>1.57</v>
       </c>
       <c r="V38" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="W38" t="n">
-        <v>1.46</v>
+        <v>1.18</v>
       </c>
       <c r="X38" t="n">
-        <v>2.44</v>
+        <v>5</v>
       </c>
       <c r="Y38" t="n">
-        <v>2.55</v>
+        <v>1.58</v>
       </c>
       <c r="Z38" t="n">
-        <v>1.51</v>
+        <v>2.38</v>
       </c>
       <c r="AA38" t="n">
-        <v>4.8</v>
+        <v>2.25</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.13</v>
+        <v>1.65</v>
       </c>
       <c r="AC38" t="n">
-        <v>2.06</v>
+        <v>1.49</v>
       </c>
       <c r="AD38" t="n">
-        <v>1.7</v>
+        <v>2.47</v>
       </c>
       <c r="AE38" t="inlineStr">
         <is>
@@ -5380,10 +5380,10 @@
         </is>
       </c>
       <c r="AG38" t="n">
-        <v>1.37</v>
+        <v>1.3</v>
       </c>
       <c r="AH38" t="n">
-        <v>1.54</v>
+        <v>1.39</v>
       </c>
       <c r="AI38" t="n">
         <v>0</v>
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,61 +5442,61 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>4.3</v>
+        <v>1.35</v>
       </c>
       <c r="M39" t="n">
-        <v>4.4</v>
+        <v>5.3</v>
       </c>
       <c r="N39" t="n">
-        <v>1.64</v>
+        <v>7</v>
       </c>
       <c r="O39" t="n">
-        <v>4.45</v>
+        <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="S39" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="T39" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="U39" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="V39" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W39" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X39" t="n">
-        <v>5.35</v>
+        <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="Z39" t="n">
-        <v>2.75</v>
+        <v>2.35</v>
       </c>
       <c r="AA39" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC39" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AD39" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AE39" t="inlineStr">
         <is>
@@ -5509,10 +5509,10 @@
         </is>
       </c>
       <c r="AG39" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AH39" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AI39" t="n">
         <v>0</v>
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Olympique Marseille</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,61 +5571,61 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>1.56</v>
+        <v>15</v>
       </c>
       <c r="M40" t="n">
-        <v>4.3</v>
+        <v>7.6</v>
       </c>
       <c r="N40" t="n">
-        <v>5.1</v>
+        <v>1.15</v>
       </c>
       <c r="O40" t="n">
-        <v>2.08</v>
+        <v>11</v>
       </c>
       <c r="P40" t="n">
-        <v>2.4</v>
+        <v>2.95</v>
       </c>
       <c r="Q40" t="n">
-        <v>4.4</v>
+        <v>1.44</v>
       </c>
       <c r="R40" t="n">
-        <v>1.28</v>
+        <v>1.19</v>
       </c>
       <c r="S40" t="n">
-        <v>3.32</v>
+        <v>4.1</v>
       </c>
       <c r="T40" t="n">
-        <v>2.46</v>
+        <v>2.12</v>
       </c>
       <c r="U40" t="n">
-        <v>1.59</v>
+        <v>1.78</v>
       </c>
       <c r="V40" t="n">
         <v>1.01</v>
       </c>
       <c r="W40" t="n">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="X40" t="n">
-        <v>4.55</v>
+        <v>6.1</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.63</v>
+        <v>1.44</v>
       </c>
       <c r="Z40" t="n">
-        <v>2.25</v>
+        <v>2.75</v>
       </c>
       <c r="AA40" t="n">
-        <v>2.4</v>
+        <v>1.95</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.52</v>
+        <v>1.79</v>
       </c>
       <c r="AC40" t="n">
-        <v>1.66</v>
+        <v>2.15</v>
       </c>
       <c r="AD40" t="n">
-        <v>2.16</v>
+        <v>1.58</v>
       </c>
       <c r="AE40" t="inlineStr">
         <is>
@@ -5638,10 +5638,10 @@
         </is>
       </c>
       <c r="AG40" t="n">
-        <v>1.24</v>
+        <v>1.09</v>
       </c>
       <c r="AH40" t="n">
-        <v>2.39</v>
+        <v>1.03</v>
       </c>
       <c r="AI40" t="n">
         <v>0</v>
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,61 +5700,61 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1.56</v>
+        <v>4.3</v>
       </c>
       <c r="M41" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="N41" t="n">
-        <v>5.4</v>
+        <v>1.64</v>
       </c>
       <c r="O41" t="n">
-        <v>2</v>
+        <v>4.45</v>
       </c>
       <c r="P41" t="n">
-        <v>2.45</v>
+        <v>2.6</v>
       </c>
       <c r="Q41" t="n">
-        <v>5</v>
+        <v>2.09</v>
       </c>
       <c r="R41" t="n">
-        <v>1.28</v>
+        <v>1.21</v>
       </c>
       <c r="S41" t="n">
-        <v>3.45</v>
+        <v>3.9</v>
       </c>
       <c r="T41" t="n">
-        <v>2.46</v>
+        <v>2.09</v>
       </c>
       <c r="U41" t="n">
-        <v>1.52</v>
+        <v>1.72</v>
       </c>
       <c r="V41" t="n">
         <v>1.01</v>
       </c>
       <c r="W41" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="X41" t="n">
-        <v>4.33</v>
+        <v>5.35</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.63</v>
+        <v>1.44</v>
       </c>
       <c r="Z41" t="n">
-        <v>2.25</v>
+        <v>2.75</v>
       </c>
       <c r="AA41" t="n">
-        <v>2.54</v>
+        <v>2.15</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.53</v>
+        <v>1.7</v>
       </c>
       <c r="AC41" t="n">
-        <v>1.61</v>
+        <v>1.49</v>
       </c>
       <c r="AD41" t="n">
-        <v>2.04</v>
+        <v>2.5</v>
       </c>
       <c r="AE41" t="inlineStr">
         <is>
@@ -5767,10 +5767,10 @@
         </is>
       </c>
       <c r="AG41" t="n">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="AH41" t="n">
-        <v>2.43</v>
+        <v>1.23</v>
       </c>
       <c r="AI41" t="n">
         <v>0</v>
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Olympique Marseille</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,61 +5829,61 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>1.35</v>
+        <v>1.56</v>
       </c>
       <c r="M42" t="n">
-        <v>5.3</v>
+        <v>4.3</v>
       </c>
       <c r="N42" t="n">
-        <v>7</v>
+        <v>5.1</v>
       </c>
       <c r="O42" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="P42" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="R42" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="S42" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="T42" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="U42" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="V42" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W42" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X42" t="n">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="Z42" t="n">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="AA42" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AB42" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AC42" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AD42" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AE42" t="inlineStr">
         <is>
@@ -5896,10 +5896,10 @@
         </is>
       </c>
       <c r="AG42" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AH42" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="AI42" t="n">
         <v>0</v>
@@ -6061,12 +6061,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6087,13 +6087,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>3</v>
+        <v>1.56</v>
       </c>
       <c r="M44" t="n">
-        <v>3.83</v>
+        <v>4.1</v>
       </c>
       <c r="N44" t="n">
-        <v>2.1</v>
+        <v>5.4</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -6126,16 +6126,16 @@
         <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Z44" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA44" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC44" t="n">
         <v>0</v>
@@ -6216,13 +6216,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>1.57</v>
+        <v>1.52</v>
       </c>
       <c r="M45" t="n">
-        <v>4.8</v>
+        <v>4</v>
       </c>
       <c r="N45" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="O45" t="n">
         <v>1.98</v>
@@ -6240,7 +6240,7 @@
         <v>4.4</v>
       </c>
       <c r="T45" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="U45" t="n">
         <v>1.81</v>
@@ -6249,10 +6249,10 @@
         <v>0</v>
       </c>
       <c r="W45" t="n">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="X45" t="n">
-        <v>6.5</v>
+        <v>6.8</v>
       </c>
       <c r="Y45" t="n">
         <v>1.3</v>
@@ -6261,16 +6261,16 @@
         <v>3.1</v>
       </c>
       <c r="AA45" t="n">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AC45" t="n">
         <v>1.4</v>
       </c>
       <c r="AD45" t="n">
-        <v>2.72</v>
+        <v>2.75</v>
       </c>
       <c r="AE45" t="inlineStr">
         <is>
@@ -6286,7 +6286,7 @@
         <v>1.18</v>
       </c>
       <c r="AH45" t="n">
-        <v>2.28</v>
+        <v>2.38</v>
       </c>
       <c r="AI45" t="n">
         <v>0</v>

--- a/jogos_2025-09-30.xlsx
+++ b/jogos_2025-09-30.xlsx
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sogdiana</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -927,13 +927,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.95</v>
+        <v>3.35</v>
       </c>
       <c r="M4" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="N4" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -966,10 +966,10 @@
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.08</v>
+        <v>2.25</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AA4" t="n">
         <v>0</v>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Sogdiana</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1056,13 +1056,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>3.35</v>
+        <v>2.95</v>
       </c>
       <c r="M5" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="N5" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1095,10 +1095,10 @@
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.25</v>
+        <v>2.08</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AA5" t="n">
         <v>0</v>
@@ -1452,34 +1452,34 @@
         <v>1.11</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>6.55</v>
       </c>
       <c r="Y8" t="n">
         <v>1.3</v>
@@ -1494,10 +1494,10 @@
         <v>1.94</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AI8" t="n">
         <v>0</v>
@@ -1665,22 +1665,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Saarbrucken</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>MSV Duisburg</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,61 +1701,61 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.56</v>
+        <v>1.87</v>
       </c>
       <c r="M10" t="n">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="N10" t="n">
-        <v>4.2</v>
+        <v>3.55</v>
       </c>
       <c r="O10" t="n">
-        <v>2</v>
+        <v>2.51</v>
       </c>
       <c r="P10" t="n">
-        <v>2.53</v>
+        <v>2.2</v>
       </c>
       <c r="Q10" t="n">
-        <v>4.75</v>
+        <v>3.98</v>
       </c>
       <c r="R10" t="n">
-        <v>1.21</v>
+        <v>1.29</v>
       </c>
       <c r="S10" t="n">
-        <v>3.75</v>
+        <v>3.26</v>
       </c>
       <c r="T10" t="n">
-        <v>2.14</v>
+        <v>2.36</v>
       </c>
       <c r="U10" t="n">
-        <v>1.66</v>
+        <v>1.52</v>
       </c>
       <c r="V10" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W10" t="n">
-        <v>1.1</v>
+        <v>1.19</v>
       </c>
       <c r="X10" t="n">
-        <v>5.2</v>
+        <v>4.45</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.42</v>
+        <v>1.59</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.5</v>
+        <v>2.22</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.92</v>
+        <v>2.42</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.78</v>
+        <v>1.44</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="AD10" t="n">
-        <v>2.37</v>
+        <v>2.36</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -1768,10 +1768,10 @@
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>1.16</v>
+        <v>1.24</v>
       </c>
       <c r="AH10" t="n">
-        <v>2.38</v>
+        <v>1.74</v>
       </c>
       <c r="AI10" t="n">
         <v>0</v>
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Hansa Rostock</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>Wehen Wiesbaden</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,61 +1830,61 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.8</v>
+        <v>2.9</v>
       </c>
       <c r="M11" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="N11" t="n">
-        <v>3.8</v>
+        <v>2.18</v>
       </c>
       <c r="O11" t="n">
-        <v>2.28</v>
+        <v>3.25</v>
       </c>
       <c r="P11" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.95</v>
+        <v>2.6</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="T11" t="n">
-        <v>2.28</v>
+        <v>2.16</v>
       </c>
       <c r="U11" t="n">
-        <v>1.54</v>
+        <v>1.6</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W11" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="X11" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.61</v>
+        <v>1.53</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.55</v>
+        <v>2.33</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.41</v>
+        <v>1.49</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="AD11" t="n">
-        <v>2.07</v>
+        <v>2.33</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -1897,10 +1897,10 @@
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>1.21</v>
+        <v>1.6</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.85</v>
+        <v>1.33</v>
       </c>
       <c r="AI11" t="n">
         <v>0</v>
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>Hansa Rostock</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Wehen Wiesbaden</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,61 +1959,61 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.9</v>
+        <v>1.8</v>
       </c>
       <c r="M12" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="N12" t="n">
-        <v>2.18</v>
+        <v>3.8</v>
       </c>
       <c r="O12" t="n">
-        <v>3.25</v>
+        <v>2.28</v>
       </c>
       <c r="P12" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.6</v>
+        <v>3.95</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="T12" t="n">
-        <v>2.16</v>
+        <v>2.28</v>
       </c>
       <c r="U12" t="n">
-        <v>1.6</v>
+        <v>1.54</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W12" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="X12" t="n">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.53</v>
+        <v>1.61</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.33</v>
+        <v>2.55</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.49</v>
+        <v>1.41</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.44</v>
+        <v>1.57</v>
       </c>
       <c r="AD12" t="n">
-        <v>2.33</v>
+        <v>2.07</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -2026,10 +2026,10 @@
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>1.6</v>
+        <v>1.21</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.33</v>
+        <v>1.85</v>
       </c>
       <c r="AI12" t="n">
         <v>0</v>
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Saarbrucken</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>MSV Duisburg</t>
+          <t>Erzgebirge Aue</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,61 +2217,61 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.87</v>
+        <v>2.03</v>
       </c>
       <c r="M14" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="N14" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="O14" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="P14" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="Q14" t="n">
         <v>3.55</v>
       </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
@@ -2284,10 +2284,10 @@
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AI14" t="n">
         <v>0</v>
@@ -2310,22 +2310,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Havelse</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Waldhof Mannheim</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,77 +2346,77 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>3.4</v>
+        <v>1.56</v>
       </c>
       <c r="M15" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="N15" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="O15" t="n">
+        <v>2</v>
+      </c>
+      <c r="P15" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="S15" t="n">
         <v>3.75</v>
       </c>
-      <c r="N15" t="n">
+      <c r="T15" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X15" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AA15" t="n">
         <v>1.92</v>
       </c>
-      <c r="O15" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="P15" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" t="n">
-        <v>0</v>
-      </c>
-      <c r="T15" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="V15" t="n">
-        <v>0</v>
-      </c>
-      <c r="W15" t="n">
+      <c r="AB15" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG15" t="n">
         <v>1.16</v>
       </c>
-      <c r="X15" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AE15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG15" t="n">
-        <v>1.2</v>
-      </c>
       <c r="AH15" t="n">
-        <v>1.26</v>
+        <v>2.38</v>
       </c>
       <c r="AI15" t="n">
         <v>0</v>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>Havelse</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Erzgebirge Aue</t>
+          <t>Waldhof Mannheim</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,61 +2475,61 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.03</v>
+        <v>3.4</v>
       </c>
       <c r="M16" t="n">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="N16" t="n">
-        <v>3.3</v>
+        <v>1.92</v>
       </c>
       <c r="O16" t="n">
-        <v>2.55</v>
+        <v>3.7</v>
       </c>
       <c r="P16" t="n">
-        <v>2.28</v>
+        <v>2.4</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.55</v>
+        <v>2.35</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="T16" t="n">
-        <v>2.43</v>
+        <v>2.23</v>
       </c>
       <c r="U16" t="n">
-        <v>1.48</v>
+        <v>1.56</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W16" t="n">
-        <v>1.21</v>
+        <v>1.16</v>
       </c>
       <c r="X16" t="n">
-        <v>3.7</v>
+        <v>4.25</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.71</v>
+        <v>1.57</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.94</v>
+        <v>2.16</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.8</v>
+        <v>2.45</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.35</v>
+        <v>1.45</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.58</v>
+        <v>1.5</v>
       </c>
       <c r="AD16" t="n">
-        <v>2.02</v>
+        <v>2.17</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
@@ -2542,10 +2542,10 @@
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.68</v>
+        <v>1.26</v>
       </c>
       <c r="AI16" t="n">
         <v>0</v>
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,61 +2604,61 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.87</v>
+        <v>3.2</v>
       </c>
       <c r="M17" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="N17" t="n">
-        <v>2.3</v>
+        <v>1.91</v>
       </c>
       <c r="O17" t="n">
-        <v>3.5</v>
+        <v>3.72</v>
       </c>
       <c r="P17" t="n">
-        <v>2.28</v>
+        <v>2.39</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.64</v>
+        <v>2.33</v>
       </c>
       <c r="R17" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="S17" t="n">
-        <v>3.4</v>
+        <v>3.58</v>
       </c>
       <c r="T17" t="n">
-        <v>2.32</v>
+        <v>2.2</v>
       </c>
       <c r="U17" t="n">
-        <v>1.54</v>
+        <v>1.63</v>
       </c>
       <c r="V17" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="W17" t="n">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="X17" t="n">
-        <v>4.85</v>
+        <v>5</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.59</v>
+        <v>1.52</v>
       </c>
       <c r="Z17" t="n">
-        <v>2.36</v>
+        <v>2.43</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.36</v>
+        <v>2.25</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.56</v>
+        <v>1.62</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AD17" t="n">
-        <v>2.41</v>
+        <v>2.56</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
@@ -2671,10 +2671,10 @@
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="AI17" t="n">
         <v>0</v>
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,61 +2991,61 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.79</v>
+        <v>2.87</v>
       </c>
       <c r="M20" t="n">
-        <v>3.95</v>
+        <v>3.5</v>
       </c>
       <c r="N20" t="n">
-        <v>3.9</v>
+        <v>2.3</v>
       </c>
       <c r="O20" t="n">
-        <v>2.25</v>
+        <v>3.5</v>
       </c>
       <c r="P20" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="Q20" t="n">
-        <v>4.62</v>
+        <v>2.64</v>
       </c>
       <c r="R20" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="S20" t="n">
-        <v>3.28</v>
+        <v>3.4</v>
       </c>
       <c r="T20" t="n">
-        <v>2.44</v>
+        <v>2.32</v>
       </c>
       <c r="U20" t="n">
-        <v>1.49</v>
+        <v>1.54</v>
       </c>
       <c r="V20" t="n">
         <v>1.03</v>
       </c>
       <c r="W20" t="n">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="X20" t="n">
-        <v>4.15</v>
+        <v>4.85</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.68</v>
+        <v>1.59</v>
       </c>
       <c r="Z20" t="n">
-        <v>2.14</v>
+        <v>2.36</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.6</v>
+        <v>2.36</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.39</v>
+        <v>1.56</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AD20" t="n">
-        <v>2.15</v>
+        <v>2.41</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
@@ -3058,10 +3058,10 @@
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="AH20" t="n">
-        <v>2.08</v>
+        <v>1.36</v>
       </c>
       <c r="AI20" t="n">
         <v>0</v>
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,61 +3120,61 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>3.2</v>
+        <v>1.79</v>
       </c>
       <c r="M21" t="n">
-        <v>3.7</v>
+        <v>3.95</v>
       </c>
       <c r="N21" t="n">
-        <v>1.91</v>
+        <v>3.9</v>
       </c>
       <c r="O21" t="n">
-        <v>3.72</v>
+        <v>2.25</v>
       </c>
       <c r="P21" t="n">
-        <v>2.39</v>
+        <v>2.3</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.33</v>
+        <v>4.62</v>
       </c>
       <c r="R21" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="S21" t="n">
-        <v>3.58</v>
+        <v>3.28</v>
       </c>
       <c r="T21" t="n">
-        <v>2.2</v>
+        <v>2.44</v>
       </c>
       <c r="U21" t="n">
-        <v>1.63</v>
+        <v>1.49</v>
       </c>
       <c r="V21" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="W21" t="n">
-        <v>1.1</v>
+        <v>1.16</v>
       </c>
       <c r="X21" t="n">
-        <v>5</v>
+        <v>4.15</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.52</v>
+        <v>1.68</v>
       </c>
       <c r="Z21" t="n">
-        <v>2.43</v>
+        <v>2.14</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.25</v>
+        <v>2.6</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.62</v>
+        <v>1.39</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.46</v>
+        <v>1.64</v>
       </c>
       <c r="AD21" t="n">
-        <v>2.56</v>
+        <v>2.15</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
@@ -3190,7 +3190,7 @@
         <v>1.24</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.29</v>
+        <v>2.08</v>
       </c>
       <c r="AI21" t="n">
         <v>0</v>
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Calcio Padova</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,22 +3249,22 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.62</v>
+        <v>2.18</v>
       </c>
       <c r="M22" t="n">
-        <v>3.24</v>
+        <v>3.32</v>
       </c>
       <c r="N22" t="n">
-        <v>2.6</v>
+        <v>3.4</v>
       </c>
       <c r="O22" t="n">
-        <v>3.25</v>
+        <v>2.8</v>
       </c>
       <c r="P22" t="n">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.35</v>
+        <v>4.24</v>
       </c>
       <c r="R22" t="n">
         <v>1.44</v>
@@ -3282,28 +3282,28 @@
         <v>1.03</v>
       </c>
       <c r="W22" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="X22" t="n">
         <v>2.78</v>
       </c>
       <c r="Y22" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="Z22" t="n">
         <v>1.66</v>
       </c>
       <c r="AA22" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="AB22" t="n">
         <v>1.19</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.87</v>
+        <v>1.92</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
@@ -3316,10 +3316,10 @@
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.49</v>
+        <v>1.69</v>
       </c>
       <c r="AI22" t="n">
         <v>0</v>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Mantova</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,61 +3507,61 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.05</v>
+        <v>1.88</v>
       </c>
       <c r="M24" t="n">
-        <v>3.4</v>
+        <v>3.65</v>
       </c>
       <c r="N24" t="n">
-        <v>3.5</v>
+        <v>4.08</v>
       </c>
       <c r="O24" t="n">
-        <v>2.81</v>
+        <v>2.45</v>
       </c>
       <c r="P24" t="n">
-        <v>2.04</v>
+        <v>2.14</v>
       </c>
       <c r="Q24" t="n">
-        <v>4.19</v>
+        <v>4.7</v>
       </c>
       <c r="R24" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="S24" t="n">
-        <v>2.57</v>
+        <v>2.71</v>
       </c>
       <c r="T24" t="n">
-        <v>3</v>
+        <v>2.79</v>
       </c>
       <c r="U24" t="n">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="V24" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="W24" t="n">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
       <c r="X24" t="n">
-        <v>2.88</v>
+        <v>3.12</v>
       </c>
       <c r="Y24" t="n">
-        <v>2.2</v>
+        <v>2.01</v>
       </c>
       <c r="Z24" t="n">
-        <v>1.69</v>
+        <v>1.8</v>
       </c>
       <c r="AA24" t="n">
-        <v>3.82</v>
+        <v>3.32</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.2</v>
+        <v>1.26</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.87</v>
+        <v>1.84</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
@@ -3574,10 +3574,10 @@
         </is>
       </c>
       <c r="AG24" t="n">
-        <v>1.32</v>
+        <v>1.23</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.7</v>
+        <v>1.94</v>
       </c>
       <c r="AI24" t="n">
         <v>0</v>
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,61 +3636,61 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.11</v>
+        <v>2.05</v>
       </c>
       <c r="M25" t="n">
         <v>3.4</v>
       </c>
       <c r="N25" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="O25" t="n">
-        <v>2.68</v>
+        <v>2.81</v>
       </c>
       <c r="P25" t="n">
-        <v>2.17</v>
+        <v>2.04</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.92</v>
+        <v>4.19</v>
       </c>
       <c r="R25" t="n">
-        <v>1.32</v>
+        <v>1.42</v>
       </c>
       <c r="S25" t="n">
-        <v>2.98</v>
+        <v>2.57</v>
       </c>
       <c r="T25" t="n">
-        <v>2.6</v>
+        <v>3</v>
       </c>
       <c r="U25" t="n">
-        <v>1.41</v>
+        <v>1.31</v>
       </c>
       <c r="V25" t="n">
         <v>1.02</v>
       </c>
       <c r="W25" t="n">
-        <v>1.21</v>
+        <v>1.34</v>
       </c>
       <c r="X25" t="n">
-        <v>3.74</v>
+        <v>2.88</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.77</v>
+        <v>2.2</v>
       </c>
       <c r="Z25" t="n">
-        <v>2</v>
+        <v>1.69</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.92</v>
+        <v>3.82</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.65</v>
+        <v>1.87</v>
       </c>
       <c r="AD25" t="n">
-        <v>2.13</v>
+        <v>1.85</v>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
@@ -3703,10 +3703,10 @@
         </is>
       </c>
       <c r="AG25" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.74</v>
+        <v>1.7</v>
       </c>
       <c r="AI25" t="n">
         <v>0</v>
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mantova</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,61 +3765,61 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.88</v>
+        <v>2.11</v>
       </c>
       <c r="M26" t="n">
-        <v>3.65</v>
+        <v>3.4</v>
       </c>
       <c r="N26" t="n">
-        <v>4.08</v>
+        <v>3.45</v>
       </c>
       <c r="O26" t="n">
-        <v>2.45</v>
+        <v>2.68</v>
       </c>
       <c r="P26" t="n">
-        <v>2.14</v>
+        <v>2.17</v>
       </c>
       <c r="Q26" t="n">
-        <v>4.7</v>
+        <v>3.92</v>
       </c>
       <c r="R26" t="n">
-        <v>1.38</v>
+        <v>1.32</v>
       </c>
       <c r="S26" t="n">
-        <v>2.71</v>
+        <v>2.98</v>
       </c>
       <c r="T26" t="n">
-        <v>2.79</v>
+        <v>2.6</v>
       </c>
       <c r="U26" t="n">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="V26" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="W26" t="n">
-        <v>1.29</v>
+        <v>1.21</v>
       </c>
       <c r="X26" t="n">
-        <v>3.12</v>
+        <v>3.74</v>
       </c>
       <c r="Y26" t="n">
-        <v>2.01</v>
+        <v>1.77</v>
       </c>
       <c r="Z26" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AA26" t="n">
-        <v>3.32</v>
+        <v>2.92</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.84</v>
+        <v>1.65</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.88</v>
+        <v>2.13</v>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
@@ -3832,10 +3832,10 @@
         </is>
       </c>
       <c r="AG26" t="n">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.94</v>
+        <v>1.74</v>
       </c>
       <c r="AI26" t="n">
         <v>0</v>
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Calcio Padova</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,22 +3894,22 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.18</v>
+        <v>2.62</v>
       </c>
       <c r="M27" t="n">
-        <v>3.32</v>
+        <v>3.24</v>
       </c>
       <c r="N27" t="n">
-        <v>3.4</v>
+        <v>2.6</v>
       </c>
       <c r="O27" t="n">
-        <v>2.8</v>
+        <v>3.25</v>
       </c>
       <c r="P27" t="n">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="Q27" t="n">
-        <v>4.24</v>
+        <v>3.35</v>
       </c>
       <c r="R27" t="n">
         <v>1.44</v>
@@ -3927,28 +3927,28 @@
         <v>1.03</v>
       </c>
       <c r="W27" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="X27" t="n">
         <v>2.78</v>
       </c>
       <c r="Y27" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="Z27" t="n">
         <v>1.66</v>
       </c>
       <c r="AA27" t="n">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="AB27" t="n">
         <v>1.19</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.92</v>
+        <v>1.87</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
@@ -3961,10 +3961,10 @@
         </is>
       </c>
       <c r="AG27" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.69</v>
+        <v>1.49</v>
       </c>
       <c r="AI27" t="n">
         <v>0</v>
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,77 +4023,77 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>3.2</v>
+        <v>1.9</v>
       </c>
       <c r="M28" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="N28" t="n">
-        <v>2.2</v>
+        <v>4</v>
       </c>
       <c r="O28" t="n">
-        <v>3.81</v>
+        <v>2.45</v>
       </c>
       <c r="P28" t="n">
-        <v>2.15</v>
+        <v>2.13</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.8</v>
+        <v>4.2</v>
       </c>
       <c r="R28" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="S28" t="n">
-        <v>2.88</v>
+        <v>2.78</v>
       </c>
       <c r="T28" t="n">
-        <v>2.71</v>
+        <v>2.84</v>
       </c>
       <c r="U28" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="V28" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="W28" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="X28" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AE28" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF28" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG28" t="n">
         <v>1.28</v>
       </c>
-      <c r="X28" t="n">
-        <v>3.48</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AE28" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF28" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG28" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AH28" t="n">
-        <v>1.36</v>
+        <v>1.8</v>
       </c>
       <c r="AI28" t="n">
         <v>0</v>
@@ -4116,7 +4116,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,61 +4152,61 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.19</v>
+        <v>3.06</v>
       </c>
       <c r="M29" t="n">
-        <v>3.47</v>
+        <v>3.19</v>
       </c>
       <c r="N29" t="n">
-        <v>3.08</v>
+        <v>2.08</v>
       </c>
       <c r="O29" t="n">
-        <v>2.82</v>
+        <v>3.6</v>
       </c>
       <c r="P29" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.9</v>
+        <v>2.92</v>
       </c>
       <c r="R29" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="S29" t="n">
         <v>2.75</v>
       </c>
       <c r="T29" t="n">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="U29" t="n">
-        <v>1.41</v>
+        <v>1.37</v>
       </c>
       <c r="V29" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="W29" t="n">
         <v>1.28</v>
       </c>
       <c r="X29" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.98</v>
+        <v>1.84</v>
       </c>
       <c r="Z29" t="n">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AA29" t="n">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AC29" t="n">
         <v>1.76</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.97</v>
+        <v>1.9</v>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
@@ -4219,10 +4219,10 @@
         </is>
       </c>
       <c r="AG29" t="n">
-        <v>1.35</v>
+        <v>1.62</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.67</v>
+        <v>1.37</v>
       </c>
       <c r="AI29" t="n">
         <v>0</v>
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,61 +4281,61 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.65</v>
+        <v>2.19</v>
       </c>
       <c r="M30" t="n">
-        <v>3.82</v>
+        <v>3.47</v>
       </c>
       <c r="N30" t="n">
-        <v>4.9</v>
+        <v>3.08</v>
       </c>
       <c r="O30" t="n">
-        <v>2.15</v>
+        <v>2.82</v>
       </c>
       <c r="P30" t="n">
-        <v>2.38</v>
+        <v>2.1</v>
       </c>
       <c r="Q30" t="n">
-        <v>5.03</v>
+        <v>3.9</v>
       </c>
       <c r="R30" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="S30" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="V30" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W30" t="n">
         <v>1.28</v>
       </c>
-      <c r="S30" t="n">
+      <c r="X30" t="n">
         <v>3.2</v>
       </c>
-      <c r="T30" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="U30" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="V30" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W30" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="X30" t="n">
-        <v>4.1</v>
-      </c>
       <c r="Y30" t="n">
-        <v>1.83</v>
+        <v>1.98</v>
       </c>
       <c r="Z30" t="n">
-        <v>1.91</v>
+        <v>1.77</v>
       </c>
       <c r="AA30" t="n">
-        <v>2.62</v>
+        <v>3.4</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="AC30" t="n">
-        <v>1.7</v>
+        <v>1.76</v>
       </c>
       <c r="AD30" t="n">
-        <v>2.05</v>
+        <v>1.97</v>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
@@ -4348,10 +4348,10 @@
         </is>
       </c>
       <c r="AG30" t="n">
-        <v>1.17</v>
+        <v>1.35</v>
       </c>
       <c r="AH30" t="n">
-        <v>2.3</v>
+        <v>1.67</v>
       </c>
       <c r="AI30" t="n">
         <v>0</v>
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,61 +4410,61 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.36</v>
+        <v>1.65</v>
       </c>
       <c r="M31" t="n">
-        <v>4.75</v>
+        <v>3.82</v>
       </c>
       <c r="N31" t="n">
-        <v>8</v>
+        <v>4.9</v>
       </c>
       <c r="O31" t="n">
-        <v>1.77</v>
+        <v>2.15</v>
       </c>
       <c r="P31" t="n">
-        <v>2.48</v>
+        <v>2.38</v>
       </c>
       <c r="Q31" t="n">
-        <v>7</v>
+        <v>5.03</v>
       </c>
       <c r="R31" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="S31" t="n">
-        <v>3.08</v>
+        <v>3.2</v>
       </c>
       <c r="T31" t="n">
-        <v>2.5</v>
+        <v>2.42</v>
       </c>
       <c r="U31" t="n">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="V31" t="n">
         <v>1.01</v>
       </c>
       <c r="W31" t="n">
-        <v>1.23</v>
+        <v>1.18</v>
       </c>
       <c r="X31" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="Z31" t="n">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="AA31" t="n">
-        <v>3</v>
+        <v>2.62</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AC31" t="n">
-        <v>2.09</v>
+        <v>1.7</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.68</v>
+        <v>2.05</v>
       </c>
       <c r="AE31" t="inlineStr">
         <is>
@@ -4477,10 +4477,10 @@
         </is>
       </c>
       <c r="AG31" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AH31" t="n">
-        <v>3.38</v>
+        <v>2.3</v>
       </c>
       <c r="AI31" t="n">
         <v>0</v>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,61 +4539,61 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.45</v>
+        <v>1.36</v>
       </c>
       <c r="M32" t="n">
-        <v>4.4</v>
+        <v>4.75</v>
       </c>
       <c r="N32" t="n">
-        <v>6.4</v>
+        <v>8</v>
       </c>
       <c r="O32" t="n">
-        <v>1.93</v>
+        <v>1.77</v>
       </c>
       <c r="P32" t="n">
-        <v>2.45</v>
+        <v>2.48</v>
       </c>
       <c r="Q32" t="n">
-        <v>5.5</v>
+        <v>7</v>
       </c>
       <c r="R32" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="S32" t="n">
-        <v>3.2</v>
+        <v>3.08</v>
       </c>
       <c r="T32" t="n">
-        <v>2.42</v>
+        <v>2.5</v>
       </c>
       <c r="U32" t="n">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="V32" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W32" t="n">
-        <v>1.17</v>
+        <v>1.23</v>
       </c>
       <c r="X32" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.65</v>
+        <v>1.85</v>
       </c>
       <c r="Z32" t="n">
-        <v>2.1</v>
+        <v>1.89</v>
       </c>
       <c r="AA32" t="n">
-        <v>2.63</v>
+        <v>3</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AC32" t="n">
-        <v>1.81</v>
+        <v>2.09</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.91</v>
+        <v>1.68</v>
       </c>
       <c r="AE32" t="inlineStr">
         <is>
@@ -4606,10 +4606,10 @@
         </is>
       </c>
       <c r="AG32" t="n">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="AH32" t="n">
-        <v>2.45</v>
+        <v>3.38</v>
       </c>
       <c r="AI32" t="n">
         <v>0</v>
@@ -4632,7 +4632,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,77 +4668,77 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>3.06</v>
+        <v>2.36</v>
       </c>
       <c r="M33" t="n">
-        <v>3.19</v>
+        <v>3.38</v>
       </c>
       <c r="N33" t="n">
-        <v>2.08</v>
+        <v>2.86</v>
       </c>
       <c r="O33" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="P33" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="Q33" t="n">
         <v>3.6</v>
       </c>
-      <c r="P33" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>2.92</v>
-      </c>
       <c r="R33" t="n">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="S33" t="n">
-        <v>2.75</v>
+        <v>3.14</v>
       </c>
       <c r="T33" t="n">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
       <c r="U33" t="n">
-        <v>1.37</v>
+        <v>1.48</v>
       </c>
       <c r="V33" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W33" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="X33" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AE33" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF33" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG33" t="n">
         <v>1.28</v>
       </c>
-      <c r="X33" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="Y33" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="Z33" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AA33" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AB33" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AC33" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AD33" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AE33" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF33" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG33" t="n">
-        <v>1.62</v>
-      </c>
       <c r="AH33" t="n">
-        <v>1.37</v>
+        <v>1.67</v>
       </c>
       <c r="AI33" t="n">
         <v>0</v>
@@ -4761,7 +4761,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,61 +4797,61 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.9</v>
+        <v>1.45</v>
       </c>
       <c r="M34" t="n">
-        <v>3.4</v>
+        <v>4.4</v>
       </c>
       <c r="N34" t="n">
-        <v>4</v>
+        <v>6.4</v>
       </c>
       <c r="O34" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="P34" t="n">
         <v>2.45</v>
       </c>
-      <c r="P34" t="n">
-        <v>2.13</v>
-      </c>
       <c r="Q34" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="R34" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S34" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="T34" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="V34" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W34" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="X34" t="n">
         <v>4.2</v>
       </c>
-      <c r="R34" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S34" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="T34" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="U34" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="V34" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W34" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="X34" t="n">
-        <v>3.25</v>
-      </c>
       <c r="Y34" t="n">
-        <v>1.98</v>
+        <v>1.65</v>
       </c>
       <c r="Z34" t="n">
-        <v>1.77</v>
+        <v>2.1</v>
       </c>
       <c r="AA34" t="n">
-        <v>3.4</v>
+        <v>2.63</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="AC34" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="AD34" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AE34" t="inlineStr">
         <is>
@@ -4864,10 +4864,10 @@
         </is>
       </c>
       <c r="AG34" t="n">
-        <v>1.28</v>
+        <v>1.11</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.8</v>
+        <v>2.45</v>
       </c>
       <c r="AI34" t="n">
         <v>0</v>
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,61 +4926,61 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.36</v>
+        <v>3.2</v>
       </c>
       <c r="M35" t="n">
-        <v>3.38</v>
+        <v>3.3</v>
       </c>
       <c r="N35" t="n">
-        <v>2.86</v>
+        <v>2.2</v>
       </c>
       <c r="O35" t="n">
-        <v>2.73</v>
+        <v>3.81</v>
       </c>
       <c r="P35" t="n">
-        <v>2.27</v>
+        <v>2.15</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.6</v>
+        <v>2.8</v>
       </c>
       <c r="R35" t="n">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
       <c r="S35" t="n">
-        <v>3.14</v>
+        <v>2.88</v>
       </c>
       <c r="T35" t="n">
-        <v>2.4</v>
+        <v>2.71</v>
       </c>
       <c r="U35" t="n">
-        <v>1.48</v>
+        <v>1.38</v>
       </c>
       <c r="V35" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="W35" t="n">
-        <v>1.18</v>
+        <v>1.28</v>
       </c>
       <c r="X35" t="n">
-        <v>4.05</v>
+        <v>3.48</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.89</v>
+        <v>1.77</v>
       </c>
       <c r="Z35" t="n">
-        <v>1.85</v>
+        <v>1.98</v>
       </c>
       <c r="AA35" t="n">
-        <v>2.56</v>
+        <v>3.08</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.42</v>
+        <v>1.3</v>
       </c>
       <c r="AC35" t="n">
-        <v>1.56</v>
+        <v>1.69</v>
       </c>
       <c r="AD35" t="n">
-        <v>2.3</v>
+        <v>2.07</v>
       </c>
       <c r="AE35" t="inlineStr">
         <is>
@@ -4993,10 +4993,10 @@
         </is>
       </c>
       <c r="AG35" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.67</v>
+        <v>1.36</v>
       </c>
       <c r="AI35" t="n">
         <v>0</v>
@@ -5148,7 +5148,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Olympique Marseille</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,61 +5184,61 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.4</v>
+        <v>1.56</v>
       </c>
       <c r="M37" t="n">
-        <v>3.39</v>
+        <v>4.3</v>
       </c>
       <c r="N37" t="n">
-        <v>2.79</v>
+        <v>5.1</v>
       </c>
       <c r="O37" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="S37" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="T37" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="U37" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="V37" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="W37" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="X37" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>2.52</v>
+        <v>1.63</v>
       </c>
       <c r="Z37" t="n">
-        <v>1.52</v>
+        <v>2.25</v>
       </c>
       <c r="AA37" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AC37" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AD37" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AE37" t="inlineStr">
         <is>
@@ -5251,10 +5251,10 @@
         </is>
       </c>
       <c r="AG37" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AH37" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AI37" t="n">
         <v>0</v>
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,61 +5313,61 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>3</v>
+        <v>1.56</v>
       </c>
       <c r="M38" t="n">
-        <v>3.83</v>
+        <v>4.1</v>
       </c>
       <c r="N38" t="n">
-        <v>2.1</v>
+        <v>5.4</v>
       </c>
       <c r="O38" t="n">
-        <v>3.58</v>
+        <v>2</v>
       </c>
       <c r="P38" t="n">
-        <v>2.38</v>
+        <v>2.43</v>
       </c>
       <c r="Q38" t="n">
-        <v>2.62</v>
+        <v>5.2</v>
       </c>
       <c r="R38" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="S38" t="n">
         <v>3.45</v>
       </c>
       <c r="T38" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="V38" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W38" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="X38" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="Z38" t="n">
         <v>2.25</v>
       </c>
-      <c r="U38" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="V38" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W38" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="X38" t="n">
-        <v>5</v>
-      </c>
-      <c r="Y38" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="Z38" t="n">
-        <v>2.38</v>
-      </c>
       <c r="AA38" t="n">
-        <v>2.25</v>
+        <v>2.54</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.65</v>
+        <v>1.52</v>
       </c>
       <c r="AC38" t="n">
-        <v>1.49</v>
+        <v>1.68</v>
       </c>
       <c r="AD38" t="n">
-        <v>2.47</v>
+        <v>2.19</v>
       </c>
       <c r="AE38" t="inlineStr">
         <is>
@@ -5380,10 +5380,10 @@
         </is>
       </c>
       <c r="AG38" t="n">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AH38" t="n">
-        <v>1.39</v>
+        <v>2.41</v>
       </c>
       <c r="AI38" t="n">
         <v>0</v>
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,13 +5442,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>1.35</v>
+        <v>4.3</v>
       </c>
       <c r="M39" t="n">
-        <v>5.3</v>
+        <v>4.4</v>
       </c>
       <c r="N39" t="n">
-        <v>7</v>
+        <v>1.64</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5481,16 +5481,16 @@
         <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.6</v>
+        <v>1.44</v>
       </c>
       <c r="Z39" t="n">
-        <v>2.35</v>
+        <v>2.75</v>
       </c>
       <c r="AA39" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB39" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC39" t="n">
         <v>0</v>
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,61 +5571,61 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>15</v>
+        <v>1.35</v>
       </c>
       <c r="M40" t="n">
-        <v>7.6</v>
+        <v>5.3</v>
       </c>
       <c r="N40" t="n">
-        <v>1.15</v>
+        <v>7</v>
       </c>
       <c r="O40" t="n">
-        <v>11</v>
+        <v>1.76</v>
       </c>
       <c r="P40" t="n">
-        <v>2.95</v>
+        <v>2.6</v>
       </c>
       <c r="Q40" t="n">
-        <v>1.44</v>
+        <v>7.4</v>
       </c>
       <c r="R40" t="n">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="S40" t="n">
-        <v>4.1</v>
+        <v>3.54</v>
       </c>
       <c r="T40" t="n">
-        <v>2.12</v>
+        <v>2.26</v>
       </c>
       <c r="U40" t="n">
-        <v>1.78</v>
+        <v>1.62</v>
       </c>
       <c r="V40" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W40" t="n">
-        <v>1.08</v>
+        <v>1.16</v>
       </c>
       <c r="X40" t="n">
-        <v>6.1</v>
+        <v>5</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="Z40" t="n">
-        <v>2.75</v>
+        <v>2.35</v>
       </c>
       <c r="AA40" t="n">
-        <v>1.95</v>
+        <v>2.42</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.79</v>
+        <v>1.6</v>
       </c>
       <c r="AC40" t="n">
-        <v>2.15</v>
+        <v>1.81</v>
       </c>
       <c r="AD40" t="n">
-        <v>1.58</v>
+        <v>1.91</v>
       </c>
       <c r="AE40" t="inlineStr">
         <is>
@@ -5638,10 +5638,10 @@
         </is>
       </c>
       <c r="AG40" t="n">
-        <v>1.09</v>
+        <v>1.17</v>
       </c>
       <c r="AH40" t="n">
-        <v>1.03</v>
+        <v>3.3</v>
       </c>
       <c r="AI40" t="n">
         <v>0</v>
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,43 +5700,43 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>4.3</v>
+        <v>15</v>
       </c>
       <c r="M41" t="n">
-        <v>4.4</v>
+        <v>7.6</v>
       </c>
       <c r="N41" t="n">
-        <v>1.64</v>
+        <v>1.15</v>
       </c>
       <c r="O41" t="n">
-        <v>4.45</v>
+        <v>11</v>
       </c>
       <c r="P41" t="n">
-        <v>2.6</v>
+        <v>2.9</v>
       </c>
       <c r="Q41" t="n">
-        <v>2.09</v>
+        <v>1.48</v>
       </c>
       <c r="R41" t="n">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="S41" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="T41" t="n">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="U41" t="n">
-        <v>1.72</v>
+        <v>1.69</v>
       </c>
       <c r="V41" t="n">
         <v>1.01</v>
       </c>
       <c r="W41" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X41" t="n">
-        <v>5.35</v>
+        <v>6.5</v>
       </c>
       <c r="Y41" t="n">
         <v>1.44</v>
@@ -5745,16 +5745,16 @@
         <v>2.75</v>
       </c>
       <c r="AA41" t="n">
-        <v>2.15</v>
+        <v>1.95</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.7</v>
+        <v>1.79</v>
       </c>
       <c r="AC41" t="n">
-        <v>1.49</v>
+        <v>2.19</v>
       </c>
       <c r="AD41" t="n">
-        <v>2.5</v>
+        <v>1.62</v>
       </c>
       <c r="AE41" t="inlineStr">
         <is>
@@ -5767,10 +5767,10 @@
         </is>
       </c>
       <c r="AG41" t="n">
-        <v>1.23</v>
+        <v>1.09</v>
       </c>
       <c r="AH41" t="n">
-        <v>1.23</v>
+        <v>1.03</v>
       </c>
       <c r="AI41" t="n">
         <v>0</v>
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Olympique Marseille</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,61 +5829,61 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>1.56</v>
+        <v>3</v>
       </c>
       <c r="M42" t="n">
-        <v>4.3</v>
+        <v>3.83</v>
       </c>
       <c r="N42" t="n">
-        <v>5.1</v>
+        <v>2.1</v>
       </c>
       <c r="O42" t="n">
-        <v>2.08</v>
+        <v>3.58</v>
       </c>
       <c r="P42" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="Q42" t="n">
-        <v>4.4</v>
+        <v>2.59</v>
       </c>
       <c r="R42" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="S42" t="n">
-        <v>3.32</v>
+        <v>3.45</v>
       </c>
       <c r="T42" t="n">
-        <v>2.46</v>
+        <v>2.25</v>
       </c>
       <c r="U42" t="n">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="V42" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W42" t="n">
         <v>1.18</v>
       </c>
       <c r="X42" t="n">
-        <v>4.55</v>
+        <v>4.75</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.63</v>
+        <v>1.58</v>
       </c>
       <c r="Z42" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="AA42" t="n">
         <v>2.25</v>
       </c>
-      <c r="AA42" t="n">
-        <v>2.4</v>
-      </c>
       <c r="AB42" t="n">
-        <v>1.52</v>
+        <v>1.65</v>
       </c>
       <c r="AC42" t="n">
-        <v>1.66</v>
+        <v>1.49</v>
       </c>
       <c r="AD42" t="n">
-        <v>2.16</v>
+        <v>2.47</v>
       </c>
       <c r="AE42" t="inlineStr">
         <is>
@@ -5896,10 +5896,10 @@
         </is>
       </c>
       <c r="AG42" t="n">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="AH42" t="n">
-        <v>2.39</v>
+        <v>1.39</v>
       </c>
       <c r="AI42" t="n">
         <v>0</v>
@@ -5970,7 +5970,7 @@
         <v>2.16</v>
       </c>
       <c r="P43" t="n">
-        <v>2.38</v>
+        <v>2.27</v>
       </c>
       <c r="Q43" t="n">
         <v>4.9</v>
@@ -6051,7 +6051,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6061,12 +6061,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6087,61 +6087,61 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>1.56</v>
+        <v>2.4</v>
       </c>
       <c r="M44" t="n">
-        <v>4.1</v>
+        <v>3.39</v>
       </c>
       <c r="N44" t="n">
-        <v>5.4</v>
+        <v>2.79</v>
       </c>
       <c r="O44" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="S44" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="T44" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="U44" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="V44" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="W44" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="X44" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.63</v>
+        <v>2.52</v>
       </c>
       <c r="Z44" t="n">
-        <v>2.25</v>
+        <v>1.52</v>
       </c>
       <c r="AA44" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AB44" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AC44" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AD44" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AE44" t="inlineStr">
         <is>
@@ -6154,10 +6154,10 @@
         </is>
       </c>
       <c r="AG44" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AH44" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AI44" t="n">
         <v>0</v>
@@ -6216,28 +6216,28 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="M45" t="n">
-        <v>4</v>
+        <v>4.7</v>
       </c>
       <c r="N45" t="n">
-        <v>4.7</v>
+        <v>4.91</v>
       </c>
       <c r="O45" t="n">
         <v>1.98</v>
       </c>
       <c r="P45" t="n">
-        <v>2.7</v>
+        <v>2.85</v>
       </c>
       <c r="Q45" t="n">
-        <v>4.6</v>
+        <v>4.35</v>
       </c>
       <c r="R45" t="n">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="S45" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="T45" t="n">
         <v>1.83</v>
@@ -6261,16 +6261,16 @@
         <v>3.1</v>
       </c>
       <c r="AA45" t="n">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AC45" t="n">
         <v>1.4</v>
       </c>
       <c r="AD45" t="n">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="AE45" t="inlineStr">
         <is>
@@ -6378,7 +6378,7 @@
         <v>1.03</v>
       </c>
       <c r="W46" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="X46" t="n">
         <v>3.4</v>
@@ -6390,16 +6390,16 @@
         <v>1.84</v>
       </c>
       <c r="AA46" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="AB46" t="n">
         <v>1.29</v>
       </c>
       <c r="AC46" t="n">
-        <v>2.06</v>
+        <v>2.14</v>
       </c>
       <c r="AD46" t="n">
-        <v>1.7</v>
+        <v>1.61</v>
       </c>
       <c r="AE46" t="inlineStr">
         <is>
@@ -6477,13 +6477,13 @@
         <v>2.05</v>
       </c>
       <c r="M47" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="N47" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="O47" t="n">
-        <v>2.67</v>
+        <v>2.66</v>
       </c>
       <c r="P47" t="n">
         <v>2</v>
@@ -6495,10 +6495,10 @@
         <v>1.51</v>
       </c>
       <c r="S47" t="n">
-        <v>2.39</v>
+        <v>2.42</v>
       </c>
       <c r="T47" t="n">
-        <v>3.34</v>
+        <v>3.3</v>
       </c>
       <c r="U47" t="n">
         <v>1.28</v>
@@ -6507,25 +6507,25 @@
         <v>1.05</v>
       </c>
       <c r="W47" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="X47" t="n">
-        <v>2.53</v>
+        <v>2.95</v>
       </c>
       <c r="Y47" t="n">
-        <v>2.38</v>
+        <v>2.49</v>
       </c>
       <c r="Z47" t="n">
-        <v>1.65</v>
+        <v>1.56</v>
       </c>
       <c r="AA47" t="n">
         <v>4.73</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="AC47" t="n">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="AD47" t="n">
         <v>1.71</v>
@@ -6541,10 +6541,10 @@
         </is>
       </c>
       <c r="AG47" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AH47" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="AI47" t="n">
         <v>0</v>

--- a/jogos_2025-09-30.xlsx
+++ b/jogos_2025-09-30.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK47"/>
+  <dimension ref="A1:AK48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -757,27 +757,27 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Kariobangi Sharks</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>KCB</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -798,13 +798,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -837,10 +837,10 @@
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AA3" t="n">
         <v>0</v>
@@ -877,7 +877,7 @@
         <v>0</v>
       </c>
       <c r="AK3" s="3" t="n">
-        <v>45930.41666666666</v>
+        <v>45930.45833333334</v>
       </c>
     </row>
     <row r="4">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Sogdiana</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -927,13 +927,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>3.35</v>
+        <v>2.95</v>
       </c>
       <c r="M4" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="N4" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -966,10 +966,10 @@
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.25</v>
+        <v>2.08</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AA4" t="n">
         <v>0</v>
@@ -1015,27 +1015,27 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Sogdiana</t>
+          <t>Botev Plovdiv</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1056,61 +1056,61 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.95</v>
+        <v>4.6</v>
       </c>
       <c r="M5" t="n">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="N5" t="n">
-        <v>2.4</v>
+        <v>1.82</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>5.84</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.08</v>
+        <v>2.25</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
@@ -1123,19 +1123,19 @@
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AK5" s="3" t="n">
-        <v>45930.45833333334</v>
+        <v>45930.47916666666</v>
       </c>
     </row>
     <row r="6">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Botev Plovdiv</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1185,61 +1185,61 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>4.6</v>
+        <v>1.86</v>
       </c>
       <c r="M6" t="n">
-        <v>3.5</v>
+        <v>3.84</v>
       </c>
       <c r="N6" t="n">
-        <v>1.82</v>
+        <v>3.7</v>
       </c>
       <c r="O6" t="n">
-        <v>5.84</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>2.25</v>
+        <v>1.7</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.65</v>
+        <v>2.15</v>
       </c>
       <c r="AA6" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
@@ -1252,19 +1252,19 @@
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AI6" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AK6" s="3" t="n">
-        <v>45930.47916666666</v>
+        <v>45930.57291666666</v>
       </c>
     </row>
     <row r="7">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Police</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ulinzi Stars</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1314,61 +1314,61 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>8.9</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>6.55</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
@@ -1381,10 +1381,10 @@
         </is>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AI7" t="n">
         <v>0</v>
@@ -1393,7 +1393,7 @@
         <v>0</v>
       </c>
       <c r="AK7" s="3" t="n">
-        <v>45930.5</v>
+        <v>45930.57291666666</v>
       </c>
     </row>
     <row r="8">
@@ -1402,12 +1402,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Havelse</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Waldhof Mannheim</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,61 +1443,61 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>19</v>
+        <v>3.4</v>
       </c>
       <c r="M8" t="n">
-        <v>8.9</v>
+        <v>3.75</v>
       </c>
       <c r="N8" t="n">
-        <v>1.11</v>
+        <v>1.92</v>
       </c>
       <c r="O8" t="n">
-        <v>13.5</v>
+        <v>3.7</v>
       </c>
       <c r="P8" t="n">
-        <v>3.76</v>
+        <v>2.4</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.42</v>
+        <v>2.35</v>
       </c>
       <c r="R8" t="n">
-        <v>1.18</v>
+        <v>1.3</v>
       </c>
       <c r="S8" t="n">
-        <v>4.25</v>
+        <v>3.2</v>
       </c>
       <c r="T8" t="n">
-        <v>2.01</v>
+        <v>2.23</v>
       </c>
       <c r="U8" t="n">
-        <v>1.84</v>
+        <v>1.56</v>
       </c>
       <c r="V8" t="n">
         <v>1.01</v>
       </c>
       <c r="W8" t="n">
-        <v>1.06</v>
+        <v>1.16</v>
       </c>
       <c r="X8" t="n">
-        <v>6.55</v>
+        <v>4.25</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.3</v>
+        <v>1.57</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.4</v>
+        <v>2.16</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.8</v>
+        <v>2.45</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.94</v>
+        <v>1.45</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.21</v>
+        <v>1.5</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.61</v>
+        <v>2.17</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>1.08</v>
+        <v>1.2</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.01</v>
+        <v>1.26</v>
       </c>
       <c r="AI8" t="n">
         <v>0</v>
@@ -1522,7 +1522,7 @@
         <v>0</v>
       </c>
       <c r="AK8" s="3" t="n">
-        <v>45930.57291666666</v>
+        <v>45930.58333333334</v>
       </c>
     </row>
     <row r="9">
@@ -1531,12 +1531,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Hansa Rostock</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,61 +1572,61 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="M9" t="n">
-        <v>3.84</v>
+        <v>3.8</v>
       </c>
       <c r="N9" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.7</v>
+        <v>1.61</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
@@ -1651,7 +1651,7 @@
         <v>0</v>
       </c>
       <c r="AK9" s="3" t="n">
-        <v>45930.57291666666</v>
+        <v>45930.58333333334</v>
       </c>
     </row>
     <row r="10">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Saarbrucken</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>MSV Duisburg</t>
+          <t>Wehen Wiesbaden</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,22 +1701,22 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.87</v>
+        <v>2.9</v>
       </c>
       <c r="M10" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="N10" t="n">
-        <v>3.55</v>
+        <v>2.18</v>
       </c>
       <c r="O10" t="n">
-        <v>2.51</v>
+        <v>3.25</v>
       </c>
       <c r="P10" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.98</v>
+        <v>2.6</v>
       </c>
       <c r="R10" t="n">
         <v>1.29</v>
@@ -1725,37 +1725,37 @@
         <v>3.26</v>
       </c>
       <c r="T10" t="n">
-        <v>2.36</v>
+        <v>2.16</v>
       </c>
       <c r="U10" t="n">
-        <v>1.52</v>
+        <v>1.6</v>
       </c>
       <c r="V10" t="n">
         <v>1.02</v>
       </c>
       <c r="W10" t="n">
-        <v>1.19</v>
+        <v>1.14</v>
       </c>
       <c r="X10" t="n">
-        <v>4.45</v>
+        <v>4.4</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.59</v>
+        <v>1.53</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.22</v>
+        <v>2.25</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.42</v>
+        <v>2.33</v>
       </c>
       <c r="AB10" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AC10" t="n">
         <v>1.44</v>
       </c>
-      <c r="AC10" t="n">
-        <v>1.51</v>
-      </c>
       <c r="AD10" t="n">
-        <v>2.36</v>
+        <v>2.33</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -1768,10 +1768,10 @@
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>1.24</v>
+        <v>1.6</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.74</v>
+        <v>1.33</v>
       </c>
       <c r="AI10" t="n">
         <v>0</v>
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Wehen Wiesbaden</t>
+          <t>Erzgebirge Aue</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,61 +1830,61 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.9</v>
+        <v>2.03</v>
       </c>
       <c r="M11" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="N11" t="n">
-        <v>2.18</v>
+        <v>3.3</v>
       </c>
       <c r="O11" t="n">
-        <v>3.25</v>
+        <v>2.55</v>
       </c>
       <c r="P11" t="n">
-        <v>2.4</v>
+        <v>2.28</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.6</v>
+        <v>3.55</v>
       </c>
       <c r="R11" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="S11" t="n">
-        <v>3.26</v>
+        <v>3.1</v>
       </c>
       <c r="T11" t="n">
-        <v>2.16</v>
+        <v>2.43</v>
       </c>
       <c r="U11" t="n">
-        <v>1.6</v>
+        <v>1.48</v>
       </c>
       <c r="V11" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="W11" t="n">
-        <v>1.14</v>
+        <v>1.21</v>
       </c>
       <c r="X11" t="n">
-        <v>4.4</v>
+        <v>3.7</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.53</v>
+        <v>1.71</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.25</v>
+        <v>1.94</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.33</v>
+        <v>2.8</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.49</v>
+        <v>1.35</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.44</v>
+        <v>1.58</v>
       </c>
       <c r="AD11" t="n">
-        <v>2.33</v>
+        <v>2.02</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -1897,10 +1897,10 @@
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>1.6</v>
+        <v>1.24</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.33</v>
+        <v>1.68</v>
       </c>
       <c r="AI11" t="n">
         <v>0</v>
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Hansa Rostock</t>
+          <t>Saarbrucken</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>MSV Duisburg</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,61 +1959,61 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.8</v>
+        <v>1.87</v>
       </c>
       <c r="M12" t="n">
         <v>3.8</v>
       </c>
       <c r="N12" t="n">
-        <v>3.8</v>
+        <v>3.55</v>
       </c>
       <c r="O12" t="n">
-        <v>2.28</v>
+        <v>2.51</v>
       </c>
       <c r="P12" t="n">
-        <v>2.38</v>
+        <v>2.2</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.95</v>
+        <v>3.98</v>
       </c>
       <c r="R12" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="S12" t="n">
-        <v>3.2</v>
+        <v>3.26</v>
       </c>
       <c r="T12" t="n">
-        <v>2.28</v>
+        <v>2.36</v>
       </c>
       <c r="U12" t="n">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="V12" t="n">
         <v>1.02</v>
       </c>
       <c r="W12" t="n">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="X12" t="n">
-        <v>4</v>
+        <v>4.45</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.1</v>
+        <v>2.22</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.55</v>
+        <v>2.42</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.57</v>
+        <v>1.51</v>
       </c>
       <c r="AD12" t="n">
-        <v>2.07</v>
+        <v>2.36</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -2026,10 +2026,10 @@
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.85</v>
+        <v>1.74</v>
       </c>
       <c r="AI12" t="n">
         <v>0</v>
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,61 +2088,61 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.26</v>
+        <v>1.53</v>
       </c>
       <c r="M13" t="n">
-        <v>5.1</v>
+        <v>4.4</v>
       </c>
       <c r="N13" t="n">
-        <v>7.6</v>
+        <v>5</v>
       </c>
       <c r="O13" t="n">
-        <v>1.83</v>
+        <v>1.95</v>
       </c>
       <c r="P13" t="n">
         <v>2.5</v>
       </c>
       <c r="Q13" t="n">
-        <v>6.89</v>
+        <v>4.95</v>
       </c>
       <c r="R13" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="S13" t="n">
-        <v>3.6</v>
+        <v>3.66</v>
       </c>
       <c r="T13" t="n">
-        <v>2.2</v>
+        <v>1.98</v>
       </c>
       <c r="U13" t="n">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="V13" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W13" t="n">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="X13" t="n">
-        <v>4.77</v>
+        <v>5.6</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.47</v>
+        <v>1.42</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.17</v>
+        <v>2.25</v>
       </c>
       <c r="AB13" t="n">
         <v>1.62</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.73</v>
+        <v>1.5</v>
       </c>
       <c r="AD13" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
@@ -2155,10 +2155,10 @@
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>1.1</v>
+        <v>1.19</v>
       </c>
       <c r="AH13" t="n">
-        <v>2.75</v>
+        <v>2.4</v>
       </c>
       <c r="AI13" t="n">
         <v>0</v>
@@ -2181,22 +2181,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Erzgebirge Aue</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,61 +2217,61 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.03</v>
+        <v>1.4</v>
       </c>
       <c r="M14" t="n">
-        <v>3.5</v>
+        <v>4.8</v>
       </c>
       <c r="N14" t="n">
-        <v>3.3</v>
+        <v>6.8</v>
       </c>
       <c r="O14" t="n">
-        <v>2.55</v>
+        <v>1.83</v>
       </c>
       <c r="P14" t="n">
-        <v>2.28</v>
+        <v>2.45</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.55</v>
+        <v>5.7</v>
       </c>
       <c r="R14" t="n">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="S14" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="T14" t="n">
-        <v>2.43</v>
+        <v>2.2</v>
       </c>
       <c r="U14" t="n">
-        <v>1.48</v>
+        <v>1.62</v>
       </c>
       <c r="V14" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="W14" t="n">
-        <v>1.21</v>
+        <v>1.14</v>
       </c>
       <c r="X14" t="n">
-        <v>3.7</v>
+        <v>5</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.71</v>
+        <v>1.53</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.94</v>
+        <v>2.4</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.8</v>
+        <v>2.45</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.35</v>
+        <v>1.54</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.58</v>
+        <v>1.73</v>
       </c>
       <c r="AD14" t="n">
-        <v>2.02</v>
+        <v>1.95</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
@@ -2284,10 +2284,10 @@
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>1.24</v>
+        <v>1.17</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.68</v>
+        <v>2.75</v>
       </c>
       <c r="AI14" t="n">
         <v>0</v>
@@ -2305,27 +2305,27 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,61 +2346,61 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.56</v>
+        <v>1.79</v>
       </c>
       <c r="M15" t="n">
-        <v>4.2</v>
+        <v>3.95</v>
       </c>
       <c r="N15" t="n">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="O15" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="P15" t="n">
-        <v>2.53</v>
+        <v>2.3</v>
       </c>
       <c r="Q15" t="n">
-        <v>4.75</v>
+        <v>4.62</v>
       </c>
       <c r="R15" t="n">
-        <v>1.21</v>
+        <v>1.29</v>
       </c>
       <c r="S15" t="n">
-        <v>3.75</v>
+        <v>3.28</v>
       </c>
       <c r="T15" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="X15" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="Z15" t="n">
         <v>2.14</v>
       </c>
-      <c r="U15" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="V15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="X15" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>2.5</v>
-      </c>
       <c r="AA15" t="n">
-        <v>1.92</v>
+        <v>2.6</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.78</v>
+        <v>1.39</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.53</v>
+        <v>1.64</v>
       </c>
       <c r="AD15" t="n">
-        <v>2.37</v>
+        <v>2.15</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
@@ -2413,10 +2413,10 @@
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>1.16</v>
+        <v>1.24</v>
       </c>
       <c r="AH15" t="n">
-        <v>2.38</v>
+        <v>2.08</v>
       </c>
       <c r="AI15" t="n">
         <v>0</v>
@@ -2425,7 +2425,7 @@
         <v>0</v>
       </c>
       <c r="AK15" s="3" t="n">
-        <v>45930.58333333334</v>
+        <v>45930.625</v>
       </c>
     </row>
     <row r="16">
@@ -2434,12 +2434,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Havelse</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Waldhof Mannheim</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,61 +2475,61 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>3.4</v>
+        <v>2.16</v>
       </c>
       <c r="M16" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="N16" t="n">
-        <v>1.92</v>
+        <v>2.97</v>
       </c>
       <c r="O16" t="n">
-        <v>3.7</v>
+        <v>2.58</v>
       </c>
       <c r="P16" t="n">
         <v>2.4</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.35</v>
+        <v>3.43</v>
       </c>
       <c r="R16" t="n">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="S16" t="n">
-        <v>3.2</v>
+        <v>3.58</v>
       </c>
       <c r="T16" t="n">
-        <v>2.23</v>
+        <v>2.21</v>
       </c>
       <c r="U16" t="n">
-        <v>1.56</v>
+        <v>1.61</v>
       </c>
       <c r="V16" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W16" t="n">
-        <v>1.16</v>
+        <v>1.12</v>
       </c>
       <c r="X16" t="n">
-        <v>4.25</v>
+        <v>4.75</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="Z16" t="n">
-        <v>2.16</v>
+        <v>2.39</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.45</v>
+        <v>2.28</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.45</v>
+        <v>1.6</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AD16" t="n">
-        <v>2.17</v>
+        <v>2.59</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
@@ -2542,10 +2542,10 @@
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.26</v>
+        <v>1.68</v>
       </c>
       <c r="AI16" t="n">
         <v>0</v>
@@ -2554,7 +2554,7 @@
         <v>0</v>
       </c>
       <c r="AK16" s="3" t="n">
-        <v>45930.58333333334</v>
+        <v>45930.625</v>
       </c>
     </row>
     <row r="17">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,61 +2862,61 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.16</v>
+        <v>2.87</v>
       </c>
       <c r="M19" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="N19" t="n">
-        <v>2.97</v>
+        <v>2.3</v>
       </c>
       <c r="O19" t="n">
-        <v>2.58</v>
+        <v>3.5</v>
       </c>
       <c r="P19" t="n">
-        <v>2.4</v>
+        <v>2.28</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.43</v>
+        <v>2.64</v>
       </c>
       <c r="R19" t="n">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="S19" t="n">
-        <v>3.58</v>
+        <v>3.4</v>
       </c>
       <c r="T19" t="n">
-        <v>2.21</v>
+        <v>2.32</v>
       </c>
       <c r="U19" t="n">
-        <v>1.61</v>
+        <v>1.54</v>
       </c>
       <c r="V19" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="W19" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="X19" t="n">
-        <v>4.75</v>
+        <v>4.85</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.55</v>
+        <v>1.59</v>
       </c>
       <c r="Z19" t="n">
-        <v>2.39</v>
+        <v>2.36</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.28</v>
+        <v>2.36</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AD19" t="n">
-        <v>2.59</v>
+        <v>2.41</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
@@ -2929,10 +2929,10 @@
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.68</v>
+        <v>1.36</v>
       </c>
       <c r="AI19" t="n">
         <v>0</v>
@@ -2950,12 +2950,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,61 +2991,61 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.87</v>
+        <v>2.62</v>
       </c>
       <c r="M20" t="n">
-        <v>3.5</v>
+        <v>3.24</v>
       </c>
       <c r="N20" t="n">
-        <v>2.3</v>
+        <v>2.6</v>
       </c>
       <c r="O20" t="n">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="P20" t="n">
-        <v>2.28</v>
+        <v>2.02</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.64</v>
+        <v>3.35</v>
       </c>
       <c r="R20" t="n">
-        <v>1.27</v>
+        <v>1.44</v>
       </c>
       <c r="S20" t="n">
-        <v>3.4</v>
+        <v>2.51</v>
       </c>
       <c r="T20" t="n">
-        <v>2.32</v>
+        <v>3.08</v>
       </c>
       <c r="U20" t="n">
-        <v>1.54</v>
+        <v>1.3</v>
       </c>
       <c r="V20" t="n">
         <v>1.03</v>
       </c>
       <c r="W20" t="n">
-        <v>1.14</v>
+        <v>1.35</v>
       </c>
       <c r="X20" t="n">
-        <v>4.85</v>
+        <v>2.78</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.59</v>
+        <v>2.2</v>
       </c>
       <c r="Z20" t="n">
-        <v>2.36</v>
+        <v>1.66</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.36</v>
+        <v>3.9</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.56</v>
+        <v>1.19</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.5</v>
+        <v>1.87</v>
       </c>
       <c r="AD20" t="n">
-        <v>2.41</v>
+        <v>1.85</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
@@ -3058,10 +3058,10 @@
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>1.26</v>
+        <v>1.35</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.36</v>
+        <v>1.49</v>
       </c>
       <c r="AI20" t="n">
         <v>0</v>
@@ -3070,7 +3070,7 @@
         <v>0</v>
       </c>
       <c r="AK20" s="3" t="n">
-        <v>45930.625</v>
+        <v>45930.64583333334</v>
       </c>
     </row>
     <row r="21">
@@ -3079,12 +3079,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,61 +3120,61 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.79</v>
+        <v>2.11</v>
       </c>
       <c r="M21" t="n">
-        <v>3.95</v>
+        <v>3.4</v>
       </c>
       <c r="N21" t="n">
-        <v>3.9</v>
+        <v>3.45</v>
       </c>
       <c r="O21" t="n">
-        <v>2.25</v>
+        <v>2.68</v>
       </c>
       <c r="P21" t="n">
-        <v>2.3</v>
+        <v>2.17</v>
       </c>
       <c r="Q21" t="n">
-        <v>4.62</v>
+        <v>3.92</v>
       </c>
       <c r="R21" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="S21" t="n">
-        <v>3.28</v>
+        <v>2.98</v>
       </c>
       <c r="T21" t="n">
-        <v>2.44</v>
+        <v>2.6</v>
       </c>
       <c r="U21" t="n">
-        <v>1.49</v>
+        <v>1.41</v>
       </c>
       <c r="V21" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="W21" t="n">
-        <v>1.16</v>
+        <v>1.21</v>
       </c>
       <c r="X21" t="n">
-        <v>4.15</v>
+        <v>3.74</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.68</v>
+        <v>1.77</v>
       </c>
       <c r="Z21" t="n">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.6</v>
+        <v>2.92</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.39</v>
+        <v>1.33</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="AD21" t="n">
-        <v>2.15</v>
+        <v>2.13</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
@@ -3187,10 +3187,10 @@
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="AH21" t="n">
-        <v>2.08</v>
+        <v>1.74</v>
       </c>
       <c r="AI21" t="n">
         <v>0</v>
@@ -3199,7 +3199,7 @@
         <v>0</v>
       </c>
       <c r="AK21" s="3" t="n">
-        <v>45930.625</v>
+        <v>45930.64583333334</v>
       </c>
     </row>
     <row r="22">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Calcio Padova</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Mantova</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,61 +3249,61 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.18</v>
+        <v>1.88</v>
       </c>
       <c r="M22" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="N22" t="n">
+        <v>4.08</v>
+      </c>
+      <c r="O22" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="P22" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S22" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V22" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="X22" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AA22" t="n">
         <v>3.32</v>
       </c>
-      <c r="N22" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="O22" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="P22" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>4.24</v>
-      </c>
-      <c r="R22" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S22" t="n">
-        <v>2.51</v>
-      </c>
-      <c r="T22" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="U22" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="V22" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W22" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="X22" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>4.2</v>
-      </c>
       <c r="AB22" t="n">
-        <v>1.19</v>
+        <v>1.26</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.92</v>
+        <v>1.84</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.8</v>
+        <v>1.88</v>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
@@ -3316,10 +3316,10 @@
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.69</v>
+        <v>1.94</v>
       </c>
       <c r="AI22" t="n">
         <v>0</v>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mantova</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,77 +3507,77 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.88</v>
+        <v>3.81</v>
       </c>
       <c r="M24" t="n">
-        <v>3.65</v>
+        <v>3.45</v>
       </c>
       <c r="N24" t="n">
-        <v>4.08</v>
+        <v>1.81</v>
       </c>
       <c r="O24" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="P24" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Q24" t="n">
         <v>2.45</v>
       </c>
-      <c r="P24" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>4.7</v>
-      </c>
       <c r="R24" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="S24" t="n">
-        <v>2.71</v>
+        <v>2.98</v>
       </c>
       <c r="T24" t="n">
-        <v>2.79</v>
+        <v>2.74</v>
       </c>
       <c r="U24" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="V24" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="W24" t="n">
-        <v>1.29</v>
+        <v>1.21</v>
       </c>
       <c r="X24" t="n">
-        <v>3.12</v>
+        <v>3.66</v>
       </c>
       <c r="Y24" t="n">
-        <v>2.01</v>
+        <v>1.71</v>
       </c>
       <c r="Z24" t="n">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="AA24" t="n">
-        <v>3.32</v>
+        <v>2.92</v>
       </c>
       <c r="AB24" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AE24" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF24" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG24" t="n">
         <v>1.26</v>
       </c>
-      <c r="AC24" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AE24" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF24" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG24" t="n">
-        <v>1.23</v>
-      </c>
       <c r="AH24" t="n">
-        <v>1.94</v>
+        <v>1.24</v>
       </c>
       <c r="AI24" t="n">
         <v>0</v>
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Calcio Padova</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,77 +3636,77 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.05</v>
+        <v>2.18</v>
       </c>
       <c r="M25" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="N25" t="n">
         <v>3.4</v>
       </c>
-      <c r="N25" t="n">
-        <v>3.5</v>
-      </c>
       <c r="O25" t="n">
-        <v>2.81</v>
+        <v>2.8</v>
       </c>
       <c r="P25" t="n">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="Q25" t="n">
-        <v>4.19</v>
+        <v>4.24</v>
       </c>
       <c r="R25" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="S25" t="n">
-        <v>2.57</v>
+        <v>2.51</v>
       </c>
       <c r="T25" t="n">
-        <v>3</v>
+        <v>3.08</v>
       </c>
       <c r="U25" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="V25" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="W25" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="X25" t="n">
-        <v>2.88</v>
+        <v>2.78</v>
       </c>
       <c r="Y25" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="Z25" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AE25" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF25" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG25" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AH25" t="n">
         <v>1.69</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>3.82</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AE25" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF25" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG25" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>1.7</v>
       </c>
       <c r="AI25" t="n">
         <v>0</v>
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,61 +3765,61 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.11</v>
+        <v>2.05</v>
       </c>
       <c r="M26" t="n">
         <v>3.4</v>
       </c>
       <c r="N26" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="O26" t="n">
-        <v>2.68</v>
+        <v>2.81</v>
       </c>
       <c r="P26" t="n">
-        <v>2.17</v>
+        <v>2.04</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.92</v>
+        <v>4.19</v>
       </c>
       <c r="R26" t="n">
-        <v>1.32</v>
+        <v>1.42</v>
       </c>
       <c r="S26" t="n">
-        <v>2.98</v>
+        <v>2.57</v>
       </c>
       <c r="T26" t="n">
-        <v>2.6</v>
+        <v>3</v>
       </c>
       <c r="U26" t="n">
-        <v>1.41</v>
+        <v>1.31</v>
       </c>
       <c r="V26" t="n">
         <v>1.02</v>
       </c>
       <c r="W26" t="n">
-        <v>1.21</v>
+        <v>1.34</v>
       </c>
       <c r="X26" t="n">
-        <v>3.74</v>
+        <v>2.88</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.77</v>
+        <v>2.2</v>
       </c>
       <c r="Z26" t="n">
-        <v>2</v>
+        <v>1.69</v>
       </c>
       <c r="AA26" t="n">
-        <v>2.92</v>
+        <v>3.82</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.65</v>
+        <v>1.87</v>
       </c>
       <c r="AD26" t="n">
-        <v>2.13</v>
+        <v>1.85</v>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
@@ -3832,10 +3832,10 @@
         </is>
       </c>
       <c r="AG26" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.74</v>
+        <v>1.7</v>
       </c>
       <c r="AI26" t="n">
         <v>0</v>
@@ -3853,12 +3853,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,61 +3894,61 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.62</v>
+        <v>1.45</v>
       </c>
       <c r="M27" t="n">
-        <v>3.24</v>
+        <v>4.4</v>
       </c>
       <c r="N27" t="n">
-        <v>2.6</v>
+        <v>6.4</v>
       </c>
       <c r="O27" t="n">
-        <v>3.25</v>
+        <v>1.93</v>
       </c>
       <c r="P27" t="n">
-        <v>2.02</v>
+        <v>2.45</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.35</v>
+        <v>5.5</v>
       </c>
       <c r="R27" t="n">
-        <v>1.44</v>
+        <v>1.28</v>
       </c>
       <c r="S27" t="n">
-        <v>2.51</v>
+        <v>3.2</v>
       </c>
       <c r="T27" t="n">
-        <v>3.08</v>
+        <v>2.42</v>
       </c>
       <c r="U27" t="n">
-        <v>1.3</v>
+        <v>1.47</v>
       </c>
       <c r="V27" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="W27" t="n">
-        <v>1.35</v>
+        <v>1.17</v>
       </c>
       <c r="X27" t="n">
-        <v>2.78</v>
+        <v>4.2</v>
       </c>
       <c r="Y27" t="n">
-        <v>2.2</v>
+        <v>1.65</v>
       </c>
       <c r="Z27" t="n">
-        <v>1.66</v>
+        <v>2.1</v>
       </c>
       <c r="AA27" t="n">
-        <v>3.9</v>
+        <v>2.63</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.19</v>
+        <v>1.4</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.87</v>
+        <v>1.81</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
@@ -3961,10 +3961,10 @@
         </is>
       </c>
       <c r="AG27" t="n">
-        <v>1.35</v>
+        <v>1.11</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.49</v>
+        <v>2.45</v>
       </c>
       <c r="AI27" t="n">
         <v>0</v>
@@ -3973,7 +3973,7 @@
         <v>0</v>
       </c>
       <c r="AK27" s="3" t="n">
-        <v>45930.64583333334</v>
+        <v>45930.65625</v>
       </c>
     </row>
     <row r="28">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,61 +4023,61 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.9</v>
+        <v>2.36</v>
       </c>
       <c r="M28" t="n">
-        <v>3.4</v>
+        <v>3.38</v>
       </c>
       <c r="N28" t="n">
-        <v>4</v>
+        <v>2.86</v>
       </c>
       <c r="O28" t="n">
-        <v>2.45</v>
+        <v>2.73</v>
       </c>
       <c r="P28" t="n">
-        <v>2.13</v>
+        <v>2.27</v>
       </c>
       <c r="Q28" t="n">
-        <v>4.2</v>
+        <v>3.6</v>
       </c>
       <c r="R28" t="n">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="S28" t="n">
-        <v>2.78</v>
+        <v>3.14</v>
       </c>
       <c r="T28" t="n">
-        <v>2.84</v>
+        <v>2.4</v>
       </c>
       <c r="U28" t="n">
-        <v>1.35</v>
+        <v>1.48</v>
       </c>
       <c r="V28" t="n">
         <v>1.01</v>
       </c>
       <c r="W28" t="n">
-        <v>1.27</v>
+        <v>1.18</v>
       </c>
       <c r="X28" t="n">
-        <v>3.25</v>
+        <v>4.05</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.98</v>
+        <v>1.89</v>
       </c>
       <c r="Z28" t="n">
-        <v>1.77</v>
+        <v>1.85</v>
       </c>
       <c r="AA28" t="n">
-        <v>3.4</v>
+        <v>2.56</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.25</v>
+        <v>1.42</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.82</v>
+        <v>1.56</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
@@ -4093,7 +4093,7 @@
         <v>1.28</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="AI28" t="n">
         <v>0</v>
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,61 +4410,61 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.65</v>
+        <v>3.2</v>
       </c>
       <c r="M31" t="n">
-        <v>3.82</v>
+        <v>3.3</v>
       </c>
       <c r="N31" t="n">
-        <v>4.9</v>
+        <v>2.2</v>
       </c>
       <c r="O31" t="n">
+        <v>3.81</v>
+      </c>
+      <c r="P31" t="n">
         <v>2.15</v>
       </c>
-      <c r="P31" t="n">
-        <v>2.38</v>
-      </c>
       <c r="Q31" t="n">
-        <v>5.03</v>
+        <v>2.8</v>
       </c>
       <c r="R31" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="S31" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="V31" t="n">
+        <v>1</v>
+      </c>
+      <c r="W31" t="n">
         <v>1.28</v>
       </c>
-      <c r="S31" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="T31" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="U31" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="V31" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W31" t="n">
-        <v>1.18</v>
-      </c>
       <c r="X31" t="n">
-        <v>4.1</v>
+        <v>3.48</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="Z31" t="n">
-        <v>1.91</v>
+        <v>1.98</v>
       </c>
       <c r="AA31" t="n">
-        <v>2.62</v>
+        <v>3.08</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="AD31" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="AE31" t="inlineStr">
         <is>
@@ -4477,10 +4477,10 @@
         </is>
       </c>
       <c r="AG31" t="n">
-        <v>1.17</v>
+        <v>1.3</v>
       </c>
       <c r="AH31" t="n">
-        <v>2.3</v>
+        <v>1.36</v>
       </c>
       <c r="AI31" t="n">
         <v>0</v>
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,61 +4539,61 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.36</v>
+        <v>1.65</v>
       </c>
       <c r="M32" t="n">
-        <v>4.75</v>
+        <v>3.82</v>
       </c>
       <c r="N32" t="n">
-        <v>8</v>
+        <v>4.9</v>
       </c>
       <c r="O32" t="n">
-        <v>1.77</v>
+        <v>2.15</v>
       </c>
       <c r="P32" t="n">
-        <v>2.48</v>
+        <v>2.38</v>
       </c>
       <c r="Q32" t="n">
-        <v>7</v>
+        <v>5.03</v>
       </c>
       <c r="R32" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="S32" t="n">
-        <v>3.08</v>
+        <v>3.2</v>
       </c>
       <c r="T32" t="n">
-        <v>2.5</v>
+        <v>2.42</v>
       </c>
       <c r="U32" t="n">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="V32" t="n">
         <v>1.01</v>
       </c>
       <c r="W32" t="n">
-        <v>1.23</v>
+        <v>1.18</v>
       </c>
       <c r="X32" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="Z32" t="n">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="AA32" t="n">
-        <v>3</v>
+        <v>2.62</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AC32" t="n">
-        <v>2.09</v>
+        <v>1.7</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.68</v>
+        <v>2.05</v>
       </c>
       <c r="AE32" t="inlineStr">
         <is>
@@ -4606,10 +4606,10 @@
         </is>
       </c>
       <c r="AG32" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AH32" t="n">
-        <v>3.38</v>
+        <v>2.3</v>
       </c>
       <c r="AI32" t="n">
         <v>0</v>
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,62 +4668,62 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.36</v>
+        <v>2.49</v>
       </c>
       <c r="M33" t="n">
-        <v>3.38</v>
+        <v>3.29</v>
       </c>
       <c r="N33" t="n">
-        <v>2.86</v>
+        <v>2.74</v>
       </c>
       <c r="O33" t="n">
-        <v>2.73</v>
+        <v>3.18</v>
       </c>
       <c r="P33" t="n">
-        <v>2.27</v>
+        <v>2.02</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.6</v>
+        <v>3.54</v>
       </c>
       <c r="R33" t="n">
-        <v>1.29</v>
+        <v>1.43</v>
       </c>
       <c r="S33" t="n">
-        <v>3.14</v>
+        <v>2.54</v>
       </c>
       <c r="T33" t="n">
-        <v>2.4</v>
+        <v>3.08</v>
       </c>
       <c r="U33" t="n">
-        <v>1.48</v>
+        <v>1.3</v>
       </c>
       <c r="V33" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W33" t="n">
-        <v>1.18</v>
+        <v>1.35</v>
       </c>
       <c r="X33" t="n">
-        <v>4.05</v>
+        <v>2.95</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.89</v>
+        <v>2.2</v>
       </c>
       <c r="Z33" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AD33" t="n">
         <v>1.85</v>
       </c>
-      <c r="AA33" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="AB33" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AC33" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AD33" t="n">
-        <v>2.3</v>
-      </c>
       <c r="AE33" t="inlineStr">
         <is>
           <t>[]</t>
@@ -4735,10 +4735,10 @@
         </is>
       </c>
       <c r="AG33" t="n">
-        <v>1.28</v>
+        <v>1.34</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.67</v>
+        <v>1.52</v>
       </c>
       <c r="AI33" t="n">
         <v>0</v>
@@ -4761,7 +4761,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,61 +4797,61 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.45</v>
+        <v>1.36</v>
       </c>
       <c r="M34" t="n">
-        <v>4.4</v>
+        <v>4.75</v>
       </c>
       <c r="N34" t="n">
-        <v>6.4</v>
+        <v>8</v>
       </c>
       <c r="O34" t="n">
-        <v>1.93</v>
+        <v>1.77</v>
       </c>
       <c r="P34" t="n">
-        <v>2.45</v>
+        <v>2.48</v>
       </c>
       <c r="Q34" t="n">
-        <v>5.5</v>
+        <v>7</v>
       </c>
       <c r="R34" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="S34" t="n">
-        <v>3.2</v>
+        <v>3.08</v>
       </c>
       <c r="T34" t="n">
-        <v>2.42</v>
+        <v>2.5</v>
       </c>
       <c r="U34" t="n">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="V34" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W34" t="n">
-        <v>1.17</v>
+        <v>1.23</v>
       </c>
       <c r="X34" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.65</v>
+        <v>1.85</v>
       </c>
       <c r="Z34" t="n">
-        <v>2.1</v>
+        <v>1.89</v>
       </c>
       <c r="AA34" t="n">
-        <v>2.63</v>
+        <v>3</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AC34" t="n">
-        <v>1.81</v>
+        <v>2.09</v>
       </c>
       <c r="AD34" t="n">
-        <v>1.91</v>
+        <v>1.68</v>
       </c>
       <c r="AE34" t="inlineStr">
         <is>
@@ -4864,10 +4864,10 @@
         </is>
       </c>
       <c r="AG34" t="n">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="AH34" t="n">
-        <v>2.45</v>
+        <v>3.38</v>
       </c>
       <c r="AI34" t="n">
         <v>0</v>
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,77 +4926,77 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>3.2</v>
+        <v>1.9</v>
       </c>
       <c r="M35" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="N35" t="n">
-        <v>2.2</v>
+        <v>4</v>
       </c>
       <c r="O35" t="n">
-        <v>3.81</v>
+        <v>2.45</v>
       </c>
       <c r="P35" t="n">
-        <v>2.15</v>
+        <v>2.13</v>
       </c>
       <c r="Q35" t="n">
-        <v>2.8</v>
+        <v>4.2</v>
       </c>
       <c r="R35" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="S35" t="n">
-        <v>2.88</v>
+        <v>2.78</v>
       </c>
       <c r="T35" t="n">
-        <v>2.71</v>
+        <v>2.84</v>
       </c>
       <c r="U35" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="V35" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="W35" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="X35" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AE35" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF35" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG35" t="n">
         <v>1.28</v>
       </c>
-      <c r="X35" t="n">
-        <v>3.48</v>
-      </c>
-      <c r="Y35" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="Z35" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AA35" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="AB35" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AC35" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AD35" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AE35" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF35" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG35" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AH35" t="n">
-        <v>1.36</v>
+        <v>1.8</v>
       </c>
       <c r="AI35" t="n">
         <v>0</v>
@@ -5014,12 +5014,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,61 +5055,61 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.49</v>
+        <v>3</v>
       </c>
       <c r="M36" t="n">
-        <v>3.29</v>
+        <v>3.83</v>
       </c>
       <c r="N36" t="n">
-        <v>2.74</v>
+        <v>2.1</v>
       </c>
       <c r="O36" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="S36" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="T36" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="U36" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="V36" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W36" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="X36" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Z36" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>3.92</v>
+        <v>2.25</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.19</v>
+        <v>1.65</v>
       </c>
       <c r="AC36" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AD36" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AE36" t="inlineStr">
         <is>
@@ -5122,10 +5122,10 @@
         </is>
       </c>
       <c r="AG36" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AH36" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AI36" t="n">
         <v>0</v>
@@ -5134,7 +5134,7 @@
         <v>0</v>
       </c>
       <c r="AK36" s="3" t="n">
-        <v>45930.65625</v>
+        <v>45930.66666666666</v>
       </c>
     </row>
     <row r="37">
@@ -5193,34 +5193,34 @@
         <v>5.1</v>
       </c>
       <c r="O37" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="R37" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="S37" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="T37" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="U37" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="V37" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W37" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X37" t="n">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="Y37" t="n">
         <v>1.63</v>
@@ -5229,16 +5229,16 @@
         <v>2.25</v>
       </c>
       <c r="AA37" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AB37" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AC37" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AD37" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AE37" t="inlineStr">
         <is>
@@ -5251,10 +5251,10 @@
         </is>
       </c>
       <c r="AG37" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AH37" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="AI37" t="n">
         <v>0</v>
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,61 +5313,61 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>1.56</v>
+        <v>1.62</v>
       </c>
       <c r="M38" t="n">
         <v>4.1</v>
       </c>
       <c r="N38" t="n">
-        <v>5.4</v>
+        <v>4.9</v>
       </c>
       <c r="O38" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P38" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="T38" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="U38" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="V38" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W38" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="X38" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.63</v>
+        <v>1.68</v>
       </c>
       <c r="Z38" t="n">
-        <v>2.25</v>
+        <v>2.18</v>
       </c>
       <c r="AA38" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AC38" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AD38" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="AE38" t="inlineStr">
         <is>
@@ -5380,10 +5380,10 @@
         </is>
       </c>
       <c r="AG38" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AH38" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="AI38" t="n">
         <v>0</v>
@@ -5406,7 +5406,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Kariobangi Sharks</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>KCB</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,13 +5442,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5481,16 +5481,16 @@
         <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="Z39" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC39" t="n">
         <v>0</v>
@@ -5535,7 +5535,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,61 +5571,61 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>1.35</v>
+        <v>2.4</v>
       </c>
       <c r="M40" t="n">
-        <v>5.3</v>
+        <v>3.39</v>
       </c>
       <c r="N40" t="n">
-        <v>7</v>
+        <v>2.79</v>
       </c>
       <c r="O40" t="n">
-        <v>1.76</v>
+        <v>3.2</v>
       </c>
       <c r="P40" t="n">
-        <v>2.6</v>
+        <v>1.92</v>
       </c>
       <c r="Q40" t="n">
-        <v>7.4</v>
+        <v>3.85</v>
       </c>
       <c r="R40" t="n">
-        <v>1.25</v>
+        <v>1.53</v>
       </c>
       <c r="S40" t="n">
-        <v>3.54</v>
+        <v>2.34</v>
       </c>
       <c r="T40" t="n">
-        <v>2.26</v>
+        <v>3.48</v>
       </c>
       <c r="U40" t="n">
-        <v>1.62</v>
+        <v>1.22</v>
       </c>
       <c r="V40" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="W40" t="n">
-        <v>1.16</v>
+        <v>1.53</v>
       </c>
       <c r="X40" t="n">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.6</v>
+        <v>2.52</v>
       </c>
       <c r="Z40" t="n">
-        <v>2.35</v>
+        <v>1.52</v>
       </c>
       <c r="AA40" t="n">
-        <v>2.42</v>
+        <v>4.8</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.6</v>
+        <v>1.13</v>
       </c>
       <c r="AC40" t="n">
-        <v>1.81</v>
+        <v>2.06</v>
       </c>
       <c r="AD40" t="n">
-        <v>1.91</v>
+        <v>1.7</v>
       </c>
       <c r="AE40" t="inlineStr">
         <is>
@@ -5638,10 +5638,10 @@
         </is>
       </c>
       <c r="AG40" t="n">
-        <v>1.17</v>
+        <v>1.37</v>
       </c>
       <c r="AH40" t="n">
-        <v>3.3</v>
+        <v>1.54</v>
       </c>
       <c r="AI40" t="n">
         <v>0</v>
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,43 +5700,43 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>15</v>
+        <v>4.3</v>
       </c>
       <c r="M41" t="n">
-        <v>7.6</v>
+        <v>4.4</v>
       </c>
       <c r="N41" t="n">
-        <v>1.15</v>
+        <v>1.64</v>
       </c>
       <c r="O41" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="P41" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="S41" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="T41" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U41" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="V41" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W41" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X41" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="Y41" t="n">
         <v>1.44</v>
@@ -5745,16 +5745,16 @@
         <v>2.75</v>
       </c>
       <c r="AA41" t="n">
-        <v>1.95</v>
+        <v>2.15</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.79</v>
+        <v>1.7</v>
       </c>
       <c r="AC41" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="AD41" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AE41" t="inlineStr">
         <is>
@@ -5767,10 +5767,10 @@
         </is>
       </c>
       <c r="AG41" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AH41" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AI41" t="n">
         <v>0</v>
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,61 +5829,61 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>3</v>
+        <v>1.35</v>
       </c>
       <c r="M42" t="n">
-        <v>3.83</v>
+        <v>5.3</v>
       </c>
       <c r="N42" t="n">
-        <v>2.1</v>
+        <v>7</v>
       </c>
       <c r="O42" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="P42" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="S42" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="T42" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="U42" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="V42" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W42" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="X42" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="Z42" t="n">
-        <v>2.39</v>
+        <v>2.35</v>
       </c>
       <c r="AA42" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC42" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AD42" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="AE42" t="inlineStr">
         <is>
@@ -5896,10 +5896,10 @@
         </is>
       </c>
       <c r="AG42" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH42" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="AI42" t="n">
         <v>0</v>
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5958,61 +5958,61 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>1.62</v>
+        <v>1.56</v>
       </c>
       <c r="M43" t="n">
         <v>4.1</v>
       </c>
       <c r="N43" t="n">
-        <v>4.9</v>
+        <v>5.4</v>
       </c>
       <c r="O43" t="n">
-        <v>2.16</v>
+        <v>2</v>
       </c>
       <c r="P43" t="n">
-        <v>2.27</v>
+        <v>2.43</v>
       </c>
       <c r="Q43" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="R43" t="n">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="S43" t="n">
-        <v>3.24</v>
+        <v>3.45</v>
       </c>
       <c r="T43" t="n">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="U43" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="V43" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W43" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="X43" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="AB43" t="n">
         <v>1.52</v>
       </c>
-      <c r="V43" t="n">
-        <v>1</v>
-      </c>
-      <c r="W43" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="X43" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="Y43" t="n">
+      <c r="AC43" t="n">
         <v>1.68</v>
       </c>
-      <c r="Z43" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AA43" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AB43" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AC43" t="n">
-        <v>1.69</v>
-      </c>
       <c r="AD43" t="n">
-        <v>2.17</v>
+        <v>2.19</v>
       </c>
       <c r="AE43" t="inlineStr">
         <is>
@@ -6028,7 +6028,7 @@
         <v>1.26</v>
       </c>
       <c r="AH43" t="n">
-        <v>2.27</v>
+        <v>2.41</v>
       </c>
       <c r="AI43" t="n">
         <v>0</v>
@@ -6051,7 +6051,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6061,12 +6061,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6087,61 +6087,61 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>2.4</v>
+        <v>15</v>
       </c>
       <c r="M44" t="n">
-        <v>3.39</v>
+        <v>7.6</v>
       </c>
       <c r="N44" t="n">
-        <v>2.79</v>
+        <v>1.15</v>
       </c>
       <c r="O44" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="P44" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="S44" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="T44" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="U44" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="V44" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="W44" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="X44" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>2.52</v>
+        <v>1.44</v>
       </c>
       <c r="Z44" t="n">
-        <v>1.52</v>
+        <v>2.75</v>
       </c>
       <c r="AA44" t="n">
-        <v>4.8</v>
+        <v>1.95</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.13</v>
+        <v>1.79</v>
       </c>
       <c r="AC44" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AD44" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AE44" t="inlineStr">
         <is>
@@ -6154,10 +6154,10 @@
         </is>
       </c>
       <c r="AG44" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AH44" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AI44" t="n">
         <v>0</v>
@@ -6175,27 +6175,27 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>Police</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>Ulinzi Stars</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6216,61 +6216,61 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="N45" t="n">
-        <v>4.91</v>
+        <v>0</v>
       </c>
       <c r="O45" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="P45" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>4.35</v>
+        <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="S45" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="T45" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="U45" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="V45" t="n">
         <v>0</v>
       </c>
       <c r="W45" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X45" t="n">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Z45" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AA45" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC45" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AD45" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AE45" t="inlineStr">
         <is>
@@ -6283,10 +6283,10 @@
         </is>
       </c>
       <c r="AG45" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AH45" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AI45" t="n">
         <v>0</v>
@@ -6295,7 +6295,7 @@
         <v>0</v>
       </c>
       <c r="AK45" s="3" t="n">
-        <v>45930.85416666666</v>
+        <v>45930.75</v>
       </c>
     </row>
     <row r="46">
@@ -6304,12 +6304,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6319,12 +6319,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6345,61 +6345,61 @@
         </is>
       </c>
       <c r="L46" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="M46" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="N46" t="n">
+        <v>4.91</v>
+      </c>
+      <c r="O46" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="P46" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="R46" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="S46" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="T46" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="U46" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="V46" t="n">
+        <v>0</v>
+      </c>
+      <c r="W46" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X46" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="Y46" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z46" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AA46" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AB46" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AC46" t="n">
         <v>1.4</v>
       </c>
-      <c r="M46" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="N46" t="n">
-        <v>6</v>
-      </c>
-      <c r="O46" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="P46" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="Q46" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="R46" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="S46" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="T46" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="U46" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="V46" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W46" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="X46" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="Y46" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="Z46" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AA46" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AB46" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AC46" t="n">
-        <v>2.14</v>
-      </c>
       <c r="AD46" t="n">
-        <v>1.61</v>
+        <v>2.7</v>
       </c>
       <c r="AE46" t="inlineStr">
         <is>
@@ -6412,10 +6412,10 @@
         </is>
       </c>
       <c r="AG46" t="n">
-        <v>1.09</v>
+        <v>1.18</v>
       </c>
       <c r="AH46" t="n">
-        <v>2.77</v>
+        <v>2.38</v>
       </c>
       <c r="AI46" t="n">
         <v>0</v>
@@ -6424,7 +6424,7 @@
         <v>0</v>
       </c>
       <c r="AK46" s="3" t="n">
-        <v>45930.89583333334</v>
+        <v>45930.85416666666</v>
       </c>
     </row>
     <row r="47">
@@ -6433,126 +6433,255 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Atlético Mineiro</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Juventude</t>
+        </is>
+      </c>
+      <c r="G47" t="n">
+        <v>0</v>
+      </c>
+      <c r="H47" t="n">
+        <v>0</v>
+      </c>
+      <c r="I47" t="n">
+        <v>0</v>
+      </c>
+      <c r="J47" t="n">
+        <v>0</v>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L47" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="M47" t="n">
+        <v>4.44</v>
+      </c>
+      <c r="N47" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="O47" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="P47" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="R47" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S47" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="T47" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="U47" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="V47" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W47" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="X47" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="Y47" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="Z47" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AA47" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AB47" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AC47" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AD47" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AE47" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF47" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG47" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AH47" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AI47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK47" s="3" t="n">
+        <v>45930.89583333334</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="n">
+        <v>45930</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
           <t>21:35</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr">
+      <c r="C48" t="inlineStr">
         <is>
           <t>Brazil Serie B</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr">
+      <c r="D48" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr">
+      <c r="E48" t="inlineStr">
         <is>
           <t>Goiás</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr">
+      <c r="F48" t="inlineStr">
         <is>
           <t>Atlético GO</t>
         </is>
       </c>
-      <c r="G47" t="n">
-        <v>0</v>
-      </c>
-      <c r="H47" t="n">
-        <v>0</v>
-      </c>
-      <c r="I47" t="n">
-        <v>0</v>
-      </c>
-      <c r="J47" t="n">
-        <v>0</v>
-      </c>
-      <c r="K47" t="inlineStr">
+      <c r="G48" t="n">
+        <v>0</v>
+      </c>
+      <c r="H48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I48" t="n">
+        <v>0</v>
+      </c>
+      <c r="J48" t="n">
+        <v>0</v>
+      </c>
+      <c r="K48" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L47" t="n">
+      <c r="L48" t="n">
         <v>2.05</v>
       </c>
-      <c r="M47" t="n">
+      <c r="M48" t="n">
         <v>3</v>
       </c>
-      <c r="N47" t="n">
+      <c r="N48" t="n">
         <v>3.8</v>
       </c>
-      <c r="O47" t="n">
+      <c r="O48" t="n">
         <v>2.66</v>
       </c>
-      <c r="P47" t="n">
+      <c r="P48" t="n">
         <v>2</v>
       </c>
-      <c r="Q47" t="n">
+      <c r="Q48" t="n">
         <v>4.25</v>
       </c>
-      <c r="R47" t="n">
+      <c r="R48" t="n">
         <v>1.51</v>
       </c>
-      <c r="S47" t="n">
+      <c r="S48" t="n">
         <v>2.42</v>
       </c>
-      <c r="T47" t="n">
+      <c r="T48" t="n">
         <v>3.3</v>
       </c>
-      <c r="U47" t="n">
+      <c r="U48" t="n">
         <v>1.28</v>
       </c>
-      <c r="V47" t="n">
+      <c r="V48" t="n">
         <v>1.05</v>
       </c>
-      <c r="W47" t="n">
+      <c r="W48" t="n">
         <v>1.4</v>
       </c>
-      <c r="X47" t="n">
+      <c r="X48" t="n">
         <v>2.95</v>
       </c>
-      <c r="Y47" t="n">
+      <c r="Y48" t="n">
         <v>2.49</v>
       </c>
-      <c r="Z47" t="n">
+      <c r="Z48" t="n">
         <v>1.56</v>
       </c>
-      <c r="AA47" t="n">
+      <c r="AA48" t="n">
         <v>4.73</v>
       </c>
-      <c r="AB47" t="n">
+      <c r="AB48" t="n">
         <v>1.18</v>
       </c>
-      <c r="AC47" t="n">
+      <c r="AC48" t="n">
         <v>2</v>
       </c>
-      <c r="AD47" t="n">
+      <c r="AD48" t="n">
         <v>1.71</v>
       </c>
-      <c r="AE47" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF47" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG47" t="n">
+      <c r="AE48" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF48" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG48" t="n">
         <v>1.27</v>
       </c>
-      <c r="AH47" t="n">
+      <c r="AH48" t="n">
         <v>1.75</v>
       </c>
-      <c r="AI47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK47" s="3" t="n">
+      <c r="AI48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK48" s="3" t="n">
         <v>45930.89930555555</v>
       </c>
     </row>

--- a/jogos_2025-09-30.xlsx
+++ b/jogos_2025-09-30.xlsx
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Sogdiana</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -798,13 +798,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>3.35</v>
+        <v>2.95</v>
       </c>
       <c r="M3" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="N3" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -837,10 +837,10 @@
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.25</v>
+        <v>2.08</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AA3" t="n">
         <v>0</v>
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sogdiana</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -927,13 +927,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.95</v>
+        <v>3.35</v>
       </c>
       <c r="M4" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="N4" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -966,10 +966,10 @@
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.08</v>
+        <v>2.25</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AA4" t="n">
         <v>0</v>
@@ -1065,34 +1065,34 @@
         <v>1.82</v>
       </c>
       <c r="O5" t="n">
-        <v>5.84</v>
+        <v>5.78</v>
       </c>
       <c r="P5" t="n">
-        <v>2.25</v>
+        <v>2.26</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="R5" t="n">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="S5" t="n">
-        <v>2.85</v>
+        <v>2.7</v>
       </c>
       <c r="T5" t="n">
-        <v>2.88</v>
+        <v>2.89</v>
       </c>
       <c r="U5" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="V5" t="n">
         <v>1.02</v>
       </c>
       <c r="W5" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="X5" t="n">
-        <v>3.2</v>
+        <v>3.26</v>
       </c>
       <c r="Y5" t="n">
         <v>2.25</v>
@@ -1101,16 +1101,16 @@
         <v>1.65</v>
       </c>
       <c r="AA5" t="n">
-        <v>3.44</v>
+        <v>3.43</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="AC5" t="n">
         <v>1.95</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.78</v>
+        <v>1.71</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="AI5" t="n">
         <v>2.38</v>
@@ -1194,34 +1194,34 @@
         <v>3.7</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="Y6" t="n">
         <v>1.7</v>
@@ -1230,16 +1230,16 @@
         <v>2.15</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
@@ -1252,10 +1252,10 @@
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AI6" t="n">
         <v>0</v>
@@ -1323,34 +1323,34 @@
         <v>1.11</v>
       </c>
       <c r="O7" t="n">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>6.55</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
         <v>1.3</v>
@@ -1365,10 +1365,10 @@
         <v>1.94</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
@@ -1381,10 +1381,10 @@
         </is>
       </c>
       <c r="AG7" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AI7" t="n">
         <v>0</v>
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Havelse</t>
+          <t>Saarbrucken</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Waldhof Mannheim</t>
+          <t>MSV Duisburg</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,61 +1443,61 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>3.4</v>
+        <v>1.87</v>
       </c>
       <c r="M8" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="N8" t="n">
-        <v>1.92</v>
+        <v>3.12</v>
       </c>
       <c r="O8" t="n">
-        <v>3.7</v>
+        <v>2.51</v>
       </c>
       <c r="P8" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.35</v>
+        <v>3.98</v>
       </c>
       <c r="R8" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="S8" t="n">
-        <v>3.2</v>
+        <v>3.26</v>
       </c>
       <c r="T8" t="n">
-        <v>2.23</v>
+        <v>2.36</v>
       </c>
       <c r="U8" t="n">
-        <v>1.56</v>
+        <v>1.52</v>
       </c>
       <c r="V8" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W8" t="n">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="X8" t="n">
-        <v>4.25</v>
+        <v>4.45</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.16</v>
+        <v>2.22</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.45</v>
+        <v>2.42</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="AD8" t="n">
-        <v>2.17</v>
+        <v>2.36</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.26</v>
+        <v>1.74</v>
       </c>
       <c r="AI8" t="n">
         <v>0</v>
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Hansa Rostock</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>Wehen Wiesbaden</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,61 +1572,61 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.8</v>
+        <v>2.9</v>
       </c>
       <c r="M9" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="N9" t="n">
-        <v>3.8</v>
+        <v>2.18</v>
       </c>
       <c r="O9" t="n">
-        <v>2.28</v>
+        <v>3.34</v>
       </c>
       <c r="P9" t="n">
-        <v>2.38</v>
+        <v>2.21</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.95</v>
+        <v>2.83</v>
       </c>
       <c r="R9" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="S9" t="n">
-        <v>3.2</v>
+        <v>3.26</v>
       </c>
       <c r="T9" t="n">
-        <v>2.28</v>
+        <v>2.39</v>
       </c>
       <c r="U9" t="n">
-        <v>1.54</v>
+        <v>1.51</v>
       </c>
       <c r="V9" t="n">
         <v>1.02</v>
       </c>
       <c r="W9" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="X9" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.61</v>
+        <v>1.53</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.55</v>
+        <v>2.33</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AD9" t="n">
-        <v>2.07</v>
+        <v>2.36</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.85</v>
+        <v>1.4</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
@@ -1665,22 +1665,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Wehen Wiesbaden</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,34 +1701,34 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.9</v>
+        <v>1.26</v>
       </c>
       <c r="M10" t="n">
-        <v>3.6</v>
+        <v>5.1</v>
       </c>
       <c r="N10" t="n">
-        <v>2.18</v>
+        <v>7.6</v>
       </c>
       <c r="O10" t="n">
-        <v>3.25</v>
+        <v>1.83</v>
       </c>
       <c r="P10" t="n">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.6</v>
+        <v>5.7</v>
       </c>
       <c r="R10" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="S10" t="n">
-        <v>3.26</v>
+        <v>3.4</v>
       </c>
       <c r="T10" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="U10" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="V10" t="n">
         <v>1.02</v>
@@ -1737,25 +1737,25 @@
         <v>1.14</v>
       </c>
       <c r="X10" t="n">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.53</v>
+        <v>1.47</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.33</v>
+        <v>2.17</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.49</v>
+        <v>1.62</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.44</v>
+        <v>1.73</v>
       </c>
       <c r="AD10" t="n">
-        <v>2.33</v>
+        <v>1.95</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -1768,10 +1768,10 @@
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>1.6</v>
+        <v>1.17</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.33</v>
+        <v>2.75</v>
       </c>
       <c r="AI10" t="n">
         <v>0</v>
@@ -1794,22 +1794,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Erzgebirge Aue</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,61 +1830,61 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.03</v>
+        <v>1.56</v>
       </c>
       <c r="M11" t="n">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="N11" t="n">
-        <v>3.3</v>
+        <v>4.2</v>
       </c>
       <c r="O11" t="n">
-        <v>2.55</v>
+        <v>1.95</v>
       </c>
       <c r="P11" t="n">
-        <v>2.28</v>
+        <v>2.5</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.55</v>
+        <v>4.95</v>
       </c>
       <c r="R11" t="n">
-        <v>1.32</v>
+        <v>1.22</v>
       </c>
       <c r="S11" t="n">
-        <v>3.1</v>
+        <v>3.66</v>
       </c>
       <c r="T11" t="n">
-        <v>2.43</v>
+        <v>1.98</v>
       </c>
       <c r="U11" t="n">
-        <v>1.48</v>
+        <v>1.71</v>
       </c>
       <c r="V11" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="W11" t="n">
-        <v>1.21</v>
+        <v>1.11</v>
       </c>
       <c r="X11" t="n">
-        <v>3.7</v>
+        <v>5.6</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.71</v>
+        <v>1.42</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.94</v>
+        <v>2.7</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.8</v>
+        <v>1.92</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.35</v>
+        <v>1.78</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.58</v>
+        <v>1.5</v>
       </c>
       <c r="AD11" t="n">
-        <v>2.02</v>
+        <v>2.3</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -1897,10 +1897,10 @@
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>1.24</v>
+        <v>1.19</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.68</v>
+        <v>2.4</v>
       </c>
       <c r="AI11" t="n">
         <v>0</v>
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Saarbrucken</t>
+          <t>Hansa Rostock</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>MSV Duisburg</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,61 +1959,61 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.87</v>
+        <v>1.98</v>
       </c>
       <c r="M12" t="n">
         <v>3.8</v>
       </c>
       <c r="N12" t="n">
-        <v>3.55</v>
+        <v>3.8</v>
       </c>
       <c r="O12" t="n">
-        <v>2.51</v>
+        <v>2.28</v>
       </c>
       <c r="P12" t="n">
-        <v>2.2</v>
+        <v>2.23</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.98</v>
+        <v>4.08</v>
       </c>
       <c r="R12" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="S12" t="n">
-        <v>3.26</v>
+        <v>3.2</v>
       </c>
       <c r="T12" t="n">
-        <v>2.36</v>
+        <v>2.28</v>
       </c>
       <c r="U12" t="n">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="V12" t="n">
         <v>1.02</v>
       </c>
       <c r="W12" t="n">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="X12" t="n">
-        <v>4.45</v>
+        <v>4</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.22</v>
+        <v>2.1</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.42</v>
+        <v>2.55</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.51</v>
+        <v>1.58</v>
       </c>
       <c r="AD12" t="n">
-        <v>2.36</v>
+        <v>2.21</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -2026,10 +2026,10 @@
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.74</v>
+        <v>1.79</v>
       </c>
       <c r="AI12" t="n">
         <v>0</v>
@@ -2052,22 +2052,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Erzgebirge Aue</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,61 +2088,61 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.53</v>
+        <v>2.03</v>
       </c>
       <c r="M13" t="n">
-        <v>4.4</v>
+        <v>3.5</v>
       </c>
       <c r="N13" t="n">
-        <v>5</v>
+        <v>3.3</v>
       </c>
       <c r="O13" t="n">
-        <v>1.95</v>
+        <v>2.54</v>
       </c>
       <c r="P13" t="n">
-        <v>2.5</v>
+        <v>2.21</v>
       </c>
       <c r="Q13" t="n">
-        <v>4.95</v>
+        <v>3.87</v>
       </c>
       <c r="R13" t="n">
-        <v>1.22</v>
+        <v>1.32</v>
       </c>
       <c r="S13" t="n">
-        <v>3.66</v>
+        <v>3.1</v>
       </c>
       <c r="T13" t="n">
-        <v>1.98</v>
+        <v>2.43</v>
       </c>
       <c r="U13" t="n">
-        <v>1.71</v>
+        <v>1.48</v>
       </c>
       <c r="V13" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="W13" t="n">
-        <v>1.11</v>
+        <v>1.21</v>
       </c>
       <c r="X13" t="n">
-        <v>5.6</v>
+        <v>3.7</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.42</v>
+        <v>1.75</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.7</v>
+        <v>2</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.25</v>
+        <v>2.8</v>
       </c>
       <c r="AB13" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AC13" t="n">
         <v>1.62</v>
       </c>
-      <c r="AC13" t="n">
-        <v>1.5</v>
-      </c>
       <c r="AD13" t="n">
-        <v>2.3</v>
+        <v>2.02</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
@@ -2155,10 +2155,10 @@
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>1.19</v>
+        <v>1.24</v>
       </c>
       <c r="AH13" t="n">
-        <v>2.4</v>
+        <v>1.68</v>
       </c>
       <c r="AI13" t="n">
         <v>0</v>
@@ -2181,22 +2181,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Havelse</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Waldhof Mannheim</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,61 +2217,61 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.4</v>
+        <v>3.4</v>
       </c>
       <c r="M14" t="n">
-        <v>4.8</v>
+        <v>3.7</v>
       </c>
       <c r="N14" t="n">
-        <v>6.8</v>
+        <v>1.92</v>
       </c>
       <c r="O14" t="n">
-        <v>1.83</v>
+        <v>4.12</v>
       </c>
       <c r="P14" t="n">
-        <v>2.45</v>
+        <v>2.24</v>
       </c>
       <c r="Q14" t="n">
-        <v>5.7</v>
+        <v>2.4</v>
       </c>
       <c r="R14" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="S14" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="T14" t="n">
-        <v>2.2</v>
+        <v>2.23</v>
       </c>
       <c r="U14" t="n">
-        <v>1.62</v>
+        <v>1.49</v>
       </c>
       <c r="V14" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W14" t="n">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="X14" t="n">
-        <v>5</v>
+        <v>4.1</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.4</v>
+        <v>2.12</v>
       </c>
       <c r="AA14" t="n">
         <v>2.45</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.54</v>
+        <v>1.45</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.73</v>
+        <v>1.5</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.95</v>
+        <v>2.17</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
@@ -2284,10 +2284,10 @@
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>1.17</v>
+        <v>1.23</v>
       </c>
       <c r="AH14" t="n">
-        <v>2.75</v>
+        <v>1.24</v>
       </c>
       <c r="AI14" t="n">
         <v>0</v>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,77 +2346,77 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.79</v>
+        <v>2.15</v>
       </c>
       <c r="M15" t="n">
-        <v>3.95</v>
+        <v>3.5</v>
       </c>
       <c r="N15" t="n">
-        <v>3.9</v>
+        <v>2.88</v>
       </c>
       <c r="O15" t="n">
-        <v>2.25</v>
+        <v>2.6</v>
       </c>
       <c r="P15" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="Q15" t="n">
-        <v>4.62</v>
+        <v>3.35</v>
       </c>
       <c r="R15" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="S15" t="n">
-        <v>3.28</v>
+        <v>3.7</v>
       </c>
       <c r="T15" t="n">
-        <v>2.44</v>
+        <v>2.21</v>
       </c>
       <c r="U15" t="n">
-        <v>1.49</v>
+        <v>1.62</v>
       </c>
       <c r="V15" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="W15" t="n">
-        <v>1.16</v>
+        <v>1.12</v>
       </c>
       <c r="X15" t="n">
-        <v>4.15</v>
+        <v>4.8</v>
       </c>
       <c r="Y15" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG15" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AH15" t="n">
         <v>1.68</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AE15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG15" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>2.08</v>
       </c>
       <c r="AI15" t="n">
         <v>0</v>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,61 +2475,61 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>2.58</v>
+        <v>1.62</v>
       </c>
       <c r="P16" t="n">
-        <v>2.4</v>
+        <v>2.68</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.43</v>
+        <v>6.49</v>
       </c>
       <c r="R16" t="n">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="S16" t="n">
-        <v>3.58</v>
+        <v>3.88</v>
       </c>
       <c r="T16" t="n">
-        <v>2.21</v>
+        <v>2.04</v>
       </c>
       <c r="U16" t="n">
-        <v>1.61</v>
+        <v>1.69</v>
       </c>
       <c r="V16" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W16" t="n">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="X16" t="n">
-        <v>4.75</v>
+        <v>5.5</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.55</v>
+        <v>1.46</v>
       </c>
       <c r="Z16" t="n">
-        <v>2.39</v>
+        <v>2.6</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.28</v>
+        <v>2.09</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.6</v>
+        <v>1.71</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.44</v>
+        <v>1.66</v>
       </c>
       <c r="AD16" t="n">
-        <v>2.59</v>
+        <v>2.12</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
@@ -2542,10 +2542,10 @@
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>1.25</v>
+        <v>1.07</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.68</v>
+        <v>3.15</v>
       </c>
       <c r="AI16" t="n">
         <v>0</v>
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,61 +2604,61 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>3.2</v>
+        <v>2.87</v>
       </c>
       <c r="M17" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="N17" t="n">
-        <v>1.91</v>
+        <v>2.3</v>
       </c>
       <c r="O17" t="n">
-        <v>3.72</v>
+        <v>3.5</v>
       </c>
       <c r="P17" t="n">
-        <v>2.39</v>
+        <v>2.25</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.33</v>
+        <v>2.55</v>
       </c>
       <c r="R17" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="S17" t="n">
-        <v>3.58</v>
+        <v>3.6</v>
       </c>
       <c r="T17" t="n">
-        <v>2.2</v>
+        <v>2.32</v>
       </c>
       <c r="U17" t="n">
-        <v>1.63</v>
+        <v>1.57</v>
       </c>
       <c r="V17" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="W17" t="n">
-        <v>1.1</v>
+        <v>1.17</v>
       </c>
       <c r="X17" t="n">
-        <v>5</v>
+        <v>4.45</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.52</v>
+        <v>1.59</v>
       </c>
       <c r="Z17" t="n">
-        <v>2.43</v>
+        <v>2.35</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.25</v>
+        <v>2.36</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.62</v>
+        <v>1.55</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="AD17" t="n">
-        <v>2.56</v>
+        <v>2.45</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
@@ -2671,10 +2671,10 @@
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="AI17" t="n">
         <v>0</v>
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,61 +2733,61 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="O18" t="n">
-        <v>1.71</v>
+        <v>3.79</v>
       </c>
       <c r="P18" t="n">
-        <v>2.74</v>
+        <v>2.39</v>
       </c>
       <c r="Q18" t="n">
-        <v>6.84</v>
+        <v>2.33</v>
       </c>
       <c r="R18" t="n">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="S18" t="n">
-        <v>3.94</v>
+        <v>3.75</v>
       </c>
       <c r="T18" t="n">
-        <v>2.08</v>
+        <v>2.2</v>
       </c>
       <c r="U18" t="n">
-        <v>1.7</v>
+        <v>1.63</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W18" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X18" t="n">
-        <v>5.65</v>
+        <v>5.16</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.37</v>
+        <v>1.53</v>
       </c>
       <c r="Z18" t="n">
-        <v>2.67</v>
+        <v>2.4</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.08</v>
+        <v>2.25</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.74</v>
+        <v>1.62</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.68</v>
+        <v>1.46</v>
       </c>
       <c r="AD18" t="n">
-        <v>2.08</v>
+        <v>2.5</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
@@ -2800,10 +2800,10 @@
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>1.13</v>
+        <v>1.24</v>
       </c>
       <c r="AH18" t="n">
-        <v>3.34</v>
+        <v>1.31</v>
       </c>
       <c r="AI18" t="n">
         <v>0</v>
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,61 +2862,61 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.87</v>
+        <v>1.78</v>
       </c>
       <c r="M19" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="N19" t="n">
-        <v>2.3</v>
+        <v>3.7</v>
       </c>
       <c r="O19" t="n">
-        <v>3.5</v>
+        <v>2.34</v>
       </c>
       <c r="P19" t="n">
-        <v>2.28</v>
+        <v>2.27</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.64</v>
+        <v>4.42</v>
       </c>
       <c r="R19" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="S19" t="n">
-        <v>3.4</v>
+        <v>3.28</v>
       </c>
       <c r="T19" t="n">
-        <v>2.32</v>
+        <v>2.47</v>
       </c>
       <c r="U19" t="n">
-        <v>1.54</v>
+        <v>1.48</v>
       </c>
       <c r="V19" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="W19" t="n">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="X19" t="n">
-        <v>4.85</v>
+        <v>4.15</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.59</v>
+        <v>1.68</v>
       </c>
       <c r="Z19" t="n">
-        <v>2.36</v>
+        <v>2.14</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.36</v>
+        <v>2.63</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.56</v>
+        <v>1.39</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.5</v>
+        <v>1.61</v>
       </c>
       <c r="AD19" t="n">
-        <v>2.41</v>
+        <v>2.2</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
@@ -2929,10 +2929,10 @@
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.36</v>
+        <v>1.95</v>
       </c>
       <c r="AI19" t="n">
         <v>0</v>
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,77 +2991,77 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.62</v>
+        <v>2.05</v>
       </c>
       <c r="M20" t="n">
-        <v>3.24</v>
+        <v>3.65</v>
       </c>
       <c r="N20" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="O20" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="P20" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S20" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="T20" t="n">
         <v>2.6</v>
       </c>
-      <c r="O20" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="P20" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="R20" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S20" t="n">
-        <v>2.51</v>
-      </c>
-      <c r="T20" t="n">
-        <v>3.08</v>
-      </c>
       <c r="U20" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X20" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AE20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG20" t="n">
         <v>1.3</v>
       </c>
-      <c r="V20" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W20" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="X20" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AE20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG20" t="n">
-        <v>1.35</v>
-      </c>
       <c r="AH20" t="n">
-        <v>1.49</v>
+        <v>1.73</v>
       </c>
       <c r="AI20" t="n">
         <v>0</v>
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Mantova</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,61 +3120,61 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.11</v>
+        <v>1.79</v>
       </c>
       <c r="M21" t="n">
+        <v>3.61</v>
+      </c>
+      <c r="N21" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="O21" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="P21" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="S21" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V21" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="X21" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AA21" t="n">
         <v>3.4</v>
       </c>
-      <c r="N21" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="O21" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="P21" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>3.92</v>
-      </c>
-      <c r="R21" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="S21" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="T21" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="U21" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="V21" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W21" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="X21" t="n">
-        <v>3.74</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>2</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>2.92</v>
-      </c>
       <c r="AB21" t="n">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.65</v>
+        <v>1.86</v>
       </c>
       <c r="AD21" t="n">
-        <v>2.13</v>
+        <v>1.86</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
@@ -3187,10 +3187,10 @@
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.74</v>
+        <v>2.03</v>
       </c>
       <c r="AI21" t="n">
         <v>0</v>
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Calcio Padova</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mantova</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,61 +3249,61 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.88</v>
+        <v>2.15</v>
       </c>
       <c r="M22" t="n">
-        <v>3.65</v>
+        <v>3.35</v>
       </c>
       <c r="N22" t="n">
-        <v>4.08</v>
+        <v>3.45</v>
       </c>
       <c r="O22" t="n">
-        <v>2.45</v>
+        <v>2.81</v>
       </c>
       <c r="P22" t="n">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="Q22" t="n">
-        <v>4.7</v>
+        <v>4.24</v>
       </c>
       <c r="R22" t="n">
-        <v>1.38</v>
+        <v>1.45</v>
       </c>
       <c r="S22" t="n">
-        <v>2.71</v>
+        <v>2.55</v>
       </c>
       <c r="T22" t="n">
-        <v>2.79</v>
+        <v>3</v>
       </c>
       <c r="U22" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V22" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W22" t="n">
         <v>1.36</v>
       </c>
-      <c r="V22" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="W22" t="n">
-        <v>1.29</v>
-      </c>
       <c r="X22" t="n">
-        <v>3.12</v>
+        <v>2.78</v>
       </c>
       <c r="Y22" t="n">
-        <v>2.01</v>
+        <v>2.2</v>
       </c>
       <c r="Z22" t="n">
-        <v>1.8</v>
+        <v>1.65</v>
       </c>
       <c r="AA22" t="n">
-        <v>3.32</v>
+        <v>3.9</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.26</v>
+        <v>1.19</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.84</v>
+        <v>1.93</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.88</v>
+        <v>1.76</v>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
@@ -3316,10 +3316,10 @@
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>1.23</v>
+        <v>1.33</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.94</v>
+        <v>1.69</v>
       </c>
       <c r="AI22" t="n">
         <v>0</v>
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,61 +3378,61 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>3.6</v>
+        <v>2.15</v>
       </c>
       <c r="M23" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="N23" t="n">
         <v>3.45</v>
       </c>
-      <c r="N23" t="n">
-        <v>2.05</v>
-      </c>
       <c r="O23" t="n">
-        <v>4.15</v>
+        <v>2.81</v>
       </c>
       <c r="P23" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.72</v>
+        <v>4.1</v>
       </c>
       <c r="R23" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="S23" t="n">
-        <v>2.64</v>
+        <v>2.57</v>
       </c>
       <c r="T23" t="n">
-        <v>2.93</v>
+        <v>3</v>
       </c>
       <c r="U23" t="n">
         <v>1.33</v>
       </c>
       <c r="V23" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="W23" t="n">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="X23" t="n">
-        <v>3.02</v>
+        <v>2.88</v>
       </c>
       <c r="Y23" t="n">
-        <v>2.07</v>
+        <v>2.18</v>
       </c>
       <c r="Z23" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AA23" t="n">
-        <v>3.6</v>
+        <v>3.82</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.89</v>
+        <v>1.85</v>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
@@ -3445,10 +3445,10 @@
         </is>
       </c>
       <c r="AG23" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.3</v>
+        <v>1.7</v>
       </c>
       <c r="AI23" t="n">
         <v>0</v>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,61 +3507,61 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>3.81</v>
+        <v>3.41</v>
       </c>
       <c r="M24" t="n">
-        <v>3.45</v>
+        <v>3.26</v>
       </c>
       <c r="N24" t="n">
-        <v>1.81</v>
+        <v>2.13</v>
       </c>
       <c r="O24" t="n">
-        <v>3.9</v>
+        <v>4.29</v>
       </c>
       <c r="P24" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.45</v>
+        <v>2.75</v>
       </c>
       <c r="R24" t="n">
-        <v>1.35</v>
+        <v>1.41</v>
       </c>
       <c r="S24" t="n">
-        <v>2.98</v>
+        <v>2.6</v>
       </c>
       <c r="T24" t="n">
-        <v>2.74</v>
+        <v>3.04</v>
       </c>
       <c r="U24" t="n">
-        <v>1.42</v>
+        <v>1.33</v>
       </c>
       <c r="V24" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="W24" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="X24" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="AB24" t="n">
         <v>1.21</v>
       </c>
-      <c r="X24" t="n">
-        <v>3.66</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>1.35</v>
-      </c>
       <c r="AC24" t="n">
-        <v>1.73</v>
+        <v>1.86</v>
       </c>
       <c r="AD24" t="n">
-        <v>2.03</v>
+        <v>1.8</v>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
@@ -3574,10 +3574,10 @@
         </is>
       </c>
       <c r="AG24" t="n">
-        <v>1.26</v>
+        <v>1.32</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.24</v>
+        <v>1.31</v>
       </c>
       <c r="AI24" t="n">
         <v>0</v>
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Calcio Padova</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,61 +3636,61 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.18</v>
+        <v>2.59</v>
       </c>
       <c r="M25" t="n">
-        <v>3.32</v>
+        <v>3.01</v>
       </c>
       <c r="N25" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="O25" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="P25" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q25" t="n">
         <v>3.4</v>
       </c>
-      <c r="O25" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="P25" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>4.24</v>
-      </c>
       <c r="R25" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="S25" t="n">
-        <v>2.51</v>
+        <v>2.48</v>
       </c>
       <c r="T25" t="n">
-        <v>3.08</v>
+        <v>3.14</v>
       </c>
       <c r="U25" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="V25" t="n">
         <v>1.03</v>
       </c>
       <c r="W25" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="X25" t="n">
-        <v>2.78</v>
+        <v>2.7</v>
       </c>
       <c r="Y25" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="Z25" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AA25" t="n">
-        <v>4.2</v>
+        <v>3.95</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
@@ -3703,10 +3703,10 @@
         </is>
       </c>
       <c r="AG25" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.69</v>
+        <v>1.48</v>
       </c>
       <c r="AI25" t="n">
         <v>0</v>
@@ -3729,7 +3729,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,61 +3765,61 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.05</v>
+        <v>3.25</v>
       </c>
       <c r="M26" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="N26" t="n">
-        <v>3.5</v>
+        <v>2.02</v>
       </c>
       <c r="O26" t="n">
-        <v>2.81</v>
+        <v>3.9</v>
       </c>
       <c r="P26" t="n">
-        <v>2.04</v>
+        <v>2.25</v>
       </c>
       <c r="Q26" t="n">
-        <v>4.19</v>
+        <v>2.45</v>
       </c>
       <c r="R26" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S26" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="U26" t="n">
         <v>1.42</v>
       </c>
-      <c r="S26" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="T26" t="n">
-        <v>3</v>
-      </c>
-      <c r="U26" t="n">
-        <v>1.31</v>
-      </c>
       <c r="V26" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="W26" t="n">
-        <v>1.34</v>
+        <v>1.21</v>
       </c>
       <c r="X26" t="n">
-        <v>2.88</v>
+        <v>3.66</v>
       </c>
       <c r="Y26" t="n">
-        <v>2.2</v>
+        <v>1.73</v>
       </c>
       <c r="Z26" t="n">
-        <v>1.69</v>
+        <v>2</v>
       </c>
       <c r="AA26" t="n">
-        <v>3.82</v>
+        <v>2.92</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.2</v>
+        <v>1.35</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.87</v>
+        <v>1.73</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.85</v>
+        <v>2.03</v>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
@@ -3832,10 +3832,10 @@
         </is>
       </c>
       <c r="AG26" t="n">
-        <v>1.32</v>
+        <v>1.26</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.7</v>
+        <v>1.24</v>
       </c>
       <c r="AI26" t="n">
         <v>0</v>
@@ -3858,7 +3858,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,61 +3894,61 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.45</v>
+        <v>2.19</v>
       </c>
       <c r="M27" t="n">
-        <v>4.4</v>
+        <v>3.47</v>
       </c>
       <c r="N27" t="n">
-        <v>6.4</v>
+        <v>3.08</v>
       </c>
       <c r="O27" t="n">
-        <v>1.93</v>
+        <v>2.88</v>
       </c>
       <c r="P27" t="n">
-        <v>2.45</v>
+        <v>2.08</v>
       </c>
       <c r="Q27" t="n">
-        <v>5.5</v>
+        <v>3.88</v>
       </c>
       <c r="R27" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S27" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="T27" t="n">
+        <v>3</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="V27" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W27" t="n">
         <v>1.28</v>
       </c>
-      <c r="S27" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="T27" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="U27" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="V27" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W27" t="n">
-        <v>1.17</v>
-      </c>
       <c r="X27" t="n">
-        <v>4.2</v>
+        <v>3.16</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.65</v>
+        <v>1.98</v>
       </c>
       <c r="Z27" t="n">
-        <v>2.1</v>
+        <v>1.77</v>
       </c>
       <c r="AA27" t="n">
-        <v>2.63</v>
+        <v>3.48</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.4</v>
+        <v>1.26</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.91</v>
+        <v>1.94</v>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
@@ -3961,10 +3961,10 @@
         </is>
       </c>
       <c r="AG27" t="n">
-        <v>1.11</v>
+        <v>1.32</v>
       </c>
       <c r="AH27" t="n">
-        <v>2.45</v>
+        <v>1.68</v>
       </c>
       <c r="AI27" t="n">
         <v>0</v>
@@ -3987,7 +3987,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,61 +4023,61 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.36</v>
+        <v>1.4</v>
       </c>
       <c r="M28" t="n">
-        <v>3.38</v>
+        <v>4.2</v>
       </c>
       <c r="N28" t="n">
-        <v>2.86</v>
+        <v>5.9</v>
       </c>
       <c r="O28" t="n">
-        <v>2.73</v>
+        <v>1.97</v>
       </c>
       <c r="P28" t="n">
-        <v>2.27</v>
+        <v>2.4</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.6</v>
+        <v>6.05</v>
       </c>
       <c r="R28" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="S28" t="n">
-        <v>3.14</v>
+        <v>3.21</v>
       </c>
       <c r="T28" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="U28" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="V28" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W28" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="X28" t="n">
         <v>4.05</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.89</v>
+        <v>1.65</v>
       </c>
       <c r="Z28" t="n">
-        <v>1.85</v>
+        <v>2.1</v>
       </c>
       <c r="AA28" t="n">
-        <v>2.56</v>
+        <v>2.63</v>
       </c>
       <c r="AB28" t="n">
         <v>1.42</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.56</v>
+        <v>1.84</v>
       </c>
       <c r="AD28" t="n">
-        <v>2.3</v>
+        <v>1.87</v>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
@@ -4090,10 +4090,10 @@
         </is>
       </c>
       <c r="AG28" t="n">
-        <v>1.28</v>
+        <v>1.21</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.67</v>
+        <v>2.64</v>
       </c>
       <c r="AI28" t="n">
         <v>0</v>
@@ -4116,7 +4116,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,61 +4152,61 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>3.06</v>
+        <v>1.65</v>
       </c>
       <c r="M29" t="n">
-        <v>3.19</v>
+        <v>3.82</v>
       </c>
       <c r="N29" t="n">
-        <v>2.08</v>
+        <v>4.9</v>
       </c>
       <c r="O29" t="n">
-        <v>3.6</v>
+        <v>2.23</v>
       </c>
       <c r="P29" t="n">
-        <v>2.05</v>
+        <v>2.22</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.92</v>
+        <v>5.36</v>
       </c>
       <c r="R29" t="n">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="S29" t="n">
-        <v>2.75</v>
+        <v>3.14</v>
       </c>
       <c r="T29" t="n">
-        <v>2.8</v>
+        <v>2.67</v>
       </c>
       <c r="U29" t="n">
-        <v>1.37</v>
+        <v>1.43</v>
       </c>
       <c r="V29" t="n">
         <v>1.02</v>
       </c>
       <c r="W29" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="X29" t="n">
-        <v>3.25</v>
+        <v>3.75</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="Z29" t="n">
-        <v>1.86</v>
+        <v>1.91</v>
       </c>
       <c r="AA29" t="n">
-        <v>3.55</v>
+        <v>3.02</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.76</v>
+        <v>1.87</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
@@ -4219,10 +4219,10 @@
         </is>
       </c>
       <c r="AG29" t="n">
-        <v>1.62</v>
+        <v>1.16</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.37</v>
+        <v>2.25</v>
       </c>
       <c r="AI29" t="n">
         <v>0</v>
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,61 +4281,61 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.19</v>
+        <v>2.49</v>
       </c>
       <c r="M30" t="n">
-        <v>3.47</v>
+        <v>3.29</v>
       </c>
       <c r="N30" t="n">
-        <v>3.08</v>
+        <v>2.74</v>
       </c>
       <c r="O30" t="n">
-        <v>2.82</v>
+        <v>3.18</v>
       </c>
       <c r="P30" t="n">
-        <v>2.1</v>
+        <v>2.01</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.9</v>
+        <v>3.4</v>
       </c>
       <c r="R30" t="n">
-        <v>1.37</v>
+        <v>1.44</v>
       </c>
       <c r="S30" t="n">
-        <v>2.75</v>
+        <v>2.66</v>
       </c>
       <c r="T30" t="n">
-        <v>2.75</v>
+        <v>3.14</v>
       </c>
       <c r="U30" t="n">
-        <v>1.41</v>
+        <v>1.29</v>
       </c>
       <c r="V30" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="W30" t="n">
-        <v>1.28</v>
+        <v>1.38</v>
       </c>
       <c r="X30" t="n">
-        <v>3.2</v>
+        <v>2.95</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.98</v>
+        <v>2.2</v>
       </c>
       <c r="Z30" t="n">
-        <v>1.77</v>
+        <v>1.68</v>
       </c>
       <c r="AA30" t="n">
-        <v>3.4</v>
+        <v>3.95</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AC30" t="n">
-        <v>1.76</v>
+        <v>1.87</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.97</v>
+        <v>1.83</v>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
@@ -4348,10 +4348,10 @@
         </is>
       </c>
       <c r="AG30" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.67</v>
+        <v>1.53</v>
       </c>
       <c r="AI30" t="n">
         <v>0</v>
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,61 +4410,61 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>3.2</v>
+        <v>1.36</v>
       </c>
       <c r="M31" t="n">
-        <v>3.3</v>
+        <v>4.75</v>
       </c>
       <c r="N31" t="n">
-        <v>2.2</v>
+        <v>8</v>
       </c>
       <c r="O31" t="n">
-        <v>3.81</v>
+        <v>1.86</v>
       </c>
       <c r="P31" t="n">
-        <v>2.15</v>
+        <v>2.38</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.8</v>
+        <v>7</v>
       </c>
       <c r="R31" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="S31" t="n">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="T31" t="n">
-        <v>2.71</v>
+        <v>2.55</v>
       </c>
       <c r="U31" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="V31" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="W31" t="n">
-        <v>1.28</v>
+        <v>1.23</v>
       </c>
       <c r="X31" t="n">
-        <v>3.48</v>
+        <v>3.7</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.77</v>
+        <v>1.85</v>
       </c>
       <c r="Z31" t="n">
-        <v>1.98</v>
+        <v>1.89</v>
       </c>
       <c r="AA31" t="n">
-        <v>3.08</v>
+        <v>2.97</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.69</v>
+        <v>2.11</v>
       </c>
       <c r="AD31" t="n">
-        <v>2.07</v>
+        <v>1.68</v>
       </c>
       <c r="AE31" t="inlineStr">
         <is>
@@ -4477,10 +4477,10 @@
         </is>
       </c>
       <c r="AG31" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.36</v>
+        <v>3.01</v>
       </c>
       <c r="AI31" t="n">
         <v>0</v>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,61 +4539,61 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.65</v>
+        <v>3.06</v>
       </c>
       <c r="M32" t="n">
-        <v>3.82</v>
+        <v>3.19</v>
       </c>
       <c r="N32" t="n">
-        <v>4.9</v>
+        <v>2.08</v>
       </c>
       <c r="O32" t="n">
-        <v>2.15</v>
+        <v>3.6</v>
       </c>
       <c r="P32" t="n">
-        <v>2.38</v>
+        <v>2.1</v>
       </c>
       <c r="Q32" t="n">
-        <v>5.03</v>
+        <v>2.74</v>
       </c>
       <c r="R32" t="n">
-        <v>1.28</v>
+        <v>1.38</v>
       </c>
       <c r="S32" t="n">
-        <v>3.2</v>
+        <v>2.84</v>
       </c>
       <c r="T32" t="n">
-        <v>2.42</v>
+        <v>2.8</v>
       </c>
       <c r="U32" t="n">
-        <v>1.47</v>
+        <v>1.37</v>
       </c>
       <c r="V32" t="n">
         <v>1.01</v>
       </c>
       <c r="W32" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="X32" t="n">
-        <v>4.1</v>
+        <v>3.45</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="Z32" t="n">
-        <v>1.91</v>
+        <v>1.86</v>
       </c>
       <c r="AA32" t="n">
-        <v>2.62</v>
+        <v>3.2</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AC32" t="n">
         <v>1.7</v>
       </c>
       <c r="AD32" t="n">
-        <v>2.05</v>
+        <v>2.03</v>
       </c>
       <c r="AE32" t="inlineStr">
         <is>
@@ -4606,10 +4606,10 @@
         </is>
       </c>
       <c r="AG32" t="n">
-        <v>1.17</v>
+        <v>1.3</v>
       </c>
       <c r="AH32" t="n">
-        <v>2.3</v>
+        <v>1.33</v>
       </c>
       <c r="AI32" t="n">
         <v>0</v>
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,61 +4668,61 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.49</v>
+        <v>3.2</v>
       </c>
       <c r="M33" t="n">
-        <v>3.29</v>
+        <v>3.3</v>
       </c>
       <c r="N33" t="n">
-        <v>2.74</v>
+        <v>2.2</v>
       </c>
       <c r="O33" t="n">
-        <v>3.18</v>
+        <v>3.58</v>
       </c>
       <c r="P33" t="n">
-        <v>2.02</v>
+        <v>2.11</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.54</v>
+        <v>2.97</v>
       </c>
       <c r="R33" t="n">
-        <v>1.43</v>
+        <v>1.35</v>
       </c>
       <c r="S33" t="n">
-        <v>2.54</v>
+        <v>3.09</v>
       </c>
       <c r="T33" t="n">
-        <v>3.08</v>
+        <v>2.6</v>
       </c>
       <c r="U33" t="n">
-        <v>1.3</v>
+        <v>1.39</v>
       </c>
       <c r="V33" t="n">
         <v>1.02</v>
       </c>
       <c r="W33" t="n">
-        <v>1.35</v>
+        <v>1.23</v>
       </c>
       <c r="X33" t="n">
-        <v>2.95</v>
+        <v>3.74</v>
       </c>
       <c r="Y33" t="n">
-        <v>2.2</v>
+        <v>1.77</v>
       </c>
       <c r="Z33" t="n">
-        <v>1.68</v>
+        <v>1.98</v>
       </c>
       <c r="AA33" t="n">
-        <v>3.92</v>
+        <v>3.17</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.19</v>
+        <v>1.31</v>
       </c>
       <c r="AC33" t="n">
-        <v>1.87</v>
+        <v>1.66</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.85</v>
+        <v>2.12</v>
       </c>
       <c r="AE33" t="inlineStr">
         <is>
@@ -4735,10 +4735,10 @@
         </is>
       </c>
       <c r="AG33" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.52</v>
+        <v>1.43</v>
       </c>
       <c r="AI33" t="n">
         <v>0</v>
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,61 +4797,61 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.36</v>
+        <v>1.9</v>
       </c>
       <c r="M34" t="n">
-        <v>4.75</v>
+        <v>3.4</v>
       </c>
       <c r="N34" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="O34" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="P34" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>4.72</v>
+      </c>
+      <c r="R34" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S34" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="T34" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="V34" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W34" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="X34" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="Z34" t="n">
         <v>1.77</v>
       </c>
-      <c r="P34" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>7</v>
-      </c>
-      <c r="R34" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S34" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="T34" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="U34" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="V34" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W34" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="X34" t="n">
-        <v>4</v>
-      </c>
-      <c r="Y34" t="n">
+      <c r="AA34" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AC34" t="n">
         <v>1.85</v>
       </c>
-      <c r="Z34" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AA34" t="n">
-        <v>3</v>
-      </c>
-      <c r="AB34" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AC34" t="n">
-        <v>2.09</v>
-      </c>
       <c r="AD34" t="n">
-        <v>1.68</v>
+        <v>1.85</v>
       </c>
       <c r="AE34" t="inlineStr">
         <is>
@@ -4864,10 +4864,10 @@
         </is>
       </c>
       <c r="AG34" t="n">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="AH34" t="n">
-        <v>3.38</v>
+        <v>1.91</v>
       </c>
       <c r="AI34" t="n">
         <v>0</v>
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,61 +4926,61 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>1.9</v>
+        <v>2.36</v>
       </c>
       <c r="M35" t="n">
-        <v>3.4</v>
+        <v>3.38</v>
       </c>
       <c r="N35" t="n">
-        <v>4</v>
+        <v>2.86</v>
       </c>
       <c r="O35" t="n">
-        <v>2.45</v>
+        <v>3.05</v>
       </c>
       <c r="P35" t="n">
-        <v>2.13</v>
+        <v>2.21</v>
       </c>
       <c r="Q35" t="n">
-        <v>4.2</v>
+        <v>3.34</v>
       </c>
       <c r="R35" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="S35" t="n">
-        <v>2.78</v>
+        <v>2.84</v>
       </c>
       <c r="T35" t="n">
-        <v>2.84</v>
+        <v>2.67</v>
       </c>
       <c r="U35" t="n">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="V35" t="n">
         <v>1.01</v>
       </c>
       <c r="W35" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="X35" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.98</v>
+        <v>1.89</v>
       </c>
       <c r="Z35" t="n">
-        <v>1.77</v>
+        <v>1.85</v>
       </c>
       <c r="AA35" t="n">
-        <v>3.4</v>
+        <v>3.08</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="AC35" t="n">
-        <v>1.82</v>
+        <v>1.62</v>
       </c>
       <c r="AD35" t="n">
-        <v>1.9</v>
+        <v>2.16</v>
       </c>
       <c r="AE35" t="inlineStr">
         <is>
@@ -4993,10 +4993,10 @@
         </is>
       </c>
       <c r="AG35" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="AI35" t="n">
         <v>0</v>
@@ -5019,7 +5019,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,61 +5055,61 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>3</v>
+        <v>2.4</v>
       </c>
       <c r="M36" t="n">
-        <v>3.83</v>
+        <v>3.39</v>
       </c>
       <c r="N36" t="n">
-        <v>2.1</v>
+        <v>2.79</v>
       </c>
       <c r="O36" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="S36" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="T36" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="U36" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="V36" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="W36" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="X36" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Y36" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="Z36" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AA36" t="n">
-        <v>2.25</v>
+        <v>4.65</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.65</v>
+        <v>1.17</v>
       </c>
       <c r="AC36" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AD36" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AE36" t="inlineStr">
         <is>
@@ -5122,10 +5122,10 @@
         </is>
       </c>
       <c r="AG36" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AH36" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AI36" t="n">
         <v>0</v>
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Olympique Marseille</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,61 +5184,61 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>1.56</v>
+        <v>3</v>
       </c>
       <c r="M37" t="n">
-        <v>4.3</v>
+        <v>3.83</v>
       </c>
       <c r="N37" t="n">
-        <v>5.1</v>
+        <v>2.1</v>
       </c>
       <c r="O37" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="S37" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="T37" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="U37" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="V37" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W37" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="X37" t="n">
-        <v>4.55</v>
+        <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Z37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA37" t="n">
         <v>2.25</v>
       </c>
-      <c r="AA37" t="n">
-        <v>2.4</v>
-      </c>
       <c r="AB37" t="n">
-        <v>1.52</v>
+        <v>1.65</v>
       </c>
       <c r="AC37" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AD37" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AE37" t="inlineStr">
         <is>
@@ -5251,10 +5251,10 @@
         </is>
       </c>
       <c r="AG37" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AH37" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="AI37" t="n">
         <v>0</v>
@@ -5322,34 +5322,34 @@
         <v>4.9</v>
       </c>
       <c r="O38" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S38" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="T38" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="U38" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="V38" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W38" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="X38" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="Y38" t="n">
         <v>1.68</v>
@@ -5358,16 +5358,16 @@
         <v>2.18</v>
       </c>
       <c r="AA38" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AB38" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AC38" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AD38" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AE38" t="inlineStr">
         <is>
@@ -5380,10 +5380,10 @@
         </is>
       </c>
       <c r="AG38" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AH38" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AI38" t="n">
         <v>0</v>
@@ -5406,7 +5406,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Kariobangi Sharks</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>KCB</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,61 +5442,61 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="O39" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="R39" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="S39" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="T39" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="U39" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="V39" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W39" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="X39" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Y39" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z39" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AA39" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AB39" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC39" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AD39" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AE39" t="inlineStr">
         <is>
@@ -5509,10 +5509,10 @@
         </is>
       </c>
       <c r="AG39" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AH39" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AI39" t="n">
         <v>0</v>
@@ -5535,7 +5535,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,61 +5571,61 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2.4</v>
+        <v>1.56</v>
       </c>
       <c r="M40" t="n">
-        <v>3.39</v>
+        <v>4.1</v>
       </c>
       <c r="N40" t="n">
-        <v>2.79</v>
+        <v>5.4</v>
       </c>
       <c r="O40" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="R40" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="S40" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="T40" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="U40" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="V40" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="W40" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="X40" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>2.52</v>
+        <v>1.63</v>
       </c>
       <c r="Z40" t="n">
-        <v>1.52</v>
+        <v>2.25</v>
       </c>
       <c r="AA40" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AC40" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AD40" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AE40" t="inlineStr">
         <is>
@@ -5638,10 +5638,10 @@
         </is>
       </c>
       <c r="AG40" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AH40" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AI40" t="n">
         <v>0</v>
@@ -5664,7 +5664,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Kariobangi Sharks</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>KCB</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,13 +5700,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5739,16 +5739,16 @@
         <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="Z41" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC41" t="n">
         <v>0</v>
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,13 +5829,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>1.35</v>
+        <v>15</v>
       </c>
       <c r="M42" t="n">
-        <v>5.3</v>
+        <v>7.6</v>
       </c>
       <c r="N42" t="n">
-        <v>7</v>
+        <v>1.15</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5868,16 +5868,16 @@
         <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.6</v>
+        <v>1.44</v>
       </c>
       <c r="Z42" t="n">
-        <v>2.35</v>
+        <v>2.75</v>
       </c>
       <c r="AA42" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB42" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC42" t="n">
         <v>0</v>
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5958,61 +5958,61 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>1.56</v>
+        <v>4.3</v>
       </c>
       <c r="M43" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="N43" t="n">
-        <v>5.4</v>
+        <v>1.64</v>
       </c>
       <c r="O43" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="P43" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Q43" t="n">
         <v>2</v>
       </c>
-      <c r="P43" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="Q43" t="n">
-        <v>5.2</v>
-      </c>
       <c r="R43" t="n">
-        <v>1.28</v>
+        <v>1.21</v>
       </c>
       <c r="S43" t="n">
-        <v>3.45</v>
+        <v>3.8</v>
       </c>
       <c r="T43" t="n">
-        <v>2.46</v>
+        <v>2.05</v>
       </c>
       <c r="U43" t="n">
-        <v>1.58</v>
+        <v>1.75</v>
       </c>
       <c r="V43" t="n">
         <v>1.01</v>
       </c>
       <c r="W43" t="n">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="X43" t="n">
-        <v>4.33</v>
+        <v>5.35</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.63</v>
+        <v>1.44</v>
       </c>
       <c r="Z43" t="n">
-        <v>2.25</v>
+        <v>2.75</v>
       </c>
       <c r="AA43" t="n">
-        <v>2.54</v>
+        <v>2.15</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.52</v>
+        <v>1.7</v>
       </c>
       <c r="AC43" t="n">
-        <v>1.68</v>
+        <v>1.5</v>
       </c>
       <c r="AD43" t="n">
-        <v>2.19</v>
+        <v>2.45</v>
       </c>
       <c r="AE43" t="inlineStr">
         <is>
@@ -6025,10 +6025,10 @@
         </is>
       </c>
       <c r="AG43" t="n">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="AH43" t="n">
-        <v>2.41</v>
+        <v>1.22</v>
       </c>
       <c r="AI43" t="n">
         <v>0</v>
@@ -6061,12 +6061,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Olympique Marseille</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6087,77 +6087,77 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>15</v>
+        <v>1.56</v>
       </c>
       <c r="M44" t="n">
-        <v>7.6</v>
+        <v>4.3</v>
       </c>
       <c r="N44" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="O44" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="P44" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="R44" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="S44" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="T44" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="U44" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="V44" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W44" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="X44" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="Y44" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="Z44" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AA44" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AB44" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AC44" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AD44" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AE44" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF44" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG44" t="n">
         <v>1.15</v>
       </c>
-      <c r="O44" t="n">
-        <v>0</v>
-      </c>
-      <c r="P44" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q44" t="n">
-        <v>0</v>
-      </c>
-      <c r="R44" t="n">
-        <v>0</v>
-      </c>
-      <c r="S44" t="n">
-        <v>0</v>
-      </c>
-      <c r="T44" t="n">
-        <v>0</v>
-      </c>
-      <c r="U44" t="n">
-        <v>0</v>
-      </c>
-      <c r="V44" t="n">
-        <v>0</v>
-      </c>
-      <c r="W44" t="n">
-        <v>0</v>
-      </c>
-      <c r="X44" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y44" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="Z44" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AA44" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AB44" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AC44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE44" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF44" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG44" t="n">
-        <v>0</v>
-      </c>
       <c r="AH44" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AI44" t="n">
         <v>0</v>
@@ -6345,13 +6345,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>1.57</v>
+        <v>1.52</v>
       </c>
       <c r="M46" t="n">
+        <v>4</v>
+      </c>
+      <c r="N46" t="n">
         <v>4.7</v>
-      </c>
-      <c r="N46" t="n">
-        <v>4.91</v>
       </c>
       <c r="O46" t="n">
         <v>1.98</v>
@@ -6390,10 +6390,10 @@
         <v>3.1</v>
       </c>
       <c r="AA46" t="n">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AC46" t="n">
         <v>1.4</v>
@@ -6474,13 +6474,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="M47" t="n">
-        <v>4.44</v>
+        <v>4.2</v>
       </c>
       <c r="N47" t="n">
-        <v>6.75</v>
+        <v>6</v>
       </c>
       <c r="O47" t="n">
         <v>1.95</v>
@@ -6513,10 +6513,10 @@
         <v>3.4</v>
       </c>
       <c r="Y47" t="n">
-        <v>1.9</v>
+        <v>1.86</v>
       </c>
       <c r="Z47" t="n">
-        <v>1.92</v>
+        <v>1.84</v>
       </c>
       <c r="AA47" t="n">
         <v>3.3</v>
@@ -6603,13 +6603,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>2.05</v>
+        <v>1.93</v>
       </c>
       <c r="M48" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="N48" t="n">
-        <v>3.8</v>
+        <v>3.57</v>
       </c>
       <c r="O48" t="n">
         <v>2.66</v>
@@ -6642,10 +6642,10 @@
         <v>2.95</v>
       </c>
       <c r="Y48" t="n">
-        <v>2.49</v>
+        <v>2.12</v>
       </c>
       <c r="Z48" t="n">
-        <v>1.56</v>
+        <v>1.64</v>
       </c>
       <c r="AA48" t="n">
         <v>4.73</v>

--- a/jogos_2025-09-30.xlsx
+++ b/jogos_2025-09-30.xlsx
@@ -757,27 +757,27 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Sogdiana</t>
+          <t>Kariobangi Sharks</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>KCB</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -798,13 +798,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -837,10 +837,10 @@
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
         <v>0</v>
@@ -877,7 +877,7 @@
         <v>0</v>
       </c>
       <c r="AK3" s="3" t="n">
-        <v>45930.45833333334</v>
+        <v>45930.41666666666</v>
       </c>
     </row>
     <row r="4">
@@ -1015,27 +1015,27 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Botev Plovdiv</t>
+          <t>Sogdiana</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1056,61 +1056,61 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>4.6</v>
+        <v>2.95</v>
       </c>
       <c r="M5" t="n">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="N5" t="n">
-        <v>1.82</v>
+        <v>2.4</v>
       </c>
       <c r="O5" t="n">
-        <v>5.78</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>3.26</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.25</v>
+        <v>2.08</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AA5" t="n">
-        <v>3.43</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
@@ -1123,19 +1123,19 @@
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AI5" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AK5" s="3" t="n">
-        <v>45930.47916666666</v>
+        <v>45930.45833333334</v>
       </c>
     </row>
     <row r="6">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Botev Plovdiv</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1185,61 +1185,61 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.86</v>
+        <v>4.6</v>
       </c>
       <c r="M6" t="n">
-        <v>3.84</v>
+        <v>3.5</v>
       </c>
       <c r="N6" t="n">
-        <v>3.7</v>
+        <v>1.82</v>
       </c>
       <c r="O6" t="n">
-        <v>2.4</v>
+        <v>5.78</v>
       </c>
       <c r="P6" t="n">
-        <v>2.4</v>
+        <v>2.26</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.95</v>
+        <v>2.18</v>
       </c>
       <c r="R6" t="n">
-        <v>1.29</v>
+        <v>1.42</v>
       </c>
       <c r="S6" t="n">
-        <v>3.4</v>
+        <v>2.7</v>
       </c>
       <c r="T6" t="n">
-        <v>2.4</v>
+        <v>2.89</v>
       </c>
       <c r="U6" t="n">
-        <v>1.54</v>
+        <v>1.37</v>
       </c>
       <c r="V6" t="n">
         <v>1.02</v>
       </c>
       <c r="W6" t="n">
-        <v>1.18</v>
+        <v>1.29</v>
       </c>
       <c r="X6" t="n">
-        <v>4.6</v>
+        <v>3.26</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.7</v>
+        <v>2.25</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.15</v>
+        <v>1.65</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.75</v>
+        <v>3.43</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.47</v>
+        <v>1.29</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.58</v>
+        <v>1.95</v>
       </c>
       <c r="AD6" t="n">
-        <v>2.25</v>
+        <v>1.71</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
@@ -1252,19 +1252,19 @@
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.85</v>
+        <v>1.16</v>
       </c>
       <c r="AI6" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AK6" s="3" t="n">
-        <v>45930.57291666666</v>
+        <v>45930.47916666666</v>
       </c>
     </row>
     <row r="7">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Police</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Ulinzi Stars</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1314,13 +1314,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>8.9</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1353,16 +1353,16 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1393,7 +1393,7 @@
         <v>0</v>
       </c>
       <c r="AK7" s="3" t="n">
-        <v>45930.57291666666</v>
+        <v>45930.5</v>
       </c>
     </row>
     <row r="8">
@@ -1402,12 +1402,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Saarbrucken</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>MSV Duisburg</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,61 +1443,61 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="M8" t="n">
-        <v>3.8</v>
+        <v>3.84</v>
       </c>
       <c r="N8" t="n">
-        <v>3.12</v>
+        <v>3.7</v>
       </c>
       <c r="O8" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.98</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>3.26</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>4.45</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.59</v>
+        <v>1.7</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.22</v>
+        <v>2.15</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AI8" t="n">
         <v>0</v>
@@ -1522,7 +1522,7 @@
         <v>0</v>
       </c>
       <c r="AK8" s="3" t="n">
-        <v>45930.58333333334</v>
+        <v>45930.57291666666</v>
       </c>
     </row>
     <row r="9">
@@ -1531,12 +1531,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Wehen Wiesbaden</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,61 +1572,61 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.9</v>
+        <v>19</v>
       </c>
       <c r="M9" t="n">
-        <v>3.6</v>
+        <v>8.9</v>
       </c>
       <c r="N9" t="n">
-        <v>2.18</v>
+        <v>1.11</v>
       </c>
       <c r="O9" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>3.26</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.53</v>
+        <v>1.3</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.25</v>
+        <v>3.4</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.33</v>
+        <v>1.8</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.42</v>
+        <v>1.94</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
@@ -1651,7 +1651,7 @@
         <v>0</v>
       </c>
       <c r="AK9" s="3" t="n">
-        <v>45930.58333333334</v>
+        <v>45930.57291666666</v>
       </c>
     </row>
     <row r="10">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,61 +1701,61 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.26</v>
+        <v>1.57</v>
       </c>
       <c r="M10" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="N10" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="O10" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="P10" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>3.96</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S10" t="n">
+        <v>3.66</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X10" t="n">
         <v>5.1</v>
       </c>
-      <c r="N10" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="O10" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="P10" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S10" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="T10" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="V10" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="X10" t="n">
-        <v>5</v>
-      </c>
       <c r="Y10" t="n">
-        <v>1.47</v>
+        <v>1.43</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.5</v>
+        <v>2.47</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.17</v>
+        <v>2.21</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.73</v>
+        <v>1.55</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.95</v>
+        <v>2.32</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -1768,10 +1768,10 @@
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="AH10" t="n">
-        <v>2.75</v>
+        <v>2.4</v>
       </c>
       <c r="AI10" t="n">
         <v>0</v>
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,61 +1830,61 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.56</v>
+        <v>1.39</v>
       </c>
       <c r="M11" t="n">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="N11" t="n">
-        <v>4.2</v>
+        <v>6.8</v>
       </c>
       <c r="O11" t="n">
-        <v>1.95</v>
+        <v>1.83</v>
       </c>
       <c r="P11" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S11" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="X11" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AA11" t="n">
         <v>2.5</v>
       </c>
-      <c r="Q11" t="n">
-        <v>4.95</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="S11" t="n">
-        <v>3.66</v>
-      </c>
-      <c r="T11" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="V11" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X11" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>1.92</v>
-      </c>
       <c r="AB11" t="n">
-        <v>1.78</v>
+        <v>1.5</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.5</v>
+        <v>1.85</v>
       </c>
       <c r="AD11" t="n">
-        <v>2.3</v>
+        <v>1.91</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -1897,10 +1897,10 @@
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AH11" t="n">
-        <v>2.4</v>
+        <v>2.78</v>
       </c>
       <c r="AI11" t="n">
         <v>0</v>
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Hansa Rostock</t>
+          <t>Havelse</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>Waldhof Mannheim</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,22 +1959,22 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.98</v>
+        <v>3.4</v>
       </c>
       <c r="M12" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="N12" t="n">
-        <v>3.8</v>
+        <v>1.92</v>
       </c>
       <c r="O12" t="n">
-        <v>2.28</v>
+        <v>4.12</v>
       </c>
       <c r="P12" t="n">
-        <v>2.23</v>
+        <v>2.24</v>
       </c>
       <c r="Q12" t="n">
-        <v>4.08</v>
+        <v>2.4</v>
       </c>
       <c r="R12" t="n">
         <v>1.3</v>
@@ -1983,37 +1983,37 @@
         <v>3.2</v>
       </c>
       <c r="T12" t="n">
-        <v>2.28</v>
+        <v>2.23</v>
       </c>
       <c r="U12" t="n">
-        <v>1.54</v>
+        <v>1.49</v>
       </c>
       <c r="V12" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W12" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="X12" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.55</v>
+        <v>2.45</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.58</v>
+        <v>1.5</v>
       </c>
       <c r="AD12" t="n">
-        <v>2.21</v>
+        <v>2.17</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -2026,10 +2026,10 @@
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.79</v>
+        <v>1.24</v>
       </c>
       <c r="AI12" t="n">
         <v>0</v>
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Havelse</t>
+          <t>Saarbrucken</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Waldhof Mannheim</t>
+          <t>MSV Duisburg</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,61 +2217,61 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>3.4</v>
+        <v>1.87</v>
       </c>
       <c r="M14" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="N14" t="n">
-        <v>1.92</v>
+        <v>3.12</v>
       </c>
       <c r="O14" t="n">
-        <v>4.12</v>
+        <v>2.51</v>
       </c>
       <c r="P14" t="n">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.4</v>
+        <v>3.98</v>
       </c>
       <c r="R14" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="S14" t="n">
-        <v>3.2</v>
+        <v>3.26</v>
       </c>
       <c r="T14" t="n">
-        <v>2.23</v>
+        <v>2.36</v>
       </c>
       <c r="U14" t="n">
-        <v>1.49</v>
+        <v>1.52</v>
       </c>
       <c r="V14" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W14" t="n">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="X14" t="n">
-        <v>4.1</v>
+        <v>4.45</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.12</v>
+        <v>2.22</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.45</v>
+        <v>2.42</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="AD14" t="n">
-        <v>2.17</v>
+        <v>2.36</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
@@ -2284,10 +2284,10 @@
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.24</v>
+        <v>1.74</v>
       </c>
       <c r="AI14" t="n">
         <v>0</v>
@@ -2305,12 +2305,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Wehen Wiesbaden</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,61 +2346,61 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.15</v>
+        <v>2.9</v>
       </c>
       <c r="M15" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="N15" t="n">
-        <v>2.88</v>
+        <v>2.18</v>
       </c>
       <c r="O15" t="n">
-        <v>2.6</v>
+        <v>3.34</v>
       </c>
       <c r="P15" t="n">
-        <v>2.4</v>
+        <v>2.21</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.35</v>
+        <v>2.83</v>
       </c>
       <c r="R15" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="S15" t="n">
-        <v>3.7</v>
+        <v>3.26</v>
       </c>
       <c r="T15" t="n">
-        <v>2.21</v>
+        <v>2.39</v>
       </c>
       <c r="U15" t="n">
-        <v>1.62</v>
+        <v>1.51</v>
       </c>
       <c r="V15" t="n">
         <v>1.02</v>
       </c>
       <c r="W15" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="X15" t="n">
-        <v>4.8</v>
+        <v>4.4</v>
       </c>
       <c r="Y15" t="n">
         <v>1.53</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.28</v>
+        <v>2.33</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.6</v>
+        <v>1.42</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="AD15" t="n">
-        <v>2.59</v>
+        <v>2.36</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
@@ -2413,10 +2413,10 @@
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>1.38</v>
+        <v>1.25</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.68</v>
+        <v>1.4</v>
       </c>
       <c r="AI15" t="n">
         <v>0</v>
@@ -2425,7 +2425,7 @@
         <v>0</v>
       </c>
       <c r="AK15" s="3" t="n">
-        <v>45930.625</v>
+        <v>45930.58333333334</v>
       </c>
     </row>
     <row r="16">
@@ -2434,12 +2434,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Hansa Rostock</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,61 +2475,61 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="O16" t="n">
-        <v>1.62</v>
+        <v>2.28</v>
       </c>
       <c r="P16" t="n">
-        <v>2.68</v>
+        <v>2.23</v>
       </c>
       <c r="Q16" t="n">
-        <v>6.49</v>
+        <v>4.08</v>
       </c>
       <c r="R16" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="S16" t="n">
-        <v>3.88</v>
+        <v>3.2</v>
       </c>
       <c r="T16" t="n">
-        <v>2.04</v>
+        <v>2.28</v>
       </c>
       <c r="U16" t="n">
-        <v>1.69</v>
+        <v>1.54</v>
       </c>
       <c r="V16" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W16" t="n">
-        <v>1.08</v>
+        <v>1.17</v>
       </c>
       <c r="X16" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.46</v>
+        <v>1.61</v>
       </c>
       <c r="Z16" t="n">
-        <v>2.6</v>
+        <v>2.1</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.09</v>
+        <v>2.55</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.71</v>
+        <v>1.41</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.66</v>
+        <v>1.58</v>
       </c>
       <c r="AD16" t="n">
-        <v>2.12</v>
+        <v>2.21</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
@@ -2542,10 +2542,10 @@
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>1.07</v>
+        <v>1.3</v>
       </c>
       <c r="AH16" t="n">
-        <v>3.15</v>
+        <v>1.79</v>
       </c>
       <c r="AI16" t="n">
         <v>0</v>
@@ -2554,7 +2554,7 @@
         <v>0</v>
       </c>
       <c r="AK16" s="3" t="n">
-        <v>45930.625</v>
+        <v>45930.58333333334</v>
       </c>
     </row>
     <row r="17">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,61 +2733,61 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>3.79</v>
+        <v>1.62</v>
       </c>
       <c r="P18" t="n">
-        <v>2.39</v>
+        <v>2.68</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.33</v>
+        <v>6.49</v>
       </c>
       <c r="R18" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="S18" t="n">
-        <v>3.75</v>
+        <v>3.88</v>
       </c>
       <c r="T18" t="n">
-        <v>2.2</v>
+        <v>2.04</v>
       </c>
       <c r="U18" t="n">
-        <v>1.63</v>
+        <v>1.69</v>
       </c>
       <c r="V18" t="n">
         <v>1.01</v>
       </c>
       <c r="W18" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X18" t="n">
-        <v>5.16</v>
+        <v>5.5</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.53</v>
+        <v>1.46</v>
       </c>
       <c r="Z18" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.25</v>
+        <v>2.09</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.46</v>
+        <v>1.66</v>
       </c>
       <c r="AD18" t="n">
-        <v>2.5</v>
+        <v>2.12</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
@@ -2800,10 +2800,10 @@
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>1.24</v>
+        <v>1.07</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.31</v>
+        <v>3.15</v>
       </c>
       <c r="AI18" t="n">
         <v>0</v>
@@ -2950,12 +2950,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,61 +2991,61 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.05</v>
+        <v>3.25</v>
       </c>
       <c r="M20" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="N20" t="n">
-        <v>3.45</v>
+        <v>1.75</v>
       </c>
       <c r="O20" t="n">
-        <v>2.68</v>
+        <v>3.79</v>
       </c>
       <c r="P20" t="n">
-        <v>2.15</v>
+        <v>2.39</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.7</v>
+        <v>2.33</v>
       </c>
       <c r="R20" t="n">
-        <v>1.35</v>
+        <v>1.25</v>
       </c>
       <c r="S20" t="n">
-        <v>2.95</v>
+        <v>3.75</v>
       </c>
       <c r="T20" t="n">
-        <v>2.6</v>
+        <v>2.2</v>
       </c>
       <c r="U20" t="n">
-        <v>1.41</v>
+        <v>1.63</v>
       </c>
       <c r="V20" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W20" t="n">
-        <v>1.25</v>
+        <v>1.1</v>
       </c>
       <c r="X20" t="n">
-        <v>3.7</v>
+        <v>5.16</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.8</v>
+        <v>1.53</v>
       </c>
       <c r="Z20" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="AA20" t="n">
-        <v>3</v>
+        <v>2.25</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.37</v>
+        <v>1.62</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.65</v>
+        <v>1.46</v>
       </c>
       <c r="AD20" t="n">
-        <v>2.13</v>
+        <v>2.5</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
@@ -3058,10 +3058,10 @@
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.73</v>
+        <v>1.31</v>
       </c>
       <c r="AI20" t="n">
         <v>0</v>
@@ -3070,7 +3070,7 @@
         <v>0</v>
       </c>
       <c r="AK20" s="3" t="n">
-        <v>45930.64583333334</v>
+        <v>45930.625</v>
       </c>
     </row>
     <row r="21">
@@ -3079,12 +3079,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mantova</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,61 +3120,61 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.79</v>
+        <v>2.15</v>
       </c>
       <c r="M21" t="n">
-        <v>3.61</v>
+        <v>3.5</v>
       </c>
       <c r="N21" t="n">
-        <v>4.3</v>
+        <v>2.88</v>
       </c>
       <c r="O21" t="n">
-        <v>2.41</v>
+        <v>2.6</v>
       </c>
       <c r="P21" t="n">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="Q21" t="n">
-        <v>4.9</v>
+        <v>3.35</v>
       </c>
       <c r="R21" t="n">
-        <v>1.39</v>
+        <v>1.25</v>
       </c>
       <c r="S21" t="n">
-        <v>2.8</v>
+        <v>3.7</v>
       </c>
       <c r="T21" t="n">
-        <v>2.84</v>
+        <v>2.21</v>
       </c>
       <c r="U21" t="n">
-        <v>1.36</v>
+        <v>1.62</v>
       </c>
       <c r="V21" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="W21" t="n">
-        <v>1.34</v>
+        <v>1.12</v>
       </c>
       <c r="X21" t="n">
-        <v>3.22</v>
+        <v>4.8</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.98</v>
+        <v>1.53</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.77</v>
+        <v>2.4</v>
       </c>
       <c r="AA21" t="n">
-        <v>3.4</v>
+        <v>2.28</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.26</v>
+        <v>1.6</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.86</v>
+        <v>1.45</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.86</v>
+        <v>2.59</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
@@ -3187,10 +3187,10 @@
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>1.2</v>
+        <v>1.38</v>
       </c>
       <c r="AH21" t="n">
-        <v>2.03</v>
+        <v>1.68</v>
       </c>
       <c r="AI21" t="n">
         <v>0</v>
@@ -3199,7 +3199,7 @@
         <v>0</v>
       </c>
       <c r="AK21" s="3" t="n">
-        <v>45930.64583333334</v>
+        <v>45930.625</v>
       </c>
     </row>
     <row r="22">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Calcio Padova</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Mantova</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,61 +3249,61 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.15</v>
+        <v>1.86</v>
       </c>
       <c r="M22" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="N22" t="n">
-        <v>3.45</v>
+        <v>4.18</v>
       </c>
       <c r="O22" t="n">
-        <v>2.81</v>
+        <v>2.43</v>
       </c>
       <c r="P22" t="n">
-        <v>2</v>
+        <v>2.13</v>
       </c>
       <c r="Q22" t="n">
-        <v>4.24</v>
+        <v>4.9</v>
       </c>
       <c r="R22" t="n">
-        <v>1.45</v>
+        <v>1.39</v>
       </c>
       <c r="S22" t="n">
-        <v>2.55</v>
+        <v>2.87</v>
       </c>
       <c r="T22" t="n">
-        <v>3</v>
+        <v>2.84</v>
       </c>
       <c r="U22" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="V22" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="W22" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="X22" t="n">
-        <v>2.78</v>
+        <v>3.1</v>
       </c>
       <c r="Y22" t="n">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="Z22" t="n">
-        <v>1.65</v>
+        <v>1.76</v>
       </c>
       <c r="AA22" t="n">
-        <v>3.9</v>
+        <v>3.55</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.19</v>
+        <v>1.27</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.93</v>
+        <v>1.86</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.76</v>
+        <v>1.86</v>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
@@ -3316,10 +3316,10 @@
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.69</v>
+        <v>1.95</v>
       </c>
       <c r="AI22" t="n">
         <v>0</v>
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,77 +3378,77 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.15</v>
+        <v>3.41</v>
       </c>
       <c r="M23" t="n">
-        <v>3.35</v>
+        <v>3.26</v>
       </c>
       <c r="N23" t="n">
-        <v>3.45</v>
+        <v>2.13</v>
       </c>
       <c r="O23" t="n">
-        <v>2.81</v>
+        <v>4.3</v>
       </c>
       <c r="P23" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S23" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="T23" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="V23" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="X23" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="Y23" t="n">
         <v>2.04</v>
       </c>
-      <c r="Q23" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="R23" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="S23" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="T23" t="n">
-        <v>3</v>
-      </c>
-      <c r="U23" t="n">
+      <c r="Z23" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AE23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG23" t="n">
         <v>1.33</v>
       </c>
-      <c r="V23" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="W23" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="X23" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>3.82</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AE23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG23" t="n">
-        <v>1.32</v>
-      </c>
       <c r="AH23" t="n">
-        <v>1.7</v>
+        <v>1.31</v>
       </c>
       <c r="AI23" t="n">
         <v>0</v>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Calcio Padova</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,58 +3507,58 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>3.41</v>
+        <v>2.18</v>
       </c>
       <c r="M24" t="n">
-        <v>3.26</v>
+        <v>3.32</v>
       </c>
       <c r="N24" t="n">
-        <v>2.13</v>
+        <v>3.5</v>
       </c>
       <c r="O24" t="n">
-        <v>4.29</v>
+        <v>2.81</v>
       </c>
       <c r="P24" t="n">
-        <v>2</v>
+        <v>2.03</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.75</v>
+        <v>4.24</v>
       </c>
       <c r="R24" t="n">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="S24" t="n">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="T24" t="n">
-        <v>3.04</v>
+        <v>3.05</v>
       </c>
       <c r="U24" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="V24" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="W24" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="X24" t="n">
-        <v>2.96</v>
+        <v>2.85</v>
       </c>
       <c r="Y24" t="n">
-        <v>2.07</v>
+        <v>2.22</v>
       </c>
       <c r="Z24" t="n">
-        <v>1.75</v>
+        <v>1.66</v>
       </c>
       <c r="AA24" t="n">
-        <v>3.72</v>
+        <v>4.2</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.86</v>
+        <v>1.92</v>
       </c>
       <c r="AD24" t="n">
         <v>1.8</v>
@@ -3574,10 +3574,10 @@
         </is>
       </c>
       <c r="AG24" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.31</v>
+        <v>1.69</v>
       </c>
       <c r="AI24" t="n">
         <v>0</v>
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,61 +3636,61 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.59</v>
+        <v>2.11</v>
       </c>
       <c r="M25" t="n">
-        <v>3.01</v>
+        <v>3.46</v>
       </c>
       <c r="N25" t="n">
-        <v>2.84</v>
+        <v>3.26</v>
       </c>
       <c r="O25" t="n">
-        <v>3.2</v>
+        <v>2.68</v>
       </c>
       <c r="P25" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>4</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S25" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="V25" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W25" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="X25" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Z25" t="n">
         <v>2</v>
       </c>
-      <c r="Q25" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="R25" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="S25" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="T25" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="U25" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="V25" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W25" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="X25" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>1.67</v>
-      </c>
       <c r="AA25" t="n">
-        <v>3.95</v>
+        <v>3</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.9</v>
+        <v>1.65</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.82</v>
+        <v>2.13</v>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
@@ -3706,7 +3706,7 @@
         <v>1.3</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.48</v>
+        <v>1.74</v>
       </c>
       <c r="AI25" t="n">
         <v>0</v>
@@ -3729,7 +3729,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,61 +3765,61 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>3.25</v>
+        <v>2.62</v>
       </c>
       <c r="M26" t="n">
-        <v>3.6</v>
+        <v>3.24</v>
       </c>
       <c r="N26" t="n">
-        <v>2.02</v>
+        <v>2.7</v>
       </c>
       <c r="O26" t="n">
-        <v>3.9</v>
+        <v>3.28</v>
       </c>
       <c r="P26" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="S26" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="T26" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="V26" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W26" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="X26" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="Y26" t="n">
         <v>2.25</v>
       </c>
-      <c r="Q26" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="R26" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="S26" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="T26" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="U26" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="V26" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W26" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="X26" t="n">
-        <v>3.66</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>1.73</v>
-      </c>
       <c r="Z26" t="n">
-        <v>2</v>
+        <v>1.64</v>
       </c>
       <c r="AA26" t="n">
-        <v>2.92</v>
+        <v>4.29</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.35</v>
+        <v>1.22</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.73</v>
+        <v>1.9</v>
       </c>
       <c r="AD26" t="n">
-        <v>2.03</v>
+        <v>1.8</v>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
@@ -3832,10 +3832,10 @@
         </is>
       </c>
       <c r="AG26" t="n">
-        <v>1.26</v>
+        <v>1.4</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.24</v>
+        <v>1.49</v>
       </c>
       <c r="AI26" t="n">
         <v>0</v>
@@ -3853,12 +3853,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,61 +3894,61 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.19</v>
+        <v>2.14</v>
       </c>
       <c r="M27" t="n">
-        <v>3.47</v>
+        <v>3.4</v>
       </c>
       <c r="N27" t="n">
-        <v>3.08</v>
+        <v>3.5</v>
       </c>
       <c r="O27" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="P27" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>4.19</v>
+      </c>
+      <c r="R27" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="S27" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="T27" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="V27" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="W27" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="X27" t="n">
         <v>2.88</v>
       </c>
-      <c r="P27" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>3.88</v>
-      </c>
-      <c r="R27" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S27" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="T27" t="n">
-        <v>3</v>
-      </c>
-      <c r="U27" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="V27" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="W27" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="X27" t="n">
-        <v>3.16</v>
-      </c>
       <c r="Y27" t="n">
-        <v>1.98</v>
+        <v>2.2</v>
       </c>
       <c r="Z27" t="n">
-        <v>1.77</v>
+        <v>1.62</v>
       </c>
       <c r="AA27" t="n">
-        <v>3.48</v>
+        <v>3.82</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.26</v>
+        <v>1.2</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.94</v>
+        <v>1.85</v>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
@@ -3964,7 +3964,7 @@
         <v>1.32</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="AI27" t="n">
         <v>0</v>
@@ -3973,7 +3973,7 @@
         <v>0</v>
       </c>
       <c r="AK27" s="3" t="n">
-        <v>45930.65625</v>
+        <v>45930.64583333334</v>
       </c>
     </row>
     <row r="28">
@@ -3982,12 +3982,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,61 +4023,61 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.4</v>
+        <v>3.81</v>
       </c>
       <c r="M28" t="n">
-        <v>4.2</v>
+        <v>3.4</v>
       </c>
       <c r="N28" t="n">
-        <v>5.9</v>
+        <v>1.8</v>
       </c>
       <c r="O28" t="n">
-        <v>1.97</v>
+        <v>4.39</v>
       </c>
       <c r="P28" t="n">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="Q28" t="n">
-        <v>6.05</v>
+        <v>2.45</v>
       </c>
       <c r="R28" t="n">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="S28" t="n">
-        <v>3.21</v>
+        <v>2.98</v>
       </c>
       <c r="T28" t="n">
-        <v>2.5</v>
+        <v>2.74</v>
       </c>
       <c r="U28" t="n">
-        <v>1.5</v>
+        <v>1.42</v>
       </c>
       <c r="V28" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="W28" t="n">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="X28" t="n">
-        <v>4.05</v>
+        <v>3.66</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.65</v>
+        <v>1.84</v>
       </c>
       <c r="Z28" t="n">
-        <v>2.1</v>
+        <v>1.93</v>
       </c>
       <c r="AA28" t="n">
-        <v>2.63</v>
+        <v>3</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.84</v>
+        <v>1.68</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.87</v>
+        <v>2.03</v>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
@@ -4090,10 +4090,10 @@
         </is>
       </c>
       <c r="AG28" t="n">
-        <v>1.21</v>
+        <v>1.3</v>
       </c>
       <c r="AH28" t="n">
-        <v>2.64</v>
+        <v>1.24</v>
       </c>
       <c r="AI28" t="n">
         <v>0</v>
@@ -4102,7 +4102,7 @@
         <v>0</v>
       </c>
       <c r="AK28" s="3" t="n">
-        <v>45930.65625</v>
+        <v>45930.64583333334</v>
       </c>
     </row>
     <row r="29">
@@ -4116,7 +4116,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,61 +4152,61 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.65</v>
+        <v>3.06</v>
       </c>
       <c r="M29" t="n">
-        <v>3.82</v>
+        <v>3.19</v>
       </c>
       <c r="N29" t="n">
-        <v>4.9</v>
+        <v>2.08</v>
       </c>
       <c r="O29" t="n">
-        <v>2.23</v>
+        <v>3.6</v>
       </c>
       <c r="P29" t="n">
-        <v>2.22</v>
+        <v>2.1</v>
       </c>
       <c r="Q29" t="n">
-        <v>5.36</v>
+        <v>2.74</v>
       </c>
       <c r="R29" t="n">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="S29" t="n">
-        <v>3.14</v>
+        <v>2.84</v>
       </c>
       <c r="T29" t="n">
-        <v>2.67</v>
+        <v>2.8</v>
       </c>
       <c r="U29" t="n">
-        <v>1.43</v>
+        <v>1.37</v>
       </c>
       <c r="V29" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W29" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X29" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AB29" t="n">
         <v>1.27</v>
       </c>
-      <c r="X29" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>3.02</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>1.31</v>
-      </c>
       <c r="AC29" t="n">
-        <v>1.87</v>
+        <v>1.7</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.93</v>
+        <v>2.03</v>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
@@ -4219,10 +4219,10 @@
         </is>
       </c>
       <c r="AG29" t="n">
-        <v>1.16</v>
+        <v>1.3</v>
       </c>
       <c r="AH29" t="n">
-        <v>2.25</v>
+        <v>1.33</v>
       </c>
       <c r="AI29" t="n">
         <v>0</v>
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,77 +4281,77 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.49</v>
+        <v>1.9</v>
       </c>
       <c r="M30" t="n">
-        <v>3.29</v>
+        <v>3.4</v>
       </c>
       <c r="N30" t="n">
-        <v>2.74</v>
+        <v>4</v>
       </c>
       <c r="O30" t="n">
-        <v>3.18</v>
+        <v>2.45</v>
       </c>
       <c r="P30" t="n">
-        <v>2.01</v>
+        <v>2.22</v>
       </c>
       <c r="Q30" t="n">
+        <v>4.72</v>
+      </c>
+      <c r="R30" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S30" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="V30" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W30" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="X30" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AA30" t="n">
         <v>3.4</v>
       </c>
-      <c r="R30" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S30" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="T30" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="U30" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="V30" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W30" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="X30" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>3.95</v>
-      </c>
       <c r="AB30" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AE30" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF30" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG30" t="n">
         <v>1.22</v>
       </c>
-      <c r="AC30" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AD30" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AE30" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF30" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG30" t="n">
-        <v>1.34</v>
-      </c>
       <c r="AH30" t="n">
-        <v>1.53</v>
+        <v>1.91</v>
       </c>
       <c r="AI30" t="n">
         <v>0</v>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,61 +4539,61 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>3.06</v>
+        <v>3.2</v>
       </c>
       <c r="M32" t="n">
-        <v>3.19</v>
+        <v>3.3</v>
       </c>
       <c r="N32" t="n">
-        <v>2.08</v>
+        <v>2.2</v>
       </c>
       <c r="O32" t="n">
-        <v>3.6</v>
+        <v>3.58</v>
       </c>
       <c r="P32" t="n">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.74</v>
+        <v>2.97</v>
       </c>
       <c r="R32" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="S32" t="n">
-        <v>2.84</v>
+        <v>3.09</v>
       </c>
       <c r="T32" t="n">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
       <c r="U32" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="V32" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W32" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="X32" t="n">
-        <v>3.45</v>
+        <v>3.74</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.84</v>
+        <v>1.77</v>
       </c>
       <c r="Z32" t="n">
-        <v>1.86</v>
+        <v>1.98</v>
       </c>
       <c r="AA32" t="n">
-        <v>3.2</v>
+        <v>3.17</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="AC32" t="n">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="AD32" t="n">
-        <v>2.03</v>
+        <v>2.12</v>
       </c>
       <c r="AE32" t="inlineStr">
         <is>
@@ -4606,10 +4606,10 @@
         </is>
       </c>
       <c r="AG32" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.33</v>
+        <v>1.43</v>
       </c>
       <c r="AI32" t="n">
         <v>0</v>
@@ -4632,7 +4632,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,61 +4668,61 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>3.2</v>
+        <v>1.4</v>
       </c>
       <c r="M33" t="n">
-        <v>3.3</v>
+        <v>4.2</v>
       </c>
       <c r="N33" t="n">
-        <v>2.2</v>
+        <v>5.9</v>
       </c>
       <c r="O33" t="n">
-        <v>3.58</v>
+        <v>1.97</v>
       </c>
       <c r="P33" t="n">
-        <v>2.11</v>
+        <v>2.4</v>
       </c>
       <c r="Q33" t="n">
-        <v>2.97</v>
+        <v>6.05</v>
       </c>
       <c r="R33" t="n">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="S33" t="n">
-        <v>3.09</v>
+        <v>3.21</v>
       </c>
       <c r="T33" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="U33" t="n">
-        <v>1.39</v>
+        <v>1.5</v>
       </c>
       <c r="V33" t="n">
         <v>1.02</v>
       </c>
       <c r="W33" t="n">
-        <v>1.23</v>
+        <v>1.19</v>
       </c>
       <c r="X33" t="n">
-        <v>3.74</v>
+        <v>4.05</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.77</v>
+        <v>1.65</v>
       </c>
       <c r="Z33" t="n">
-        <v>1.98</v>
+        <v>2.1</v>
       </c>
       <c r="AA33" t="n">
-        <v>3.17</v>
+        <v>2.63</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.31</v>
+        <v>1.42</v>
       </c>
       <c r="AC33" t="n">
-        <v>1.66</v>
+        <v>1.84</v>
       </c>
       <c r="AD33" t="n">
-        <v>2.12</v>
+        <v>1.87</v>
       </c>
       <c r="AE33" t="inlineStr">
         <is>
@@ -4735,10 +4735,10 @@
         </is>
       </c>
       <c r="AG33" t="n">
-        <v>1.32</v>
+        <v>1.21</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.43</v>
+        <v>2.64</v>
       </c>
       <c r="AI33" t="n">
         <v>0</v>
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,61 +4797,61 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.9</v>
+        <v>2.36</v>
       </c>
       <c r="M34" t="n">
-        <v>3.4</v>
+        <v>3.38</v>
       </c>
       <c r="N34" t="n">
-        <v>4</v>
+        <v>2.86</v>
       </c>
       <c r="O34" t="n">
-        <v>2.45</v>
+        <v>3.05</v>
       </c>
       <c r="P34" t="n">
-        <v>2.22</v>
+        <v>2.21</v>
       </c>
       <c r="Q34" t="n">
-        <v>4.72</v>
+        <v>3.34</v>
       </c>
       <c r="R34" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="S34" t="n">
-        <v>2.71</v>
+        <v>2.84</v>
       </c>
       <c r="T34" t="n">
-        <v>2.88</v>
+        <v>2.67</v>
       </c>
       <c r="U34" t="n">
-        <v>1.34</v>
+        <v>1.39</v>
       </c>
       <c r="V34" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="W34" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="X34" t="n">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.98</v>
+        <v>1.89</v>
       </c>
       <c r="Z34" t="n">
-        <v>1.77</v>
+        <v>1.85</v>
       </c>
       <c r="AA34" t="n">
-        <v>3.4</v>
+        <v>3.08</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="AC34" t="n">
-        <v>1.85</v>
+        <v>1.62</v>
       </c>
       <c r="AD34" t="n">
-        <v>1.85</v>
+        <v>2.16</v>
       </c>
       <c r="AE34" t="inlineStr">
         <is>
@@ -4864,10 +4864,10 @@
         </is>
       </c>
       <c r="AG34" t="n">
-        <v>1.22</v>
+        <v>1.31</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.91</v>
+        <v>1.5</v>
       </c>
       <c r="AI34" t="n">
         <v>0</v>
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,61 +4926,61 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.36</v>
+        <v>1.65</v>
       </c>
       <c r="M35" t="n">
-        <v>3.38</v>
+        <v>3.82</v>
       </c>
       <c r="N35" t="n">
-        <v>2.86</v>
+        <v>4.9</v>
       </c>
       <c r="O35" t="n">
-        <v>3.05</v>
+        <v>2.23</v>
       </c>
       <c r="P35" t="n">
-        <v>2.21</v>
+        <v>2.22</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.34</v>
+        <v>5.36</v>
       </c>
       <c r="R35" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="S35" t="n">
-        <v>2.84</v>
+        <v>3.14</v>
       </c>
       <c r="T35" t="n">
         <v>2.67</v>
       </c>
       <c r="U35" t="n">
-        <v>1.39</v>
+        <v>1.43</v>
       </c>
       <c r="V35" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W35" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="X35" t="n">
-        <v>3.35</v>
+        <v>3.75</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.89</v>
+        <v>1.83</v>
       </c>
       <c r="Z35" t="n">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="AA35" t="n">
-        <v>3.08</v>
+        <v>3.02</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="AC35" t="n">
-        <v>1.62</v>
+        <v>1.87</v>
       </c>
       <c r="AD35" t="n">
-        <v>2.16</v>
+        <v>1.93</v>
       </c>
       <c r="AE35" t="inlineStr">
         <is>
@@ -4993,10 +4993,10 @@
         </is>
       </c>
       <c r="AG35" t="n">
-        <v>1.31</v>
+        <v>1.16</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.5</v>
+        <v>2.25</v>
       </c>
       <c r="AI35" t="n">
         <v>0</v>
@@ -5014,7 +5014,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,78 +5055,78 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.4</v>
+        <v>2.49</v>
       </c>
       <c r="M36" t="n">
-        <v>3.39</v>
+        <v>3.29</v>
       </c>
       <c r="N36" t="n">
-        <v>2.79</v>
+        <v>2.74</v>
       </c>
       <c r="O36" t="n">
-        <v>3.26</v>
+        <v>3.18</v>
       </c>
       <c r="P36" t="n">
-        <v>1.93</v>
+        <v>2.01</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.84</v>
+        <v>3.4</v>
       </c>
       <c r="R36" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S36" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="T36" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="U36" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="V36" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W36" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="X36" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AE36" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF36" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG36" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AH36" t="n">
         <v>1.53</v>
       </c>
-      <c r="S36" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="T36" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="U36" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="V36" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="W36" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="X36" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Y36" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="Z36" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AA36" t="n">
-        <v>4.65</v>
-      </c>
-      <c r="AB36" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AC36" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="AD36" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AE36" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF36" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG36" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AH36" t="n">
-        <v>1.52</v>
-      </c>
       <c r="AI36" t="n">
         <v>0</v>
       </c>
@@ -5134,7 +5134,7 @@
         <v>0</v>
       </c>
       <c r="AK36" s="3" t="n">
-        <v>45930.66666666666</v>
+        <v>45930.65625</v>
       </c>
     </row>
     <row r="37">
@@ -5143,12 +5143,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,61 +5184,61 @@
         </is>
       </c>
       <c r="L37" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="M37" t="n">
+        <v>3.47</v>
+      </c>
+      <c r="N37" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="O37" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="P37" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="R37" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S37" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="T37" t="n">
         <v>3</v>
       </c>
-      <c r="M37" t="n">
-        <v>3.83</v>
-      </c>
-      <c r="N37" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="O37" t="n">
-        <v>0</v>
-      </c>
-      <c r="P37" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q37" t="n">
-        <v>0</v>
-      </c>
-      <c r="R37" t="n">
-        <v>0</v>
-      </c>
-      <c r="S37" t="n">
-        <v>0</v>
-      </c>
-      <c r="T37" t="n">
-        <v>0</v>
-      </c>
       <c r="U37" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="V37" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="W37" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="X37" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="Y37" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="Z37" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AA37" t="n">
-        <v>2.25</v>
+        <v>3.48</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.65</v>
+        <v>1.26</v>
       </c>
       <c r="AC37" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AD37" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AE37" t="inlineStr">
         <is>
@@ -5251,10 +5251,10 @@
         </is>
       </c>
       <c r="AG37" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AH37" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AI37" t="n">
         <v>0</v>
@@ -5263,7 +5263,7 @@
         <v>0</v>
       </c>
       <c r="AK37" s="3" t="n">
-        <v>45930.66666666666</v>
+        <v>45930.65625</v>
       </c>
     </row>
     <row r="38">
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,61 +5313,61 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>1.62</v>
+        <v>1.56</v>
       </c>
       <c r="M38" t="n">
         <v>4.1</v>
       </c>
       <c r="N38" t="n">
-        <v>4.9</v>
+        <v>5.4</v>
       </c>
       <c r="O38" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="P38" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="T38" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="U38" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="V38" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W38" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="X38" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.68</v>
+        <v>1.63</v>
       </c>
       <c r="Z38" t="n">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AA38" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AC38" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AD38" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AE38" t="inlineStr">
         <is>
@@ -5380,10 +5380,10 @@
         </is>
       </c>
       <c r="AG38" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AH38" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="AI38" t="n">
         <v>0</v>
@@ -5451,34 +5451,34 @@
         <v>7</v>
       </c>
       <c r="O39" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="S39" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="T39" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="U39" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="V39" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W39" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="X39" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Y39" t="n">
         <v>1.6</v>
@@ -5487,16 +5487,16 @@
         <v>2.35</v>
       </c>
       <c r="AA39" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AC39" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AD39" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AE39" t="inlineStr">
         <is>
@@ -5509,10 +5509,10 @@
         </is>
       </c>
       <c r="AG39" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AH39" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AI39" t="n">
         <v>0</v>
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,13 +5571,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>1.56</v>
+        <v>4.3</v>
       </c>
       <c r="M40" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="N40" t="n">
-        <v>5.4</v>
+        <v>1.64</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5610,16 +5610,16 @@
         <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.63</v>
+        <v>1.44</v>
       </c>
       <c r="Z40" t="n">
-        <v>2.25</v>
+        <v>2.75</v>
       </c>
       <c r="AA40" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB40" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -5664,7 +5664,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Kariobangi Sharks</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>KCB</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,61 +5700,61 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>3.83</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O41" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S41" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="T41" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="U41" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="V41" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W41" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X41" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Y41" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z41" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AA41" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB41" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC41" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AD41" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AE41" t="inlineStr">
         <is>
@@ -5767,10 +5767,10 @@
         </is>
       </c>
       <c r="AG41" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AH41" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AI41" t="n">
         <v>0</v>
@@ -5838,34 +5838,34 @@
         <v>1.15</v>
       </c>
       <c r="O42" t="n">
-        <v>0</v>
+        <v>11.2</v>
       </c>
       <c r="P42" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="R42" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="S42" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="T42" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="U42" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="V42" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W42" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X42" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="Y42" t="n">
         <v>1.44</v>
@@ -5880,10 +5880,10 @@
         <v>1.79</v>
       </c>
       <c r="AC42" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD42" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AE42" t="inlineStr">
         <is>
@@ -5896,10 +5896,10 @@
         </is>
       </c>
       <c r="AG42" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AH42" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AI42" t="n">
         <v>0</v>
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5958,61 +5958,61 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>4.3</v>
+        <v>1.62</v>
       </c>
       <c r="M43" t="n">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="N43" t="n">
-        <v>1.64</v>
+        <v>4.9</v>
       </c>
       <c r="O43" t="n">
-        <v>4.6</v>
+        <v>2.1</v>
       </c>
       <c r="P43" t="n">
-        <v>2.5</v>
+        <v>2.41</v>
       </c>
       <c r="Q43" t="n">
-        <v>2</v>
+        <v>5.25</v>
       </c>
       <c r="R43" t="n">
-        <v>1.21</v>
+        <v>1.3</v>
       </c>
       <c r="S43" t="n">
-        <v>3.8</v>
+        <v>3.3</v>
       </c>
       <c r="T43" t="n">
-        <v>2.05</v>
+        <v>2.4</v>
       </c>
       <c r="U43" t="n">
-        <v>1.75</v>
+        <v>1.54</v>
       </c>
       <c r="V43" t="n">
         <v>1.01</v>
       </c>
       <c r="W43" t="n">
-        <v>1.1</v>
+        <v>1.19</v>
       </c>
       <c r="X43" t="n">
-        <v>5.35</v>
+        <v>4.4</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.44</v>
+        <v>1.68</v>
       </c>
       <c r="Z43" t="n">
-        <v>2.75</v>
+        <v>2.18</v>
       </c>
       <c r="AA43" t="n">
-        <v>2.15</v>
+        <v>2.56</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.7</v>
+        <v>1.47</v>
       </c>
       <c r="AC43" t="n">
-        <v>1.5</v>
+        <v>1.68</v>
       </c>
       <c r="AD43" t="n">
-        <v>2.45</v>
+        <v>2.02</v>
       </c>
       <c r="AE43" t="inlineStr">
         <is>
@@ -6028,7 +6028,7 @@
         <v>1.23</v>
       </c>
       <c r="AH43" t="n">
-        <v>1.22</v>
+        <v>2.36</v>
       </c>
       <c r="AI43" t="n">
         <v>0</v>
@@ -6175,12 +6175,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Police</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Ulinzi Stars</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6216,61 +6216,61 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M45" t="n">
-        <v>0</v>
+        <v>3.39</v>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="O45" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="P45" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="R45" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="S45" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="T45" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="U45" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="V45" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="W45" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="X45" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Y45" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="Z45" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AA45" t="n">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="AB45" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AC45" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AD45" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AE45" t="inlineStr">
         <is>
@@ -6283,10 +6283,10 @@
         </is>
       </c>
       <c r="AG45" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AH45" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AI45" t="n">
         <v>0</v>
@@ -6295,7 +6295,7 @@
         <v>0</v>
       </c>
       <c r="AK45" s="3" t="n">
-        <v>45930.75</v>
+        <v>45930.66666666666</v>
       </c>
     </row>
     <row r="46">
@@ -6603,16 +6603,16 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>1.93</v>
+        <v>2.02</v>
       </c>
       <c r="M48" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="N48" t="n">
-        <v>3.57</v>
+        <v>3.7</v>
       </c>
       <c r="O48" t="n">
-        <v>2.66</v>
+        <v>2.67</v>
       </c>
       <c r="P48" t="n">
         <v>2</v>
@@ -6621,10 +6621,10 @@
         <v>4.25</v>
       </c>
       <c r="R48" t="n">
-        <v>1.51</v>
+        <v>1.43</v>
       </c>
       <c r="S48" t="n">
-        <v>2.42</v>
+        <v>2.39</v>
       </c>
       <c r="T48" t="n">
         <v>3.3</v>
@@ -6633,28 +6633,28 @@
         <v>1.28</v>
       </c>
       <c r="V48" t="n">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="W48" t="n">
         <v>1.4</v>
       </c>
       <c r="X48" t="n">
-        <v>2.95</v>
+        <v>2.53</v>
       </c>
       <c r="Y48" t="n">
-        <v>2.12</v>
+        <v>2.49</v>
       </c>
       <c r="Z48" t="n">
-        <v>1.64</v>
+        <v>1.56</v>
       </c>
       <c r="AA48" t="n">
-        <v>4.73</v>
+        <v>4.1</v>
       </c>
       <c r="AB48" t="n">
         <v>1.18</v>
       </c>
       <c r="AC48" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="AD48" t="n">
         <v>1.71</v>

--- a/jogos_2025-09-30.xlsx
+++ b/jogos_2025-09-30.xlsx
@@ -1194,34 +1194,34 @@
         <v>1.82</v>
       </c>
       <c r="O6" t="n">
-        <v>5.78</v>
+        <v>5.5</v>
       </c>
       <c r="P6" t="n">
-        <v>2.26</v>
+        <v>2.1</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.18</v>
+        <v>2.09</v>
       </c>
       <c r="R6" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="S6" t="n">
-        <v>2.7</v>
+        <v>2.92</v>
       </c>
       <c r="T6" t="n">
-        <v>2.89</v>
+        <v>2.92</v>
       </c>
       <c r="U6" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="V6" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W6" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="X6" t="n">
-        <v>3.26</v>
+        <v>3.33</v>
       </c>
       <c r="Y6" t="n">
         <v>2.25</v>
@@ -1230,16 +1230,16 @@
         <v>1.65</v>
       </c>
       <c r="AA6" t="n">
-        <v>3.43</v>
+        <v>3.35</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.95</v>
+        <v>1.99</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
@@ -1255,7 +1255,7 @@
         <v>1.25</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="AI6" t="n">
         <v>2.38</v>
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,13 +1443,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.86</v>
+        <v>19</v>
       </c>
       <c r="M8" t="n">
-        <v>3.84</v>
+        <v>8.9</v>
       </c>
       <c r="N8" t="n">
-        <v>3.7</v>
+        <v>1.11</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1482,16 +1482,16 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.7</v>
+        <v>1.3</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.15</v>
+        <v>3.4</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,61 +1572,61 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>19</v>
+        <v>1.91</v>
       </c>
       <c r="M9" t="n">
-        <v>8.9</v>
+        <v>4</v>
       </c>
       <c r="N9" t="n">
-        <v>1.11</v>
+        <v>3.6</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.3</v>
+        <v>1.65</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.4</v>
+        <v>2.31</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.8</v>
+        <v>2.54</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.94</v>
+        <v>1.47</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
@@ -1701,34 +1701,34 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="M10" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="N10" t="n">
-        <v>4.8</v>
+        <v>4.2</v>
       </c>
       <c r="O10" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="P10" t="n">
         <v>2.5</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.96</v>
+        <v>4.95</v>
       </c>
       <c r="R10" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="S10" t="n">
         <v>3.66</v>
       </c>
       <c r="T10" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="U10" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="V10" t="n">
         <v>1.01</v>
@@ -1737,25 +1737,25 @@
         <v>1.11</v>
       </c>
       <c r="X10" t="n">
-        <v>5.1</v>
+        <v>5.6</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.47</v>
+        <v>2.7</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.21</v>
+        <v>1.92</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.64</v>
+        <v>1.78</v>
       </c>
       <c r="AC10" t="n">
         <v>1.55</v>
       </c>
       <c r="AD10" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -1794,22 +1794,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Wehen Wiesbaden</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,61 +1830,61 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.39</v>
+        <v>2.51</v>
       </c>
       <c r="M11" t="n">
-        <v>4.8</v>
+        <v>3.45</v>
       </c>
       <c r="N11" t="n">
-        <v>6.8</v>
+        <v>2.31</v>
       </c>
       <c r="O11" t="n">
-        <v>1.83</v>
+        <v>3.34</v>
       </c>
       <c r="P11" t="n">
-        <v>2.45</v>
+        <v>2.21</v>
       </c>
       <c r="Q11" t="n">
-        <v>5.7</v>
+        <v>3</v>
       </c>
       <c r="R11" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="S11" t="n">
-        <v>3.6</v>
+        <v>3.26</v>
       </c>
       <c r="T11" t="n">
-        <v>2.2</v>
+        <v>2.39</v>
       </c>
       <c r="U11" t="n">
-        <v>1.62</v>
+        <v>1.51</v>
       </c>
       <c r="V11" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="W11" t="n">
         <v>1.15</v>
       </c>
       <c r="X11" t="n">
-        <v>4.5</v>
+        <v>4.35</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.61</v>
+        <v>1.53</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.3</v>
+        <v>2.19</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.5</v>
+        <v>2.33</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.85</v>
+        <v>1.44</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.91</v>
+        <v>2.33</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -1897,10 +1897,10 @@
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AH11" t="n">
-        <v>2.78</v>
+        <v>1.4</v>
       </c>
       <c r="AI11" t="n">
         <v>0</v>
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Havelse</t>
+          <t>Saarbrucken</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Waldhof Mannheim</t>
+          <t>MSV Duisburg</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,22 +1959,22 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>3.4</v>
+        <v>2.08</v>
       </c>
       <c r="M12" t="n">
-        <v>3.7</v>
+        <v>3.45</v>
       </c>
       <c r="N12" t="n">
-        <v>1.92</v>
+        <v>2.84</v>
       </c>
       <c r="O12" t="n">
-        <v>4.12</v>
+        <v>2.61</v>
       </c>
       <c r="P12" t="n">
-        <v>2.24</v>
+        <v>2.18</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.4</v>
+        <v>3.46</v>
       </c>
       <c r="R12" t="n">
         <v>1.3</v>
@@ -1983,37 +1983,37 @@
         <v>3.2</v>
       </c>
       <c r="T12" t="n">
-        <v>2.23</v>
+        <v>2.39</v>
       </c>
       <c r="U12" t="n">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="V12" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="W12" t="n">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="X12" t="n">
-        <v>4.1</v>
+        <v>4.33</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.12</v>
+        <v>2.19</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.45</v>
+        <v>2.56</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="AD12" t="n">
-        <v>2.17</v>
+        <v>2.36</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -2026,10 +2026,10 @@
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.24</v>
+        <v>1.62</v>
       </c>
       <c r="AI12" t="n">
         <v>0</v>
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>Havelse</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Erzgebirge Aue</t>
+          <t>Waldhof Mannheim</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,61 +2088,61 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.03</v>
+        <v>3.1</v>
       </c>
       <c r="M13" t="n">
         <v>3.5</v>
       </c>
       <c r="N13" t="n">
-        <v>3.3</v>
+        <v>1.95</v>
       </c>
       <c r="O13" t="n">
-        <v>2.54</v>
+        <v>4.12</v>
       </c>
       <c r="P13" t="n">
-        <v>2.21</v>
+        <v>2.39</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.87</v>
+        <v>2.47</v>
       </c>
       <c r="R13" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="S13" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="T13" t="n">
-        <v>2.43</v>
+        <v>2.49</v>
       </c>
       <c r="U13" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="V13" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="W13" t="n">
-        <v>1.21</v>
+        <v>1.16</v>
       </c>
       <c r="X13" t="n">
-        <v>3.7</v>
+        <v>4.11</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="Z13" t="n">
-        <v>2</v>
+        <v>2.13</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.8</v>
+        <v>2.45</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AD13" t="n">
-        <v>2.02</v>
+        <v>2.23</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
@@ -2155,10 +2155,10 @@
         </is>
       </c>
       <c r="AG13" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AH13" t="n">
         <v>1.24</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>1.68</v>
       </c>
       <c r="AI13" t="n">
         <v>0</v>
@@ -2181,22 +2181,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Saarbrucken</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>MSV Duisburg</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,61 +2217,61 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.87</v>
+        <v>1.26</v>
       </c>
       <c r="M14" t="n">
-        <v>3.8</v>
+        <v>5.1</v>
       </c>
       <c r="N14" t="n">
-        <v>3.12</v>
+        <v>7.6</v>
       </c>
       <c r="O14" t="n">
-        <v>2.51</v>
+        <v>1.83</v>
       </c>
       <c r="P14" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S14" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="T14" t="n">
         <v>2.2</v>
       </c>
-      <c r="Q14" t="n">
-        <v>3.98</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="S14" t="n">
-        <v>3.26</v>
-      </c>
-      <c r="T14" t="n">
-        <v>2.36</v>
-      </c>
       <c r="U14" t="n">
-        <v>1.52</v>
+        <v>1.62</v>
       </c>
       <c r="V14" t="n">
         <v>1.02</v>
       </c>
       <c r="W14" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="X14" t="n">
-        <v>4.45</v>
+        <v>4.5</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.59</v>
+        <v>1.47</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.22</v>
+        <v>2.5</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.42</v>
+        <v>2.17</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.44</v>
+        <v>1.62</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.51</v>
+        <v>1.86</v>
       </c>
       <c r="AD14" t="n">
-        <v>2.36</v>
+        <v>1.91</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
@@ -2284,10 +2284,10 @@
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>1.24</v>
+        <v>1.17</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.74</v>
+        <v>2.78</v>
       </c>
       <c r="AI14" t="n">
         <v>0</v>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Wehen Wiesbaden</t>
+          <t>Erzgebirge Aue</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,61 +2346,61 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.9</v>
+        <v>2.01</v>
       </c>
       <c r="M15" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="N15" t="n">
-        <v>2.18</v>
+        <v>2.96</v>
       </c>
       <c r="O15" t="n">
-        <v>3.34</v>
+        <v>2.53</v>
       </c>
       <c r="P15" t="n">
-        <v>2.21</v>
+        <v>2.32</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.83</v>
+        <v>3.91</v>
       </c>
       <c r="R15" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="S15" t="n">
-        <v>3.26</v>
+        <v>3.1</v>
       </c>
       <c r="T15" t="n">
-        <v>2.39</v>
+        <v>2.55</v>
       </c>
       <c r="U15" t="n">
-        <v>1.51</v>
+        <v>1.46</v>
       </c>
       <c r="V15" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="W15" t="n">
-        <v>1.14</v>
+        <v>1.23</v>
       </c>
       <c r="X15" t="n">
-        <v>4.4</v>
+        <v>3.68</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.53</v>
+        <v>1.71</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.25</v>
+        <v>1.98</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.33</v>
+        <v>2.74</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.42</v>
+        <v>1.35</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AD15" t="n">
-        <v>2.36</v>
+        <v>2.11</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
@@ -2413,10 +2413,10 @@
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.4</v>
+        <v>1.68</v>
       </c>
       <c r="AI15" t="n">
         <v>0</v>
@@ -2475,22 +2475,22 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="M16" t="n">
-        <v>3.8</v>
+        <v>3.45</v>
       </c>
       <c r="N16" t="n">
-        <v>3.8</v>
+        <v>3.1</v>
       </c>
       <c r="O16" t="n">
-        <v>2.28</v>
+        <v>2.47</v>
       </c>
       <c r="P16" t="n">
-        <v>2.23</v>
+        <v>2.22</v>
       </c>
       <c r="Q16" t="n">
-        <v>4.08</v>
+        <v>4.01</v>
       </c>
       <c r="R16" t="n">
         <v>1.3</v>
@@ -2499,22 +2499,22 @@
         <v>3.2</v>
       </c>
       <c r="T16" t="n">
-        <v>2.28</v>
+        <v>2.46</v>
       </c>
       <c r="U16" t="n">
-        <v>1.54</v>
+        <v>1.48</v>
       </c>
       <c r="V16" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="W16" t="n">
         <v>1.17</v>
       </c>
       <c r="X16" t="n">
-        <v>4</v>
+        <v>4.21</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.61</v>
+        <v>1.67</v>
       </c>
       <c r="Z16" t="n">
         <v>2.1</v>
@@ -2545,7 +2545,7 @@
         <v>1.3</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.79</v>
+        <v>1.9</v>
       </c>
       <c r="AI16" t="n">
         <v>0</v>
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,61 +2604,61 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.87</v>
+        <v>2.16</v>
       </c>
       <c r="M17" t="n">
-        <v>3.5</v>
+        <v>3.86</v>
       </c>
       <c r="N17" t="n">
-        <v>2.3</v>
+        <v>2.94</v>
       </c>
       <c r="O17" t="n">
-        <v>3.5</v>
+        <v>2.6</v>
       </c>
       <c r="P17" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="S17" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="T17" t="n">
         <v>2.25</v>
       </c>
-      <c r="Q17" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="S17" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="T17" t="n">
-        <v>2.32</v>
-      </c>
       <c r="U17" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="V17" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="W17" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="X17" t="n">
-        <v>4.45</v>
+        <v>5.32</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.59</v>
+        <v>1.53</v>
       </c>
       <c r="Z17" t="n">
-        <v>2.35</v>
+        <v>2.51</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.36</v>
+        <v>2.28</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AD17" t="n">
-        <v>2.45</v>
+        <v>2.59</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
@@ -2671,10 +2671,10 @@
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.35</v>
+        <v>1.67</v>
       </c>
       <c r="AI17" t="n">
         <v>0</v>
@@ -2742,52 +2742,52 @@
         <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>1.62</v>
+        <v>1.84</v>
       </c>
       <c r="P18" t="n">
-        <v>2.68</v>
+        <v>2.85</v>
       </c>
       <c r="Q18" t="n">
-        <v>6.49</v>
+        <v>5.93</v>
       </c>
       <c r="R18" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="S18" t="n">
-        <v>3.88</v>
+        <v>3.75</v>
       </c>
       <c r="T18" t="n">
-        <v>2.04</v>
+        <v>2.13</v>
       </c>
       <c r="U18" t="n">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="V18" t="n">
         <v>1.01</v>
       </c>
       <c r="W18" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X18" t="n">
-        <v>5.5</v>
+        <v>5.35</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="Z18" t="n">
-        <v>2.6</v>
+        <v>2.57</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.09</v>
+        <v>2.14</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.71</v>
+        <v>1.68</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.66</v>
+        <v>1.62</v>
       </c>
       <c r="AD18" t="n">
-        <v>2.12</v>
+        <v>2.18</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
@@ -2800,10 +2800,10 @@
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>1.07</v>
+        <v>1.16</v>
       </c>
       <c r="AH18" t="n">
-        <v>3.15</v>
+        <v>2.86</v>
       </c>
       <c r="AI18" t="n">
         <v>0</v>
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,61 +2862,61 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.78</v>
+        <v>3.34</v>
       </c>
       <c r="M19" t="n">
-        <v>3.7</v>
+        <v>3.92</v>
       </c>
       <c r="N19" t="n">
-        <v>3.7</v>
+        <v>1.97</v>
       </c>
       <c r="O19" t="n">
-        <v>2.34</v>
+        <v>3.59</v>
       </c>
       <c r="P19" t="n">
-        <v>2.27</v>
+        <v>2.39</v>
       </c>
       <c r="Q19" t="n">
-        <v>4.42</v>
+        <v>2.4</v>
       </c>
       <c r="R19" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="S19" t="n">
-        <v>3.28</v>
+        <v>3.75</v>
       </c>
       <c r="T19" t="n">
-        <v>2.47</v>
+        <v>2.2</v>
       </c>
       <c r="U19" t="n">
-        <v>1.48</v>
+        <v>1.63</v>
       </c>
       <c r="V19" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="W19" t="n">
         <v>1.16</v>
       </c>
       <c r="X19" t="n">
-        <v>4.15</v>
+        <v>5.16</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.68</v>
+        <v>1.45</v>
       </c>
       <c r="Z19" t="n">
-        <v>2.14</v>
+        <v>2.5</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.63</v>
+        <v>2.25</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.39</v>
+        <v>1.62</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.61</v>
+        <v>1.44</v>
       </c>
       <c r="AD19" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
@@ -2929,10 +2929,10 @@
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.95</v>
+        <v>1.3</v>
       </c>
       <c r="AI19" t="n">
         <v>0</v>
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,61 +2991,61 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>3.25</v>
+        <v>1.79</v>
       </c>
       <c r="M20" t="n">
-        <v>3.75</v>
+        <v>3.88</v>
       </c>
       <c r="N20" t="n">
-        <v>1.75</v>
+        <v>4.01</v>
       </c>
       <c r="O20" t="n">
-        <v>3.79</v>
+        <v>2.3</v>
       </c>
       <c r="P20" t="n">
-        <v>2.39</v>
+        <v>2.28</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.33</v>
+        <v>4.52</v>
       </c>
       <c r="R20" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="S20" t="n">
-        <v>3.75</v>
+        <v>3.28</v>
       </c>
       <c r="T20" t="n">
-        <v>2.2</v>
+        <v>2.47</v>
       </c>
       <c r="U20" t="n">
-        <v>1.63</v>
+        <v>1.48</v>
       </c>
       <c r="V20" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="W20" t="n">
-        <v>1.1</v>
+        <v>1.16</v>
       </c>
       <c r="X20" t="n">
-        <v>5.16</v>
+        <v>4.15</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.53</v>
+        <v>1.68</v>
       </c>
       <c r="Z20" t="n">
-        <v>2.4</v>
+        <v>2.19</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.25</v>
+        <v>2.63</v>
       </c>
       <c r="AB20" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AC20" t="n">
         <v>1.62</v>
       </c>
-      <c r="AC20" t="n">
-        <v>1.46</v>
-      </c>
       <c r="AD20" t="n">
-        <v>2.5</v>
+        <v>2.18</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
@@ -3061,7 +3061,7 @@
         <v>1.24</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.31</v>
+        <v>1.98</v>
       </c>
       <c r="AI20" t="n">
         <v>0</v>
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,61 +3120,61 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.15</v>
+        <v>2.9</v>
       </c>
       <c r="M21" t="n">
+        <v>3.66</v>
+      </c>
+      <c r="N21" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="O21" t="n">
         <v>3.5</v>
       </c>
-      <c r="N21" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="O21" t="n">
-        <v>2.6</v>
-      </c>
       <c r="P21" t="n">
-        <v>2.4</v>
+        <v>2.43</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.35</v>
+        <v>2.65</v>
       </c>
       <c r="R21" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="S21" t="n">
-        <v>3.7</v>
+        <v>3.34</v>
       </c>
       <c r="T21" t="n">
-        <v>2.21</v>
+        <v>2.3</v>
       </c>
       <c r="U21" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="V21" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="W21" t="n">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="X21" t="n">
-        <v>4.8</v>
+        <v>4.75</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.53</v>
+        <v>1.59</v>
       </c>
       <c r="Z21" t="n">
-        <v>2.4</v>
+        <v>2.33</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.28</v>
+        <v>2.36</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="AD21" t="n">
-        <v>2.59</v>
+        <v>2.45</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
@@ -3187,10 +3187,10 @@
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>1.38</v>
+        <v>1.27</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.68</v>
+        <v>1.36</v>
       </c>
       <c r="AI21" t="n">
         <v>0</v>
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mantova</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,61 +3249,61 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.86</v>
+        <v>2.12</v>
       </c>
       <c r="M22" t="n">
-        <v>3.25</v>
+        <v>3.37</v>
       </c>
       <c r="N22" t="n">
-        <v>4.18</v>
+        <v>3.38</v>
       </c>
       <c r="O22" t="n">
-        <v>2.43</v>
+        <v>2.73</v>
       </c>
       <c r="P22" t="n">
-        <v>2.13</v>
+        <v>2.1</v>
       </c>
       <c r="Q22" t="n">
-        <v>4.9</v>
+        <v>4</v>
       </c>
       <c r="R22" t="n">
-        <v>1.39</v>
+        <v>1.33</v>
       </c>
       <c r="S22" t="n">
-        <v>2.87</v>
+        <v>2.91</v>
       </c>
       <c r="T22" t="n">
-        <v>2.84</v>
+        <v>2.67</v>
       </c>
       <c r="U22" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="V22" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="W22" t="n">
-        <v>1.34</v>
+        <v>1.22</v>
       </c>
       <c r="X22" t="n">
-        <v>3.1</v>
+        <v>3.75</v>
       </c>
       <c r="Y22" t="n">
-        <v>2.05</v>
+        <v>1.9</v>
       </c>
       <c r="Z22" t="n">
-        <v>1.76</v>
+        <v>1.95</v>
       </c>
       <c r="AA22" t="n">
-        <v>3.55</v>
+        <v>3.02</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.86</v>
+        <v>1.67</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.86</v>
+        <v>2.04</v>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
@@ -3316,10 +3316,10 @@
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.95</v>
+        <v>1.7</v>
       </c>
       <c r="AI22" t="n">
         <v>0</v>
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Calcio Padova</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,61 +3378,61 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>3.41</v>
+        <v>2.31</v>
       </c>
       <c r="M23" t="n">
-        <v>3.26</v>
+        <v>3.1</v>
       </c>
       <c r="N23" t="n">
-        <v>2.13</v>
+        <v>3.1</v>
       </c>
       <c r="O23" t="n">
-        <v>4.3</v>
+        <v>3.16</v>
       </c>
       <c r="P23" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.82</v>
+        <v>4.11</v>
       </c>
       <c r="R23" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="S23" t="n">
-        <v>2.59</v>
+        <v>2.42</v>
       </c>
       <c r="T23" t="n">
-        <v>3.33</v>
+        <v>3.2</v>
       </c>
       <c r="U23" t="n">
         <v>1.28</v>
       </c>
       <c r="V23" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="W23" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="X23" t="n">
-        <v>2.77</v>
+        <v>2.65</v>
       </c>
       <c r="Y23" t="n">
-        <v>2.04</v>
+        <v>2.35</v>
       </c>
       <c r="Z23" t="n">
-        <v>1.64</v>
+        <v>1.55</v>
       </c>
       <c r="AA23" t="n">
-        <v>4.05</v>
+        <v>4.75</v>
       </c>
       <c r="AB23" t="n">
         <v>1.18</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.93</v>
+        <v>1.96</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
@@ -3445,10 +3445,10 @@
         </is>
       </c>
       <c r="AG23" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.31</v>
+        <v>1.58</v>
       </c>
       <c r="AI23" t="n">
         <v>0</v>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Calcio Padova</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,31 +3507,31 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.18</v>
+        <v>3.41</v>
       </c>
       <c r="M24" t="n">
-        <v>3.32</v>
+        <v>3.26</v>
       </c>
       <c r="N24" t="n">
-        <v>3.5</v>
+        <v>2.13</v>
       </c>
       <c r="O24" t="n">
-        <v>2.81</v>
+        <v>4</v>
       </c>
       <c r="P24" t="n">
-        <v>2.03</v>
+        <v>1.95</v>
       </c>
       <c r="Q24" t="n">
-        <v>4.24</v>
+        <v>2.86</v>
       </c>
       <c r="R24" t="n">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="S24" t="n">
-        <v>2.55</v>
+        <v>2.42</v>
       </c>
       <c r="T24" t="n">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="U24" t="n">
         <v>1.3</v>
@@ -3540,28 +3540,28 @@
         <v>1.03</v>
       </c>
       <c r="W24" t="n">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="X24" t="n">
-        <v>2.85</v>
+        <v>2.75</v>
       </c>
       <c r="Y24" t="n">
-        <v>2.22</v>
+        <v>2.31</v>
       </c>
       <c r="Z24" t="n">
-        <v>1.66</v>
+        <v>1.6</v>
       </c>
       <c r="AA24" t="n">
-        <v>4.2</v>
+        <v>4.41</v>
       </c>
       <c r="AB24" t="n">
         <v>1.19</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.92</v>
+        <v>1.96</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
@@ -3574,10 +3574,10 @@
         </is>
       </c>
       <c r="AG24" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.69</v>
+        <v>1.3</v>
       </c>
       <c r="AI24" t="n">
         <v>0</v>
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,77 +3636,77 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="M25" t="n">
-        <v>3.46</v>
+        <v>3.2</v>
       </c>
       <c r="N25" t="n">
-        <v>3.26</v>
+        <v>3.5</v>
       </c>
       <c r="O25" t="n">
-        <v>2.68</v>
+        <v>2.75</v>
       </c>
       <c r="P25" t="n">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="Q25" t="n">
-        <v>4</v>
+        <v>4.38</v>
       </c>
       <c r="R25" t="n">
-        <v>1.32</v>
+        <v>1.44</v>
       </c>
       <c r="S25" t="n">
-        <v>2.98</v>
+        <v>2.51</v>
       </c>
       <c r="T25" t="n">
-        <v>2.6</v>
+        <v>3.14</v>
       </c>
       <c r="U25" t="n">
-        <v>1.41</v>
+        <v>1.29</v>
       </c>
       <c r="V25" t="n">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="W25" t="n">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="X25" t="n">
-        <v>3.74</v>
+        <v>2.78</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.8</v>
+        <v>2.14</v>
       </c>
       <c r="Z25" t="n">
-        <v>2</v>
+        <v>1.65</v>
       </c>
       <c r="AA25" t="n">
-        <v>3</v>
+        <v>3.95</v>
       </c>
       <c r="AB25" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AE25" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF25" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG25" t="n">
         <v>1.33</v>
       </c>
-      <c r="AC25" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="AE25" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF25" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG25" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AH25" t="n">
-        <v>1.74</v>
+        <v>1.71</v>
       </c>
       <c r="AI25" t="n">
         <v>0</v>
@@ -3729,7 +3729,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,77 +3765,77 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.62</v>
+        <v>3.75</v>
       </c>
       <c r="M26" t="n">
-        <v>3.24</v>
+        <v>3.4</v>
       </c>
       <c r="N26" t="n">
-        <v>2.7</v>
+        <v>1.91</v>
       </c>
       <c r="O26" t="n">
-        <v>3.28</v>
+        <v>3.9</v>
       </c>
       <c r="P26" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="S26" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="V26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W26" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="X26" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AD26" t="n">
         <v>2</v>
       </c>
-      <c r="Q26" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="R26" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="S26" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="T26" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="U26" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="V26" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W26" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="X26" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>4.29</v>
-      </c>
-      <c r="AB26" t="n">
+      <c r="AE26" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF26" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG26" t="n">
         <v>1.22</v>
       </c>
-      <c r="AC26" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AE26" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF26" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG26" t="n">
-        <v>1.4</v>
-      </c>
       <c r="AH26" t="n">
-        <v>1.49</v>
+        <v>1.25</v>
       </c>
       <c r="AI26" t="n">
         <v>0</v>
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Mantova</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,61 +3894,61 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.14</v>
+        <v>1.86</v>
       </c>
       <c r="M27" t="n">
         <v>3.4</v>
       </c>
       <c r="N27" t="n">
-        <v>3.5</v>
+        <v>4.18</v>
       </c>
       <c r="O27" t="n">
-        <v>2.81</v>
+        <v>2.5</v>
       </c>
       <c r="P27" t="n">
-        <v>2.12</v>
+        <v>2.18</v>
       </c>
       <c r="Q27" t="n">
-        <v>4.19</v>
+        <v>4.8</v>
       </c>
       <c r="R27" t="n">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="S27" t="n">
-        <v>2.63</v>
+        <v>2.67</v>
       </c>
       <c r="T27" t="n">
-        <v>3.04</v>
+        <v>2.85</v>
       </c>
       <c r="U27" t="n">
-        <v>1.31</v>
+        <v>1.37</v>
       </c>
       <c r="V27" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="W27" t="n">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="X27" t="n">
-        <v>2.88</v>
+        <v>3.08</v>
       </c>
       <c r="Y27" t="n">
-        <v>2.2</v>
+        <v>2.03</v>
       </c>
       <c r="Z27" t="n">
-        <v>1.62</v>
+        <v>1.75</v>
       </c>
       <c r="AA27" t="n">
-        <v>3.82</v>
+        <v>3.55</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
@@ -3961,10 +3961,10 @@
         </is>
       </c>
       <c r="AG27" t="n">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.7</v>
+        <v>1.91</v>
       </c>
       <c r="AI27" t="n">
         <v>0</v>
@@ -3987,7 +3987,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,77 +4023,77 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>3.81</v>
+        <v>2.55</v>
       </c>
       <c r="M28" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="N28" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="O28" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="P28" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q28" t="n">
         <v>3.4</v>
       </c>
-      <c r="N28" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="O28" t="n">
-        <v>4.39</v>
-      </c>
-      <c r="P28" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>2.45</v>
-      </c>
       <c r="R28" t="n">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="S28" t="n">
-        <v>2.98</v>
+        <v>2.6</v>
       </c>
       <c r="T28" t="n">
-        <v>2.74</v>
+        <v>3.2</v>
       </c>
       <c r="U28" t="n">
-        <v>1.42</v>
+        <v>1.3</v>
       </c>
       <c r="V28" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="W28" t="n">
-        <v>1.21</v>
+        <v>1.35</v>
       </c>
       <c r="X28" t="n">
-        <v>3.66</v>
+        <v>2.92</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.84</v>
+        <v>2.18</v>
       </c>
       <c r="Z28" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AC28" t="n">
         <v>1.93</v>
       </c>
-      <c r="AA28" t="n">
-        <v>3</v>
-      </c>
-      <c r="AB28" t="n">
+      <c r="AD28" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AE28" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF28" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG28" t="n">
         <v>1.38</v>
       </c>
-      <c r="AC28" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="AE28" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF28" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG28" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AH28" t="n">
-        <v>1.24</v>
+        <v>1.48</v>
       </c>
       <c r="AI28" t="n">
         <v>0</v>
@@ -4116,7 +4116,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,61 +4152,61 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>3.06</v>
+        <v>2.52</v>
       </c>
       <c r="M29" t="n">
-        <v>3.19</v>
+        <v>3.25</v>
       </c>
       <c r="N29" t="n">
-        <v>2.08</v>
+        <v>2.8</v>
       </c>
       <c r="O29" t="n">
-        <v>3.6</v>
+        <v>3.15</v>
       </c>
       <c r="P29" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.74</v>
+        <v>3.4</v>
       </c>
       <c r="R29" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S29" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="T29" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="V29" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W29" t="n">
         <v>1.38</v>
       </c>
-      <c r="S29" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="T29" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="U29" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="V29" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W29" t="n">
-        <v>1.25</v>
-      </c>
       <c r="X29" t="n">
-        <v>3.45</v>
+        <v>2.78</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.84</v>
+        <v>2.22</v>
       </c>
       <c r="Z29" t="n">
-        <v>1.86</v>
+        <v>1.66</v>
       </c>
       <c r="AA29" t="n">
-        <v>3.2</v>
+        <v>3.95</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.27</v>
+        <v>1.19</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.7</v>
+        <v>1.92</v>
       </c>
       <c r="AD29" t="n">
-        <v>2.03</v>
+        <v>1.85</v>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
@@ -4219,10 +4219,10 @@
         </is>
       </c>
       <c r="AG29" t="n">
-        <v>1.3</v>
+        <v>1.42</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.33</v>
+        <v>1.53</v>
       </c>
       <c r="AI29" t="n">
         <v>0</v>
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,61 +4281,61 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.9</v>
+        <v>2.5</v>
       </c>
       <c r="M30" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="N30" t="n">
-        <v>4</v>
+        <v>2.62</v>
       </c>
       <c r="O30" t="n">
-        <v>2.45</v>
+        <v>3.12</v>
       </c>
       <c r="P30" t="n">
-        <v>2.22</v>
+        <v>2.23</v>
       </c>
       <c r="Q30" t="n">
-        <v>4.72</v>
+        <v>3.33</v>
       </c>
       <c r="R30" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S30" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="U30" t="n">
         <v>1.38</v>
       </c>
-      <c r="S30" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="T30" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="U30" t="n">
-        <v>1.34</v>
-      </c>
       <c r="V30" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="W30" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="X30" t="n">
-        <v>3.2</v>
+        <v>3.45</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.98</v>
+        <v>1.93</v>
       </c>
       <c r="Z30" t="n">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="AA30" t="n">
-        <v>3.4</v>
+        <v>3.08</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AC30" t="n">
-        <v>1.85</v>
+        <v>1.78</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.85</v>
+        <v>2.05</v>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
@@ -4348,10 +4348,10 @@
         </is>
       </c>
       <c r="AG30" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.91</v>
+        <v>1.57</v>
       </c>
       <c r="AI30" t="n">
         <v>0</v>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,61 +4410,61 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="M31" t="n">
-        <v>4.75</v>
+        <v>4.2</v>
       </c>
       <c r="N31" t="n">
-        <v>8</v>
+        <v>5.9</v>
       </c>
       <c r="O31" t="n">
-        <v>1.86</v>
+        <v>2.01</v>
       </c>
       <c r="P31" t="n">
         <v>2.38</v>
       </c>
       <c r="Q31" t="n">
-        <v>7</v>
+        <v>5.5</v>
       </c>
       <c r="R31" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="S31" t="n">
-        <v>3</v>
+        <v>3.14</v>
       </c>
       <c r="T31" t="n">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="U31" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="V31" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="W31" t="n">
-        <v>1.23</v>
+        <v>1.18</v>
       </c>
       <c r="X31" t="n">
-        <v>3.7</v>
+        <v>3.86</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.85</v>
+        <v>1.65</v>
       </c>
       <c r="Z31" t="n">
-        <v>1.89</v>
+        <v>2.1</v>
       </c>
       <c r="AA31" t="n">
-        <v>2.97</v>
+        <v>2.63</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="AC31" t="n">
-        <v>2.11</v>
+        <v>1.83</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.68</v>
+        <v>1.84</v>
       </c>
       <c r="AE31" t="inlineStr">
         <is>
@@ -4477,10 +4477,10 @@
         </is>
       </c>
       <c r="AG31" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AH31" t="n">
-        <v>3.01</v>
+        <v>2.68</v>
       </c>
       <c r="AI31" t="n">
         <v>0</v>
@@ -4539,61 +4539,61 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>3.2</v>
+        <v>2.92</v>
       </c>
       <c r="M32" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="N32" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="O32" t="n">
-        <v>3.58</v>
+        <v>3.54</v>
       </c>
       <c r="P32" t="n">
         <v>2.11</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.97</v>
+        <v>2.99</v>
       </c>
       <c r="R32" t="n">
         <v>1.35</v>
       </c>
       <c r="S32" t="n">
-        <v>3.09</v>
+        <v>2.8</v>
       </c>
       <c r="T32" t="n">
-        <v>2.6</v>
+        <v>2.71</v>
       </c>
       <c r="U32" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="V32" t="n">
         <v>1.02</v>
       </c>
       <c r="W32" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="X32" t="n">
-        <v>3.74</v>
+        <v>3.75</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.77</v>
+        <v>1.88</v>
       </c>
       <c r="Z32" t="n">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="AA32" t="n">
-        <v>3.17</v>
+        <v>3.2</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AC32" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AD32" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="AE32" t="inlineStr">
         <is>
@@ -4609,7 +4609,7 @@
         <v>1.32</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="AI32" t="n">
         <v>0</v>
@@ -4632,7 +4632,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,61 +4668,61 @@
         </is>
       </c>
       <c r="L33" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="M33" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="N33" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="O33" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="P33" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="R33" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S33" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="U33" t="n">
         <v>1.4</v>
-      </c>
-      <c r="M33" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="N33" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="O33" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="P33" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>6.05</v>
-      </c>
-      <c r="R33" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="S33" t="n">
-        <v>3.21</v>
-      </c>
-      <c r="T33" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="U33" t="n">
-        <v>1.5</v>
       </c>
       <c r="V33" t="n">
         <v>1.02</v>
       </c>
       <c r="W33" t="n">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="X33" t="n">
-        <v>4.05</v>
+        <v>3.4</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.65</v>
+        <v>1.89</v>
       </c>
       <c r="Z33" t="n">
-        <v>2.1</v>
+        <v>1.94</v>
       </c>
       <c r="AA33" t="n">
-        <v>2.63</v>
+        <v>3.08</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.42</v>
+        <v>1.3</v>
       </c>
       <c r="AC33" t="n">
-        <v>1.84</v>
+        <v>1.88</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="AE33" t="inlineStr">
         <is>
@@ -4735,10 +4735,10 @@
         </is>
       </c>
       <c r="AG33" t="n">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="AH33" t="n">
-        <v>2.64</v>
+        <v>2.13</v>
       </c>
       <c r="AI33" t="n">
         <v>0</v>
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,61 +4797,61 @@
         </is>
       </c>
       <c r="L34" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="M34" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="N34" t="n">
+        <v>7.75</v>
+      </c>
+      <c r="O34" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="P34" t="n">
         <v>2.36</v>
       </c>
-      <c r="M34" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="N34" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="O34" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="P34" t="n">
-        <v>2.21</v>
-      </c>
       <c r="Q34" t="n">
-        <v>3.34</v>
+        <v>6.5</v>
       </c>
       <c r="R34" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="S34" t="n">
-        <v>2.84</v>
+        <v>3</v>
       </c>
       <c r="T34" t="n">
-        <v>2.67</v>
+        <v>2.64</v>
       </c>
       <c r="U34" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="V34" t="n">
         <v>1.01</v>
       </c>
       <c r="W34" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="X34" t="n">
-        <v>3.35</v>
+        <v>3.7</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.89</v>
+        <v>1.85</v>
       </c>
       <c r="Z34" t="n">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AA34" t="n">
-        <v>3.08</v>
+        <v>2.97</v>
       </c>
       <c r="AB34" t="n">
         <v>1.32</v>
       </c>
       <c r="AC34" t="n">
-        <v>1.62</v>
+        <v>2.08</v>
       </c>
       <c r="AD34" t="n">
-        <v>2.16</v>
+        <v>1.68</v>
       </c>
       <c r="AE34" t="inlineStr">
         <is>
@@ -4864,10 +4864,10 @@
         </is>
       </c>
       <c r="AG34" t="n">
-        <v>1.31</v>
+        <v>1.19</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.5</v>
+        <v>2.99</v>
       </c>
       <c r="AI34" t="n">
         <v>0</v>
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,77 +4926,77 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>1.65</v>
+        <v>1.91</v>
       </c>
       <c r="M35" t="n">
-        <v>3.82</v>
+        <v>3.5</v>
       </c>
       <c r="N35" t="n">
-        <v>4.9</v>
+        <v>4.06</v>
       </c>
       <c r="O35" t="n">
-        <v>2.23</v>
+        <v>2.45</v>
       </c>
       <c r="P35" t="n">
         <v>2.22</v>
       </c>
       <c r="Q35" t="n">
-        <v>5.36</v>
+        <v>4.72</v>
       </c>
       <c r="R35" t="n">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="S35" t="n">
-        <v>3.14</v>
+        <v>2.9</v>
       </c>
       <c r="T35" t="n">
-        <v>2.67</v>
+        <v>2.91</v>
       </c>
       <c r="U35" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="V35" t="n">
         <v>1.02</v>
       </c>
       <c r="W35" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="X35" t="n">
-        <v>3.75</v>
+        <v>3.2</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.83</v>
+        <v>2.02</v>
       </c>
       <c r="Z35" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AE35" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF35" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG35" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AH35" t="n">
         <v>1.91</v>
-      </c>
-      <c r="AA35" t="n">
-        <v>3.02</v>
-      </c>
-      <c r="AB35" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AC35" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AD35" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AE35" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF35" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG35" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AH35" t="n">
-        <v>2.25</v>
       </c>
       <c r="AI35" t="n">
         <v>0</v>
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,61 +5055,61 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.49</v>
+        <v>2.2</v>
       </c>
       <c r="M36" t="n">
-        <v>3.29</v>
+        <v>3.4</v>
       </c>
       <c r="N36" t="n">
-        <v>2.74</v>
+        <v>3.3</v>
       </c>
       <c r="O36" t="n">
-        <v>3.18</v>
+        <v>2.7</v>
       </c>
       <c r="P36" t="n">
-        <v>2.01</v>
+        <v>2.08</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.4</v>
+        <v>3.88</v>
       </c>
       <c r="R36" t="n">
-        <v>1.44</v>
+        <v>1.35</v>
       </c>
       <c r="S36" t="n">
-        <v>2.66</v>
+        <v>2.9</v>
       </c>
       <c r="T36" t="n">
-        <v>3.14</v>
+        <v>3</v>
       </c>
       <c r="U36" t="n">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
       <c r="V36" t="n">
         <v>1.02</v>
       </c>
       <c r="W36" t="n">
-        <v>1.38</v>
+        <v>1.28</v>
       </c>
       <c r="X36" t="n">
-        <v>2.95</v>
+        <v>3.15</v>
       </c>
       <c r="Y36" t="n">
-        <v>2.2</v>
+        <v>2.03</v>
       </c>
       <c r="Z36" t="n">
-        <v>1.68</v>
+        <v>1.72</v>
       </c>
       <c r="AA36" t="n">
-        <v>3.95</v>
+        <v>3.48</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AC36" t="n">
-        <v>1.87</v>
+        <v>1.79</v>
       </c>
       <c r="AD36" t="n">
-        <v>1.83</v>
+        <v>1.94</v>
       </c>
       <c r="AE36" t="inlineStr">
         <is>
@@ -5122,10 +5122,10 @@
         </is>
       </c>
       <c r="AG36" t="n">
-        <v>1.34</v>
+        <v>1.25</v>
       </c>
       <c r="AH36" t="n">
-        <v>1.53</v>
+        <v>1.64</v>
       </c>
       <c r="AI36" t="n">
         <v>0</v>
@@ -5148,7 +5148,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,77 +5184,77 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.19</v>
+        <v>3.06</v>
       </c>
       <c r="M37" t="n">
-        <v>3.47</v>
+        <v>3.19</v>
       </c>
       <c r="N37" t="n">
-        <v>3.08</v>
+        <v>2.08</v>
       </c>
       <c r="O37" t="n">
-        <v>2.88</v>
+        <v>3.9</v>
       </c>
       <c r="P37" t="n">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.88</v>
+        <v>2.75</v>
       </c>
       <c r="R37" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="S37" t="n">
-        <v>2.71</v>
+        <v>2.79</v>
       </c>
       <c r="T37" t="n">
-        <v>3</v>
+        <v>2.67</v>
       </c>
       <c r="U37" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="V37" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W37" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="X37" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AE37" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF37" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG37" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AH37" t="n">
         <v>1.34</v>
-      </c>
-      <c r="V37" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="W37" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="X37" t="n">
-        <v>3.16</v>
-      </c>
-      <c r="Y37" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="Z37" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AA37" t="n">
-        <v>3.48</v>
-      </c>
-      <c r="AB37" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AC37" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AD37" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AE37" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF37" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG37" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AH37" t="n">
-        <v>1.68</v>
       </c>
       <c r="AI37" t="n">
         <v>0</v>
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,61 +5442,61 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>1.35</v>
+        <v>4.54</v>
       </c>
       <c r="M39" t="n">
-        <v>5.3</v>
+        <v>4.62</v>
       </c>
       <c r="N39" t="n">
-        <v>7</v>
+        <v>1.66</v>
       </c>
       <c r="O39" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="R39" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="S39" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="T39" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="U39" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="V39" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W39" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X39" t="n">
-        <v>0</v>
+        <v>5.35</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.6</v>
+        <v>1.44</v>
       </c>
       <c r="Z39" t="n">
-        <v>2.35</v>
+        <v>2.67</v>
       </c>
       <c r="AA39" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AB39" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC39" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AD39" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AE39" t="inlineStr">
         <is>
@@ -5509,10 +5509,10 @@
         </is>
       </c>
       <c r="AG39" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AH39" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AI39" t="n">
         <v>0</v>
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,13 +5571,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>4.3</v>
+        <v>1.35</v>
       </c>
       <c r="M40" t="n">
-        <v>4.4</v>
+        <v>5.3</v>
       </c>
       <c r="N40" t="n">
-        <v>1.64</v>
+        <v>7</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5610,16 +5610,16 @@
         <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="Z40" t="n">
-        <v>2.75</v>
+        <v>2.35</v>
       </c>
       <c r="AA40" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -5664,7 +5664,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,61 +5700,61 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>3</v>
+        <v>2.63</v>
       </c>
       <c r="M41" t="n">
-        <v>3.83</v>
+        <v>3.1</v>
       </c>
       <c r="N41" t="n">
-        <v>2.1</v>
+        <v>2.88</v>
       </c>
       <c r="O41" t="n">
-        <v>3.58</v>
+        <v>3.32</v>
       </c>
       <c r="P41" t="n">
-        <v>2.38</v>
+        <v>2</v>
       </c>
       <c r="Q41" t="n">
-        <v>2.62</v>
+        <v>3.65</v>
       </c>
       <c r="R41" t="n">
-        <v>1.25</v>
+        <v>1.52</v>
       </c>
       <c r="S41" t="n">
-        <v>3.45</v>
+        <v>2.35</v>
       </c>
       <c r="T41" t="n">
-        <v>2.25</v>
+        <v>3.4</v>
       </c>
       <c r="U41" t="n">
-        <v>1.61</v>
+        <v>1.24</v>
       </c>
       <c r="V41" t="n">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="W41" t="n">
-        <v>1.18</v>
+        <v>1.48</v>
       </c>
       <c r="X41" t="n">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.65</v>
+        <v>2.5</v>
       </c>
       <c r="Z41" t="n">
-        <v>2.31</v>
+        <v>1.53</v>
       </c>
       <c r="AA41" t="n">
-        <v>2.25</v>
+        <v>4.7</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.65</v>
+        <v>1.14</v>
       </c>
       <c r="AC41" t="n">
-        <v>1.49</v>
+        <v>2.03</v>
       </c>
       <c r="AD41" t="n">
-        <v>2.48</v>
+        <v>1.72</v>
       </c>
       <c r="AE41" t="inlineStr">
         <is>
@@ -5767,10 +5767,10 @@
         </is>
       </c>
       <c r="AG41" t="n">
-        <v>1.26</v>
+        <v>1.34</v>
       </c>
       <c r="AH41" t="n">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AI41" t="n">
         <v>0</v>
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,61 +5829,61 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>15</v>
+        <v>1.6</v>
       </c>
       <c r="M42" t="n">
-        <v>7.6</v>
+        <v>4.28</v>
       </c>
       <c r="N42" t="n">
-        <v>1.15</v>
+        <v>5.29</v>
       </c>
       <c r="O42" t="n">
-        <v>11.2</v>
+        <v>2.1</v>
       </c>
       <c r="P42" t="n">
-        <v>2.95</v>
+        <v>2.43</v>
       </c>
       <c r="Q42" t="n">
-        <v>1.42</v>
+        <v>4.35</v>
       </c>
       <c r="R42" t="n">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="S42" t="n">
-        <v>3.95</v>
+        <v>3.4</v>
       </c>
       <c r="T42" t="n">
-        <v>2.05</v>
+        <v>2.35</v>
       </c>
       <c r="U42" t="n">
-        <v>1.75</v>
+        <v>1.56</v>
       </c>
       <c r="V42" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="W42" t="n">
-        <v>1.08</v>
+        <v>1.18</v>
       </c>
       <c r="X42" t="n">
-        <v>5.75</v>
+        <v>4.45</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.44</v>
+        <v>1.62</v>
       </c>
       <c r="Z42" t="n">
-        <v>2.75</v>
+        <v>2.38</v>
       </c>
       <c r="AA42" t="n">
-        <v>1.95</v>
+        <v>2.54</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.79</v>
+        <v>1.55</v>
       </c>
       <c r="AC42" t="n">
-        <v>2.25</v>
+        <v>1.67</v>
       </c>
       <c r="AD42" t="n">
-        <v>1.63</v>
+        <v>2.13</v>
       </c>
       <c r="AE42" t="inlineStr">
         <is>
@@ -5896,10 +5896,10 @@
         </is>
       </c>
       <c r="AG42" t="n">
-        <v>5.5</v>
+        <v>1.24</v>
       </c>
       <c r="AH42" t="n">
-        <v>1.03</v>
+        <v>2.41</v>
       </c>
       <c r="AI42" t="n">
         <v>0</v>
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Olympique Marseille</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5958,61 +5958,61 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>1.62</v>
+        <v>1.56</v>
       </c>
       <c r="M43" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="N43" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="O43" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="P43" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="R43" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="S43" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="T43" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="U43" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="V43" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W43" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="X43" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.68</v>
+        <v>1.63</v>
       </c>
       <c r="Z43" t="n">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AA43" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AC43" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AD43" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AE43" t="inlineStr">
         <is>
@@ -6025,10 +6025,10 @@
         </is>
       </c>
       <c r="AG43" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AH43" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="AI43" t="n">
         <v>0</v>
@@ -6061,12 +6061,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Olympique Marseille</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6087,61 +6087,61 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>1.56</v>
+        <v>2.71</v>
       </c>
       <c r="M44" t="n">
-        <v>4.3</v>
+        <v>3.75</v>
       </c>
       <c r="N44" t="n">
-        <v>5.1</v>
+        <v>2.1</v>
       </c>
       <c r="O44" t="n">
-        <v>2.08</v>
+        <v>3.32</v>
       </c>
       <c r="P44" t="n">
-        <v>2.53</v>
+        <v>2.32</v>
       </c>
       <c r="Q44" t="n">
-        <v>4.4</v>
+        <v>2.52</v>
       </c>
       <c r="R44" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="S44" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="T44" t="n">
-        <v>2.45</v>
+        <v>2.25</v>
       </c>
       <c r="U44" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="V44" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="W44" t="n">
         <v>1.18</v>
       </c>
       <c r="X44" t="n">
-        <v>4.55</v>
+        <v>5</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.63</v>
+        <v>1.59</v>
       </c>
       <c r="Z44" t="n">
-        <v>2.25</v>
+        <v>2.44</v>
       </c>
       <c r="AA44" t="n">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="AC44" t="n">
-        <v>1.71</v>
+        <v>1.49</v>
       </c>
       <c r="AD44" t="n">
-        <v>2.14</v>
+        <v>2.48</v>
       </c>
       <c r="AE44" t="inlineStr">
         <is>
@@ -6154,10 +6154,10 @@
         </is>
       </c>
       <c r="AG44" t="n">
-        <v>1.15</v>
+        <v>1.3</v>
       </c>
       <c r="AH44" t="n">
-        <v>2.52</v>
+        <v>1.39</v>
       </c>
       <c r="AI44" t="n">
         <v>0</v>
@@ -6180,7 +6180,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6216,61 +6216,61 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>2.4</v>
+        <v>15</v>
       </c>
       <c r="M45" t="n">
-        <v>3.39</v>
+        <v>7.6</v>
       </c>
       <c r="N45" t="n">
-        <v>2.79</v>
+        <v>1.15</v>
       </c>
       <c r="O45" t="n">
-        <v>3.26</v>
+        <v>11.5</v>
       </c>
       <c r="P45" t="n">
-        <v>1.93</v>
+        <v>3</v>
       </c>
       <c r="Q45" t="n">
-        <v>3.84</v>
+        <v>1.46</v>
       </c>
       <c r="R45" t="n">
-        <v>1.53</v>
+        <v>1.19</v>
       </c>
       <c r="S45" t="n">
-        <v>2.35</v>
+        <v>4.25</v>
       </c>
       <c r="T45" t="n">
-        <v>3.55</v>
+        <v>2.03</v>
       </c>
       <c r="U45" t="n">
-        <v>1.27</v>
+        <v>1.79</v>
       </c>
       <c r="V45" t="n">
-        <v>1.09</v>
+        <v>1.01</v>
       </c>
       <c r="W45" t="n">
-        <v>1.53</v>
+        <v>1.08</v>
       </c>
       <c r="X45" t="n">
-        <v>2.5</v>
+        <v>5.85</v>
       </c>
       <c r="Y45" t="n">
-        <v>2.52</v>
+        <v>1.38</v>
       </c>
       <c r="Z45" t="n">
-        <v>1.52</v>
+        <v>2.82</v>
       </c>
       <c r="AA45" t="n">
-        <v>4.65</v>
+        <v>2.1</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.17</v>
+        <v>1.76</v>
       </c>
       <c r="AC45" t="n">
-        <v>2.11</v>
+        <v>2.31</v>
       </c>
       <c r="AD45" t="n">
-        <v>1.73</v>
+        <v>1.6</v>
       </c>
       <c r="AE45" t="inlineStr">
         <is>
@@ -6283,10 +6283,10 @@
         </is>
       </c>
       <c r="AG45" t="n">
-        <v>1.37</v>
+        <v>1.08</v>
       </c>
       <c r="AH45" t="n">
-        <v>1.52</v>
+        <v>1.01</v>
       </c>
       <c r="AI45" t="n">
         <v>0</v>
@@ -6603,13 +6603,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>2.02</v>
+        <v>1.93</v>
       </c>
       <c r="M48" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="N48" t="n">
-        <v>3.7</v>
+        <v>3.57</v>
       </c>
       <c r="O48" t="n">
         <v>2.67</v>
@@ -6618,13 +6618,13 @@
         <v>2</v>
       </c>
       <c r="Q48" t="n">
-        <v>4.25</v>
+        <v>4.35</v>
       </c>
       <c r="R48" t="n">
-        <v>1.43</v>
+        <v>1.51</v>
       </c>
       <c r="S48" t="n">
-        <v>2.39</v>
+        <v>2.47</v>
       </c>
       <c r="T48" t="n">
         <v>3.3</v>
@@ -6636,16 +6636,16 @@
         <v>1.09</v>
       </c>
       <c r="W48" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="X48" t="n">
         <v>2.53</v>
       </c>
       <c r="Y48" t="n">
-        <v>2.49</v>
+        <v>2.12</v>
       </c>
       <c r="Z48" t="n">
-        <v>1.56</v>
+        <v>1.64</v>
       </c>
       <c r="AA48" t="n">
         <v>4.1</v>
@@ -6654,10 +6654,10 @@
         <v>1.18</v>
       </c>
       <c r="AC48" t="n">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="AD48" t="n">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AE48" t="inlineStr">
         <is>
@@ -6670,10 +6670,10 @@
         </is>
       </c>
       <c r="AG48" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AH48" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="AI48" t="n">
         <v>0</v>

--- a/jogos_2025-09-30.xlsx
+++ b/jogos_2025-09-30.xlsx
@@ -1185,31 +1185,31 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>4.6</v>
+        <v>5.5</v>
       </c>
       <c r="M6" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="N6" t="n">
-        <v>1.82</v>
+        <v>1.55</v>
       </c>
       <c r="O6" t="n">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="P6" t="n">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.09</v>
+        <v>2.15</v>
       </c>
       <c r="R6" t="n">
         <v>1.38</v>
       </c>
       <c r="S6" t="n">
-        <v>2.92</v>
+        <v>2.75</v>
       </c>
       <c r="T6" t="n">
-        <v>2.92</v>
+        <v>2.75</v>
       </c>
       <c r="U6" t="n">
         <v>1.38</v>
@@ -1221,25 +1221,25 @@
         <v>1.28</v>
       </c>
       <c r="X6" t="n">
-        <v>3.33</v>
+        <v>3.1</v>
       </c>
       <c r="Y6" t="n">
-        <v>2.25</v>
+        <v>2.07</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.65</v>
+        <v>1.79</v>
       </c>
       <c r="AA6" t="n">
         <v>3.35</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AC6" t="n">
         <v>1.99</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.73</v>
+        <v>1.68</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
@@ -1252,10 +1252,10 @@
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AI6" t="n">
         <v>2.38</v>
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,13 +1443,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>19</v>
+        <v>1.86</v>
       </c>
       <c r="M8" t="n">
-        <v>8.9</v>
+        <v>3.84</v>
       </c>
       <c r="N8" t="n">
-        <v>1.11</v>
+        <v>3.7</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1482,16 +1482,16 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.3</v>
+        <v>1.7</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.4</v>
+        <v>2.15</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,61 +1572,61 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.91</v>
+        <v>19</v>
       </c>
       <c r="M9" t="n">
-        <v>4</v>
+        <v>8.9</v>
       </c>
       <c r="N9" t="n">
-        <v>3.6</v>
+        <v>1.11</v>
       </c>
       <c r="O9" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.65</v>
+        <v>1.3</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.31</v>
+        <v>3.4</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.54</v>
+        <v>1.8</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.47</v>
+        <v>1.94</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
@@ -1665,22 +1665,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Havelse</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Waldhof Mannheim</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,77 +1701,77 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.56</v>
+        <v>3.6</v>
       </c>
       <c r="M10" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="N10" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="O10" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="P10" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S10" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="X10" t="n">
         <v>4.2</v>
       </c>
-      <c r="N10" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="O10" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="P10" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>4.95</v>
-      </c>
-      <c r="R10" t="n">
+      <c r="Y10" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG10" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AH10" t="n">
         <v>1.25</v>
-      </c>
-      <c r="S10" t="n">
-        <v>3.66</v>
-      </c>
-      <c r="T10" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="V10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X10" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AE10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG10" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>2.4</v>
       </c>
       <c r="AI10" t="n">
         <v>0</v>
@@ -1839,52 +1839,52 @@
         <v>2.31</v>
       </c>
       <c r="O11" t="n">
-        <v>3.34</v>
+        <v>3</v>
       </c>
       <c r="P11" t="n">
-        <v>2.21</v>
+        <v>2.3</v>
       </c>
       <c r="Q11" t="n">
-        <v>3</v>
+        <v>2.83</v>
       </c>
       <c r="R11" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="S11" t="n">
-        <v>3.26</v>
+        <v>3.2</v>
       </c>
       <c r="T11" t="n">
-        <v>2.39</v>
+        <v>2.41</v>
       </c>
       <c r="U11" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="V11" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="W11" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="X11" t="n">
-        <v>4.35</v>
+        <v>4.2</v>
       </c>
       <c r="Y11" t="n">
         <v>1.53</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.33</v>
+        <v>2.49</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.44</v>
+        <v>1.51</v>
       </c>
       <c r="AD11" t="n">
-        <v>2.33</v>
+        <v>2.3</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -1897,7 +1897,7 @@
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>1.25</v>
+        <v>1.57</v>
       </c>
       <c r="AH11" t="n">
         <v>1.4</v>
@@ -1959,61 +1959,61 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.08</v>
+        <v>1.87</v>
       </c>
       <c r="M12" t="n">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="N12" t="n">
-        <v>2.84</v>
+        <v>2.95</v>
       </c>
       <c r="O12" t="n">
-        <v>2.61</v>
+        <v>2.7</v>
       </c>
       <c r="P12" t="n">
-        <v>2.18</v>
+        <v>2.3</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.46</v>
+        <v>3.3</v>
       </c>
       <c r="R12" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="S12" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="T12" t="n">
-        <v>2.39</v>
+        <v>2.49</v>
       </c>
       <c r="U12" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="V12" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="W12" t="n">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="X12" t="n">
-        <v>4.33</v>
+        <v>4.1</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.61</v>
+        <v>1.67</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.19</v>
+        <v>2.09</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.56</v>
+        <v>2.59</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.51</v>
+        <v>1.57</v>
       </c>
       <c r="AD12" t="n">
-        <v>2.36</v>
+        <v>2.3</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -2029,7 +2029,7 @@
         <v>1.3</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="AI12" t="n">
         <v>0</v>
@@ -2052,22 +2052,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Havelse</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Waldhof Mannheim</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,61 +2088,61 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>3.1</v>
+        <v>1.56</v>
       </c>
       <c r="M13" t="n">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="N13" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="O13" t="n">
         <v>1.95</v>
       </c>
-      <c r="O13" t="n">
-        <v>4.12</v>
-      </c>
       <c r="P13" t="n">
-        <v>2.39</v>
+        <v>2.5</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.47</v>
+        <v>4.95</v>
       </c>
       <c r="R13" t="n">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="S13" t="n">
-        <v>3.2</v>
+        <v>3.66</v>
       </c>
       <c r="T13" t="n">
-        <v>2.49</v>
+        <v>2.2</v>
       </c>
       <c r="U13" t="n">
-        <v>1.49</v>
+        <v>1.63</v>
       </c>
       <c r="V13" t="n">
         <v>1.01</v>
       </c>
       <c r="W13" t="n">
-        <v>1.16</v>
+        <v>1.11</v>
       </c>
       <c r="X13" t="n">
-        <v>4.11</v>
+        <v>5.6</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.65</v>
+        <v>1.42</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.13</v>
+        <v>2.7</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.45</v>
+        <v>1.92</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.4</v>
+        <v>1.78</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AD13" t="n">
-        <v>2.23</v>
+        <v>2.3</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
@@ -2155,10 +2155,10 @@
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>1.23</v>
+        <v>1.19</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.24</v>
+        <v>2.4</v>
       </c>
       <c r="AI13" t="n">
         <v>0</v>
@@ -2181,22 +2181,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Hansa Rostock</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,61 +2217,61 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.26</v>
+        <v>1.96</v>
       </c>
       <c r="M14" t="n">
-        <v>5.1</v>
+        <v>3.63</v>
       </c>
       <c r="N14" t="n">
-        <v>7.6</v>
+        <v>3.16</v>
       </c>
       <c r="O14" t="n">
-        <v>1.83</v>
+        <v>2.28</v>
       </c>
       <c r="P14" t="n">
-        <v>2.45</v>
+        <v>2.25</v>
       </c>
       <c r="Q14" t="n">
-        <v>5.7</v>
+        <v>3.75</v>
       </c>
       <c r="R14" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="S14" t="n">
-        <v>3.6</v>
+        <v>3.14</v>
       </c>
       <c r="T14" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="U14" t="n">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="V14" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="W14" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="X14" t="n">
-        <v>4.5</v>
+        <v>3.96</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.47</v>
+        <v>1.61</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.17</v>
+        <v>2.7</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.62</v>
+        <v>1.45</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.86</v>
+        <v>1.57</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.91</v>
+        <v>2.07</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
@@ -2284,10 +2284,10 @@
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>1.17</v>
+        <v>1.24</v>
       </c>
       <c r="AH14" t="n">
-        <v>2.78</v>
+        <v>1.76</v>
       </c>
       <c r="AI14" t="n">
         <v>0</v>
@@ -2310,22 +2310,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Erzgebirge Aue</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,61 +2346,61 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.01</v>
+        <v>1.26</v>
       </c>
       <c r="M15" t="n">
-        <v>3.5</v>
+        <v>5.1</v>
       </c>
       <c r="N15" t="n">
-        <v>2.96</v>
+        <v>7.6</v>
       </c>
       <c r="O15" t="n">
-        <v>2.53</v>
+        <v>1.83</v>
       </c>
       <c r="P15" t="n">
-        <v>2.32</v>
+        <v>2.45</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.91</v>
+        <v>5.7</v>
       </c>
       <c r="R15" t="n">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="S15" t="n">
-        <v>3.1</v>
+        <v>3.6</v>
       </c>
       <c r="T15" t="n">
-        <v>2.55</v>
+        <v>2.2</v>
       </c>
       <c r="U15" t="n">
-        <v>1.46</v>
+        <v>1.62</v>
       </c>
       <c r="V15" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="W15" t="n">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="X15" t="n">
-        <v>3.68</v>
+        <v>4.5</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.71</v>
+        <v>1.47</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.98</v>
+        <v>2.5</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.74</v>
+        <v>2.17</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.35</v>
+        <v>1.62</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.62</v>
+        <v>1.86</v>
       </c>
       <c r="AD15" t="n">
-        <v>2.11</v>
+        <v>1.91</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
@@ -2413,10 +2413,10 @@
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>1.28</v>
+        <v>1.17</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.68</v>
+        <v>2.78</v>
       </c>
       <c r="AI15" t="n">
         <v>0</v>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Hansa Rostock</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>Erzgebirge Aue</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,61 +2475,61 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="M16" t="n">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="N16" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="O16" t="n">
-        <v>2.47</v>
+        <v>2.55</v>
       </c>
       <c r="P16" t="n">
-        <v>2.22</v>
+        <v>2.21</v>
       </c>
       <c r="Q16" t="n">
-        <v>4.01</v>
+        <v>3.89</v>
       </c>
       <c r="R16" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="S16" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="T16" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="U16" t="n">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="V16" t="n">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="W16" t="n">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="X16" t="n">
-        <v>4.21</v>
+        <v>3.68</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="Z16" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.55</v>
+        <v>2.95</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.41</v>
+        <v>1.35</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="AD16" t="n">
-        <v>2.21</v>
+        <v>2.15</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
@@ -2542,10 +2542,10 @@
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.9</v>
+        <v>1.71</v>
       </c>
       <c r="AI16" t="n">
         <v>0</v>
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,62 +2604,62 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.16</v>
+        <v>1.7</v>
       </c>
       <c r="M17" t="n">
-        <v>3.86</v>
+        <v>3.5</v>
       </c>
       <c r="N17" t="n">
-        <v>2.94</v>
+        <v>3.81</v>
       </c>
       <c r="O17" t="n">
-        <v>2.6</v>
+        <v>2.35</v>
       </c>
       <c r="P17" t="n">
-        <v>2.45</v>
+        <v>2.2</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="R17" t="n">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="S17" t="n">
-        <v>3.7</v>
+        <v>3.28</v>
       </c>
       <c r="T17" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="X17" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AD17" t="n">
         <v>2.25</v>
       </c>
-      <c r="U17" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="V17" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="X17" t="n">
-        <v>5.32</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>2.51</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>2.59</v>
-      </c>
       <c r="AE17" t="inlineStr">
         <is>
           <t>[]</t>
@@ -2671,10 +2671,10 @@
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.67</v>
+        <v>1.93</v>
       </c>
       <c r="AI17" t="n">
         <v>0</v>
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,77 +2733,77 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="O18" t="n">
-        <v>1.84</v>
+        <v>3.5</v>
       </c>
       <c r="P18" t="n">
-        <v>2.85</v>
+        <v>2.47</v>
       </c>
       <c r="Q18" t="n">
-        <v>5.93</v>
+        <v>2.55</v>
       </c>
       <c r="R18" t="n">
-        <v>1.21</v>
+        <v>1.28</v>
       </c>
       <c r="S18" t="n">
-        <v>3.75</v>
+        <v>3.34</v>
       </c>
       <c r="T18" t="n">
-        <v>2.13</v>
+        <v>2.32</v>
       </c>
       <c r="U18" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="X18" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AE18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG18" t="n">
         <v>1.67</v>
       </c>
-      <c r="V18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="X18" t="n">
-        <v>5.35</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AE18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG18" t="n">
-        <v>1.16</v>
-      </c>
       <c r="AH18" t="n">
-        <v>2.86</v>
+        <v>1.37</v>
       </c>
       <c r="AI18" t="n">
         <v>0</v>
@@ -2862,58 +2862,58 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>3.34</v>
+        <v>3.1</v>
       </c>
       <c r="M19" t="n">
-        <v>3.92</v>
+        <v>3.5</v>
       </c>
       <c r="N19" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="O19" t="n">
-        <v>3.59</v>
+        <v>3.7</v>
       </c>
       <c r="P19" t="n">
-        <v>2.39</v>
+        <v>2.38</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.4</v>
+        <v>2.61</v>
       </c>
       <c r="R19" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="S19" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="T19" t="n">
         <v>2.2</v>
       </c>
       <c r="U19" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="V19" t="n">
         <v>1.01</v>
       </c>
       <c r="W19" t="n">
-        <v>1.16</v>
+        <v>1.11</v>
       </c>
       <c r="X19" t="n">
-        <v>5.16</v>
+        <v>4.95</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="Z19" t="n">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.25</v>
+        <v>2.26</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="AD19" t="n">
         <v>2.5</v>
@@ -2929,10 +2929,10 @@
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>1.24</v>
+        <v>1.75</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AI19" t="n">
         <v>0</v>
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,61 +2991,61 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>4.01</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>2.3</v>
+        <v>1.85</v>
       </c>
       <c r="P20" t="n">
-        <v>2.28</v>
+        <v>2.61</v>
       </c>
       <c r="Q20" t="n">
-        <v>4.52</v>
+        <v>5.93</v>
       </c>
       <c r="R20" t="n">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="S20" t="n">
-        <v>3.28</v>
+        <v>3.9</v>
       </c>
       <c r="T20" t="n">
-        <v>2.47</v>
+        <v>2.05</v>
       </c>
       <c r="U20" t="n">
-        <v>1.48</v>
+        <v>1.7</v>
       </c>
       <c r="V20" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="W20" t="n">
-        <v>1.16</v>
+        <v>1.09</v>
       </c>
       <c r="X20" t="n">
-        <v>4.15</v>
+        <v>5.75</v>
       </c>
       <c r="Y20" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AB20" t="n">
         <v>1.68</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>1.39</v>
       </c>
       <c r="AC20" t="n">
         <v>1.62</v>
       </c>
       <c r="AD20" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
@@ -3058,10 +3058,10 @@
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>1.24</v>
+        <v>1.1</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.98</v>
+        <v>2.5</v>
       </c>
       <c r="AI20" t="n">
         <v>0</v>
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,61 +3120,61 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.9</v>
+        <v>2.1</v>
       </c>
       <c r="M21" t="n">
-        <v>3.66</v>
+        <v>3.6</v>
       </c>
       <c r="N21" t="n">
-        <v>2.18</v>
+        <v>2.87</v>
       </c>
       <c r="O21" t="n">
-        <v>3.5</v>
+        <v>2.65</v>
       </c>
       <c r="P21" t="n">
-        <v>2.43</v>
+        <v>2.51</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.65</v>
+        <v>3.4</v>
       </c>
       <c r="R21" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="S21" t="n">
-        <v>3.34</v>
+        <v>3.45</v>
       </c>
       <c r="T21" t="n">
-        <v>2.3</v>
+        <v>2.21</v>
       </c>
       <c r="U21" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="V21" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="W21" t="n">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="X21" t="n">
-        <v>4.75</v>
+        <v>5.32</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.59</v>
+        <v>1.53</v>
       </c>
       <c r="Z21" t="n">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.36</v>
+        <v>2.28</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="AD21" t="n">
-        <v>2.45</v>
+        <v>2.59</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
@@ -3187,10 +3187,10 @@
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.36</v>
+        <v>1.68</v>
       </c>
       <c r="AI21" t="n">
         <v>0</v>
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,61 +3249,61 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.12</v>
+        <v>3.41</v>
       </c>
       <c r="M22" t="n">
-        <v>3.37</v>
+        <v>3.26</v>
       </c>
       <c r="N22" t="n">
-        <v>3.38</v>
+        <v>2.13</v>
       </c>
       <c r="O22" t="n">
-        <v>2.73</v>
+        <v>4</v>
       </c>
       <c r="P22" t="n">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="Q22" t="n">
-        <v>4</v>
+        <v>2.86</v>
       </c>
       <c r="R22" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="S22" t="n">
-        <v>2.91</v>
+        <v>2.42</v>
       </c>
       <c r="T22" t="n">
-        <v>2.67</v>
+        <v>3.2</v>
       </c>
       <c r="U22" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="V22" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="W22" t="n">
-        <v>1.22</v>
+        <v>1.44</v>
       </c>
       <c r="X22" t="n">
-        <v>3.75</v>
+        <v>2.75</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.9</v>
+        <v>2.31</v>
       </c>
       <c r="Z22" t="n">
-        <v>1.95</v>
+        <v>1.6</v>
       </c>
       <c r="AA22" t="n">
-        <v>3.02</v>
+        <v>4.41</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.31</v>
+        <v>1.19</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.67</v>
+        <v>1.96</v>
       </c>
       <c r="AD22" t="n">
-        <v>2.04</v>
+        <v>1.77</v>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
@@ -3316,10 +3316,10 @@
         </is>
       </c>
       <c r="AG22" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AH22" t="n">
         <v>1.3</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>1.7</v>
       </c>
       <c r="AI22" t="n">
         <v>0</v>
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Calcio Padova</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,61 +3378,61 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.31</v>
+        <v>2</v>
       </c>
       <c r="M23" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="N23" t="n">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="O23" t="n">
-        <v>3.16</v>
+        <v>2.75</v>
       </c>
       <c r="P23" t="n">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="Q23" t="n">
-        <v>4.11</v>
+        <v>4.38</v>
       </c>
       <c r="R23" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="S23" t="n">
-        <v>2.42</v>
+        <v>2.51</v>
       </c>
       <c r="T23" t="n">
-        <v>3.2</v>
+        <v>3.14</v>
       </c>
       <c r="U23" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="V23" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="W23" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="X23" t="n">
-        <v>2.65</v>
+        <v>2.78</v>
       </c>
       <c r="Y23" t="n">
-        <v>2.35</v>
+        <v>2.14</v>
       </c>
       <c r="Z23" t="n">
-        <v>1.55</v>
+        <v>1.65</v>
       </c>
       <c r="AA23" t="n">
-        <v>4.75</v>
+        <v>3.95</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.96</v>
+        <v>1.85</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.75</v>
+        <v>1.81</v>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
@@ -3445,10 +3445,10 @@
         </is>
       </c>
       <c r="AG23" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.58</v>
+        <v>1.71</v>
       </c>
       <c r="AI23" t="n">
         <v>0</v>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Calcio Padova</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,22 +3507,22 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>3.41</v>
+        <v>2.31</v>
       </c>
       <c r="M24" t="n">
-        <v>3.26</v>
+        <v>3.1</v>
       </c>
       <c r="N24" t="n">
-        <v>2.13</v>
+        <v>3.1</v>
       </c>
       <c r="O24" t="n">
-        <v>4</v>
+        <v>3.16</v>
       </c>
       <c r="P24" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.86</v>
+        <v>4.11</v>
       </c>
       <c r="R24" t="n">
         <v>1.5</v>
@@ -3534,34 +3534,34 @@
         <v>3.2</v>
       </c>
       <c r="U24" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="V24" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="W24" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="X24" t="n">
-        <v>2.75</v>
+        <v>2.65</v>
       </c>
       <c r="Y24" t="n">
-        <v>2.31</v>
+        <v>2.35</v>
       </c>
       <c r="Z24" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AA24" t="n">
-        <v>4.41</v>
+        <v>4.75</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AC24" t="n">
         <v>1.96</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
@@ -3574,10 +3574,10 @@
         </is>
       </c>
       <c r="AG24" t="n">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.3</v>
+        <v>1.58</v>
       </c>
       <c r="AI24" t="n">
         <v>0</v>
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Mantova</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,61 +3636,61 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="M25" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="N25" t="n">
-        <v>3.5</v>
+        <v>4.18</v>
       </c>
       <c r="O25" t="n">
-        <v>2.75</v>
+        <v>2.5</v>
       </c>
       <c r="P25" t="n">
-        <v>2</v>
+        <v>2.18</v>
       </c>
       <c r="Q25" t="n">
-        <v>4.38</v>
+        <v>4.8</v>
       </c>
       <c r="R25" t="n">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="S25" t="n">
-        <v>2.51</v>
+        <v>2.67</v>
       </c>
       <c r="T25" t="n">
-        <v>3.14</v>
+        <v>2.85</v>
       </c>
       <c r="U25" t="n">
-        <v>1.29</v>
+        <v>1.37</v>
       </c>
       <c r="V25" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="W25" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="X25" t="n">
-        <v>2.78</v>
+        <v>3.08</v>
       </c>
       <c r="Y25" t="n">
-        <v>2.14</v>
+        <v>2.03</v>
       </c>
       <c r="Z25" t="n">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="AA25" t="n">
-        <v>3.95</v>
+        <v>3.55</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
@@ -3703,10 +3703,10 @@
         </is>
       </c>
       <c r="AG25" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.71</v>
+        <v>1.91</v>
       </c>
       <c r="AI25" t="n">
         <v>0</v>
@@ -3729,7 +3729,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,61 +3765,61 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>3.75</v>
+        <v>2.55</v>
       </c>
       <c r="M26" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="N26" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="O26" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="P26" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q26" t="n">
         <v>3.4</v>
       </c>
-      <c r="N26" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="O26" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="P26" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>2.44</v>
-      </c>
       <c r="R26" t="n">
-        <v>1.34</v>
+        <v>1.44</v>
       </c>
       <c r="S26" t="n">
-        <v>3.11</v>
+        <v>2.6</v>
       </c>
       <c r="T26" t="n">
-        <v>2.43</v>
+        <v>3.2</v>
       </c>
       <c r="U26" t="n">
-        <v>1.42</v>
+        <v>1.3</v>
       </c>
       <c r="V26" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="W26" t="n">
-        <v>1.22</v>
+        <v>1.35</v>
       </c>
       <c r="X26" t="n">
-        <v>3.6</v>
+        <v>2.92</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.8</v>
+        <v>2.18</v>
       </c>
       <c r="Z26" t="n">
-        <v>1.95</v>
+        <v>1.62</v>
       </c>
       <c r="AA26" t="n">
-        <v>2.92</v>
+        <v>4.29</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.35</v>
+        <v>1.18</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.67</v>
+        <v>1.93</v>
       </c>
       <c r="AD26" t="n">
-        <v>2</v>
+        <v>1.87</v>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
@@ -3832,10 +3832,10 @@
         </is>
       </c>
       <c r="AG26" t="n">
-        <v>1.22</v>
+        <v>1.38</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.25</v>
+        <v>1.48</v>
       </c>
       <c r="AI26" t="n">
         <v>0</v>
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mantova</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,77 +3894,77 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.86</v>
+        <v>2.12</v>
       </c>
       <c r="M27" t="n">
-        <v>3.4</v>
+        <v>3.37</v>
       </c>
       <c r="N27" t="n">
-        <v>4.18</v>
+        <v>3.38</v>
       </c>
       <c r="O27" t="n">
-        <v>2.5</v>
+        <v>2.73</v>
       </c>
       <c r="P27" t="n">
-        <v>2.18</v>
+        <v>2.1</v>
       </c>
       <c r="Q27" t="n">
-        <v>4.8</v>
+        <v>4</v>
       </c>
       <c r="R27" t="n">
-        <v>1.39</v>
+        <v>1.33</v>
       </c>
       <c r="S27" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="T27" t="n">
         <v>2.67</v>
       </c>
-      <c r="T27" t="n">
-        <v>2.85</v>
-      </c>
       <c r="U27" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="V27" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="W27" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="X27" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AE27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG27" t="n">
         <v>1.3</v>
       </c>
-      <c r="X27" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AE27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG27" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AH27" t="n">
-        <v>1.91</v>
+        <v>1.7</v>
       </c>
       <c r="AI27" t="n">
         <v>0</v>
@@ -3987,7 +3987,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,62 +4023,62 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.55</v>
+        <v>3.75</v>
       </c>
       <c r="M28" t="n">
-        <v>3.24</v>
+        <v>3.4</v>
       </c>
       <c r="N28" t="n">
-        <v>2.7</v>
+        <v>1.91</v>
       </c>
       <c r="O28" t="n">
-        <v>3.2</v>
+        <v>3.9</v>
       </c>
       <c r="P28" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="R28" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="S28" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="V28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W28" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="X28" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AD28" t="n">
         <v>2</v>
       </c>
-      <c r="Q28" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="R28" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S28" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="T28" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="U28" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="V28" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W28" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="X28" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>4.29</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>1.87</v>
-      </c>
       <c r="AE28" t="inlineStr">
         <is>
           <t>[]</t>
@@ -4090,10 +4090,10 @@
         </is>
       </c>
       <c r="AG28" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.48</v>
+        <v>1.25</v>
       </c>
       <c r="AI28" t="n">
         <v>0</v>
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,61 +4152,61 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.52</v>
+        <v>1.67</v>
       </c>
       <c r="M29" t="n">
-        <v>3.25</v>
+        <v>3.8</v>
       </c>
       <c r="N29" t="n">
-        <v>2.8</v>
+        <v>4.8</v>
       </c>
       <c r="O29" t="n">
-        <v>3.15</v>
+        <v>2.2</v>
       </c>
       <c r="P29" t="n">
-        <v>2.05</v>
+        <v>2.34</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.4</v>
+        <v>4.7</v>
       </c>
       <c r="R29" t="n">
-        <v>1.44</v>
+        <v>1.35</v>
       </c>
       <c r="S29" t="n">
-        <v>2.51</v>
+        <v>3.05</v>
       </c>
       <c r="T29" t="n">
-        <v>3.14</v>
+        <v>2.6</v>
       </c>
       <c r="U29" t="n">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="V29" t="n">
         <v>1.02</v>
       </c>
       <c r="W29" t="n">
-        <v>1.38</v>
+        <v>1.25</v>
       </c>
       <c r="X29" t="n">
-        <v>2.78</v>
+        <v>3.4</v>
       </c>
       <c r="Y29" t="n">
-        <v>2.22</v>
+        <v>1.89</v>
       </c>
       <c r="Z29" t="n">
-        <v>1.66</v>
+        <v>1.94</v>
       </c>
       <c r="AA29" t="n">
-        <v>3.95</v>
+        <v>3.08</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.19</v>
+        <v>1.3</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.92</v>
+        <v>1.88</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
@@ -4219,10 +4219,10 @@
         </is>
       </c>
       <c r="AG29" t="n">
-        <v>1.42</v>
+        <v>1.18</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.53</v>
+        <v>2.13</v>
       </c>
       <c r="AI29" t="n">
         <v>0</v>
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,61 +4281,61 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.5</v>
+        <v>1.41</v>
       </c>
       <c r="M30" t="n">
-        <v>3.25</v>
+        <v>4.6</v>
       </c>
       <c r="N30" t="n">
-        <v>2.62</v>
+        <v>7.75</v>
       </c>
       <c r="O30" t="n">
-        <v>3.12</v>
+        <v>1.88</v>
       </c>
       <c r="P30" t="n">
-        <v>2.23</v>
+        <v>2.36</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.33</v>
+        <v>6.5</v>
       </c>
       <c r="R30" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="S30" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="T30" t="n">
-        <v>2.71</v>
+        <v>2.64</v>
       </c>
       <c r="U30" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="V30" t="n">
         <v>1.01</v>
       </c>
       <c r="W30" t="n">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="X30" t="n">
-        <v>3.45</v>
+        <v>3.7</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.93</v>
+        <v>1.85</v>
       </c>
       <c r="Z30" t="n">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="AA30" t="n">
-        <v>3.08</v>
+        <v>2.97</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AC30" t="n">
-        <v>1.78</v>
+        <v>2.08</v>
       </c>
       <c r="AD30" t="n">
-        <v>2.05</v>
+        <v>1.68</v>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
@@ -4348,10 +4348,10 @@
         </is>
       </c>
       <c r="AG30" t="n">
-        <v>1.3</v>
+        <v>1.19</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.57</v>
+        <v>2.99</v>
       </c>
       <c r="AI30" t="n">
         <v>0</v>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,61 +4410,61 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.4</v>
+        <v>2.92</v>
       </c>
       <c r="M31" t="n">
-        <v>4.2</v>
+        <v>3.6</v>
       </c>
       <c r="N31" t="n">
-        <v>5.9</v>
+        <v>2.4</v>
       </c>
       <c r="O31" t="n">
-        <v>2.01</v>
+        <v>3.54</v>
       </c>
       <c r="P31" t="n">
-        <v>2.38</v>
+        <v>2.11</v>
       </c>
       <c r="Q31" t="n">
-        <v>5.5</v>
+        <v>2.99</v>
       </c>
       <c r="R31" t="n">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="S31" t="n">
-        <v>3.14</v>
+        <v>2.8</v>
       </c>
       <c r="T31" t="n">
-        <v>2.6</v>
+        <v>2.71</v>
       </c>
       <c r="U31" t="n">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="V31" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="W31" t="n">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="X31" t="n">
-        <v>3.86</v>
+        <v>3.75</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.65</v>
+        <v>1.88</v>
       </c>
       <c r="Z31" t="n">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="AA31" t="n">
-        <v>2.63</v>
+        <v>3.2</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.42</v>
+        <v>1.3</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.83</v>
+        <v>1.67</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.84</v>
+        <v>2.11</v>
       </c>
       <c r="AE31" t="inlineStr">
         <is>
@@ -4477,10 +4477,10 @@
         </is>
       </c>
       <c r="AG31" t="n">
-        <v>1.21</v>
+        <v>1.32</v>
       </c>
       <c r="AH31" t="n">
-        <v>2.68</v>
+        <v>1.41</v>
       </c>
       <c r="AI31" t="n">
         <v>0</v>
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,61 +4539,61 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.92</v>
+        <v>2.52</v>
       </c>
       <c r="M32" t="n">
-        <v>3.6</v>
+        <v>3.25</v>
       </c>
       <c r="N32" t="n">
-        <v>2.4</v>
+        <v>2.8</v>
       </c>
       <c r="O32" t="n">
-        <v>3.54</v>
+        <v>3.15</v>
       </c>
       <c r="P32" t="n">
-        <v>2.11</v>
+        <v>2.05</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.99</v>
+        <v>3.4</v>
       </c>
       <c r="R32" t="n">
-        <v>1.35</v>
+        <v>1.44</v>
       </c>
       <c r="S32" t="n">
-        <v>2.8</v>
+        <v>2.51</v>
       </c>
       <c r="T32" t="n">
-        <v>2.71</v>
+        <v>3.14</v>
       </c>
       <c r="U32" t="n">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="V32" t="n">
         <v>1.02</v>
       </c>
       <c r="W32" t="n">
-        <v>1.24</v>
+        <v>1.38</v>
       </c>
       <c r="X32" t="n">
-        <v>3.75</v>
+        <v>2.78</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.88</v>
+        <v>2.22</v>
       </c>
       <c r="Z32" t="n">
-        <v>1.95</v>
+        <v>1.66</v>
       </c>
       <c r="AA32" t="n">
-        <v>3.2</v>
+        <v>3.95</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.3</v>
+        <v>1.19</v>
       </c>
       <c r="AC32" t="n">
-        <v>1.67</v>
+        <v>1.92</v>
       </c>
       <c r="AD32" t="n">
-        <v>2.11</v>
+        <v>1.85</v>
       </c>
       <c r="AE32" t="inlineStr">
         <is>
@@ -4606,10 +4606,10 @@
         </is>
       </c>
       <c r="AG32" t="n">
-        <v>1.32</v>
+        <v>1.42</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.41</v>
+        <v>1.53</v>
       </c>
       <c r="AI32" t="n">
         <v>0</v>
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,49 +4668,49 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.67</v>
+        <v>2.5</v>
       </c>
       <c r="M33" t="n">
-        <v>3.8</v>
+        <v>3.25</v>
       </c>
       <c r="N33" t="n">
-        <v>4.8</v>
+        <v>2.62</v>
       </c>
       <c r="O33" t="n">
-        <v>2.2</v>
+        <v>3.12</v>
       </c>
       <c r="P33" t="n">
-        <v>2.34</v>
+        <v>2.23</v>
       </c>
       <c r="Q33" t="n">
-        <v>4.7</v>
+        <v>3.33</v>
       </c>
       <c r="R33" t="n">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="S33" t="n">
-        <v>3.05</v>
+        <v>2.9</v>
       </c>
       <c r="T33" t="n">
-        <v>2.6</v>
+        <v>2.71</v>
       </c>
       <c r="U33" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="V33" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W33" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="X33" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.89</v>
+        <v>1.93</v>
       </c>
       <c r="Z33" t="n">
-        <v>1.94</v>
+        <v>1.8</v>
       </c>
       <c r="AA33" t="n">
         <v>3.08</v>
@@ -4719,10 +4719,10 @@
         <v>1.3</v>
       </c>
       <c r="AC33" t="n">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.91</v>
+        <v>2.05</v>
       </c>
       <c r="AE33" t="inlineStr">
         <is>
@@ -4735,10 +4735,10 @@
         </is>
       </c>
       <c r="AG33" t="n">
-        <v>1.18</v>
+        <v>1.3</v>
       </c>
       <c r="AH33" t="n">
-        <v>2.13</v>
+        <v>1.57</v>
       </c>
       <c r="AI33" t="n">
         <v>0</v>
@@ -4761,7 +4761,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,61 +4797,61 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.41</v>
+        <v>1.47</v>
       </c>
       <c r="M34" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="N34" t="n">
-        <v>7.75</v>
+        <v>6.4</v>
       </c>
       <c r="O34" t="n">
-        <v>1.88</v>
+        <v>2.01</v>
       </c>
       <c r="P34" t="n">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="Q34" t="n">
-        <v>6.5</v>
+        <v>5</v>
       </c>
       <c r="R34" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="S34" t="n">
-        <v>3</v>
+        <v>3.08</v>
       </c>
       <c r="T34" t="n">
-        <v>2.64</v>
+        <v>2.51</v>
       </c>
       <c r="U34" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="V34" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="W34" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="X34" t="n">
-        <v>3.7</v>
+        <v>3.95</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="Z34" t="n">
-        <v>1.95</v>
+        <v>2.07</v>
       </c>
       <c r="AA34" t="n">
-        <v>2.97</v>
+        <v>2.78</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.32</v>
+        <v>1.44</v>
       </c>
       <c r="AC34" t="n">
-        <v>2.08</v>
+        <v>1.84</v>
       </c>
       <c r="AD34" t="n">
-        <v>1.68</v>
+        <v>1.86</v>
       </c>
       <c r="AE34" t="inlineStr">
         <is>
@@ -4864,10 +4864,10 @@
         </is>
       </c>
       <c r="AG34" t="n">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="AH34" t="n">
-        <v>2.99</v>
+        <v>2.61</v>
       </c>
       <c r="AI34" t="n">
         <v>0</v>
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,34 +4926,34 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>1.91</v>
+        <v>2.2</v>
       </c>
       <c r="M35" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="N35" t="n">
-        <v>4.06</v>
+        <v>3.3</v>
       </c>
       <c r="O35" t="n">
-        <v>2.45</v>
+        <v>2.7</v>
       </c>
       <c r="P35" t="n">
-        <v>2.22</v>
+        <v>2.08</v>
       </c>
       <c r="Q35" t="n">
-        <v>4.72</v>
+        <v>3.88</v>
       </c>
       <c r="R35" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="S35" t="n">
         <v>2.9</v>
       </c>
       <c r="T35" t="n">
-        <v>2.91</v>
+        <v>3</v>
       </c>
       <c r="U35" t="n">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="V35" t="n">
         <v>1.02</v>
@@ -4962,25 +4962,25 @@
         <v>1.28</v>
       </c>
       <c r="X35" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="Y35" t="n">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="Z35" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AC35" t="n">
         <v>1.79</v>
       </c>
-      <c r="AA35" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AB35" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AC35" t="n">
-        <v>1.85</v>
-      </c>
       <c r="AD35" t="n">
-        <v>1.86</v>
+        <v>1.94</v>
       </c>
       <c r="AE35" t="inlineStr">
         <is>
@@ -4996,7 +4996,7 @@
         <v>1.25</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.91</v>
+        <v>1.64</v>
       </c>
       <c r="AI35" t="n">
         <v>0</v>
@@ -5019,7 +5019,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,61 +5055,61 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.2</v>
+        <v>3.25</v>
       </c>
       <c r="M36" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="N36" t="n">
-        <v>3.3</v>
+        <v>2.15</v>
       </c>
       <c r="O36" t="n">
-        <v>2.7</v>
+        <v>3.95</v>
       </c>
       <c r="P36" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.88</v>
+        <v>2.75</v>
       </c>
       <c r="R36" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="S36" t="n">
-        <v>2.9</v>
+        <v>2.85</v>
       </c>
       <c r="T36" t="n">
-        <v>3</v>
+        <v>2.67</v>
       </c>
       <c r="U36" t="n">
-        <v>1.34</v>
+        <v>1.41</v>
       </c>
       <c r="V36" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W36" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="X36" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="Y36" t="n">
-        <v>2.03</v>
+        <v>1.9</v>
       </c>
       <c r="Z36" t="n">
-        <v>1.72</v>
+        <v>1.76</v>
       </c>
       <c r="AA36" t="n">
-        <v>3.48</v>
+        <v>3.2</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="AC36" t="n">
         <v>1.79</v>
       </c>
       <c r="AD36" t="n">
-        <v>1.94</v>
+        <v>1.9</v>
       </c>
       <c r="AE36" t="inlineStr">
         <is>
@@ -5122,10 +5122,10 @@
         </is>
       </c>
       <c r="AG36" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AH36" t="n">
-        <v>1.64</v>
+        <v>1.32</v>
       </c>
       <c r="AI36" t="n">
         <v>0</v>
@@ -5148,7 +5148,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,62 +5184,62 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>3.06</v>
+        <v>1.91</v>
       </c>
       <c r="M37" t="n">
-        <v>3.19</v>
+        <v>3.5</v>
       </c>
       <c r="N37" t="n">
-        <v>2.08</v>
+        <v>4.06</v>
       </c>
       <c r="O37" t="n">
-        <v>3.9</v>
+        <v>2.45</v>
       </c>
       <c r="P37" t="n">
-        <v>2.15</v>
+        <v>2.22</v>
       </c>
       <c r="Q37" t="n">
-        <v>2.75</v>
+        <v>4.72</v>
       </c>
       <c r="R37" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="S37" t="n">
-        <v>2.79</v>
+        <v>2.9</v>
       </c>
       <c r="T37" t="n">
-        <v>2.67</v>
+        <v>2.91</v>
       </c>
       <c r="U37" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="V37" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="W37" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="X37" t="n">
-        <v>3.32</v>
+        <v>3.2</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.84</v>
+        <v>2.02</v>
       </c>
       <c r="Z37" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AD37" t="n">
         <v>1.86</v>
       </c>
-      <c r="AA37" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AB37" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AC37" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AD37" t="n">
-        <v>2.13</v>
-      </c>
       <c r="AE37" t="inlineStr">
         <is>
           <t>[]</t>
@@ -5251,10 +5251,10 @@
         </is>
       </c>
       <c r="AG37" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AH37" t="n">
-        <v>1.34</v>
+        <v>1.91</v>
       </c>
       <c r="AI37" t="n">
         <v>0</v>
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,61 +5313,61 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>1.56</v>
+        <v>4.54</v>
       </c>
       <c r="M38" t="n">
+        <v>4.62</v>
+      </c>
+      <c r="N38" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="O38" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="P38" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="R38" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="S38" t="n">
         <v>4.1</v>
       </c>
-      <c r="N38" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="O38" t="n">
-        <v>0</v>
-      </c>
-      <c r="P38" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q38" t="n">
-        <v>0</v>
-      </c>
-      <c r="R38" t="n">
-        <v>0</v>
-      </c>
-      <c r="S38" t="n">
-        <v>0</v>
-      </c>
       <c r="T38" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="U38" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="V38" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W38" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X38" t="n">
-        <v>0</v>
+        <v>5.35</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.63</v>
+        <v>1.44</v>
       </c>
       <c r="Z38" t="n">
-        <v>2.25</v>
+        <v>2.67</v>
       </c>
       <c r="AA38" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AB38" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC38" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AD38" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AE38" t="inlineStr">
         <is>
@@ -5380,10 +5380,10 @@
         </is>
       </c>
       <c r="AG38" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AH38" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AI38" t="n">
         <v>0</v>
@@ -5406,7 +5406,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,61 +5442,61 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>4.54</v>
+        <v>2.63</v>
       </c>
       <c r="M39" t="n">
-        <v>4.62</v>
+        <v>3.1</v>
       </c>
       <c r="N39" t="n">
-        <v>1.66</v>
+        <v>2.88</v>
       </c>
       <c r="O39" t="n">
-        <v>4.5</v>
+        <v>3.32</v>
       </c>
       <c r="P39" t="n">
-        <v>2.6</v>
+        <v>2</v>
       </c>
       <c r="Q39" t="n">
-        <v>2.08</v>
+        <v>3.65</v>
       </c>
       <c r="R39" t="n">
-        <v>1.21</v>
+        <v>1.52</v>
       </c>
       <c r="S39" t="n">
-        <v>4.1</v>
+        <v>2.35</v>
       </c>
       <c r="T39" t="n">
-        <v>2.14</v>
+        <v>3.4</v>
       </c>
       <c r="U39" t="n">
-        <v>1.71</v>
+        <v>1.24</v>
       </c>
       <c r="V39" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="W39" t="n">
-        <v>1.1</v>
+        <v>1.48</v>
       </c>
       <c r="X39" t="n">
-        <v>5.35</v>
+        <v>2.5</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.44</v>
+        <v>2.5</v>
       </c>
       <c r="Z39" t="n">
-        <v>2.67</v>
+        <v>1.53</v>
       </c>
       <c r="AA39" t="n">
-        <v>2.13</v>
+        <v>4.7</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.78</v>
+        <v>1.14</v>
       </c>
       <c r="AC39" t="n">
-        <v>1.49</v>
+        <v>2.03</v>
       </c>
       <c r="AD39" t="n">
-        <v>2.48</v>
+        <v>1.72</v>
       </c>
       <c r="AE39" t="inlineStr">
         <is>
@@ -5509,10 +5509,10 @@
         </is>
       </c>
       <c r="AG39" t="n">
-        <v>1.23</v>
+        <v>1.34</v>
       </c>
       <c r="AH39" t="n">
-        <v>1.23</v>
+        <v>1.5</v>
       </c>
       <c r="AI39" t="n">
         <v>0</v>
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,13 +5571,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>1.35</v>
+        <v>15</v>
       </c>
       <c r="M40" t="n">
-        <v>5.3</v>
+        <v>7.6</v>
       </c>
       <c r="N40" t="n">
-        <v>7</v>
+        <v>1.15</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5610,16 +5610,16 @@
         <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.6</v>
+        <v>1.44</v>
       </c>
       <c r="Z40" t="n">
-        <v>2.35</v>
+        <v>2.75</v>
       </c>
       <c r="AA40" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB40" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -5664,7 +5664,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,77 +5700,77 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>2.63</v>
+        <v>1.6</v>
       </c>
       <c r="M41" t="n">
-        <v>3.1</v>
+        <v>4.28</v>
       </c>
       <c r="N41" t="n">
-        <v>2.88</v>
+        <v>5.29</v>
       </c>
       <c r="O41" t="n">
-        <v>3.32</v>
+        <v>2.1</v>
       </c>
       <c r="P41" t="n">
-        <v>2</v>
+        <v>2.43</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.65</v>
+        <v>4.35</v>
       </c>
       <c r="R41" t="n">
-        <v>1.52</v>
+        <v>1.28</v>
       </c>
       <c r="S41" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T41" t="n">
         <v>2.35</v>
       </c>
-      <c r="T41" t="n">
-        <v>3.4</v>
-      </c>
       <c r="U41" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="V41" t="n">
+        <v>1</v>
+      </c>
+      <c r="W41" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="X41" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AE41" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF41" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG41" t="n">
         <v>1.24</v>
       </c>
-      <c r="V41" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="W41" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="X41" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Y41" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Z41" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AA41" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AB41" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AC41" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="AD41" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AE41" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF41" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG41" t="n">
-        <v>1.34</v>
-      </c>
       <c r="AH41" t="n">
-        <v>1.5</v>
+        <v>2.41</v>
       </c>
       <c r="AI41" t="n">
         <v>0</v>
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Olympique Marseille</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,77 +5829,77 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="M42" t="n">
-        <v>4.28</v>
+        <v>4.1</v>
       </c>
       <c r="N42" t="n">
-        <v>5.29</v>
+        <v>5.4</v>
       </c>
       <c r="O42" t="n">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="P42" t="n">
-        <v>2.43</v>
+        <v>2.57</v>
       </c>
       <c r="Q42" t="n">
-        <v>4.35</v>
+        <v>4.4</v>
       </c>
       <c r="R42" t="n">
         <v>1.28</v>
       </c>
       <c r="S42" t="n">
-        <v>3.4</v>
+        <v>3.32</v>
       </c>
       <c r="T42" t="n">
-        <v>2.35</v>
+        <v>2.32</v>
       </c>
       <c r="U42" t="n">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
       <c r="V42" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="W42" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="X42" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AE42" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF42" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG42" t="n">
         <v>1.18</v>
       </c>
-      <c r="X42" t="n">
-        <v>4.45</v>
-      </c>
-      <c r="Y42" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="Z42" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AA42" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="AB42" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AC42" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AD42" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="AE42" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF42" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG42" t="n">
-        <v>1.24</v>
-      </c>
       <c r="AH42" t="n">
-        <v>2.41</v>
+        <v>2.3</v>
       </c>
       <c r="AI42" t="n">
         <v>0</v>
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Olympique Marseille</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5958,61 +5958,61 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>1.56</v>
+        <v>1.35</v>
       </c>
       <c r="M43" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="N43" t="n">
-        <v>5.1</v>
+        <v>7.8</v>
       </c>
       <c r="O43" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="P43" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q43" t="n">
-        <v>0</v>
+        <v>7.59</v>
       </c>
       <c r="R43" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S43" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="T43" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="U43" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="V43" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W43" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="X43" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.63</v>
+        <v>1.53</v>
       </c>
       <c r="Z43" t="n">
-        <v>2.25</v>
+        <v>2.51</v>
       </c>
       <c r="AA43" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AB43" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AC43" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD43" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AE43" t="inlineStr">
         <is>
@@ -6025,10 +6025,10 @@
         </is>
       </c>
       <c r="AG43" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AH43" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AI43" t="n">
         <v>0</v>
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6216,61 +6216,61 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>15</v>
+        <v>1.57</v>
       </c>
       <c r="M45" t="n">
-        <v>7.6</v>
+        <v>4</v>
       </c>
       <c r="N45" t="n">
-        <v>1.15</v>
+        <v>5.91</v>
       </c>
       <c r="O45" t="n">
-        <v>11.5</v>
+        <v>2</v>
       </c>
       <c r="P45" t="n">
-        <v>3</v>
+        <v>2.44</v>
       </c>
       <c r="Q45" t="n">
-        <v>1.46</v>
+        <v>5.25</v>
       </c>
       <c r="R45" t="n">
-        <v>1.19</v>
+        <v>1.28</v>
       </c>
       <c r="S45" t="n">
-        <v>4.25</v>
+        <v>3.45</v>
       </c>
       <c r="T45" t="n">
-        <v>2.03</v>
+        <v>2.25</v>
       </c>
       <c r="U45" t="n">
-        <v>1.79</v>
+        <v>1.59</v>
       </c>
       <c r="V45" t="n">
         <v>1.01</v>
       </c>
       <c r="W45" t="n">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="X45" t="n">
-        <v>5.85</v>
+        <v>4.33</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.38</v>
+        <v>1.64</v>
       </c>
       <c r="Z45" t="n">
-        <v>2.82</v>
+        <v>2.38</v>
       </c>
       <c r="AA45" t="n">
-        <v>2.1</v>
+        <v>2.59</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.76</v>
+        <v>1.47</v>
       </c>
       <c r="AC45" t="n">
-        <v>2.31</v>
+        <v>1.62</v>
       </c>
       <c r="AD45" t="n">
-        <v>1.6</v>
+        <v>2.18</v>
       </c>
       <c r="AE45" t="inlineStr">
         <is>
@@ -6283,10 +6283,10 @@
         </is>
       </c>
       <c r="AG45" t="n">
-        <v>1.08</v>
+        <v>1.25</v>
       </c>
       <c r="AH45" t="n">
-        <v>1.01</v>
+        <v>2.47</v>
       </c>
       <c r="AI45" t="n">
         <v>0</v>
@@ -6474,61 +6474,61 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="M47" t="n">
-        <v>4.2</v>
+        <v>4.01</v>
       </c>
       <c r="N47" t="n">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="O47" t="n">
-        <v>1.95</v>
+        <v>2.06</v>
       </c>
       <c r="P47" t="n">
-        <v>2.31</v>
+        <v>2.21</v>
       </c>
       <c r="Q47" t="n">
-        <v>6.75</v>
+        <v>6.25</v>
       </c>
       <c r="R47" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="S47" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="T47" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U47" t="n">
         <v>1.35</v>
-      </c>
-      <c r="S47" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="T47" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="U47" t="n">
-        <v>1.39</v>
       </c>
       <c r="V47" t="n">
         <v>1.01</v>
       </c>
       <c r="W47" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="X47" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="Y47" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="Z47" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AA47" t="n">
         <v>3.4</v>
       </c>
-      <c r="Y47" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="Z47" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AA47" t="n">
-        <v>3.3</v>
-      </c>
       <c r="AB47" t="n">
-        <v>1.33</v>
+        <v>1.24</v>
       </c>
       <c r="AC47" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AD47" t="n">
-        <v>1.61</v>
+        <v>1.68</v>
       </c>
       <c r="AE47" t="inlineStr">
         <is>
@@ -6541,10 +6541,10 @@
         </is>
       </c>
       <c r="AG47" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="AH47" t="n">
-        <v>2.7</v>
+        <v>2.51</v>
       </c>
       <c r="AI47" t="n">
         <v>0</v>

--- a/jogos_2025-09-30.xlsx
+++ b/jogos_2025-09-30.xlsx
@@ -1185,7 +1185,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>5.5</v>
+        <v>5.25</v>
       </c>
       <c r="M6" t="n">
         <v>3.4</v>
@@ -1206,7 +1206,7 @@
         <v>1.38</v>
       </c>
       <c r="S6" t="n">
-        <v>2.75</v>
+        <v>2.69</v>
       </c>
       <c r="T6" t="n">
         <v>2.75</v>
@@ -1227,7 +1227,7 @@
         <v>2.07</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AA6" t="n">
         <v>3.35</v>
@@ -1236,10 +1236,10 @@
         <v>1.25</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.99</v>
+        <v>1.91</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.68</v>
+        <v>1.8</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
@@ -1701,13 +1701,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="M10" t="n">
         <v>3.55</v>
       </c>
       <c r="N10" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="O10" t="n">
         <v>3.7</v>
@@ -1716,13 +1716,13 @@
         <v>2.24</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="R10" t="n">
         <v>1.3</v>
       </c>
       <c r="S10" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="T10" t="n">
         <v>2.44</v>
@@ -1734,16 +1734,16 @@
         <v>1.04</v>
       </c>
       <c r="W10" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="X10" t="n">
-        <v>4.2</v>
+        <v>4.11</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="AA10" t="n">
         <v>2.45</v>
@@ -1752,10 +1752,10 @@
         <v>1.43</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AD10" t="n">
-        <v>2.25</v>
+        <v>2.19</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -1794,22 +1794,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Wehen Wiesbaden</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,61 +1830,61 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.51</v>
+        <v>1.38</v>
       </c>
       <c r="M11" t="n">
-        <v>3.45</v>
+        <v>4.77</v>
       </c>
       <c r="N11" t="n">
-        <v>2.31</v>
+        <v>6.5</v>
       </c>
       <c r="O11" t="n">
-        <v>3</v>
+        <v>1.83</v>
       </c>
       <c r="P11" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S11" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="X11" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="Z11" t="n">
         <v>2.3</v>
       </c>
-      <c r="Q11" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S11" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="T11" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V11" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="X11" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>2.2</v>
-      </c>
       <c r="AA11" t="n">
-        <v>2.49</v>
+        <v>2.5</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.42</v>
+        <v>1.52</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.51</v>
+        <v>1.84</v>
       </c>
       <c r="AD11" t="n">
-        <v>2.3</v>
+        <v>1.86</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -1897,10 +1897,10 @@
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>1.57</v>
+        <v>1.13</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.4</v>
+        <v>2.82</v>
       </c>
       <c r="AI11" t="n">
         <v>0</v>
@@ -1923,22 +1923,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Saarbrucken</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>MSV Duisburg</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,58 +1959,58 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.87</v>
+        <v>1.5</v>
       </c>
       <c r="M12" t="n">
-        <v>3.6</v>
+        <v>4.51</v>
       </c>
       <c r="N12" t="n">
-        <v>2.95</v>
+        <v>4.75</v>
       </c>
       <c r="O12" t="n">
-        <v>2.7</v>
+        <v>1.95</v>
       </c>
       <c r="P12" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.3</v>
+        <v>5.07</v>
       </c>
       <c r="R12" t="n">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="S12" t="n">
-        <v>3.1</v>
+        <v>3.66</v>
       </c>
       <c r="T12" t="n">
-        <v>2.49</v>
+        <v>2.18</v>
       </c>
       <c r="U12" t="n">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="V12" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="W12" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="X12" t="n">
-        <v>4.1</v>
+        <v>5.6</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.67</v>
+        <v>1.42</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.09</v>
+        <v>2.47</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.59</v>
+        <v>2.05</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.48</v>
+        <v>1.62</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AD12" t="n">
         <v>2.3</v>
@@ -2026,10 +2026,10 @@
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>1.3</v>
+        <v>1.19</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.64</v>
+        <v>2.31</v>
       </c>
       <c r="AI12" t="n">
         <v>0</v>
@@ -2052,22 +2052,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Hansa Rostock</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,61 +2088,61 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.56</v>
+        <v>2.08</v>
       </c>
       <c r="M13" t="n">
-        <v>4.2</v>
+        <v>3.59</v>
       </c>
       <c r="N13" t="n">
-        <v>4.2</v>
+        <v>3.06</v>
       </c>
       <c r="O13" t="n">
-        <v>1.95</v>
+        <v>2.44</v>
       </c>
       <c r="P13" t="n">
-        <v>2.5</v>
+        <v>2.18</v>
       </c>
       <c r="Q13" t="n">
-        <v>4.95</v>
+        <v>3.78</v>
       </c>
       <c r="R13" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="S13" t="n">
-        <v>3.66</v>
+        <v>3.3</v>
       </c>
       <c r="T13" t="n">
-        <v>2.2</v>
+        <v>2.52</v>
       </c>
       <c r="U13" t="n">
-        <v>1.63</v>
+        <v>1.49</v>
       </c>
       <c r="V13" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="W13" t="n">
-        <v>1.11</v>
+        <v>1.22</v>
       </c>
       <c r="X13" t="n">
-        <v>5.6</v>
+        <v>3.9</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.42</v>
+        <v>1.7</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.7</v>
+        <v>1.97</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.92</v>
+        <v>2.71</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.78</v>
+        <v>1.37</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.55</v>
+        <v>1.59</v>
       </c>
       <c r="AD13" t="n">
-        <v>2.3</v>
+        <v>2.08</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
@@ -2155,10 +2155,10 @@
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>1.19</v>
+        <v>1.24</v>
       </c>
       <c r="AH13" t="n">
-        <v>2.4</v>
+        <v>1.67</v>
       </c>
       <c r="AI13" t="n">
         <v>0</v>
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Hansa Rostock</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>Wehen Wiesbaden</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,61 +2217,61 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.96</v>
+        <v>2.7</v>
       </c>
       <c r="M14" t="n">
-        <v>3.63</v>
+        <v>3.4</v>
       </c>
       <c r="N14" t="n">
-        <v>3.16</v>
+        <v>2.3</v>
       </c>
       <c r="O14" t="n">
-        <v>2.28</v>
+        <v>3.34</v>
       </c>
       <c r="P14" t="n">
-        <v>2.25</v>
+        <v>2.21</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.75</v>
+        <v>2.83</v>
       </c>
       <c r="R14" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="S14" t="n">
-        <v>3.14</v>
+        <v>3.2</v>
       </c>
       <c r="T14" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="U14" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="V14" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="W14" t="n">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="X14" t="n">
-        <v>3.96</v>
+        <v>4.2</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.61</v>
+        <v>1.53</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.7</v>
+        <v>2.49</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.57</v>
+        <v>1.51</v>
       </c>
       <c r="AD14" t="n">
-        <v>2.07</v>
+        <v>2.36</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
@@ -2284,10 +2284,10 @@
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.76</v>
+        <v>1.4</v>
       </c>
       <c r="AI14" t="n">
         <v>0</v>
@@ -2310,22 +2310,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Erzgebirge Aue</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,61 +2346,61 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.26</v>
+        <v>2</v>
       </c>
       <c r="M15" t="n">
-        <v>5.1</v>
+        <v>3.6</v>
       </c>
       <c r="N15" t="n">
-        <v>7.6</v>
+        <v>3.25</v>
       </c>
       <c r="O15" t="n">
-        <v>1.83</v>
+        <v>2.5</v>
       </c>
       <c r="P15" t="n">
-        <v>2.45</v>
+        <v>2.21</v>
       </c>
       <c r="Q15" t="n">
-        <v>5.7</v>
+        <v>3.89</v>
       </c>
       <c r="R15" t="n">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="S15" t="n">
-        <v>3.6</v>
+        <v>3.1</v>
       </c>
       <c r="T15" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="U15" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="X15" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AC15" t="n">
         <v>1.62</v>
       </c>
-      <c r="V15" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="X15" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>1.86</v>
-      </c>
       <c r="AD15" t="n">
-        <v>1.91</v>
+        <v>2.15</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
@@ -2413,10 +2413,10 @@
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>1.17</v>
+        <v>1.24</v>
       </c>
       <c r="AH15" t="n">
-        <v>2.78</v>
+        <v>1.71</v>
       </c>
       <c r="AI15" t="n">
         <v>0</v>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>Saarbrucken</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Erzgebirge Aue</t>
+          <t>MSV Duisburg</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,61 +2475,61 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2</v>
+        <v>1.87</v>
       </c>
       <c r="M16" t="n">
         <v>3.6</v>
       </c>
       <c r="N16" t="n">
-        <v>3.25</v>
+        <v>2.95</v>
       </c>
       <c r="O16" t="n">
-        <v>2.55</v>
+        <v>2.69</v>
       </c>
       <c r="P16" t="n">
-        <v>2.21</v>
+        <v>2.14</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.89</v>
+        <v>3.71</v>
       </c>
       <c r="R16" t="n">
         <v>1.32</v>
       </c>
       <c r="S16" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="T16" t="n">
-        <v>2.5</v>
+        <v>2.49</v>
       </c>
       <c r="U16" t="n">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="V16" t="n">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="W16" t="n">
-        <v>1.21</v>
+        <v>1.16</v>
       </c>
       <c r="X16" t="n">
-        <v>3.68</v>
+        <v>4.05</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="Z16" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.95</v>
+        <v>2.59</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.62</v>
+        <v>1.54</v>
       </c>
       <c r="AD16" t="n">
-        <v>2.15</v>
+        <v>2.29</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
@@ -2542,10 +2542,10 @@
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.71</v>
+        <v>1.61</v>
       </c>
       <c r="AI16" t="n">
         <v>0</v>
@@ -2610,16 +2610,16 @@
         <v>3.5</v>
       </c>
       <c r="N17" t="n">
-        <v>3.81</v>
+        <v>3.72</v>
       </c>
       <c r="O17" t="n">
-        <v>2.35</v>
+        <v>2.32</v>
       </c>
       <c r="P17" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="Q17" t="n">
-        <v>4</v>
+        <v>3.54</v>
       </c>
       <c r="R17" t="n">
         <v>1.3</v>
@@ -2640,10 +2640,10 @@
         <v>1.16</v>
       </c>
       <c r="X17" t="n">
-        <v>4.15</v>
+        <v>4.2</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.68</v>
+        <v>1.64</v>
       </c>
       <c r="Z17" t="n">
         <v>2.14</v>
@@ -2652,13 +2652,13 @@
         <v>2.63</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="AC17" t="n">
         <v>1.6</v>
       </c>
       <c r="AD17" t="n">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
@@ -2674,7 +2674,7 @@
         <v>1.25</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="AI17" t="n">
         <v>0</v>
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,61 +2733,61 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>3.5</v>
+        <v>1.91</v>
       </c>
       <c r="P18" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>5.34</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S18" t="n">
+        <v>3.66</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X18" t="n">
+        <v>4.98</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="Z18" t="n">
         <v>2.47</v>
       </c>
-      <c r="Q18" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="R18" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="S18" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="T18" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="U18" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="V18" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="X18" t="n">
-        <v>4.45</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>2.35</v>
-      </c>
       <c r="AA18" t="n">
-        <v>2.36</v>
+        <v>2.27</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.52</v>
+        <v>1.64</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.5</v>
+        <v>1.66</v>
       </c>
       <c r="AD18" t="n">
-        <v>2.45</v>
+        <v>2.24</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
@@ -2800,10 +2800,10 @@
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>1.67</v>
+        <v>1.12</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.37</v>
+        <v>2.61</v>
       </c>
       <c r="AI18" t="n">
         <v>0</v>
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,61 +2862,61 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>3.1</v>
+        <v>2.1</v>
       </c>
       <c r="M19" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="N19" t="n">
-        <v>1.98</v>
+        <v>2.87</v>
       </c>
       <c r="O19" t="n">
-        <v>3.7</v>
+        <v>2.65</v>
       </c>
       <c r="P19" t="n">
-        <v>2.38</v>
+        <v>2.51</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.61</v>
+        <v>3.25</v>
       </c>
       <c r="R19" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="S19" t="n">
-        <v>3.7</v>
+        <v>3.45</v>
       </c>
       <c r="T19" t="n">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="U19" t="n">
         <v>1.62</v>
       </c>
       <c r="V19" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="W19" t="n">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="X19" t="n">
-        <v>4.95</v>
+        <v>4.75</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.46</v>
+        <v>1.53</v>
       </c>
       <c r="Z19" t="n">
-        <v>2.55</v>
+        <v>2.39</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.61</v>
+        <v>1.54</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="AD19" t="n">
-        <v>2.5</v>
+        <v>2.59</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
@@ -2929,10 +2929,10 @@
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>1.75</v>
+        <v>1.25</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.28</v>
+        <v>1.68</v>
       </c>
       <c r="AI19" t="n">
         <v>0</v>
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,61 +2991,61 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O20" t="n">
-        <v>1.85</v>
+        <v>3.7</v>
       </c>
       <c r="P20" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="Q20" t="n">
         <v>2.61</v>
       </c>
-      <c r="Q20" t="n">
-        <v>5.93</v>
-      </c>
       <c r="R20" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="S20" t="n">
-        <v>3.9</v>
+        <v>3.58</v>
       </c>
       <c r="T20" t="n">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="U20" t="n">
-        <v>1.7</v>
+        <v>1.61</v>
       </c>
       <c r="V20" t="n">
         <v>1.01</v>
       </c>
       <c r="W20" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="X20" t="n">
-        <v>5.75</v>
+        <v>4.9</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="Z20" t="n">
-        <v>2.57</v>
+        <v>2.39</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.15</v>
+        <v>2.28</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.68</v>
+        <v>1.6</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.62</v>
+        <v>1.46</v>
       </c>
       <c r="AD20" t="n">
-        <v>2.16</v>
+        <v>2.5</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
@@ -3058,10 +3058,10 @@
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>1.1</v>
+        <v>1.79</v>
       </c>
       <c r="AH20" t="n">
-        <v>2.5</v>
+        <v>1.27</v>
       </c>
       <c r="AI20" t="n">
         <v>0</v>
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,61 +3120,61 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.1</v>
+        <v>2.73</v>
       </c>
       <c r="M21" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="N21" t="n">
-        <v>2.87</v>
+        <v>2.18</v>
       </c>
       <c r="O21" t="n">
-        <v>2.65</v>
+        <v>3.5</v>
       </c>
       <c r="P21" t="n">
-        <v>2.51</v>
+        <v>2.47</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.4</v>
+        <v>2.55</v>
       </c>
       <c r="R21" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="S21" t="n">
-        <v>3.45</v>
+        <v>3.34</v>
       </c>
       <c r="T21" t="n">
-        <v>2.21</v>
+        <v>2.32</v>
       </c>
       <c r="U21" t="n">
-        <v>1.62</v>
+        <v>1.54</v>
       </c>
       <c r="V21" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="W21" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="X21" t="n">
-        <v>5.32</v>
+        <v>4.5</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="Z21" t="n">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.28</v>
+        <v>2.36</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.45</v>
+        <v>1.52</v>
       </c>
       <c r="AD21" t="n">
-        <v>2.59</v>
+        <v>2.45</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
@@ -3187,10 +3187,10 @@
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>1.25</v>
+        <v>1.67</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.68</v>
+        <v>1.37</v>
       </c>
       <c r="AI21" t="n">
         <v>0</v>
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,77 +3249,77 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>3.41</v>
+        <v>2.5</v>
       </c>
       <c r="M22" t="n">
-        <v>3.26</v>
+        <v>3.24</v>
       </c>
       <c r="N22" t="n">
-        <v>2.13</v>
+        <v>2.7</v>
       </c>
       <c r="O22" t="n">
-        <v>4</v>
+        <v>3.39</v>
       </c>
       <c r="P22" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.86</v>
+        <v>3.4</v>
       </c>
       <c r="R22" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="S22" t="n">
-        <v>2.42</v>
+        <v>2.62</v>
       </c>
       <c r="T22" t="n">
         <v>3.2</v>
       </c>
       <c r="U22" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="V22" t="n">
         <v>1.03</v>
       </c>
       <c r="W22" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="X22" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AE22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG22" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AH22" t="n">
         <v>1.44</v>
-      </c>
-      <c r="X22" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>4.41</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AE22" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF22" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG22" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>1.3</v>
       </c>
       <c r="AI22" t="n">
         <v>0</v>
@@ -3378,13 +3378,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="M23" t="n">
-        <v>3.2</v>
+        <v>3.28</v>
       </c>
       <c r="N23" t="n">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="O23" t="n">
         <v>2.75</v>
@@ -3393,46 +3393,46 @@
         <v>2</v>
       </c>
       <c r="Q23" t="n">
-        <v>4.38</v>
+        <v>4.25</v>
       </c>
       <c r="R23" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="S23" t="n">
-        <v>2.51</v>
+        <v>2.48</v>
       </c>
       <c r="T23" t="n">
-        <v>3.14</v>
+        <v>3.2</v>
       </c>
       <c r="U23" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="V23" t="n">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="W23" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="X23" t="n">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="Y23" t="n">
         <v>2.14</v>
       </c>
       <c r="Z23" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="AA23" t="n">
-        <v>3.95</v>
+        <v>4.05</v>
       </c>
       <c r="AB23" t="n">
         <v>1.23</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.85</v>
+        <v>1.94</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.81</v>
+        <v>1.77</v>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
@@ -3445,10 +3445,10 @@
         </is>
       </c>
       <c r="AG23" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="AI23" t="n">
         <v>0</v>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Calcio Padova</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,22 +3507,22 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.31</v>
+        <v>3.41</v>
       </c>
       <c r="M24" t="n">
-        <v>3.1</v>
+        <v>3.26</v>
       </c>
       <c r="N24" t="n">
-        <v>3.1</v>
+        <v>2.13</v>
       </c>
       <c r="O24" t="n">
-        <v>3.16</v>
+        <v>4</v>
       </c>
       <c r="P24" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="Q24" t="n">
-        <v>4.11</v>
+        <v>2.88</v>
       </c>
       <c r="R24" t="n">
         <v>1.5</v>
@@ -3531,34 +3531,34 @@
         <v>2.42</v>
       </c>
       <c r="T24" t="n">
-        <v>3.2</v>
+        <v>3.28</v>
       </c>
       <c r="U24" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="V24" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="W24" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="X24" t="n">
-        <v>2.65</v>
+        <v>2.7</v>
       </c>
       <c r="Y24" t="n">
-        <v>2.35</v>
+        <v>2.33</v>
       </c>
       <c r="Z24" t="n">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="AA24" t="n">
-        <v>4.75</v>
+        <v>4.43</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="AD24" t="n">
         <v>1.75</v>
@@ -3574,10 +3574,10 @@
         </is>
       </c>
       <c r="AG24" t="n">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.58</v>
+        <v>1.31</v>
       </c>
       <c r="AI24" t="n">
         <v>0</v>
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mantova</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,61 +3636,61 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.86</v>
+        <v>2.03</v>
       </c>
       <c r="M25" t="n">
         <v>3.4</v>
       </c>
       <c r="N25" t="n">
-        <v>4.18</v>
+        <v>3.4</v>
       </c>
       <c r="O25" t="n">
-        <v>2.5</v>
+        <v>2.51</v>
       </c>
       <c r="P25" t="n">
-        <v>2.18</v>
+        <v>2.1</v>
       </c>
       <c r="Q25" t="n">
-        <v>4.8</v>
+        <v>4.04</v>
       </c>
       <c r="R25" t="n">
-        <v>1.39</v>
+        <v>1.35</v>
       </c>
       <c r="S25" t="n">
-        <v>2.67</v>
+        <v>2.84</v>
       </c>
       <c r="T25" t="n">
-        <v>2.85</v>
+        <v>2.71</v>
       </c>
       <c r="U25" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="V25" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="W25" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="X25" t="n">
-        <v>3.08</v>
+        <v>3.48</v>
       </c>
       <c r="Y25" t="n">
-        <v>2.03</v>
+        <v>1.9</v>
       </c>
       <c r="Z25" t="n">
-        <v>1.75</v>
+        <v>1.9</v>
       </c>
       <c r="AA25" t="n">
-        <v>3.55</v>
+        <v>2.9</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.91</v>
+        <v>1.7</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
@@ -3703,10 +3703,10 @@
         </is>
       </c>
       <c r="AG25" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.91</v>
+        <v>1.7</v>
       </c>
       <c r="AI25" t="n">
         <v>0</v>
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>Mantova</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,77 +3765,77 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.55</v>
+        <v>1.83</v>
       </c>
       <c r="M26" t="n">
-        <v>3.24</v>
+        <v>3.58</v>
       </c>
       <c r="N26" t="n">
-        <v>2.7</v>
+        <v>4</v>
       </c>
       <c r="O26" t="n">
-        <v>3.2</v>
+        <v>2.31</v>
       </c>
       <c r="P26" t="n">
-        <v>2</v>
+        <v>2.13</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.4</v>
+        <v>4.33</v>
       </c>
       <c r="R26" t="n">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="S26" t="n">
-        <v>2.6</v>
+        <v>2.67</v>
       </c>
       <c r="T26" t="n">
-        <v>3.2</v>
+        <v>2.8</v>
       </c>
       <c r="U26" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="V26" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W26" t="n">
         <v>1.3</v>
       </c>
-      <c r="V26" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W26" t="n">
-        <v>1.35</v>
-      </c>
       <c r="X26" t="n">
-        <v>2.92</v>
+        <v>3.08</v>
       </c>
       <c r="Y26" t="n">
-        <v>2.18</v>
+        <v>2.03</v>
       </c>
       <c r="Z26" t="n">
-        <v>1.62</v>
+        <v>1.78</v>
       </c>
       <c r="AA26" t="n">
-        <v>4.29</v>
+        <v>3.55</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.18</v>
+        <v>1.28</v>
       </c>
       <c r="AC26" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AE26" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF26" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG26" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AH26" t="n">
         <v>1.93</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AE26" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF26" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG26" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AH26" t="n">
-        <v>1.48</v>
       </c>
       <c r="AI26" t="n">
         <v>0</v>
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Calcio Padova</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,61 +3894,61 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.12</v>
+        <v>2.37</v>
       </c>
       <c r="M27" t="n">
-        <v>3.37</v>
+        <v>2.91</v>
       </c>
       <c r="N27" t="n">
-        <v>3.38</v>
+        <v>3.26</v>
       </c>
       <c r="O27" t="n">
-        <v>2.73</v>
+        <v>3.01</v>
       </c>
       <c r="P27" t="n">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="Q27" t="n">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="R27" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="S27" t="n">
-        <v>2.91</v>
+        <v>2.4</v>
       </c>
       <c r="T27" t="n">
-        <v>2.67</v>
+        <v>3.28</v>
       </c>
       <c r="U27" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="V27" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="W27" t="n">
-        <v>1.22</v>
+        <v>1.48</v>
       </c>
       <c r="X27" t="n">
-        <v>3.75</v>
+        <v>2.56</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.9</v>
+        <v>2.4</v>
       </c>
       <c r="Z27" t="n">
-        <v>1.95</v>
+        <v>1.55</v>
       </c>
       <c r="AA27" t="n">
-        <v>3.02</v>
+        <v>4.75</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.31</v>
+        <v>1.16</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.67</v>
+        <v>1.99</v>
       </c>
       <c r="AD27" t="n">
-        <v>2.04</v>
+        <v>1.74</v>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
@@ -3961,10 +3961,10 @@
         </is>
       </c>
       <c r="AG27" t="n">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.7</v>
+        <v>1.61</v>
       </c>
       <c r="AI27" t="n">
         <v>0</v>
@@ -4029,13 +4029,13 @@
         <v>3.4</v>
       </c>
       <c r="N28" t="n">
-        <v>1.91</v>
+        <v>1.8</v>
       </c>
       <c r="O28" t="n">
         <v>3.9</v>
       </c>
       <c r="P28" t="n">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="Q28" t="n">
         <v>2.44</v>
@@ -4044,13 +4044,13 @@
         <v>1.34</v>
       </c>
       <c r="S28" t="n">
-        <v>3.11</v>
+        <v>2.9</v>
       </c>
       <c r="T28" t="n">
         <v>2.43</v>
       </c>
       <c r="U28" t="n">
-        <v>1.42</v>
+        <v>1.48</v>
       </c>
       <c r="V28" t="n">
         <v>1.01</v>
@@ -4059,10 +4059,10 @@
         <v>1.22</v>
       </c>
       <c r="X28" t="n">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="Z28" t="n">
         <v>1.95</v>
@@ -4071,7 +4071,7 @@
         <v>2.92</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="AC28" t="n">
         <v>1.67</v>
@@ -4093,7 +4093,7 @@
         <v>1.22</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AI28" t="n">
         <v>0</v>
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,61 +4152,61 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.67</v>
+        <v>2.5</v>
       </c>
       <c r="M29" t="n">
-        <v>3.8</v>
+        <v>3.25</v>
       </c>
       <c r="N29" t="n">
-        <v>4.8</v>
+        <v>2.8</v>
       </c>
       <c r="O29" t="n">
-        <v>2.2</v>
+        <v>3.15</v>
       </c>
       <c r="P29" t="n">
-        <v>2.34</v>
+        <v>2.05</v>
       </c>
       <c r="Q29" t="n">
-        <v>4.7</v>
+        <v>3.4</v>
       </c>
       <c r="R29" t="n">
-        <v>1.35</v>
+        <v>1.43</v>
       </c>
       <c r="S29" t="n">
-        <v>3.05</v>
+        <v>2.54</v>
       </c>
       <c r="T29" t="n">
-        <v>2.6</v>
+        <v>3.08</v>
       </c>
       <c r="U29" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="V29" t="n">
         <v>1.02</v>
       </c>
       <c r="W29" t="n">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="X29" t="n">
-        <v>3.4</v>
+        <v>2.83</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.89</v>
+        <v>2.2</v>
       </c>
       <c r="Z29" t="n">
-        <v>1.94</v>
+        <v>1.65</v>
       </c>
       <c r="AA29" t="n">
-        <v>3.08</v>
+        <v>3.9</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.3</v>
+        <v>1.19</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.88</v>
+        <v>1.92</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.91</v>
+        <v>1.86</v>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
@@ -4219,10 +4219,10 @@
         </is>
       </c>
       <c r="AG29" t="n">
-        <v>1.18</v>
+        <v>1.43</v>
       </c>
       <c r="AH29" t="n">
-        <v>2.13</v>
+        <v>1.52</v>
       </c>
       <c r="AI29" t="n">
         <v>0</v>
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,61 +4281,61 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.41</v>
+        <v>1.67</v>
       </c>
       <c r="M30" t="n">
-        <v>4.6</v>
+        <v>3.8</v>
       </c>
       <c r="N30" t="n">
-        <v>7.75</v>
+        <v>5</v>
       </c>
       <c r="O30" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="P30" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>5.35</v>
+      </c>
+      <c r="R30" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S30" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="V30" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W30" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X30" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="Y30" t="n">
         <v>1.88</v>
       </c>
-      <c r="P30" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="R30" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S30" t="n">
-        <v>3</v>
-      </c>
-      <c r="T30" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="U30" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V30" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W30" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="X30" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>1.85</v>
-      </c>
       <c r="Z30" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="AA30" t="n">
-        <v>2.97</v>
+        <v>3.25</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="AC30" t="n">
-        <v>2.08</v>
+        <v>1.81</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.68</v>
+        <v>1.91</v>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
@@ -4348,10 +4348,10 @@
         </is>
       </c>
       <c r="AG30" t="n">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="AH30" t="n">
-        <v>2.99</v>
+        <v>2.17</v>
       </c>
       <c r="AI30" t="n">
         <v>0</v>
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,61 +4410,61 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.92</v>
+        <v>2.19</v>
       </c>
       <c r="M31" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="N31" t="n">
-        <v>2.4</v>
+        <v>3.3</v>
       </c>
       <c r="O31" t="n">
-        <v>3.54</v>
+        <v>2.75</v>
       </c>
       <c r="P31" t="n">
-        <v>2.11</v>
+        <v>2.07</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.99</v>
+        <v>3.86</v>
       </c>
       <c r="R31" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="S31" t="n">
-        <v>2.8</v>
+        <v>2.77</v>
       </c>
       <c r="T31" t="n">
-        <v>2.71</v>
+        <v>3.08</v>
       </c>
       <c r="U31" t="n">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="V31" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="W31" t="n">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="X31" t="n">
-        <v>3.75</v>
+        <v>3.15</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.88</v>
+        <v>2.07</v>
       </c>
       <c r="Z31" t="n">
-        <v>1.95</v>
+        <v>1.72</v>
       </c>
       <c r="AA31" t="n">
-        <v>3.2</v>
+        <v>3.64</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.67</v>
+        <v>1.81</v>
       </c>
       <c r="AD31" t="n">
-        <v>2.11</v>
+        <v>1.91</v>
       </c>
       <c r="AE31" t="inlineStr">
         <is>
@@ -4477,10 +4477,10 @@
         </is>
       </c>
       <c r="AG31" t="n">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.41</v>
+        <v>1.66</v>
       </c>
       <c r="AI31" t="n">
         <v>0</v>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,61 +4539,61 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.52</v>
+        <v>1.47</v>
       </c>
       <c r="M32" t="n">
-        <v>3.25</v>
+        <v>4.3</v>
       </c>
       <c r="N32" t="n">
-        <v>2.8</v>
+        <v>6.4</v>
       </c>
       <c r="O32" t="n">
-        <v>3.15</v>
+        <v>2.01</v>
       </c>
       <c r="P32" t="n">
-        <v>2.05</v>
+        <v>2.35</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.4</v>
+        <v>5</v>
       </c>
       <c r="R32" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S32" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="T32" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="U32" t="n">
         <v>1.44</v>
       </c>
-      <c r="S32" t="n">
-        <v>2.51</v>
-      </c>
-      <c r="T32" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="U32" t="n">
-        <v>1.29</v>
-      </c>
       <c r="V32" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="W32" t="n">
-        <v>1.38</v>
+        <v>1.19</v>
       </c>
       <c r="X32" t="n">
-        <v>2.78</v>
+        <v>3.95</v>
       </c>
       <c r="Y32" t="n">
-        <v>2.22</v>
+        <v>1.75</v>
       </c>
       <c r="Z32" t="n">
-        <v>1.66</v>
+        <v>2.07</v>
       </c>
       <c r="AA32" t="n">
-        <v>3.95</v>
+        <v>2.77</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.19</v>
+        <v>1.36</v>
       </c>
       <c r="AC32" t="n">
-        <v>1.92</v>
+        <v>1.84</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="AE32" t="inlineStr">
         <is>
@@ -4606,10 +4606,10 @@
         </is>
       </c>
       <c r="AG32" t="n">
-        <v>1.42</v>
+        <v>1.12</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.53</v>
+        <v>2.61</v>
       </c>
       <c r="AI32" t="n">
         <v>0</v>
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,61 +4668,61 @@
         </is>
       </c>
       <c r="L33" t="n">
+        <v>2</v>
+      </c>
+      <c r="M33" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N33" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="O33" t="n">
         <v>2.5</v>
       </c>
-      <c r="M33" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="N33" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="O33" t="n">
-        <v>3.12</v>
-      </c>
       <c r="P33" t="n">
-        <v>2.23</v>
+        <v>2.2</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.33</v>
+        <v>4.55</v>
       </c>
       <c r="R33" t="n">
-        <v>1.32</v>
+        <v>1.39</v>
       </c>
       <c r="S33" t="n">
-        <v>2.9</v>
+        <v>2.86</v>
       </c>
       <c r="T33" t="n">
-        <v>2.71</v>
+        <v>3.04</v>
       </c>
       <c r="U33" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="V33" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="W33" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="X33" t="n">
-        <v>3.45</v>
+        <v>3.16</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.93</v>
+        <v>2.02</v>
       </c>
       <c r="Z33" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="AA33" t="n">
-        <v>3.08</v>
+        <v>3.55</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AC33" t="n">
-        <v>1.78</v>
+        <v>1.83</v>
       </c>
       <c r="AD33" t="n">
-        <v>2.05</v>
+        <v>1.89</v>
       </c>
       <c r="AE33" t="inlineStr">
         <is>
@@ -4735,10 +4735,10 @@
         </is>
       </c>
       <c r="AG33" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.57</v>
+        <v>1.81</v>
       </c>
       <c r="AI33" t="n">
         <v>0</v>
@@ -4761,7 +4761,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,61 +4797,61 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.47</v>
+        <v>2.92</v>
       </c>
       <c r="M34" t="n">
-        <v>4.3</v>
+        <v>3.4</v>
       </c>
       <c r="N34" t="n">
-        <v>6.4</v>
+        <v>2.4</v>
       </c>
       <c r="O34" t="n">
-        <v>2.01</v>
+        <v>3.55</v>
       </c>
       <c r="P34" t="n">
-        <v>2.4</v>
+        <v>2.11</v>
       </c>
       <c r="Q34" t="n">
-        <v>5</v>
+        <v>2.98</v>
       </c>
       <c r="R34" t="n">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="S34" t="n">
-        <v>3.08</v>
+        <v>2.8</v>
       </c>
       <c r="T34" t="n">
-        <v>2.51</v>
+        <v>2.65</v>
       </c>
       <c r="U34" t="n">
         <v>1.44</v>
       </c>
       <c r="V34" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="W34" t="n">
-        <v>1.19</v>
+        <v>1.24</v>
       </c>
       <c r="X34" t="n">
-        <v>3.95</v>
+        <v>3.75</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.75</v>
+        <v>1.88</v>
       </c>
       <c r="Z34" t="n">
-        <v>2.07</v>
+        <v>1.95</v>
       </c>
       <c r="AA34" t="n">
-        <v>2.78</v>
+        <v>3.2</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="AC34" t="n">
-        <v>1.84</v>
+        <v>1.67</v>
       </c>
       <c r="AD34" t="n">
-        <v>1.86</v>
+        <v>2.11</v>
       </c>
       <c r="AE34" t="inlineStr">
         <is>
@@ -4864,10 +4864,10 @@
         </is>
       </c>
       <c r="AG34" t="n">
-        <v>1.21</v>
+        <v>1.58</v>
       </c>
       <c r="AH34" t="n">
-        <v>2.61</v>
+        <v>1.36</v>
       </c>
       <c r="AI34" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,77 +4926,77 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.2</v>
+        <v>3</v>
       </c>
       <c r="M35" t="n">
         <v>3.4</v>
       </c>
       <c r="N35" t="n">
-        <v>3.3</v>
+        <v>2.15</v>
       </c>
       <c r="O35" t="n">
-        <v>2.7</v>
+        <v>3.6</v>
       </c>
       <c r="P35" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.88</v>
+        <v>2.74</v>
       </c>
       <c r="R35" t="n">
         <v>1.35</v>
       </c>
       <c r="S35" t="n">
-        <v>2.9</v>
+        <v>2.85</v>
       </c>
       <c r="T35" t="n">
-        <v>3</v>
+        <v>2.67</v>
       </c>
       <c r="U35" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="V35" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W35" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X35" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AE35" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF35" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG35" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AH35" t="n">
         <v>1.34</v>
-      </c>
-      <c r="V35" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W35" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="X35" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="Y35" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="Z35" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AA35" t="n">
-        <v>3.48</v>
-      </c>
-      <c r="AB35" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AC35" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AD35" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AE35" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF35" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG35" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AH35" t="n">
-        <v>1.64</v>
       </c>
       <c r="AI35" t="n">
         <v>0</v>
@@ -5019,7 +5019,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,61 +5055,61 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>3.25</v>
+        <v>2.2</v>
       </c>
       <c r="M36" t="n">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="N36" t="n">
-        <v>2.15</v>
+        <v>2.62</v>
       </c>
       <c r="O36" t="n">
-        <v>3.95</v>
+        <v>3.12</v>
       </c>
       <c r="P36" t="n">
-        <v>2.1</v>
+        <v>2.23</v>
       </c>
       <c r="Q36" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="R36" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S36" t="n">
         <v>2.75</v>
       </c>
-      <c r="R36" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S36" t="n">
-        <v>2.85</v>
-      </c>
       <c r="T36" t="n">
-        <v>2.67</v>
+        <v>2.75</v>
       </c>
       <c r="U36" t="n">
-        <v>1.41</v>
+        <v>1.37</v>
       </c>
       <c r="V36" t="n">
         <v>1.01</v>
       </c>
       <c r="W36" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="X36" t="n">
-        <v>3.25</v>
+        <v>3.85</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="Z36" t="n">
-        <v>1.76</v>
+        <v>1.86</v>
       </c>
       <c r="AA36" t="n">
         <v>3.2</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AC36" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="AD36" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AE36" t="inlineStr">
         <is>
@@ -5122,10 +5122,10 @@
         </is>
       </c>
       <c r="AG36" t="n">
-        <v>1.27</v>
+        <v>1.32</v>
       </c>
       <c r="AH36" t="n">
-        <v>1.32</v>
+        <v>1.5</v>
       </c>
       <c r="AI36" t="n">
         <v>0</v>
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,61 +5184,61 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>1.91</v>
+        <v>1.41</v>
       </c>
       <c r="M37" t="n">
-        <v>3.5</v>
+        <v>4.51</v>
       </c>
       <c r="N37" t="n">
-        <v>4.06</v>
+        <v>7.9</v>
       </c>
       <c r="O37" t="n">
-        <v>2.45</v>
+        <v>1.89</v>
       </c>
       <c r="P37" t="n">
-        <v>2.22</v>
+        <v>2.35</v>
       </c>
       <c r="Q37" t="n">
-        <v>4.72</v>
+        <v>6.5</v>
       </c>
       <c r="R37" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="S37" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="T37" t="n">
-        <v>2.91</v>
+        <v>2.64</v>
       </c>
       <c r="U37" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="V37" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W37" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="X37" t="n">
-        <v>3.2</v>
+        <v>3.48</v>
       </c>
       <c r="Y37" t="n">
-        <v>2.02</v>
+        <v>1.85</v>
       </c>
       <c r="Z37" t="n">
-        <v>1.79</v>
+        <v>1.94</v>
       </c>
       <c r="AA37" t="n">
-        <v>3.55</v>
+        <v>3.02</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="AC37" t="n">
-        <v>1.85</v>
+        <v>2.16</v>
       </c>
       <c r="AD37" t="n">
-        <v>1.86</v>
+        <v>1.69</v>
       </c>
       <c r="AE37" t="inlineStr">
         <is>
@@ -5251,10 +5251,10 @@
         </is>
       </c>
       <c r="AG37" t="n">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="AH37" t="n">
-        <v>1.91</v>
+        <v>2.99</v>
       </c>
       <c r="AI37" t="n">
         <v>0</v>
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,61 +5313,61 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>4.54</v>
+        <v>3</v>
       </c>
       <c r="M38" t="n">
-        <v>4.62</v>
+        <v>3.83</v>
       </c>
       <c r="N38" t="n">
-        <v>1.66</v>
+        <v>2.1</v>
       </c>
       <c r="O38" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="P38" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="T38" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="U38" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="V38" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W38" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X38" t="n">
-        <v>5.35</v>
+        <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="Z38" t="n">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>2.13</v>
+        <v>2.25</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.78</v>
+        <v>1.65</v>
       </c>
       <c r="AC38" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AD38" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="AE38" t="inlineStr">
         <is>
@@ -5380,10 +5380,10 @@
         </is>
       </c>
       <c r="AG38" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AH38" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AI38" t="n">
         <v>0</v>
@@ -5406,7 +5406,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,62 +5442,62 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.63</v>
+        <v>4.7</v>
       </c>
       <c r="M39" t="n">
-        <v>3.1</v>
+        <v>4.6</v>
       </c>
       <c r="N39" t="n">
-        <v>2.88</v>
+        <v>1.63</v>
       </c>
       <c r="O39" t="n">
-        <v>3.32</v>
+        <v>4.45</v>
       </c>
       <c r="P39" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="Q39" t="n">
-        <v>3.65</v>
+        <v>2.05</v>
       </c>
       <c r="R39" t="n">
-        <v>1.52</v>
+        <v>1.2</v>
       </c>
       <c r="S39" t="n">
-        <v>2.35</v>
+        <v>4</v>
       </c>
       <c r="T39" t="n">
-        <v>3.4</v>
+        <v>2.15</v>
       </c>
       <c r="U39" t="n">
-        <v>1.24</v>
+        <v>1.72</v>
       </c>
       <c r="V39" t="n">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="W39" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X39" t="n">
+        <v>5.35</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AC39" t="n">
         <v>1.48</v>
       </c>
-      <c r="X39" t="n">
+      <c r="AD39" t="n">
         <v>2.5</v>
       </c>
-      <c r="Y39" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Z39" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AA39" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AB39" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AC39" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="AD39" t="n">
-        <v>1.72</v>
-      </c>
       <c r="AE39" t="inlineStr">
         <is>
           <t>[]</t>
@@ -5509,10 +5509,10 @@
         </is>
       </c>
       <c r="AG39" t="n">
-        <v>1.34</v>
+        <v>1.23</v>
       </c>
       <c r="AH39" t="n">
-        <v>1.5</v>
+        <v>1.23</v>
       </c>
       <c r="AI39" t="n">
         <v>0</v>
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Olympique Marseille</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,61 +5571,61 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>15</v>
+        <v>1.53</v>
       </c>
       <c r="M40" t="n">
-        <v>7.6</v>
+        <v>4.5</v>
       </c>
       <c r="N40" t="n">
-        <v>1.15</v>
+        <v>5.5</v>
       </c>
       <c r="O40" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="R40" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S40" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="T40" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="U40" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="V40" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W40" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X40" t="n">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.44</v>
+        <v>1.57</v>
       </c>
       <c r="Z40" t="n">
-        <v>2.75</v>
+        <v>2.46</v>
       </c>
       <c r="AA40" t="n">
-        <v>1.95</v>
+        <v>2.38</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.79</v>
+        <v>1.53</v>
       </c>
       <c r="AC40" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AD40" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AE40" t="inlineStr">
         <is>
@@ -5638,10 +5638,10 @@
         </is>
       </c>
       <c r="AG40" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AH40" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AI40" t="n">
         <v>0</v>
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,61 +5700,61 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1.6</v>
+        <v>15</v>
       </c>
       <c r="M41" t="n">
-        <v>4.28</v>
+        <v>7.6</v>
       </c>
       <c r="N41" t="n">
-        <v>5.29</v>
+        <v>1.15</v>
       </c>
       <c r="O41" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="P41" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>4.35</v>
+        <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="S41" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="T41" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="U41" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="V41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W41" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="X41" t="n">
-        <v>4.45</v>
+        <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.62</v>
+        <v>1.44</v>
       </c>
       <c r="Z41" t="n">
-        <v>2.38</v>
+        <v>2.75</v>
       </c>
       <c r="AA41" t="n">
-        <v>2.54</v>
+        <v>1.95</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.55</v>
+        <v>1.79</v>
       </c>
       <c r="AC41" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AD41" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="AE41" t="inlineStr">
         <is>
@@ -5767,10 +5767,10 @@
         </is>
       </c>
       <c r="AG41" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AH41" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="AI41" t="n">
         <v>0</v>
@@ -5793,7 +5793,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Olympique Marseille</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,61 +5829,61 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>1.57</v>
+        <v>2.56</v>
       </c>
       <c r="M42" t="n">
-        <v>4.1</v>
+        <v>3.1</v>
       </c>
       <c r="N42" t="n">
-        <v>5.4</v>
+        <v>2.7</v>
       </c>
       <c r="O42" t="n">
-        <v>2.14</v>
+        <v>3.32</v>
       </c>
       <c r="P42" t="n">
-        <v>2.57</v>
+        <v>1.93</v>
       </c>
       <c r="Q42" t="n">
-        <v>4.4</v>
+        <v>3.65</v>
       </c>
       <c r="R42" t="n">
-        <v>1.28</v>
+        <v>1.52</v>
       </c>
       <c r="S42" t="n">
-        <v>3.32</v>
+        <v>2.35</v>
       </c>
       <c r="T42" t="n">
-        <v>2.32</v>
+        <v>3.4</v>
       </c>
       <c r="U42" t="n">
-        <v>1.59</v>
+        <v>1.24</v>
       </c>
       <c r="V42" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="W42" t="n">
-        <v>1.17</v>
+        <v>1.48</v>
       </c>
       <c r="X42" t="n">
-        <v>4.55</v>
+        <v>2.5</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.61</v>
+        <v>2.5</v>
       </c>
       <c r="Z42" t="n">
-        <v>2.33</v>
+        <v>1.53</v>
       </c>
       <c r="AA42" t="n">
-        <v>2.5</v>
+        <v>4.7</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.52</v>
+        <v>1.14</v>
       </c>
       <c r="AC42" t="n">
-        <v>1.68</v>
+        <v>2.03</v>
       </c>
       <c r="AD42" t="n">
-        <v>2.11</v>
+        <v>1.72</v>
       </c>
       <c r="AE42" t="inlineStr">
         <is>
@@ -5896,10 +5896,10 @@
         </is>
       </c>
       <c r="AG42" t="n">
-        <v>1.18</v>
+        <v>1.38</v>
       </c>
       <c r="AH42" t="n">
-        <v>2.3</v>
+        <v>1.5</v>
       </c>
       <c r="AI42" t="n">
         <v>0</v>
@@ -5961,58 +5961,58 @@
         <v>1.35</v>
       </c>
       <c r="M43" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="N43" t="n">
-        <v>7.8</v>
+        <v>8.25</v>
       </c>
       <c r="O43" t="n">
-        <v>1.76</v>
+        <v>1.81</v>
       </c>
       <c r="P43" t="n">
         <v>2.6</v>
       </c>
       <c r="Q43" t="n">
-        <v>7.59</v>
+        <v>6.5</v>
       </c>
       <c r="R43" t="n">
         <v>1.25</v>
       </c>
       <c r="S43" t="n">
-        <v>3.54</v>
+        <v>3.75</v>
       </c>
       <c r="T43" t="n">
-        <v>2.29</v>
+        <v>2.24</v>
       </c>
       <c r="U43" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="V43" t="n">
         <v>1.01</v>
       </c>
       <c r="W43" t="n">
-        <v>1.16</v>
+        <v>1.11</v>
       </c>
       <c r="X43" t="n">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="Z43" t="n">
-        <v>2.51</v>
+        <v>2.43</v>
       </c>
       <c r="AA43" t="n">
         <v>2.42</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="AC43" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="AD43" t="n">
-        <v>1.89</v>
+        <v>1.93</v>
       </c>
       <c r="AE43" t="inlineStr">
         <is>
@@ -6025,10 +6025,10 @@
         </is>
       </c>
       <c r="AG43" t="n">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="AH43" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="AI43" t="n">
         <v>0</v>
@@ -6061,12 +6061,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6087,61 +6087,61 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>2.71</v>
+        <v>1.6</v>
       </c>
       <c r="M44" t="n">
-        <v>3.75</v>
+        <v>4.21</v>
       </c>
       <c r="N44" t="n">
-        <v>2.1</v>
+        <v>5.4</v>
       </c>
       <c r="O44" t="n">
-        <v>3.32</v>
+        <v>2.05</v>
       </c>
       <c r="P44" t="n">
-        <v>2.32</v>
+        <v>2.45</v>
       </c>
       <c r="Q44" t="n">
-        <v>2.52</v>
+        <v>5.25</v>
       </c>
       <c r="R44" t="n">
         <v>1.28</v>
       </c>
       <c r="S44" t="n">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="T44" t="n">
         <v>2.25</v>
       </c>
       <c r="U44" t="n">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
       <c r="V44" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="W44" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="X44" t="n">
-        <v>5</v>
+        <v>4.33</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.59</v>
+        <v>1.64</v>
       </c>
       <c r="Z44" t="n">
-        <v>2.44</v>
+        <v>2.27</v>
       </c>
       <c r="AA44" t="n">
-        <v>2.44</v>
+        <v>2.6</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AC44" t="n">
-        <v>1.49</v>
+        <v>1.65</v>
       </c>
       <c r="AD44" t="n">
-        <v>2.48</v>
+        <v>2.1</v>
       </c>
       <c r="AE44" t="inlineStr">
         <is>
@@ -6154,10 +6154,10 @@
         </is>
       </c>
       <c r="AG44" t="n">
-        <v>1.3</v>
+        <v>1.17</v>
       </c>
       <c r="AH44" t="n">
-        <v>1.39</v>
+        <v>2.45</v>
       </c>
       <c r="AI44" t="n">
         <v>0</v>
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6216,61 +6216,61 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="M45" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="N45" t="n">
-        <v>5.91</v>
+        <v>5</v>
       </c>
       <c r="O45" t="n">
         <v>2</v>
       </c>
       <c r="P45" t="n">
-        <v>2.44</v>
+        <v>2.43</v>
       </c>
       <c r="Q45" t="n">
-        <v>5.25</v>
+        <v>5.05</v>
       </c>
       <c r="R45" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="S45" t="n">
-        <v>3.45</v>
+        <v>3.38</v>
       </c>
       <c r="T45" t="n">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="U45" t="n">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="V45" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="W45" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="X45" t="n">
-        <v>4.33</v>
+        <v>4.5</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.64</v>
+        <v>1.61</v>
       </c>
       <c r="Z45" t="n">
         <v>2.38</v>
       </c>
       <c r="AA45" t="n">
-        <v>2.59</v>
+        <v>2.52</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.47</v>
+        <v>1.56</v>
       </c>
       <c r="AC45" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AD45" t="n">
-        <v>2.18</v>
+        <v>2.27</v>
       </c>
       <c r="AE45" t="inlineStr">
         <is>
@@ -6286,7 +6286,7 @@
         <v>1.25</v>
       </c>
       <c r="AH45" t="n">
-        <v>2.47</v>
+        <v>2.41</v>
       </c>
       <c r="AI45" t="n">
         <v>0</v>
@@ -6345,58 +6345,58 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>1.52</v>
+        <v>1.74</v>
       </c>
       <c r="M46" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="N46" t="n">
-        <v>4.7</v>
+        <v>4.15</v>
       </c>
       <c r="O46" t="n">
-        <v>1.98</v>
+        <v>2.2</v>
       </c>
       <c r="P46" t="n">
-        <v>2.85</v>
+        <v>2.5</v>
       </c>
       <c r="Q46" t="n">
-        <v>4.35</v>
+        <v>4.23</v>
       </c>
       <c r="R46" t="n">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="S46" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="T46" t="n">
-        <v>1.83</v>
+        <v>1.88</v>
       </c>
       <c r="U46" t="n">
-        <v>1.81</v>
+        <v>1.78</v>
       </c>
       <c r="V46" t="n">
         <v>0</v>
       </c>
       <c r="W46" t="n">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="X46" t="n">
-        <v>6.8</v>
+        <v>6.54</v>
       </c>
       <c r="Y46" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="Z46" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="AA46" t="n">
-        <v>1.85</v>
+        <v>1.94</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="AC46" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="AD46" t="n">
         <v>2.7</v>
@@ -6412,10 +6412,10 @@
         </is>
       </c>
       <c r="AG46" t="n">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="AH46" t="n">
-        <v>2.38</v>
+        <v>2.12</v>
       </c>
       <c r="AI46" t="n">
         <v>0</v>
@@ -6474,28 +6474,28 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="M47" t="n">
-        <v>4.01</v>
+        <v>4</v>
       </c>
       <c r="N47" t="n">
-        <v>7.5</v>
+        <v>6.25</v>
       </c>
       <c r="O47" t="n">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="P47" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="Q47" t="n">
-        <v>6.25</v>
+        <v>6.1</v>
       </c>
       <c r="R47" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="S47" t="n">
-        <v>2.9</v>
+        <v>2.95</v>
       </c>
       <c r="T47" t="n">
         <v>2.75</v>
@@ -6507,10 +6507,10 @@
         <v>1.01</v>
       </c>
       <c r="W47" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="X47" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="Y47" t="n">
         <v>2.06</v>
@@ -6519,16 +6519,16 @@
         <v>1.75</v>
       </c>
       <c r="AA47" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="AC47" t="n">
         <v>2.2</v>
       </c>
       <c r="AD47" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="AE47" t="inlineStr">
         <is>
@@ -6603,16 +6603,16 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="M48" t="n">
         <v>3.1</v>
       </c>
       <c r="N48" t="n">
-        <v>3.57</v>
+        <v>4</v>
       </c>
       <c r="O48" t="n">
-        <v>2.67</v>
+        <v>2.66</v>
       </c>
       <c r="P48" t="n">
         <v>2</v>
@@ -6624,7 +6624,7 @@
         <v>1.51</v>
       </c>
       <c r="S48" t="n">
-        <v>2.47</v>
+        <v>2.39</v>
       </c>
       <c r="T48" t="n">
         <v>3.3</v>
@@ -6633,7 +6633,7 @@
         <v>1.28</v>
       </c>
       <c r="V48" t="n">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="W48" t="n">
         <v>1.41</v>
@@ -6642,10 +6642,10 @@
         <v>2.53</v>
       </c>
       <c r="Y48" t="n">
-        <v>2.12</v>
+        <v>2.23</v>
       </c>
       <c r="Z48" t="n">
-        <v>1.64</v>
+        <v>1.53</v>
       </c>
       <c r="AA48" t="n">
         <v>4.1</v>
@@ -6670,10 +6670,10 @@
         </is>
       </c>
       <c r="AG48" t="n">
-        <v>1.25</v>
+        <v>1.34</v>
       </c>
       <c r="AH48" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="AI48" t="n">
         <v>0</v>

--- a/jogos_2025-09-30.xlsx
+++ b/jogos_2025-09-30.xlsx
@@ -757,27 +757,27 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Kariobangi Sharks</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>KCB</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -798,61 +798,61 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
@@ -865,19 +865,19 @@
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AK3" s="3" t="n">
-        <v>45930.41666666666</v>
+        <v>45930.45833333334</v>
       </c>
     </row>
     <row r="4">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Sogdiana</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -927,61 +927,61 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>3.35</v>
+        <v>2.95</v>
       </c>
       <c r="M4" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="N4" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.25</v>
+        <v>2.08</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
@@ -994,16 +994,16 @@
         </is>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AK4" s="3" t="n">
         <v>45930.45833333334</v>
@@ -1015,27 +1015,27 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Sogdiana</t>
+          <t>Botev Plovdiv</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1056,61 +1056,61 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.95</v>
+        <v>4.6</v>
       </c>
       <c r="M5" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="N5" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="O5" t="n">
+        <v>6.42</v>
+      </c>
+      <c r="P5" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="S5" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="X5" t="n">
         <v>3.1</v>
       </c>
-      <c r="N5" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W5" t="n">
-        <v>0</v>
-      </c>
-      <c r="X5" t="n">
-        <v>0</v>
-      </c>
       <c r="Y5" t="n">
-        <v>2.08</v>
+        <v>2.25</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
@@ -1123,19 +1123,19 @@
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AK5" s="3" t="n">
-        <v>45930.45833333334</v>
+        <v>45930.47916666666</v>
       </c>
     </row>
     <row r="6">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Botev Plovdiv</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1185,61 +1185,61 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>5.25</v>
+        <v>19</v>
       </c>
       <c r="M6" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="N6" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z6" t="n">
         <v>3.4</v>
       </c>
-      <c r="N6" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="O6" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="P6" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="S6" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="T6" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U6" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="V6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W6" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="X6" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="Z6" t="n">
+      <c r="AA6" t="n">
         <v>1.8</v>
       </c>
-      <c r="AA6" t="n">
-        <v>3.35</v>
-      </c>
       <c r="AB6" t="n">
-        <v>1.25</v>
+        <v>1.94</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
@@ -1252,19 +1252,19 @@
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AI6" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AK6" s="3" t="n">
-        <v>45930.47916666666</v>
+        <v>45930.57291666666</v>
       </c>
     </row>
     <row r="7">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Police</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ulinzi Stars</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1314,13 +1314,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1353,10 +1353,10 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AA7" t="n">
         <v>0</v>
@@ -1393,7 +1393,7 @@
         <v>0</v>
       </c>
       <c r="AK7" s="3" t="n">
-        <v>45930.5</v>
+        <v>45930.57291666666</v>
       </c>
     </row>
     <row r="8">
@@ -1402,12 +1402,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Wehen Wiesbaden</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,61 +1443,61 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.86</v>
+        <v>2.68</v>
       </c>
       <c r="M8" t="n">
-        <v>3.84</v>
+        <v>3.55</v>
       </c>
       <c r="N8" t="n">
-        <v>3.7</v>
+        <v>2.35</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="Z8" t="n">
         <v>2.15</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AI8" t="n">
         <v>0</v>
@@ -1522,7 +1522,7 @@
         <v>0</v>
       </c>
       <c r="AK8" s="3" t="n">
-        <v>45930.57291666666</v>
+        <v>45930.58333333334</v>
       </c>
     </row>
     <row r="9">
@@ -1531,27 +1531,27 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,61 +1572,61 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>19</v>
+        <v>1.26</v>
       </c>
       <c r="M9" t="n">
-        <v>8.9</v>
+        <v>5.1</v>
       </c>
       <c r="N9" t="n">
-        <v>1.11</v>
+        <v>7.6</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.3</v>
+        <v>1.47</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.4</v>
+        <v>2.5</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.8</v>
+        <v>2.17</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.94</v>
+        <v>1.62</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
@@ -1651,7 +1651,7 @@
         <v>0</v>
       </c>
       <c r="AK9" s="3" t="n">
-        <v>45930.57291666666</v>
+        <v>45930.58333333334</v>
       </c>
     </row>
     <row r="10">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Havelse</t>
+          <t>Saarbrucken</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Waldhof Mannheim</t>
+          <t>MSV Duisburg</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,34 +1701,34 @@
         </is>
       </c>
       <c r="L10" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="M10" t="n">
         <v>3.4</v>
       </c>
-      <c r="M10" t="n">
-        <v>3.55</v>
-      </c>
       <c r="N10" t="n">
-        <v>1.93</v>
+        <v>3.02</v>
       </c>
       <c r="O10" t="n">
-        <v>3.7</v>
+        <v>2.71</v>
       </c>
       <c r="P10" t="n">
-        <v>2.24</v>
+        <v>2.14</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.38</v>
+        <v>3.54</v>
       </c>
       <c r="R10" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="S10" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="T10" t="n">
-        <v>2.44</v>
+        <v>2.48</v>
       </c>
       <c r="U10" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="V10" t="n">
         <v>1.04</v>
@@ -1737,25 +1737,25 @@
         <v>1.22</v>
       </c>
       <c r="X10" t="n">
-        <v>4.11</v>
+        <v>4.05</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.65</v>
+        <v>1.71</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.45</v>
+        <v>2.59</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.43</v>
+        <v>1.39</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="AD10" t="n">
-        <v>2.19</v>
+        <v>2.29</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -1768,10 +1768,10 @@
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.25</v>
+        <v>1.64</v>
       </c>
       <c r="AI10" t="n">
         <v>0</v>
@@ -1794,22 +1794,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Erzgebirge Aue</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,61 +1830,61 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.38</v>
+        <v>1.93</v>
       </c>
       <c r="M11" t="n">
-        <v>4.77</v>
+        <v>3.65</v>
       </c>
       <c r="N11" t="n">
-        <v>6.5</v>
+        <v>3.28</v>
       </c>
       <c r="O11" t="n">
-        <v>1.83</v>
+        <v>2.5</v>
       </c>
       <c r="P11" t="n">
-        <v>2.45</v>
+        <v>2.17</v>
       </c>
       <c r="Q11" t="n">
-        <v>5.7</v>
+        <v>3.33</v>
       </c>
       <c r="R11" t="n">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="S11" t="n">
-        <v>3.28</v>
+        <v>3.25</v>
       </c>
       <c r="T11" t="n">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
       <c r="U11" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="X11" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AC11" t="n">
         <v>1.62</v>
       </c>
-      <c r="V11" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="X11" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>1.84</v>
-      </c>
       <c r="AD11" t="n">
-        <v>1.86</v>
+        <v>2.15</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -1897,10 +1897,10 @@
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>1.13</v>
+        <v>1.24</v>
       </c>
       <c r="AH11" t="n">
-        <v>2.82</v>
+        <v>1.71</v>
       </c>
       <c r="AI11" t="n">
         <v>0</v>
@@ -1923,22 +1923,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Havelse</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Waldhof Mannheim</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,61 +1959,61 @@
         </is>
       </c>
       <c r="L12" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="M12" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="N12" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="O12" t="n">
+        <v>4.12</v>
+      </c>
+      <c r="P12" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S12" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="U12" t="n">
         <v>1.5</v>
       </c>
-      <c r="M12" t="n">
-        <v>4.51</v>
-      </c>
-      <c r="N12" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="O12" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="P12" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>5.07</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S12" t="n">
-        <v>3.66</v>
-      </c>
-      <c r="T12" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="U12" t="n">
-        <v>1.64</v>
-      </c>
       <c r="V12" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="W12" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="X12" t="n">
-        <v>5.6</v>
+        <v>4.1</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.42</v>
+        <v>1.65</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.47</v>
+        <v>2.12</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.05</v>
+        <v>2.56</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.62</v>
+        <v>1.44</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AD12" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -2026,10 +2026,10 @@
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>1.19</v>
+        <v>1.81</v>
       </c>
       <c r="AH12" t="n">
-        <v>2.31</v>
+        <v>1.24</v>
       </c>
       <c r="AI12" t="n">
         <v>0</v>
@@ -2052,22 +2052,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Hansa Rostock</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,61 +2088,61 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.08</v>
+        <v>1.56</v>
       </c>
       <c r="M13" t="n">
-        <v>3.59</v>
+        <v>4.2</v>
       </c>
       <c r="N13" t="n">
-        <v>3.06</v>
+        <v>4.2</v>
       </c>
       <c r="O13" t="n">
-        <v>2.44</v>
+        <v>1.95</v>
       </c>
       <c r="P13" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>5.07</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S13" t="n">
+        <v>3.66</v>
+      </c>
+      <c r="T13" t="n">
         <v>2.18</v>
       </c>
-      <c r="Q13" t="n">
-        <v>3.78</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S13" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="T13" t="n">
-        <v>2.52</v>
-      </c>
       <c r="U13" t="n">
-        <v>1.49</v>
+        <v>1.64</v>
       </c>
       <c r="V13" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="W13" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="X13" t="n">
-        <v>3.9</v>
+        <v>5.6</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.7</v>
+        <v>1.45</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.97</v>
+        <v>2.56</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.71</v>
+        <v>1.92</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.37</v>
+        <v>1.78</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.59</v>
+        <v>1.55</v>
       </c>
       <c r="AD13" t="n">
-        <v>2.08</v>
+        <v>2.3</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
@@ -2155,10 +2155,10 @@
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>1.24</v>
+        <v>1.19</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.67</v>
+        <v>2.31</v>
       </c>
       <c r="AI13" t="n">
         <v>0</v>
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>Hansa Rostock</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Wehen Wiesbaden</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,61 +2217,61 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.7</v>
+        <v>2.05</v>
       </c>
       <c r="M14" t="n">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="N14" t="n">
-        <v>2.3</v>
+        <v>3.15</v>
       </c>
       <c r="O14" t="n">
-        <v>3.34</v>
+        <v>2.44</v>
       </c>
       <c r="P14" t="n">
-        <v>2.21</v>
+        <v>2.18</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.83</v>
+        <v>3.78</v>
       </c>
       <c r="R14" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="S14" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="T14" t="n">
-        <v>2.38</v>
+        <v>2.52</v>
       </c>
       <c r="U14" t="n">
-        <v>1.53</v>
+        <v>1.49</v>
       </c>
       <c r="V14" t="n">
         <v>1.03</v>
       </c>
       <c r="W14" t="n">
-        <v>1.16</v>
+        <v>1.21</v>
       </c>
       <c r="X14" t="n">
-        <v>4.2</v>
+        <v>4.19</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.53</v>
+        <v>1.7</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.15</v>
+        <v>1.97</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.49</v>
+        <v>2.75</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.42</v>
+        <v>1.37</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.51</v>
+        <v>1.58</v>
       </c>
       <c r="AD14" t="n">
-        <v>2.36</v>
+        <v>2.32</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
@@ -2284,10 +2284,10 @@
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.4</v>
+        <v>1.66</v>
       </c>
       <c r="AI14" t="n">
         <v>0</v>
@@ -2305,12 +2305,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Erzgebirge Aue</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,61 +2346,61 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="M15" t="n">
         <v>3.6</v>
       </c>
       <c r="N15" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="O15" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="P15" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="Q15" t="n">
         <v>3.25</v>
       </c>
-      <c r="O15" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="P15" t="n">
+      <c r="R15" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S15" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="T15" t="n">
         <v>2.21</v>
       </c>
-      <c r="Q15" t="n">
-        <v>3.89</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="S15" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="T15" t="n">
-        <v>2.5</v>
-      </c>
       <c r="U15" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="X15" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AC15" t="n">
         <v>1.45</v>
       </c>
-      <c r="V15" t="n">
-        <v>1</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="X15" t="n">
-        <v>3.68</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>2</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>1.62</v>
-      </c>
       <c r="AD15" t="n">
-        <v>2.15</v>
+        <v>2.59</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
@@ -2413,10 +2413,10 @@
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.71</v>
+        <v>1.68</v>
       </c>
       <c r="AI15" t="n">
         <v>0</v>
@@ -2425,7 +2425,7 @@
         <v>0</v>
       </c>
       <c r="AK15" s="3" t="n">
-        <v>45930.58333333334</v>
+        <v>45930.625</v>
       </c>
     </row>
     <row r="16">
@@ -2434,12 +2434,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Saarbrucken</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>MSV Duisburg</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,34 +2475,34 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.87</v>
+        <v>1.7</v>
       </c>
       <c r="M16" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="N16" t="n">
-        <v>2.95</v>
+        <v>3.72</v>
       </c>
       <c r="O16" t="n">
-        <v>2.69</v>
+        <v>2.32</v>
       </c>
       <c r="P16" t="n">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.71</v>
+        <v>3.54</v>
       </c>
       <c r="R16" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="S16" t="n">
-        <v>3.1</v>
+        <v>3.28</v>
       </c>
       <c r="T16" t="n">
-        <v>2.49</v>
+        <v>2.47</v>
       </c>
       <c r="U16" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="V16" t="n">
         <v>1.04</v>
@@ -2511,25 +2511,25 @@
         <v>1.16</v>
       </c>
       <c r="X16" t="n">
-        <v>4.05</v>
+        <v>4.2</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="Z16" t="n">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.59</v>
+        <v>2.63</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.39</v>
+        <v>1.46</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.54</v>
+        <v>1.6</v>
       </c>
       <c r="AD16" t="n">
-        <v>2.29</v>
+        <v>2.23</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
@@ -2542,10 +2542,10 @@
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.61</v>
+        <v>1.95</v>
       </c>
       <c r="AI16" t="n">
         <v>0</v>
@@ -2554,7 +2554,7 @@
         <v>0</v>
       </c>
       <c r="AK16" s="3" t="n">
-        <v>45930.58333333334</v>
+        <v>45930.625</v>
       </c>
     </row>
     <row r="17">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,61 +2604,61 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.7</v>
+        <v>2.73</v>
       </c>
       <c r="M17" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="N17" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="O17" t="n">
         <v>3.5</v>
       </c>
-      <c r="N17" t="n">
-        <v>3.72</v>
-      </c>
-      <c r="O17" t="n">
+      <c r="P17" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S17" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="T17" t="n">
         <v>2.32</v>
       </c>
-      <c r="P17" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>3.54</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S17" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="T17" t="n">
-        <v>2.47</v>
-      </c>
       <c r="U17" t="n">
-        <v>1.48</v>
+        <v>1.54</v>
       </c>
       <c r="V17" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="W17" t="n">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="X17" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.64</v>
+        <v>1.57</v>
       </c>
       <c r="Z17" t="n">
-        <v>2.14</v>
+        <v>2.35</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.63</v>
+        <v>2.36</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.46</v>
+        <v>1.52</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.6</v>
+        <v>1.52</v>
       </c>
       <c r="AD17" t="n">
-        <v>2.23</v>
+        <v>2.45</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
@@ -2671,10 +2671,10 @@
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>1.25</v>
+        <v>1.67</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.95</v>
+        <v>1.37</v>
       </c>
       <c r="AI17" t="n">
         <v>0</v>
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,61 +2733,61 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O18" t="n">
-        <v>1.91</v>
+        <v>3.7</v>
       </c>
       <c r="P18" t="n">
-        <v>2.63</v>
+        <v>2.38</v>
       </c>
       <c r="Q18" t="n">
-        <v>5.34</v>
+        <v>2.61</v>
       </c>
       <c r="R18" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="S18" t="n">
-        <v>3.66</v>
+        <v>3.58</v>
       </c>
       <c r="T18" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="U18" t="n">
-        <v>1.64</v>
+        <v>1.61</v>
       </c>
       <c r="V18" t="n">
         <v>1.01</v>
       </c>
       <c r="W18" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X18" t="n">
-        <v>4.98</v>
+        <v>4.9</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="Z18" t="n">
-        <v>2.47</v>
+        <v>2.39</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.27</v>
+        <v>2.28</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.66</v>
+        <v>1.46</v>
       </c>
       <c r="AD18" t="n">
-        <v>2.24</v>
+        <v>2.5</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
@@ -2800,10 +2800,10 @@
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>1.12</v>
+        <v>1.79</v>
       </c>
       <c r="AH18" t="n">
-        <v>2.61</v>
+        <v>1.27</v>
       </c>
       <c r="AI18" t="n">
         <v>0</v>
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,61 +2862,61 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>2.65</v>
+        <v>1.91</v>
       </c>
       <c r="P19" t="n">
-        <v>2.51</v>
+        <v>2.63</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.25</v>
+        <v>5.34</v>
       </c>
       <c r="R19" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="S19" t="n">
-        <v>3.45</v>
+        <v>3.66</v>
       </c>
       <c r="T19" t="n">
-        <v>2.21</v>
+        <v>2.15</v>
       </c>
       <c r="U19" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="V19" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="W19" t="n">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="X19" t="n">
-        <v>4.75</v>
+        <v>4.98</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.53</v>
+        <v>1.43</v>
       </c>
       <c r="Z19" t="n">
-        <v>2.39</v>
+        <v>2.47</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.28</v>
+        <v>2.27</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.45</v>
+        <v>1.66</v>
       </c>
       <c r="AD19" t="n">
-        <v>2.59</v>
+        <v>2.24</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
@@ -2929,10 +2929,10 @@
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>1.25</v>
+        <v>1.12</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.68</v>
+        <v>2.61</v>
       </c>
       <c r="AI19" t="n">
         <v>0</v>
@@ -2950,12 +2950,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,78 +2991,78 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>3.7</v>
+        <v>3.25</v>
       </c>
       <c r="M20" t="n">
         <v>3.6</v>
       </c>
       <c r="N20" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="O20" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="P20" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="S20" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="X20" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="Z20" t="n">
         <v>2</v>
       </c>
-      <c r="O20" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="P20" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>2.61</v>
-      </c>
-      <c r="R20" t="n">
+      <c r="AA20" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AE20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG20" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AH20" t="n">
         <v>1.23</v>
       </c>
-      <c r="S20" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="T20" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="U20" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="V20" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W20" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X20" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AE20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG20" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>1.27</v>
-      </c>
       <c r="AI20" t="n">
         <v>0</v>
       </c>
@@ -3070,7 +3070,7 @@
         <v>0</v>
       </c>
       <c r="AK20" s="3" t="n">
-        <v>45930.625</v>
+        <v>45930.64583333334</v>
       </c>
     </row>
     <row r="21">
@@ -3079,12 +3079,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,61 +3120,61 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.73</v>
+        <v>2.59</v>
       </c>
       <c r="M21" t="n">
-        <v>3.7</v>
+        <v>3.01</v>
       </c>
       <c r="N21" t="n">
-        <v>2.18</v>
+        <v>2.84</v>
       </c>
       <c r="O21" t="n">
-        <v>3.5</v>
+        <v>2.97</v>
       </c>
       <c r="P21" t="n">
-        <v>2.47</v>
+        <v>1.91</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.55</v>
+        <v>3.4</v>
       </c>
       <c r="R21" t="n">
-        <v>1.28</v>
+        <v>1.45</v>
       </c>
       <c r="S21" t="n">
-        <v>3.34</v>
+        <v>2.48</v>
       </c>
       <c r="T21" t="n">
-        <v>2.32</v>
+        <v>3.14</v>
       </c>
       <c r="U21" t="n">
-        <v>1.54</v>
+        <v>1.29</v>
       </c>
       <c r="V21" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="W21" t="n">
-        <v>1.14</v>
+        <v>1.4</v>
       </c>
       <c r="X21" t="n">
-        <v>4.5</v>
+        <v>2.92</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.57</v>
+        <v>2.2</v>
       </c>
       <c r="Z21" t="n">
-        <v>2.35</v>
+        <v>1.67</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.36</v>
+        <v>4</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.52</v>
+        <v>1.18</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.52</v>
+        <v>2.01</v>
       </c>
       <c r="AD21" t="n">
-        <v>2.45</v>
+        <v>1.82</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
@@ -3187,10 +3187,10 @@
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>1.67</v>
+        <v>1.31</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.37</v>
+        <v>1.48</v>
       </c>
       <c r="AI21" t="n">
         <v>0</v>
@@ -3199,7 +3199,7 @@
         <v>0</v>
       </c>
       <c r="AK21" s="3" t="n">
-        <v>45930.625</v>
+        <v>45930.64583333334</v>
       </c>
     </row>
     <row r="22">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,62 +3249,62 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.5</v>
+        <v>1.98</v>
       </c>
       <c r="M22" t="n">
-        <v>3.24</v>
+        <v>3.47</v>
       </c>
       <c r="N22" t="n">
-        <v>2.7</v>
+        <v>3.62</v>
       </c>
       <c r="O22" t="n">
-        <v>3.39</v>
+        <v>2.71</v>
       </c>
       <c r="P22" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>4.04</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S22" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="V22" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="X22" t="n">
+        <v>3.56</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AD22" t="n">
         <v>2</v>
       </c>
-      <c r="Q22" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="R22" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S22" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="T22" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="U22" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="V22" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W22" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="X22" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>4.29</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>1.82</v>
-      </c>
       <c r="AE22" t="inlineStr">
         <is>
           <t>[]</t>
@@ -3316,10 +3316,10 @@
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>1.45</v>
+        <v>1.31</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.44</v>
+        <v>1.73</v>
       </c>
       <c r="AI22" t="n">
         <v>0</v>
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Calcio Padova</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,61 +3378,61 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.05</v>
+        <v>2.39</v>
       </c>
       <c r="M23" t="n">
-        <v>3.28</v>
+        <v>2.95</v>
       </c>
       <c r="N23" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="O23" t="n">
-        <v>2.75</v>
+        <v>3.14</v>
       </c>
       <c r="P23" t="n">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="Q23" t="n">
-        <v>4.25</v>
+        <v>4.15</v>
       </c>
       <c r="R23" t="n">
-        <v>1.45</v>
+        <v>1.53</v>
       </c>
       <c r="S23" t="n">
-        <v>2.48</v>
+        <v>2.49</v>
       </c>
       <c r="T23" t="n">
-        <v>3.2</v>
+        <v>3.34</v>
       </c>
       <c r="U23" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="V23" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="W23" t="n">
-        <v>1.37</v>
+        <v>1.47</v>
       </c>
       <c r="X23" t="n">
-        <v>2.74</v>
+        <v>2.5</v>
       </c>
       <c r="Y23" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="Z23" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="AA23" t="n">
-        <v>4.05</v>
+        <v>4.45</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.23</v>
+        <v>1.15</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.94</v>
+        <v>2.03</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.77</v>
+        <v>1.72</v>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
@@ -3445,10 +3445,10 @@
         </is>
       </c>
       <c r="AG23" t="n">
-        <v>1.34</v>
+        <v>1.31</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.7</v>
+        <v>1.61</v>
       </c>
       <c r="AI23" t="n">
         <v>0</v>
@@ -3516,52 +3516,52 @@
         <v>2.13</v>
       </c>
       <c r="O24" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="P24" t="n">
         <v>1.95</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.88</v>
+        <v>3.16</v>
       </c>
       <c r="R24" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="S24" t="n">
-        <v>2.42</v>
+        <v>2.57</v>
       </c>
       <c r="T24" t="n">
         <v>3.28</v>
       </c>
       <c r="U24" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="V24" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="W24" t="n">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="X24" t="n">
-        <v>2.7</v>
+        <v>2.63</v>
       </c>
       <c r="Y24" t="n">
-        <v>2.33</v>
+        <v>2.07</v>
       </c>
       <c r="Z24" t="n">
-        <v>1.6</v>
+        <v>1.75</v>
       </c>
       <c r="AA24" t="n">
-        <v>4.43</v>
+        <v>4.4</v>
       </c>
       <c r="AB24" t="n">
         <v>1.16</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
@@ -3574,10 +3574,10 @@
         </is>
       </c>
       <c r="AG24" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.31</v>
+        <v>1.38</v>
       </c>
       <c r="AI24" t="n">
         <v>0</v>
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Mantova</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,61 +3636,61 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.03</v>
+        <v>1.79</v>
       </c>
       <c r="M25" t="n">
-        <v>3.4</v>
+        <v>3.61</v>
       </c>
       <c r="N25" t="n">
-        <v>3.4</v>
+        <v>4.3</v>
       </c>
       <c r="O25" t="n">
-        <v>2.51</v>
+        <v>2.54</v>
       </c>
       <c r="P25" t="n">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="Q25" t="n">
-        <v>4.04</v>
+        <v>4.2</v>
       </c>
       <c r="R25" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="S25" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V25" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="W25" t="n">
         <v>1.35</v>
       </c>
-      <c r="S25" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="T25" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="U25" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="V25" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W25" t="n">
-        <v>1.22</v>
-      </c>
       <c r="X25" t="n">
-        <v>3.48</v>
+        <v>3.18</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.9</v>
+        <v>1.98</v>
       </c>
       <c r="Z25" t="n">
-        <v>1.9</v>
+        <v>1.77</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.9</v>
+        <v>3.55</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.29</v>
+        <v>1.23</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.7</v>
+        <v>1.89</v>
       </c>
       <c r="AD25" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
@@ -3703,10 +3703,10 @@
         </is>
       </c>
       <c r="AG25" t="n">
-        <v>1.26</v>
+        <v>1.32</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.7</v>
+        <v>1.86</v>
       </c>
       <c r="AI25" t="n">
         <v>0</v>
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mantova</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,61 +3765,61 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.83</v>
+        <v>2.02</v>
       </c>
       <c r="M26" t="n">
-        <v>3.58</v>
+        <v>3.23</v>
       </c>
       <c r="N26" t="n">
-        <v>4</v>
+        <v>3.78</v>
       </c>
       <c r="O26" t="n">
-        <v>2.31</v>
+        <v>2.86</v>
       </c>
       <c r="P26" t="n">
-        <v>2.13</v>
+        <v>1.99</v>
       </c>
       <c r="Q26" t="n">
-        <v>4.33</v>
+        <v>4.3</v>
       </c>
       <c r="R26" t="n">
-        <v>1.39</v>
+        <v>1.46</v>
       </c>
       <c r="S26" t="n">
-        <v>2.67</v>
+        <v>2.45</v>
       </c>
       <c r="T26" t="n">
-        <v>2.8</v>
+        <v>3.2</v>
       </c>
       <c r="U26" t="n">
-        <v>1.37</v>
+        <v>1.28</v>
       </c>
       <c r="V26" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="W26" t="n">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="X26" t="n">
-        <v>3.08</v>
+        <v>2.9</v>
       </c>
       <c r="Y26" t="n">
-        <v>2.03</v>
+        <v>2.18</v>
       </c>
       <c r="Z26" t="n">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AA26" t="n">
-        <v>3.55</v>
+        <v>3.85</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.28</v>
+        <v>1.18</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.86</v>
+        <v>2.06</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.84</v>
+        <v>1.74</v>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
@@ -3832,10 +3832,10 @@
         </is>
       </c>
       <c r="AG26" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.93</v>
+        <v>1.72</v>
       </c>
       <c r="AI26" t="n">
         <v>0</v>
@@ -3853,12 +3853,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Calcio Padova</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,61 +3894,61 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.37</v>
+        <v>2.19</v>
       </c>
       <c r="M27" t="n">
-        <v>2.91</v>
+        <v>3.47</v>
       </c>
       <c r="N27" t="n">
-        <v>3.26</v>
+        <v>3.08</v>
       </c>
       <c r="O27" t="n">
-        <v>3.01</v>
+        <v>2.65</v>
       </c>
       <c r="P27" t="n">
-        <v>1.91</v>
+        <v>2.07</v>
       </c>
       <c r="Q27" t="n">
         <v>3.75</v>
       </c>
       <c r="R27" t="n">
-        <v>1.5</v>
+        <v>1.39</v>
       </c>
       <c r="S27" t="n">
-        <v>2.4</v>
+        <v>2.67</v>
       </c>
       <c r="T27" t="n">
-        <v>3.28</v>
+        <v>3.08</v>
       </c>
       <c r="U27" t="n">
-        <v>1.27</v>
+        <v>1.34</v>
       </c>
       <c r="V27" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="W27" t="n">
-        <v>1.48</v>
+        <v>1.32</v>
       </c>
       <c r="X27" t="n">
-        <v>2.56</v>
+        <v>3.08</v>
       </c>
       <c r="Y27" t="n">
-        <v>2.4</v>
+        <v>1.98</v>
       </c>
       <c r="Z27" t="n">
-        <v>1.55</v>
+        <v>1.77</v>
       </c>
       <c r="AA27" t="n">
-        <v>4.75</v>
+        <v>3.64</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.16</v>
+        <v>1.26</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.99</v>
+        <v>1.81</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.74</v>
+        <v>1.91</v>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
@@ -3964,7 +3964,7 @@
         <v>1.35</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="AI27" t="n">
         <v>0</v>
@@ -3973,7 +3973,7 @@
         <v>0</v>
       </c>
       <c r="AK27" s="3" t="n">
-        <v>45930.64583333334</v>
+        <v>45930.65625</v>
       </c>
     </row>
     <row r="28">
@@ -3982,12 +3982,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,61 +4023,61 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>3.75</v>
+        <v>1.65</v>
       </c>
       <c r="M28" t="n">
-        <v>3.4</v>
+        <v>3.82</v>
       </c>
       <c r="N28" t="n">
-        <v>1.8</v>
+        <v>4.9</v>
       </c>
       <c r="O28" t="n">
-        <v>3.9</v>
+        <v>2.27</v>
       </c>
       <c r="P28" t="n">
-        <v>2.16</v>
+        <v>2.17</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.44</v>
+        <v>4.65</v>
       </c>
       <c r="R28" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="S28" t="n">
-        <v>2.9</v>
+        <v>3.09</v>
       </c>
       <c r="T28" t="n">
-        <v>2.43</v>
+        <v>2.7</v>
       </c>
       <c r="U28" t="n">
-        <v>1.48</v>
+        <v>1.4</v>
       </c>
       <c r="V28" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W28" t="n">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="X28" t="n">
-        <v>3.9</v>
+        <v>3.48</v>
       </c>
       <c r="Y28" t="n">
         <v>1.83</v>
       </c>
       <c r="Z28" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="AA28" t="n">
-        <v>2.92</v>
+        <v>3.18</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.67</v>
+        <v>1.88</v>
       </c>
       <c r="AD28" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
@@ -4090,10 +4090,10 @@
         </is>
       </c>
       <c r="AG28" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.23</v>
+        <v>2.05</v>
       </c>
       <c r="AI28" t="n">
         <v>0</v>
@@ -4102,7 +4102,7 @@
         <v>0</v>
       </c>
       <c r="AK28" s="3" t="n">
-        <v>45930.64583333334</v>
+        <v>45930.65625</v>
       </c>
     </row>
     <row r="29">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,61 +4152,61 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.5</v>
+        <v>2.36</v>
       </c>
       <c r="M29" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="N29" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="O29" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="P29" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q29" t="n">
         <v>3.25</v>
       </c>
-      <c r="N29" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="O29" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="P29" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>3.4</v>
-      </c>
       <c r="R29" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="S29" t="n">
-        <v>2.54</v>
+        <v>2.75</v>
       </c>
       <c r="T29" t="n">
-        <v>3.08</v>
+        <v>2.6</v>
       </c>
       <c r="U29" t="n">
-        <v>1.3</v>
+        <v>1.37</v>
       </c>
       <c r="V29" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W29" t="n">
-        <v>1.38</v>
+        <v>1.27</v>
       </c>
       <c r="X29" t="n">
-        <v>2.83</v>
+        <v>3.36</v>
       </c>
       <c r="Y29" t="n">
-        <v>2.2</v>
+        <v>1.89</v>
       </c>
       <c r="Z29" t="n">
-        <v>1.65</v>
+        <v>1.85</v>
       </c>
       <c r="AA29" t="n">
-        <v>3.9</v>
+        <v>3.2</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.19</v>
+        <v>1.28</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.92</v>
+        <v>1.79</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.86</v>
+        <v>2.02</v>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
@@ -4219,10 +4219,10 @@
         </is>
       </c>
       <c r="AG29" t="n">
-        <v>1.43</v>
+        <v>1.32</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="AI29" t="n">
         <v>0</v>
@@ -4245,7 +4245,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,61 +4281,61 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.67</v>
+        <v>1.4</v>
       </c>
       <c r="M30" t="n">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="N30" t="n">
-        <v>5</v>
+        <v>5.9</v>
       </c>
       <c r="O30" t="n">
-        <v>2.27</v>
+        <v>2.01</v>
       </c>
       <c r="P30" t="n">
-        <v>2.2</v>
+        <v>2.35</v>
       </c>
       <c r="Q30" t="n">
-        <v>5.35</v>
+        <v>6.05</v>
       </c>
       <c r="R30" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="S30" t="n">
-        <v>2.84</v>
+        <v>3.14</v>
       </c>
       <c r="T30" t="n">
-        <v>2.6</v>
+        <v>2.51</v>
       </c>
       <c r="U30" t="n">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="V30" t="n">
         <v>1.02</v>
       </c>
       <c r="W30" t="n">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="X30" t="n">
-        <v>3.48</v>
+        <v>3.98</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.88</v>
+        <v>1.65</v>
       </c>
       <c r="Z30" t="n">
-        <v>1.94</v>
+        <v>2.1</v>
       </c>
       <c r="AA30" t="n">
-        <v>3.25</v>
+        <v>2.63</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="AC30" t="n">
-        <v>1.81</v>
+        <v>1.84</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.91</v>
+        <v>1.84</v>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
@@ -4348,10 +4348,10 @@
         </is>
       </c>
       <c r="AG30" t="n">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="AH30" t="n">
-        <v>2.17</v>
+        <v>2.61</v>
       </c>
       <c r="AI30" t="n">
         <v>0</v>
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,61 +4410,61 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.19</v>
+        <v>1.36</v>
       </c>
       <c r="M31" t="n">
-        <v>3.3</v>
+        <v>4.75</v>
       </c>
       <c r="N31" t="n">
-        <v>3.3</v>
+        <v>8</v>
       </c>
       <c r="O31" t="n">
-        <v>2.75</v>
+        <v>1.94</v>
       </c>
       <c r="P31" t="n">
-        <v>2.07</v>
+        <v>2.35</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.86</v>
+        <v>6.5</v>
       </c>
       <c r="R31" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="S31" t="n">
-        <v>2.77</v>
+        <v>2.93</v>
       </c>
       <c r="T31" t="n">
-        <v>3.08</v>
+        <v>2.64</v>
       </c>
       <c r="U31" t="n">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="V31" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="W31" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="X31" t="n">
-        <v>3.15</v>
+        <v>3.48</v>
       </c>
       <c r="Y31" t="n">
-        <v>2.07</v>
+        <v>1.85</v>
       </c>
       <c r="Z31" t="n">
-        <v>1.72</v>
+        <v>1.89</v>
       </c>
       <c r="AA31" t="n">
-        <v>3.64</v>
+        <v>3.02</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.22</v>
+        <v>1.38</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.81</v>
+        <v>2.1</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.91</v>
+        <v>1.7</v>
       </c>
       <c r="AE31" t="inlineStr">
         <is>
@@ -4477,10 +4477,10 @@
         </is>
       </c>
       <c r="AG31" t="n">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.66</v>
+        <v>2.99</v>
       </c>
       <c r="AI31" t="n">
         <v>0</v>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,61 +4539,61 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.47</v>
+        <v>3.2</v>
       </c>
       <c r="M32" t="n">
-        <v>4.3</v>
+        <v>3.3</v>
       </c>
       <c r="N32" t="n">
-        <v>6.4</v>
+        <v>2.2</v>
       </c>
       <c r="O32" t="n">
-        <v>2.01</v>
+        <v>3.62</v>
       </c>
       <c r="P32" t="n">
-        <v>2.35</v>
+        <v>2.11</v>
       </c>
       <c r="Q32" t="n">
-        <v>5</v>
+        <v>2.98</v>
       </c>
       <c r="R32" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S32" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="T32" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="V32" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W32" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="X32" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AB32" t="n">
         <v>1.3</v>
       </c>
-      <c r="S32" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="T32" t="n">
-        <v>2.51</v>
-      </c>
-      <c r="U32" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="V32" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W32" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="X32" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="Y32" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>1.36</v>
-      </c>
       <c r="AC32" t="n">
-        <v>1.84</v>
+        <v>1.67</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.88</v>
+        <v>2.18</v>
       </c>
       <c r="AE32" t="inlineStr">
         <is>
@@ -4606,10 +4606,10 @@
         </is>
       </c>
       <c r="AG32" t="n">
-        <v>1.12</v>
+        <v>1.32</v>
       </c>
       <c r="AH32" t="n">
-        <v>2.61</v>
+        <v>1.41</v>
       </c>
       <c r="AI32" t="n">
         <v>0</v>
@@ -4668,31 +4668,31 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="M33" t="n">
         <v>3.4</v>
       </c>
       <c r="N33" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="O33" t="n">
-        <v>2.5</v>
+        <v>2.57</v>
       </c>
       <c r="P33" t="n">
-        <v>2.2</v>
+        <v>2.08</v>
       </c>
       <c r="Q33" t="n">
-        <v>4.55</v>
+        <v>4.65</v>
       </c>
       <c r="R33" t="n">
-        <v>1.39</v>
+        <v>1.35</v>
       </c>
       <c r="S33" t="n">
         <v>2.86</v>
       </c>
       <c r="T33" t="n">
-        <v>3.04</v>
+        <v>2.93</v>
       </c>
       <c r="U33" t="n">
         <v>1.36</v>
@@ -4707,22 +4707,22 @@
         <v>3.16</v>
       </c>
       <c r="Y33" t="n">
-        <v>2.02</v>
+        <v>1.98</v>
       </c>
       <c r="Z33" t="n">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="AA33" t="n">
         <v>3.55</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="AC33" t="n">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.89</v>
+        <v>1.93</v>
       </c>
       <c r="AE33" t="inlineStr">
         <is>
@@ -4735,10 +4735,10 @@
         </is>
       </c>
       <c r="AG33" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.81</v>
+        <v>1.86</v>
       </c>
       <c r="AI33" t="n">
         <v>0</v>
@@ -4761,7 +4761,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,61 +4797,61 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.92</v>
+        <v>3.06</v>
       </c>
       <c r="M34" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="N34" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="O34" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="P34" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="R34" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S34" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="T34" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="V34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W34" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X34" t="n">
         <v>3.4</v>
       </c>
-      <c r="N34" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="O34" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="P34" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="R34" t="n">
+      <c r="Y34" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AB34" t="n">
         <v>1.35</v>
       </c>
-      <c r="S34" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="T34" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="U34" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="V34" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W34" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="X34" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="Y34" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="Z34" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AA34" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AB34" t="n">
-        <v>1.33</v>
-      </c>
       <c r="AC34" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AD34" t="n">
-        <v>2.11</v>
+        <v>2.05</v>
       </c>
       <c r="AE34" t="inlineStr">
         <is>
@@ -4864,10 +4864,10 @@
         </is>
       </c>
       <c r="AG34" t="n">
-        <v>1.58</v>
+        <v>1.7</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AI34" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,61 +4926,61 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>3</v>
+        <v>2.49</v>
       </c>
       <c r="M35" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="N35" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="O35" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="P35" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="Q35" t="n">
         <v>3.4</v>
       </c>
-      <c r="N35" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="O35" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="P35" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Q35" t="n">
-        <v>2.74</v>
-      </c>
       <c r="R35" t="n">
-        <v>1.35</v>
+        <v>1.43</v>
       </c>
       <c r="S35" t="n">
-        <v>2.85</v>
+        <v>2.54</v>
       </c>
       <c r="T35" t="n">
-        <v>2.67</v>
+        <v>3.08</v>
       </c>
       <c r="U35" t="n">
-        <v>1.37</v>
+        <v>1.3</v>
       </c>
       <c r="V35" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W35" t="n">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="X35" t="n">
-        <v>3.25</v>
+        <v>2.83</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.9</v>
+        <v>2.2</v>
       </c>
       <c r="Z35" t="n">
-        <v>1.91</v>
+        <v>1.68</v>
       </c>
       <c r="AA35" t="n">
-        <v>3.15</v>
+        <v>4.2</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.35</v>
+        <v>1.19</v>
       </c>
       <c r="AC35" t="n">
-        <v>1.7</v>
+        <v>1.92</v>
       </c>
       <c r="AD35" t="n">
-        <v>2.03</v>
+        <v>1.86</v>
       </c>
       <c r="AE35" t="inlineStr">
         <is>
@@ -4993,10 +4993,10 @@
         </is>
       </c>
       <c r="AG35" t="n">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.34</v>
+        <v>1.52</v>
       </c>
       <c r="AI35" t="n">
         <v>0</v>
@@ -5014,7 +5014,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,77 +5055,77 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="M36" t="n">
-        <v>3.8</v>
+        <v>3.39</v>
       </c>
       <c r="N36" t="n">
-        <v>2.62</v>
+        <v>2.79</v>
       </c>
       <c r="O36" t="n">
-        <v>3.12</v>
+        <v>3.34</v>
       </c>
       <c r="P36" t="n">
-        <v>2.23</v>
+        <v>1.86</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.34</v>
+        <v>3.68</v>
       </c>
       <c r="R36" t="n">
-        <v>1.32</v>
+        <v>1.51</v>
       </c>
       <c r="S36" t="n">
-        <v>2.75</v>
+        <v>2.32</v>
       </c>
       <c r="T36" t="n">
-        <v>2.75</v>
+        <v>3.7</v>
       </c>
       <c r="U36" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="V36" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="W36" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="X36" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AE36" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF36" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG36" t="n">
         <v>1.37</v>
       </c>
-      <c r="V36" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W36" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="X36" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="Y36" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="Z36" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AA36" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AB36" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AC36" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AD36" t="n">
-        <v>2</v>
-      </c>
-      <c r="AE36" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF36" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG36" t="n">
-        <v>1.32</v>
-      </c>
       <c r="AH36" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="AI36" t="n">
         <v>0</v>
@@ -5134,7 +5134,7 @@
         <v>0</v>
       </c>
       <c r="AK36" s="3" t="n">
-        <v>45930.65625</v>
+        <v>45930.66666666666</v>
       </c>
     </row>
     <row r="37">
@@ -5143,12 +5143,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,61 +5184,61 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>1.41</v>
+        <v>1.62</v>
       </c>
       <c r="M37" t="n">
-        <v>4.51</v>
+        <v>4.1</v>
       </c>
       <c r="N37" t="n">
-        <v>7.9</v>
+        <v>4.9</v>
       </c>
       <c r="O37" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S37" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T37" t="n">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="U37" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="V37" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W37" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="X37" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.85</v>
+        <v>1.68</v>
       </c>
       <c r="Z37" t="n">
-        <v>1.94</v>
+        <v>2.18</v>
       </c>
       <c r="AA37" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AC37" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AD37" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AE37" t="inlineStr">
         <is>
@@ -5251,10 +5251,10 @@
         </is>
       </c>
       <c r="AG37" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AH37" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="AI37" t="n">
         <v>0</v>
@@ -5263,7 +5263,7 @@
         <v>0</v>
       </c>
       <c r="AK37" s="3" t="n">
-        <v>45930.65625</v>
+        <v>45930.66666666666</v>
       </c>
     </row>
     <row r="38">
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,61 +5313,61 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>3</v>
+        <v>4.3</v>
       </c>
       <c r="M38" t="n">
-        <v>3.83</v>
+        <v>4.4</v>
       </c>
       <c r="N38" t="n">
-        <v>2.1</v>
+        <v>1.64</v>
       </c>
       <c r="O38" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="S38" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="T38" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="U38" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="V38" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W38" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X38" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="Y38" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="Z38" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AA38" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="AC38" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AD38" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="AE38" t="inlineStr">
         <is>
@@ -5380,10 +5380,10 @@
         </is>
       </c>
       <c r="AG38" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AH38" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AI38" t="n">
         <v>0</v>
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,61 +5442,61 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>4.7</v>
+        <v>15</v>
       </c>
       <c r="M39" t="n">
-        <v>4.6</v>
+        <v>7.6</v>
       </c>
       <c r="N39" t="n">
-        <v>1.63</v>
+        <v>1.15</v>
       </c>
       <c r="O39" t="n">
-        <v>4.45</v>
+        <v>11.7</v>
       </c>
       <c r="P39" t="n">
-        <v>2.5</v>
+        <v>3.1</v>
       </c>
       <c r="Q39" t="n">
-        <v>2.05</v>
+        <v>1.43</v>
       </c>
       <c r="R39" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="S39" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="T39" t="n">
-        <v>2.15</v>
+        <v>1.98</v>
       </c>
       <c r="U39" t="n">
-        <v>1.72</v>
+        <v>1.8</v>
       </c>
       <c r="V39" t="n">
         <v>1.01</v>
       </c>
       <c r="W39" t="n">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="X39" t="n">
-        <v>5.35</v>
+        <v>6.15</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="Z39" t="n">
-        <v>2.67</v>
+        <v>2.9</v>
       </c>
       <c r="AA39" t="n">
-        <v>2.14</v>
+        <v>1.95</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="AC39" t="n">
-        <v>1.48</v>
+        <v>2.46</v>
       </c>
       <c r="AD39" t="n">
-        <v>2.5</v>
+        <v>1.57</v>
       </c>
       <c r="AE39" t="inlineStr">
         <is>
@@ -5509,10 +5509,10 @@
         </is>
       </c>
       <c r="AG39" t="n">
-        <v>1.23</v>
+        <v>1.08</v>
       </c>
       <c r="AH39" t="n">
-        <v>1.23</v>
+        <v>1.01</v>
       </c>
       <c r="AI39" t="n">
         <v>0</v>
@@ -5535,7 +5535,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Olympique Marseille</t>
+          <t>Kariobangi Sharks</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>KCB</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,61 +5571,61 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="O40" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="R40" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="S40" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="T40" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="U40" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="V40" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W40" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="X40" t="n">
-        <v>4.65</v>
+        <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="Z40" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AC40" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AD40" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AE40" t="inlineStr">
         <is>
@@ -5638,10 +5638,10 @@
         </is>
       </c>
       <c r="AG40" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AH40" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AI40" t="n">
         <v>0</v>
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,61 +5700,61 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>15</v>
+        <v>1.56</v>
       </c>
       <c r="M41" t="n">
-        <v>7.6</v>
+        <v>4.1</v>
       </c>
       <c r="N41" t="n">
-        <v>1.15</v>
+        <v>5.4</v>
       </c>
       <c r="O41" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="S41" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="T41" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="U41" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="V41" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W41" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="X41" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.44</v>
+        <v>1.63</v>
       </c>
       <c r="Z41" t="n">
-        <v>2.75</v>
+        <v>2.25</v>
       </c>
       <c r="AA41" t="n">
-        <v>1.95</v>
+        <v>2.64</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.79</v>
+        <v>1.52</v>
       </c>
       <c r="AC41" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AD41" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AE41" t="inlineStr">
         <is>
@@ -5767,10 +5767,10 @@
         </is>
       </c>
       <c r="AG41" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AH41" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AI41" t="n">
         <v>0</v>
@@ -5793,7 +5793,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,61 +5829,61 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>2.56</v>
+        <v>3</v>
       </c>
       <c r="M42" t="n">
-        <v>3.1</v>
+        <v>3.83</v>
       </c>
       <c r="N42" t="n">
-        <v>2.7</v>
+        <v>2.1</v>
       </c>
       <c r="O42" t="n">
-        <v>3.32</v>
+        <v>3.45</v>
       </c>
       <c r="P42" t="n">
-        <v>1.93</v>
+        <v>2.38</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.65</v>
+        <v>2.58</v>
       </c>
       <c r="R42" t="n">
-        <v>1.52</v>
+        <v>1.25</v>
       </c>
       <c r="S42" t="n">
-        <v>2.35</v>
+        <v>3.45</v>
       </c>
       <c r="T42" t="n">
-        <v>3.4</v>
+        <v>2.25</v>
       </c>
       <c r="U42" t="n">
-        <v>1.24</v>
+        <v>1.59</v>
       </c>
       <c r="V42" t="n">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="W42" t="n">
-        <v>1.48</v>
+        <v>1.18</v>
       </c>
       <c r="X42" t="n">
-        <v>2.5</v>
+        <v>5.2</v>
       </c>
       <c r="Y42" t="n">
-        <v>2.5</v>
+        <v>1.58</v>
       </c>
       <c r="Z42" t="n">
-        <v>1.53</v>
+        <v>2.22</v>
       </c>
       <c r="AA42" t="n">
-        <v>4.7</v>
+        <v>2.25</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.14</v>
+        <v>1.65</v>
       </c>
       <c r="AC42" t="n">
-        <v>2.03</v>
+        <v>1.49</v>
       </c>
       <c r="AD42" t="n">
-        <v>1.72</v>
+        <v>2.48</v>
       </c>
       <c r="AE42" t="inlineStr">
         <is>
@@ -5896,10 +5896,10 @@
         </is>
       </c>
       <c r="AG42" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AH42" t="n">
         <v>1.38</v>
-      </c>
-      <c r="AH42" t="n">
-        <v>1.5</v>
       </c>
       <c r="AI42" t="n">
         <v>0</v>
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Olympique Marseille</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5958,31 +5958,31 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>1.35</v>
+        <v>1.56</v>
       </c>
       <c r="M43" t="n">
-        <v>5</v>
+        <v>4.3</v>
       </c>
       <c r="N43" t="n">
-        <v>8.25</v>
+        <v>5.1</v>
       </c>
       <c r="O43" t="n">
-        <v>1.81</v>
+        <v>2</v>
       </c>
       <c r="P43" t="n">
         <v>2.6</v>
       </c>
       <c r="Q43" t="n">
-        <v>6.5</v>
+        <v>4.84</v>
       </c>
       <c r="R43" t="n">
         <v>1.25</v>
       </c>
       <c r="S43" t="n">
-        <v>3.75</v>
+        <v>3.38</v>
       </c>
       <c r="T43" t="n">
-        <v>2.24</v>
+        <v>2.3</v>
       </c>
       <c r="U43" t="n">
         <v>1.6</v>
@@ -5991,28 +5991,28 @@
         <v>1.01</v>
       </c>
       <c r="W43" t="n">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="X43" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.51</v>
+        <v>1.63</v>
       </c>
       <c r="Z43" t="n">
-        <v>2.43</v>
+        <v>2.25</v>
       </c>
       <c r="AA43" t="n">
-        <v>2.42</v>
+        <v>2.35</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="AC43" t="n">
-        <v>1.81</v>
+        <v>1.7</v>
       </c>
       <c r="AD43" t="n">
-        <v>1.93</v>
+        <v>2.05</v>
       </c>
       <c r="AE43" t="inlineStr">
         <is>
@@ -6025,10 +6025,10 @@
         </is>
       </c>
       <c r="AG43" t="n">
-        <v>1.17</v>
+        <v>1.23</v>
       </c>
       <c r="AH43" t="n">
-        <v>3.2</v>
+        <v>2.58</v>
       </c>
       <c r="AI43" t="n">
         <v>0</v>
@@ -6061,12 +6061,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6087,61 +6087,61 @@
         </is>
       </c>
       <c r="L44" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="M44" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="N44" t="n">
+        <v>7</v>
+      </c>
+      <c r="O44" t="n">
+        <v>0</v>
+      </c>
+      <c r="P44" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>0</v>
+      </c>
+      <c r="R44" t="n">
+        <v>0</v>
+      </c>
+      <c r="S44" t="n">
+        <v>0</v>
+      </c>
+      <c r="T44" t="n">
+        <v>0</v>
+      </c>
+      <c r="U44" t="n">
+        <v>0</v>
+      </c>
+      <c r="V44" t="n">
+        <v>0</v>
+      </c>
+      <c r="W44" t="n">
+        <v>0</v>
+      </c>
+      <c r="X44" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y44" t="n">
         <v>1.6</v>
       </c>
-      <c r="M44" t="n">
-        <v>4.21</v>
-      </c>
-      <c r="N44" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="O44" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="P44" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="Q44" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="R44" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="S44" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="T44" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="U44" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="V44" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W44" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="X44" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="Y44" t="n">
-        <v>1.64</v>
-      </c>
       <c r="Z44" t="n">
-        <v>2.27</v>
+        <v>2.35</v>
       </c>
       <c r="AA44" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AC44" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AD44" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AE44" t="inlineStr">
         <is>
@@ -6154,10 +6154,10 @@
         </is>
       </c>
       <c r="AG44" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AH44" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AI44" t="n">
         <v>0</v>
@@ -6175,12 +6175,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Police</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Ulinzi Stars</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6216,61 +6216,61 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="N45" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O45" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P45" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>5.05</v>
+        <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="S45" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="T45" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="U45" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="V45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W45" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="X45" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="Z45" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AA45" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AC45" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AD45" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="AE45" t="inlineStr">
         <is>
@@ -6283,10 +6283,10 @@
         </is>
       </c>
       <c r="AG45" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH45" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="AI45" t="n">
         <v>0</v>
@@ -6295,7 +6295,7 @@
         <v>0</v>
       </c>
       <c r="AK45" s="3" t="n">
-        <v>45930.66666666666</v>
+        <v>45930.75</v>
       </c>
     </row>
     <row r="46">
@@ -6345,61 +6345,61 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>1.74</v>
+        <v>1.52</v>
       </c>
       <c r="M46" t="n">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="N46" t="n">
-        <v>4.15</v>
+        <v>4.7</v>
       </c>
       <c r="O46" t="n">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="P46" t="n">
         <v>2.5</v>
       </c>
       <c r="Q46" t="n">
-        <v>4.23</v>
+        <v>4.2</v>
       </c>
       <c r="R46" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="S46" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="T46" t="n">
-        <v>1.88</v>
+        <v>1.99</v>
       </c>
       <c r="U46" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="V46" t="n">
         <v>0</v>
       </c>
       <c r="W46" t="n">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="X46" t="n">
-        <v>6.54</v>
+        <v>6.8</v>
       </c>
       <c r="Y46" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="Z46" t="n">
-        <v>3</v>
+        <v>3.04</v>
       </c>
       <c r="AA46" t="n">
-        <v>1.94</v>
+        <v>1.85</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="AC46" t="n">
         <v>1.41</v>
       </c>
       <c r="AD46" t="n">
-        <v>2.7</v>
+        <v>2.89</v>
       </c>
       <c r="AE46" t="inlineStr">
         <is>
@@ -6412,10 +6412,10 @@
         </is>
       </c>
       <c r="AG46" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AH46" t="n">
-        <v>2.12</v>
+        <v>2.24</v>
       </c>
       <c r="AI46" t="n">
         <v>0</v>
@@ -6474,58 +6474,58 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>1.53</v>
+        <v>1.4</v>
       </c>
       <c r="M47" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="N47" t="n">
-        <v>6.25</v>
+        <v>6</v>
       </c>
       <c r="O47" t="n">
-        <v>2</v>
+        <v>2.16</v>
       </c>
       <c r="P47" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="Q47" t="n">
-        <v>6.1</v>
+        <v>5.75</v>
       </c>
       <c r="R47" t="n">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="S47" t="n">
-        <v>2.95</v>
+        <v>2.85</v>
       </c>
       <c r="T47" t="n">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="U47" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="V47" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="W47" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="X47" t="n">
-        <v>3.55</v>
+        <v>3.02</v>
       </c>
       <c r="Y47" t="n">
-        <v>2.06</v>
+        <v>1.86</v>
       </c>
       <c r="Z47" t="n">
-        <v>1.75</v>
+        <v>1.84</v>
       </c>
       <c r="AA47" t="n">
-        <v>3.35</v>
+        <v>3.7</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AC47" t="n">
-        <v>2.2</v>
+        <v>2.08</v>
       </c>
       <c r="AD47" t="n">
         <v>1.67</v>
@@ -6541,10 +6541,10 @@
         </is>
       </c>
       <c r="AG47" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AH47" t="n">
-        <v>2.51</v>
+        <v>2.42</v>
       </c>
       <c r="AI47" t="n">
         <v>0</v>
@@ -6603,16 +6603,16 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="M48" t="n">
         <v>3.1</v>
       </c>
       <c r="N48" t="n">
-        <v>4</v>
+        <v>3.57</v>
       </c>
       <c r="O48" t="n">
-        <v>2.66</v>
+        <v>2.67</v>
       </c>
       <c r="P48" t="n">
         <v>2</v>
@@ -6636,22 +6636,22 @@
         <v>1.05</v>
       </c>
       <c r="W48" t="n">
-        <v>1.41</v>
+        <v>1.47</v>
       </c>
       <c r="X48" t="n">
-        <v>2.53</v>
+        <v>2.95</v>
       </c>
       <c r="Y48" t="n">
-        <v>2.23</v>
+        <v>2.12</v>
       </c>
       <c r="Z48" t="n">
-        <v>1.53</v>
+        <v>1.64</v>
       </c>
       <c r="AA48" t="n">
         <v>4.1</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="AC48" t="n">
         <v>2</v>

--- a/jogos_2025-09-30.xlsx
+++ b/jogos_2025-09-30.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK48"/>
+  <dimension ref="A1:AK49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -757,27 +757,27 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Kariobangi Sharks</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>KCB</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -798,61 +798,61 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
@@ -865,19 +865,19 @@
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AI3" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AK3" s="3" t="n">
-        <v>45930.45833333334</v>
+        <v>45930.41666666666</v>
       </c>
     </row>
     <row r="4">
@@ -1015,27 +1015,27 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Botev Plovdiv</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1056,61 +1056,61 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>4.6</v>
+        <v>3.35</v>
       </c>
       <c r="M5" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="N5" t="n">
-        <v>1.82</v>
+        <v>2.2</v>
       </c>
       <c r="O5" t="n">
-        <v>6.42</v>
+        <v>4.05</v>
       </c>
       <c r="P5" t="n">
-        <v>2.25</v>
+        <v>1.91</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.15</v>
+        <v>2.89</v>
       </c>
       <c r="R5" t="n">
-        <v>1.41</v>
+        <v>1.47</v>
       </c>
       <c r="S5" t="n">
-        <v>2.69</v>
+        <v>2.43</v>
       </c>
       <c r="T5" t="n">
-        <v>2.92</v>
+        <v>3.22</v>
       </c>
       <c r="U5" t="n">
-        <v>1.38</v>
+        <v>1.28</v>
       </c>
       <c r="V5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="W5" t="n">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="X5" t="n">
-        <v>3.1</v>
+        <v>2.74</v>
       </c>
       <c r="Y5" t="n">
         <v>2.25</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="AA5" t="n">
-        <v>3.28</v>
+        <v>4.05</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.25</v>
+        <v>1.16</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.99</v>
+        <v>1.9</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.68</v>
+        <v>1.79</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
@@ -1123,19 +1123,19 @@
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>1.26</v>
+        <v>1.32</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.12</v>
+        <v>1.3</v>
       </c>
       <c r="AI5" t="n">
-        <v>2.38</v>
+        <v>2.31</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="AK5" s="3" t="n">
-        <v>45930.47916666666</v>
+        <v>45930.45833333334</v>
       </c>
     </row>
     <row r="6">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Botev Plovdiv</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1185,86 +1185,86 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>19</v>
+        <v>4.6</v>
       </c>
       <c r="M6" t="n">
-        <v>8.9</v>
+        <v>3.5</v>
       </c>
       <c r="N6" t="n">
-        <v>1.11</v>
+        <v>1.82</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>6.42</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.3</v>
+        <v>2.25</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.4</v>
+        <v>1.65</v>
       </c>
       <c r="AA6" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG6" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AJ6" t="n">
         <v>1.8</v>
       </c>
-      <c r="AB6" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>0</v>
-      </c>
       <c r="AK6" s="3" t="n">
-        <v>45930.57291666666</v>
+        <v>45930.47916666666</v>
       </c>
     </row>
     <row r="7">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Police</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Ulinzi Stars</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1314,13 +1314,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1353,10 +1353,10 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
         <v>0</v>
@@ -1393,7 +1393,7 @@
         <v>0</v>
       </c>
       <c r="AK7" s="3" t="n">
-        <v>45930.57291666666</v>
+        <v>45930.5</v>
       </c>
     </row>
     <row r="8">
@@ -1402,12 +1402,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Wehen Wiesbaden</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,61 +1443,61 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.68</v>
+        <v>19</v>
       </c>
       <c r="M8" t="n">
-        <v>3.55</v>
+        <v>8.9</v>
       </c>
       <c r="N8" t="n">
-        <v>2.35</v>
+        <v>1.11</v>
       </c>
       <c r="O8" t="n">
-        <v>3.34</v>
+        <v>15</v>
       </c>
       <c r="P8" t="n">
-        <v>2.38</v>
+        <v>3.38</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.6</v>
+        <v>1.38</v>
       </c>
       <c r="R8" t="n">
-        <v>1.3</v>
+        <v>1.17</v>
       </c>
       <c r="S8" t="n">
-        <v>3.2</v>
+        <v>4.33</v>
       </c>
       <c r="T8" t="n">
-        <v>2.38</v>
+        <v>1.9</v>
       </c>
       <c r="U8" t="n">
-        <v>1.5</v>
+        <v>1.88</v>
       </c>
       <c r="V8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="W8" t="n">
-        <v>1.16</v>
+        <v>1.05</v>
       </c>
       <c r="X8" t="n">
-        <v>4.2</v>
+        <v>8</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.65</v>
+        <v>1.29</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.15</v>
+        <v>3.4</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.49</v>
+        <v>1.8</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.42</v>
+        <v>1.94</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.51</v>
+        <v>2.32</v>
       </c>
       <c r="AD8" t="n">
-        <v>2.32</v>
+        <v>1.55</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>1.25</v>
+        <v>1.06</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.4</v>
+        <v>1.01</v>
       </c>
       <c r="AI8" t="n">
         <v>0</v>
@@ -1522,7 +1522,7 @@
         <v>0</v>
       </c>
       <c r="AK8" s="3" t="n">
-        <v>45930.58333333334</v>
+        <v>45930.57291666666</v>
       </c>
     </row>
     <row r="9">
@@ -1531,27 +1531,27 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,61 +1572,61 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.26</v>
+        <v>1.86</v>
       </c>
       <c r="M9" t="n">
-        <v>5.1</v>
+        <v>3.84</v>
       </c>
       <c r="N9" t="n">
-        <v>7.6</v>
+        <v>3.7</v>
       </c>
       <c r="O9" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.47</v>
+        <v>1.7</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.5</v>
+        <v>2.15</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
@@ -1651,7 +1651,7 @@
         <v>0</v>
       </c>
       <c r="AK9" s="3" t="n">
-        <v>45930.58333333334</v>
+        <v>45930.57291666666</v>
       </c>
     </row>
     <row r="10">
@@ -1665,22 +1665,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Saarbrucken</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>MSV Duisburg</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,61 +1701,61 @@
         </is>
       </c>
       <c r="L10" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="M10" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="N10" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="O10" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="P10" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>5.07</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S10" t="n">
+        <v>3.66</v>
+      </c>
+      <c r="T10" t="n">
         <v>2.18</v>
       </c>
-      <c r="M10" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="N10" t="n">
-        <v>3.02</v>
-      </c>
-      <c r="O10" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="P10" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>3.54</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="S10" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="T10" t="n">
-        <v>2.48</v>
-      </c>
       <c r="U10" t="n">
-        <v>1.51</v>
+        <v>1.64</v>
       </c>
       <c r="V10" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="W10" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="X10" t="n">
-        <v>4.05</v>
+        <v>5.6</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.71</v>
+        <v>1.45</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.16</v>
+        <v>2.56</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.59</v>
+        <v>1.92</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.39</v>
+        <v>1.78</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="AD10" t="n">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -1768,10 +1768,10 @@
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>1.3</v>
+        <v>1.19</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.64</v>
+        <v>2.31</v>
       </c>
       <c r="AI10" t="n">
         <v>0</v>
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Erzgebirge Aue</t>
+          <t>Wehen Wiesbaden</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,77 +1830,77 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.93</v>
+        <v>2.68</v>
       </c>
       <c r="M11" t="n">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="N11" t="n">
-        <v>3.28</v>
+        <v>2.35</v>
       </c>
       <c r="O11" t="n">
-        <v>2.5</v>
+        <v>3.34</v>
       </c>
       <c r="P11" t="n">
-        <v>2.17</v>
+        <v>2.38</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.33</v>
+        <v>2.6</v>
       </c>
       <c r="R11" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="S11" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="T11" t="n">
-        <v>2.6</v>
+        <v>2.38</v>
       </c>
       <c r="U11" t="n">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="V11" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="W11" t="n">
-        <v>1.21</v>
+        <v>1.16</v>
       </c>
       <c r="X11" t="n">
-        <v>3.68</v>
+        <v>4.2</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.06</v>
+        <v>2.15</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.95</v>
+        <v>2.49</v>
       </c>
       <c r="AB11" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG11" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AH11" t="n">
         <v>1.4</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AE11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG11" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>1.71</v>
       </c>
       <c r="AI11" t="n">
         <v>0</v>
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Havelse</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Waldhof Mannheim</t>
+          <t>Erzgebirge Aue</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,61 +1959,61 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>3.5</v>
+        <v>1.93</v>
       </c>
       <c r="M12" t="n">
         <v>3.65</v>
       </c>
       <c r="N12" t="n">
-        <v>1.91</v>
+        <v>3.28</v>
       </c>
       <c r="O12" t="n">
-        <v>4.12</v>
+        <v>2.5</v>
       </c>
       <c r="P12" t="n">
-        <v>2.24</v>
+        <v>2.17</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.4</v>
+        <v>3.33</v>
       </c>
       <c r="R12" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="S12" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="T12" t="n">
-        <v>2.44</v>
+        <v>2.6</v>
       </c>
       <c r="U12" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="V12" t="n">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="W12" t="n">
-        <v>1.16</v>
+        <v>1.21</v>
       </c>
       <c r="X12" t="n">
-        <v>4.1</v>
+        <v>3.68</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.65</v>
+        <v>1.73</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.12</v>
+        <v>2.06</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.56</v>
+        <v>2.95</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AD12" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -2026,10 +2026,10 @@
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>1.81</v>
+        <v>1.24</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.24</v>
+        <v>1.71</v>
       </c>
       <c r="AI12" t="n">
         <v>0</v>
@@ -2052,22 +2052,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Hansa Rostock</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,61 +2088,61 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.56</v>
+        <v>2.05</v>
       </c>
       <c r="M13" t="n">
-        <v>4.2</v>
+        <v>3.55</v>
       </c>
       <c r="N13" t="n">
-        <v>4.2</v>
+        <v>3.15</v>
       </c>
       <c r="O13" t="n">
-        <v>1.95</v>
+        <v>2.44</v>
       </c>
       <c r="P13" t="n">
-        <v>2.5</v>
+        <v>2.18</v>
       </c>
       <c r="Q13" t="n">
-        <v>5.07</v>
+        <v>3.78</v>
       </c>
       <c r="R13" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="S13" t="n">
-        <v>3.66</v>
+        <v>3.3</v>
       </c>
       <c r="T13" t="n">
-        <v>2.18</v>
+        <v>2.52</v>
       </c>
       <c r="U13" t="n">
-        <v>1.64</v>
+        <v>1.49</v>
       </c>
       <c r="V13" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="W13" t="n">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="X13" t="n">
-        <v>5.6</v>
+        <v>4.19</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.45</v>
+        <v>1.7</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.56</v>
+        <v>1.97</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.92</v>
+        <v>2.75</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.78</v>
+        <v>1.37</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="AD13" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
@@ -2155,10 +2155,10 @@
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>1.19</v>
+        <v>1.24</v>
       </c>
       <c r="AH13" t="n">
-        <v>2.31</v>
+        <v>1.66</v>
       </c>
       <c r="AI13" t="n">
         <v>0</v>
@@ -2181,22 +2181,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Hansa Rostock</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,61 +2217,61 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.05</v>
+        <v>1.26</v>
       </c>
       <c r="M14" t="n">
-        <v>3.55</v>
+        <v>5.1</v>
       </c>
       <c r="N14" t="n">
-        <v>3.15</v>
+        <v>7.6</v>
       </c>
       <c r="O14" t="n">
-        <v>2.44</v>
+        <v>1.83</v>
       </c>
       <c r="P14" t="n">
-        <v>2.18</v>
+        <v>2.45</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.78</v>
+        <v>5.7</v>
       </c>
       <c r="R14" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="S14" t="n">
-        <v>3.3</v>
+        <v>3.28</v>
       </c>
       <c r="T14" t="n">
-        <v>2.52</v>
+        <v>2.2</v>
       </c>
       <c r="U14" t="n">
-        <v>1.49</v>
+        <v>1.62</v>
       </c>
       <c r="V14" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="W14" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="X14" t="n">
-        <v>4.19</v>
+        <v>4.5</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.7</v>
+        <v>1.47</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.97</v>
+        <v>2.5</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.75</v>
+        <v>2.17</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.37</v>
+        <v>1.62</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.58</v>
+        <v>1.84</v>
       </c>
       <c r="AD14" t="n">
-        <v>2.32</v>
+        <v>1.86</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
@@ -2284,10 +2284,10 @@
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>1.24</v>
+        <v>1.13</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.66</v>
+        <v>2.82</v>
       </c>
       <c r="AI14" t="n">
         <v>0</v>
@@ -2305,12 +2305,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Havelse</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Waldhof Mannheim</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,61 +2346,61 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.1</v>
+        <v>3.5</v>
       </c>
       <c r="M15" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="N15" t="n">
-        <v>2.87</v>
+        <v>1.91</v>
       </c>
       <c r="O15" t="n">
-        <v>2.65</v>
+        <v>4.12</v>
       </c>
       <c r="P15" t="n">
-        <v>2.51</v>
+        <v>2.24</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.25</v>
+        <v>2.4</v>
       </c>
       <c r="R15" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="S15" t="n">
-        <v>3.45</v>
+        <v>3.2</v>
       </c>
       <c r="T15" t="n">
-        <v>2.21</v>
+        <v>2.44</v>
       </c>
       <c r="U15" t="n">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="V15" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="W15" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="X15" t="n">
-        <v>4.75</v>
+        <v>4.1</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.53</v>
+        <v>1.65</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.39</v>
+        <v>2.12</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.28</v>
+        <v>2.56</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.54</v>
+        <v>1.44</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.45</v>
+        <v>1.57</v>
       </c>
       <c r="AD15" t="n">
-        <v>2.59</v>
+        <v>2.25</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
@@ -2413,10 +2413,10 @@
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>1.25</v>
+        <v>1.81</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.68</v>
+        <v>1.24</v>
       </c>
       <c r="AI15" t="n">
         <v>0</v>
@@ -2425,7 +2425,7 @@
         <v>0</v>
       </c>
       <c r="AK15" s="3" t="n">
-        <v>45930.625</v>
+        <v>45930.58333333334</v>
       </c>
     </row>
     <row r="16">
@@ -2434,12 +2434,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Saarbrucken</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>MSV Duisburg</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,78 +2475,78 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.7</v>
+        <v>2.18</v>
       </c>
       <c r="M16" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="N16" t="n">
-        <v>3.72</v>
+        <v>3.02</v>
       </c>
       <c r="O16" t="n">
-        <v>2.32</v>
+        <v>2.71</v>
       </c>
       <c r="P16" t="n">
-        <v>2.18</v>
+        <v>2.14</v>
       </c>
       <c r="Q16" t="n">
         <v>3.54</v>
       </c>
       <c r="R16" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="S16" t="n">
-        <v>3.28</v>
+        <v>3.1</v>
       </c>
       <c r="T16" t="n">
-        <v>2.47</v>
+        <v>2.48</v>
       </c>
       <c r="U16" t="n">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="V16" t="n">
         <v>1.04</v>
       </c>
       <c r="W16" t="n">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="X16" t="n">
-        <v>4.2</v>
+        <v>4.05</v>
       </c>
       <c r="Y16" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AE16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG16" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AH16" t="n">
         <v>1.64</v>
       </c>
-      <c r="Z16" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AE16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG16" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>1.95</v>
-      </c>
       <c r="AI16" t="n">
         <v>0</v>
       </c>
@@ -2554,7 +2554,7 @@
         <v>0</v>
       </c>
       <c r="AK16" s="3" t="n">
-        <v>45930.625</v>
+        <v>45930.58333333334</v>
       </c>
     </row>
     <row r="17">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2600,65 +2600,65 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.73</v>
+        <v>1.53</v>
       </c>
       <c r="M17" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="N17" t="n">
-        <v>2.18</v>
+        <v>7</v>
       </c>
       <c r="O17" t="n">
-        <v>3.5</v>
+        <v>2.15</v>
       </c>
       <c r="P17" t="n">
-        <v>2.47</v>
+        <v>2.05</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.55</v>
+        <v>6.5</v>
       </c>
       <c r="R17" t="n">
-        <v>1.28</v>
+        <v>1.5</v>
       </c>
       <c r="S17" t="n">
-        <v>3.34</v>
+        <v>2.5</v>
       </c>
       <c r="T17" t="n">
-        <v>2.32</v>
+        <v>3.48</v>
       </c>
       <c r="U17" t="n">
-        <v>1.54</v>
+        <v>1.3</v>
       </c>
       <c r="V17" t="n">
-        <v>1.02</v>
+        <v>1.1</v>
       </c>
       <c r="W17" t="n">
-        <v>1.14</v>
+        <v>1.45</v>
       </c>
       <c r="X17" t="n">
-        <v>4.5</v>
+        <v>2.45</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.57</v>
+        <v>2.62</v>
       </c>
       <c r="Z17" t="n">
-        <v>2.35</v>
+        <v>1.48</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.36</v>
+        <v>4.75</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.52</v>
+        <v>1.15</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.52</v>
+        <v>2.54</v>
       </c>
       <c r="AD17" t="n">
-        <v>2.45</v>
+        <v>1.42</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
@@ -2671,19 +2671,19 @@
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>1.67</v>
+        <v>1.3</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.37</v>
+        <v>2.4</v>
       </c>
       <c r="AI17" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AK17" s="3" t="n">
-        <v>45930.625</v>
+        <v>45930.60416666666</v>
       </c>
     </row>
     <row r="18">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,61 +2733,61 @@
         </is>
       </c>
       <c r="L18" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="M18" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="N18" t="n">
         <v>3.7</v>
       </c>
-      <c r="M18" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="N18" t="n">
-        <v>2</v>
-      </c>
       <c r="O18" t="n">
-        <v>3.7</v>
+        <v>2.37</v>
       </c>
       <c r="P18" t="n">
-        <v>2.38</v>
+        <v>2.18</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.61</v>
+        <v>3.54</v>
       </c>
       <c r="R18" t="n">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="S18" t="n">
-        <v>3.58</v>
+        <v>3.28</v>
       </c>
       <c r="T18" t="n">
-        <v>2.2</v>
+        <v>2.47</v>
       </c>
       <c r="U18" t="n">
-        <v>1.61</v>
+        <v>1.48</v>
       </c>
       <c r="V18" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="W18" t="n">
-        <v>1.11</v>
+        <v>1.21</v>
       </c>
       <c r="X18" t="n">
-        <v>4.9</v>
+        <v>4.31</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.46</v>
+        <v>1.68</v>
       </c>
       <c r="Z18" t="n">
-        <v>2.39</v>
+        <v>2.19</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.28</v>
+        <v>2.68</v>
       </c>
       <c r="AB18" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AC18" t="n">
         <v>1.6</v>
       </c>
-      <c r="AC18" t="n">
-        <v>1.46</v>
-      </c>
       <c r="AD18" t="n">
-        <v>2.5</v>
+        <v>2.22</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
@@ -2800,10 +2800,10 @@
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>1.79</v>
+        <v>1.25</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.27</v>
+        <v>1.92</v>
       </c>
       <c r="AI18" t="n">
         <v>0</v>
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,77 +2862,77 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="O19" t="n">
-        <v>1.91</v>
+        <v>2.58</v>
       </c>
       <c r="P19" t="n">
-        <v>2.63</v>
+        <v>2.51</v>
       </c>
       <c r="Q19" t="n">
-        <v>5.34</v>
+        <v>3.25</v>
       </c>
       <c r="R19" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S19" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X19" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="AE19" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF19" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG19" t="n">
         <v>1.22</v>
       </c>
-      <c r="S19" t="n">
-        <v>3.66</v>
-      </c>
-      <c r="T19" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="U19" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="V19" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="X19" t="n">
-        <v>4.98</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="AE19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG19" t="n">
-        <v>1.12</v>
-      </c>
       <c r="AH19" t="n">
-        <v>2.61</v>
+        <v>1.65</v>
       </c>
       <c r="AI19" t="n">
         <v>0</v>
@@ -2950,12 +2950,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,61 +2991,61 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>4.2</v>
+        <v>1.93</v>
       </c>
       <c r="P20" t="n">
-        <v>2.16</v>
+        <v>2.53</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.44</v>
+        <v>5.48</v>
       </c>
       <c r="R20" t="n">
-        <v>1.34</v>
+        <v>1.22</v>
       </c>
       <c r="S20" t="n">
-        <v>2.98</v>
+        <v>3.66</v>
       </c>
       <c r="T20" t="n">
-        <v>2.43</v>
+        <v>2.15</v>
       </c>
       <c r="U20" t="n">
-        <v>1.48</v>
+        <v>1.64</v>
       </c>
       <c r="V20" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="W20" t="n">
-        <v>1.21</v>
+        <v>1.11</v>
       </c>
       <c r="X20" t="n">
-        <v>3.5</v>
+        <v>4.98</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.73</v>
+        <v>1.43</v>
       </c>
       <c r="Z20" t="n">
-        <v>2</v>
+        <v>2.49</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.92</v>
+        <v>2.27</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.31</v>
+        <v>1.64</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AD20" t="n">
-        <v>2.03</v>
+        <v>2.22</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
@@ -3058,10 +3058,10 @@
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>1.24</v>
+        <v>1.18</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.23</v>
+        <v>2.61</v>
       </c>
       <c r="AI20" t="n">
         <v>0</v>
@@ -3070,7 +3070,7 @@
         <v>0</v>
       </c>
       <c r="AK20" s="3" t="n">
-        <v>45930.64583333334</v>
+        <v>45930.625</v>
       </c>
     </row>
     <row r="21">
@@ -3079,12 +3079,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,61 +3120,61 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.59</v>
+        <v>3</v>
       </c>
       <c r="M21" t="n">
-        <v>3.01</v>
+        <v>3.5</v>
       </c>
       <c r="N21" t="n">
-        <v>2.84</v>
+        <v>2.18</v>
       </c>
       <c r="O21" t="n">
-        <v>2.97</v>
+        <v>3.35</v>
       </c>
       <c r="P21" t="n">
-        <v>1.91</v>
+        <v>2.47</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.4</v>
+        <v>2.66</v>
       </c>
       <c r="R21" t="n">
-        <v>1.45</v>
+        <v>1.28</v>
       </c>
       <c r="S21" t="n">
-        <v>2.48</v>
+        <v>3.34</v>
       </c>
       <c r="T21" t="n">
-        <v>3.14</v>
+        <v>2.32</v>
       </c>
       <c r="U21" t="n">
-        <v>1.29</v>
+        <v>1.54</v>
       </c>
       <c r="V21" t="n">
         <v>1.03</v>
       </c>
       <c r="W21" t="n">
-        <v>1.4</v>
+        <v>1.14</v>
       </c>
       <c r="X21" t="n">
-        <v>2.92</v>
+        <v>4.5</v>
       </c>
       <c r="Y21" t="n">
-        <v>2.2</v>
+        <v>1.54</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.67</v>
+        <v>2.3</v>
       </c>
       <c r="AA21" t="n">
-        <v>4</v>
+        <v>2.36</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.18</v>
+        <v>1.47</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.01</v>
+        <v>1.5</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.82</v>
+        <v>2.45</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
@@ -3187,10 +3187,10 @@
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>1.31</v>
+        <v>1.26</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.48</v>
+        <v>1.37</v>
       </c>
       <c r="AI21" t="n">
         <v>0</v>
@@ -3199,7 +3199,7 @@
         <v>0</v>
       </c>
       <c r="AK21" s="3" t="n">
-        <v>45930.64583333334</v>
+        <v>45930.625</v>
       </c>
     </row>
     <row r="22">
@@ -3208,12 +3208,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,77 +3249,77 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.98</v>
+        <v>3.05</v>
       </c>
       <c r="M22" t="n">
-        <v>3.47</v>
+        <v>3.7</v>
       </c>
       <c r="N22" t="n">
-        <v>3.62</v>
+        <v>2.08</v>
       </c>
       <c r="O22" t="n">
-        <v>2.71</v>
+        <v>3.1</v>
       </c>
       <c r="P22" t="n">
-        <v>2.1</v>
+        <v>2.38</v>
       </c>
       <c r="Q22" t="n">
-        <v>4.04</v>
+        <v>2.4</v>
       </c>
       <c r="R22" t="n">
-        <v>1.35</v>
+        <v>1.23</v>
       </c>
       <c r="S22" t="n">
-        <v>2.84</v>
+        <v>3.58</v>
       </c>
       <c r="T22" t="n">
-        <v>2.71</v>
+        <v>2.2</v>
       </c>
       <c r="U22" t="n">
-        <v>1.41</v>
+        <v>1.61</v>
       </c>
       <c r="V22" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="W22" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="X22" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AE22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG22" t="n">
         <v>1.24</v>
       </c>
-      <c r="X22" t="n">
-        <v>3.56</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>2</v>
-      </c>
-      <c r="AE22" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF22" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG22" t="n">
-        <v>1.31</v>
-      </c>
       <c r="AH22" t="n">
-        <v>1.73</v>
+        <v>1.27</v>
       </c>
       <c r="AI22" t="n">
         <v>0</v>
@@ -3328,7 +3328,7 @@
         <v>0</v>
       </c>
       <c r="AK22" s="3" t="n">
-        <v>45930.64583333334</v>
+        <v>45930.625</v>
       </c>
     </row>
     <row r="23">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Calcio Padova</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,61 +3378,61 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.39</v>
+        <v>2.59</v>
       </c>
       <c r="M23" t="n">
-        <v>2.95</v>
+        <v>3.01</v>
       </c>
       <c r="N23" t="n">
-        <v>3.2</v>
+        <v>2.84</v>
       </c>
       <c r="O23" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="P23" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="S23" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="T23" t="n">
         <v>3.14</v>
       </c>
-      <c r="P23" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="R23" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="S23" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="T23" t="n">
-        <v>3.34</v>
-      </c>
       <c r="U23" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="V23" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="W23" t="n">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="X23" t="n">
-        <v>2.5</v>
+        <v>2.92</v>
       </c>
       <c r="Y23" t="n">
         <v>2.2</v>
       </c>
       <c r="Z23" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AA23" t="n">
-        <v>4.45</v>
+        <v>4</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.03</v>
+        <v>2.01</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.72</v>
+        <v>1.82</v>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
@@ -3448,7 +3448,7 @@
         <v>1.31</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.61</v>
+        <v>1.48</v>
       </c>
       <c r="AI23" t="n">
         <v>0</v>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,61 +3507,61 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>3.41</v>
+        <v>3.25</v>
       </c>
       <c r="M24" t="n">
-        <v>3.26</v>
+        <v>3.6</v>
       </c>
       <c r="N24" t="n">
-        <v>2.13</v>
+        <v>2.02</v>
       </c>
       <c r="O24" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="P24" t="n">
-        <v>1.95</v>
+        <v>2.16</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.16</v>
+        <v>2.44</v>
       </c>
       <c r="R24" t="n">
-        <v>1.51</v>
+        <v>1.34</v>
       </c>
       <c r="S24" t="n">
-        <v>2.57</v>
+        <v>2.98</v>
       </c>
       <c r="T24" t="n">
-        <v>3.28</v>
+        <v>2.43</v>
       </c>
       <c r="U24" t="n">
-        <v>1.27</v>
+        <v>1.48</v>
       </c>
       <c r="V24" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="W24" t="n">
-        <v>1.45</v>
+        <v>1.21</v>
       </c>
       <c r="X24" t="n">
-        <v>2.63</v>
+        <v>3.5</v>
       </c>
       <c r="Y24" t="n">
-        <v>2.07</v>
+        <v>1.73</v>
       </c>
       <c r="Z24" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AA24" t="n">
-        <v>4.4</v>
+        <v>2.92</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.16</v>
+        <v>1.31</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.96</v>
+        <v>1.67</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.77</v>
+        <v>2.03</v>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
@@ -3574,10 +3574,10 @@
         </is>
       </c>
       <c r="AG24" t="n">
-        <v>1.36</v>
+        <v>1.24</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.38</v>
+        <v>1.23</v>
       </c>
       <c r="AI24" t="n">
         <v>0</v>
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mantova</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,61 +3636,61 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.79</v>
+        <v>1.98</v>
       </c>
       <c r="M25" t="n">
-        <v>3.61</v>
+        <v>3.47</v>
       </c>
       <c r="N25" t="n">
-        <v>4.3</v>
+        <v>3.62</v>
       </c>
       <c r="O25" t="n">
-        <v>2.54</v>
+        <v>2.71</v>
       </c>
       <c r="P25" t="n">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="Q25" t="n">
-        <v>4.2</v>
+        <v>4.04</v>
       </c>
       <c r="R25" t="n">
-        <v>1.42</v>
+        <v>1.35</v>
       </c>
       <c r="S25" t="n">
-        <v>2.57</v>
+        <v>2.84</v>
       </c>
       <c r="T25" t="n">
-        <v>2.93</v>
+        <v>2.71</v>
       </c>
       <c r="U25" t="n">
-        <v>1.33</v>
+        <v>1.41</v>
       </c>
       <c r="V25" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="W25" t="n">
-        <v>1.35</v>
+        <v>1.24</v>
       </c>
       <c r="X25" t="n">
-        <v>3.18</v>
+        <v>3.56</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.98</v>
+        <v>1.87</v>
       </c>
       <c r="Z25" t="n">
-        <v>1.77</v>
+        <v>1.87</v>
       </c>
       <c r="AA25" t="n">
-        <v>3.55</v>
+        <v>3.12</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
@@ -3703,10 +3703,10 @@
         </is>
       </c>
       <c r="AG25" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.86</v>
+        <v>1.73</v>
       </c>
       <c r="AI25" t="n">
         <v>0</v>
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Calcio Padova</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,61 +3765,61 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.02</v>
+        <v>2.39</v>
       </c>
       <c r="M26" t="n">
-        <v>3.23</v>
+        <v>2.95</v>
       </c>
       <c r="N26" t="n">
-        <v>3.78</v>
+        <v>3.2</v>
       </c>
       <c r="O26" t="n">
-        <v>2.86</v>
+        <v>3.14</v>
       </c>
       <c r="P26" t="n">
-        <v>1.99</v>
+        <v>2.01</v>
       </c>
       <c r="Q26" t="n">
-        <v>4.3</v>
+        <v>4.15</v>
       </c>
       <c r="R26" t="n">
-        <v>1.46</v>
+        <v>1.53</v>
       </c>
       <c r="S26" t="n">
-        <v>2.45</v>
+        <v>2.49</v>
       </c>
       <c r="T26" t="n">
-        <v>3.2</v>
+        <v>3.34</v>
       </c>
       <c r="U26" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="V26" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="W26" t="n">
-        <v>1.38</v>
+        <v>1.47</v>
       </c>
       <c r="X26" t="n">
-        <v>2.9</v>
+        <v>2.5</v>
       </c>
       <c r="Y26" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="Z26" t="n">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AA26" t="n">
-        <v>3.85</v>
+        <v>4.45</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="AC26" t="n">
-        <v>2.06</v>
+        <v>2.03</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
@@ -3832,10 +3832,10 @@
         </is>
       </c>
       <c r="AG26" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.72</v>
+        <v>1.61</v>
       </c>
       <c r="AI26" t="n">
         <v>0</v>
@@ -3853,12 +3853,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,61 +3894,61 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.19</v>
+        <v>2.02</v>
       </c>
       <c r="M27" t="n">
-        <v>3.47</v>
+        <v>3.23</v>
       </c>
       <c r="N27" t="n">
-        <v>3.08</v>
+        <v>3.78</v>
       </c>
       <c r="O27" t="n">
-        <v>2.65</v>
+        <v>2.86</v>
       </c>
       <c r="P27" t="n">
-        <v>2.07</v>
+        <v>1.99</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.75</v>
+        <v>4.3</v>
       </c>
       <c r="R27" t="n">
-        <v>1.39</v>
+        <v>1.46</v>
       </c>
       <c r="S27" t="n">
-        <v>2.67</v>
+        <v>2.45</v>
       </c>
       <c r="T27" t="n">
-        <v>3.08</v>
+        <v>3.2</v>
       </c>
       <c r="U27" t="n">
-        <v>1.34</v>
+        <v>1.28</v>
       </c>
       <c r="V27" t="n">
-        <v>1</v>
+        <v>1.08</v>
       </c>
       <c r="W27" t="n">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
       <c r="X27" t="n">
-        <v>3.08</v>
+        <v>2.9</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.98</v>
+        <v>2.18</v>
       </c>
       <c r="Z27" t="n">
-        <v>1.77</v>
+        <v>1.7</v>
       </c>
       <c r="AA27" t="n">
-        <v>3.64</v>
+        <v>3.85</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.26</v>
+        <v>1.18</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.81</v>
+        <v>2.06</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.91</v>
+        <v>1.74</v>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
@@ -3961,10 +3961,10 @@
         </is>
       </c>
       <c r="AG27" t="n">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.65</v>
+        <v>1.72</v>
       </c>
       <c r="AI27" t="n">
         <v>0</v>
@@ -3973,7 +3973,7 @@
         <v>0</v>
       </c>
       <c r="AK27" s="3" t="n">
-        <v>45930.65625</v>
+        <v>45930.64583333334</v>
       </c>
     </row>
     <row r="28">
@@ -3982,12 +3982,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Mantova</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,62 +4023,62 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.65</v>
+        <v>1.79</v>
       </c>
       <c r="M28" t="n">
-        <v>3.82</v>
+        <v>3.61</v>
       </c>
       <c r="N28" t="n">
-        <v>4.9</v>
+        <v>4.3</v>
       </c>
       <c r="O28" t="n">
-        <v>2.27</v>
+        <v>2.54</v>
       </c>
       <c r="P28" t="n">
-        <v>2.17</v>
+        <v>2.06</v>
       </c>
       <c r="Q28" t="n">
-        <v>4.65</v>
+        <v>4.2</v>
       </c>
       <c r="R28" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="S28" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V28" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="W28" t="n">
         <v>1.35</v>
       </c>
-      <c r="S28" t="n">
-        <v>3.09</v>
-      </c>
-      <c r="T28" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="U28" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V28" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W28" t="n">
-        <v>1.28</v>
-      </c>
       <c r="X28" t="n">
-        <v>3.48</v>
+        <v>3.18</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.83</v>
+        <v>1.98</v>
       </c>
       <c r="Z28" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AD28" t="n">
         <v>1.91</v>
       </c>
-      <c r="AA28" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>1.9</v>
-      </c>
       <c r="AE28" t="inlineStr">
         <is>
           <t>[]</t>
@@ -4090,10 +4090,10 @@
         </is>
       </c>
       <c r="AG28" t="n">
-        <v>1.17</v>
+        <v>1.32</v>
       </c>
       <c r="AH28" t="n">
-        <v>2.05</v>
+        <v>1.86</v>
       </c>
       <c r="AI28" t="n">
         <v>0</v>
@@ -4102,7 +4102,7 @@
         <v>0</v>
       </c>
       <c r="AK28" s="3" t="n">
-        <v>45930.65625</v>
+        <v>45930.64583333334</v>
       </c>
     </row>
     <row r="29">
@@ -4111,12 +4111,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,78 +4152,78 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.36</v>
+        <v>3.41</v>
       </c>
       <c r="M29" t="n">
-        <v>3.38</v>
+        <v>3.26</v>
       </c>
       <c r="N29" t="n">
-        <v>2.86</v>
+        <v>2.13</v>
       </c>
       <c r="O29" t="n">
-        <v>3.12</v>
+        <v>3.9</v>
       </c>
       <c r="P29" t="n">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.25</v>
+        <v>3.16</v>
       </c>
       <c r="R29" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="S29" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="T29" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="V29" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W29" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="X29" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AE29" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF29" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG29" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AH29" t="n">
         <v>1.38</v>
       </c>
-      <c r="S29" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="T29" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="U29" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="V29" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W29" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="X29" t="n">
-        <v>3.36</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AE29" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF29" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG29" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AH29" t="n">
-        <v>1.51</v>
-      </c>
       <c r="AI29" t="n">
         <v>0</v>
       </c>
@@ -4231,7 +4231,7 @@
         <v>0</v>
       </c>
       <c r="AK29" s="3" t="n">
-        <v>45930.65625</v>
+        <v>45930.64583333334</v>
       </c>
     </row>
     <row r="30">
@@ -4245,7 +4245,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,77 +4281,77 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="M30" t="n">
-        <v>4.2</v>
+        <v>4.75</v>
       </c>
       <c r="N30" t="n">
-        <v>5.9</v>
+        <v>8</v>
       </c>
       <c r="O30" t="n">
-        <v>2.01</v>
+        <v>1.94</v>
       </c>
       <c r="P30" t="n">
         <v>2.35</v>
       </c>
       <c r="Q30" t="n">
-        <v>6.05</v>
+        <v>6.5</v>
       </c>
       <c r="R30" t="n">
         <v>1.3</v>
       </c>
       <c r="S30" t="n">
-        <v>3.14</v>
+        <v>2.93</v>
       </c>
       <c r="T30" t="n">
-        <v>2.51</v>
+        <v>2.64</v>
       </c>
       <c r="U30" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="V30" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W30" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="X30" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AE30" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF30" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG30" t="n">
         <v>1.19</v>
       </c>
-      <c r="X30" t="n">
-        <v>3.98</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AC30" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AD30" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AE30" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF30" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG30" t="n">
-        <v>1.21</v>
-      </c>
       <c r="AH30" t="n">
-        <v>2.61</v>
+        <v>2.99</v>
       </c>
       <c r="AI30" t="n">
         <v>0</v>
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,61 +4410,61 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.36</v>
+        <v>2.49</v>
       </c>
       <c r="M31" t="n">
-        <v>4.75</v>
+        <v>3.29</v>
       </c>
       <c r="N31" t="n">
-        <v>8</v>
+        <v>2.74</v>
       </c>
       <c r="O31" t="n">
-        <v>1.94</v>
+        <v>3.18</v>
       </c>
       <c r="P31" t="n">
-        <v>2.35</v>
+        <v>2.02</v>
       </c>
       <c r="Q31" t="n">
-        <v>6.5</v>
+        <v>3.4</v>
       </c>
       <c r="R31" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="S31" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="T31" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="U31" t="n">
         <v>1.3</v>
       </c>
-      <c r="S31" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="T31" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="U31" t="n">
-        <v>1.4</v>
-      </c>
       <c r="V31" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W31" t="n">
-        <v>1.28</v>
+        <v>1.38</v>
       </c>
       <c r="X31" t="n">
-        <v>3.48</v>
+        <v>2.83</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.85</v>
+        <v>2.2</v>
       </c>
       <c r="Z31" t="n">
-        <v>1.89</v>
+        <v>1.68</v>
       </c>
       <c r="AA31" t="n">
-        <v>3.02</v>
+        <v>4.2</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.38</v>
+        <v>1.19</v>
       </c>
       <c r="AC31" t="n">
-        <v>2.1</v>
+        <v>1.92</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.7</v>
+        <v>1.86</v>
       </c>
       <c r="AE31" t="inlineStr">
         <is>
@@ -4477,10 +4477,10 @@
         </is>
       </c>
       <c r="AG31" t="n">
-        <v>1.19</v>
+        <v>1.34</v>
       </c>
       <c r="AH31" t="n">
-        <v>2.99</v>
+        <v>1.52</v>
       </c>
       <c r="AI31" t="n">
         <v>0</v>
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,61 +4539,61 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>3.2</v>
+        <v>2.19</v>
       </c>
       <c r="M32" t="n">
-        <v>3.3</v>
+        <v>3.47</v>
       </c>
       <c r="N32" t="n">
-        <v>2.2</v>
+        <v>3.08</v>
       </c>
       <c r="O32" t="n">
-        <v>3.62</v>
+        <v>2.65</v>
       </c>
       <c r="P32" t="n">
-        <v>2.11</v>
+        <v>2.07</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.98</v>
+        <v>3.75</v>
       </c>
       <c r="R32" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="S32" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="T32" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="V32" t="n">
+        <v>1</v>
+      </c>
+      <c r="W32" t="n">
         <v>1.32</v>
       </c>
-      <c r="S32" t="n">
-        <v>3.09</v>
-      </c>
-      <c r="T32" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="U32" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="V32" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W32" t="n">
-        <v>1.24</v>
-      </c>
       <c r="X32" t="n">
-        <v>3.48</v>
+        <v>3.08</v>
       </c>
       <c r="Y32" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="Z32" t="n">
         <v>1.77</v>
       </c>
-      <c r="Z32" t="n">
-        <v>1.98</v>
-      </c>
       <c r="AA32" t="n">
-        <v>3.08</v>
+        <v>3.64</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AC32" t="n">
-        <v>1.67</v>
+        <v>1.81</v>
       </c>
       <c r="AD32" t="n">
-        <v>2.18</v>
+        <v>1.91</v>
       </c>
       <c r="AE32" t="inlineStr">
         <is>
@@ -4606,10 +4606,10 @@
         </is>
       </c>
       <c r="AG32" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.41</v>
+        <v>1.65</v>
       </c>
       <c r="AI32" t="n">
         <v>0</v>
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,61 +4668,61 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.9</v>
+        <v>2.36</v>
       </c>
       <c r="M33" t="n">
-        <v>3.4</v>
+        <v>3.38</v>
       </c>
       <c r="N33" t="n">
-        <v>4</v>
+        <v>2.86</v>
       </c>
       <c r="O33" t="n">
-        <v>2.57</v>
+        <v>3.12</v>
       </c>
       <c r="P33" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="Q33" t="n">
-        <v>4.65</v>
+        <v>3.25</v>
       </c>
       <c r="R33" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="S33" t="n">
-        <v>2.86</v>
+        <v>2.75</v>
       </c>
       <c r="T33" t="n">
-        <v>2.93</v>
+        <v>2.6</v>
       </c>
       <c r="U33" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="V33" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="W33" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="X33" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AB33" t="n">
         <v>1.28</v>
       </c>
-      <c r="X33" t="n">
-        <v>3.16</v>
-      </c>
-      <c r="Y33" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="Z33" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AA33" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AB33" t="n">
-        <v>1.24</v>
-      </c>
       <c r="AC33" t="n">
-        <v>1.87</v>
+        <v>1.79</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.93</v>
+        <v>2.02</v>
       </c>
       <c r="AE33" t="inlineStr">
         <is>
@@ -4735,10 +4735,10 @@
         </is>
       </c>
       <c r="AG33" t="n">
-        <v>1.23</v>
+        <v>1.32</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.86</v>
+        <v>1.51</v>
       </c>
       <c r="AI33" t="n">
         <v>0</v>
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,61 +4926,61 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.49</v>
+        <v>3.2</v>
       </c>
       <c r="M35" t="n">
-        <v>3.29</v>
+        <v>3.3</v>
       </c>
       <c r="N35" t="n">
-        <v>2.74</v>
+        <v>2.2</v>
       </c>
       <c r="O35" t="n">
-        <v>3.18</v>
+        <v>3.62</v>
       </c>
       <c r="P35" t="n">
-        <v>2.02</v>
+        <v>2.11</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.4</v>
+        <v>2.98</v>
       </c>
       <c r="R35" t="n">
-        <v>1.43</v>
+        <v>1.32</v>
       </c>
       <c r="S35" t="n">
-        <v>2.54</v>
+        <v>3.09</v>
       </c>
       <c r="T35" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="V35" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W35" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="X35" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AA35" t="n">
         <v>3.08</v>
       </c>
-      <c r="U35" t="n">
+      <c r="AB35" t="n">
         <v>1.3</v>
       </c>
-      <c r="V35" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W35" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="X35" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="Y35" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Z35" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AA35" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AB35" t="n">
-        <v>1.19</v>
-      </c>
       <c r="AC35" t="n">
-        <v>1.92</v>
+        <v>1.67</v>
       </c>
       <c r="AD35" t="n">
-        <v>1.86</v>
+        <v>2.18</v>
       </c>
       <c r="AE35" t="inlineStr">
         <is>
@@ -4993,10 +4993,10 @@
         </is>
       </c>
       <c r="AG35" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.52</v>
+        <v>1.41</v>
       </c>
       <c r="AI35" t="n">
         <v>0</v>
@@ -5014,7 +5014,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,78 +5055,78 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.4</v>
+        <v>1.9</v>
       </c>
       <c r="M36" t="n">
-        <v>3.39</v>
+        <v>3.4</v>
       </c>
       <c r="N36" t="n">
-        <v>2.79</v>
+        <v>4</v>
       </c>
       <c r="O36" t="n">
-        <v>3.34</v>
+        <v>2.57</v>
       </c>
       <c r="P36" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="R36" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S36" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="T36" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="U36" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V36" t="n">
+        <v>1</v>
+      </c>
+      <c r="W36" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="X36" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AE36" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF36" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG36" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AH36" t="n">
         <v>1.86</v>
       </c>
-      <c r="Q36" t="n">
-        <v>3.68</v>
-      </c>
-      <c r="R36" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="S36" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="T36" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="U36" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="V36" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="W36" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="X36" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Y36" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="Z36" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AA36" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AB36" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AC36" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AD36" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AE36" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF36" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG36" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AH36" t="n">
-        <v>1.49</v>
-      </c>
       <c r="AI36" t="n">
         <v>0</v>
       </c>
@@ -5134,7 +5134,7 @@
         <v>0</v>
       </c>
       <c r="AK36" s="3" t="n">
-        <v>45930.66666666666</v>
+        <v>45930.65625</v>
       </c>
     </row>
     <row r="37">
@@ -5143,12 +5143,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,61 +5184,61 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="M37" t="n">
-        <v>4.1</v>
+        <v>3.82</v>
       </c>
       <c r="N37" t="n">
         <v>4.9</v>
       </c>
       <c r="O37" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="R37" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S37" t="n">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="T37" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U37" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V37" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W37" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="X37" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.68</v>
+        <v>1.83</v>
       </c>
       <c r="Z37" t="n">
-        <v>2.18</v>
+        <v>1.91</v>
       </c>
       <c r="AA37" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="AB37" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AC37" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AD37" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AE37" t="inlineStr">
         <is>
@@ -5251,10 +5251,10 @@
         </is>
       </c>
       <c r="AG37" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AH37" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AI37" t="n">
         <v>0</v>
@@ -5263,7 +5263,7 @@
         <v>0</v>
       </c>
       <c r="AK37" s="3" t="n">
-        <v>45930.66666666666</v>
+        <v>45930.65625</v>
       </c>
     </row>
     <row r="38">
@@ -5272,12 +5272,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,77 +5313,77 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>4.3</v>
+        <v>1.4</v>
       </c>
       <c r="M38" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="N38" t="n">
-        <v>1.64</v>
+        <v>5.9</v>
       </c>
       <c r="O38" t="n">
-        <v>3.94</v>
+        <v>2.01</v>
       </c>
       <c r="P38" t="n">
-        <v>2.72</v>
+        <v>2.35</v>
       </c>
       <c r="Q38" t="n">
-        <v>2.15</v>
+        <v>6.05</v>
       </c>
       <c r="R38" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S38" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="T38" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V38" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W38" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="X38" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AE38" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF38" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG38" t="n">
         <v>1.21</v>
       </c>
-      <c r="S38" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="T38" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="U38" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="V38" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W38" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="X38" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="Y38" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="Z38" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="AA38" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AB38" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AC38" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AD38" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="AE38" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF38" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG38" t="n">
-        <v>1.23</v>
-      </c>
       <c r="AH38" t="n">
-        <v>1.23</v>
+        <v>2.61</v>
       </c>
       <c r="AI38" t="n">
         <v>0</v>
@@ -5392,7 +5392,7 @@
         <v>0</v>
       </c>
       <c r="AK38" s="3" t="n">
-        <v>45930.66666666666</v>
+        <v>45930.65625</v>
       </c>
     </row>
     <row r="39">
@@ -5451,40 +5451,40 @@
         <v>1.15</v>
       </c>
       <c r="O39" t="n">
-        <v>11.7</v>
+        <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="S39" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="T39" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="U39" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="V39" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W39" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X39" t="n">
-        <v>6.15</v>
+        <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="Z39" t="n">
-        <v>2.9</v>
+        <v>2.75</v>
       </c>
       <c r="AA39" t="n">
         <v>1.95</v>
@@ -5493,10 +5493,10 @@
         <v>1.79</v>
       </c>
       <c r="AC39" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="AD39" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AE39" t="inlineStr">
         <is>
@@ -5509,10 +5509,10 @@
         </is>
       </c>
       <c r="AG39" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AH39" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AI39" t="n">
         <v>0</v>
@@ -5535,7 +5535,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Kariobangi Sharks</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>KCB</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,13 +5571,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5610,10 +5610,10 @@
         <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Z40" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AA40" t="n">
         <v>0</v>
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,61 +5700,61 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1.56</v>
+        <v>4.3</v>
       </c>
       <c r="M41" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="N41" t="n">
-        <v>5.4</v>
+        <v>1.64</v>
       </c>
       <c r="O41" t="n">
-        <v>2.2</v>
+        <v>3.94</v>
       </c>
       <c r="P41" t="n">
-        <v>2.48</v>
+        <v>2.72</v>
       </c>
       <c r="Q41" t="n">
-        <v>5</v>
+        <v>2.15</v>
       </c>
       <c r="R41" t="n">
-        <v>1.28</v>
+        <v>1.21</v>
       </c>
       <c r="S41" t="n">
-        <v>3.38</v>
+        <v>3.9</v>
       </c>
       <c r="T41" t="n">
-        <v>2.25</v>
+        <v>2.16</v>
       </c>
       <c r="U41" t="n">
-        <v>1.53</v>
+        <v>1.71</v>
       </c>
       <c r="V41" t="n">
         <v>1.01</v>
       </c>
       <c r="W41" t="n">
-        <v>1.16</v>
+        <v>1.1</v>
       </c>
       <c r="X41" t="n">
-        <v>4.3</v>
+        <v>5.3</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.63</v>
+        <v>1.42</v>
       </c>
       <c r="Z41" t="n">
-        <v>2.25</v>
+        <v>2.74</v>
       </c>
       <c r="AA41" t="n">
-        <v>2.64</v>
+        <v>2.15</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.52</v>
+        <v>1.7</v>
       </c>
       <c r="AC41" t="n">
-        <v>1.65</v>
+        <v>1.48</v>
       </c>
       <c r="AD41" t="n">
-        <v>2.15</v>
+        <v>2.44</v>
       </c>
       <c r="AE41" t="inlineStr">
         <is>
@@ -5767,10 +5767,10 @@
         </is>
       </c>
       <c r="AG41" t="n">
-        <v>1.17</v>
+        <v>1.23</v>
       </c>
       <c r="AH41" t="n">
-        <v>2.17</v>
+        <v>1.23</v>
       </c>
       <c r="AI41" t="n">
         <v>0</v>
@@ -5793,7 +5793,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,77 +5829,77 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>3</v>
+        <v>2.4</v>
       </c>
       <c r="M42" t="n">
-        <v>3.83</v>
+        <v>3.39</v>
       </c>
       <c r="N42" t="n">
-        <v>2.1</v>
+        <v>2.79</v>
       </c>
       <c r="O42" t="n">
-        <v>3.45</v>
+        <v>3.34</v>
       </c>
       <c r="P42" t="n">
-        <v>2.38</v>
+        <v>1.86</v>
       </c>
       <c r="Q42" t="n">
-        <v>2.58</v>
+        <v>3.68</v>
       </c>
       <c r="R42" t="n">
-        <v>1.25</v>
+        <v>1.51</v>
       </c>
       <c r="S42" t="n">
-        <v>3.45</v>
+        <v>2.32</v>
       </c>
       <c r="T42" t="n">
-        <v>2.25</v>
+        <v>3.7</v>
       </c>
       <c r="U42" t="n">
-        <v>1.59</v>
+        <v>1.24</v>
       </c>
       <c r="V42" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="W42" t="n">
-        <v>1.18</v>
+        <v>1.53</v>
       </c>
       <c r="X42" t="n">
-        <v>5.2</v>
+        <v>2.5</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.58</v>
+        <v>2.52</v>
       </c>
       <c r="Z42" t="n">
-        <v>2.22</v>
+        <v>1.52</v>
       </c>
       <c r="AA42" t="n">
-        <v>2.25</v>
+        <v>4.8</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.65</v>
+        <v>1.13</v>
       </c>
       <c r="AC42" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AE42" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF42" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG42" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AH42" t="n">
         <v>1.49</v>
-      </c>
-      <c r="AD42" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AE42" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF42" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG42" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AH42" t="n">
-        <v>1.38</v>
       </c>
       <c r="AI42" t="n">
         <v>0</v>
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Olympique Marseille</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5958,61 +5958,61 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>1.56</v>
+        <v>1.35</v>
       </c>
       <c r="M43" t="n">
-        <v>4.3</v>
+        <v>5.3</v>
       </c>
       <c r="N43" t="n">
-        <v>5.1</v>
+        <v>7</v>
       </c>
       <c r="O43" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P43" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>4.84</v>
+        <v>0</v>
       </c>
       <c r="R43" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="S43" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="T43" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="U43" t="n">
+        <v>0</v>
+      </c>
+      <c r="V43" t="n">
+        <v>0</v>
+      </c>
+      <c r="W43" t="n">
+        <v>0</v>
+      </c>
+      <c r="X43" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y43" t="n">
         <v>1.6</v>
       </c>
-      <c r="V43" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W43" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="X43" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="Y43" t="n">
-        <v>1.63</v>
-      </c>
       <c r="Z43" t="n">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
       <c r="AA43" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AC43" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AD43" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AE43" t="inlineStr">
         <is>
@@ -6025,10 +6025,10 @@
         </is>
       </c>
       <c r="AG43" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AH43" t="n">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="AI43" t="n">
         <v>0</v>
@@ -6061,12 +6061,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Olympique Marseille</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6087,13 +6087,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>1.35</v>
+        <v>1.56</v>
       </c>
       <c r="M44" t="n">
-        <v>5.3</v>
+        <v>4.3</v>
       </c>
       <c r="N44" t="n">
-        <v>7</v>
+        <v>5.1</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -6126,10 +6126,10 @@
         <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="Z44" t="n">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="AA44" t="n">
         <v>0</v>
@@ -6175,12 +6175,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Police</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Ulinzi Stars</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6216,13 +6216,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="M45" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -6255,10 +6255,10 @@
         <v>0</v>
       </c>
       <c r="Y45" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Z45" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA45" t="n">
         <v>0</v>
@@ -6295,7 +6295,7 @@
         <v>0</v>
       </c>
       <c r="AK45" s="3" t="n">
-        <v>45930.75</v>
+        <v>45930.66666666666</v>
       </c>
     </row>
     <row r="46">
@@ -6304,27 +6304,27 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6345,61 +6345,61 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>1.52</v>
+        <v>3</v>
       </c>
       <c r="M46" t="n">
-        <v>4</v>
+        <v>3.83</v>
       </c>
       <c r="N46" t="n">
-        <v>4.7</v>
+        <v>2.1</v>
       </c>
       <c r="O46" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="P46" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="R46" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="S46" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="T46" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="U46" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="V46" t="n">
         <v>0</v>
       </c>
       <c r="W46" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X46" t="n">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="Y46" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="Z46" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="AA46" t="n">
-        <v>1.85</v>
+        <v>2.25</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.85</v>
+        <v>1.65</v>
       </c>
       <c r="AC46" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AD46" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="AE46" t="inlineStr">
         <is>
@@ -6412,10 +6412,10 @@
         </is>
       </c>
       <c r="AG46" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AH46" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="AI46" t="n">
         <v>0</v>
@@ -6424,7 +6424,7 @@
         <v>0</v>
       </c>
       <c r="AK46" s="3" t="n">
-        <v>45930.85416666666</v>
+        <v>45930.66666666666</v>
       </c>
     </row>
     <row r="47">
@@ -6433,12 +6433,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -6448,12 +6448,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6474,61 +6474,61 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>1.4</v>
+        <v>1.52</v>
       </c>
       <c r="M47" t="n">
+        <v>4</v>
+      </c>
+      <c r="N47" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="O47" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="P47" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Q47" t="n">
         <v>4.2</v>
       </c>
-      <c r="N47" t="n">
-        <v>6</v>
-      </c>
-      <c r="O47" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="P47" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Q47" t="n">
-        <v>5.75</v>
-      </c>
       <c r="R47" t="n">
-        <v>1.39</v>
+        <v>1.18</v>
       </c>
       <c r="S47" t="n">
-        <v>2.85</v>
+        <v>4.4</v>
       </c>
       <c r="T47" t="n">
-        <v>2.88</v>
+        <v>1.99</v>
       </c>
       <c r="U47" t="n">
-        <v>1.37</v>
+        <v>1.79</v>
       </c>
       <c r="V47" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="W47" t="n">
-        <v>1.32</v>
+        <v>1.09</v>
       </c>
       <c r="X47" t="n">
-        <v>3.02</v>
+        <v>6.8</v>
       </c>
       <c r="Y47" t="n">
-        <v>1.86</v>
+        <v>1.35</v>
       </c>
       <c r="Z47" t="n">
-        <v>1.84</v>
+        <v>3.04</v>
       </c>
       <c r="AA47" t="n">
-        <v>3.7</v>
+        <v>1.85</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.25</v>
+        <v>1.85</v>
       </c>
       <c r="AC47" t="n">
-        <v>2.08</v>
+        <v>1.41</v>
       </c>
       <c r="AD47" t="n">
-        <v>1.67</v>
+        <v>2.89</v>
       </c>
       <c r="AE47" t="inlineStr">
         <is>
@@ -6541,10 +6541,10 @@
         </is>
       </c>
       <c r="AG47" t="n">
-        <v>1.13</v>
+        <v>1.22</v>
       </c>
       <c r="AH47" t="n">
-        <v>2.42</v>
+        <v>2.24</v>
       </c>
       <c r="AI47" t="n">
         <v>0</v>
@@ -6553,7 +6553,7 @@
         <v>0</v>
       </c>
       <c r="AK47" s="3" t="n">
-        <v>45930.89583333334</v>
+        <v>45930.85416666666</v>
       </c>
     </row>
     <row r="48">
@@ -6562,12 +6562,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>21:35</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6577,12 +6577,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6603,58 +6603,58 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>1.93</v>
+        <v>1.4</v>
       </c>
       <c r="M48" t="n">
-        <v>3.1</v>
+        <v>4.2</v>
       </c>
       <c r="N48" t="n">
-        <v>3.57</v>
+        <v>6</v>
       </c>
       <c r="O48" t="n">
-        <v>2.67</v>
+        <v>2.16</v>
       </c>
       <c r="P48" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="Q48" t="n">
-        <v>4.35</v>
+        <v>5.75</v>
       </c>
       <c r="R48" t="n">
-        <v>1.51</v>
+        <v>1.39</v>
       </c>
       <c r="S48" t="n">
-        <v>2.39</v>
+        <v>2.85</v>
       </c>
       <c r="T48" t="n">
-        <v>3.3</v>
+        <v>2.88</v>
       </c>
       <c r="U48" t="n">
-        <v>1.28</v>
+        <v>1.37</v>
       </c>
       <c r="V48" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="W48" t="n">
-        <v>1.47</v>
+        <v>1.32</v>
       </c>
       <c r="X48" t="n">
-        <v>2.95</v>
+        <v>3.02</v>
       </c>
       <c r="Y48" t="n">
-        <v>2.12</v>
+        <v>1.86</v>
       </c>
       <c r="Z48" t="n">
-        <v>1.64</v>
+        <v>1.84</v>
       </c>
       <c r="AA48" t="n">
-        <v>4.1</v>
+        <v>3.7</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="AC48" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AD48" t="n">
         <v>1.67</v>
@@ -6670,18 +6670,147 @@
         </is>
       </c>
       <c r="AG48" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AH48" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AI48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK48" s="3" t="n">
+        <v>45930.89583333334</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="n">
+        <v>45930</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>21:35</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Goiás</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Atlético GO</t>
+        </is>
+      </c>
+      <c r="G49" t="n">
+        <v>0</v>
+      </c>
+      <c r="H49" t="n">
+        <v>0</v>
+      </c>
+      <c r="I49" t="n">
+        <v>0</v>
+      </c>
+      <c r="J49" t="n">
+        <v>0</v>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L49" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="M49" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="N49" t="n">
+        <v>3.57</v>
+      </c>
+      <c r="O49" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="P49" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="R49" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="S49" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="T49" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="U49" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="V49" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W49" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="X49" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="Y49" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="Z49" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AA49" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AB49" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AC49" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD49" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AE49" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF49" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG49" t="n">
         <v>1.34</v>
       </c>
-      <c r="AH48" t="n">
+      <c r="AH49" t="n">
         <v>1.76</v>
       </c>
-      <c r="AI48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK48" s="3" t="n">
+      <c r="AI49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK49" s="3" t="n">
         <v>45930.89930555555</v>
       </c>
     </row>

--- a/jogos_2025-09-30.xlsx
+++ b/jogos_2025-09-30.xlsx
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sogdiana</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -927,61 +927,61 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.95</v>
+        <v>3.35</v>
       </c>
       <c r="M4" t="n">
+        <v>3</v>
+      </c>
+      <c r="N4" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="O4" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="P4" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S4" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="T4" t="n">
         <v>3.1</v>
       </c>
-      <c r="N4" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="O4" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="P4" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="S4" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="T4" t="n">
-        <v>2.94</v>
-      </c>
       <c r="U4" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="V4" t="n">
         <v>1.03</v>
       </c>
       <c r="W4" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="X4" t="n">
-        <v>2.88</v>
+        <v>2.7</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.08</v>
+        <v>2.25</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AA4" t="n">
-        <v>3.48</v>
+        <v>4.05</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.79</v>
+        <v>1.91</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.87</v>
+        <v>1.8</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
@@ -997,13 +997,13 @@
         <v>1.33</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AI4" t="n">
-        <v>2.18</v>
+        <v>2.31</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1.93</v>
+        <v>1.81</v>
       </c>
       <c r="AK4" s="3" t="n">
         <v>45930.45833333334</v>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Sogdiana</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1056,61 +1056,61 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>3.35</v>
+        <v>2.95</v>
       </c>
       <c r="M5" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="N5" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="O5" t="n">
-        <v>4.05</v>
+        <v>3.65</v>
       </c>
       <c r="P5" t="n">
-        <v>1.91</v>
+        <v>2.12</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.89</v>
+        <v>3.02</v>
       </c>
       <c r="R5" t="n">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="S5" t="n">
-        <v>2.43</v>
+        <v>2.49</v>
       </c>
       <c r="T5" t="n">
-        <v>3.22</v>
+        <v>2.94</v>
       </c>
       <c r="U5" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="V5" t="n">
         <v>1.03</v>
       </c>
       <c r="W5" t="n">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="X5" t="n">
-        <v>2.74</v>
+        <v>3.02</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.25</v>
+        <v>2.08</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AA5" t="n">
-        <v>4.05</v>
+        <v>3.48</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.9</v>
+        <v>1.79</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
@@ -1123,16 +1123,16 @@
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AI5" t="n">
-        <v>2.31</v>
+        <v>2.18</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1.81</v>
+        <v>1.93</v>
       </c>
       <c r="AK5" s="3" t="n">
         <v>45930.45833333334</v>
@@ -1194,25 +1194,25 @@
         <v>1.82</v>
       </c>
       <c r="O6" t="n">
-        <v>6.42</v>
+        <v>6.16</v>
       </c>
       <c r="P6" t="n">
-        <v>2.25</v>
+        <v>2.09</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="R6" t="n">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="S6" t="n">
         <v>2.69</v>
       </c>
       <c r="T6" t="n">
-        <v>2.92</v>
+        <v>2.85</v>
       </c>
       <c r="U6" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="V6" t="n">
         <v>1.01</v>
@@ -1236,10 +1236,10 @@
         <v>1.25</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.99</v>
+        <v>1.9</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.68</v>
+        <v>1.78</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
@@ -1252,10 +1252,10 @@
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>1.26</v>
+        <v>2.22</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AI6" t="n">
         <v>2.38</v>
@@ -1452,25 +1452,25 @@
         <v>1.11</v>
       </c>
       <c r="O8" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="P8" t="n">
-        <v>3.38</v>
+        <v>3.4</v>
       </c>
       <c r="Q8" t="n">
         <v>1.38</v>
       </c>
       <c r="R8" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="S8" t="n">
-        <v>4.33</v>
+        <v>4.8</v>
       </c>
       <c r="T8" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="U8" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="V8" t="n">
         <v>1.01</v>
@@ -1494,10 +1494,10 @@
         <v>1.94</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.32</v>
+        <v>2.27</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
@@ -1516,10 +1516,10 @@
         <v>1.01</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>6.55</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK8" s="3" t="n">
         <v>45930.57291666666</v>
@@ -1665,22 +1665,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Saarbrucken</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>MSV Duisburg</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,61 +1701,61 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.56</v>
+        <v>2.22</v>
       </c>
       <c r="M10" t="n">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="N10" t="n">
-        <v>4.2</v>
+        <v>2.9</v>
       </c>
       <c r="O10" t="n">
-        <v>1.95</v>
+        <v>2.75</v>
       </c>
       <c r="P10" t="n">
-        <v>2.5</v>
+        <v>2.28</v>
       </c>
       <c r="Q10" t="n">
-        <v>5.07</v>
+        <v>3.3</v>
       </c>
       <c r="R10" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="S10" t="n">
-        <v>3.66</v>
+        <v>3.1</v>
       </c>
       <c r="T10" t="n">
-        <v>2.18</v>
+        <v>2.45</v>
       </c>
       <c r="U10" t="n">
-        <v>1.64</v>
+        <v>1.47</v>
       </c>
       <c r="V10" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="W10" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="X10" t="n">
-        <v>5.6</v>
+        <v>4.05</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.45</v>
+        <v>1.67</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.56</v>
+        <v>2.16</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.92</v>
+        <v>2.62</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.78</v>
+        <v>1.38</v>
       </c>
       <c r="AC10" t="n">
         <v>1.55</v>
       </c>
       <c r="AD10" t="n">
-        <v>2.3</v>
+        <v>2.27</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -1768,16 +1768,16 @@
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>1.19</v>
+        <v>1.26</v>
       </c>
       <c r="AH10" t="n">
-        <v>2.31</v>
+        <v>1.62</v>
       </c>
       <c r="AI10" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AK10" s="3" t="n">
         <v>45930.58333333334</v>
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Wehen Wiesbaden</t>
+          <t>Erzgebirge Aue</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,61 +1830,61 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.68</v>
+        <v>2.05</v>
       </c>
       <c r="M11" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="N11" t="n">
-        <v>2.35</v>
+        <v>3.2</v>
       </c>
       <c r="O11" t="n">
-        <v>3.34</v>
+        <v>2.44</v>
       </c>
       <c r="P11" t="n">
-        <v>2.38</v>
+        <v>2.17</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.6</v>
+        <v>3.33</v>
       </c>
       <c r="R11" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="S11" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="T11" t="n">
-        <v>2.38</v>
+        <v>2.55</v>
       </c>
       <c r="U11" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="V11" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="W11" t="n">
-        <v>1.16</v>
+        <v>1.21</v>
       </c>
       <c r="X11" t="n">
-        <v>4.2</v>
+        <v>3.68</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.15</v>
+        <v>2.07</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.49</v>
+        <v>2.95</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.42</v>
+        <v>1.35</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.51</v>
+        <v>1.62</v>
       </c>
       <c r="AD11" t="n">
-        <v>2.32</v>
+        <v>2.11</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -1897,16 +1897,16 @@
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="AI11" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AK11" s="3" t="n">
         <v>45930.58333333334</v>
@@ -1923,22 +1923,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Erzgebirge Aue</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,83 +1959,83 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.93</v>
+        <v>1.26</v>
       </c>
       <c r="M12" t="n">
-        <v>3.65</v>
+        <v>5.1</v>
       </c>
       <c r="N12" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="O12" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="P12" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>5.03</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="S12" t="n">
         <v>3.28</v>
       </c>
-      <c r="O12" t="n">
+      <c r="T12" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="X12" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="Z12" t="n">
         <v>2.5</v>
       </c>
-      <c r="P12" t="n">
+      <c r="AA12" t="n">
         <v>2.17</v>
       </c>
-      <c r="Q12" t="n">
-        <v>3.33</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="S12" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="T12" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="U12" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="V12" t="n">
-        <v>1</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="X12" t="n">
-        <v>3.68</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>2.95</v>
-      </c>
       <c r="AB12" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG12" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="AI12" t="n">
         <v>1.4</v>
       </c>
-      <c r="AC12" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AE12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG12" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>0</v>
-      </c>
       <c r="AJ12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AK12" s="3" t="n">
         <v>45930.58333333334</v>
@@ -2088,13 +2088,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="M13" t="n">
-        <v>3.55</v>
+        <v>3.25</v>
       </c>
       <c r="N13" t="n">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="O13" t="n">
         <v>2.44</v>
@@ -2103,40 +2103,40 @@
         <v>2.18</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.78</v>
+        <v>3.31</v>
       </c>
       <c r="R13" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="S13" t="n">
-        <v>3.3</v>
+        <v>3.14</v>
       </c>
       <c r="T13" t="n">
-        <v>2.52</v>
+        <v>2.49</v>
       </c>
       <c r="U13" t="n">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="V13" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="W13" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="X13" t="n">
-        <v>4.19</v>
+        <v>3.8</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.97</v>
+        <v>2.05</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.75</v>
+        <v>2.72</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.37</v>
+        <v>1.43</v>
       </c>
       <c r="AC13" t="n">
         <v>1.58</v>
@@ -2158,13 +2158,13 @@
         <v>1.24</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.66</v>
+        <v>1.62</v>
       </c>
       <c r="AI13" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AK13" s="3" t="n">
         <v>45930.58333333334</v>
@@ -2181,22 +2181,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Wehen Wiesbaden</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,61 +2217,61 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.26</v>
+        <v>2.62</v>
       </c>
       <c r="M14" t="n">
-        <v>5.1</v>
+        <v>3.5</v>
       </c>
       <c r="N14" t="n">
-        <v>7.6</v>
+        <v>2.35</v>
       </c>
       <c r="O14" t="n">
-        <v>1.83</v>
+        <v>3.32</v>
       </c>
       <c r="P14" t="n">
-        <v>2.45</v>
+        <v>2.21</v>
       </c>
       <c r="Q14" t="n">
-        <v>5.7</v>
+        <v>2.88</v>
       </c>
       <c r="R14" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="S14" t="n">
-        <v>3.28</v>
+        <v>3.2</v>
       </c>
       <c r="T14" t="n">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="U14" t="n">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="V14" t="n">
         <v>1.04</v>
       </c>
       <c r="W14" t="n">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="X14" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.47</v>
+        <v>1.65</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.5</v>
+        <v>2.15</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.17</v>
+        <v>2.49</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.62</v>
+        <v>1.46</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.84</v>
+        <v>1.44</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.86</v>
+        <v>2.32</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
@@ -2284,16 +2284,16 @@
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>1.13</v>
+        <v>1.25</v>
       </c>
       <c r="AH14" t="n">
-        <v>2.82</v>
+        <v>1.4</v>
       </c>
       <c r="AI14" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AK14" s="3" t="n">
         <v>45930.58333333334</v>
@@ -2310,22 +2310,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Havelse</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Waldhof Mannheim</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,61 +2346,61 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>3.5</v>
+        <v>1.56</v>
       </c>
       <c r="M15" t="n">
-        <v>3.65</v>
+        <v>4.2</v>
       </c>
       <c r="N15" t="n">
-        <v>1.91</v>
+        <v>4.2</v>
       </c>
       <c r="O15" t="n">
-        <v>4.12</v>
+        <v>2.05</v>
       </c>
       <c r="P15" t="n">
-        <v>2.24</v>
+        <v>2.51</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.4</v>
+        <v>5.02</v>
       </c>
       <c r="R15" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="S15" t="n">
-        <v>3.2</v>
+        <v>3.66</v>
       </c>
       <c r="T15" t="n">
-        <v>2.44</v>
+        <v>2.2</v>
       </c>
       <c r="U15" t="n">
-        <v>1.5</v>
+        <v>1.65</v>
       </c>
       <c r="V15" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="W15" t="n">
-        <v>1.16</v>
+        <v>1.1</v>
       </c>
       <c r="X15" t="n">
-        <v>4.1</v>
+        <v>5.1</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.65</v>
+        <v>1.45</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.12</v>
+        <v>2.56</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.56</v>
+        <v>1.92</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.44</v>
+        <v>1.78</v>
       </c>
       <c r="AC15" t="n">
         <v>1.57</v>
       </c>
       <c r="AD15" t="n">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
@@ -2413,16 +2413,16 @@
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>1.81</v>
+        <v>1.19</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.24</v>
+        <v>2.43</v>
       </c>
       <c r="AI15" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AK15" s="3" t="n">
         <v>45930.58333333334</v>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Saarbrucken</t>
+          <t>Havelse</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>MSV Duisburg</t>
+          <t>Waldhof Mannheim</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,34 +2475,34 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.18</v>
+        <v>3.5</v>
       </c>
       <c r="M16" t="n">
-        <v>3.4</v>
+        <v>3.77</v>
       </c>
       <c r="N16" t="n">
-        <v>3.02</v>
+        <v>1.83</v>
       </c>
       <c r="O16" t="n">
-        <v>2.71</v>
+        <v>3.54</v>
       </c>
       <c r="P16" t="n">
-        <v>2.14</v>
+        <v>2.21</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.54</v>
+        <v>2.3</v>
       </c>
       <c r="R16" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="S16" t="n">
         <v>3.1</v>
       </c>
       <c r="T16" t="n">
-        <v>2.48</v>
+        <v>2.44</v>
       </c>
       <c r="U16" t="n">
-        <v>1.51</v>
+        <v>1.49</v>
       </c>
       <c r="V16" t="n">
         <v>1.04</v>
@@ -2511,25 +2511,25 @@
         <v>1.22</v>
       </c>
       <c r="X16" t="n">
-        <v>4.05</v>
+        <v>4.2</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.71</v>
+        <v>1.66</v>
       </c>
       <c r="Z16" t="n">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.59</v>
+        <v>2.56</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="AD16" t="n">
-        <v>2.29</v>
+        <v>2.17</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
@@ -2542,16 +2542,16 @@
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>1.3</v>
+        <v>1.8</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.64</v>
+        <v>1.24</v>
       </c>
       <c r="AI16" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AK16" s="3" t="n">
         <v>45930.58333333334</v>
@@ -2600,17 +2600,17 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.53</v>
+        <v>1.45</v>
       </c>
       <c r="M17" t="n">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="N17" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="O17" t="n">
         <v>2.15</v>
@@ -2637,16 +2637,16 @@
         <v>1.1</v>
       </c>
       <c r="W17" t="n">
-        <v>1.45</v>
+        <v>1.53</v>
       </c>
       <c r="X17" t="n">
-        <v>2.45</v>
+        <v>2.25</v>
       </c>
       <c r="Y17" t="n">
-        <v>2.62</v>
+        <v>2.05</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.48</v>
+        <v>1.68</v>
       </c>
       <c r="AA17" t="n">
         <v>4.75</v>
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,61 +2733,61 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.82</v>
+        <v>3.05</v>
       </c>
       <c r="M18" t="n">
-        <v>3.95</v>
+        <v>3.7</v>
       </c>
       <c r="N18" t="n">
-        <v>3.7</v>
+        <v>2.08</v>
       </c>
       <c r="O18" t="n">
-        <v>2.37</v>
+        <v>3.1</v>
       </c>
       <c r="P18" t="n">
-        <v>2.18</v>
+        <v>2.38</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.54</v>
+        <v>2.4</v>
       </c>
       <c r="R18" t="n">
-        <v>1.29</v>
+        <v>1.23</v>
       </c>
       <c r="S18" t="n">
-        <v>3.28</v>
+        <v>3.58</v>
       </c>
       <c r="T18" t="n">
-        <v>2.47</v>
+        <v>2.2</v>
       </c>
       <c r="U18" t="n">
-        <v>1.48</v>
+        <v>1.61</v>
       </c>
       <c r="V18" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="W18" t="n">
-        <v>1.21</v>
+        <v>1.16</v>
       </c>
       <c r="X18" t="n">
-        <v>4.31</v>
+        <v>5.4</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.68</v>
+        <v>1.46</v>
       </c>
       <c r="Z18" t="n">
-        <v>2.19</v>
+        <v>2.39</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.68</v>
+        <v>2.28</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.39</v>
+        <v>1.6</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="AD18" t="n">
-        <v>2.22</v>
+        <v>2.56</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
@@ -2800,10 +2800,10 @@
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.92</v>
+        <v>1.27</v>
       </c>
       <c r="AI18" t="n">
         <v>0</v>
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,61 +2862,61 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.1</v>
+        <v>3</v>
       </c>
       <c r="M19" t="n">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="N19" t="n">
-        <v>2.89</v>
+        <v>2.18</v>
       </c>
       <c r="O19" t="n">
-        <v>2.58</v>
+        <v>3.35</v>
       </c>
       <c r="P19" t="n">
-        <v>2.51</v>
+        <v>2.47</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.25</v>
+        <v>2.66</v>
       </c>
       <c r="R19" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="S19" t="n">
-        <v>3.58</v>
+        <v>3.34</v>
       </c>
       <c r="T19" t="n">
-        <v>2.21</v>
+        <v>2.32</v>
       </c>
       <c r="U19" t="n">
-        <v>1.62</v>
+        <v>1.54</v>
       </c>
       <c r="V19" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="W19" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="X19" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="Z19" t="n">
-        <v>2.33</v>
+        <v>2.3</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.35</v>
+        <v>2.36</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.6</v>
+        <v>1.47</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="AD19" t="n">
-        <v>2.59</v>
+        <v>2.45</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
@@ -2929,10 +2929,10 @@
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.65</v>
+        <v>1.37</v>
       </c>
       <c r="AI19" t="n">
         <v>0</v>
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,55 +2991,55 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="O20" t="n">
-        <v>1.93</v>
+        <v>2.37</v>
       </c>
       <c r="P20" t="n">
-        <v>2.53</v>
+        <v>2.18</v>
       </c>
       <c r="Q20" t="n">
-        <v>5.48</v>
+        <v>3.54</v>
       </c>
       <c r="R20" t="n">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="S20" t="n">
-        <v>3.66</v>
+        <v>3.28</v>
       </c>
       <c r="T20" t="n">
-        <v>2.15</v>
+        <v>2.47</v>
       </c>
       <c r="U20" t="n">
-        <v>1.64</v>
+        <v>1.48</v>
       </c>
       <c r="V20" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="W20" t="n">
-        <v>1.11</v>
+        <v>1.21</v>
       </c>
       <c r="X20" t="n">
-        <v>4.98</v>
+        <v>4.31</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.43</v>
+        <v>1.68</v>
       </c>
       <c r="Z20" t="n">
-        <v>2.49</v>
+        <v>2.19</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.27</v>
+        <v>2.68</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.64</v>
+        <v>1.39</v>
       </c>
       <c r="AC20" t="n">
         <v>1.6</v>
@@ -3058,10 +3058,10 @@
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AH20" t="n">
-        <v>2.61</v>
+        <v>1.92</v>
       </c>
       <c r="AI20" t="n">
         <v>0</v>
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,61 +3120,61 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>3</v>
+        <v>2.1</v>
       </c>
       <c r="M21" t="n">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="N21" t="n">
-        <v>2.18</v>
+        <v>2.89</v>
       </c>
       <c r="O21" t="n">
-        <v>3.35</v>
+        <v>2.58</v>
       </c>
       <c r="P21" t="n">
-        <v>2.47</v>
+        <v>2.51</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.66</v>
+        <v>3.25</v>
       </c>
       <c r="R21" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="S21" t="n">
-        <v>3.34</v>
+        <v>3.58</v>
       </c>
       <c r="T21" t="n">
-        <v>2.32</v>
+        <v>2.21</v>
       </c>
       <c r="U21" t="n">
-        <v>1.54</v>
+        <v>1.62</v>
       </c>
       <c r="V21" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="W21" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="X21" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="Z21" t="n">
-        <v>2.3</v>
+        <v>2.33</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.36</v>
+        <v>2.35</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.47</v>
+        <v>1.6</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AD21" t="n">
-        <v>2.45</v>
+        <v>2.59</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
@@ -3187,10 +3187,10 @@
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.37</v>
+        <v>1.65</v>
       </c>
       <c r="AI21" t="n">
         <v>0</v>
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,61 +3249,61 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>3.1</v>
+        <v>1.93</v>
       </c>
       <c r="P22" t="n">
-        <v>2.38</v>
+        <v>2.53</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.4</v>
+        <v>5.48</v>
       </c>
       <c r="R22" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="S22" t="n">
-        <v>3.58</v>
+        <v>3.66</v>
       </c>
       <c r="T22" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="U22" t="n">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="V22" t="n">
         <v>1.01</v>
       </c>
       <c r="W22" t="n">
-        <v>1.16</v>
+        <v>1.11</v>
       </c>
       <c r="X22" t="n">
-        <v>5.4</v>
+        <v>4.98</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="Z22" t="n">
-        <v>2.39</v>
+        <v>2.49</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.28</v>
+        <v>2.27</v>
       </c>
       <c r="AB22" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AC22" t="n">
         <v>1.6</v>
       </c>
-      <c r="AC22" t="n">
-        <v>1.45</v>
-      </c>
       <c r="AD22" t="n">
-        <v>2.56</v>
+        <v>2.22</v>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
@@ -3316,10 +3316,10 @@
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>1.24</v>
+        <v>1.18</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.27</v>
+        <v>2.61</v>
       </c>
       <c r="AI22" t="n">
         <v>0</v>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,62 +3378,62 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.59</v>
+        <v>3.25</v>
       </c>
       <c r="M23" t="n">
-        <v>3.01</v>
+        <v>3.6</v>
       </c>
       <c r="N23" t="n">
-        <v>2.84</v>
+        <v>2.02</v>
       </c>
       <c r="O23" t="n">
-        <v>2.97</v>
+        <v>4.31</v>
       </c>
       <c r="P23" t="n">
-        <v>1.91</v>
+        <v>2.29</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.4</v>
+        <v>2.48</v>
       </c>
       <c r="R23" t="n">
-        <v>1.45</v>
+        <v>1.34</v>
       </c>
       <c r="S23" t="n">
-        <v>2.48</v>
+        <v>2.98</v>
       </c>
       <c r="T23" t="n">
-        <v>3.14</v>
+        <v>2.65</v>
       </c>
       <c r="U23" t="n">
-        <v>1.29</v>
+        <v>1.42</v>
       </c>
       <c r="V23" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="W23" t="n">
-        <v>1.4</v>
+        <v>1.26</v>
       </c>
       <c r="X23" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA23" t="n">
         <v>2.92</v>
       </c>
-      <c r="Y23" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>4</v>
-      </c>
       <c r="AB23" t="n">
-        <v>1.18</v>
+        <v>1.31</v>
       </c>
       <c r="AC23" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AD23" t="n">
         <v>2.01</v>
       </c>
-      <c r="AD23" t="n">
-        <v>1.82</v>
-      </c>
       <c r="AE23" t="inlineStr">
         <is>
           <t>[]</t>
@@ -3445,16 +3445,16 @@
         </is>
       </c>
       <c r="AG23" t="n">
-        <v>1.31</v>
+        <v>1.88</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.48</v>
+        <v>1.24</v>
       </c>
       <c r="AI23" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AJ23" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AK23" s="3" t="n">
         <v>45930.64583333334</v>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,61 +3507,61 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>3.25</v>
+        <v>3.41</v>
       </c>
       <c r="M24" t="n">
-        <v>3.6</v>
+        <v>3.26</v>
       </c>
       <c r="N24" t="n">
-        <v>2.02</v>
+        <v>2.13</v>
       </c>
       <c r="O24" t="n">
-        <v>4.2</v>
+        <v>3.82</v>
       </c>
       <c r="P24" t="n">
-        <v>2.16</v>
+        <v>1.95</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.44</v>
+        <v>3</v>
       </c>
       <c r="R24" t="n">
-        <v>1.34</v>
+        <v>1.51</v>
       </c>
       <c r="S24" t="n">
-        <v>2.98</v>
+        <v>2.4</v>
       </c>
       <c r="T24" t="n">
-        <v>2.43</v>
+        <v>3.28</v>
       </c>
       <c r="U24" t="n">
-        <v>1.48</v>
+        <v>1.27</v>
       </c>
       <c r="V24" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="W24" t="n">
-        <v>1.21</v>
+        <v>1.46</v>
       </c>
       <c r="X24" t="n">
-        <v>3.5</v>
+        <v>2.63</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.73</v>
+        <v>2.07</v>
       </c>
       <c r="Z24" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.92</v>
+        <v>4.54</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.31</v>
+        <v>1.16</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.67</v>
+        <v>2.04</v>
       </c>
       <c r="AD24" t="n">
-        <v>2.03</v>
+        <v>1.75</v>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
@@ -3574,16 +3574,16 @@
         </is>
       </c>
       <c r="AG24" t="n">
-        <v>1.24</v>
+        <v>1.56</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.23</v>
+        <v>1.38</v>
       </c>
       <c r="AI24" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AJ24" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AK24" s="3" t="n">
         <v>45930.64583333334</v>
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Calcio Padova</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,61 +3636,61 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.98</v>
+        <v>2.39</v>
       </c>
       <c r="M25" t="n">
-        <v>3.47</v>
+        <v>2.95</v>
       </c>
       <c r="N25" t="n">
-        <v>3.62</v>
+        <v>3.2</v>
       </c>
       <c r="O25" t="n">
-        <v>2.71</v>
+        <v>3.1</v>
       </c>
       <c r="P25" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="Q25" t="n">
-        <v>4.04</v>
+        <v>4.14</v>
       </c>
       <c r="R25" t="n">
-        <v>1.35</v>
+        <v>1.5</v>
       </c>
       <c r="S25" t="n">
-        <v>2.84</v>
+        <v>2.35</v>
       </c>
       <c r="T25" t="n">
-        <v>2.71</v>
+        <v>3.34</v>
       </c>
       <c r="U25" t="n">
-        <v>1.41</v>
+        <v>1.26</v>
       </c>
       <c r="V25" t="n">
         <v>1.05</v>
       </c>
       <c r="W25" t="n">
-        <v>1.24</v>
+        <v>1.44</v>
       </c>
       <c r="X25" t="n">
-        <v>3.56</v>
+        <v>2.55</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.87</v>
+        <v>2.2</v>
       </c>
       <c r="Z25" t="n">
-        <v>1.87</v>
+        <v>1.65</v>
       </c>
       <c r="AA25" t="n">
-        <v>3.12</v>
+        <v>4.4</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.29</v>
+        <v>1.15</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.8</v>
+        <v>2.03</v>
       </c>
       <c r="AD25" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
@@ -3706,13 +3706,13 @@
         <v>1.31</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.73</v>
+        <v>1.61</v>
       </c>
       <c r="AI25" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AJ25" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AK25" s="3" t="n">
         <v>45930.64583333334</v>
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Calcio Padova</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,61 +3765,61 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.39</v>
+        <v>2.59</v>
       </c>
       <c r="M26" t="n">
-        <v>2.95</v>
+        <v>3.01</v>
       </c>
       <c r="N26" t="n">
-        <v>3.2</v>
+        <v>2.84</v>
       </c>
       <c r="O26" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="P26" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S26" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="T26" t="n">
         <v>3.14</v>
       </c>
-      <c r="P26" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="R26" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="S26" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="T26" t="n">
-        <v>3.34</v>
-      </c>
       <c r="U26" t="n">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="V26" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="W26" t="n">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="X26" t="n">
-        <v>2.5</v>
+        <v>2.92</v>
       </c>
       <c r="Y26" t="n">
         <v>2.2</v>
       </c>
       <c r="Z26" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AA26" t="n">
-        <v>4.45</v>
+        <v>3.95</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="AC26" t="n">
-        <v>2.03</v>
+        <v>1.85</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.72</v>
+        <v>1.8</v>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
@@ -3832,16 +3832,16 @@
         </is>
       </c>
       <c r="AG26" t="n">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.61</v>
+        <v>1.49</v>
       </c>
       <c r="AI26" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AJ26" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AK26" s="3" t="n">
         <v>45930.64583333334</v>
@@ -3903,22 +3903,22 @@
         <v>3.78</v>
       </c>
       <c r="O27" t="n">
-        <v>2.86</v>
+        <v>2.58</v>
       </c>
       <c r="P27" t="n">
-        <v>1.99</v>
+        <v>1.93</v>
       </c>
       <c r="Q27" t="n">
-        <v>4.3</v>
+        <v>3.76</v>
       </c>
       <c r="R27" t="n">
-        <v>1.46</v>
+        <v>1.52</v>
       </c>
       <c r="S27" t="n">
         <v>2.45</v>
       </c>
       <c r="T27" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="U27" t="n">
         <v>1.28</v>
@@ -3927,10 +3927,10 @@
         <v>1.08</v>
       </c>
       <c r="W27" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="X27" t="n">
-        <v>2.9</v>
+        <v>2.75</v>
       </c>
       <c r="Y27" t="n">
         <v>2.18</v>
@@ -3939,16 +3939,16 @@
         <v>1.7</v>
       </c>
       <c r="AA27" t="n">
-        <v>3.85</v>
+        <v>4.15</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AC27" t="n">
-        <v>2.06</v>
+        <v>1.95</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.74</v>
+        <v>1.78</v>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
@@ -3961,16 +3961,16 @@
         </is>
       </c>
       <c r="AG27" t="n">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="AI27" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AJ27" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AK27" s="3" t="n">
         <v>45930.64583333334</v>
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mantova</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,83 +4023,83 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.79</v>
+        <v>1.98</v>
       </c>
       <c r="M28" t="n">
-        <v>3.61</v>
+        <v>3.47</v>
       </c>
       <c r="N28" t="n">
-        <v>4.3</v>
+        <v>3.62</v>
       </c>
       <c r="O28" t="n">
-        <v>2.54</v>
+        <v>2.7</v>
       </c>
       <c r="P28" t="n">
-        <v>2.06</v>
+        <v>2.13</v>
       </c>
       <c r="Q28" t="n">
-        <v>4.2</v>
+        <v>4.08</v>
       </c>
       <c r="R28" t="n">
-        <v>1.42</v>
+        <v>1.35</v>
       </c>
       <c r="S28" t="n">
-        <v>2.57</v>
+        <v>2.84</v>
       </c>
       <c r="T28" t="n">
-        <v>2.93</v>
+        <v>2.55</v>
       </c>
       <c r="U28" t="n">
-        <v>1.33</v>
+        <v>1.45</v>
       </c>
       <c r="V28" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="W28" t="n">
-        <v>1.35</v>
+        <v>1.24</v>
       </c>
       <c r="X28" t="n">
-        <v>3.18</v>
+        <v>3.48</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.98</v>
+        <v>1.87</v>
       </c>
       <c r="Z28" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AE28" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF28" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG28" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AI28" t="n">
         <v>1.77</v>
       </c>
-      <c r="AA28" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AE28" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF28" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG28" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AH28" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AI28" t="n">
-        <v>0</v>
-      </c>
       <c r="AJ28" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AK28" s="3" t="n">
         <v>45930.64583333334</v>
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>Mantova</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,61 +4152,61 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>3.41</v>
+        <v>1.79</v>
       </c>
       <c r="M29" t="n">
-        <v>3.26</v>
+        <v>3.61</v>
       </c>
       <c r="N29" t="n">
-        <v>2.13</v>
+        <v>4.3</v>
       </c>
       <c r="O29" t="n">
-        <v>3.9</v>
+        <v>2.53</v>
       </c>
       <c r="P29" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.16</v>
+        <v>3.86</v>
       </c>
       <c r="R29" t="n">
-        <v>1.51</v>
+        <v>1.42</v>
       </c>
       <c r="S29" t="n">
         <v>2.57</v>
       </c>
       <c r="T29" t="n">
-        <v>3.28</v>
+        <v>2.93</v>
       </c>
       <c r="U29" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="V29" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="W29" t="n">
-        <v>1.45</v>
+        <v>1.38</v>
       </c>
       <c r="X29" t="n">
-        <v>2.63</v>
+        <v>3.22</v>
       </c>
       <c r="Y29" t="n">
-        <v>2.07</v>
+        <v>1.98</v>
       </c>
       <c r="Z29" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="AA29" t="n">
-        <v>4.4</v>
+        <v>3.8</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.16</v>
+        <v>1.23</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.96</v>
+        <v>1.89</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.77</v>
+        <v>1.81</v>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
@@ -4219,16 +4219,16 @@
         </is>
       </c>
       <c r="AG29" t="n">
-        <v>1.36</v>
+        <v>1.26</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.38</v>
+        <v>1.89</v>
       </c>
       <c r="AI29" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AJ29" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AK29" s="3" t="n">
         <v>45930.64583333334</v>
@@ -4293,13 +4293,13 @@
         <v>1.94</v>
       </c>
       <c r="P30" t="n">
-        <v>2.35</v>
+        <v>2.19</v>
       </c>
       <c r="Q30" t="n">
-        <v>6.5</v>
+        <v>5.7</v>
       </c>
       <c r="R30" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="S30" t="n">
         <v>2.93</v>
@@ -4311,10 +4311,10 @@
         <v>1.4</v>
       </c>
       <c r="V30" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="W30" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="X30" t="n">
         <v>3.48</v>
@@ -4329,13 +4329,13 @@
         <v>3.02</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AC30" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
@@ -4354,10 +4354,10 @@
         <v>2.99</v>
       </c>
       <c r="AI30" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AJ30" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AK30" s="3" t="n">
         <v>45930.65625</v>
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,83 +4410,83 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.49</v>
+        <v>2.19</v>
       </c>
       <c r="M31" t="n">
-        <v>3.29</v>
+        <v>3.47</v>
       </c>
       <c r="N31" t="n">
-        <v>2.74</v>
+        <v>3.08</v>
       </c>
       <c r="O31" t="n">
-        <v>3.18</v>
+        <v>2.64</v>
       </c>
       <c r="P31" t="n">
         <v>2.02</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.4</v>
+        <v>3.62</v>
       </c>
       <c r="R31" t="n">
-        <v>1.43</v>
+        <v>1.39</v>
       </c>
       <c r="S31" t="n">
-        <v>2.54</v>
+        <v>2.86</v>
       </c>
       <c r="T31" t="n">
-        <v>3.08</v>
+        <v>2.98</v>
       </c>
       <c r="U31" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="V31" t="n">
+        <v>1</v>
+      </c>
+      <c r="W31" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="X31" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="AB31" t="n">
         <v>1.3</v>
       </c>
-      <c r="V31" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W31" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="X31" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="Y31" t="n">
+      <c r="AC31" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AE31" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF31" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG31" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AJ31" t="n">
         <v>2.2</v>
-      </c>
-      <c r="Z31" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AE31" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF31" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG31" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AH31" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AI31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ31" t="n">
-        <v>0</v>
       </c>
       <c r="AK31" s="3" t="n">
         <v>45930.65625</v>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,83 +4539,83 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.19</v>
+        <v>3.06</v>
       </c>
       <c r="M32" t="n">
-        <v>3.47</v>
+        <v>3.19</v>
       </c>
       <c r="N32" t="n">
-        <v>3.08</v>
+        <v>2.08</v>
       </c>
       <c r="O32" t="n">
-        <v>2.65</v>
+        <v>3.52</v>
       </c>
       <c r="P32" t="n">
-        <v>2.07</v>
+        <v>2.16</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.75</v>
+        <v>2.47</v>
       </c>
       <c r="R32" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S32" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="T32" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="U32" t="n">
         <v>1.39</v>
       </c>
-      <c r="S32" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="T32" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="U32" t="n">
+      <c r="V32" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W32" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X32" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AE32" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF32" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG32" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AH32" t="n">
         <v>1.34</v>
       </c>
-      <c r="V32" t="n">
-        <v>1</v>
-      </c>
-      <c r="W32" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="X32" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="Y32" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>3.64</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AE32" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF32" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG32" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AH32" t="n">
-        <v>1.65</v>
-      </c>
       <c r="AI32" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AJ32" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AK32" s="3" t="n">
         <v>45930.65625</v>
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,62 +4668,62 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.36</v>
+        <v>1.9</v>
       </c>
       <c r="M33" t="n">
-        <v>3.38</v>
+        <v>3.4</v>
       </c>
       <c r="N33" t="n">
-        <v>2.86</v>
+        <v>4</v>
       </c>
       <c r="O33" t="n">
-        <v>3.12</v>
+        <v>2.58</v>
       </c>
       <c r="P33" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.25</v>
+        <v>4.6</v>
       </c>
       <c r="R33" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="S33" t="n">
-        <v>2.75</v>
+        <v>2.67</v>
       </c>
       <c r="T33" t="n">
-        <v>2.6</v>
+        <v>3.03</v>
       </c>
       <c r="U33" t="n">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="V33" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="W33" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="X33" t="n">
-        <v>3.36</v>
+        <v>3.28</v>
       </c>
       <c r="Y33" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AD33" t="n">
         <v>1.89</v>
       </c>
-      <c r="Z33" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AA33" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AB33" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AC33" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AD33" t="n">
-        <v>2.02</v>
-      </c>
       <c r="AE33" t="inlineStr">
         <is>
           <t>[]</t>
@@ -4735,16 +4735,16 @@
         </is>
       </c>
       <c r="AG33" t="n">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.51</v>
+        <v>1.84</v>
       </c>
       <c r="AI33" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AJ33" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="AK33" s="3" t="n">
         <v>45930.65625</v>
@@ -4761,7 +4761,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,83 +4797,83 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>3.06</v>
+        <v>3.2</v>
       </c>
       <c r="M34" t="n">
-        <v>3.19</v>
+        <v>3.3</v>
       </c>
       <c r="N34" t="n">
-        <v>2.08</v>
+        <v>2.2</v>
       </c>
       <c r="O34" t="n">
-        <v>3.6</v>
+        <v>3.62</v>
       </c>
       <c r="P34" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="Q34" t="n">
-        <v>2.47</v>
+        <v>3</v>
       </c>
       <c r="R34" t="n">
-        <v>1.38</v>
+        <v>1.32</v>
       </c>
       <c r="S34" t="n">
-        <v>2.84</v>
+        <v>3</v>
       </c>
       <c r="T34" t="n">
-        <v>2.8</v>
+        <v>2.77</v>
       </c>
       <c r="U34" t="n">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="V34" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="W34" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="X34" t="n">
-        <v>3.4</v>
+        <v>3.48</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.84</v>
+        <v>1.77</v>
       </c>
       <c r="Z34" t="n">
-        <v>1.86</v>
+        <v>1.98</v>
       </c>
       <c r="AA34" t="n">
-        <v>3.08</v>
+        <v>3.2</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="AC34" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AD34" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AE34" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF34" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG34" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AH34" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AI34" t="n">
         <v>2.05</v>
       </c>
-      <c r="AE34" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF34" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG34" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AH34" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AI34" t="n">
-        <v>0</v>
-      </c>
       <c r="AJ34" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AK34" s="3" t="n">
         <v>45930.65625</v>
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,61 +4926,61 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>3.2</v>
+        <v>2.36</v>
       </c>
       <c r="M35" t="n">
-        <v>3.3</v>
+        <v>3.38</v>
       </c>
       <c r="N35" t="n">
-        <v>2.2</v>
+        <v>2.86</v>
       </c>
       <c r="O35" t="n">
-        <v>3.62</v>
+        <v>3.12</v>
       </c>
       <c r="P35" t="n">
         <v>2.11</v>
       </c>
       <c r="Q35" t="n">
-        <v>2.98</v>
+        <v>3.34</v>
       </c>
       <c r="R35" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="S35" t="n">
-        <v>3.09</v>
+        <v>2.95</v>
       </c>
       <c r="T35" t="n">
-        <v>2.6</v>
+        <v>2.9</v>
       </c>
       <c r="U35" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="V35" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="W35" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="X35" t="n">
-        <v>3.48</v>
+        <v>3.39</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.77</v>
+        <v>1.89</v>
       </c>
       <c r="Z35" t="n">
-        <v>1.98</v>
+        <v>1.85</v>
       </c>
       <c r="AA35" t="n">
-        <v>3.08</v>
+        <v>3.35</v>
       </c>
       <c r="AB35" t="n">
         <v>1.3</v>
       </c>
       <c r="AC35" t="n">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AD35" t="n">
-        <v>2.18</v>
+        <v>2.01</v>
       </c>
       <c r="AE35" t="inlineStr">
         <is>
@@ -4993,16 +4993,16 @@
         </is>
       </c>
       <c r="AG35" t="n">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="AI35" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AJ35" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AK35" s="3" t="n">
         <v>45930.65625</v>
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,61 +5055,61 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>1.9</v>
+        <v>2.49</v>
       </c>
       <c r="M36" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="N36" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="O36" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="P36" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Q36" t="n">
         <v>3.4</v>
       </c>
-      <c r="N36" t="n">
-        <v>4</v>
-      </c>
-      <c r="O36" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="P36" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="Q36" t="n">
-        <v>4.65</v>
-      </c>
       <c r="R36" t="n">
-        <v>1.35</v>
+        <v>1.43</v>
       </c>
       <c r="S36" t="n">
-        <v>2.86</v>
+        <v>2.66</v>
       </c>
       <c r="T36" t="n">
-        <v>2.93</v>
+        <v>3.24</v>
       </c>
       <c r="U36" t="n">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="V36" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="W36" t="n">
-        <v>1.28</v>
+        <v>1.4</v>
       </c>
       <c r="X36" t="n">
-        <v>3.16</v>
+        <v>2.83</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.98</v>
+        <v>2.2</v>
       </c>
       <c r="Z36" t="n">
-        <v>1.77</v>
+        <v>1.68</v>
       </c>
       <c r="AA36" t="n">
-        <v>3.55</v>
+        <v>4.1</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="AC36" t="n">
-        <v>1.87</v>
+        <v>1.93</v>
       </c>
       <c r="AD36" t="n">
-        <v>1.93</v>
+        <v>1.88</v>
       </c>
       <c r="AE36" t="inlineStr">
         <is>
@@ -5122,16 +5122,16 @@
         </is>
       </c>
       <c r="AG36" t="n">
-        <v>1.23</v>
+        <v>1.34</v>
       </c>
       <c r="AH36" t="n">
-        <v>1.86</v>
+        <v>1.44</v>
       </c>
       <c r="AI36" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AJ36" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AK36" s="3" t="n">
         <v>45930.65625</v>
@@ -5193,31 +5193,31 @@
         <v>4.9</v>
       </c>
       <c r="O37" t="n">
-        <v>2.27</v>
+        <v>2.21</v>
       </c>
       <c r="P37" t="n">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="Q37" t="n">
-        <v>4.65</v>
+        <v>4.28</v>
       </c>
       <c r="R37" t="n">
         <v>1.35</v>
       </c>
       <c r="S37" t="n">
-        <v>3.09</v>
+        <v>2.84</v>
       </c>
       <c r="T37" t="n">
-        <v>2.7</v>
+        <v>2.76</v>
       </c>
       <c r="U37" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="V37" t="n">
         <v>1.02</v>
       </c>
       <c r="W37" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="X37" t="n">
         <v>3.48</v>
@@ -5229,16 +5229,16 @@
         <v>1.91</v>
       </c>
       <c r="AA37" t="n">
-        <v>3.18</v>
+        <v>3.09</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="AC37" t="n">
         <v>1.88</v>
       </c>
       <c r="AD37" t="n">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="AE37" t="inlineStr">
         <is>
@@ -5251,16 +5251,16 @@
         </is>
       </c>
       <c r="AG37" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AH37" t="n">
-        <v>2.05</v>
+        <v>2.13</v>
       </c>
       <c r="AI37" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AJ37" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AK37" s="3" t="n">
         <v>45930.65625</v>
@@ -5322,16 +5322,16 @@
         <v>5.9</v>
       </c>
       <c r="O38" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="P38" t="n">
-        <v>2.35</v>
+        <v>2.22</v>
       </c>
       <c r="Q38" t="n">
-        <v>6.05</v>
+        <v>4.53</v>
       </c>
       <c r="R38" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="S38" t="n">
         <v>3.14</v>
@@ -5340,16 +5340,16 @@
         <v>2.51</v>
       </c>
       <c r="U38" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="V38" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="W38" t="n">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="X38" t="n">
-        <v>3.98</v>
+        <v>4.11</v>
       </c>
       <c r="Y38" t="n">
         <v>1.65</v>
@@ -5361,13 +5361,13 @@
         <v>2.63</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="AC38" t="n">
-        <v>1.84</v>
+        <v>1.89</v>
       </c>
       <c r="AD38" t="n">
-        <v>1.84</v>
+        <v>1.91</v>
       </c>
       <c r="AE38" t="inlineStr">
         <is>
@@ -5386,10 +5386,10 @@
         <v>2.61</v>
       </c>
       <c r="AI38" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AJ38" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AK38" s="3" t="n">
         <v>45930.65625</v>
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,13 +5442,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>15</v>
+        <v>1.56</v>
       </c>
       <c r="M39" t="n">
-        <v>7.6</v>
+        <v>4.1</v>
       </c>
       <c r="N39" t="n">
-        <v>1.15</v>
+        <v>5.4</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5481,16 +5481,16 @@
         <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.44</v>
+        <v>1.63</v>
       </c>
       <c r="Z39" t="n">
-        <v>2.75</v>
+        <v>2.25</v>
       </c>
       <c r="AA39" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AC39" t="n">
         <v>0</v>
@@ -5535,7 +5535,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,61 +5571,61 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>1.62</v>
+        <v>2.4</v>
       </c>
       <c r="M40" t="n">
-        <v>4.1</v>
+        <v>3.39</v>
       </c>
       <c r="N40" t="n">
-        <v>4.9</v>
+        <v>2.79</v>
       </c>
       <c r="O40" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="R40" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="S40" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="T40" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="U40" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="V40" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="W40" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="X40" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.68</v>
+        <v>2.52</v>
       </c>
       <c r="Z40" t="n">
-        <v>2.18</v>
+        <v>1.52</v>
       </c>
       <c r="AA40" t="n">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="AB40" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AC40" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AD40" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AE40" t="inlineStr">
         <is>
@@ -5638,16 +5638,16 @@
         </is>
       </c>
       <c r="AG40" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH40" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AI40" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AJ40" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AK40" s="3" t="n">
         <v>45930.66666666666</v>
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Olympique Marseille</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,61 +5700,61 @@
         </is>
       </c>
       <c r="L41" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="M41" t="n">
         <v>4.3</v>
       </c>
-      <c r="M41" t="n">
-        <v>4.4</v>
-      </c>
       <c r="N41" t="n">
-        <v>1.64</v>
+        <v>5.1</v>
       </c>
       <c r="O41" t="n">
-        <v>3.94</v>
+        <v>0</v>
       </c>
       <c r="P41" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="S41" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="T41" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="U41" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="V41" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W41" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X41" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.42</v>
+        <v>1.63</v>
       </c>
       <c r="Z41" t="n">
-        <v>2.74</v>
+        <v>2.25</v>
       </c>
       <c r="AA41" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC41" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AD41" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="AE41" t="inlineStr">
         <is>
@@ -5767,10 +5767,10 @@
         </is>
       </c>
       <c r="AG41" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AH41" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AI41" t="n">
         <v>0</v>
@@ -5793,7 +5793,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,83 +5829,83 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>2.4</v>
+        <v>1.62</v>
       </c>
       <c r="M42" t="n">
-        <v>3.39</v>
+        <v>4.1</v>
       </c>
       <c r="N42" t="n">
-        <v>2.79</v>
+        <v>4.9</v>
       </c>
       <c r="O42" t="n">
-        <v>3.34</v>
+        <v>2.09</v>
       </c>
       <c r="P42" t="n">
-        <v>1.86</v>
+        <v>2.59</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.68</v>
+        <v>5.05</v>
       </c>
       <c r="R42" t="n">
-        <v>1.51</v>
+        <v>1.27</v>
       </c>
       <c r="S42" t="n">
-        <v>2.32</v>
+        <v>3.38</v>
       </c>
       <c r="T42" t="n">
-        <v>3.7</v>
+        <v>2.28</v>
       </c>
       <c r="U42" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="V42" t="n">
+        <v>1</v>
+      </c>
+      <c r="W42" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="X42" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AE42" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF42" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG42" t="n">
         <v>1.24</v>
       </c>
-      <c r="V42" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="W42" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="X42" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Y42" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="Z42" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AA42" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AB42" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AC42" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AD42" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AE42" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF42" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG42" t="n">
-        <v>1.37</v>
-      </c>
       <c r="AH42" t="n">
-        <v>1.49</v>
+        <v>2.47</v>
       </c>
       <c r="AI42" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AJ42" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AK42" s="3" t="n">
         <v>45930.66666666666</v>
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5958,61 +5958,61 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>1.35</v>
+        <v>4.3</v>
       </c>
       <c r="M43" t="n">
-        <v>5.3</v>
+        <v>4.4</v>
       </c>
       <c r="N43" t="n">
-        <v>7</v>
+        <v>1.64</v>
       </c>
       <c r="O43" t="n">
-        <v>0</v>
+        <v>3.83</v>
       </c>
       <c r="P43" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="Q43" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="R43" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="S43" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="T43" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="U43" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="V43" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W43" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X43" t="n">
-        <v>0</v>
+        <v>5.35</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.6</v>
+        <v>1.42</v>
       </c>
       <c r="Z43" t="n">
-        <v>2.35</v>
+        <v>2.74</v>
       </c>
       <c r="AA43" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB43" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC43" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AD43" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AE43" t="inlineStr">
         <is>
@@ -6025,16 +6025,16 @@
         </is>
       </c>
       <c r="AG43" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AH43" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AI43" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="AJ43" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AK43" s="3" t="n">
         <v>45930.66666666666</v>
@@ -6061,12 +6061,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Olympique Marseille</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6087,61 +6087,61 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>1.56</v>
+        <v>3</v>
       </c>
       <c r="M44" t="n">
-        <v>4.3</v>
+        <v>3.83</v>
       </c>
       <c r="N44" t="n">
-        <v>5.1</v>
+        <v>2.1</v>
       </c>
       <c r="O44" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="S44" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="T44" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="U44" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="V44" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W44" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X44" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.63</v>
+        <v>1.58</v>
       </c>
       <c r="Z44" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="AA44" t="n">
         <v>2.25</v>
       </c>
-      <c r="AA44" t="n">
-        <v>0</v>
-      </c>
       <c r="AB44" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC44" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AD44" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AE44" t="inlineStr">
         <is>
@@ -6154,16 +6154,16 @@
         </is>
       </c>
       <c r="AG44" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AH44" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AI44" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AJ44" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AK44" s="3" t="n">
         <v>45930.66666666666</v>
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6216,61 +6216,61 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>1.56</v>
+        <v>15</v>
       </c>
       <c r="M45" t="n">
-        <v>4.1</v>
+        <v>7.6</v>
       </c>
       <c r="N45" t="n">
-        <v>5.4</v>
+        <v>1.15</v>
       </c>
       <c r="O45" t="n">
-        <v>0</v>
+        <v>11.7</v>
       </c>
       <c r="P45" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="R45" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="S45" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="T45" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="U45" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="V45" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W45" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X45" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.63</v>
+        <v>1.38</v>
       </c>
       <c r="Z45" t